--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,264 +479,990 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>177.28</v>
+        <v>285.2</v>
       </c>
       <c r="C2" t="n">
-        <v>177.9</v>
+        <v>289.7</v>
       </c>
       <c r="D2" t="n">
-        <v>176.04</v>
+        <v>283.9</v>
       </c>
       <c r="E2" t="n">
-        <v>176.72</v>
+        <v>286.35</v>
       </c>
       <c r="F2" t="n">
-        <v>9835632</v>
+        <v>19958107</v>
       </c>
       <c r="G2" t="n">
-        <v>24014261</v>
+        <v>47583835</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5904253726566893</v>
+        <v>-0.5805695988984494</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>ETERNAL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>377.45</v>
+        <v>2033.9</v>
       </c>
       <c r="C3" t="n">
-        <v>378.4</v>
+        <v>2050.3</v>
       </c>
       <c r="D3" t="n">
-        <v>372.95</v>
+        <v>2023.8</v>
       </c>
       <c r="E3" t="n">
-        <v>374.3</v>
+        <v>2042</v>
       </c>
       <c r="F3" t="n">
-        <v>2696607</v>
+        <v>580680</v>
       </c>
       <c r="G3" t="n">
-        <v>6352805</v>
+        <v>1240712</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5755249846327725</v>
+        <v>-0.5319784123954633</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>SBILIFE</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ASTRAL</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1589</v>
+        <v>1404</v>
       </c>
       <c r="C4" t="n">
-        <v>1604.6</v>
+        <v>1414</v>
       </c>
       <c r="D4" t="n">
-        <v>1559.5</v>
+        <v>1400.5</v>
       </c>
       <c r="E4" t="n">
-        <v>1601</v>
+        <v>1413</v>
       </c>
       <c r="F4" t="n">
-        <v>585825</v>
+        <v>5000042</v>
       </c>
       <c r="G4" t="n">
-        <v>1241019</v>
+        <v>12228083</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.527948403690838</v>
+        <v>-0.5911017287010564</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ASTRAL</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HINDPETRO</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>452.35</v>
+        <v>12897</v>
       </c>
       <c r="C5" t="n">
-        <v>455.25</v>
+        <v>12997</v>
       </c>
       <c r="D5" t="n">
-        <v>448.75</v>
+        <v>12861</v>
       </c>
       <c r="E5" t="n">
-        <v>451</v>
+        <v>12949</v>
       </c>
       <c r="F5" t="n">
-        <v>1912866</v>
+        <v>81768</v>
       </c>
       <c r="G5" t="n">
-        <v>3949831</v>
+        <v>178236</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.515709406301181</v>
+        <v>-0.5412374604457012</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>HINDPETRO</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SRF</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2815</v>
+        <v>625.35</v>
       </c>
       <c r="C6" t="n">
-        <v>2841</v>
+        <v>645.3</v>
       </c>
       <c r="D6" t="n">
-        <v>2765.6</v>
+        <v>622</v>
       </c>
       <c r="E6" t="n">
-        <v>2833</v>
+        <v>643.5</v>
       </c>
       <c r="F6" t="n">
-        <v>196550</v>
+        <v>2231253</v>
       </c>
       <c r="G6" t="n">
-        <v>395601</v>
+        <v>4838136</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5031610132431414</v>
+        <v>-0.5388197024639241</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>SRF</t>
+          <t>DLF</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FORTIS</t>
+          <t>HAVELLS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>928.15</v>
+        <v>1404</v>
       </c>
       <c r="C7" t="n">
-        <v>930.9</v>
+        <v>1428.5</v>
       </c>
       <c r="D7" t="n">
-        <v>914.3</v>
+        <v>1396.2</v>
       </c>
       <c r="E7" t="n">
-        <v>919</v>
+        <v>1417.3</v>
       </c>
       <c r="F7" t="n">
-        <v>1221319</v>
+        <v>369629</v>
       </c>
       <c r="G7" t="n">
-        <v>2457834</v>
+        <v>774193</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5030913397731499</v>
+        <v>-0.5225622034815608</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>FORTIS</t>
+          <t>HAVELLS</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SUPREMEIND</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3827.9</v>
+        <v>669</v>
       </c>
       <c r="C8" t="n">
-        <v>3831.7</v>
+        <v>681.45</v>
       </c>
       <c r="D8" t="n">
-        <v>3745.3</v>
+        <v>665.25</v>
       </c>
       <c r="E8" t="n">
-        <v>3760</v>
+        <v>679.8</v>
       </c>
       <c r="F8" t="n">
-        <v>82044</v>
+        <v>6387272</v>
       </c>
       <c r="G8" t="n">
-        <v>193500</v>
+        <v>15868021</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.576</v>
+        <v>-0.5974751987031023</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>SUPREMEIND</t>
+          <t>VEDL</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>SHREECEM</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>25940</v>
+      </c>
+      <c r="C9" t="n">
+        <v>26375</v>
+      </c>
+      <c r="D9" t="n">
+        <v>25915</v>
+      </c>
+      <c r="E9" t="n">
+        <v>26250</v>
+      </c>
+      <c r="F9" t="n">
+        <v>11713</v>
+      </c>
+      <c r="G9" t="n">
+        <v>27809</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.5788054227048797</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>SHREECEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1470</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1494</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1465.2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1484.8</v>
+      </c>
+      <c r="F10" t="n">
+        <v>217908</v>
+      </c>
+      <c r="G10" t="n">
+        <v>474002</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.5402804207577183</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>585.95</v>
+      </c>
+      <c r="C11" t="n">
+        <v>596.3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>582.6</v>
+      </c>
+      <c r="E11" t="n">
+        <v>594.5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4181298</v>
+      </c>
+      <c r="G11" t="n">
+        <v>9424678</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.5563457977025846</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>270.95</v>
+      </c>
+      <c r="C12" t="n">
+        <v>277.39</v>
+      </c>
+      <c r="D12" t="n">
+        <v>269.24</v>
+      </c>
+      <c r="E12" t="n">
+        <v>275.06</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3543432</v>
+      </c>
+      <c r="G12" t="n">
+        <v>8182107</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.5669291540675281</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MFSL</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1815.9</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1857.4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1815.9</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1846.1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>693364</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1588459</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.5634989634608133</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MFSL</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NMDC</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>79.31999999999999</v>
+      </c>
+      <c r="C14" t="n">
+        <v>80.64</v>
+      </c>
+      <c r="D14" t="n">
+        <v>78.45</v>
+      </c>
+      <c r="E14" t="n">
+        <v>80.27</v>
+      </c>
+      <c r="F14" t="n">
+        <v>15298184</v>
+      </c>
+      <c r="G14" t="n">
+        <v>31361483</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.5121983230193546</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>NMDC</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>288.3</v>
+      </c>
+      <c r="C15" t="n">
+        <v>295.25</v>
+      </c>
+      <c r="D15" t="n">
+        <v>287.35</v>
+      </c>
+      <c r="E15" t="n">
+        <v>293</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1110180</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2767142</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.5987990497054362</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1544.8</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1568.4</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1536.9</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1560.6</v>
+      </c>
+      <c r="F16" t="n">
+        <v>217779</v>
+      </c>
+      <c r="G16" t="n">
+        <v>494872</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.5599286280088589</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>HUDCO</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>201.5</v>
-      </c>
-      <c r="C9" t="n">
-        <v>201.5</v>
-      </c>
-      <c r="D9" t="n">
-        <v>193.78</v>
-      </c>
-      <c r="E9" t="n">
-        <v>195.4</v>
-      </c>
-      <c r="F9" t="n">
+      <c r="B17" t="n">
+        <v>195</v>
+      </c>
+      <c r="C17" t="n">
+        <v>197.34</v>
+      </c>
+      <c r="D17" t="n">
+        <v>193.05</v>
+      </c>
+      <c r="E17" t="n">
+        <v>196.86</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4351756</v>
+      </c>
+      <c r="G17" t="n">
         <v>10052817</v>
       </c>
-      <c r="G9" t="n">
-        <v>22244997</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-0.5480863854465793</v>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="H17" t="n">
+        <v>-0.5671107909355159</v>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t>HUDCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>204.95</v>
+      </c>
+      <c r="C18" t="n">
+        <v>206.89</v>
+      </c>
+      <c r="D18" t="n">
+        <v>203</v>
+      </c>
+      <c r="E18" t="n">
+        <v>205.5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>11066053</v>
+      </c>
+      <c r="G18" t="n">
+        <v>26832686</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.5875905602592301</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>HINDPETRO</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>448</v>
+      </c>
+      <c r="C19" t="n">
+        <v>452.6</v>
+      </c>
+      <c r="D19" t="n">
+        <v>445</v>
+      </c>
+      <c r="E19" t="n">
+        <v>451.9</v>
+      </c>
+      <c r="F19" t="n">
+        <v>879388</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1912866</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.5402772593584705</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>HINDPETRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>COLPAL</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2120.6</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2128.3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2100.7</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2117</v>
+      </c>
+      <c r="F20" t="n">
+        <v>154505</v>
+      </c>
+      <c r="G20" t="n">
+        <v>374088</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-0.5869822073950515</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>COLPAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TATAELXSI</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>4824</v>
+      </c>
+      <c r="C21" t="n">
+        <v>4845</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4750</v>
+      </c>
+      <c r="E21" t="n">
+        <v>4811</v>
+      </c>
+      <c r="F21" t="n">
+        <v>215518</v>
+      </c>
+      <c r="G21" t="n">
+        <v>441804</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.5121863993988285</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>TATAELXSI</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>158</v>
+      </c>
+      <c r="C22" t="n">
+        <v>160.14</v>
+      </c>
+      <c r="D22" t="n">
+        <v>157.25</v>
+      </c>
+      <c r="E22" t="n">
+        <v>158.8</v>
+      </c>
+      <c r="F22" t="n">
+        <v>8429730</v>
+      </c>
+      <c r="G22" t="n">
+        <v>19899685</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-0.5763887719830741</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TIINDIA</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2490</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2524</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2479</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2491</v>
+      </c>
+      <c r="F23" t="n">
+        <v>138570</v>
+      </c>
+      <c r="G23" t="n">
+        <v>315365</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.5606043790528435</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>TIINDIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1120.5</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1126.9</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1101.8</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1122</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2605903</v>
+      </c>
+      <c r="G24" t="n">
+        <v>6319748</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.5876571344300437</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ICICIPRULI</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>643</v>
+      </c>
+      <c r="C25" t="n">
+        <v>643.75</v>
+      </c>
+      <c r="D25" t="n">
+        <v>633.7</v>
+      </c>
+      <c r="E25" t="n">
+        <v>639.75</v>
+      </c>
+      <c r="F25" t="n">
+        <v>295460</v>
+      </c>
+      <c r="G25" t="n">
+        <v>711887</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.5849622201276327</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ICICIPRULI</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PIIND</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>3089.7</v>
+      </c>
+      <c r="C26" t="n">
+        <v>3167.4</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3021.7</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3050</v>
+      </c>
+      <c r="F26" t="n">
+        <v>600277</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1327261</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0.5477325107872528</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>PIIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>PNBHOUSING</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>832</v>
+      </c>
+      <c r="C27" t="n">
+        <v>853.8</v>
+      </c>
+      <c r="D27" t="n">
+        <v>830.15</v>
+      </c>
+      <c r="E27" t="n">
+        <v>845</v>
+      </c>
+      <c r="F27" t="n">
+        <v>503367</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1057628</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-0.5240604446932192</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>PNBHOUSING</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AMBER</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>7760</v>
+      </c>
+      <c r="C28" t="n">
+        <v>7812.5</v>
+      </c>
+      <c r="D28" t="n">
+        <v>7687.5</v>
+      </c>
+      <c r="E28" t="n">
+        <v>7757</v>
+      </c>
+      <c r="F28" t="n">
+        <v>163902</v>
+      </c>
+      <c r="G28" t="n">
+        <v>351861</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-0.5341853743381619</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>AMBER</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>312.35</v>
+      </c>
+      <c r="C29" t="n">
+        <v>315.3</v>
+      </c>
+      <c r="D29" t="n">
+        <v>310.25</v>
+      </c>
+      <c r="E29" t="n">
+        <v>313.6</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1778001</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3835217</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-0.536401460464949</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>IIFL</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>505.1</v>
+      </c>
+      <c r="C30" t="n">
+        <v>512.95</v>
+      </c>
+      <c r="D30" t="n">
+        <v>496.15</v>
+      </c>
+      <c r="E30" t="n">
+        <v>507.55</v>
+      </c>
+      <c r="F30" t="n">
+        <v>965895</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2280434</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-0.5764424666532774</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>IIFL</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>CYIENT</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1002.1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>985</v>
+      </c>
+      <c r="E31" t="n">
+        <v>992</v>
+      </c>
+      <c r="F31" t="n">
+        <v>167975</v>
+      </c>
+      <c r="G31" t="n">
+        <v>370990</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-0.5472249925874013</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>CYIENT</t>
         </is>
       </c>
     </row>
@@ -751,7 +1477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -804,528 +1530,297 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>265</v>
+        <v>1128.5</v>
       </c>
       <c r="C2" t="n">
-        <v>267.25</v>
+        <v>1141.8</v>
       </c>
       <c r="D2" t="n">
-        <v>262.85</v>
+        <v>1117.1</v>
       </c>
       <c r="E2" t="n">
-        <v>263.85</v>
+        <v>1138.8</v>
       </c>
       <c r="F2" t="n">
-        <v>12222314</v>
+        <v>780629</v>
       </c>
       <c r="G2" t="n">
-        <v>8681589</v>
+        <v>525887</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4078429651530383</v>
+        <v>0.4844044443007718</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>913</v>
+        <v>949.5</v>
       </c>
       <c r="C3" t="n">
-        <v>928.2</v>
+        <v>999</v>
       </c>
       <c r="D3" t="n">
-        <v>901</v>
+        <v>936.45</v>
       </c>
       <c r="E3" t="n">
-        <v>903.9</v>
+        <v>991.8</v>
       </c>
       <c r="F3" t="n">
-        <v>50188359</v>
+        <v>4171950</v>
       </c>
       <c r="G3" t="n">
-        <v>33872203</v>
+        <v>2943844</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4816975146257833</v>
+        <v>0.4171776765344903</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>348.1</v>
+        <v>5980</v>
       </c>
       <c r="C4" t="n">
-        <v>348.5</v>
+        <v>6134</v>
       </c>
       <c r="D4" t="n">
-        <v>339.8</v>
+        <v>5964.5</v>
       </c>
       <c r="E4" t="n">
-        <v>346</v>
+        <v>6100</v>
       </c>
       <c r="F4" t="n">
-        <v>8552636</v>
+        <v>255274</v>
       </c>
       <c r="G4" t="n">
-        <v>5630751</v>
+        <v>159821</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5189156828280987</v>
+        <v>0.5972494227917483</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>LTF</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>479</v>
+        <v>284</v>
       </c>
       <c r="C5" t="n">
-        <v>479</v>
+        <v>295.45</v>
       </c>
       <c r="D5" t="n">
-        <v>468.85</v>
+        <v>281.2</v>
       </c>
       <c r="E5" t="n">
-        <v>471.4</v>
+        <v>295.1</v>
       </c>
       <c r="F5" t="n">
-        <v>1171877</v>
+        <v>6790971</v>
       </c>
       <c r="G5" t="n">
-        <v>831728</v>
+        <v>4322331</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4089666333224323</v>
+        <v>0.5711362688327202</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>LTF</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BOSCHLTD</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36415</v>
+        <v>869</v>
       </c>
       <c r="C6" t="n">
-        <v>36420</v>
+        <v>892.4</v>
       </c>
       <c r="D6" t="n">
-        <v>35600</v>
+        <v>863.1</v>
       </c>
       <c r="E6" t="n">
-        <v>35700</v>
+        <v>890</v>
       </c>
       <c r="F6" t="n">
-        <v>13848</v>
+        <v>1290153</v>
       </c>
       <c r="G6" t="n">
-        <v>9373</v>
+        <v>877486</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4774351861730503</v>
+        <v>0.4702832865709539</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>BOSCHLTD</t>
+          <t>INDIANB</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SOLARINDS</t>
+          <t>IRB</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13250</v>
+        <v>44</v>
       </c>
       <c r="C7" t="n">
-        <v>13300</v>
+        <v>44</v>
       </c>
       <c r="D7" t="n">
-        <v>12935</v>
+        <v>41.88</v>
       </c>
       <c r="E7" t="n">
-        <v>12965</v>
+        <v>42.21</v>
       </c>
       <c r="F7" t="n">
-        <v>90669</v>
+        <v>11141730</v>
       </c>
       <c r="G7" t="n">
-        <v>60892</v>
+        <v>7597646</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4890133350850687</v>
+        <v>0.466471325460544</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SOLARINDS</t>
+          <t>IRB</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>641.6</v>
+        <v>2240</v>
       </c>
       <c r="C8" t="n">
-        <v>641.6</v>
+        <v>2358.2</v>
       </c>
       <c r="D8" t="n">
-        <v>623.55</v>
+        <v>2168</v>
       </c>
       <c r="E8" t="n">
-        <v>626.95</v>
+        <v>2350</v>
       </c>
       <c r="F8" t="n">
-        <v>4838136</v>
+        <v>5065061</v>
       </c>
       <c r="G8" t="n">
-        <v>3109096</v>
+        <v>3459271</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5561230659973189</v>
+        <v>0.4641989598386481</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>MCX</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>GRANULES</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1149.1</v>
+        <v>560.6</v>
       </c>
       <c r="C9" t="n">
-        <v>1157.4</v>
+        <v>567.3</v>
       </c>
       <c r="D9" t="n">
-        <v>1126.8</v>
+        <v>556</v>
       </c>
       <c r="E9" t="n">
-        <v>1157</v>
+        <v>564</v>
       </c>
       <c r="F9" t="n">
-        <v>1682470</v>
+        <v>522642</v>
       </c>
       <c r="G9" t="n">
-        <v>1090045</v>
+        <v>366379</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5434867367860959</v>
+        <v>0.4265064318642717</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>GRANULES</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>MANAPPURAM</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4425</v>
+        <v>303.25</v>
       </c>
       <c r="C10" t="n">
-        <v>4491.9</v>
+        <v>306</v>
       </c>
       <c r="D10" t="n">
-        <v>4395.2</v>
+        <v>295.35</v>
       </c>
       <c r="E10" t="n">
-        <v>4412</v>
+        <v>302.8</v>
       </c>
       <c r="F10" t="n">
-        <v>512643</v>
+        <v>7805766</v>
       </c>
       <c r="G10" t="n">
-        <v>360796</v>
+        <v>4916102</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4208666393197264</v>
+        <v>0.5877957780371522</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>MPHASIS</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2387.6</v>
-      </c>
-      <c r="C11" t="n">
-        <v>2501.2</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2355.2</v>
-      </c>
-      <c r="E11" t="n">
-        <v>2452.5</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1725163</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1136104</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.5184903846830924</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>MPHASIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>LUPIN</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2210</v>
-      </c>
-      <c r="C12" t="n">
-        <v>2219.2</v>
-      </c>
-      <c r="D12" t="n">
-        <v>2160</v>
-      </c>
-      <c r="E12" t="n">
-        <v>2194</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1126141</v>
-      </c>
-      <c r="G12" t="n">
-        <v>804229</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.4002740512963348</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>LUPIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>DIXON</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>11500</v>
-      </c>
-      <c r="C13" t="n">
-        <v>11548</v>
-      </c>
-      <c r="D13" t="n">
-        <v>11250</v>
-      </c>
-      <c r="E13" t="n">
-        <v>11398</v>
-      </c>
-      <c r="F13" t="n">
-        <v>446533</v>
-      </c>
-      <c r="G13" t="n">
-        <v>288312</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.5487839562695969</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>DIXON</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>BANKINDIA</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>164.1</v>
-      </c>
-      <c r="C14" t="n">
-        <v>164.45</v>
-      </c>
-      <c r="D14" t="n">
-        <v>161.26</v>
-      </c>
-      <c r="E14" t="n">
-        <v>161.69</v>
-      </c>
-      <c r="F14" t="n">
-        <v>8120034</v>
-      </c>
-      <c r="G14" t="n">
-        <v>5243794</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.5485036216144265</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>BANKINDIA</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>BSE</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>3100</v>
-      </c>
-      <c r="C15" t="n">
-        <v>3127</v>
-      </c>
-      <c r="D15" t="n">
-        <v>3017.9</v>
-      </c>
-      <c r="E15" t="n">
-        <v>3023.9</v>
-      </c>
-      <c r="F15" t="n">
-        <v>3885000</v>
-      </c>
-      <c r="G15" t="n">
-        <v>2525871</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.5380832987907933</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>BSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>CROMPTON</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>264</v>
-      </c>
-      <c r="C16" t="n">
-        <v>269.85</v>
-      </c>
-      <c r="D16" t="n">
-        <v>255.9</v>
-      </c>
-      <c r="E16" t="n">
-        <v>266.8</v>
-      </c>
-      <c r="F16" t="n">
-        <v>4504154</v>
-      </c>
-      <c r="G16" t="n">
-        <v>3035533</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.4838099272845988</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>CROMPTON</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>CDSL</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1350</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1359</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1321.1</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1335.6</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1663043</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1133736</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.4668697121728515</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>CDSL</t>
+          <t>MANAPPURAM</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,990 +479,528 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>285.2</v>
+        <v>7981</v>
       </c>
       <c r="C2" t="n">
-        <v>289.7</v>
+        <v>8051.5</v>
       </c>
       <c r="D2" t="n">
-        <v>283.9</v>
+        <v>7925</v>
       </c>
       <c r="E2" t="n">
-        <v>286.35</v>
+        <v>8022</v>
       </c>
       <c r="F2" t="n">
-        <v>19958107</v>
+        <v>266572</v>
       </c>
       <c r="G2" t="n">
-        <v>47583835</v>
+        <v>589984</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5805695988984494</v>
+        <v>-0.5481707978521452</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2033.9</v>
+        <v>299.3</v>
       </c>
       <c r="C3" t="n">
-        <v>2050.3</v>
+        <v>301.6</v>
       </c>
       <c r="D3" t="n">
-        <v>2023.8</v>
+        <v>297</v>
       </c>
       <c r="E3" t="n">
-        <v>2042</v>
+        <v>300.3</v>
       </c>
       <c r="F3" t="n">
-        <v>580680</v>
+        <v>11190989</v>
       </c>
       <c r="G3" t="n">
-        <v>1240712</v>
+        <v>22196951</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5319784123954633</v>
+        <v>-0.4958321528033287</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>POWERGRID</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1404</v>
+        <v>422.25</v>
       </c>
       <c r="C4" t="n">
-        <v>1414</v>
+        <v>424.6</v>
       </c>
       <c r="D4" t="n">
-        <v>1400.5</v>
+        <v>418.5</v>
       </c>
       <c r="E4" t="n">
-        <v>1413</v>
+        <v>422</v>
       </c>
       <c r="F4" t="n">
-        <v>5000042</v>
+        <v>4564907</v>
       </c>
       <c r="G4" t="n">
-        <v>12228083</v>
+        <v>9719418</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5911017287010564</v>
+        <v>-0.5303312399981152</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>COALINDIA</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12897</v>
+        <v>643</v>
       </c>
       <c r="C5" t="n">
-        <v>12997</v>
+        <v>643.3</v>
       </c>
       <c r="D5" t="n">
-        <v>12861</v>
+        <v>635.7</v>
       </c>
       <c r="E5" t="n">
-        <v>12949</v>
+        <v>638.8</v>
       </c>
       <c r="F5" t="n">
-        <v>81768</v>
+        <v>1136224</v>
       </c>
       <c r="G5" t="n">
-        <v>178236</v>
+        <v>2231253</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5412374604457012</v>
+        <v>-0.4907686398628932</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>DLF</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>PIIND</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>625.35</v>
+        <v>3068.1</v>
       </c>
       <c r="C6" t="n">
-        <v>645.3</v>
+        <v>3084</v>
       </c>
       <c r="D6" t="n">
-        <v>622</v>
+        <v>3015</v>
       </c>
       <c r="E6" t="n">
-        <v>643.5</v>
+        <v>3084</v>
       </c>
       <c r="F6" t="n">
-        <v>2231253</v>
+        <v>287746</v>
       </c>
       <c r="G6" t="n">
-        <v>4838136</v>
+        <v>600277</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5388197024639241</v>
+        <v>-0.5206446357265062</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>PIIND</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>IGL</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1404</v>
+        <v>172.01</v>
       </c>
       <c r="C7" t="n">
-        <v>1428.5</v>
+        <v>173.4</v>
       </c>
       <c r="D7" t="n">
-        <v>1396.2</v>
+        <v>170.71</v>
       </c>
       <c r="E7" t="n">
-        <v>1417.3</v>
+        <v>172.24</v>
       </c>
       <c r="F7" t="n">
-        <v>369629</v>
+        <v>3228324</v>
       </c>
       <c r="G7" t="n">
-        <v>774193</v>
+        <v>7930421</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5225622034815608</v>
+        <v>-0.5929189635707864</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>IGL</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>IREDA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>669</v>
+        <v>127.07</v>
       </c>
       <c r="C8" t="n">
-        <v>681.45</v>
+        <v>127.59</v>
       </c>
       <c r="D8" t="n">
-        <v>665.25</v>
+        <v>126.25</v>
       </c>
       <c r="E8" t="n">
-        <v>679.8</v>
+        <v>127.25</v>
       </c>
       <c r="F8" t="n">
-        <v>6387272</v>
+        <v>5252696</v>
       </c>
       <c r="G8" t="n">
-        <v>15868021</v>
+        <v>12339521</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5974751987031023</v>
+        <v>-0.5743192948899718</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>IREDA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>ASTRAL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25940</v>
+        <v>1639.8</v>
       </c>
       <c r="C9" t="n">
-        <v>26375</v>
+        <v>1653</v>
       </c>
       <c r="D9" t="n">
-        <v>25915</v>
+        <v>1612.7</v>
       </c>
       <c r="E9" t="n">
-        <v>26250</v>
+        <v>1640</v>
       </c>
       <c r="F9" t="n">
-        <v>11713</v>
+        <v>490265</v>
       </c>
       <c r="G9" t="n">
-        <v>27809</v>
+        <v>1221002</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5788054227048797</v>
+        <v>-0.5984732211740849</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>ASTRAL</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>PRESTIGE</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1470</v>
+        <v>1516.3</v>
       </c>
       <c r="C10" t="n">
-        <v>1494</v>
+        <v>1548.6</v>
       </c>
       <c r="D10" t="n">
-        <v>1465.2</v>
+        <v>1512</v>
       </c>
       <c r="E10" t="n">
-        <v>1484.8</v>
+        <v>1522.7</v>
       </c>
       <c r="F10" t="n">
-        <v>217908</v>
+        <v>298593</v>
       </c>
       <c r="G10" t="n">
-        <v>474002</v>
+        <v>601273</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5402804207577183</v>
+        <v>-0.5033986225890735</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>PRESTIGE</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>GMRAIRPORT</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>585.95</v>
+        <v>99.87</v>
       </c>
       <c r="C11" t="n">
-        <v>596.3</v>
+        <v>102.55</v>
       </c>
       <c r="D11" t="n">
-        <v>582.6</v>
+        <v>99.12</v>
       </c>
       <c r="E11" t="n">
-        <v>594.5</v>
+        <v>99.8</v>
       </c>
       <c r="F11" t="n">
-        <v>4181298</v>
+        <v>25514687</v>
       </c>
       <c r="G11" t="n">
-        <v>9424678</v>
+        <v>50976360</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5563457977025846</v>
+        <v>-0.4994800138730973</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>GMRAIRPORT</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NYKAA</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>270.95</v>
+        <v>11750</v>
       </c>
       <c r="C12" t="n">
-        <v>277.39</v>
+        <v>11818</v>
       </c>
       <c r="D12" t="n">
-        <v>269.24</v>
+        <v>11605</v>
       </c>
       <c r="E12" t="n">
-        <v>275.06</v>
+        <v>11640</v>
       </c>
       <c r="F12" t="n">
-        <v>3543432</v>
+        <v>286065</v>
       </c>
       <c r="G12" t="n">
-        <v>8182107</v>
+        <v>600256</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5669291540675281</v>
+        <v>-0.5234283372427764</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>NYKAA</t>
+          <t>DIXON</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>FORTIS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1815.9</v>
+        <v>921.9</v>
       </c>
       <c r="C13" t="n">
-        <v>1857.4</v>
+        <v>930</v>
       </c>
       <c r="D13" t="n">
-        <v>1815.9</v>
+        <v>902.65</v>
       </c>
       <c r="E13" t="n">
-        <v>1846.1</v>
+        <v>904</v>
       </c>
       <c r="F13" t="n">
-        <v>693364</v>
+        <v>912616</v>
       </c>
       <c r="G13" t="n">
-        <v>1588459</v>
+        <v>2094816</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.5634989634608133</v>
+        <v>-0.5643455081496418</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>FORTIS</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>GRANULES</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>79.31999999999999</v>
+        <v>558</v>
       </c>
       <c r="C14" t="n">
-        <v>80.64</v>
+        <v>571</v>
       </c>
       <c r="D14" t="n">
-        <v>78.45</v>
+        <v>558</v>
       </c>
       <c r="E14" t="n">
-        <v>80.27</v>
+        <v>568.5</v>
       </c>
       <c r="F14" t="n">
-        <v>15298184</v>
+        <v>247457</v>
       </c>
       <c r="G14" t="n">
-        <v>31361483</v>
+        <v>522642</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5121983230193546</v>
+        <v>-0.5265267621048443</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>GRANULES</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>CESC</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>288.3</v>
+        <v>154.47</v>
       </c>
       <c r="C15" t="n">
-        <v>295.25</v>
+        <v>156</v>
       </c>
       <c r="D15" t="n">
-        <v>287.35</v>
+        <v>153.5</v>
       </c>
       <c r="E15" t="n">
-        <v>293</v>
+        <v>155.3</v>
       </c>
       <c r="F15" t="n">
-        <v>1110180</v>
+        <v>595578</v>
       </c>
       <c r="G15" t="n">
-        <v>2767142</v>
+        <v>1268149</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5987990497054362</v>
+        <v>-0.53035644865075</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>CESC</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>PPLPHARMA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1544.8</v>
+        <v>161.99</v>
       </c>
       <c r="C16" t="n">
-        <v>1568.4</v>
+        <v>165.3</v>
       </c>
       <c r="D16" t="n">
-        <v>1536.9</v>
+        <v>161.87</v>
       </c>
       <c r="E16" t="n">
-        <v>1560.6</v>
+        <v>164.5</v>
       </c>
       <c r="F16" t="n">
-        <v>217779</v>
+        <v>1640770</v>
       </c>
       <c r="G16" t="n">
-        <v>494872</v>
+        <v>3946154</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.5599286280088589</v>
+        <v>-0.5842103475941385</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>PPLPHARMA</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HUDCO</t>
+          <t>ANGELONE</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>195</v>
+        <v>2565.1</v>
       </c>
       <c r="C17" t="n">
-        <v>197.34</v>
+        <v>2609.9</v>
       </c>
       <c r="D17" t="n">
-        <v>193.05</v>
+        <v>2541.4</v>
       </c>
       <c r="E17" t="n">
-        <v>196.86</v>
+        <v>2575</v>
       </c>
       <c r="F17" t="n">
-        <v>4351756</v>
+        <v>882255</v>
       </c>
       <c r="G17" t="n">
-        <v>10052817</v>
+        <v>1996002</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5671107909355159</v>
+        <v>-0.5579889198507817</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>HUDCO</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>ASHOKLEY</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>204.95</v>
-      </c>
-      <c r="C18" t="n">
-        <v>206.89</v>
-      </c>
-      <c r="D18" t="n">
-        <v>203</v>
-      </c>
-      <c r="E18" t="n">
-        <v>205.5</v>
-      </c>
-      <c r="F18" t="n">
-        <v>11066053</v>
-      </c>
-      <c r="G18" t="n">
-        <v>26832686</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-0.5875905602592301</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>ASHOKLEY</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>HINDPETRO</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>448</v>
-      </c>
-      <c r="C19" t="n">
-        <v>452.6</v>
-      </c>
-      <c r="D19" t="n">
-        <v>445</v>
-      </c>
-      <c r="E19" t="n">
-        <v>451.9</v>
-      </c>
-      <c r="F19" t="n">
-        <v>879388</v>
-      </c>
-      <c r="G19" t="n">
-        <v>1912866</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-0.5402772593584705</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>HINDPETRO</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>COLPAL</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>2120.6</v>
-      </c>
-      <c r="C20" t="n">
-        <v>2128.3</v>
-      </c>
-      <c r="D20" t="n">
-        <v>2100.7</v>
-      </c>
-      <c r="E20" t="n">
-        <v>2117</v>
-      </c>
-      <c r="F20" t="n">
-        <v>154505</v>
-      </c>
-      <c r="G20" t="n">
-        <v>374088</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-0.5869822073950515</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>COLPAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>TATAELXSI</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>4824</v>
-      </c>
-      <c r="C21" t="n">
-        <v>4845</v>
-      </c>
-      <c r="D21" t="n">
-        <v>4750</v>
-      </c>
-      <c r="E21" t="n">
-        <v>4811</v>
-      </c>
-      <c r="F21" t="n">
-        <v>215518</v>
-      </c>
-      <c r="G21" t="n">
-        <v>441804</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-0.5121863993988285</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>TATAELXSI</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>SAIL</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>158</v>
-      </c>
-      <c r="C22" t="n">
-        <v>160.14</v>
-      </c>
-      <c r="D22" t="n">
-        <v>157.25</v>
-      </c>
-      <c r="E22" t="n">
-        <v>158.8</v>
-      </c>
-      <c r="F22" t="n">
-        <v>8429730</v>
-      </c>
-      <c r="G22" t="n">
-        <v>19899685</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-0.5763887719830741</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>SAIL</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>TIINDIA</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>2490</v>
-      </c>
-      <c r="C23" t="n">
-        <v>2524</v>
-      </c>
-      <c r="D23" t="n">
-        <v>2479</v>
-      </c>
-      <c r="E23" t="n">
-        <v>2491</v>
-      </c>
-      <c r="F23" t="n">
-        <v>138570</v>
-      </c>
-      <c r="G23" t="n">
-        <v>315365</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-0.5606043790528435</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>TIINDIA</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>PAYTM</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>1120.5</v>
-      </c>
-      <c r="C24" t="n">
-        <v>1126.9</v>
-      </c>
-      <c r="D24" t="n">
-        <v>1101.8</v>
-      </c>
-      <c r="E24" t="n">
-        <v>1122</v>
-      </c>
-      <c r="F24" t="n">
-        <v>2605903</v>
-      </c>
-      <c r="G24" t="n">
-        <v>6319748</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-0.5876571344300437</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>PAYTM</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>ICICIPRULI</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>643</v>
-      </c>
-      <c r="C25" t="n">
-        <v>643.75</v>
-      </c>
-      <c r="D25" t="n">
-        <v>633.7</v>
-      </c>
-      <c r="E25" t="n">
-        <v>639.75</v>
-      </c>
-      <c r="F25" t="n">
-        <v>295460</v>
-      </c>
-      <c r="G25" t="n">
-        <v>711887</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-0.5849622201276327</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>ICICIPRULI</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>PIIND</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>3089.7</v>
-      </c>
-      <c r="C26" t="n">
-        <v>3167.4</v>
-      </c>
-      <c r="D26" t="n">
-        <v>3021.7</v>
-      </c>
-      <c r="E26" t="n">
-        <v>3050</v>
-      </c>
-      <c r="F26" t="n">
-        <v>600277</v>
-      </c>
-      <c r="G26" t="n">
-        <v>1327261</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-0.5477325107872528</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>PIIND</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>PNBHOUSING</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>832</v>
-      </c>
-      <c r="C27" t="n">
-        <v>853.8</v>
-      </c>
-      <c r="D27" t="n">
-        <v>830.15</v>
-      </c>
-      <c r="E27" t="n">
-        <v>845</v>
-      </c>
-      <c r="F27" t="n">
-        <v>503367</v>
-      </c>
-      <c r="G27" t="n">
-        <v>1057628</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-0.5240604446932192</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>PNBHOUSING</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>AMBER</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>7760</v>
-      </c>
-      <c r="C28" t="n">
-        <v>7812.5</v>
-      </c>
-      <c r="D28" t="n">
-        <v>7687.5</v>
-      </c>
-      <c r="E28" t="n">
-        <v>7757</v>
-      </c>
-      <c r="F28" t="n">
-        <v>163902</v>
-      </c>
-      <c r="G28" t="n">
-        <v>351861</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-0.5341853743381619</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>AMBER</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>RBLBANK</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>312.35</v>
-      </c>
-      <c r="C29" t="n">
-        <v>315.3</v>
-      </c>
-      <c r="D29" t="n">
-        <v>310.25</v>
-      </c>
-      <c r="E29" t="n">
-        <v>313.6</v>
-      </c>
-      <c r="F29" t="n">
-        <v>1778001</v>
-      </c>
-      <c r="G29" t="n">
-        <v>3835217</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-0.536401460464949</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>RBLBANK</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>IIFL</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>505.1</v>
-      </c>
-      <c r="C30" t="n">
-        <v>512.95</v>
-      </c>
-      <c r="D30" t="n">
-        <v>496.15</v>
-      </c>
-      <c r="E30" t="n">
-        <v>507.55</v>
-      </c>
-      <c r="F30" t="n">
-        <v>965895</v>
-      </c>
-      <c r="G30" t="n">
-        <v>2280434</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-0.5764424666532774</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>IIFL</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>CYIENT</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C31" t="n">
-        <v>1002.1</v>
-      </c>
-      <c r="D31" t="n">
-        <v>985</v>
-      </c>
-      <c r="E31" t="n">
-        <v>992</v>
-      </c>
-      <c r="F31" t="n">
-        <v>167975</v>
-      </c>
-      <c r="G31" t="n">
-        <v>370990</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-0.5472249925874013</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>CYIENT</t>
+          <t>ANGELONE</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1530,297 +1068,528 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1128.5</v>
+        <v>2399.5</v>
       </c>
       <c r="C2" t="n">
-        <v>1141.8</v>
+        <v>2452.4</v>
       </c>
       <c r="D2" t="n">
-        <v>1117.1</v>
+        <v>2399.5</v>
       </c>
       <c r="E2" t="n">
-        <v>1138.8</v>
+        <v>2439</v>
       </c>
       <c r="F2" t="n">
-        <v>780629</v>
+        <v>1004356</v>
       </c>
       <c r="G2" t="n">
-        <v>525887</v>
+        <v>683108</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4844044443007718</v>
+        <v>0.4702741001422908</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>949.5</v>
+        <v>1266</v>
       </c>
       <c r="C3" t="n">
-        <v>999</v>
+        <v>1286.8</v>
       </c>
       <c r="D3" t="n">
-        <v>936.45</v>
+        <v>1258.2</v>
       </c>
       <c r="E3" t="n">
-        <v>991.8</v>
+        <v>1281.3</v>
       </c>
       <c r="F3" t="n">
-        <v>4171950</v>
+        <v>687326</v>
       </c>
       <c r="G3" t="n">
-        <v>2943844</v>
+        <v>469592</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4171776765344903</v>
+        <v>0.4636663316240481</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>DRREDDY</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5980</v>
+        <v>2716</v>
       </c>
       <c r="C4" t="n">
-        <v>6134</v>
+        <v>2760</v>
       </c>
       <c r="D4" t="n">
-        <v>5964.5</v>
+        <v>2695.2</v>
       </c>
       <c r="E4" t="n">
-        <v>6100</v>
+        <v>2719.8</v>
       </c>
       <c r="F4" t="n">
-        <v>255274</v>
+        <v>4209118</v>
       </c>
       <c r="G4" t="n">
-        <v>159821</v>
+        <v>2918730</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5972494227917483</v>
+        <v>0.4421059844521418</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>TCS</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LTF</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>284</v>
+        <v>1002</v>
       </c>
       <c r="C5" t="n">
-        <v>295.45</v>
+        <v>1035</v>
       </c>
       <c r="D5" t="n">
-        <v>281.2</v>
+        <v>996</v>
       </c>
       <c r="E5" t="n">
-        <v>295.1</v>
+        <v>1030.45</v>
       </c>
       <c r="F5" t="n">
-        <v>6790971</v>
+        <v>1460922</v>
       </c>
       <c r="G5" t="n">
-        <v>4322331</v>
+        <v>976113</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5711362688327202</v>
+        <v>0.4966730286350043</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>LTF</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>LTIM</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>869</v>
+        <v>5097</v>
       </c>
       <c r="C6" t="n">
-        <v>892.4</v>
+        <v>5234.5</v>
       </c>
       <c r="D6" t="n">
-        <v>863.1</v>
+        <v>5051</v>
       </c>
       <c r="E6" t="n">
-        <v>890</v>
+        <v>5156</v>
       </c>
       <c r="F6" t="n">
-        <v>1290153</v>
+        <v>316641</v>
       </c>
       <c r="G6" t="n">
-        <v>877486</v>
+        <v>216966</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4702832865709539</v>
+        <v>0.4594037775503996</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>LTIM</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IRB</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>44</v>
+        <v>1479</v>
       </c>
       <c r="C7" t="n">
-        <v>44</v>
+        <v>1497.8</v>
       </c>
       <c r="D7" t="n">
-        <v>41.88</v>
+        <v>1477.4</v>
       </c>
       <c r="E7" t="n">
-        <v>42.21</v>
+        <v>1495</v>
       </c>
       <c r="F7" t="n">
-        <v>11141730</v>
+        <v>344682</v>
       </c>
       <c r="G7" t="n">
-        <v>7597646</v>
+        <v>217908</v>
       </c>
       <c r="H7" t="n">
-        <v>0.466471325460544</v>
+        <v>0.5817776309268131</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>IRB</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>BPCL</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2240</v>
+        <v>374.35</v>
       </c>
       <c r="C8" t="n">
-        <v>2358.2</v>
+        <v>375.8</v>
       </c>
       <c r="D8" t="n">
-        <v>2168</v>
+        <v>366.55</v>
       </c>
       <c r="E8" t="n">
-        <v>2350</v>
+        <v>375</v>
       </c>
       <c r="F8" t="n">
-        <v>5065061</v>
+        <v>2646518</v>
       </c>
       <c r="G8" t="n">
-        <v>3459271</v>
+        <v>1709180</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4641989598386481</v>
+        <v>0.5484138592775483</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>BPCL</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GRANULES</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>560.6</v>
+        <v>132.31</v>
       </c>
       <c r="C9" t="n">
-        <v>567.3</v>
+        <v>133.97</v>
       </c>
       <c r="D9" t="n">
-        <v>556</v>
+        <v>131.22</v>
       </c>
       <c r="E9" t="n">
-        <v>564</v>
+        <v>132.5</v>
       </c>
       <c r="F9" t="n">
-        <v>522642</v>
+        <v>17075133</v>
       </c>
       <c r="G9" t="n">
-        <v>366379</v>
+        <v>10892515</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4265064318642717</v>
+        <v>0.5676024315780148</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>GRANULES</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MANAPPURAM</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>303.25</v>
+        <v>679.8</v>
       </c>
       <c r="C10" t="n">
-        <v>306</v>
+        <v>680</v>
       </c>
       <c r="D10" t="n">
-        <v>295.35</v>
+        <v>660.3</v>
       </c>
       <c r="E10" t="n">
-        <v>302.8</v>
+        <v>667.3</v>
       </c>
       <c r="F10" t="n">
-        <v>7805766</v>
+        <v>10070194</v>
       </c>
       <c r="G10" t="n">
-        <v>4916102</v>
+        <v>6387272</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5877957780371522</v>
+        <v>0.5766032822776296</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MANAPPURAM</t>
+          <t>VEDL</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>590</v>
+      </c>
+      <c r="C11" t="n">
+        <v>590</v>
+      </c>
+      <c r="D11" t="n">
+        <v>575</v>
+      </c>
+      <c r="E11" t="n">
+        <v>581.6</v>
+      </c>
+      <c r="F11" t="n">
+        <v>6472316</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4181298</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.5479202869539554</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>888</v>
+      </c>
+      <c r="C12" t="n">
+        <v>921.9</v>
+      </c>
+      <c r="D12" t="n">
+        <v>881</v>
+      </c>
+      <c r="E12" t="n">
+        <v>920</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1893818</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1290153</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.4679018690031337</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SUPREMEIND</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>3900</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3927.9</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3871.5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3920</v>
+      </c>
+      <c r="F13" t="n">
+        <v>256640</v>
+      </c>
+      <c r="G13" t="n">
+        <v>171503</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.4964169722978607</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>SUPREMEIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PATANJALI</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>524.9</v>
+      </c>
+      <c r="C14" t="n">
+        <v>535.95</v>
+      </c>
+      <c r="D14" t="n">
+        <v>521.85</v>
+      </c>
+      <c r="E14" t="n">
+        <v>528.5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1777456</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1260588</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.4100213551136454</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>PATANJALI</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>DABUR</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>511.1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>519.05</v>
+      </c>
+      <c r="D15" t="n">
+        <v>511.1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>516</v>
+      </c>
+      <c r="F15" t="n">
+        <v>963143</v>
+      </c>
+      <c r="G15" t="n">
+        <v>667469</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.4429778761260822</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>DABUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>VOLTAS</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1540</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1540</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1513.2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1533</v>
+      </c>
+      <c r="F16" t="n">
+        <v>444923</v>
+      </c>
+      <c r="G16" t="n">
+        <v>300771</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.4792749300963191</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>VOLTAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>289</v>
+      </c>
+      <c r="C17" t="n">
+        <v>291.05</v>
+      </c>
+      <c r="D17" t="n">
+        <v>282.6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>288.5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>7052510</v>
+      </c>
+      <c r="G17" t="n">
+        <v>4743148</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.4868838164021025</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,528 +479,462 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7981</v>
+        <v>1076.15</v>
       </c>
       <c r="C2" t="n">
-        <v>8051.5</v>
+        <v>1087.9</v>
       </c>
       <c r="D2" t="n">
-        <v>7925</v>
+        <v>1071.65</v>
       </c>
       <c r="E2" t="n">
-        <v>8022</v>
+        <v>1085</v>
       </c>
       <c r="F2" t="n">
-        <v>266572</v>
+        <v>680966</v>
       </c>
       <c r="G2" t="n">
-        <v>589984</v>
+        <v>1701396</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5481707978521452</v>
+        <v>-0.5997604320217045</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>299.3</v>
+        <v>2020.1</v>
       </c>
       <c r="C3" t="n">
-        <v>301.6</v>
+        <v>2028.6</v>
       </c>
       <c r="D3" t="n">
-        <v>297</v>
+        <v>2015</v>
       </c>
       <c r="E3" t="n">
-        <v>300.3</v>
+        <v>2021.6</v>
       </c>
       <c r="F3" t="n">
-        <v>11190989</v>
+        <v>2182669</v>
       </c>
       <c r="G3" t="n">
-        <v>22196951</v>
+        <v>4471158</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4958321528033287</v>
+        <v>-0.5118336234147842</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>422.25</v>
+        <v>1410.1</v>
       </c>
       <c r="C4" t="n">
-        <v>424.6</v>
+        <v>1412.3</v>
       </c>
       <c r="D4" t="n">
-        <v>418.5</v>
+        <v>1398.9</v>
       </c>
       <c r="E4" t="n">
-        <v>422</v>
+        <v>1406</v>
       </c>
       <c r="F4" t="n">
-        <v>4564907</v>
+        <v>4758071</v>
       </c>
       <c r="G4" t="n">
-        <v>9719418</v>
+        <v>11756187</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5303312399981152</v>
+        <v>-0.5952708986340555</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>643</v>
+        <v>1565</v>
       </c>
       <c r="C5" t="n">
-        <v>643.3</v>
+        <v>1565</v>
       </c>
       <c r="D5" t="n">
-        <v>635.7</v>
+        <v>1540</v>
       </c>
       <c r="E5" t="n">
-        <v>638.8</v>
+        <v>1550</v>
       </c>
       <c r="F5" t="n">
-        <v>1136224</v>
+        <v>1326139</v>
       </c>
       <c r="G5" t="n">
-        <v>2231253</v>
+        <v>3168457</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4907686398628932</v>
+        <v>-0.5814558947778051</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PIIND</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3068.1</v>
+        <v>1214</v>
       </c>
       <c r="C6" t="n">
-        <v>3084</v>
+        <v>1229.3</v>
       </c>
       <c r="D6" t="n">
-        <v>3015</v>
+        <v>1211.5</v>
       </c>
       <c r="E6" t="n">
-        <v>3084</v>
+        <v>1218.7</v>
       </c>
       <c r="F6" t="n">
-        <v>287746</v>
+        <v>918546</v>
       </c>
       <c r="G6" t="n">
-        <v>600277</v>
+        <v>1950738</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5206446357265062</v>
+        <v>-0.5291289758030038</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>PIIND</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IGL</t>
+          <t>BANKBARODA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>172.01</v>
+        <v>303.25</v>
       </c>
       <c r="C7" t="n">
-        <v>173.4</v>
+        <v>307</v>
       </c>
       <c r="D7" t="n">
-        <v>170.71</v>
+        <v>303.25</v>
       </c>
       <c r="E7" t="n">
-        <v>172.24</v>
+        <v>304.6</v>
       </c>
       <c r="F7" t="n">
-        <v>3228324</v>
+        <v>7867687</v>
       </c>
       <c r="G7" t="n">
-        <v>7930421</v>
+        <v>17496015</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5929189635707864</v>
+        <v>-0.5503154861264122</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>IGL</t>
+          <t>BANKBARODA</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IREDA</t>
+          <t>UNITDSPR</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>127.07</v>
+        <v>1430</v>
       </c>
       <c r="C8" t="n">
-        <v>127.59</v>
+        <v>1431.3</v>
       </c>
       <c r="D8" t="n">
-        <v>126.25</v>
+        <v>1416.1</v>
       </c>
       <c r="E8" t="n">
-        <v>127.25</v>
+        <v>1425</v>
       </c>
       <c r="F8" t="n">
-        <v>5252696</v>
+        <v>271072</v>
       </c>
       <c r="G8" t="n">
-        <v>12339521</v>
+        <v>567457</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5743192948899718</v>
+        <v>-0.52230389262975</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>IREDA</t>
+          <t>UNITDSPR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ASTRAL</t>
+          <t>SBICARD</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1639.8</v>
+        <v>776.6</v>
       </c>
       <c r="C9" t="n">
-        <v>1653</v>
+        <v>795.6</v>
       </c>
       <c r="D9" t="n">
-        <v>1612.7</v>
+        <v>775.6</v>
       </c>
       <c r="E9" t="n">
-        <v>1640</v>
+        <v>788</v>
       </c>
       <c r="F9" t="n">
-        <v>490265</v>
+        <v>861645</v>
       </c>
       <c r="G9" t="n">
-        <v>1221002</v>
+        <v>1777812</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5984732211740849</v>
+        <v>-0.5153340173201666</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ASTRAL</t>
+          <t>SBICARD</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PRESTIGE</t>
+          <t>GMRAIRPORT</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1516.3</v>
+        <v>99.8</v>
       </c>
       <c r="C10" t="n">
-        <v>1548.6</v>
+        <v>101.64</v>
       </c>
       <c r="D10" t="n">
-        <v>1512</v>
+        <v>99.12</v>
       </c>
       <c r="E10" t="n">
-        <v>1522.7</v>
+        <v>100.4</v>
       </c>
       <c r="F10" t="n">
-        <v>298593</v>
+        <v>12811121</v>
       </c>
       <c r="G10" t="n">
-        <v>601273</v>
+        <v>25514687</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5033986225890735</v>
+        <v>-0.4978922923883017</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>PRESTIGE</t>
+          <t>GMRAIRPORT</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GMRAIRPORT</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>99.87</v>
+        <v>2255</v>
       </c>
       <c r="C11" t="n">
-        <v>102.55</v>
+        <v>2255</v>
       </c>
       <c r="D11" t="n">
-        <v>99.12</v>
+        <v>2220.8</v>
       </c>
       <c r="E11" t="n">
-        <v>99.8</v>
+        <v>2230.8</v>
       </c>
       <c r="F11" t="n">
-        <v>25514687</v>
+        <v>381520</v>
       </c>
       <c r="G11" t="n">
-        <v>50976360</v>
+        <v>932836</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4994800138730973</v>
+        <v>-0.5910106385259574</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>GMRAIRPORT</t>
+          <t>LUPIN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>TATAELXSI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>11750</v>
+        <v>4940</v>
       </c>
       <c r="C12" t="n">
-        <v>11818</v>
+        <v>4940</v>
       </c>
       <c r="D12" t="n">
-        <v>11605</v>
+        <v>4821</v>
       </c>
       <c r="E12" t="n">
-        <v>11640</v>
+        <v>4881</v>
       </c>
       <c r="F12" t="n">
-        <v>286065</v>
+        <v>181973</v>
       </c>
       <c r="G12" t="n">
-        <v>600256</v>
+        <v>423010</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5234283372427764</v>
+        <v>-0.5698139523888324</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>TATAELXSI</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FORTIS</t>
+          <t>KFINTECH</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>921.9</v>
+        <v>1034.5</v>
       </c>
       <c r="C13" t="n">
-        <v>930</v>
+        <v>1041.7</v>
       </c>
       <c r="D13" t="n">
-        <v>902.65</v>
+        <v>1012.1</v>
       </c>
       <c r="E13" t="n">
-        <v>904</v>
+        <v>1038.8</v>
       </c>
       <c r="F13" t="n">
-        <v>912616</v>
+        <v>1311588</v>
       </c>
       <c r="G13" t="n">
-        <v>2094816</v>
+        <v>2964027</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.5643455081496418</v>
+        <v>-0.5574979580145525</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>FORTIS</t>
+          <t>KFINTECH</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GRANULES</t>
+          <t>CROMPTON</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>558</v>
+        <v>271</v>
       </c>
       <c r="C14" t="n">
-        <v>571</v>
+        <v>273.07</v>
       </c>
       <c r="D14" t="n">
-        <v>558</v>
+        <v>267.5</v>
       </c>
       <c r="E14" t="n">
-        <v>568.5</v>
+        <v>271</v>
       </c>
       <c r="F14" t="n">
-        <v>247457</v>
+        <v>1942687</v>
       </c>
       <c r="G14" t="n">
-        <v>522642</v>
+        <v>4061488</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5265267621048443</v>
+        <v>-0.5216809701272046</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>GRANULES</t>
+          <t>CROMPTON</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CESC</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>154.47</v>
+        <v>438.55</v>
       </c>
       <c r="C15" t="n">
-        <v>156</v>
+        <v>438.55</v>
       </c>
       <c r="D15" t="n">
-        <v>153.5</v>
+        <v>430.05</v>
       </c>
       <c r="E15" t="n">
-        <v>155.3</v>
+        <v>432</v>
       </c>
       <c r="F15" t="n">
-        <v>595578</v>
+        <v>1442525</v>
       </c>
       <c r="G15" t="n">
-        <v>1268149</v>
+        <v>3217185</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.53035644865075</v>
+        <v>-0.5516188842108862</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>CESC</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>PPLPHARMA</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>161.99</v>
-      </c>
-      <c r="C16" t="n">
-        <v>165.3</v>
-      </c>
-      <c r="D16" t="n">
-        <v>161.87</v>
-      </c>
-      <c r="E16" t="n">
-        <v>164.5</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1640770</v>
-      </c>
-      <c r="G16" t="n">
-        <v>3946154</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-0.5842103475941385</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>PPLPHARMA</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>ANGELONE</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>2565.1</v>
-      </c>
-      <c r="C17" t="n">
-        <v>2609.9</v>
-      </c>
-      <c r="D17" t="n">
-        <v>2541.4</v>
-      </c>
-      <c r="E17" t="n">
-        <v>2575</v>
-      </c>
-      <c r="F17" t="n">
-        <v>882255</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1996002</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-0.5579889198507817</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>ANGELONE</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
     </row>
@@ -1068,528 +1002,528 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2399.5</v>
+        <v>1148</v>
       </c>
       <c r="C2" t="n">
-        <v>2452.4</v>
+        <v>1173.2</v>
       </c>
       <c r="D2" t="n">
-        <v>2399.5</v>
+        <v>1145.8</v>
       </c>
       <c r="E2" t="n">
-        <v>2439</v>
+        <v>1167</v>
       </c>
       <c r="F2" t="n">
-        <v>1004356</v>
+        <v>641938</v>
       </c>
       <c r="G2" t="n">
-        <v>683108</v>
+        <v>442621</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4702741001422908</v>
+        <v>0.450310762480768</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1266</v>
+        <v>175.86</v>
       </c>
       <c r="C3" t="n">
-        <v>1286.8</v>
+        <v>179</v>
       </c>
       <c r="D3" t="n">
-        <v>1258.2</v>
+        <v>175.86</v>
       </c>
       <c r="E3" t="n">
-        <v>1281.3</v>
+        <v>178.52</v>
       </c>
       <c r="F3" t="n">
-        <v>687326</v>
+        <v>8191312</v>
       </c>
       <c r="G3" t="n">
-        <v>469592</v>
+        <v>5249228</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4636663316240481</v>
+        <v>0.5604793695377682</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>IOC</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>VBL</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2716</v>
+        <v>458.05</v>
       </c>
       <c r="C4" t="n">
-        <v>2760</v>
+        <v>464.4</v>
       </c>
       <c r="D4" t="n">
-        <v>2695.2</v>
+        <v>455.2</v>
       </c>
       <c r="E4" t="n">
-        <v>2719.8</v>
+        <v>462.75</v>
       </c>
       <c r="F4" t="n">
-        <v>4209118</v>
+        <v>2991343</v>
       </c>
       <c r="G4" t="n">
-        <v>2918730</v>
+        <v>2033633</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4421059844521418</v>
+        <v>0.4709355129465346</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>VBL</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1002</v>
+        <v>683</v>
       </c>
       <c r="C5" t="n">
-        <v>1035</v>
+        <v>696.9</v>
       </c>
       <c r="D5" t="n">
-        <v>996</v>
+        <v>682.3</v>
       </c>
       <c r="E5" t="n">
-        <v>1030.45</v>
+        <v>692.9</v>
       </c>
       <c r="F5" t="n">
-        <v>1460922</v>
+        <v>1977779</v>
       </c>
       <c r="G5" t="n">
-        <v>976113</v>
+        <v>1325438</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4966730286350043</v>
+        <v>0.4921701354571092</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LTIM</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5097</v>
+        <v>5836</v>
       </c>
       <c r="C6" t="n">
-        <v>5234.5</v>
+        <v>5909</v>
       </c>
       <c r="D6" t="n">
-        <v>5051</v>
+        <v>5771.5</v>
       </c>
       <c r="E6" t="n">
-        <v>5156</v>
+        <v>5865</v>
       </c>
       <c r="F6" t="n">
-        <v>316641</v>
+        <v>178419</v>
       </c>
       <c r="G6" t="n">
-        <v>216966</v>
+        <v>116120</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4594037775503996</v>
+        <v>0.5365053393041681</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>LTIM</t>
+          <t>ABB</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>IDFCFIRSTB</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1479</v>
+        <v>83.34999999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>1497.8</v>
+        <v>85.55</v>
       </c>
       <c r="D7" t="n">
-        <v>1477.4</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>1495</v>
+        <v>85.34999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>344682</v>
+        <v>27410289</v>
       </c>
       <c r="G7" t="n">
-        <v>217908</v>
+        <v>19451127</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5817776309268131</v>
+        <v>0.4091877041366292</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>IDFCFIRSTB</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>374.35</v>
+        <v>1001.9</v>
       </c>
       <c r="C8" t="n">
-        <v>375.8</v>
+        <v>1024.1</v>
       </c>
       <c r="D8" t="n">
-        <v>366.55</v>
+        <v>995.7</v>
       </c>
       <c r="E8" t="n">
-        <v>375</v>
+        <v>1023.5</v>
       </c>
       <c r="F8" t="n">
-        <v>2646518</v>
+        <v>3081772</v>
       </c>
       <c r="G8" t="n">
-        <v>1709180</v>
+        <v>1966733</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5484138592775483</v>
+        <v>0.566949860504705</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>AUBANK</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>132.31</v>
+        <v>11.41</v>
       </c>
       <c r="C9" t="n">
-        <v>133.97</v>
+        <v>11.66</v>
       </c>
       <c r="D9" t="n">
-        <v>131.22</v>
+        <v>11.4</v>
       </c>
       <c r="E9" t="n">
-        <v>132.5</v>
+        <v>11.55</v>
       </c>
       <c r="F9" t="n">
-        <v>17075133</v>
+        <v>358955663</v>
       </c>
       <c r="G9" t="n">
-        <v>10892515</v>
+        <v>252469405</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5676024315780148</v>
+        <v>0.4217788606900705</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>IDEA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>679.8</v>
+        <v>472.8</v>
       </c>
       <c r="C10" t="n">
-        <v>680</v>
+        <v>481.05</v>
       </c>
       <c r="D10" t="n">
-        <v>660.3</v>
+        <v>469.5</v>
       </c>
       <c r="E10" t="n">
-        <v>667.3</v>
+        <v>478.45</v>
       </c>
       <c r="F10" t="n">
-        <v>10070194</v>
+        <v>5407805</v>
       </c>
       <c r="G10" t="n">
-        <v>6387272</v>
+        <v>3763634</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5766032822776296</v>
+        <v>0.4368573033403355</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>PAGEIND</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>590</v>
+        <v>33880</v>
       </c>
       <c r="C11" t="n">
-        <v>590</v>
+        <v>33950</v>
       </c>
       <c r="D11" t="n">
-        <v>575</v>
+        <v>33250</v>
       </c>
       <c r="E11" t="n">
-        <v>581.6</v>
+        <v>33430</v>
       </c>
       <c r="F11" t="n">
-        <v>6472316</v>
+        <v>8975</v>
       </c>
       <c r="G11" t="n">
-        <v>4181298</v>
+        <v>6156</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5479202869539554</v>
+        <v>0.4579272254710851</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>PAGEIND</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>JUBLFOOD</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>888</v>
+        <v>531</v>
       </c>
       <c r="C12" t="n">
-        <v>921.9</v>
+        <v>533.4</v>
       </c>
       <c r="D12" t="n">
-        <v>881</v>
+        <v>522.3</v>
       </c>
       <c r="E12" t="n">
-        <v>920</v>
+        <v>523.55</v>
       </c>
       <c r="F12" t="n">
-        <v>1893818</v>
+        <v>986314</v>
       </c>
       <c r="G12" t="n">
-        <v>1290153</v>
+        <v>661200</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4679018690031337</v>
+        <v>0.49170296430732</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>JUBLFOOD</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SUPREMEIND</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3900</v>
+        <v>1850</v>
       </c>
       <c r="C13" t="n">
-        <v>3927.9</v>
+        <v>1863.3</v>
       </c>
       <c r="D13" t="n">
-        <v>3871.5</v>
+        <v>1827.1</v>
       </c>
       <c r="E13" t="n">
-        <v>3920</v>
+        <v>1827.1</v>
       </c>
       <c r="F13" t="n">
-        <v>256640</v>
+        <v>835001</v>
       </c>
       <c r="G13" t="n">
-        <v>171503</v>
+        <v>551161</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4964169722978607</v>
+        <v>0.51498563940482</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>SUPREMEIND</t>
+          <t>MFSL</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PATANJALI</t>
+          <t>KAYNES</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>524.9</v>
+        <v>3978.3</v>
       </c>
       <c r="C14" t="n">
-        <v>535.95</v>
+        <v>4075</v>
       </c>
       <c r="D14" t="n">
-        <v>521.85</v>
+        <v>3905</v>
       </c>
       <c r="E14" t="n">
-        <v>528.5</v>
+        <v>4035</v>
       </c>
       <c r="F14" t="n">
-        <v>1777456</v>
+        <v>1341272</v>
       </c>
       <c r="G14" t="n">
-        <v>1260588</v>
+        <v>863254</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4100213551136454</v>
+        <v>0.5537396872762825</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>PATANJALI</t>
+          <t>KAYNES</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>511.1</v>
+        <v>168.5</v>
       </c>
       <c r="C15" t="n">
-        <v>519.05</v>
+        <v>172.2</v>
       </c>
       <c r="D15" t="n">
-        <v>511.1</v>
+        <v>167.59</v>
       </c>
       <c r="E15" t="n">
-        <v>516</v>
+        <v>171.2</v>
       </c>
       <c r="F15" t="n">
-        <v>963143</v>
+        <v>6135908</v>
       </c>
       <c r="G15" t="n">
-        <v>667469</v>
+        <v>4077654</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4429778761260822</v>
+        <v>0.5047642590568008</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>VOLTAS</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1540</v>
+        <v>1340.1</v>
       </c>
       <c r="C16" t="n">
-        <v>1540</v>
+        <v>1358.4</v>
       </c>
       <c r="D16" t="n">
-        <v>1513.2</v>
+        <v>1334</v>
       </c>
       <c r="E16" t="n">
-        <v>1533</v>
+        <v>1356</v>
       </c>
       <c r="F16" t="n">
-        <v>444923</v>
+        <v>1366930</v>
       </c>
       <c r="G16" t="n">
-        <v>300771</v>
+        <v>901508</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4792749300963191</v>
+        <v>0.5162705156249306</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>VOLTAS</t>
+          <t>CDSL</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>PPLPHARMA</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>289</v>
+        <v>165</v>
       </c>
       <c r="C17" t="n">
-        <v>291.05</v>
+        <v>166.46</v>
       </c>
       <c r="D17" t="n">
-        <v>282.6</v>
+        <v>164.2</v>
       </c>
       <c r="E17" t="n">
-        <v>288.5</v>
+        <v>166</v>
       </c>
       <c r="F17" t="n">
-        <v>7052510</v>
+        <v>2453587</v>
       </c>
       <c r="G17" t="n">
-        <v>4743148</v>
+        <v>1640770</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4868838164021025</v>
+        <v>0.4953875314638859</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>PPLPHARMA</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,462 +479,231 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MAXHEALTH</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1076.15</v>
+        <v>7610</v>
       </c>
       <c r="C2" t="n">
-        <v>1087.9</v>
+        <v>7649</v>
       </c>
       <c r="D2" t="n">
-        <v>1071.65</v>
+        <v>7551.5</v>
       </c>
       <c r="E2" t="n">
-        <v>1085</v>
+        <v>7551.5</v>
       </c>
       <c r="F2" t="n">
-        <v>680966</v>
+        <v>186713</v>
       </c>
       <c r="G2" t="n">
-        <v>1701396</v>
+        <v>385965</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5997604320217045</v>
+        <v>-0.5162437008537043</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MAXHEALTH</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2020.1</v>
+        <v>1381.1</v>
       </c>
       <c r="C3" t="n">
-        <v>2028.6</v>
+        <v>1382.8</v>
       </c>
       <c r="D3" t="n">
-        <v>2015</v>
+        <v>1351</v>
       </c>
       <c r="E3" t="n">
-        <v>2021.6</v>
+        <v>1351</v>
       </c>
       <c r="F3" t="n">
-        <v>2182669</v>
+        <v>2744704</v>
       </c>
       <c r="G3" t="n">
-        <v>4471158</v>
+        <v>5556076</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5118336234147842</v>
+        <v>-0.5059995579614102</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>AXISBANK</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1410.1</v>
+        <v>6255</v>
       </c>
       <c r="C4" t="n">
-        <v>1412.3</v>
+        <v>6350</v>
       </c>
       <c r="D4" t="n">
-        <v>1398.9</v>
+        <v>6251</v>
       </c>
       <c r="E4" t="n">
-        <v>1406</v>
+        <v>6275</v>
       </c>
       <c r="F4" t="n">
-        <v>4758071</v>
+        <v>185828</v>
       </c>
       <c r="G4" t="n">
-        <v>11756187</v>
+        <v>438670</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5952708986340555</v>
+        <v>-0.5763831581826886</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1565</v>
+        <v>128.12</v>
       </c>
       <c r="C5" t="n">
-        <v>1565</v>
+        <v>128.35</v>
       </c>
       <c r="D5" t="n">
-        <v>1540</v>
+        <v>125.52</v>
       </c>
       <c r="E5" t="n">
-        <v>1550</v>
+        <v>126.2</v>
       </c>
       <c r="F5" t="n">
-        <v>1326139</v>
+        <v>18850093</v>
       </c>
       <c r="G5" t="n">
-        <v>3168457</v>
+        <v>37051990</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5814558947778051</v>
+        <v>-0.4912528854725482</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>PNB</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>KEI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1214</v>
+        <v>4644.4</v>
       </c>
       <c r="C6" t="n">
-        <v>1229.3</v>
+        <v>4644.4</v>
       </c>
       <c r="D6" t="n">
-        <v>1211.5</v>
+        <v>4551</v>
       </c>
       <c r="E6" t="n">
-        <v>1218.7</v>
+        <v>4562.3</v>
       </c>
       <c r="F6" t="n">
-        <v>918546</v>
+        <v>99931</v>
       </c>
       <c r="G6" t="n">
-        <v>1950738</v>
+        <v>222240</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5291289758030038</v>
+        <v>-0.5503464722822174</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>KEI</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>303.25</v>
+        <v>1521</v>
       </c>
       <c r="C7" t="n">
-        <v>307</v>
+        <v>1544.9</v>
       </c>
       <c r="D7" t="n">
-        <v>303.25</v>
+        <v>1485.9</v>
       </c>
       <c r="E7" t="n">
-        <v>304.6</v>
+        <v>1491</v>
       </c>
       <c r="F7" t="n">
-        <v>7867687</v>
+        <v>521702</v>
       </c>
       <c r="G7" t="n">
-        <v>17496015</v>
+        <v>1031052</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5503154861264122</v>
+        <v>-0.4940100014354271</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>BLUESTARCO</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1430</v>
+        <v>2016.7</v>
       </c>
       <c r="C8" t="n">
-        <v>1431.3</v>
+        <v>2017.7</v>
       </c>
       <c r="D8" t="n">
-        <v>1416.1</v>
+        <v>1957.1</v>
       </c>
       <c r="E8" t="n">
-        <v>1425</v>
+        <v>1965</v>
       </c>
       <c r="F8" t="n">
-        <v>271072</v>
+        <v>243797</v>
       </c>
       <c r="G8" t="n">
-        <v>567457</v>
+        <v>495144</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.52230389262975</v>
+        <v>-0.5076240447223433</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>SBICARD</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>776.6</v>
-      </c>
-      <c r="C9" t="n">
-        <v>795.6</v>
-      </c>
-      <c r="D9" t="n">
-        <v>775.6</v>
-      </c>
-      <c r="E9" t="n">
-        <v>788</v>
-      </c>
-      <c r="F9" t="n">
-        <v>861645</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1777812</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-0.5153340173201666</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>SBICARD</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>GMRAIRPORT</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>99.8</v>
-      </c>
-      <c r="C10" t="n">
-        <v>101.64</v>
-      </c>
-      <c r="D10" t="n">
-        <v>99.12</v>
-      </c>
-      <c r="E10" t="n">
-        <v>100.4</v>
-      </c>
-      <c r="F10" t="n">
-        <v>12811121</v>
-      </c>
-      <c r="G10" t="n">
-        <v>25514687</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-0.4978922923883017</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>GMRAIRPORT</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>LUPIN</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2255</v>
-      </c>
-      <c r="C11" t="n">
-        <v>2255</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2220.8</v>
-      </c>
-      <c r="E11" t="n">
-        <v>2230.8</v>
-      </c>
-      <c r="F11" t="n">
-        <v>381520</v>
-      </c>
-      <c r="G11" t="n">
-        <v>932836</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-0.5910106385259574</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>LUPIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>TATAELXSI</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>4940</v>
-      </c>
-      <c r="C12" t="n">
-        <v>4940</v>
-      </c>
-      <c r="D12" t="n">
-        <v>4821</v>
-      </c>
-      <c r="E12" t="n">
-        <v>4881</v>
-      </c>
-      <c r="F12" t="n">
-        <v>181973</v>
-      </c>
-      <c r="G12" t="n">
-        <v>423010</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-0.5698139523888324</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>TATAELXSI</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>KFINTECH</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1034.5</v>
-      </c>
-      <c r="C13" t="n">
-        <v>1041.7</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1012.1</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1038.8</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1311588</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2964027</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-0.5574979580145525</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>KFINTECH</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CROMPTON</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>271</v>
-      </c>
-      <c r="C14" t="n">
-        <v>273.07</v>
-      </c>
-      <c r="D14" t="n">
-        <v>267.5</v>
-      </c>
-      <c r="E14" t="n">
-        <v>271</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1942687</v>
-      </c>
-      <c r="G14" t="n">
-        <v>4061488</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-0.5216809701272046</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>CROMPTON</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>DELHIVERY</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>438.55</v>
-      </c>
-      <c r="C15" t="n">
-        <v>438.55</v>
-      </c>
-      <c r="D15" t="n">
-        <v>430.05</v>
-      </c>
-      <c r="E15" t="n">
-        <v>432</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1442525</v>
-      </c>
-      <c r="G15" t="n">
-        <v>3217185</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-0.5516188842108862</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>DELHIVERY</t>
+          <t>BLUESTARCO</t>
         </is>
       </c>
     </row>
@@ -949,7 +718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1006,25 +775,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1148</v>
+        <v>1169</v>
       </c>
       <c r="C2" t="n">
-        <v>1173.2</v>
+        <v>1169</v>
       </c>
       <c r="D2" t="n">
-        <v>1145.8</v>
+        <v>1151.7</v>
       </c>
       <c r="E2" t="n">
-        <v>1167</v>
+        <v>1162.1</v>
       </c>
       <c r="F2" t="n">
+        <v>994383</v>
+      </c>
+      <c r="G2" t="n">
         <v>641938</v>
       </c>
-      <c r="G2" t="n">
-        <v>442621</v>
-      </c>
       <c r="H2" t="n">
-        <v>0.450310762480768</v>
+        <v>0.5490327726353635</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -1035,495 +804,561 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>175.86</v>
+        <v>1299.8</v>
       </c>
       <c r="C3" t="n">
-        <v>179</v>
+        <v>1300</v>
       </c>
       <c r="D3" t="n">
-        <v>175.86</v>
+        <v>1271.9</v>
       </c>
       <c r="E3" t="n">
-        <v>178.52</v>
+        <v>1278</v>
       </c>
       <c r="F3" t="n">
-        <v>8191312</v>
+        <v>659360</v>
       </c>
       <c r="G3" t="n">
-        <v>5249228</v>
+        <v>446022</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5604793695377682</v>
+        <v>0.4783127289685262</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VBL</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>458.05</v>
+        <v>4181</v>
       </c>
       <c r="C4" t="n">
-        <v>464.4</v>
+        <v>4181.1</v>
       </c>
       <c r="D4" t="n">
-        <v>455.2</v>
+        <v>4053</v>
       </c>
       <c r="E4" t="n">
-        <v>462.75</v>
+        <v>4069.9</v>
       </c>
       <c r="F4" t="n">
-        <v>2991343</v>
+        <v>587295</v>
       </c>
       <c r="G4" t="n">
-        <v>2033633</v>
+        <v>372954</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4709355129465346</v>
+        <v>0.5747116266349201</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>VBL</t>
+          <t>TRENT</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>683</v>
+        <v>3534.9</v>
       </c>
       <c r="C5" t="n">
-        <v>696.9</v>
+        <v>3546.5</v>
       </c>
       <c r="D5" t="n">
-        <v>682.3</v>
+        <v>3421.3</v>
       </c>
       <c r="E5" t="n">
-        <v>692.9</v>
+        <v>3427</v>
       </c>
       <c r="F5" t="n">
-        <v>1977779</v>
+        <v>2479531</v>
       </c>
       <c r="G5" t="n">
-        <v>1325438</v>
+        <v>1682427</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4921701354571092</v>
+        <v>0.4737822205658849</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>M&amp;M</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5836</v>
+        <v>167.31</v>
       </c>
       <c r="C6" t="n">
-        <v>5909</v>
+        <v>169.36</v>
       </c>
       <c r="D6" t="n">
-        <v>5771.5</v>
+        <v>165.85</v>
       </c>
       <c r="E6" t="n">
-        <v>5865</v>
+        <v>166.8</v>
       </c>
       <c r="F6" t="n">
-        <v>178419</v>
+        <v>17067659</v>
       </c>
       <c r="G6" t="n">
-        <v>116120</v>
+        <v>11790520</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5365053393041681</v>
+        <v>0.4475747464912489</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>GAIL</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IDFCFIRSTB</t>
+          <t>SOLARINDS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>83.34999999999999</v>
+        <v>13403</v>
       </c>
       <c r="C7" t="n">
-        <v>85.55</v>
+        <v>13525</v>
       </c>
       <c r="D7" t="n">
-        <v>82.65000000000001</v>
+        <v>13284</v>
       </c>
       <c r="E7" t="n">
-        <v>85.34999999999999</v>
+        <v>13309</v>
       </c>
       <c r="F7" t="n">
-        <v>27410289</v>
+        <v>102729</v>
       </c>
       <c r="G7" t="n">
-        <v>19451127</v>
+        <v>68820</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4091877041366292</v>
+        <v>0.492720139494333</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>IDFCFIRSTB</t>
+          <t>SOLARINDS</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>AMBUJACEM</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1001.9</v>
+        <v>522</v>
       </c>
       <c r="C8" t="n">
-        <v>1024.1</v>
+        <v>526.35</v>
       </c>
       <c r="D8" t="n">
-        <v>995.7</v>
+        <v>510.8</v>
       </c>
       <c r="E8" t="n">
-        <v>1023.5</v>
+        <v>515.3</v>
       </c>
       <c r="F8" t="n">
-        <v>3081772</v>
+        <v>2535330</v>
       </c>
       <c r="G8" t="n">
-        <v>1966733</v>
+        <v>1773473</v>
       </c>
       <c r="H8" t="n">
-        <v>0.566949860504705</v>
+        <v>0.4295847751840597</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>AMBUJACEM</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11.41</v>
+        <v>379.5</v>
       </c>
       <c r="C9" t="n">
-        <v>11.66</v>
+        <v>381.75</v>
       </c>
       <c r="D9" t="n">
-        <v>11.4</v>
+        <v>368.3</v>
       </c>
       <c r="E9" t="n">
-        <v>11.55</v>
+        <v>370</v>
       </c>
       <c r="F9" t="n">
-        <v>358955663</v>
+        <v>3203557</v>
       </c>
       <c r="G9" t="n">
-        <v>252469405</v>
+        <v>2150233</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4217788606900705</v>
+        <v>0.4898650518339175</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>INDUSTOWER</t>
+          <t>TATAELXSI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>472.8</v>
+        <v>4889.5</v>
       </c>
       <c r="C10" t="n">
-        <v>481.05</v>
+        <v>4981</v>
       </c>
       <c r="D10" t="n">
-        <v>469.5</v>
+        <v>4812</v>
       </c>
       <c r="E10" t="n">
-        <v>478.45</v>
+        <v>4828</v>
       </c>
       <c r="F10" t="n">
-        <v>5407805</v>
+        <v>282759</v>
       </c>
       <c r="G10" t="n">
-        <v>3763634</v>
+        <v>181973</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4368573033403355</v>
+        <v>0.5538513955367005</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>INDUSTOWER</t>
+          <t>TATAELXSI</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PAGEIND</t>
+          <t>ASTRAL</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>33880</v>
+        <v>1630</v>
       </c>
       <c r="C11" t="n">
-        <v>33950</v>
+        <v>1645</v>
       </c>
       <c r="D11" t="n">
-        <v>33250</v>
+        <v>1613.1</v>
       </c>
       <c r="E11" t="n">
-        <v>33430</v>
+        <v>1617</v>
       </c>
       <c r="F11" t="n">
-        <v>8975</v>
+        <v>525038</v>
       </c>
       <c r="G11" t="n">
-        <v>6156</v>
+        <v>357889</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4579272254710851</v>
+        <v>0.4670414569880605</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>PAGEIND</t>
+          <t>ASTRAL</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>JUBLFOOD</t>
+          <t>RVNL</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>531</v>
+        <v>310.9</v>
       </c>
       <c r="C12" t="n">
-        <v>533.4</v>
+        <v>314.45</v>
       </c>
       <c r="D12" t="n">
-        <v>522.3</v>
+        <v>305</v>
       </c>
       <c r="E12" t="n">
-        <v>523.55</v>
+        <v>305.65</v>
       </c>
       <c r="F12" t="n">
-        <v>986314</v>
+        <v>8070615</v>
       </c>
       <c r="G12" t="n">
-        <v>661200</v>
+        <v>5539696</v>
       </c>
       <c r="H12" t="n">
-        <v>0.49170296430732</v>
+        <v>0.4568696549413542</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>JUBLFOOD</t>
+          <t>RVNL</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1850</v>
+        <v>1204.9</v>
       </c>
       <c r="C13" t="n">
-        <v>1863.3</v>
+        <v>1215.7</v>
       </c>
       <c r="D13" t="n">
-        <v>1827.1</v>
+        <v>1185</v>
       </c>
       <c r="E13" t="n">
-        <v>1827.1</v>
+        <v>1191.1</v>
       </c>
       <c r="F13" t="n">
-        <v>835001</v>
+        <v>640809</v>
       </c>
       <c r="G13" t="n">
-        <v>551161</v>
+        <v>406638</v>
       </c>
       <c r="H13" t="n">
-        <v>0.51498563940482</v>
+        <v>0.5758709220486035</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>KAYNES</t>
+          <t>NMDC</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3978.3</v>
+        <v>80.5</v>
       </c>
       <c r="C14" t="n">
-        <v>4075</v>
+        <v>81.05</v>
       </c>
       <c r="D14" t="n">
-        <v>3905</v>
+        <v>78.73</v>
       </c>
       <c r="E14" t="n">
-        <v>4035</v>
+        <v>78.88</v>
       </c>
       <c r="F14" t="n">
-        <v>1341272</v>
+        <v>17807737</v>
       </c>
       <c r="G14" t="n">
-        <v>863254</v>
+        <v>12495946</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5537396872762825</v>
+        <v>0.425081142316076</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>KAYNES</t>
+          <t>NMDC</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>SJVN</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>168.5</v>
+        <v>76.65000000000001</v>
       </c>
       <c r="C15" t="n">
-        <v>172.2</v>
+        <v>77.28</v>
       </c>
       <c r="D15" t="n">
-        <v>167.59</v>
+        <v>74.58</v>
       </c>
       <c r="E15" t="n">
-        <v>171.2</v>
+        <v>75.2</v>
       </c>
       <c r="F15" t="n">
-        <v>6135908</v>
+        <v>3925513</v>
       </c>
       <c r="G15" t="n">
-        <v>4077654</v>
+        <v>2773487</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5047642590568008</v>
+        <v>0.4153709752380307</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>SJVN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1340.1</v>
+        <v>350</v>
       </c>
       <c r="C16" t="n">
-        <v>1358.4</v>
+        <v>350.95</v>
       </c>
       <c r="D16" t="n">
-        <v>1334</v>
+        <v>340.6</v>
       </c>
       <c r="E16" t="n">
-        <v>1356</v>
+        <v>341.8</v>
       </c>
       <c r="F16" t="n">
-        <v>1366930</v>
+        <v>6020376</v>
       </c>
       <c r="G16" t="n">
-        <v>901508</v>
+        <v>3968030</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5162705156249306</v>
+        <v>0.5172203839184684</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PPLPHARMA</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>165</v>
+        <v>1492</v>
       </c>
       <c r="C17" t="n">
-        <v>166.46</v>
+        <v>1507.7</v>
       </c>
       <c r="D17" t="n">
-        <v>164.2</v>
+        <v>1460</v>
       </c>
       <c r="E17" t="n">
-        <v>166</v>
+        <v>1465</v>
       </c>
       <c r="F17" t="n">
-        <v>2453587</v>
+        <v>1716054</v>
       </c>
       <c r="G17" t="n">
-        <v>1640770</v>
+        <v>1087280</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4953875314638859</v>
+        <v>0.5782999779265691</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>PPLPHARMA</t>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>5600</v>
+      </c>
+      <c r="C18" t="n">
+        <v>5644.5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5387.5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>5405</v>
+      </c>
+      <c r="F18" t="n">
+        <v>307768</v>
+      </c>
+      <c r="G18" t="n">
+        <v>197770</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.5561915356221874</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>GODREJPROP</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1880</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1887</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1806</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1820</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1845151</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1207699</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.5278235719330727</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>GODREJPROP</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -479,231 +479,231 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7610</v>
+        <v>1162.1</v>
       </c>
       <c r="C2" t="n">
-        <v>7649</v>
+        <v>1168.5</v>
       </c>
       <c r="D2" t="n">
-        <v>7551.5</v>
+        <v>1153.5</v>
       </c>
       <c r="E2" t="n">
-        <v>7551.5</v>
+        <v>1155.2</v>
       </c>
       <c r="F2" t="n">
-        <v>186713</v>
+        <v>484995</v>
       </c>
       <c r="G2" t="n">
-        <v>385965</v>
+        <v>994383</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5162437008537043</v>
+        <v>-0.5122653947221544</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1381.1</v>
+        <v>26250</v>
       </c>
       <c r="C3" t="n">
-        <v>1382.8</v>
+        <v>26700</v>
       </c>
       <c r="D3" t="n">
-        <v>1351</v>
+        <v>25965</v>
       </c>
       <c r="E3" t="n">
-        <v>1351</v>
+        <v>26490</v>
       </c>
       <c r="F3" t="n">
-        <v>2744704</v>
+        <v>16060</v>
       </c>
       <c r="G3" t="n">
-        <v>5556076</v>
+        <v>32451</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5059995579614102</v>
+        <v>-0.5050999969184309</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>SHREECEM</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>PAGEIND</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6255</v>
+        <v>32695</v>
       </c>
       <c r="C4" t="n">
-        <v>6350</v>
+        <v>33135</v>
       </c>
       <c r="D4" t="n">
-        <v>6251</v>
+        <v>32465</v>
       </c>
       <c r="E4" t="n">
-        <v>6275</v>
+        <v>32790</v>
       </c>
       <c r="F4" t="n">
-        <v>185828</v>
+        <v>9328</v>
       </c>
       <c r="G4" t="n">
-        <v>438670</v>
+        <v>19153</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5763831581826886</v>
+        <v>-0.5129744687516316</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>PAGEIND</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>IDFCFIRSTB</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>128.12</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>128.35</v>
+        <v>83.8</v>
       </c>
       <c r="D5" t="n">
-        <v>125.52</v>
+        <v>82.3</v>
       </c>
       <c r="E5" t="n">
-        <v>126.2</v>
+        <v>83.25</v>
       </c>
       <c r="F5" t="n">
-        <v>18850093</v>
+        <v>11974786</v>
       </c>
       <c r="G5" t="n">
-        <v>37051990</v>
+        <v>29470408</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4912528854725482</v>
+        <v>-0.5936674510919564</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>IDFCFIRSTB</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KEI</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4644.4</v>
+        <v>480.35</v>
       </c>
       <c r="C6" t="n">
-        <v>4644.4</v>
+        <v>486.15</v>
       </c>
       <c r="D6" t="n">
-        <v>4551</v>
+        <v>471.95</v>
       </c>
       <c r="E6" t="n">
-        <v>4562.3</v>
+        <v>473.95</v>
       </c>
       <c r="F6" t="n">
-        <v>99931</v>
+        <v>8314392</v>
       </c>
       <c r="G6" t="n">
-        <v>222240</v>
+        <v>19628154</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5503464722822174</v>
+        <v>-0.5764047907918392</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>KEI</t>
+          <t>OIL</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TORNTPOWER</t>
+          <t>MANAPPURAM</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1521</v>
+        <v>304.8</v>
       </c>
       <c r="C7" t="n">
-        <v>1544.9</v>
+        <v>308.1</v>
       </c>
       <c r="D7" t="n">
-        <v>1485.9</v>
+        <v>303.35</v>
       </c>
       <c r="E7" t="n">
-        <v>1491</v>
+        <v>306.8</v>
       </c>
       <c r="F7" t="n">
-        <v>521702</v>
+        <v>1307604</v>
       </c>
       <c r="G7" t="n">
-        <v>1031052</v>
+        <v>2951795</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4940100014354271</v>
+        <v>-0.5570139525271911</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>TORNTPOWER</t>
+          <t>MANAPPURAM</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BLUESTARCO</t>
+          <t>NUVAMA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2016.7</v>
+        <v>1298.4</v>
       </c>
       <c r="C8" t="n">
-        <v>2017.7</v>
+        <v>1311</v>
       </c>
       <c r="D8" t="n">
-        <v>1957.1</v>
+        <v>1280.8</v>
       </c>
       <c r="E8" t="n">
-        <v>1965</v>
+        <v>1281.6</v>
       </c>
       <c r="F8" t="n">
-        <v>243797</v>
+        <v>187016</v>
       </c>
       <c r="G8" t="n">
-        <v>495144</v>
+        <v>380851</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5076240447223433</v>
+        <v>-0.508952319936143</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BLUESTARCO</t>
+          <t>NUVAMA</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -771,594 +771,330 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1169</v>
+        <v>295.55</v>
       </c>
       <c r="C2" t="n">
-        <v>1169</v>
+        <v>302.05</v>
       </c>
       <c r="D2" t="n">
-        <v>1151.7</v>
+        <v>294.25</v>
       </c>
       <c r="E2" t="n">
-        <v>1162.1</v>
+        <v>299</v>
       </c>
       <c r="F2" t="n">
-        <v>994383</v>
+        <v>11762183</v>
       </c>
       <c r="G2" t="n">
-        <v>641938</v>
+        <v>7552362</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5490327726353635</v>
+        <v>0.5574177985642108</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>POWERGRID</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>GRASIM</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1299.8</v>
+        <v>2864.9</v>
       </c>
       <c r="C3" t="n">
-        <v>1300</v>
+        <v>2890</v>
       </c>
       <c r="D3" t="n">
-        <v>1271.9</v>
+        <v>2822.7</v>
       </c>
       <c r="E3" t="n">
-        <v>1278</v>
+        <v>2835</v>
       </c>
       <c r="F3" t="n">
-        <v>659360</v>
+        <v>597887</v>
       </c>
       <c r="G3" t="n">
-        <v>446022</v>
+        <v>388104</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4783127289685262</v>
+        <v>0.5405329499309464</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>GRASIM</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4181</v>
+        <v>1465</v>
       </c>
       <c r="C4" t="n">
-        <v>4181.1</v>
+        <v>1477.3</v>
       </c>
       <c r="D4" t="n">
-        <v>4053</v>
+        <v>1453.1</v>
       </c>
       <c r="E4" t="n">
-        <v>4069.9</v>
+        <v>1464</v>
       </c>
       <c r="F4" t="n">
-        <v>587295</v>
+        <v>1599813</v>
       </c>
       <c r="G4" t="n">
-        <v>372954</v>
+        <v>1108260</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5747116266349201</v>
+        <v>0.4435358128958908</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>TECHM</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>GODREJCP</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3534.9</v>
+        <v>1188.5</v>
       </c>
       <c r="C5" t="n">
-        <v>3546.5</v>
+        <v>1210</v>
       </c>
       <c r="D5" t="n">
-        <v>3421.3</v>
+        <v>1184</v>
       </c>
       <c r="E5" t="n">
-        <v>3427</v>
+        <v>1205</v>
       </c>
       <c r="F5" t="n">
-        <v>2479531</v>
+        <v>576360</v>
       </c>
       <c r="G5" t="n">
-        <v>1682427</v>
+        <v>376142</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4737822205658849</v>
+        <v>0.5322936550558034</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>GODREJCP</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>167.31</v>
+        <v>202.56</v>
       </c>
       <c r="C6" t="n">
-        <v>169.36</v>
+        <v>209.36</v>
       </c>
       <c r="D6" t="n">
-        <v>165.85</v>
+        <v>201.81</v>
       </c>
       <c r="E6" t="n">
-        <v>166.8</v>
+        <v>208.3</v>
       </c>
       <c r="F6" t="n">
-        <v>17067659</v>
+        <v>14624480</v>
       </c>
       <c r="G6" t="n">
-        <v>11790520</v>
+        <v>9638504</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4475747464912489</v>
+        <v>0.5172977051210437</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SOLARINDS</t>
+          <t>VOLTAS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13403</v>
+        <v>1509.9</v>
       </c>
       <c r="C7" t="n">
-        <v>13525</v>
+        <v>1550.9</v>
       </c>
       <c r="D7" t="n">
-        <v>13284</v>
+        <v>1505.1</v>
       </c>
       <c r="E7" t="n">
-        <v>13309</v>
+        <v>1543.4</v>
       </c>
       <c r="F7" t="n">
-        <v>102729</v>
+        <v>935468</v>
       </c>
       <c r="G7" t="n">
-        <v>68820</v>
+        <v>657967</v>
       </c>
       <c r="H7" t="n">
-        <v>0.492720139494333</v>
+        <v>0.4217551944094461</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SOLARINDS</t>
+          <t>VOLTAS</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AMBUJACEM</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>522</v>
+        <v>7780</v>
       </c>
       <c r="C8" t="n">
-        <v>526.35</v>
+        <v>7932</v>
       </c>
       <c r="D8" t="n">
-        <v>510.8</v>
+        <v>7710</v>
       </c>
       <c r="E8" t="n">
-        <v>515.3</v>
+        <v>7829</v>
       </c>
       <c r="F8" t="n">
-        <v>2535330</v>
+        <v>393536</v>
       </c>
       <c r="G8" t="n">
-        <v>1773473</v>
+        <v>264268</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4295847751840597</v>
+        <v>0.4891549487641334</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AMBUJACEM</t>
+          <t>POLYCAB</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>379.5</v>
+        <v>2360.2</v>
       </c>
       <c r="C9" t="n">
-        <v>381.75</v>
+        <v>2402</v>
       </c>
       <c r="D9" t="n">
-        <v>368.3</v>
+        <v>2321.2</v>
       </c>
       <c r="E9" t="n">
-        <v>370</v>
+        <v>2365</v>
       </c>
       <c r="F9" t="n">
-        <v>3203557</v>
+        <v>686221</v>
       </c>
       <c r="G9" t="n">
-        <v>2150233</v>
+        <v>483838</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4898650518339175</v>
+        <v>0.41828669926711</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>MPHASIS</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TATAELXSI</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4889.5</v>
+        <v>2203</v>
       </c>
       <c r="C10" t="n">
-        <v>4981</v>
+        <v>2231.7</v>
       </c>
       <c r="D10" t="n">
-        <v>4812</v>
+        <v>2177.4</v>
       </c>
       <c r="E10" t="n">
-        <v>4828</v>
+        <v>2177.4</v>
       </c>
       <c r="F10" t="n">
-        <v>282759</v>
+        <v>390445</v>
       </c>
       <c r="G10" t="n">
-        <v>181973</v>
+        <v>268013</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5538513955367005</v>
+        <v>0.456813662023857</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>TATAELXSI</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ASTRAL</t>
+          <t>PPLPHARMA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1630</v>
+        <v>163</v>
       </c>
       <c r="C11" t="n">
-        <v>1645</v>
+        <v>164.03</v>
       </c>
       <c r="D11" t="n">
-        <v>1613.1</v>
+        <v>159.93</v>
       </c>
       <c r="E11" t="n">
-        <v>1617</v>
+        <v>160.12</v>
       </c>
       <c r="F11" t="n">
-        <v>525038</v>
+        <v>1989983</v>
       </c>
       <c r="G11" t="n">
-        <v>357889</v>
+        <v>1388727</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4670414569880605</v>
+        <v>0.432954785209764</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ASTRAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>RVNL</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>310.9</v>
-      </c>
-      <c r="C12" t="n">
-        <v>314.45</v>
-      </c>
-      <c r="D12" t="n">
-        <v>305</v>
-      </c>
-      <c r="E12" t="n">
-        <v>305.65</v>
-      </c>
-      <c r="F12" t="n">
-        <v>8070615</v>
-      </c>
-      <c r="G12" t="n">
-        <v>5539696</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.4568696549413542</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>RVNL</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>UNOMINDA</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1204.9</v>
-      </c>
-      <c r="C13" t="n">
-        <v>1215.7</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1185</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1191.1</v>
-      </c>
-      <c r="F13" t="n">
-        <v>640809</v>
-      </c>
-      <c r="G13" t="n">
-        <v>406638</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.5758709220486035</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>UNOMINDA</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>NMDC</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>80.5</v>
-      </c>
-      <c r="C14" t="n">
-        <v>81.05</v>
-      </c>
-      <c r="D14" t="n">
-        <v>78.73</v>
-      </c>
-      <c r="E14" t="n">
-        <v>78.88</v>
-      </c>
-      <c r="F14" t="n">
-        <v>17807737</v>
-      </c>
-      <c r="G14" t="n">
-        <v>12495946</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.425081142316076</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>NMDC</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>SJVN</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>76.65000000000001</v>
-      </c>
-      <c r="C15" t="n">
-        <v>77.28</v>
-      </c>
-      <c r="D15" t="n">
-        <v>74.58</v>
-      </c>
-      <c r="E15" t="n">
-        <v>75.2</v>
-      </c>
-      <c r="F15" t="n">
-        <v>3925513</v>
-      </c>
-      <c r="G15" t="n">
-        <v>2773487</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.4153709752380307</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>SJVN</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>ABCAPITAL</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>350</v>
-      </c>
-      <c r="C16" t="n">
-        <v>350.95</v>
-      </c>
-      <c r="D16" t="n">
-        <v>340.6</v>
-      </c>
-      <c r="E16" t="n">
-        <v>341.8</v>
-      </c>
-      <c r="F16" t="n">
-        <v>6020376</v>
-      </c>
-      <c r="G16" t="n">
-        <v>3968030</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.5172203839184684</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>ABCAPITAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>POLICYBZR</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1492</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1507.7</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1460</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1465</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1716054</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1087280</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.5782999779265691</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>POLICYBZR</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>HEROMOTOCO</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>5600</v>
-      </c>
-      <c r="C18" t="n">
-        <v>5644.5</v>
-      </c>
-      <c r="D18" t="n">
-        <v>5387.5</v>
-      </c>
-      <c r="E18" t="n">
-        <v>5405</v>
-      </c>
-      <c r="F18" t="n">
-        <v>307768</v>
-      </c>
-      <c r="G18" t="n">
-        <v>197770</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.5561915356221874</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>HEROMOTOCO</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>GODREJPROP</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1880</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1887</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1806</v>
-      </c>
-      <c r="E19" t="n">
-        <v>1820</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1845151</v>
-      </c>
-      <c r="G19" t="n">
-        <v>1207699</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.5278235719330727</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>GODREJPROP</t>
+          <t>PPLPHARMA</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,231 +479,330 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1162.1</v>
+        <v>9851</v>
       </c>
       <c r="C2" t="n">
-        <v>1168.5</v>
+        <v>9930</v>
       </c>
       <c r="D2" t="n">
-        <v>1153.5</v>
+        <v>9814</v>
       </c>
       <c r="E2" t="n">
-        <v>1155.2</v>
+        <v>9884.5</v>
       </c>
       <c r="F2" t="n">
-        <v>484995</v>
+        <v>145464</v>
       </c>
       <c r="G2" t="n">
-        <v>994383</v>
+        <v>291070</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5122653947221544</v>
+        <v>-0.5002439275775586</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26250</v>
+        <v>15050</v>
       </c>
       <c r="C3" t="n">
-        <v>26700</v>
+        <v>15118</v>
       </c>
       <c r="D3" t="n">
-        <v>25965</v>
+        <v>14984</v>
       </c>
       <c r="E3" t="n">
-        <v>26490</v>
+        <v>15050</v>
       </c>
       <c r="F3" t="n">
-        <v>16060</v>
+        <v>242968</v>
       </c>
       <c r="G3" t="n">
-        <v>32451</v>
+        <v>515847</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5050999969184309</v>
+        <v>-0.528992123633558</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>MARUTI</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PAGEIND</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>32695</v>
+        <v>279.9</v>
       </c>
       <c r="C4" t="n">
-        <v>33135</v>
+        <v>279.9</v>
       </c>
       <c r="D4" t="n">
-        <v>32465</v>
+        <v>272.2</v>
       </c>
       <c r="E4" t="n">
-        <v>32790</v>
+        <v>276.05</v>
       </c>
       <c r="F4" t="n">
-        <v>9328</v>
+        <v>13113050</v>
       </c>
       <c r="G4" t="n">
-        <v>19153</v>
+        <v>31971956</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5129744687516316</v>
+        <v>-0.5898577490848542</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>PAGEIND</t>
+          <t>ONGC</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IDFCFIRSTB</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>82.59999999999999</v>
+        <v>1003.1</v>
       </c>
       <c r="C5" t="n">
-        <v>83.8</v>
+        <v>1010</v>
       </c>
       <c r="D5" t="n">
-        <v>82.3</v>
+        <v>993.15</v>
       </c>
       <c r="E5" t="n">
-        <v>83.25</v>
+        <v>1001.9</v>
       </c>
       <c r="F5" t="n">
-        <v>11974786</v>
+        <v>1266712</v>
       </c>
       <c r="G5" t="n">
-        <v>29470408</v>
+        <v>2534563</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5936674510919564</v>
+        <v>-0.5002246935665043</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>IDFCFIRSTB</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>HAVELLS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>480.35</v>
+        <v>1420</v>
       </c>
       <c r="C6" t="n">
-        <v>486.15</v>
+        <v>1423.9</v>
       </c>
       <c r="D6" t="n">
-        <v>471.95</v>
+        <v>1402</v>
       </c>
       <c r="E6" t="n">
-        <v>473.95</v>
+        <v>1406.2</v>
       </c>
       <c r="F6" t="n">
-        <v>8314392</v>
+        <v>221863</v>
       </c>
       <c r="G6" t="n">
-        <v>19628154</v>
+        <v>543595</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5764047907918392</v>
+        <v>-0.5918597485260166</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>HAVELLS</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MANAPPURAM</t>
+          <t>SUPREMEIND</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>304.8</v>
+        <v>3918.3</v>
       </c>
       <c r="C7" t="n">
-        <v>308.1</v>
+        <v>3955</v>
       </c>
       <c r="D7" t="n">
-        <v>303.35</v>
+        <v>3910</v>
       </c>
       <c r="E7" t="n">
-        <v>306.8</v>
+        <v>3936.4</v>
       </c>
       <c r="F7" t="n">
-        <v>1307604</v>
+        <v>186576</v>
       </c>
       <c r="G7" t="n">
-        <v>2951795</v>
+        <v>455886</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5570139525271911</v>
+        <v>-0.5907397902107105</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MANAPPURAM</t>
+          <t>SUPREMEIND</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NUVAMA</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1298.4</v>
+        <v>1540</v>
       </c>
       <c r="C8" t="n">
-        <v>1311</v>
+        <v>1552.8</v>
       </c>
       <c r="D8" t="n">
-        <v>1280.8</v>
+        <v>1525</v>
       </c>
       <c r="E8" t="n">
-        <v>1281.6</v>
+        <v>1533</v>
       </c>
       <c r="F8" t="n">
-        <v>187016</v>
+        <v>618797</v>
       </c>
       <c r="G8" t="n">
-        <v>380851</v>
+        <v>1254354</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.508952319936143</v>
+        <v>-0.5066807296823703</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>NUVAMA</t>
+          <t>TORNTPOWER</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>527.85</v>
+      </c>
+      <c r="C9" t="n">
+        <v>529.4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>520.25</v>
+      </c>
+      <c r="E9" t="n">
+        <v>524.5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>842871</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1801249</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.5320630295977957</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SBICARD</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>792</v>
+      </c>
+      <c r="C10" t="n">
+        <v>792.3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>779.6</v>
+      </c>
+      <c r="E10" t="n">
+        <v>782.9</v>
+      </c>
+      <c r="F10" t="n">
+        <v>625260</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1292865</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.5163764198118133</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>SBICARD</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>5090</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5120</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4916</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4970</v>
+      </c>
+      <c r="F11" t="n">
+        <v>835461</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1666625</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.4987108677716943</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
         </is>
       </c>
     </row>
@@ -718,7 +817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -771,330 +870,627 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>295.55</v>
+        <v>423</v>
       </c>
       <c r="C2" t="n">
-        <v>302.05</v>
+        <v>431.8</v>
       </c>
       <c r="D2" t="n">
-        <v>294.25</v>
+        <v>420.35</v>
       </c>
       <c r="E2" t="n">
-        <v>299</v>
+        <v>430.8</v>
       </c>
       <c r="F2" t="n">
-        <v>11762183</v>
+        <v>10399627</v>
       </c>
       <c r="G2" t="n">
-        <v>7552362</v>
+        <v>6603883</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5574177985642108</v>
+        <v>0.5747745682350823</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2864.9</v>
+        <v>2180</v>
       </c>
       <c r="C3" t="n">
-        <v>2890</v>
+        <v>2203</v>
       </c>
       <c r="D3" t="n">
-        <v>2822.7</v>
+        <v>2155.3</v>
       </c>
       <c r="E3" t="n">
-        <v>2835</v>
+        <v>2186.7</v>
       </c>
       <c r="F3" t="n">
-        <v>597887</v>
+        <v>1103960</v>
       </c>
       <c r="G3" t="n">
-        <v>388104</v>
+        <v>738454</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5405329499309464</v>
+        <v>0.4949610943945053</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>ADANIENT</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1465</v>
+        <v>7680</v>
       </c>
       <c r="C4" t="n">
-        <v>1477.3</v>
+        <v>7710</v>
       </c>
       <c r="D4" t="n">
-        <v>1453.1</v>
+        <v>7615.5</v>
       </c>
       <c r="E4" t="n">
-        <v>1464</v>
+        <v>7698</v>
       </c>
       <c r="F4" t="n">
-        <v>1599813</v>
+        <v>399710</v>
       </c>
       <c r="G4" t="n">
-        <v>1108260</v>
+        <v>256304</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4435358128958908</v>
+        <v>0.559515263125039</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1188.5</v>
+        <v>1335.9</v>
       </c>
       <c r="C5" t="n">
-        <v>1210</v>
+        <v>1335.9</v>
       </c>
       <c r="D5" t="n">
-        <v>1184</v>
+        <v>1308.8</v>
       </c>
       <c r="E5" t="n">
-        <v>1205</v>
+        <v>1327</v>
       </c>
       <c r="F5" t="n">
-        <v>576360</v>
+        <v>2435610</v>
       </c>
       <c r="G5" t="n">
-        <v>376142</v>
+        <v>1551722</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5322936550558034</v>
+        <v>0.5696174959174388</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>CIPLA</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>202.56</v>
+        <v>607</v>
       </c>
       <c r="C6" t="n">
-        <v>209.36</v>
+        <v>607.35</v>
       </c>
       <c r="D6" t="n">
-        <v>201.81</v>
+        <v>585.7</v>
       </c>
       <c r="E6" t="n">
-        <v>208.3</v>
+        <v>591.75</v>
       </c>
       <c r="F6" t="n">
-        <v>14624480</v>
+        <v>7862513</v>
       </c>
       <c r="G6" t="n">
-        <v>9638504</v>
+        <v>5062307</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5172977051210437</v>
+        <v>0.5531481990325755</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>HINDZINC</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VOLTAS</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1509.9</v>
+        <v>3835</v>
       </c>
       <c r="C7" t="n">
-        <v>1550.9</v>
+        <v>3894.8</v>
       </c>
       <c r="D7" t="n">
-        <v>1505.1</v>
+        <v>3814.2</v>
       </c>
       <c r="E7" t="n">
-        <v>1543.4</v>
+        <v>3826.6</v>
       </c>
       <c r="F7" t="n">
-        <v>935468</v>
+        <v>605954</v>
       </c>
       <c r="G7" t="n">
-        <v>657967</v>
+        <v>386586</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4217551944094461</v>
+        <v>0.5674494161713047</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>VOLTAS</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7780</v>
+        <v>26520</v>
       </c>
       <c r="C8" t="n">
-        <v>7932</v>
+        <v>27045</v>
       </c>
       <c r="D8" t="n">
-        <v>7710</v>
+        <v>26365</v>
       </c>
       <c r="E8" t="n">
-        <v>7829</v>
+        <v>26450</v>
       </c>
       <c r="F8" t="n">
-        <v>393536</v>
+        <v>24261</v>
       </c>
       <c r="G8" t="n">
-        <v>264268</v>
+        <v>16060</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4891549487641334</v>
+        <v>0.5106475716064757</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>SHREECEM</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2360.2</v>
+        <v>695</v>
       </c>
       <c r="C9" t="n">
-        <v>2402</v>
+        <v>695.75</v>
       </c>
       <c r="D9" t="n">
-        <v>2321.2</v>
+        <v>670.3</v>
       </c>
       <c r="E9" t="n">
-        <v>2365</v>
+        <v>679.5</v>
       </c>
       <c r="F9" t="n">
-        <v>686221</v>
+        <v>10762317</v>
       </c>
       <c r="G9" t="n">
-        <v>483838</v>
+        <v>6871777</v>
       </c>
       <c r="H9" t="n">
-        <v>0.41828669926711</v>
+        <v>0.5661621440858747</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>VEDL</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>LTIM</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2203</v>
+        <v>4849.5</v>
       </c>
       <c r="C10" t="n">
-        <v>2231.7</v>
+        <v>4876</v>
       </c>
       <c r="D10" t="n">
-        <v>2177.4</v>
+        <v>4765</v>
       </c>
       <c r="E10" t="n">
-        <v>2177.4</v>
+        <v>4822.5</v>
       </c>
       <c r="F10" t="n">
-        <v>390445</v>
+        <v>363966</v>
       </c>
       <c r="G10" t="n">
-        <v>268013</v>
+        <v>244127</v>
       </c>
       <c r="H10" t="n">
-        <v>0.456813662023857</v>
+        <v>0.4908879394741262</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>LTIM</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PPLPHARMA</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>163</v>
+        <v>2370</v>
       </c>
       <c r="C11" t="n">
-        <v>164.03</v>
+        <v>2370</v>
       </c>
       <c r="D11" t="n">
-        <v>159.93</v>
+        <v>2271.1</v>
       </c>
       <c r="E11" t="n">
-        <v>160.12</v>
+        <v>2284.1</v>
       </c>
       <c r="F11" t="n">
-        <v>1989983</v>
+        <v>1137814</v>
       </c>
       <c r="G11" t="n">
-        <v>1388727</v>
+        <v>805052</v>
       </c>
       <c r="H11" t="n">
-        <v>0.432954785209764</v>
+        <v>0.4133422437308397</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>PPLPHARMA</t>
+          <t>MAZDOCK</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MARICO</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>795</v>
+      </c>
+      <c r="C12" t="n">
+        <v>804.95</v>
+      </c>
+      <c r="D12" t="n">
+        <v>787.2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>801.15</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1445444</v>
+      </c>
+      <c r="G12" t="n">
+        <v>974730</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.4829173206939358</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MARICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1157.8</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1179.5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1156.8</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1172</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1976282</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1287270</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.5352505690336915</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>LUPIN</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2220</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2254.4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2210.5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2247</v>
+      </c>
+      <c r="F14" t="n">
+        <v>745467</v>
+      </c>
+      <c r="G14" t="n">
+        <v>509573</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.4629248409943227</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>LUPIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PAGEIND</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>32800</v>
+      </c>
+      <c r="C15" t="n">
+        <v>33280</v>
+      </c>
+      <c r="D15" t="n">
+        <v>32740</v>
+      </c>
+      <c r="E15" t="n">
+        <v>33035</v>
+      </c>
+      <c r="F15" t="n">
+        <v>13411</v>
+      </c>
+      <c r="G15" t="n">
+        <v>9328</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.4377144082332762</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>PAGEIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ABCAPITAL</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>346.15</v>
+      </c>
+      <c r="C16" t="n">
+        <v>350.95</v>
+      </c>
+      <c r="D16" t="n">
+        <v>342.85</v>
+      </c>
+      <c r="E16" t="n">
+        <v>346.5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>8310977</v>
+      </c>
+      <c r="G16" t="n">
+        <v>5688023</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.4611363210029214</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ABCAPITAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>IRB</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>40.89</v>
+      </c>
+      <c r="C17" t="n">
+        <v>41.06</v>
+      </c>
+      <c r="D17" t="n">
+        <v>40</v>
+      </c>
+      <c r="E17" t="n">
+        <v>40.22</v>
+      </c>
+      <c r="F17" t="n">
+        <v>6925701</v>
+      </c>
+      <c r="G17" t="n">
+        <v>4781082</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.448563525996835</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>IRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TATAELXSI</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>4845.5</v>
+      </c>
+      <c r="C18" t="n">
+        <v>4873</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4679</v>
+      </c>
+      <c r="E18" t="n">
+        <v>4700</v>
+      </c>
+      <c r="F18" t="n">
+        <v>327068</v>
+      </c>
+      <c r="G18" t="n">
+        <v>227011</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.4407583773473532</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>TATAELXSI</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>IEX</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>125.75</v>
+      </c>
+      <c r="C19" t="n">
+        <v>126.52</v>
+      </c>
+      <c r="D19" t="n">
+        <v>124.7</v>
+      </c>
+      <c r="E19" t="n">
+        <v>126</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4319720</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3070434</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.4068760312060119</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>IEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CAMS</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>724.8</v>
+      </c>
+      <c r="C20" t="n">
+        <v>729.8</v>
+      </c>
+      <c r="D20" t="n">
+        <v>711.2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>718.5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>621904</v>
+      </c>
+      <c r="G20" t="n">
+        <v>407454</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.5263170811919873</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>CAMS</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,330 +479,132 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9851</v>
+        <v>1553.7</v>
       </c>
       <c r="C2" t="n">
-        <v>9930</v>
+        <v>1564</v>
       </c>
       <c r="D2" t="n">
-        <v>9814</v>
+        <v>1536.4</v>
       </c>
       <c r="E2" t="n">
-        <v>9884.5</v>
+        <v>1561.9</v>
       </c>
       <c r="F2" t="n">
-        <v>145464</v>
+        <v>1360612</v>
       </c>
       <c r="G2" t="n">
-        <v>291070</v>
+        <v>3113728</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5002439275775586</v>
+        <v>-0.5630279844610705</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15050</v>
+        <v>4005</v>
       </c>
       <c r="C3" t="n">
-        <v>15118</v>
+        <v>4032.4</v>
       </c>
       <c r="D3" t="n">
-        <v>14984</v>
+        <v>3937.1</v>
       </c>
       <c r="E3" t="n">
-        <v>15050</v>
+        <v>3953</v>
       </c>
       <c r="F3" t="n">
-        <v>242968</v>
+        <v>1605651</v>
       </c>
       <c r="G3" t="n">
-        <v>515847</v>
+        <v>3750121</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.528992123633558</v>
+        <v>-0.5718402152890534</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>HAL</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>CUMMINSIND</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>279.9</v>
+        <v>4860</v>
       </c>
       <c r="C4" t="n">
-        <v>279.9</v>
+        <v>4941.9</v>
       </c>
       <c r="D4" t="n">
-        <v>272.2</v>
+        <v>4830.2</v>
       </c>
       <c r="E4" t="n">
-        <v>276.05</v>
+        <v>4915</v>
       </c>
       <c r="F4" t="n">
-        <v>13113050</v>
+        <v>672139</v>
       </c>
       <c r="G4" t="n">
-        <v>31971956</v>
+        <v>1570603</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5898577490848542</v>
+        <v>-0.5720503526352617</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>CUMMINSIND</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>INOXWIND</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1003.1</v>
+        <v>95.8</v>
       </c>
       <c r="C5" t="n">
-        <v>1010</v>
+        <v>97.29000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>993.15</v>
+        <v>93.45</v>
       </c>
       <c r="E5" t="n">
-        <v>1001.9</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>1266712</v>
+        <v>9395145</v>
       </c>
       <c r="G5" t="n">
-        <v>2534563</v>
+        <v>18928491</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5002246935665043</v>
+        <v>-0.50365060796447</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>HAVELLS</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1420</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1423.9</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1402</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1406.2</v>
-      </c>
-      <c r="F6" t="n">
-        <v>221863</v>
-      </c>
-      <c r="G6" t="n">
-        <v>543595</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-0.5918597485260166</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>HAVELLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>SUPREMEIND</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>3918.3</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3955</v>
-      </c>
-      <c r="D7" t="n">
-        <v>3910</v>
-      </c>
-      <c r="E7" t="n">
-        <v>3936.4</v>
-      </c>
-      <c r="F7" t="n">
-        <v>186576</v>
-      </c>
-      <c r="G7" t="n">
-        <v>455886</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-0.5907397902107105</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>SUPREMEIND</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>TORNTPOWER</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1540</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1552.8</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1525</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1533</v>
-      </c>
-      <c r="F8" t="n">
-        <v>618797</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1254354</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-0.5066807296823703</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>TORNTPOWER</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>LICHSGFIN</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>527.85</v>
-      </c>
-      <c r="C9" t="n">
-        <v>529.4</v>
-      </c>
-      <c r="D9" t="n">
-        <v>520.25</v>
-      </c>
-      <c r="E9" t="n">
-        <v>524.5</v>
-      </c>
-      <c r="F9" t="n">
-        <v>842871</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1801249</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-0.5320630295977957</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>LICHSGFIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>SBICARD</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>792</v>
-      </c>
-      <c r="C10" t="n">
-        <v>792.3</v>
-      </c>
-      <c r="D10" t="n">
-        <v>779.6</v>
-      </c>
-      <c r="E10" t="n">
-        <v>782.9</v>
-      </c>
-      <c r="F10" t="n">
-        <v>625260</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1292865</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-0.5163764198118133</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>SBICARD</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>PERSISTENT</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>5090</v>
-      </c>
-      <c r="C11" t="n">
-        <v>5120</v>
-      </c>
-      <c r="D11" t="n">
-        <v>4916</v>
-      </c>
-      <c r="E11" t="n">
-        <v>4970</v>
-      </c>
-      <c r="F11" t="n">
-        <v>835461</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1666625</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-0.4987108677716943</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>PERSISTENT</t>
+          <t>INOXWIND</t>
         </is>
       </c>
     </row>
@@ -817,7 +619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -874,25 +676,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>423</v>
+        <v>430.9</v>
       </c>
       <c r="C2" t="n">
-        <v>431.8</v>
+        <v>432.45</v>
       </c>
       <c r="D2" t="n">
-        <v>420.35</v>
+        <v>425.8</v>
       </c>
       <c r="E2" t="n">
-        <v>430.8</v>
+        <v>428</v>
       </c>
       <c r="F2" t="n">
+        <v>15016915</v>
+      </c>
+      <c r="G2" t="n">
         <v>10399627</v>
       </c>
-      <c r="G2" t="n">
-        <v>6603883</v>
-      </c>
       <c r="H2" t="n">
-        <v>0.5747745682350823</v>
+        <v>0.4439859237259183</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -903,495 +705,495 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2180</v>
+        <v>130.82</v>
       </c>
       <c r="C3" t="n">
-        <v>2203</v>
+        <v>132.34</v>
       </c>
       <c r="D3" t="n">
-        <v>2155.3</v>
+        <v>130</v>
       </c>
       <c r="E3" t="n">
-        <v>2186.7</v>
+        <v>132.3</v>
       </c>
       <c r="F3" t="n">
-        <v>1103960</v>
+        <v>14440301</v>
       </c>
       <c r="G3" t="n">
-        <v>738454</v>
+        <v>10219233</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4949610943945053</v>
+        <v>0.4130513513098292</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>GODREJCP</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7680</v>
+        <v>1226.8</v>
       </c>
       <c r="C4" t="n">
-        <v>7710</v>
+        <v>1237.9</v>
       </c>
       <c r="D4" t="n">
-        <v>7615.5</v>
+        <v>1214.3</v>
       </c>
       <c r="E4" t="n">
-        <v>7698</v>
+        <v>1236</v>
       </c>
       <c r="F4" t="n">
-        <v>399710</v>
+        <v>1187285</v>
       </c>
       <c r="G4" t="n">
-        <v>256304</v>
+        <v>806171</v>
       </c>
       <c r="H4" t="n">
-        <v>0.559515263125039</v>
+        <v>0.4727458566482793</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>GODREJCP</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1335.9</v>
+        <v>3830</v>
       </c>
       <c r="C5" t="n">
-        <v>1335.9</v>
+        <v>3835</v>
       </c>
       <c r="D5" t="n">
-        <v>1308.8</v>
+        <v>3743.4</v>
       </c>
       <c r="E5" t="n">
-        <v>1327</v>
+        <v>3820</v>
       </c>
       <c r="F5" t="n">
-        <v>2435610</v>
+        <v>896496</v>
       </c>
       <c r="G5" t="n">
-        <v>1551722</v>
+        <v>605954</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5696174959174388</v>
+        <v>0.4794786402928275</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>IRFC</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>607</v>
+        <v>111.34</v>
       </c>
       <c r="C6" t="n">
-        <v>607.35</v>
+        <v>111.56</v>
       </c>
       <c r="D6" t="n">
-        <v>585.7</v>
+        <v>109.05</v>
       </c>
       <c r="E6" t="n">
-        <v>591.75</v>
+        <v>109.9</v>
       </c>
       <c r="F6" t="n">
-        <v>7862513</v>
+        <v>13884700</v>
       </c>
       <c r="G6" t="n">
-        <v>5062307</v>
+        <v>9897270</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5531481990325755</v>
+        <v>0.4028818047805102</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>IRFC</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3835</v>
+        <v>623.15</v>
       </c>
       <c r="C7" t="n">
-        <v>3894.8</v>
+        <v>624.3</v>
       </c>
       <c r="D7" t="n">
-        <v>3814.2</v>
+        <v>608.25</v>
       </c>
       <c r="E7" t="n">
-        <v>3826.6</v>
+        <v>613.55</v>
       </c>
       <c r="F7" t="n">
-        <v>605954</v>
+        <v>2835264</v>
       </c>
       <c r="G7" t="n">
-        <v>386586</v>
+        <v>1932609</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5674494161713047</v>
+        <v>0.4670655057489642</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>DLF</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>SJVN</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26520</v>
+        <v>73.86</v>
       </c>
       <c r="C8" t="n">
-        <v>27045</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>26365</v>
+        <v>72.91</v>
       </c>
       <c r="E8" t="n">
-        <v>26450</v>
+        <v>74.58</v>
       </c>
       <c r="F8" t="n">
-        <v>24261</v>
+        <v>4242452</v>
       </c>
       <c r="G8" t="n">
-        <v>16060</v>
+        <v>2710062</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5106475716064757</v>
+        <v>0.565444628204078</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>SJVN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>695</v>
+        <v>514.45</v>
       </c>
       <c r="C9" t="n">
-        <v>695.75</v>
+        <v>519.75</v>
       </c>
       <c r="D9" t="n">
-        <v>670.3</v>
+        <v>512.75</v>
       </c>
       <c r="E9" t="n">
-        <v>679.5</v>
+        <v>517.1</v>
       </c>
       <c r="F9" t="n">
-        <v>10762317</v>
+        <v>1517098</v>
       </c>
       <c r="G9" t="n">
-        <v>6871777</v>
+        <v>1044529</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5661621440858747</v>
+        <v>0.452423053835748</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>DABUR</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LTIM</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4849.5</v>
+        <v>1535.4</v>
       </c>
       <c r="C10" t="n">
-        <v>4876</v>
+        <v>1569</v>
       </c>
       <c r="D10" t="n">
-        <v>4765</v>
+        <v>1525.2</v>
       </c>
       <c r="E10" t="n">
-        <v>4822.5</v>
+        <v>1544</v>
       </c>
       <c r="F10" t="n">
-        <v>363966</v>
+        <v>902713</v>
       </c>
       <c r="G10" t="n">
-        <v>244127</v>
+        <v>618797</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4908879394741262</v>
+        <v>0.4588192896862784</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>LTIM</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2370</v>
+        <v>2252.5</v>
       </c>
       <c r="C11" t="n">
-        <v>2370</v>
+        <v>2257.9</v>
       </c>
       <c r="D11" t="n">
-        <v>2271.1</v>
+        <v>2235</v>
       </c>
       <c r="E11" t="n">
-        <v>2284.1</v>
+        <v>2252</v>
       </c>
       <c r="F11" t="n">
-        <v>1137814</v>
+        <v>1074791</v>
       </c>
       <c r="G11" t="n">
-        <v>805052</v>
+        <v>745467</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4133422437308397</v>
+        <v>0.4417687167909512</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>LUPIN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>BLUESTARCO</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>795</v>
+        <v>1960</v>
       </c>
       <c r="C12" t="n">
-        <v>804.95</v>
+        <v>1968</v>
       </c>
       <c r="D12" t="n">
-        <v>787.2</v>
+        <v>1933.4</v>
       </c>
       <c r="E12" t="n">
-        <v>801.15</v>
+        <v>1967</v>
       </c>
       <c r="F12" t="n">
-        <v>1445444</v>
+        <v>315256</v>
       </c>
       <c r="G12" t="n">
-        <v>974730</v>
+        <v>221246</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4829173206939358</v>
+        <v>0.4249116368205527</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>BLUESTARCO</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PAYTM</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1157.8</v>
+        <v>209</v>
       </c>
       <c r="C13" t="n">
-        <v>1179.5</v>
+        <v>211.02</v>
       </c>
       <c r="D13" t="n">
-        <v>1156.8</v>
+        <v>208.62</v>
       </c>
       <c r="E13" t="n">
-        <v>1172</v>
+        <v>210.6</v>
       </c>
       <c r="F13" t="n">
-        <v>1976282</v>
+        <v>12888307</v>
       </c>
       <c r="G13" t="n">
-        <v>1287270</v>
+        <v>8533992</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5352505690336915</v>
+        <v>0.5102319055372914</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>PAYTM</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>YESBANK</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2220</v>
+        <v>20.89</v>
       </c>
       <c r="C14" t="n">
-        <v>2254.4</v>
+        <v>21.01</v>
       </c>
       <c r="D14" t="n">
-        <v>2210.5</v>
+        <v>20.61</v>
       </c>
       <c r="E14" t="n">
-        <v>2247</v>
+        <v>20.85</v>
       </c>
       <c r="F14" t="n">
-        <v>745467</v>
+        <v>81564930</v>
       </c>
       <c r="G14" t="n">
-        <v>509573</v>
+        <v>51401565</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4629248409943227</v>
+        <v>0.5868180278168573</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>YESBANK</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PAGEIND</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32800</v>
+        <v>469.9</v>
       </c>
       <c r="C15" t="n">
-        <v>33280</v>
+        <v>473</v>
       </c>
       <c r="D15" t="n">
-        <v>32740</v>
+        <v>464.05</v>
       </c>
       <c r="E15" t="n">
-        <v>33035</v>
+        <v>471</v>
       </c>
       <c r="F15" t="n">
-        <v>13411</v>
+        <v>5575559</v>
       </c>
       <c r="G15" t="n">
-        <v>9328</v>
+        <v>3640333</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4377144082332762</v>
+        <v>0.5316068612404414</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>PAGEIND</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>HUDCO</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>346.15</v>
+        <v>194</v>
       </c>
       <c r="C16" t="n">
-        <v>350.95</v>
+        <v>194</v>
       </c>
       <c r="D16" t="n">
-        <v>342.85</v>
+        <v>188.36</v>
       </c>
       <c r="E16" t="n">
-        <v>346.5</v>
+        <v>190.3</v>
       </c>
       <c r="F16" t="n">
-        <v>8310977</v>
+        <v>4069852</v>
       </c>
       <c r="G16" t="n">
-        <v>5688023</v>
+        <v>2718891</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4611363210029214</v>
+        <v>0.4968794262072294</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>HUDCO</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IRB</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>40.89</v>
+        <v>636.9</v>
       </c>
       <c r="C17" t="n">
-        <v>41.06</v>
+        <v>636.9</v>
       </c>
       <c r="D17" t="n">
-        <v>40</v>
+        <v>611.15</v>
       </c>
       <c r="E17" t="n">
-        <v>40.22</v>
+        <v>614.8</v>
       </c>
       <c r="F17" t="n">
-        <v>6925701</v>
+        <v>4217676</v>
       </c>
       <c r="G17" t="n">
-        <v>4781082</v>
+        <v>2983677</v>
       </c>
       <c r="H17" t="n">
-        <v>0.448563525996835</v>
+        <v>0.4135833067721473</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>IRB</t>
+          <t>IRCTC</t>
         </is>
       </c>
     </row>
@@ -1402,25 +1204,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4845.5</v>
+        <v>4675.5</v>
       </c>
       <c r="C18" t="n">
-        <v>4873</v>
+        <v>4700</v>
       </c>
       <c r="D18" t="n">
-        <v>4679</v>
+        <v>4455</v>
       </c>
       <c r="E18" t="n">
-        <v>4700</v>
+        <v>4518</v>
       </c>
       <c r="F18" t="n">
+        <v>465584</v>
+      </c>
+      <c r="G18" t="n">
         <v>327068</v>
       </c>
-      <c r="G18" t="n">
-        <v>227011</v>
-      </c>
       <c r="H18" t="n">
-        <v>0.4407583773473532</v>
+        <v>0.4235082612790001</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1431,66 +1233,99 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>KPITTECH</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>125.75</v>
+        <v>809</v>
       </c>
       <c r="C19" t="n">
-        <v>126.52</v>
+        <v>809.3</v>
       </c>
       <c r="D19" t="n">
-        <v>124.7</v>
+        <v>758</v>
       </c>
       <c r="E19" t="n">
-        <v>126</v>
+        <v>760</v>
       </c>
       <c r="F19" t="n">
-        <v>4319720</v>
+        <v>3617378</v>
       </c>
       <c r="G19" t="n">
-        <v>3070434</v>
+        <v>2364931</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4068760312060119</v>
+        <v>0.5295913495996289</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>KPITTECH</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>724.8</v>
+        <v>125.5</v>
       </c>
       <c r="C20" t="n">
-        <v>729.8</v>
+        <v>126.5</v>
       </c>
       <c r="D20" t="n">
-        <v>711.2</v>
+        <v>124.5</v>
       </c>
       <c r="E20" t="n">
-        <v>718.5</v>
+        <v>126.2</v>
       </c>
       <c r="F20" t="n">
-        <v>621904</v>
+        <v>6405727</v>
       </c>
       <c r="G20" t="n">
-        <v>407454</v>
+        <v>4319720</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5263170811919873</v>
+        <v>0.4829032900280574</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>IEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CDSL</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1325.9</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1342</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1318.4</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1328.2</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1312682</v>
+      </c>
+      <c r="G21" t="n">
+        <v>901439</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.4562072419764399</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>CDSL</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,132 +479,759 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1553.7</v>
+        <v>2596</v>
       </c>
       <c r="C2" t="n">
-        <v>1564</v>
+        <v>2654.2</v>
       </c>
       <c r="D2" t="n">
-        <v>1536.4</v>
+        <v>2595</v>
       </c>
       <c r="E2" t="n">
-        <v>1561.9</v>
+        <v>2629</v>
       </c>
       <c r="F2" t="n">
-        <v>1360612</v>
+        <v>3621285</v>
       </c>
       <c r="G2" t="n">
-        <v>3113728</v>
+        <v>7798833</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5630279844610705</v>
+        <v>-0.5356632203818187</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>TCS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4005</v>
+        <v>1742</v>
       </c>
       <c r="C3" t="n">
-        <v>4032.4</v>
+        <v>1770.4</v>
       </c>
       <c r="D3" t="n">
-        <v>3937.1</v>
+        <v>1733.4</v>
       </c>
       <c r="E3" t="n">
-        <v>3953</v>
+        <v>1763.3</v>
       </c>
       <c r="F3" t="n">
-        <v>1605651</v>
+        <v>1200997</v>
       </c>
       <c r="G3" t="n">
-        <v>3750121</v>
+        <v>2769363</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5718402152890534</v>
+        <v>-0.5663273467580812</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4860</v>
+        <v>1326.7</v>
       </c>
       <c r="C4" t="n">
-        <v>4941.9</v>
+        <v>1349</v>
       </c>
       <c r="D4" t="n">
-        <v>4830.2</v>
+        <v>1326.7</v>
       </c>
       <c r="E4" t="n">
-        <v>4915</v>
+        <v>1345</v>
       </c>
       <c r="F4" t="n">
-        <v>672139</v>
+        <v>1018377</v>
       </c>
       <c r="G4" t="n">
-        <v>1570603</v>
+        <v>2109672</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5720503526352617</v>
+        <v>-0.5172818333845262</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>CIPLA</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>INOXWIND</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>95.8</v>
+        <v>276.5</v>
       </c>
       <c r="C5" t="n">
-        <v>97.29000000000001</v>
+        <v>278.95</v>
       </c>
       <c r="D5" t="n">
-        <v>93.45</v>
+        <v>274</v>
       </c>
       <c r="E5" t="n">
-        <v>95.48999999999999</v>
+        <v>277.25</v>
       </c>
       <c r="F5" t="n">
-        <v>9395145</v>
+        <v>7573116</v>
       </c>
       <c r="G5" t="n">
-        <v>18928491</v>
+        <v>16311581</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.50365060796447</v>
+        <v>-0.5357215220278156</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>INOXWIND</t>
+          <t>ONGC</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2074.9</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2043</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2043</v>
+      </c>
+      <c r="F6" t="n">
+        <v>508162</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1054129</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.5179318660239876</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BAJFINANCE</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1028</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1034</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1013.4</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1020.4</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3182612</v>
+      </c>
+      <c r="G7" t="n">
+        <v>6610984</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.5185872481312918</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>BAJFINANCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2089.7</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2106</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2069.5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2075</v>
+      </c>
+      <c r="F8" t="n">
+        <v>355352</v>
+      </c>
+      <c r="G8" t="n">
+        <v>841918</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.5779256412144651</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>6101</v>
+      </c>
+      <c r="C9" t="n">
+        <v>6180</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6046.5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>6158</v>
+      </c>
+      <c r="F9" t="n">
+        <v>363747</v>
+      </c>
+      <c r="G9" t="n">
+        <v>782563</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.5351850266368331</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>LTIM</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4524</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4661.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4515.5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4549.5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>370208</v>
+      </c>
+      <c r="G10" t="n">
+        <v>883696</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.5810686027774257</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>LTIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>4420</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4443.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4358</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4435</v>
+      </c>
+      <c r="F11" t="n">
+        <v>359916</v>
+      </c>
+      <c r="G11" t="n">
+        <v>846802</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.5749703000229097</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2208.7</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2233.4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2186.3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2231</v>
+      </c>
+      <c r="F12" t="n">
+        <v>627610</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1362267</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.5392900217064643</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>JSL</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>797</v>
+      </c>
+      <c r="C13" t="n">
+        <v>808.3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>789.5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>803.4</v>
+      </c>
+      <c r="F13" t="n">
+        <v>825590</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1700672</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.5145507187746962</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>JSL</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2230</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2323.4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2227.3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2250</v>
+      </c>
+      <c r="F14" t="n">
+        <v>667290</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1348323</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.5050963307753409</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MFSL</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1844.6</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1857.5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1836.4</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1855.8</v>
+      </c>
+      <c r="F15" t="n">
+        <v>378587</v>
+      </c>
+      <c r="G15" t="n">
+        <v>783572</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.5168446549902243</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>MFSL</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TATATECH</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>573</v>
+      </c>
+      <c r="C16" t="n">
+        <v>584.65</v>
+      </c>
+      <c r="D16" t="n">
+        <v>573</v>
+      </c>
+      <c r="E16" t="n">
+        <v>576.25</v>
+      </c>
+      <c r="F16" t="n">
+        <v>891075</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1747763</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.4901625678081067</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>TATATECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1142.7</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1147.8</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1119.7</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1135.6</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2046403</v>
+      </c>
+      <c r="G17" t="n">
+        <v>4165307</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.5087029599498909</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1227.9</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1265.9</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1208</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1211.8</v>
+      </c>
+      <c r="F18" t="n">
+        <v>5227982</v>
+      </c>
+      <c r="G18" t="n">
+        <v>10454471</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.4999285951436472</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BANKINDIA</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>175.8</v>
+      </c>
+      <c r="C19" t="n">
+        <v>176.35</v>
+      </c>
+      <c r="D19" t="n">
+        <v>173.7</v>
+      </c>
+      <c r="E19" t="n">
+        <v>175.2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>9784182</v>
+      </c>
+      <c r="G19" t="n">
+        <v>22315167</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.5615456518877945</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>BANKINDIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>JUBLFOOD</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>518.9</v>
+      </c>
+      <c r="C20" t="n">
+        <v>525.55</v>
+      </c>
+      <c r="D20" t="n">
+        <v>510.45</v>
+      </c>
+      <c r="E20" t="n">
+        <v>517</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1325873</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3283010</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-0.5961410413005138</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>JUBLFOOD</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>328</v>
+      </c>
+      <c r="C21" t="n">
+        <v>332.95</v>
+      </c>
+      <c r="D21" t="n">
+        <v>322.55</v>
+      </c>
+      <c r="E21" t="n">
+        <v>330</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4824687</v>
+      </c>
+      <c r="G21" t="n">
+        <v>9940401</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.5146385945597165</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PPLPHARMA</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>159.99</v>
+      </c>
+      <c r="C22" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="D22" t="n">
+        <v>159.35</v>
+      </c>
+      <c r="E22" t="n">
+        <v>161.05</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1292223</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2663225</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-0.5147901510386843</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>PPLPHARMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ABFRL</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>68.33</v>
+      </c>
+      <c r="C23" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="D23" t="n">
+        <v>68.33</v>
+      </c>
+      <c r="E23" t="n">
+        <v>68.68000000000001</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1019290</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2176039</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.5315846820760106</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ABFRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>KFINTECH</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1004</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1009.6</v>
+      </c>
+      <c r="D24" t="n">
+        <v>990.3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>998</v>
+      </c>
+      <c r="F24" t="n">
+        <v>391925</v>
+      </c>
+      <c r="G24" t="n">
+        <v>782889</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.4993862476034278</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>KFINTECH</t>
         </is>
       </c>
     </row>
@@ -619,7 +1246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,660 +1299,495 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>430.9</v>
+        <v>7930</v>
       </c>
       <c r="C2" t="n">
-        <v>432.45</v>
+        <v>8082</v>
       </c>
       <c r="D2" t="n">
-        <v>425.8</v>
+        <v>7772</v>
       </c>
       <c r="E2" t="n">
-        <v>428</v>
+        <v>8040</v>
       </c>
       <c r="F2" t="n">
-        <v>15016915</v>
+        <v>618719</v>
       </c>
       <c r="G2" t="n">
-        <v>10399627</v>
+        <v>430812</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4439859237259183</v>
+        <v>0.4361693731836625</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>130.82</v>
+        <v>1567</v>
       </c>
       <c r="C3" t="n">
-        <v>132.34</v>
+        <v>1584</v>
       </c>
       <c r="D3" t="n">
-        <v>130</v>
+        <v>1518.5</v>
       </c>
       <c r="E3" t="n">
-        <v>132.3</v>
+        <v>1529</v>
       </c>
       <c r="F3" t="n">
-        <v>14440301</v>
+        <v>2153982</v>
       </c>
       <c r="G3" t="n">
-        <v>10219233</v>
+        <v>1360612</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4130513513098292</v>
+        <v>0.5830979000626189</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1226.8</v>
+        <v>903.5</v>
       </c>
       <c r="C4" t="n">
-        <v>1237.9</v>
+        <v>921</v>
       </c>
       <c r="D4" t="n">
-        <v>1214.3</v>
+        <v>902.1</v>
       </c>
       <c r="E4" t="n">
-        <v>1236</v>
+        <v>918.7</v>
       </c>
       <c r="F4" t="n">
-        <v>1187285</v>
+        <v>564586</v>
       </c>
       <c r="G4" t="n">
-        <v>806171</v>
+        <v>369018</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4727458566482793</v>
+        <v>0.5299687278127354</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>KPITTECH</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3830</v>
+        <v>764.1</v>
       </c>
       <c r="C5" t="n">
-        <v>3835</v>
+        <v>805</v>
       </c>
       <c r="D5" t="n">
-        <v>3743.4</v>
+        <v>764</v>
       </c>
       <c r="E5" t="n">
-        <v>3820</v>
+        <v>791.9</v>
       </c>
       <c r="F5" t="n">
-        <v>896496</v>
+        <v>5094300</v>
       </c>
       <c r="G5" t="n">
-        <v>605954</v>
+        <v>3617378</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4794786402928275</v>
+        <v>0.4082852275874957</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>KPITTECH</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IRFC</t>
+          <t>SONACOMS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>111.34</v>
+        <v>530.2</v>
       </c>
       <c r="C6" t="n">
-        <v>111.56</v>
+        <v>543.3</v>
       </c>
       <c r="D6" t="n">
-        <v>109.05</v>
+        <v>529.05</v>
       </c>
       <c r="E6" t="n">
-        <v>109.9</v>
+        <v>542.5</v>
       </c>
       <c r="F6" t="n">
-        <v>13884700</v>
+        <v>1312350</v>
       </c>
       <c r="G6" t="n">
-        <v>9897270</v>
+        <v>821398</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4028818047805102</v>
+        <v>0.5977029405963978</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>IRFC</t>
+          <t>SONACOMS</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>623.15</v>
+        <v>1120</v>
       </c>
       <c r="C7" t="n">
-        <v>624.3</v>
+        <v>1137.3</v>
       </c>
       <c r="D7" t="n">
-        <v>608.25</v>
+        <v>1104.5</v>
       </c>
       <c r="E7" t="n">
-        <v>613.55</v>
+        <v>1137.3</v>
       </c>
       <c r="F7" t="n">
-        <v>2835264</v>
+        <v>682336</v>
       </c>
       <c r="G7" t="n">
-        <v>1932609</v>
+        <v>432011</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4670655057489642</v>
+        <v>0.5794412642270683</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>360ONE</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SJVN</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>73.86</v>
+        <v>351.5</v>
       </c>
       <c r="C8" t="n">
-        <v>74.65000000000001</v>
+        <v>360</v>
       </c>
       <c r="D8" t="n">
-        <v>72.91</v>
+        <v>350.2</v>
       </c>
       <c r="E8" t="n">
-        <v>74.58</v>
+        <v>352.9</v>
       </c>
       <c r="F8" t="n">
-        <v>4242452</v>
+        <v>16813613</v>
       </c>
       <c r="G8" t="n">
-        <v>2710062</v>
+        <v>10786939</v>
       </c>
       <c r="H8" t="n">
-        <v>0.565444628204078</v>
+        <v>0.5587010365034975</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>SJVN</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>GMRAIRPORT</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>514.45</v>
+        <v>102.78</v>
       </c>
       <c r="C9" t="n">
-        <v>519.75</v>
+        <v>103.03</v>
       </c>
       <c r="D9" t="n">
-        <v>512.75</v>
+        <v>101.5</v>
       </c>
       <c r="E9" t="n">
-        <v>517.1</v>
+        <v>102.15</v>
       </c>
       <c r="F9" t="n">
-        <v>1517098</v>
+        <v>10916245</v>
       </c>
       <c r="G9" t="n">
-        <v>1044529</v>
+        <v>7047232</v>
       </c>
       <c r="H9" t="n">
-        <v>0.452423053835748</v>
+        <v>0.5490117254547601</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>GMRAIRPORT</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TORNTPOWER</t>
+          <t>PATANJALI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1535.4</v>
+        <v>523</v>
       </c>
       <c r="C10" t="n">
-        <v>1569</v>
+        <v>527.8</v>
       </c>
       <c r="D10" t="n">
-        <v>1525.2</v>
+        <v>513</v>
       </c>
       <c r="E10" t="n">
-        <v>1544</v>
+        <v>514</v>
       </c>
       <c r="F10" t="n">
-        <v>902713</v>
+        <v>2476713</v>
       </c>
       <c r="G10" t="n">
-        <v>618797</v>
+        <v>1556379</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4588192896862784</v>
+        <v>0.5913302608169347</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>TORNTPOWER</t>
+          <t>PATANJALI</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>HINDPETRO</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2252.5</v>
+        <v>449.7</v>
       </c>
       <c r="C11" t="n">
-        <v>2257.9</v>
+        <v>454.7</v>
       </c>
       <c r="D11" t="n">
-        <v>2235</v>
+        <v>432.45</v>
       </c>
       <c r="E11" t="n">
-        <v>2252</v>
+        <v>437.35</v>
       </c>
       <c r="F11" t="n">
-        <v>1074791</v>
+        <v>5442008</v>
       </c>
       <c r="G11" t="n">
-        <v>745467</v>
+        <v>3515127</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4417687167909512</v>
+        <v>0.5481682454147461</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>HINDPETRO</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BLUESTARCO</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1960</v>
+        <v>1035</v>
       </c>
       <c r="C12" t="n">
-        <v>1968</v>
+        <v>1078.9</v>
       </c>
       <c r="D12" t="n">
-        <v>1933.4</v>
+        <v>1032.15</v>
       </c>
       <c r="E12" t="n">
-        <v>1967</v>
+        <v>1075</v>
       </c>
       <c r="F12" t="n">
-        <v>315256</v>
+        <v>2096497</v>
       </c>
       <c r="G12" t="n">
-        <v>221246</v>
+        <v>1411849</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4249116368205527</v>
+        <v>0.4849300456351919</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BLUESTARCO</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>209</v>
+        <v>2414.9</v>
       </c>
       <c r="C13" t="n">
-        <v>211.02</v>
+        <v>2484.9</v>
       </c>
       <c r="D13" t="n">
-        <v>208.62</v>
+        <v>2400.2</v>
       </c>
       <c r="E13" t="n">
-        <v>210.6</v>
+        <v>2448</v>
       </c>
       <c r="F13" t="n">
-        <v>12888307</v>
+        <v>2689531</v>
       </c>
       <c r="G13" t="n">
-        <v>8533992</v>
+        <v>1777072</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5102319055372914</v>
+        <v>0.5134620319266749</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>MCX</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>YESBANK</t>
+          <t>KAYNES</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>20.89</v>
+        <v>3871</v>
       </c>
       <c r="C14" t="n">
-        <v>21.01</v>
+        <v>3982</v>
       </c>
       <c r="D14" t="n">
-        <v>20.61</v>
+        <v>3865.1</v>
       </c>
       <c r="E14" t="n">
-        <v>20.85</v>
+        <v>3916.2</v>
       </c>
       <c r="F14" t="n">
-        <v>81564930</v>
+        <v>1305141</v>
       </c>
       <c r="G14" t="n">
-        <v>51401565</v>
+        <v>893784</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5868180278168573</v>
+        <v>0.4602420719099917</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>YESBANK</t>
+          <t>KAYNES</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>INDUSTOWER</t>
+          <t>NBCC</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>469.9</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="C15" t="n">
-        <v>473</v>
+        <v>95.93000000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>464.05</v>
+        <v>93.73999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>471</v>
+        <v>94.75</v>
       </c>
       <c r="F15" t="n">
-        <v>5575559</v>
+        <v>10414932</v>
       </c>
       <c r="G15" t="n">
-        <v>3640333</v>
+        <v>7043891</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5316068612404414</v>
+        <v>0.4785765424252022</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>INDUSTOWER</t>
+          <t>NBCC</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HUDCO</t>
+          <t>GRANULES</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>194</v>
+        <v>599.6</v>
       </c>
       <c r="C16" t="n">
-        <v>194</v>
+        <v>606.95</v>
       </c>
       <c r="D16" t="n">
-        <v>188.36</v>
+        <v>594.95</v>
       </c>
       <c r="E16" t="n">
-        <v>190.3</v>
+        <v>599.95</v>
       </c>
       <c r="F16" t="n">
-        <v>4069852</v>
+        <v>775187</v>
       </c>
       <c r="G16" t="n">
-        <v>2718891</v>
+        <v>532195</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4968794262072294</v>
+        <v>0.4565845225904039</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>HUDCO</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>IRCTC</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>636.9</v>
-      </c>
-      <c r="C17" t="n">
-        <v>636.9</v>
-      </c>
-      <c r="D17" t="n">
-        <v>611.15</v>
-      </c>
-      <c r="E17" t="n">
-        <v>614.8</v>
-      </c>
-      <c r="F17" t="n">
-        <v>4217676</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2983677</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.4135833067721473</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>IRCTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>TATAELXSI</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>4675.5</v>
-      </c>
-      <c r="C18" t="n">
-        <v>4700</v>
-      </c>
-      <c r="D18" t="n">
-        <v>4455</v>
-      </c>
-      <c r="E18" t="n">
-        <v>4518</v>
-      </c>
-      <c r="F18" t="n">
-        <v>465584</v>
-      </c>
-      <c r="G18" t="n">
-        <v>327068</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.4235082612790001</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>TATAELXSI</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>KPITTECH</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>809</v>
-      </c>
-      <c r="C19" t="n">
-        <v>809.3</v>
-      </c>
-      <c r="D19" t="n">
-        <v>758</v>
-      </c>
-      <c r="E19" t="n">
-        <v>760</v>
-      </c>
-      <c r="F19" t="n">
-        <v>3617378</v>
-      </c>
-      <c r="G19" t="n">
-        <v>2364931</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.5295913495996289</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>KPITTECH</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>IEX</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>125.5</v>
-      </c>
-      <c r="C20" t="n">
-        <v>126.5</v>
-      </c>
-      <c r="D20" t="n">
-        <v>124.5</v>
-      </c>
-      <c r="E20" t="n">
-        <v>126.2</v>
-      </c>
-      <c r="F20" t="n">
-        <v>6405727</v>
-      </c>
-      <c r="G20" t="n">
-        <v>4319720</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.4829032900280574</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>IEX</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>CDSL</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1325.9</v>
-      </c>
-      <c r="C21" t="n">
-        <v>1342</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1318.4</v>
-      </c>
-      <c r="E21" t="n">
-        <v>1328.2</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1312682</v>
-      </c>
-      <c r="G21" t="n">
-        <v>901439</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.4562072419764399</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>CDSL</t>
+          <t>GRANULES</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,759 +479,429 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2596</v>
+        <v>1391</v>
       </c>
       <c r="C2" t="n">
-        <v>2654.2</v>
+        <v>1405</v>
       </c>
       <c r="D2" t="n">
-        <v>2595</v>
+        <v>1368</v>
       </c>
       <c r="E2" t="n">
-        <v>2629</v>
+        <v>1373</v>
       </c>
       <c r="F2" t="n">
-        <v>3621285</v>
+        <v>2329520</v>
       </c>
       <c r="G2" t="n">
-        <v>7798833</v>
+        <v>5703505</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5356632203818187</v>
+        <v>-0.5915634333624674</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>HCLTECH</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1742</v>
+        <v>1329.2</v>
       </c>
       <c r="C3" t="n">
-        <v>1770.4</v>
+        <v>1329.2</v>
       </c>
       <c r="D3" t="n">
-        <v>1733.4</v>
+        <v>1310.6</v>
       </c>
       <c r="E3" t="n">
-        <v>1763.3</v>
+        <v>1318.4</v>
       </c>
       <c r="F3" t="n">
-        <v>1200997</v>
+        <v>438946</v>
       </c>
       <c r="G3" t="n">
-        <v>2769363</v>
+        <v>991399</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5663273467580812</v>
+        <v>-0.5572458717428603</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1326.7</v>
+        <v>1044</v>
       </c>
       <c r="C4" t="n">
-        <v>1349</v>
+        <v>1059.7</v>
       </c>
       <c r="D4" t="n">
-        <v>1326.7</v>
+        <v>1037.2</v>
       </c>
       <c r="E4" t="n">
-        <v>1345</v>
+        <v>1052.5</v>
       </c>
       <c r="F4" t="n">
-        <v>1018377</v>
+        <v>1180849</v>
       </c>
       <c r="G4" t="n">
-        <v>2109672</v>
+        <v>2557686</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5172818333845262</v>
+        <v>-0.538313538096545</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>NAUKRI</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>IRFC</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>276.5</v>
+        <v>104.4</v>
       </c>
       <c r="C5" t="n">
-        <v>278.95</v>
+        <v>105.29</v>
       </c>
       <c r="D5" t="n">
-        <v>274</v>
+        <v>102.54</v>
       </c>
       <c r="E5" t="n">
-        <v>277.25</v>
+        <v>103.2</v>
       </c>
       <c r="F5" t="n">
-        <v>7573116</v>
+        <v>22825499</v>
       </c>
       <c r="G5" t="n">
-        <v>16311581</v>
+        <v>56904412</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5357215220278156</v>
+        <v>-0.59887997788291</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>IRFC</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2050</v>
+        <v>620.5</v>
       </c>
       <c r="C6" t="n">
-        <v>2074.9</v>
+        <v>620.5</v>
       </c>
       <c r="D6" t="n">
-        <v>2043</v>
+        <v>608.15</v>
       </c>
       <c r="E6" t="n">
-        <v>2043</v>
+        <v>610</v>
       </c>
       <c r="F6" t="n">
-        <v>508162</v>
+        <v>4592362</v>
       </c>
       <c r="G6" t="n">
-        <v>1054129</v>
+        <v>10715612</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5179318660239876</v>
+        <v>-0.5714325975968522</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>HINDZINC</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>CUMMINSIND</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1028</v>
+        <v>4944</v>
       </c>
       <c r="C7" t="n">
-        <v>1034</v>
+        <v>4975</v>
       </c>
       <c r="D7" t="n">
-        <v>1013.4</v>
+        <v>4916.3</v>
       </c>
       <c r="E7" t="n">
-        <v>1020.4</v>
+        <v>4970</v>
       </c>
       <c r="F7" t="n">
-        <v>3182612</v>
+        <v>346327</v>
       </c>
       <c r="G7" t="n">
-        <v>6610984</v>
+        <v>708623</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5185872481312918</v>
+        <v>-0.5112676274972728</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>CUMMINSIND</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>EXIDEIND</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2089.7</v>
+        <v>338.65</v>
       </c>
       <c r="C8" t="n">
-        <v>2106</v>
+        <v>340.3</v>
       </c>
       <c r="D8" t="n">
-        <v>2069.5</v>
+        <v>334.85</v>
       </c>
       <c r="E8" t="n">
-        <v>2075</v>
+        <v>339.8</v>
       </c>
       <c r="F8" t="n">
-        <v>355352</v>
+        <v>1055014</v>
       </c>
       <c r="G8" t="n">
-        <v>841918</v>
+        <v>2484898</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5779256412144651</v>
+        <v>-0.5754296554627192</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>EXIDEIND</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6101</v>
+        <v>363.6</v>
       </c>
       <c r="C9" t="n">
-        <v>6180</v>
+        <v>363.95</v>
       </c>
       <c r="D9" t="n">
-        <v>6046.5</v>
+        <v>357.75</v>
       </c>
       <c r="E9" t="n">
-        <v>6158</v>
+        <v>360.5</v>
       </c>
       <c r="F9" t="n">
-        <v>363747</v>
+        <v>6425639</v>
       </c>
       <c r="G9" t="n">
-        <v>782563</v>
+        <v>14931791</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5351850266368331</v>
+        <v>-0.5696672288006174</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LTIM</t>
+          <t>GMRAIRPORT</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4524</v>
+        <v>101.81</v>
       </c>
       <c r="C10" t="n">
-        <v>4661.5</v>
+        <v>103</v>
       </c>
       <c r="D10" t="n">
-        <v>4515.5</v>
+        <v>101.51</v>
       </c>
       <c r="E10" t="n">
-        <v>4549.5</v>
+        <v>102.35</v>
       </c>
       <c r="F10" t="n">
-        <v>370208</v>
+        <v>4703063</v>
       </c>
       <c r="G10" t="n">
-        <v>883696</v>
+        <v>10916245</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5810686027774257</v>
+        <v>-0.5691684274217004</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>LTIM</t>
+          <t>GMRAIRPORT</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>DALBHARAT</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4420</v>
+        <v>2056.5</v>
       </c>
       <c r="C11" t="n">
-        <v>4443.5</v>
+        <v>2080</v>
       </c>
       <c r="D11" t="n">
-        <v>4358</v>
+        <v>2040</v>
       </c>
       <c r="E11" t="n">
-        <v>4435</v>
+        <v>2060.6</v>
       </c>
       <c r="F11" t="n">
-        <v>359916</v>
+        <v>97795</v>
       </c>
       <c r="G11" t="n">
-        <v>846802</v>
+        <v>223028</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5749703000229097</v>
+        <v>-0.5615124558351418</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>DALBHARAT</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2208.7</v>
+        <v>547</v>
       </c>
       <c r="C12" t="n">
-        <v>2233.4</v>
+        <v>550.9</v>
       </c>
       <c r="D12" t="n">
-        <v>2186.3</v>
+        <v>540.2</v>
       </c>
       <c r="E12" t="n">
-        <v>2231</v>
+        <v>545</v>
       </c>
       <c r="F12" t="n">
-        <v>627610</v>
+        <v>887973</v>
       </c>
       <c r="G12" t="n">
-        <v>1362267</v>
+        <v>2120355</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5392900217064643</v>
+        <v>-0.5812149380646165</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>JSL</t>
+          <t>LTF</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>797</v>
+        <v>304.65</v>
       </c>
       <c r="C13" t="n">
-        <v>808.3</v>
+        <v>304.65</v>
       </c>
       <c r="D13" t="n">
-        <v>789.5</v>
+        <v>296.4</v>
       </c>
       <c r="E13" t="n">
-        <v>803.4</v>
+        <v>299.3</v>
       </c>
       <c r="F13" t="n">
-        <v>825590</v>
+        <v>3806988</v>
       </c>
       <c r="G13" t="n">
-        <v>1700672</v>
+        <v>9098084</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.5145507187746962</v>
+        <v>-0.5815615683477972</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>JSL</t>
+          <t>LTF</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>TATACHEM</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2230</v>
+        <v>720</v>
       </c>
       <c r="C14" t="n">
-        <v>2323.4</v>
+        <v>726.9</v>
       </c>
       <c r="D14" t="n">
-        <v>2227.3</v>
+        <v>713.2</v>
       </c>
       <c r="E14" t="n">
-        <v>2250</v>
+        <v>715</v>
       </c>
       <c r="F14" t="n">
-        <v>667290</v>
+        <v>264578</v>
       </c>
       <c r="G14" t="n">
-        <v>1348323</v>
+        <v>544976</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5050963307753409</v>
+        <v>-0.5145144006341563</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>MFSL</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1844.6</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1857.5</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1836.4</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1855.8</v>
-      </c>
-      <c r="F15" t="n">
-        <v>378587</v>
-      </c>
-      <c r="G15" t="n">
-        <v>783572</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-0.5168446549902243</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>MFSL</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>TATATECH</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>573</v>
-      </c>
-      <c r="C16" t="n">
-        <v>584.65</v>
-      </c>
-      <c r="D16" t="n">
-        <v>573</v>
-      </c>
-      <c r="E16" t="n">
-        <v>576.25</v>
-      </c>
-      <c r="F16" t="n">
-        <v>891075</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1747763</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-0.4901625678081067</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>TATATECH</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>PAYTM</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1142.7</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1147.8</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1119.7</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1135.6</v>
-      </c>
-      <c r="F17" t="n">
-        <v>2046403</v>
-      </c>
-      <c r="G17" t="n">
-        <v>4165307</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-0.5087029599498909</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>PAYTM</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>COFORGE</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1227.9</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1265.9</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1208</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1211.8</v>
-      </c>
-      <c r="F18" t="n">
-        <v>5227982</v>
-      </c>
-      <c r="G18" t="n">
-        <v>10454471</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-0.4999285951436472</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>COFORGE</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>BANKINDIA</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>175.8</v>
-      </c>
-      <c r="C19" t="n">
-        <v>176.35</v>
-      </c>
-      <c r="D19" t="n">
-        <v>173.7</v>
-      </c>
-      <c r="E19" t="n">
-        <v>175.2</v>
-      </c>
-      <c r="F19" t="n">
-        <v>9784182</v>
-      </c>
-      <c r="G19" t="n">
-        <v>22315167</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-0.5615456518877945</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>BANKINDIA</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>JUBLFOOD</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>518.9</v>
-      </c>
-      <c r="C20" t="n">
-        <v>525.55</v>
-      </c>
-      <c r="D20" t="n">
-        <v>510.45</v>
-      </c>
-      <c r="E20" t="n">
-        <v>517</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1325873</v>
-      </c>
-      <c r="G20" t="n">
-        <v>3283010</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-0.5961410413005138</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>JUBLFOOD</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>RBLBANK</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>328</v>
-      </c>
-      <c r="C21" t="n">
-        <v>332.95</v>
-      </c>
-      <c r="D21" t="n">
-        <v>322.55</v>
-      </c>
-      <c r="E21" t="n">
-        <v>330</v>
-      </c>
-      <c r="F21" t="n">
-        <v>4824687</v>
-      </c>
-      <c r="G21" t="n">
-        <v>9940401</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-0.5146385945597165</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>RBLBANK</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>PPLPHARMA</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>159.99</v>
-      </c>
-      <c r="C22" t="n">
-        <v>162.5</v>
-      </c>
-      <c r="D22" t="n">
-        <v>159.35</v>
-      </c>
-      <c r="E22" t="n">
-        <v>161.05</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1292223</v>
-      </c>
-      <c r="G22" t="n">
-        <v>2663225</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-0.5147901510386843</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>PPLPHARMA</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>ABFRL</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>68.33</v>
-      </c>
-      <c r="C23" t="n">
-        <v>69.8</v>
-      </c>
-      <c r="D23" t="n">
-        <v>68.33</v>
-      </c>
-      <c r="E23" t="n">
-        <v>68.68000000000001</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1019290</v>
-      </c>
-      <c r="G23" t="n">
-        <v>2176039</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-0.5315846820760106</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>ABFRL</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>KFINTECH</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>1004</v>
-      </c>
-      <c r="C24" t="n">
-        <v>1009.6</v>
-      </c>
-      <c r="D24" t="n">
-        <v>990.3</v>
-      </c>
-      <c r="E24" t="n">
-        <v>998</v>
-      </c>
-      <c r="F24" t="n">
-        <v>391925</v>
-      </c>
-      <c r="G24" t="n">
-        <v>782889</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-0.4993862476034278</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>KFINTECH</t>
+          <t>TATACHEM</t>
         </is>
       </c>
     </row>
@@ -1246,7 +916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1299,495 +969,462 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7930</v>
+        <v>440.6</v>
       </c>
       <c r="C2" t="n">
-        <v>8082</v>
+        <v>449.9</v>
       </c>
       <c r="D2" t="n">
-        <v>7772</v>
+        <v>440</v>
       </c>
       <c r="E2" t="n">
-        <v>8040</v>
+        <v>449.3</v>
       </c>
       <c r="F2" t="n">
-        <v>618719</v>
+        <v>13738213</v>
       </c>
       <c r="G2" t="n">
-        <v>430812</v>
+        <v>9469190</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4361693731836625</v>
+        <v>0.4508329645935925</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>BEL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1567</v>
+        <v>1398.5</v>
       </c>
       <c r="C3" t="n">
-        <v>1584</v>
+        <v>1412.9</v>
       </c>
       <c r="D3" t="n">
-        <v>1518.5</v>
+        <v>1391.9</v>
       </c>
       <c r="E3" t="n">
-        <v>1529</v>
+        <v>1409</v>
       </c>
       <c r="F3" t="n">
-        <v>2153982</v>
+        <v>16683858</v>
       </c>
       <c r="G3" t="n">
-        <v>1360612</v>
+        <v>10728792</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5830979000626189</v>
+        <v>0.555054660394199</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>RELIANCE</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>903.5</v>
+        <v>2080</v>
       </c>
       <c r="C4" t="n">
-        <v>921</v>
+        <v>2103.4</v>
       </c>
       <c r="D4" t="n">
-        <v>902.1</v>
+        <v>2063.3</v>
       </c>
       <c r="E4" t="n">
-        <v>918.7</v>
+        <v>2084.9</v>
       </c>
       <c r="F4" t="n">
-        <v>564586</v>
+        <v>567098</v>
       </c>
       <c r="G4" t="n">
-        <v>369018</v>
+        <v>355352</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5299687278127354</v>
+        <v>0.5958767644476463</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>SBILIFE</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KPITTECH</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>764.1</v>
+        <v>912</v>
       </c>
       <c r="C5" t="n">
-        <v>805</v>
+        <v>912</v>
       </c>
       <c r="D5" t="n">
-        <v>764</v>
+        <v>895</v>
       </c>
       <c r="E5" t="n">
-        <v>791.9</v>
+        <v>896</v>
       </c>
       <c r="F5" t="n">
-        <v>5094300</v>
+        <v>41165937</v>
       </c>
       <c r="G5" t="n">
-        <v>3617378</v>
+        <v>27884303</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4082852275874957</v>
+        <v>0.4763122104934809</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>KPITTECH</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SONACOMS</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>530.2</v>
+        <v>2240</v>
       </c>
       <c r="C6" t="n">
-        <v>543.3</v>
+        <v>2273.2</v>
       </c>
       <c r="D6" t="n">
-        <v>529.05</v>
+        <v>2230</v>
       </c>
       <c r="E6" t="n">
-        <v>542.5</v>
+        <v>2255</v>
       </c>
       <c r="F6" t="n">
-        <v>1312350</v>
+        <v>765678</v>
       </c>
       <c r="G6" t="n">
-        <v>821398</v>
+        <v>517093</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5977029405963978</v>
+        <v>0.4807355736782358</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>SONACOMS</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>UNITDSPR</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1120</v>
+        <v>1405.5</v>
       </c>
       <c r="C7" t="n">
-        <v>1137.3</v>
+        <v>1409.8</v>
       </c>
       <c r="D7" t="n">
-        <v>1104.5</v>
+        <v>1375.7</v>
       </c>
       <c r="E7" t="n">
-        <v>1137.3</v>
+        <v>1390.4</v>
       </c>
       <c r="F7" t="n">
-        <v>682336</v>
+        <v>559059</v>
       </c>
       <c r="G7" t="n">
-        <v>432011</v>
+        <v>381768</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5794412642270683</v>
+        <v>0.4643946061482366</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>UNITDSPR</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>IDFCFIRSTB</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>351.5</v>
+        <v>70.22</v>
       </c>
       <c r="C8" t="n">
-        <v>360</v>
+        <v>73.16</v>
       </c>
       <c r="D8" t="n">
-        <v>350.2</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>352.9</v>
+        <v>72.73999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>16813613</v>
+        <v>142273285</v>
       </c>
       <c r="G8" t="n">
-        <v>10786939</v>
+        <v>90865348</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5587010365034975</v>
+        <v>0.5657595346468051</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>IDFCFIRSTB</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GMRAIRPORT</t>
+          <t>IGL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>102.78</v>
+        <v>168.9</v>
       </c>
       <c r="C9" t="n">
-        <v>103.03</v>
+        <v>172.68</v>
       </c>
       <c r="D9" t="n">
-        <v>101.5</v>
+        <v>168.42</v>
       </c>
       <c r="E9" t="n">
-        <v>102.15</v>
+        <v>172</v>
       </c>
       <c r="F9" t="n">
-        <v>10916245</v>
+        <v>2845471</v>
       </c>
       <c r="G9" t="n">
-        <v>7047232</v>
+        <v>1913191</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5490117254547601</v>
+        <v>0.4872906050676592</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>GMRAIRPORT</t>
+          <t>IGL</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PATANJALI</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>523</v>
+        <v>200</v>
       </c>
       <c r="C10" t="n">
-        <v>527.8</v>
+        <v>203.2</v>
       </c>
       <c r="D10" t="n">
-        <v>513</v>
+        <v>197.9</v>
       </c>
       <c r="E10" t="n">
-        <v>514</v>
+        <v>201.45</v>
       </c>
       <c r="F10" t="n">
-        <v>2476713</v>
+        <v>30109110</v>
       </c>
       <c r="G10" t="n">
-        <v>1556379</v>
+        <v>20245353</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5913302608169347</v>
+        <v>0.4872109169941369</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>PATANJALI</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HINDPETRO</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>449.7</v>
+        <v>2784</v>
       </c>
       <c r="C11" t="n">
-        <v>454.7</v>
+        <v>2832</v>
       </c>
       <c r="D11" t="n">
-        <v>432.45</v>
+        <v>2752</v>
       </c>
       <c r="E11" t="n">
-        <v>437.35</v>
+        <v>2774</v>
       </c>
       <c r="F11" t="n">
-        <v>5442008</v>
+        <v>4270945</v>
       </c>
       <c r="G11" t="n">
-        <v>3515127</v>
+        <v>2863159</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5481682454147461</v>
+        <v>0.4916897734285801</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>HINDPETRO</t>
+          <t>BSE</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1035</v>
+        <v>1861.9</v>
       </c>
       <c r="C12" t="n">
-        <v>1078.9</v>
+        <v>1869.6</v>
       </c>
       <c r="D12" t="n">
-        <v>1032.15</v>
+        <v>1839.4</v>
       </c>
       <c r="E12" t="n">
-        <v>1075</v>
+        <v>1854.6</v>
       </c>
       <c r="F12" t="n">
-        <v>2096497</v>
+        <v>568774</v>
       </c>
       <c r="G12" t="n">
-        <v>1411849</v>
+        <v>378587</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4849300456351919</v>
+        <v>0.5023600916037794</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>MFSL</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2414.9</v>
+        <v>1564</v>
       </c>
       <c r="C13" t="n">
-        <v>2484.9</v>
+        <v>1579</v>
       </c>
       <c r="D13" t="n">
-        <v>2400.2</v>
+        <v>1547.5</v>
       </c>
       <c r="E13" t="n">
-        <v>2448</v>
+        <v>1561.2</v>
       </c>
       <c r="F13" t="n">
-        <v>2689531</v>
+        <v>725480</v>
       </c>
       <c r="G13" t="n">
-        <v>1777072</v>
+        <v>499561</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5134620319266749</v>
+        <v>0.4522350623847738</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>KAYNES</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3871</v>
+        <v>10361</v>
       </c>
       <c r="C14" t="n">
-        <v>3982</v>
+        <v>10462</v>
       </c>
       <c r="D14" t="n">
-        <v>3865.1</v>
+        <v>10081</v>
       </c>
       <c r="E14" t="n">
-        <v>3916.2</v>
+        <v>10120</v>
       </c>
       <c r="F14" t="n">
-        <v>1305141</v>
+        <v>562899</v>
       </c>
       <c r="G14" t="n">
-        <v>893784</v>
+        <v>384975</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4602420719099917</v>
+        <v>0.462170270796805</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>KAYNES</t>
+          <t>DIXON</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NBCC</t>
+          <t>NCC</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>94.90000000000001</v>
+        <v>152</v>
       </c>
       <c r="C15" t="n">
-        <v>95.93000000000001</v>
+        <v>154.99</v>
       </c>
       <c r="D15" t="n">
-        <v>93.73999999999999</v>
+        <v>151.22</v>
       </c>
       <c r="E15" t="n">
-        <v>94.75</v>
+        <v>153.3</v>
       </c>
       <c r="F15" t="n">
-        <v>10414932</v>
+        <v>2533427</v>
       </c>
       <c r="G15" t="n">
-        <v>7043891</v>
+        <v>1678509</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4785765424252022</v>
+        <v>0.5093317938718231</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>NBCC</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>GRANULES</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>599.6</v>
-      </c>
-      <c r="C16" t="n">
-        <v>606.95</v>
-      </c>
-      <c r="D16" t="n">
-        <v>594.95</v>
-      </c>
-      <c r="E16" t="n">
-        <v>599.95</v>
-      </c>
-      <c r="F16" t="n">
-        <v>775187</v>
-      </c>
-      <c r="G16" t="n">
-        <v>532195</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.4565845225904039</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>GRANULES</t>
+          <t>NCC</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,429 +479,231 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1391</v>
+        <v>963</v>
       </c>
       <c r="C2" t="n">
-        <v>1405</v>
+        <v>968</v>
       </c>
       <c r="D2" t="n">
-        <v>1368</v>
+        <v>951.2</v>
       </c>
       <c r="E2" t="n">
-        <v>1373</v>
+        <v>957</v>
       </c>
       <c r="F2" t="n">
-        <v>2329520</v>
+        <v>3745120</v>
       </c>
       <c r="G2" t="n">
-        <v>5703505</v>
+        <v>8974624</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5915634333624674</v>
+        <v>-0.5826989520675183</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>SYNGENE</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1329.2</v>
+        <v>425</v>
       </c>
       <c r="C3" t="n">
-        <v>1329.2</v>
+        <v>427.25</v>
       </c>
       <c r="D3" t="n">
-        <v>1310.6</v>
+        <v>418.1</v>
       </c>
       <c r="E3" t="n">
-        <v>1318.4</v>
+        <v>422</v>
       </c>
       <c r="F3" t="n">
-        <v>438946</v>
+        <v>870034</v>
       </c>
       <c r="G3" t="n">
-        <v>991399</v>
+        <v>1977089</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5572458717428603</v>
+        <v>-0.5599419146027316</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>SYNGENE</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>IGL</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1044</v>
+        <v>172.04</v>
       </c>
       <c r="C4" t="n">
-        <v>1059.7</v>
+        <v>172.2</v>
       </c>
       <c r="D4" t="n">
-        <v>1037.2</v>
+        <v>170.05</v>
       </c>
       <c r="E4" t="n">
-        <v>1052.5</v>
+        <v>170.48</v>
       </c>
       <c r="F4" t="n">
-        <v>1180849</v>
+        <v>1149810</v>
       </c>
       <c r="G4" t="n">
-        <v>2557686</v>
+        <v>2845471</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.538313538096545</v>
+        <v>-0.5959157552475495</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>IGL</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IRFC</t>
+          <t>YESBANK</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>104.4</v>
+        <v>21.01</v>
       </c>
       <c r="C5" t="n">
-        <v>105.29</v>
+        <v>21.01</v>
       </c>
       <c r="D5" t="n">
-        <v>102.54</v>
+        <v>20.65</v>
       </c>
       <c r="E5" t="n">
-        <v>103.2</v>
+        <v>20.7</v>
       </c>
       <c r="F5" t="n">
-        <v>22825499</v>
+        <v>98977180</v>
       </c>
       <c r="G5" t="n">
-        <v>56904412</v>
+        <v>214470676</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.59887997788291</v>
+        <v>-0.5385048350386139</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>IRFC</t>
+          <t>YESBANK</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>PATANJALI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>620.5</v>
+        <v>514</v>
       </c>
       <c r="C6" t="n">
-        <v>620.5</v>
+        <v>518.2</v>
       </c>
       <c r="D6" t="n">
-        <v>608.15</v>
+        <v>502.65</v>
       </c>
       <c r="E6" t="n">
-        <v>610</v>
+        <v>504.55</v>
       </c>
       <c r="F6" t="n">
-        <v>4592362</v>
+        <v>1817346</v>
       </c>
       <c r="G6" t="n">
-        <v>10715612</v>
+        <v>4079114</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5714325975968522</v>
+        <v>-0.5544753100795908</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>PATANJALI</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4944</v>
+        <v>1290</v>
       </c>
       <c r="C7" t="n">
-        <v>4975</v>
+        <v>1299</v>
       </c>
       <c r="D7" t="n">
-        <v>4916.3</v>
+        <v>1268</v>
       </c>
       <c r="E7" t="n">
-        <v>4970</v>
+        <v>1272</v>
       </c>
       <c r="F7" t="n">
-        <v>346327</v>
+        <v>1682338</v>
       </c>
       <c r="G7" t="n">
-        <v>708623</v>
+        <v>3319781</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5112676274972728</v>
+        <v>-0.4932382587887574</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>CDSL</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EXIDEIND</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>338.65</v>
+        <v>442.35</v>
       </c>
       <c r="C8" t="n">
-        <v>340.3</v>
+        <v>445.75</v>
       </c>
       <c r="D8" t="n">
-        <v>334.85</v>
+        <v>431.15</v>
       </c>
       <c r="E8" t="n">
-        <v>339.8</v>
+        <v>433.6</v>
       </c>
       <c r="F8" t="n">
-        <v>1055014</v>
+        <v>1104679</v>
       </c>
       <c r="G8" t="n">
-        <v>2484898</v>
+        <v>2498925</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5754296554627192</v>
+        <v>-0.5579383134747942</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>EXIDEIND</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>NATIONALUM</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>363.6</v>
-      </c>
-      <c r="C9" t="n">
-        <v>363.95</v>
-      </c>
-      <c r="D9" t="n">
-        <v>357.75</v>
-      </c>
-      <c r="E9" t="n">
-        <v>360.5</v>
-      </c>
-      <c r="F9" t="n">
-        <v>6425639</v>
-      </c>
-      <c r="G9" t="n">
-        <v>14931791</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-0.5696672288006174</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>NATIONALUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>GMRAIRPORT</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>101.81</v>
-      </c>
-      <c r="C10" t="n">
-        <v>103</v>
-      </c>
-      <c r="D10" t="n">
-        <v>101.51</v>
-      </c>
-      <c r="E10" t="n">
-        <v>102.35</v>
-      </c>
-      <c r="F10" t="n">
-        <v>4703063</v>
-      </c>
-      <c r="G10" t="n">
-        <v>10916245</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-0.5691684274217004</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>GMRAIRPORT</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>DALBHARAT</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2056.5</v>
-      </c>
-      <c r="C11" t="n">
-        <v>2080</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E11" t="n">
-        <v>2060.6</v>
-      </c>
-      <c r="F11" t="n">
-        <v>97795</v>
-      </c>
-      <c r="G11" t="n">
-        <v>223028</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-0.5615124558351418</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>DALBHARAT</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>LICHSGFIN</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>547</v>
-      </c>
-      <c r="C12" t="n">
-        <v>550.9</v>
-      </c>
-      <c r="D12" t="n">
-        <v>540.2</v>
-      </c>
-      <c r="E12" t="n">
-        <v>545</v>
-      </c>
-      <c r="F12" t="n">
-        <v>887973</v>
-      </c>
-      <c r="G12" t="n">
-        <v>2120355</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-0.5812149380646165</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>LICHSGFIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>LTF</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>304.65</v>
-      </c>
-      <c r="C13" t="n">
-        <v>304.65</v>
-      </c>
-      <c r="D13" t="n">
-        <v>296.4</v>
-      </c>
-      <c r="E13" t="n">
-        <v>299.3</v>
-      </c>
-      <c r="F13" t="n">
-        <v>3806988</v>
-      </c>
-      <c r="G13" t="n">
-        <v>9098084</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-0.5815615683477972</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>LTF</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>TATACHEM</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>720</v>
-      </c>
-      <c r="C14" t="n">
-        <v>726.9</v>
-      </c>
-      <c r="D14" t="n">
-        <v>713.2</v>
-      </c>
-      <c r="E14" t="n">
-        <v>715</v>
-      </c>
-      <c r="F14" t="n">
-        <v>264578</v>
-      </c>
-      <c r="G14" t="n">
-        <v>544976</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-0.5145144006341563</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>TATACHEM</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
     </row>
@@ -916,7 +718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -969,462 +771,660 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>440.6</v>
+        <v>2681.6</v>
       </c>
       <c r="C2" t="n">
-        <v>449.9</v>
+        <v>2688.6</v>
       </c>
       <c r="D2" t="n">
-        <v>440</v>
+        <v>2626.1</v>
       </c>
       <c r="E2" t="n">
-        <v>449.3</v>
+        <v>2639.7</v>
       </c>
       <c r="F2" t="n">
-        <v>13738213</v>
+        <v>5083717</v>
       </c>
       <c r="G2" t="n">
-        <v>9469190</v>
+        <v>3464267</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4508329645935925</v>
+        <v>0.467472628408838</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>TCS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>JIOFIN</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1398.5</v>
+        <v>257</v>
       </c>
       <c r="C3" t="n">
-        <v>1412.9</v>
+        <v>259.2</v>
       </c>
       <c r="D3" t="n">
-        <v>1391.9</v>
+        <v>254.65</v>
       </c>
       <c r="E3" t="n">
-        <v>1409</v>
+        <v>254.9</v>
       </c>
       <c r="F3" t="n">
-        <v>16683858</v>
+        <v>13283249</v>
       </c>
       <c r="G3" t="n">
-        <v>10728792</v>
+        <v>8691253</v>
       </c>
       <c r="H3" t="n">
-        <v>0.555054660394199</v>
+        <v>0.528346833304703</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>JIOFIN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2080</v>
+        <v>305.8</v>
       </c>
       <c r="C4" t="n">
-        <v>2103.4</v>
+        <v>305.8</v>
       </c>
       <c r="D4" t="n">
-        <v>2063.3</v>
+        <v>297.9</v>
       </c>
       <c r="E4" t="n">
-        <v>2084.9</v>
+        <v>299.5</v>
       </c>
       <c r="F4" t="n">
-        <v>567098</v>
+        <v>21400679</v>
       </c>
       <c r="G4" t="n">
-        <v>355352</v>
+        <v>14249515</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5958767644476463</v>
+        <v>0.501853150791448</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>POWERGRID</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>912</v>
+        <v>733</v>
       </c>
       <c r="C5" t="n">
-        <v>912</v>
+        <v>736.8</v>
       </c>
       <c r="D5" t="n">
-        <v>895</v>
+        <v>714.25</v>
       </c>
       <c r="E5" t="n">
-        <v>896</v>
+        <v>716.75</v>
       </c>
       <c r="F5" t="n">
-        <v>41165937</v>
+        <v>3416009</v>
       </c>
       <c r="G5" t="n">
-        <v>27884303</v>
+        <v>2329954</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4763122104934809</v>
+        <v>0.4661272282628756</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2240</v>
+        <v>1779</v>
       </c>
       <c r="C6" t="n">
-        <v>2273.2</v>
+        <v>1788.1</v>
       </c>
       <c r="D6" t="n">
-        <v>2230</v>
+        <v>1730.9</v>
       </c>
       <c r="E6" t="n">
-        <v>2255</v>
+        <v>1742.9</v>
       </c>
       <c r="F6" t="n">
-        <v>765678</v>
+        <v>3041489</v>
       </c>
       <c r="G6" t="n">
-        <v>517093</v>
+        <v>2076586</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4807355736782358</v>
+        <v>0.4646583382532676</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1405.5</v>
+        <v>15110</v>
       </c>
       <c r="C7" t="n">
-        <v>1409.8</v>
+        <v>15192</v>
       </c>
       <c r="D7" t="n">
-        <v>1375.7</v>
+        <v>14804</v>
       </c>
       <c r="E7" t="n">
-        <v>1390.4</v>
+        <v>14832</v>
       </c>
       <c r="F7" t="n">
-        <v>559059</v>
+        <v>478164</v>
       </c>
       <c r="G7" t="n">
-        <v>381768</v>
+        <v>308213</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4643946061482366</v>
+        <v>0.5514076304373923</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>MARUTI</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IDFCFIRSTB</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>70.22</v>
+        <v>2210</v>
       </c>
       <c r="C8" t="n">
-        <v>73.16</v>
+        <v>2216.4</v>
       </c>
       <c r="D8" t="n">
-        <v>69.84999999999999</v>
+        <v>2153</v>
       </c>
       <c r="E8" t="n">
-        <v>72.73999999999999</v>
+        <v>2157</v>
       </c>
       <c r="F8" t="n">
-        <v>142273285</v>
+        <v>1433096</v>
       </c>
       <c r="G8" t="n">
-        <v>90865348</v>
+        <v>915342</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5657595346468051</v>
+        <v>0.5656399465991946</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>IDFCFIRSTB</t>
+          <t>ADANIENT</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IGL</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>168.9</v>
+        <v>187.11</v>
       </c>
       <c r="C9" t="n">
-        <v>172.68</v>
+        <v>188.96</v>
       </c>
       <c r="D9" t="n">
-        <v>168.42</v>
+        <v>185.77</v>
       </c>
       <c r="E9" t="n">
-        <v>172</v>
+        <v>186.98</v>
       </c>
       <c r="F9" t="n">
-        <v>2845471</v>
+        <v>24422609</v>
       </c>
       <c r="G9" t="n">
-        <v>1913191</v>
+        <v>17206460</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4872906050676592</v>
+        <v>0.4193860329201939</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>IGL</t>
+          <t>IOC</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>200</v>
+        <v>610</v>
       </c>
       <c r="C10" t="n">
-        <v>203.2</v>
+        <v>613.05</v>
       </c>
       <c r="D10" t="n">
-        <v>197.9</v>
+        <v>600.9</v>
       </c>
       <c r="E10" t="n">
-        <v>201.45</v>
+        <v>602.05</v>
       </c>
       <c r="F10" t="n">
-        <v>30109110</v>
+        <v>4023729</v>
       </c>
       <c r="G10" t="n">
-        <v>20245353</v>
+        <v>2671861</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4872109169941369</v>
+        <v>0.5059649435356106</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>DLF</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2784</v>
+        <v>6135.5</v>
       </c>
       <c r="C11" t="n">
-        <v>2832</v>
+        <v>6142.5</v>
       </c>
       <c r="D11" t="n">
-        <v>2752</v>
+        <v>5975</v>
       </c>
       <c r="E11" t="n">
-        <v>2774</v>
+        <v>6000</v>
       </c>
       <c r="F11" t="n">
-        <v>4270945</v>
+        <v>350612</v>
       </c>
       <c r="G11" t="n">
-        <v>2863159</v>
+        <v>245317</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4916897734285801</v>
+        <v>0.4292201518851119</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1861.9</v>
+        <v>4001</v>
       </c>
       <c r="C12" t="n">
-        <v>1869.6</v>
+        <v>4001</v>
       </c>
       <c r="D12" t="n">
-        <v>1839.4</v>
+        <v>3900</v>
       </c>
       <c r="E12" t="n">
-        <v>1854.6</v>
+        <v>3910.8</v>
       </c>
       <c r="F12" t="n">
-        <v>568774</v>
+        <v>2191138</v>
       </c>
       <c r="G12" t="n">
-        <v>378587</v>
+        <v>1423043</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5023600916037794</v>
+        <v>0.5397552990317228</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>HAL</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TORNTPOWER</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1564</v>
+        <v>870.75</v>
       </c>
       <c r="C13" t="n">
-        <v>1579</v>
+        <v>870.75</v>
       </c>
       <c r="D13" t="n">
-        <v>1547.5</v>
+        <v>845</v>
       </c>
       <c r="E13" t="n">
-        <v>1561.2</v>
+        <v>846</v>
       </c>
       <c r="F13" t="n">
-        <v>725480</v>
+        <v>1088524</v>
       </c>
       <c r="G13" t="n">
-        <v>499561</v>
+        <v>740587</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4522350623847738</v>
+        <v>0.469812459575985</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>TORNTPOWER</t>
+          <t>LICI</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10361</v>
+        <v>8502</v>
       </c>
       <c r="C14" t="n">
-        <v>10462</v>
+        <v>8722</v>
       </c>
       <c r="D14" t="n">
-        <v>10081</v>
+        <v>8469.5</v>
       </c>
       <c r="E14" t="n">
-        <v>10120</v>
+        <v>8606.5</v>
       </c>
       <c r="F14" t="n">
-        <v>562899</v>
+        <v>926904</v>
       </c>
       <c r="G14" t="n">
-        <v>384975</v>
+        <v>629664</v>
       </c>
       <c r="H14" t="n">
-        <v>0.462170270796805</v>
+        <v>0.4720612898307669</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>POLYCAB</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NCC</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>152</v>
+        <v>988.1</v>
       </c>
       <c r="C15" t="n">
-        <v>154.99</v>
+        <v>1000</v>
       </c>
       <c r="D15" t="n">
-        <v>151.22</v>
+        <v>980</v>
       </c>
       <c r="E15" t="n">
-        <v>153.3</v>
+        <v>987</v>
       </c>
       <c r="F15" t="n">
-        <v>2533427</v>
+        <v>2343944</v>
       </c>
       <c r="G15" t="n">
-        <v>1678509</v>
+        <v>1532659</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5093317938718231</v>
+        <v>0.529331703921094</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>NCC</t>
+          <t>INDIANB</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>357.25</v>
+      </c>
+      <c r="C16" t="n">
+        <v>362.15</v>
+      </c>
+      <c r="D16" t="n">
+        <v>353.2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>354.55</v>
+      </c>
+      <c r="F16" t="n">
+        <v>9832443</v>
+      </c>
+      <c r="G16" t="n">
+        <v>6425639</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.5301891376095047</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SRF</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2601</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2615.2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2555</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2566</v>
+      </c>
+      <c r="F17" t="n">
+        <v>655543</v>
+      </c>
+      <c r="G17" t="n">
+        <v>441973</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.4832195631859865</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>SRF</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ALKEM</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>5752</v>
+      </c>
+      <c r="C18" t="n">
+        <v>5781.5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5614</v>
+      </c>
+      <c r="E18" t="n">
+        <v>5614</v>
+      </c>
+      <c r="F18" t="n">
+        <v>131566</v>
+      </c>
+      <c r="G18" t="n">
+        <v>84228</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.5620221304079404</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ALKEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>KPITTECH</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>800</v>
+      </c>
+      <c r="C19" t="n">
+        <v>808.4</v>
+      </c>
+      <c r="D19" t="n">
+        <v>768</v>
+      </c>
+      <c r="E19" t="n">
+        <v>771</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2159691</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1399625</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.5430497454675359</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>KPITTECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>621</v>
+      </c>
+      <c r="C20" t="n">
+        <v>634.65</v>
+      </c>
+      <c r="D20" t="n">
+        <v>616.55</v>
+      </c>
+      <c r="E20" t="n">
+        <v>627.5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1612812</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1039233</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.5519253141499548</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TITAGARH</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>714.75</v>
+      </c>
+      <c r="C21" t="n">
+        <v>714.75</v>
+      </c>
+      <c r="D21" t="n">
+        <v>699.05</v>
+      </c>
+      <c r="E21" t="n">
+        <v>700.5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>486019</v>
+      </c>
+      <c r="G21" t="n">
+        <v>328591</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.4791001579471136</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>TITAGARH</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,231 +479,396 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>963</v>
+        <v>1291</v>
       </c>
       <c r="C2" t="n">
-        <v>968</v>
+        <v>1298.8</v>
       </c>
       <c r="D2" t="n">
-        <v>951.2</v>
+        <v>1273</v>
       </c>
       <c r="E2" t="n">
-        <v>957</v>
+        <v>1288.9</v>
       </c>
       <c r="F2" t="n">
-        <v>3745120</v>
+        <v>9700361</v>
       </c>
       <c r="G2" t="n">
-        <v>8974624</v>
+        <v>23141724</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5826989520675183</v>
+        <v>-0.5808280748659866</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>INFY</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SYNGENE</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>425</v>
+        <v>5840</v>
       </c>
       <c r="C3" t="n">
-        <v>427.25</v>
+        <v>6073</v>
       </c>
       <c r="D3" t="n">
-        <v>418.1</v>
+        <v>5835</v>
       </c>
       <c r="E3" t="n">
-        <v>422</v>
+        <v>5980</v>
       </c>
       <c r="F3" t="n">
-        <v>870034</v>
+        <v>275442</v>
       </c>
       <c r="G3" t="n">
-        <v>1977089</v>
+        <v>602254</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5599419146027316</v>
+        <v>-0.5426481185679132</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SYNGENE</t>
+          <t>ABB</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IGL</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>172.04</v>
+        <v>1430</v>
       </c>
       <c r="C4" t="n">
-        <v>172.2</v>
+        <v>1476.8</v>
       </c>
       <c r="D4" t="n">
-        <v>170.05</v>
+        <v>1430</v>
       </c>
       <c r="E4" t="n">
-        <v>170.48</v>
+        <v>1469</v>
       </c>
       <c r="F4" t="n">
-        <v>1149810</v>
+        <v>699279</v>
       </c>
       <c r="G4" t="n">
-        <v>2845471</v>
+        <v>1606678</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5959157552475495</v>
+        <v>-0.5647671779908606</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>IGL</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>YESBANK</t>
+          <t>ICICIGI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.01</v>
+        <v>1835.6</v>
       </c>
       <c r="C5" t="n">
-        <v>21.01</v>
+        <v>1913.3</v>
       </c>
       <c r="D5" t="n">
-        <v>20.65</v>
+        <v>1835.6</v>
       </c>
       <c r="E5" t="n">
-        <v>20.7</v>
+        <v>1892.6</v>
       </c>
       <c r="F5" t="n">
-        <v>98977180</v>
+        <v>368735</v>
       </c>
       <c r="G5" t="n">
-        <v>214470676</v>
+        <v>852656</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5385048350386139</v>
+        <v>-0.567545411045017</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>YESBANK</t>
+          <t>ICICIGI</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PATANJALI</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>514</v>
+        <v>893.65</v>
       </c>
       <c r="C6" t="n">
-        <v>518.2</v>
+        <v>911.45</v>
       </c>
       <c r="D6" t="n">
-        <v>502.65</v>
+        <v>893</v>
       </c>
       <c r="E6" t="n">
-        <v>504.55</v>
+        <v>905.4</v>
       </c>
       <c r="F6" t="n">
-        <v>1817346</v>
+        <v>518652</v>
       </c>
       <c r="G6" t="n">
-        <v>4079114</v>
+        <v>1044991</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5544753100795908</v>
+        <v>-0.5036780221073675</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>PATANJALI</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1290</v>
+        <v>939</v>
       </c>
       <c r="C7" t="n">
-        <v>1299</v>
+        <v>955.95</v>
       </c>
       <c r="D7" t="n">
-        <v>1268</v>
+        <v>933.2</v>
       </c>
       <c r="E7" t="n">
-        <v>1272</v>
+        <v>943</v>
       </c>
       <c r="F7" t="n">
-        <v>1682338</v>
+        <v>1568186</v>
       </c>
       <c r="G7" t="n">
-        <v>3319781</v>
+        <v>3745120</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4932382587887574</v>
+        <v>-0.5812721621737087</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DELHIVERY</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>442.35</v>
+        <v>439.15</v>
       </c>
       <c r="C8" t="n">
-        <v>445.75</v>
+        <v>459.3</v>
       </c>
       <c r="D8" t="n">
-        <v>431.15</v>
+        <v>439.15</v>
       </c>
       <c r="E8" t="n">
-        <v>433.6</v>
+        <v>449.65</v>
       </c>
       <c r="F8" t="n">
-        <v>1104679</v>
+        <v>3235580</v>
       </c>
       <c r="G8" t="n">
-        <v>2498925</v>
+        <v>7170798</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5579383134747942</v>
+        <v>-0.5487838313113826</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>DELHIVERY</t>
+          <t>INDUSTOWER</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1186.2</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1223.9</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1186.2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1212</v>
+      </c>
+      <c r="F9" t="n">
+        <v>888443</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1781292</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.5012367427687319</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2205</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2310.1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2205</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2268</v>
+      </c>
+      <c r="F10" t="n">
+        <v>349774</v>
+      </c>
+      <c r="G10" t="n">
+        <v>861454</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.5939725162341808</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DALBHARAT</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1911.7</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1975</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1911.7</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1968.9</v>
+      </c>
+      <c r="F11" t="n">
+        <v>388419</v>
+      </c>
+      <c r="G11" t="n">
+        <v>775987</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.4994516660717254</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>DALBHARAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>6755</v>
+      </c>
+      <c r="C12" t="n">
+        <v>6980.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>6755</v>
+      </c>
+      <c r="E12" t="n">
+        <v>6860</v>
+      </c>
+      <c r="F12" t="n">
+        <v>106501</v>
+      </c>
+      <c r="G12" t="n">
+        <v>257521</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.5864376109132847</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ALKEM</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>5415</v>
+      </c>
+      <c r="C13" t="n">
+        <v>5619.5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5415</v>
+      </c>
+      <c r="E13" t="n">
+        <v>5582.5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>54260</v>
+      </c>
+      <c r="G13" t="n">
+        <v>131566</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.5875834182083517</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ALKEM</t>
         </is>
       </c>
     </row>
@@ -718,7 +883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -771,660 +936,495 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2681.6</v>
+        <v>1185</v>
       </c>
       <c r="C2" t="n">
-        <v>2688.6</v>
+        <v>1197.3</v>
       </c>
       <c r="D2" t="n">
-        <v>2626.1</v>
+        <v>1179.4</v>
       </c>
       <c r="E2" t="n">
-        <v>2639.7</v>
+        <v>1189.5</v>
       </c>
       <c r="F2" t="n">
-        <v>5083717</v>
+        <v>16270835</v>
       </c>
       <c r="G2" t="n">
-        <v>3464267</v>
+        <v>10700355</v>
       </c>
       <c r="H2" t="n">
-        <v>0.467472628408838</v>
+        <v>0.5205883356206407</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>SBIN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>257</v>
+        <v>442.1</v>
       </c>
       <c r="C3" t="n">
-        <v>259.2</v>
+        <v>456.7</v>
       </c>
       <c r="D3" t="n">
-        <v>254.65</v>
+        <v>441.7</v>
       </c>
       <c r="E3" t="n">
-        <v>254.9</v>
+        <v>454.15</v>
       </c>
       <c r="F3" t="n">
-        <v>13283249</v>
+        <v>35034174</v>
       </c>
       <c r="G3" t="n">
-        <v>8691253</v>
+        <v>22732811</v>
       </c>
       <c r="H3" t="n">
-        <v>0.528346833304703</v>
+        <v>0.541128107738194</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>BEL</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>305.8</v>
+        <v>307</v>
       </c>
       <c r="C4" t="n">
-        <v>305.8</v>
+        <v>315.75</v>
       </c>
       <c r="D4" t="n">
-        <v>297.9</v>
+        <v>307</v>
       </c>
       <c r="E4" t="n">
-        <v>299.5</v>
+        <v>314.7</v>
       </c>
       <c r="F4" t="n">
-        <v>21400679</v>
+        <v>22194311</v>
       </c>
       <c r="G4" t="n">
-        <v>14249515</v>
+        <v>13892595</v>
       </c>
       <c r="H4" t="n">
-        <v>0.501853150791448</v>
+        <v>0.5975640979960907</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>ITC</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>733</v>
+        <v>2093</v>
       </c>
       <c r="C5" t="n">
-        <v>736.8</v>
+        <v>2147.9</v>
       </c>
       <c r="D5" t="n">
-        <v>714.25</v>
+        <v>2073.7</v>
       </c>
       <c r="E5" t="n">
-        <v>716.75</v>
+        <v>2124</v>
       </c>
       <c r="F5" t="n">
-        <v>3416009</v>
+        <v>2134522</v>
       </c>
       <c r="G5" t="n">
-        <v>2329954</v>
+        <v>1433096</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4661272282628756</v>
+        <v>0.4894480202303265</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>ADANIENT</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1779</v>
+        <v>9725.5</v>
       </c>
       <c r="C6" t="n">
-        <v>1788.1</v>
+        <v>9941.5</v>
       </c>
       <c r="D6" t="n">
-        <v>1730.9</v>
+        <v>9565</v>
       </c>
       <c r="E6" t="n">
-        <v>1742.9</v>
+        <v>9769.5</v>
       </c>
       <c r="F6" t="n">
-        <v>3041489</v>
+        <v>330330</v>
       </c>
       <c r="G6" t="n">
-        <v>2076586</v>
+        <v>231926</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4646583382532676</v>
+        <v>0.424290506454645</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15110</v>
+        <v>3837</v>
       </c>
       <c r="C7" t="n">
-        <v>15192</v>
+        <v>3983</v>
       </c>
       <c r="D7" t="n">
-        <v>14804</v>
+        <v>3825.5</v>
       </c>
       <c r="E7" t="n">
-        <v>14832</v>
+        <v>3956.9</v>
       </c>
       <c r="F7" t="n">
-        <v>478164</v>
+        <v>3263290</v>
       </c>
       <c r="G7" t="n">
-        <v>308213</v>
+        <v>2191138</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5514076304373923</v>
+        <v>0.4893128593452352</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>HAL</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>IRFC</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2210</v>
+        <v>97.5</v>
       </c>
       <c r="C8" t="n">
-        <v>2216.4</v>
+        <v>101.35</v>
       </c>
       <c r="D8" t="n">
-        <v>2153</v>
+        <v>97.2</v>
       </c>
       <c r="E8" t="n">
-        <v>2157</v>
+        <v>99.73</v>
       </c>
       <c r="F8" t="n">
-        <v>1433096</v>
+        <v>27730177</v>
       </c>
       <c r="G8" t="n">
-        <v>915342</v>
+        <v>19027229</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5656399465991946</v>
+        <v>0.4573944004142695</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>IRFC</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>187.11</v>
+        <v>256.05</v>
       </c>
       <c r="C9" t="n">
-        <v>188.96</v>
+        <v>266.4</v>
       </c>
       <c r="D9" t="n">
-        <v>185.77</v>
+        <v>256.05</v>
       </c>
       <c r="E9" t="n">
-        <v>186.98</v>
+        <v>262.1</v>
       </c>
       <c r="F9" t="n">
-        <v>24422609</v>
+        <v>12870609</v>
       </c>
       <c r="G9" t="n">
-        <v>17206460</v>
+        <v>8367571</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4193860329201939</v>
+        <v>0.538153545395671</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>BHEL</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>YESBANK</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>610</v>
+        <v>19.93</v>
       </c>
       <c r="C10" t="n">
-        <v>613.05</v>
+        <v>20.52</v>
       </c>
       <c r="D10" t="n">
-        <v>600.9</v>
+        <v>19.91</v>
       </c>
       <c r="E10" t="n">
-        <v>602.05</v>
+        <v>20.24</v>
       </c>
       <c r="F10" t="n">
-        <v>4023729</v>
+        <v>141054900</v>
       </c>
       <c r="G10" t="n">
-        <v>2671861</v>
+        <v>98977180</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5059649435356106</v>
+        <v>0.4251254683150197</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>YESBANK</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6135.5</v>
+        <v>1055</v>
       </c>
       <c r="C11" t="n">
-        <v>6142.5</v>
+        <v>1094.8</v>
       </c>
       <c r="D11" t="n">
-        <v>5975</v>
+        <v>1048.2</v>
       </c>
       <c r="E11" t="n">
-        <v>6000</v>
+        <v>1068.4</v>
       </c>
       <c r="F11" t="n">
-        <v>350612</v>
+        <v>1837718</v>
       </c>
       <c r="G11" t="n">
-        <v>245317</v>
+        <v>1253674</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4292201518851119</v>
+        <v>0.4658659268677503</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>360ONE</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4001</v>
+        <v>1130</v>
       </c>
       <c r="C12" t="n">
-        <v>4001</v>
+        <v>1171.5</v>
       </c>
       <c r="D12" t="n">
-        <v>3900</v>
+        <v>1120</v>
       </c>
       <c r="E12" t="n">
-        <v>3910.8</v>
+        <v>1147.3</v>
       </c>
       <c r="F12" t="n">
-        <v>2191138</v>
+        <v>1212211</v>
       </c>
       <c r="G12" t="n">
-        <v>1423043</v>
+        <v>770804</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5397552990317228</v>
+        <v>0.5726579000627916</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>TATATECH</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>870.75</v>
+        <v>568</v>
       </c>
       <c r="C13" t="n">
-        <v>870.75</v>
+        <v>585.7</v>
       </c>
       <c r="D13" t="n">
-        <v>845</v>
+        <v>567</v>
       </c>
       <c r="E13" t="n">
-        <v>846</v>
+        <v>582.75</v>
       </c>
       <c r="F13" t="n">
-        <v>1088524</v>
+        <v>1019890</v>
       </c>
       <c r="G13" t="n">
-        <v>740587</v>
+        <v>724585</v>
       </c>
       <c r="H13" t="n">
-        <v>0.469812459575985</v>
+        <v>0.4075505289234527</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>TATATECH</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>SJVN</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8502</v>
+        <v>69.5</v>
       </c>
       <c r="C14" t="n">
-        <v>8722</v>
+        <v>71.48999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>8469.5</v>
+        <v>69.37</v>
       </c>
       <c r="E14" t="n">
-        <v>8606.5</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>926904</v>
+        <v>4672987</v>
       </c>
       <c r="G14" t="n">
-        <v>629664</v>
+        <v>2964768</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4720612898307669</v>
+        <v>0.5761729079644681</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>SJVN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>988.1</v>
+        <v>410.05</v>
       </c>
       <c r="C15" t="n">
-        <v>1000</v>
+        <v>434.3</v>
       </c>
       <c r="D15" t="n">
-        <v>980</v>
+        <v>410.05</v>
       </c>
       <c r="E15" t="n">
-        <v>987</v>
+        <v>429</v>
       </c>
       <c r="F15" t="n">
-        <v>2343944</v>
+        <v>1760668</v>
       </c>
       <c r="G15" t="n">
-        <v>1532659</v>
+        <v>1104679</v>
       </c>
       <c r="H15" t="n">
-        <v>0.529331703921094</v>
+        <v>0.5938277092259381</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>CESC</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>357.25</v>
+        <v>146.92</v>
       </c>
       <c r="C16" t="n">
-        <v>362.15</v>
+        <v>156.44</v>
       </c>
       <c r="D16" t="n">
-        <v>353.2</v>
+        <v>146.84</v>
       </c>
       <c r="E16" t="n">
-        <v>354.55</v>
+        <v>154</v>
       </c>
       <c r="F16" t="n">
-        <v>9832443</v>
+        <v>2033533</v>
       </c>
       <c r="G16" t="n">
-        <v>6425639</v>
+        <v>1409632</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5301891376095047</v>
+        <v>0.4425984937912874</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>SRF</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>2601</v>
-      </c>
-      <c r="C17" t="n">
-        <v>2615.2</v>
-      </c>
-      <c r="D17" t="n">
-        <v>2555</v>
-      </c>
-      <c r="E17" t="n">
-        <v>2566</v>
-      </c>
-      <c r="F17" t="n">
-        <v>655543</v>
-      </c>
-      <c r="G17" t="n">
-        <v>441973</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.4832195631859865</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>SRF</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>ALKEM</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>5752</v>
-      </c>
-      <c r="C18" t="n">
-        <v>5781.5</v>
-      </c>
-      <c r="D18" t="n">
-        <v>5614</v>
-      </c>
-      <c r="E18" t="n">
-        <v>5614</v>
-      </c>
-      <c r="F18" t="n">
-        <v>131566</v>
-      </c>
-      <c r="G18" t="n">
-        <v>84228</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.5620221304079404</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>ALKEM</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>KPITTECH</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>800</v>
-      </c>
-      <c r="C19" t="n">
-        <v>808.4</v>
-      </c>
-      <c r="D19" t="n">
-        <v>768</v>
-      </c>
-      <c r="E19" t="n">
-        <v>771</v>
-      </c>
-      <c r="F19" t="n">
-        <v>2159691</v>
-      </c>
-      <c r="G19" t="n">
-        <v>1399625</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.5430497454675359</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>KPITTECH</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>PGEL</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>621</v>
-      </c>
-      <c r="C20" t="n">
-        <v>634.65</v>
-      </c>
-      <c r="D20" t="n">
-        <v>616.55</v>
-      </c>
-      <c r="E20" t="n">
-        <v>627.5</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1612812</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1039233</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.5519253141499548</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>PGEL</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>TITAGARH</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>714.75</v>
-      </c>
-      <c r="C21" t="n">
-        <v>714.75</v>
-      </c>
-      <c r="D21" t="n">
-        <v>699.05</v>
-      </c>
-      <c r="E21" t="n">
-        <v>700.5</v>
-      </c>
-      <c r="F21" t="n">
-        <v>486019</v>
-      </c>
-      <c r="G21" t="n">
-        <v>328591</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.4791001579471136</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>TITAGARH</t>
+          <t>CESC</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,6 +473,72 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>filterdata</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BDL</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1274.2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1294.9</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1258.4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1269.5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1508091</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3471100</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-0.5655293710927372</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>BDL</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>VOLTAS</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1470.1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1480</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1430</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1430.2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>664840</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1419196</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-0.5315375747958704</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>VOLTAS</t>
         </is>
       </c>
     </row>
@@ -487,7 +553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,6 +603,534 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1292</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1317</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1292</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1306.1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>15154950</v>
+      </c>
+      <c r="G2" t="n">
+        <v>9700361</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.5623078357599268</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3240</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3278.1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3207.9</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3269.5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4537215</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2997529</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.5136517444868757</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1356</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1382</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1356</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1364</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3161598</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2088938</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.5134953742045001</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>700</v>
+      </c>
+      <c r="C5" t="n">
+        <v>702</v>
+      </c>
+      <c r="D5" t="n">
+        <v>676.4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>685.4</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3881115</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2579526</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.5045845632104503</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1695.9</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1695.9</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1628.1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1652.3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1509341</v>
+      </c>
+      <c r="G6" t="n">
+        <v>985503</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.5315437903283907</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>DMART</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3772.2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3795</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3736</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3754.6</v>
+      </c>
+      <c r="F7" t="n">
+        <v>603969</v>
+      </c>
+      <c r="G7" t="n">
+        <v>378340</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.596365702806999</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>DMART</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GODREJCP</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1152.9</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1152.9</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1122.7</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1138</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1760408</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1173402</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.5002599279701245</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>GODREJCP</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>5901.5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>5924</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5845.5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5875</v>
+      </c>
+      <c r="F9" t="n">
+        <v>293377</v>
+      </c>
+      <c r="G9" t="n">
+        <v>185417</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.58225513302448</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>UPL</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>621</v>
+      </c>
+      <c r="C10" t="n">
+        <v>621</v>
+      </c>
+      <c r="D10" t="n">
+        <v>601</v>
+      </c>
+      <c r="E10" t="n">
+        <v>612</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3558558</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2404381</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.4800308270611022</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>UPL</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>472</v>
+      </c>
+      <c r="C11" t="n">
+        <v>473.95</v>
+      </c>
+      <c r="D11" t="n">
+        <v>460.45</v>
+      </c>
+      <c r="E11" t="n">
+        <v>462</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2452543</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1656198</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.4808271716304451</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MARICO</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>782.1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>785.95</v>
+      </c>
+      <c r="D12" t="n">
+        <v>768.9</v>
+      </c>
+      <c r="E12" t="n">
+        <v>771.9</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1179796</v>
+      </c>
+      <c r="G12" t="n">
+        <v>752861</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.5670834323998719</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MARICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>600</v>
+      </c>
+      <c r="C13" t="n">
+        <v>606.95</v>
+      </c>
+      <c r="D13" t="n">
+        <v>576.3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>592.65</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2730154</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1893193</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.4420896337563048</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>KFINTECH</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>920</v>
+      </c>
+      <c r="C14" t="n">
+        <v>921</v>
+      </c>
+      <c r="D14" t="n">
+        <v>899.4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>907.5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1106118</v>
+      </c>
+      <c r="G14" t="n">
+        <v>778066</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.4216249007153635</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>KFINTECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NUVAMA</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1210.1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1178.1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1192.3</v>
+      </c>
+      <c r="F15" t="n">
+        <v>759299</v>
+      </c>
+      <c r="G15" t="n">
+        <v>478751</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.5859998203659105</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>NUVAMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TITAGARH</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>661</v>
+      </c>
+      <c r="C16" t="n">
+        <v>663</v>
+      </c>
+      <c r="D16" t="n">
+        <v>637.7</v>
+      </c>
+      <c r="E16" t="n">
+        <v>641.5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1007968</v>
+      </c>
+      <c r="G16" t="n">
+        <v>652594</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.5445560333070791</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>TITAGARH</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CYIENT</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>889.95</v>
+      </c>
+      <c r="C17" t="n">
+        <v>907.5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>875.9</v>
+      </c>
+      <c r="E17" t="n">
+        <v>877</v>
+      </c>
+      <c r="F17" t="n">
+        <v>259099</v>
+      </c>
+      <c r="G17" t="n">
+        <v>181048</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.4311066678449914</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>CYIENT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,66 +479,462 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BDL</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1274.2</v>
+        <v>3277.3</v>
       </c>
       <c r="C2" t="n">
-        <v>1294.9</v>
+        <v>3360.6</v>
       </c>
       <c r="D2" t="n">
-        <v>1258.4</v>
+        <v>3276.2</v>
       </c>
       <c r="E2" t="n">
-        <v>1269.5</v>
+        <v>3350</v>
       </c>
       <c r="F2" t="n">
-        <v>1508091</v>
+        <v>2304760</v>
       </c>
       <c r="G2" t="n">
-        <v>3471100</v>
+        <v>4537215</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5655293710927372</v>
+        <v>-0.492032006418034</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>BDL</t>
+          <t>M&amp;M</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VOLTAS</t>
+          <t>SOLARINDS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1470.1</v>
+        <v>14796</v>
       </c>
       <c r="C3" t="n">
-        <v>1480</v>
+        <v>14980</v>
       </c>
       <c r="D3" t="n">
-        <v>1430</v>
+        <v>14502</v>
       </c>
       <c r="E3" t="n">
-        <v>1430.2</v>
+        <v>14720</v>
       </c>
       <c r="F3" t="n">
-        <v>664840</v>
+        <v>310453</v>
       </c>
       <c r="G3" t="n">
-        <v>1419196</v>
+        <v>662105</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5315375747958704</v>
+        <v>-0.5311121347822475</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>VOLTAS</t>
+          <t>SOLARINDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>IRFC</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>98.20999999999999</v>
+      </c>
+      <c r="C4" t="n">
+        <v>99.25</v>
+      </c>
+      <c r="D4" t="n">
+        <v>97</v>
+      </c>
+      <c r="E4" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>16588277</v>
+      </c>
+      <c r="G4" t="n">
+        <v>32963143</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.4967628845344025</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>IRFC</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>33450</v>
+      </c>
+      <c r="C5" t="n">
+        <v>33715</v>
+      </c>
+      <c r="D5" t="n">
+        <v>33005</v>
+      </c>
+      <c r="E5" t="n">
+        <v>33305</v>
+      </c>
+      <c r="F5" t="n">
+        <v>22632</v>
+      </c>
+      <c r="G5" t="n">
+        <v>50693</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.5535478271161699</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>495</v>
+      </c>
+      <c r="C6" t="n">
+        <v>502.4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>474.4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>481.95</v>
+      </c>
+      <c r="F6" t="n">
+        <v>8668042</v>
+      </c>
+      <c r="G6" t="n">
+        <v>20190436</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.5706857444782272</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>LTF</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>272</v>
+      </c>
+      <c r="C7" t="n">
+        <v>276.9</v>
+      </c>
+      <c r="D7" t="n">
+        <v>270</v>
+      </c>
+      <c r="E7" t="n">
+        <v>276</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3609412</v>
+      </c>
+      <c r="G7" t="n">
+        <v>8234278</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.5616601722701128</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>LTF</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FORTIS</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>916.8</v>
+      </c>
+      <c r="C8" t="n">
+        <v>923.65</v>
+      </c>
+      <c r="D8" t="n">
+        <v>905.6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>920.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>964390</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2075902</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.5354356804897341</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>FORTIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>JUBLFOOD</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>500</v>
+      </c>
+      <c r="C9" t="n">
+        <v>506.9</v>
+      </c>
+      <c r="D9" t="n">
+        <v>492.55</v>
+      </c>
+      <c r="E9" t="n">
+        <v>501.5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1708258</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3801903</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.5506834340592066</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>JUBLFOOD</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MANKIND</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2210.8</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2239.8</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2191.6</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2218</v>
+      </c>
+      <c r="F10" t="n">
+        <v>312313</v>
+      </c>
+      <c r="G10" t="n">
+        <v>687980</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.5460434896363267</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MANKIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PRESTIGE</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1360</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1383.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1351.4</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1370.5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>369602</v>
+      </c>
+      <c r="G11" t="n">
+        <v>868953</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.5746582381325572</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>PRESTIGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>519.1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>522.9</v>
+      </c>
+      <c r="D12" t="n">
+        <v>513.8</v>
+      </c>
+      <c r="E12" t="n">
+        <v>520.1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>745762</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1795199</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.5845797596812387</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DALBHARAT</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1905.5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1936.3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1867</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1933</v>
+      </c>
+      <c r="F13" t="n">
+        <v>103976</v>
+      </c>
+      <c r="G13" t="n">
+        <v>204137</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.4906557850855063</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>DALBHARAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>KFINTECH</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>920.95</v>
+      </c>
+      <c r="C14" t="n">
+        <v>937.4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>911.85</v>
+      </c>
+      <c r="E14" t="n">
+        <v>929.9</v>
+      </c>
+      <c r="F14" t="n">
+        <v>515445</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1106118</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.534005413527309</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>KFINTECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NUVAMA</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1200.1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1246</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1200.1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1243</v>
+      </c>
+      <c r="F15" t="n">
+        <v>365340</v>
+      </c>
+      <c r="G15" t="n">
+        <v>759299</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.5188456721265272</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>NUVAMA</t>
         </is>
       </c>
     </row>
@@ -553,7 +949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -606,528 +1002,429 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1292</v>
+        <v>1181</v>
       </c>
       <c r="C2" t="n">
-        <v>1317</v>
+        <v>1183.2</v>
       </c>
       <c r="D2" t="n">
-        <v>1292</v>
+        <v>1150.6</v>
       </c>
       <c r="E2" t="n">
-        <v>1306.1</v>
+        <v>1168.5</v>
       </c>
       <c r="F2" t="n">
-        <v>15154950</v>
+        <v>22100665</v>
       </c>
       <c r="G2" t="n">
-        <v>9700361</v>
+        <v>13855065</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5623078357599268</v>
+        <v>0.5951325381728632</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>SBIN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3240</v>
+        <v>440.15</v>
       </c>
       <c r="C3" t="n">
-        <v>3278.1</v>
+        <v>458.5</v>
       </c>
       <c r="D3" t="n">
-        <v>3207.9</v>
+        <v>440</v>
       </c>
       <c r="E3" t="n">
-        <v>3269.5</v>
+        <v>448</v>
       </c>
       <c r="F3" t="n">
-        <v>4537215</v>
+        <v>30106255</v>
       </c>
       <c r="G3" t="n">
-        <v>2997529</v>
+        <v>18921256</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5136517444868757</v>
+        <v>0.5911340663643048</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>COALINDIA</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1356</v>
+        <v>366.95</v>
       </c>
       <c r="C4" t="n">
-        <v>1382</v>
+        <v>379.9</v>
       </c>
       <c r="D4" t="n">
-        <v>1356</v>
+        <v>366.6</v>
       </c>
       <c r="E4" t="n">
-        <v>1364</v>
+        <v>377.45</v>
       </c>
       <c r="F4" t="n">
-        <v>3161598</v>
+        <v>16158714</v>
       </c>
       <c r="G4" t="n">
-        <v>2088938</v>
+        <v>11433169</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5134953742045001</v>
+        <v>0.4133189144671963</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>NTPC</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>700</v>
+        <v>706.45</v>
       </c>
       <c r="C5" t="n">
-        <v>702</v>
+        <v>737.9</v>
       </c>
       <c r="D5" t="n">
-        <v>676.4</v>
+        <v>706</v>
       </c>
       <c r="E5" t="n">
-        <v>685.4</v>
+        <v>713</v>
       </c>
       <c r="F5" t="n">
-        <v>3881115</v>
+        <v>22092809</v>
       </c>
       <c r="G5" t="n">
-        <v>2579526</v>
+        <v>14669674</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5045845632104503</v>
+        <v>0.5060190839960043</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>VEDL</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1695.9</v>
+        <v>123.98</v>
       </c>
       <c r="C6" t="n">
-        <v>1695.9</v>
+        <v>127.29</v>
       </c>
       <c r="D6" t="n">
-        <v>1628.1</v>
+        <v>123.7</v>
       </c>
       <c r="E6" t="n">
-        <v>1652.3</v>
+        <v>126.7</v>
       </c>
       <c r="F6" t="n">
-        <v>1509341</v>
+        <v>23410571</v>
       </c>
       <c r="G6" t="n">
-        <v>985503</v>
+        <v>16183188</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5315437903283907</v>
+        <v>0.4465982227976342</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3772.2</v>
+        <v>1008</v>
       </c>
       <c r="C7" t="n">
-        <v>3795</v>
+        <v>1021.2</v>
       </c>
       <c r="D7" t="n">
-        <v>3736</v>
+        <v>996.2</v>
       </c>
       <c r="E7" t="n">
-        <v>3754.6</v>
+        <v>1010.4</v>
       </c>
       <c r="F7" t="n">
-        <v>603969</v>
+        <v>2499934</v>
       </c>
       <c r="G7" t="n">
-        <v>378340</v>
+        <v>1770489</v>
       </c>
       <c r="H7" t="n">
-        <v>0.596365702806999</v>
+        <v>0.4120019949290846</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>NAUKRI</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1152.9</v>
+        <v>2710</v>
       </c>
       <c r="C8" t="n">
-        <v>1152.9</v>
+        <v>2782</v>
       </c>
       <c r="D8" t="n">
-        <v>1122.7</v>
+        <v>2656.3</v>
       </c>
       <c r="E8" t="n">
-        <v>1138</v>
+        <v>2771</v>
       </c>
       <c r="F8" t="n">
-        <v>1760408</v>
+        <v>7464269</v>
       </c>
       <c r="G8" t="n">
-        <v>1173402</v>
+        <v>4779189</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5002599279701245</v>
+        <v>0.5618275401956273</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>BSE</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>HINDPETRO</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5901.5</v>
+        <v>403.8</v>
       </c>
       <c r="C9" t="n">
-        <v>5924</v>
+        <v>426.5</v>
       </c>
       <c r="D9" t="n">
-        <v>5845.5</v>
+        <v>400.1</v>
       </c>
       <c r="E9" t="n">
-        <v>5875</v>
+        <v>416.8</v>
       </c>
       <c r="F9" t="n">
-        <v>293377</v>
+        <v>10165454</v>
       </c>
       <c r="G9" t="n">
-        <v>185417</v>
+        <v>6582702</v>
       </c>
       <c r="H9" t="n">
-        <v>0.58225513302448</v>
+        <v>0.5442676882532431</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>HINDPETRO</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UPL</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>621</v>
+        <v>1470</v>
       </c>
       <c r="C10" t="n">
-        <v>621</v>
+        <v>1490</v>
       </c>
       <c r="D10" t="n">
-        <v>601</v>
+        <v>1459.6</v>
       </c>
       <c r="E10" t="n">
-        <v>612</v>
+        <v>1485</v>
       </c>
       <c r="F10" t="n">
-        <v>3558558</v>
+        <v>1232606</v>
       </c>
       <c r="G10" t="n">
-        <v>2404381</v>
+        <v>807048</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4800308270611022</v>
+        <v>0.5273019696474064</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>UPL</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>472</v>
+        <v>1630</v>
       </c>
       <c r="C11" t="n">
-        <v>473.95</v>
+        <v>1654.9</v>
       </c>
       <c r="D11" t="n">
-        <v>460.45</v>
+        <v>1609.8</v>
       </c>
       <c r="E11" t="n">
-        <v>462</v>
+        <v>1609.9</v>
       </c>
       <c r="F11" t="n">
-        <v>2452543</v>
+        <v>643717</v>
       </c>
       <c r="G11" t="n">
-        <v>1656198</v>
+        <v>403023</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4808271716304451</v>
+        <v>0.597221498524898</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>PAGEIND</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>782.1</v>
+        <v>30950</v>
       </c>
       <c r="C12" t="n">
-        <v>785.95</v>
+        <v>31795</v>
       </c>
       <c r="D12" t="n">
-        <v>768.9</v>
+        <v>30940</v>
       </c>
       <c r="E12" t="n">
-        <v>771.9</v>
+        <v>31485</v>
       </c>
       <c r="F12" t="n">
-        <v>1179796</v>
+        <v>31871</v>
       </c>
       <c r="G12" t="n">
-        <v>752861</v>
+        <v>22570</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5670834323998719</v>
+        <v>0.4120957022596367</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>PAGEIND</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>600</v>
+        <v>639.4</v>
       </c>
       <c r="C13" t="n">
-        <v>606.95</v>
+        <v>655.35</v>
       </c>
       <c r="D13" t="n">
-        <v>576.3</v>
+        <v>635.45</v>
       </c>
       <c r="E13" t="n">
-        <v>592.65</v>
+        <v>655.1</v>
       </c>
       <c r="F13" t="n">
-        <v>2730154</v>
+        <v>4749237</v>
       </c>
       <c r="G13" t="n">
-        <v>1893193</v>
+        <v>3113387</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4420896337563048</v>
+        <v>0.5254245617393534</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>CAMS</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>KFINTECH</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>920</v>
+        <v>418.55</v>
       </c>
       <c r="C14" t="n">
-        <v>921</v>
+        <v>429.75</v>
       </c>
       <c r="D14" t="n">
-        <v>899.4</v>
+        <v>413.75</v>
       </c>
       <c r="E14" t="n">
-        <v>907.5</v>
+        <v>428.55</v>
       </c>
       <c r="F14" t="n">
-        <v>1106118</v>
+        <v>1604071</v>
       </c>
       <c r="G14" t="n">
-        <v>778066</v>
+        <v>1090764</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4216249007153635</v>
+        <v>0.4705940056694207</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>KFINTECH</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>NUVAMA</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1200</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1210.1</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1178.1</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1192.3</v>
-      </c>
-      <c r="F15" t="n">
-        <v>759299</v>
-      </c>
-      <c r="G15" t="n">
-        <v>478751</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.5859998203659105</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>NUVAMA</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>TITAGARH</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>661</v>
-      </c>
-      <c r="C16" t="n">
-        <v>663</v>
-      </c>
-      <c r="D16" t="n">
-        <v>637.7</v>
-      </c>
-      <c r="E16" t="n">
-        <v>641.5</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1007968</v>
-      </c>
-      <c r="G16" t="n">
-        <v>652594</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.5445560333070791</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>TITAGARH</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>CYIENT</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>889.95</v>
-      </c>
-      <c r="C17" t="n">
-        <v>907.5</v>
-      </c>
-      <c r="D17" t="n">
-        <v>875.9</v>
-      </c>
-      <c r="E17" t="n">
-        <v>877</v>
-      </c>
-      <c r="F17" t="n">
-        <v>259099</v>
-      </c>
-      <c r="G17" t="n">
-        <v>181048</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.4311066678449914</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>CYIENT</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,462 +479,660 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3277.3</v>
+        <v>4015</v>
       </c>
       <c r="C2" t="n">
-        <v>3360.6</v>
+        <v>4015</v>
       </c>
       <c r="D2" t="n">
-        <v>3276.2</v>
+        <v>3941</v>
       </c>
       <c r="E2" t="n">
-        <v>3350</v>
+        <v>3949</v>
       </c>
       <c r="F2" t="n">
-        <v>2304760</v>
+        <v>2379314</v>
       </c>
       <c r="G2" t="n">
-        <v>4537215</v>
+        <v>4996312</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.492032006418034</v>
+        <v>-0.5237859445126726</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>LT</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SOLARINDS</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14796</v>
+        <v>955</v>
       </c>
       <c r="C3" t="n">
-        <v>14980</v>
+        <v>971.65</v>
       </c>
       <c r="D3" t="n">
-        <v>14502</v>
+        <v>943.15</v>
       </c>
       <c r="E3" t="n">
-        <v>14720</v>
+        <v>960.6</v>
       </c>
       <c r="F3" t="n">
-        <v>310453</v>
+        <v>8295000</v>
       </c>
       <c r="G3" t="n">
-        <v>662105</v>
+        <v>16533658</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5311121347822475</v>
+        <v>-0.4982961423297857</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SOLARINDS</t>
+          <t>HINDALCO</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IRFC</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>98.20999999999999</v>
+        <v>7770</v>
       </c>
       <c r="C4" t="n">
-        <v>99.25</v>
+        <v>7781</v>
       </c>
       <c r="D4" t="n">
-        <v>97</v>
+        <v>7669</v>
       </c>
       <c r="E4" t="n">
-        <v>99.09999999999999</v>
+        <v>7746</v>
       </c>
       <c r="F4" t="n">
-        <v>16588277</v>
+        <v>225749</v>
       </c>
       <c r="G4" t="n">
-        <v>32963143</v>
+        <v>446578</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4967628845344025</v>
+        <v>-0.4944914438239232</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>IRFC</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BOSCHLTD</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>33450</v>
+        <v>1930</v>
       </c>
       <c r="C5" t="n">
-        <v>33715</v>
+        <v>1962.9</v>
       </c>
       <c r="D5" t="n">
-        <v>33005</v>
+        <v>1924.8</v>
       </c>
       <c r="E5" t="n">
-        <v>33305</v>
+        <v>1946</v>
       </c>
       <c r="F5" t="n">
-        <v>22632</v>
+        <v>858666</v>
       </c>
       <c r="G5" t="n">
-        <v>50693</v>
+        <v>1955176</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5535478271161699</v>
+        <v>-0.5608241917863149</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>BOSCHLTD</t>
+          <t>SBILIFE</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>495</v>
+        <v>340</v>
       </c>
       <c r="C6" t="n">
-        <v>502.4</v>
+        <v>350.8</v>
       </c>
       <c r="D6" t="n">
-        <v>474.4</v>
+        <v>338.5</v>
       </c>
       <c r="E6" t="n">
-        <v>481.95</v>
+        <v>338.9</v>
       </c>
       <c r="F6" t="n">
-        <v>8668042</v>
+        <v>5579379</v>
       </c>
       <c r="G6" t="n">
-        <v>20190436</v>
+        <v>11657520</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5706857444782272</v>
+        <v>-0.5213922858378112</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>RECLTD</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LTF</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>272</v>
+        <v>1664</v>
       </c>
       <c r="C7" t="n">
-        <v>276.9</v>
+        <v>1674.6</v>
       </c>
       <c r="D7" t="n">
-        <v>270</v>
+        <v>1620</v>
       </c>
       <c r="E7" t="n">
-        <v>276</v>
+        <v>1621.5</v>
       </c>
       <c r="F7" t="n">
-        <v>3609412</v>
+        <v>1022219</v>
       </c>
       <c r="G7" t="n">
-        <v>8234278</v>
+        <v>2076383</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5616601722701128</v>
+        <v>-0.507692463288324</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>LTF</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FORTIS</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>916.8</v>
+        <v>126.34</v>
       </c>
       <c r="C8" t="n">
-        <v>923.65</v>
+        <v>126.7</v>
       </c>
       <c r="D8" t="n">
-        <v>905.6</v>
+        <v>122.49</v>
       </c>
       <c r="E8" t="n">
-        <v>920.5</v>
+        <v>122.97</v>
       </c>
       <c r="F8" t="n">
-        <v>964390</v>
+        <v>10309068</v>
       </c>
       <c r="G8" t="n">
-        <v>2075902</v>
+        <v>23410571</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5354356804897341</v>
+        <v>-0.5596404718193332</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>FORTIS</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>JUBLFOOD</t>
+          <t>GODREJCP</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>500</v>
+        <v>1132.4</v>
       </c>
       <c r="C9" t="n">
-        <v>506.9</v>
+        <v>1132.5</v>
       </c>
       <c r="D9" t="n">
-        <v>492.55</v>
+        <v>1114</v>
       </c>
       <c r="E9" t="n">
-        <v>501.5</v>
+        <v>1115.1</v>
       </c>
       <c r="F9" t="n">
-        <v>1708258</v>
+        <v>883212</v>
       </c>
       <c r="G9" t="n">
-        <v>3801903</v>
+        <v>1925968</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5506834340592066</v>
+        <v>-0.5414191720734717</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>JUBLFOOD</t>
+          <t>GODREJCP</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>DMART</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2210.8</v>
+        <v>3825</v>
       </c>
       <c r="C10" t="n">
-        <v>2239.8</v>
+        <v>3903.9</v>
       </c>
       <c r="D10" t="n">
-        <v>2191.6</v>
+        <v>3825</v>
       </c>
       <c r="E10" t="n">
-        <v>2218</v>
+        <v>3881.5</v>
       </c>
       <c r="F10" t="n">
-        <v>312313</v>
+        <v>224906</v>
       </c>
       <c r="G10" t="n">
-        <v>687980</v>
+        <v>516200</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5460434896363267</v>
+        <v>-0.564304533126695</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>DMART</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PRESTIGE</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1360</v>
+        <v>2750</v>
       </c>
       <c r="C11" t="n">
-        <v>1383.5</v>
+        <v>2789</v>
       </c>
       <c r="D11" t="n">
-        <v>1351.4</v>
+        <v>2736.4</v>
       </c>
       <c r="E11" t="n">
-        <v>1370.5</v>
+        <v>2750.9</v>
       </c>
       <c r="F11" t="n">
-        <v>369602</v>
+        <v>3007569</v>
       </c>
       <c r="G11" t="n">
-        <v>868953</v>
+        <v>7464269</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5746582381325572</v>
+        <v>-0.5970711934417154</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>PRESTIGE</t>
+          <t>BSE</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>519.1</v>
+        <v>948.05</v>
       </c>
       <c r="C12" t="n">
-        <v>522.9</v>
+        <v>954.55</v>
       </c>
       <c r="D12" t="n">
-        <v>513.8</v>
+        <v>936.65</v>
       </c>
       <c r="E12" t="n">
-        <v>520.1</v>
+        <v>944</v>
       </c>
       <c r="F12" t="n">
-        <v>745762</v>
+        <v>1071588</v>
       </c>
       <c r="G12" t="n">
-        <v>1795199</v>
+        <v>2154862</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5845797596812387</v>
+        <v>-0.5027115425488964</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>INDIANB</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DALBHARAT</t>
+          <t>SBICARD</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1905.5</v>
+        <v>728.5</v>
       </c>
       <c r="C13" t="n">
-        <v>1936.3</v>
+        <v>735.45</v>
       </c>
       <c r="D13" t="n">
-        <v>1867</v>
+        <v>720.6</v>
       </c>
       <c r="E13" t="n">
-        <v>1933</v>
+        <v>722.1</v>
       </c>
       <c r="F13" t="n">
-        <v>103976</v>
+        <v>981079</v>
       </c>
       <c r="G13" t="n">
-        <v>204137</v>
+        <v>2088983</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4906557850855063</v>
+        <v>-0.5303556802520653</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>DALBHARAT</t>
+          <t>SBICARD</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>KFINTECH</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>920.95</v>
+        <v>2230</v>
       </c>
       <c r="C14" t="n">
-        <v>937.4</v>
+        <v>2286.9</v>
       </c>
       <c r="D14" t="n">
-        <v>911.85</v>
+        <v>2210</v>
       </c>
       <c r="E14" t="n">
-        <v>929.9</v>
+        <v>2224.9</v>
       </c>
       <c r="F14" t="n">
-        <v>515445</v>
+        <v>287592</v>
       </c>
       <c r="G14" t="n">
-        <v>1106118</v>
+        <v>684794</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.534005413527309</v>
+        <v>-0.5800313670972584</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>KFINTECH</t>
+          <t>MPHASIS</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NUVAMA</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1200.1</v>
+        <v>1117.9</v>
       </c>
       <c r="C15" t="n">
-        <v>1246</v>
+        <v>1134.9</v>
       </c>
       <c r="D15" t="n">
-        <v>1200.1</v>
+        <v>1112.1</v>
       </c>
       <c r="E15" t="n">
-        <v>1243</v>
+        <v>1127.4</v>
       </c>
       <c r="F15" t="n">
-        <v>365340</v>
+        <v>425766</v>
       </c>
       <c r="G15" t="n">
-        <v>759299</v>
+        <v>938497</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5188456721265272</v>
+        <v>-0.5463320607311478</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>NUVAMA</t>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1626</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1626</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1596.5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1613.1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>289704</v>
+      </c>
+      <c r="G16" t="n">
+        <v>643717</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.5499512984743296</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>IGL</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>159</v>
+      </c>
+      <c r="C17" t="n">
+        <v>159.2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>156.08</v>
+      </c>
+      <c r="E17" t="n">
+        <v>157.65</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2074749</v>
+      </c>
+      <c r="G17" t="n">
+        <v>4311565</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.5187944516666222</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>IGL</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SJVN</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>72.06</v>
+      </c>
+      <c r="C18" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="E18" t="n">
+        <v>70.95</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3487613</v>
+      </c>
+      <c r="G18" t="n">
+        <v>8398954</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.5847562684591439</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>SJVN</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ALKEM</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>5580</v>
+      </c>
+      <c r="C19" t="n">
+        <v>5583</v>
+      </c>
+      <c r="D19" t="n">
+        <v>5497</v>
+      </c>
+      <c r="E19" t="n">
+        <v>5525</v>
+      </c>
+      <c r="F19" t="n">
+        <v>41269</v>
+      </c>
+      <c r="G19" t="n">
+        <v>96348</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.5716672894092248</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ALKEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2562</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2590.7</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2522.8</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2541</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1832576</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3764228</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-0.5131602017731126</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ABFRL</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>64.28</v>
+      </c>
+      <c r="C21" t="n">
+        <v>64.76000000000001</v>
+      </c>
+      <c r="D21" t="n">
+        <v>61.99</v>
+      </c>
+      <c r="E21" t="n">
+        <v>62.49</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2407538</v>
+      </c>
+      <c r="G21" t="n">
+        <v>4821195</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.5006345937055025</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ABFRL</t>
         </is>
       </c>
     </row>
@@ -949,7 +1147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1002,429 +1200,264 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1181</v>
+        <v>1908.9</v>
       </c>
       <c r="C2" t="n">
-        <v>1183.2</v>
+        <v>1908.9</v>
       </c>
       <c r="D2" t="n">
-        <v>1150.6</v>
+        <v>1865</v>
       </c>
       <c r="E2" t="n">
-        <v>1168.5</v>
+        <v>1870.4</v>
       </c>
       <c r="F2" t="n">
-        <v>22100665</v>
+        <v>2267317</v>
       </c>
       <c r="G2" t="n">
-        <v>13855065</v>
+        <v>1515601</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5951325381728632</v>
+        <v>0.4959854209650165</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>440.15</v>
+        <v>5900</v>
       </c>
       <c r="C3" t="n">
-        <v>458.5</v>
+        <v>6118</v>
       </c>
       <c r="D3" t="n">
-        <v>440</v>
+        <v>5869</v>
       </c>
       <c r="E3" t="n">
-        <v>448</v>
+        <v>6058</v>
       </c>
       <c r="F3" t="n">
-        <v>30106255</v>
+        <v>377080</v>
       </c>
       <c r="G3" t="n">
-        <v>18921256</v>
+        <v>268401</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5911340663643048</v>
+        <v>0.4049127983874874</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>ABB</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>366.95</v>
+        <v>4353.5</v>
       </c>
       <c r="C4" t="n">
-        <v>379.9</v>
+        <v>4380.3</v>
       </c>
       <c r="D4" t="n">
-        <v>366.6</v>
+        <v>4287</v>
       </c>
       <c r="E4" t="n">
-        <v>377.45</v>
+        <v>4325.9</v>
       </c>
       <c r="F4" t="n">
-        <v>16158714</v>
+        <v>413700</v>
       </c>
       <c r="G4" t="n">
-        <v>11433169</v>
+        <v>284382</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4133189144671963</v>
+        <v>0.4547334219465367</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>706.45</v>
+        <v>980</v>
       </c>
       <c r="C5" t="n">
-        <v>737.9</v>
+        <v>1007.7</v>
       </c>
       <c r="D5" t="n">
-        <v>706</v>
+        <v>979.8</v>
       </c>
       <c r="E5" t="n">
-        <v>713</v>
+        <v>997.2</v>
       </c>
       <c r="F5" t="n">
-        <v>22092809</v>
+        <v>1529030</v>
       </c>
       <c r="G5" t="n">
-        <v>14669674</v>
+        <v>1006629</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5060190839960043</v>
+        <v>0.5189608087984749</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>HAVELLS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>123.98</v>
+        <v>1352.5</v>
       </c>
       <c r="C6" t="n">
-        <v>127.29</v>
+        <v>1365</v>
       </c>
       <c r="D6" t="n">
-        <v>123.7</v>
+        <v>1340.3</v>
       </c>
       <c r="E6" t="n">
-        <v>126.7</v>
+        <v>1351</v>
       </c>
       <c r="F6" t="n">
-        <v>23410571</v>
+        <v>489820</v>
       </c>
       <c r="G6" t="n">
-        <v>16183188</v>
+        <v>320753</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4465982227976342</v>
+        <v>0.5270940567975981</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>HAVELLS</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>NMDC</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1008</v>
+        <v>78</v>
       </c>
       <c r="C7" t="n">
-        <v>1021.2</v>
+        <v>81.91</v>
       </c>
       <c r="D7" t="n">
-        <v>996.2</v>
+        <v>77.95</v>
       </c>
       <c r="E7" t="n">
-        <v>1010.4</v>
+        <v>79.89</v>
       </c>
       <c r="F7" t="n">
-        <v>2499934</v>
+        <v>32383963</v>
       </c>
       <c r="G7" t="n">
-        <v>1770489</v>
+        <v>20259988</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4120019949290846</v>
+        <v>0.5984196535555697</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>NMDC</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2710</v>
+        <v>1741.6</v>
       </c>
       <c r="C8" t="n">
-        <v>2782</v>
+        <v>1748.5</v>
       </c>
       <c r="D8" t="n">
-        <v>2656.3</v>
+        <v>1693.3</v>
       </c>
       <c r="E8" t="n">
-        <v>2771</v>
+        <v>1706.9</v>
       </c>
       <c r="F8" t="n">
-        <v>7464269</v>
+        <v>1221346</v>
       </c>
       <c r="G8" t="n">
-        <v>4779189</v>
+        <v>833743</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5618275401956273</v>
+        <v>0.4648950575896889</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>MFSL</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HINDPETRO</t>
+          <t>IREDA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>403.8</v>
+        <v>116.5</v>
       </c>
       <c r="C9" t="n">
-        <v>426.5</v>
+        <v>120.35</v>
       </c>
       <c r="D9" t="n">
-        <v>400.1</v>
+        <v>115.08</v>
       </c>
       <c r="E9" t="n">
-        <v>416.8</v>
+        <v>117.4</v>
       </c>
       <c r="F9" t="n">
-        <v>10165454</v>
+        <v>12595130</v>
       </c>
       <c r="G9" t="n">
-        <v>6582702</v>
+        <v>8974731</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5442676882532431</v>
+        <v>0.4033991659471465</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>HINDPETRO</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>OBEROIRLTY</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1470</v>
-      </c>
-      <c r="C10" t="n">
-        <v>1490</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1459.6</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1485</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1232606</v>
-      </c>
-      <c r="G10" t="n">
-        <v>807048</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.5273019696474064</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>OBEROIRLTY</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>PHOENIXLTD</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1630</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1654.9</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1609.8</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1609.9</v>
-      </c>
-      <c r="F11" t="n">
-        <v>643717</v>
-      </c>
-      <c r="G11" t="n">
-        <v>403023</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.597221498524898</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>PHOENIXLTD</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>PAGEIND</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>30950</v>
-      </c>
-      <c r="C12" t="n">
-        <v>31795</v>
-      </c>
-      <c r="D12" t="n">
-        <v>30940</v>
-      </c>
-      <c r="E12" t="n">
-        <v>31485</v>
-      </c>
-      <c r="F12" t="n">
-        <v>31871</v>
-      </c>
-      <c r="G12" t="n">
-        <v>22570</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.4120957022596367</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>PAGEIND</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>CAMS</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>639.4</v>
-      </c>
-      <c r="C13" t="n">
-        <v>655.35</v>
-      </c>
-      <c r="D13" t="n">
-        <v>635.45</v>
-      </c>
-      <c r="E13" t="n">
-        <v>655.1</v>
-      </c>
-      <c r="F13" t="n">
-        <v>4749237</v>
-      </c>
-      <c r="G13" t="n">
-        <v>3113387</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.5254245617393534</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>CAMS</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>DELHIVERY</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>418.55</v>
-      </c>
-      <c r="C14" t="n">
-        <v>429.75</v>
-      </c>
-      <c r="D14" t="n">
-        <v>413.75</v>
-      </c>
-      <c r="E14" t="n">
-        <v>428.55</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1604071</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1090764</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.4705940056694207</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>DELHIVERY</t>
+          <t>IREDA</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,660 +479,264 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4015</v>
+        <v>1839.1</v>
       </c>
       <c r="C2" t="n">
-        <v>4015</v>
+        <v>1844.6</v>
       </c>
       <c r="D2" t="n">
-        <v>3941</v>
+        <v>1802</v>
       </c>
       <c r="E2" t="n">
-        <v>3949</v>
+        <v>1840.9</v>
       </c>
       <c r="F2" t="n">
-        <v>2379314</v>
+        <v>1009617</v>
       </c>
       <c r="G2" t="n">
-        <v>4996312</v>
+        <v>2267317</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5237859445126726</v>
+        <v>-0.5547084946657217</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>IRFC</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>955</v>
+        <v>97.11</v>
       </c>
       <c r="C3" t="n">
-        <v>971.65</v>
+        <v>97.95</v>
       </c>
       <c r="D3" t="n">
-        <v>943.15</v>
+        <v>95.27</v>
       </c>
       <c r="E3" t="n">
-        <v>960.6</v>
+        <v>97.75</v>
       </c>
       <c r="F3" t="n">
-        <v>8295000</v>
+        <v>16395706</v>
       </c>
       <c r="G3" t="n">
-        <v>16533658</v>
+        <v>35489993</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4982961423297857</v>
+        <v>-0.5380189001446126</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>IRFC</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>BDL</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7770</v>
+        <v>1357</v>
       </c>
       <c r="C4" t="n">
-        <v>7781</v>
+        <v>1358.8</v>
       </c>
       <c r="D4" t="n">
-        <v>7669</v>
+        <v>1298</v>
       </c>
       <c r="E4" t="n">
-        <v>7746</v>
+        <v>1331.1</v>
       </c>
       <c r="F4" t="n">
-        <v>225749</v>
+        <v>2077090</v>
       </c>
       <c r="G4" t="n">
-        <v>446578</v>
+        <v>5023734</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4944914438239232</v>
+        <v>-0.5865445901395256</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>BDL</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>CUMMINSIND</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1930</v>
+        <v>4740</v>
       </c>
       <c r="C5" t="n">
-        <v>1962.9</v>
+        <v>4750</v>
       </c>
       <c r="D5" t="n">
-        <v>1924.8</v>
+        <v>4621.8</v>
       </c>
       <c r="E5" t="n">
-        <v>1946</v>
+        <v>4681.1</v>
       </c>
       <c r="F5" t="n">
-        <v>858666</v>
+        <v>360922</v>
       </c>
       <c r="G5" t="n">
-        <v>1955176</v>
+        <v>892005</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5608241917863149</v>
+        <v>-0.5953811918094629</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>CUMMINSIND</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>ASTRAL</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>340</v>
+        <v>1677</v>
       </c>
       <c r="C6" t="n">
-        <v>350.8</v>
+        <v>1677</v>
       </c>
       <c r="D6" t="n">
-        <v>338.5</v>
+        <v>1595.2</v>
       </c>
       <c r="E6" t="n">
-        <v>338.9</v>
+        <v>1602.5</v>
       </c>
       <c r="F6" t="n">
-        <v>5579379</v>
+        <v>527194</v>
       </c>
       <c r="G6" t="n">
-        <v>11657520</v>
+        <v>1096077</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5213922858378112</v>
+        <v>-0.519017368305329</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>ASTRAL</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>PAGEIND</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1664</v>
+        <v>30940</v>
       </c>
       <c r="C7" t="n">
-        <v>1674.6</v>
+        <v>31350</v>
       </c>
       <c r="D7" t="n">
-        <v>1620</v>
+        <v>30820</v>
       </c>
       <c r="E7" t="n">
-        <v>1621.5</v>
+        <v>31085</v>
       </c>
       <c r="F7" t="n">
-        <v>1022219</v>
+        <v>11361</v>
       </c>
       <c r="G7" t="n">
-        <v>2076383</v>
+        <v>24708</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.507692463288324</v>
+        <v>-0.5401894123360855</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>PAGEIND</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>DALBHARAT</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>126.34</v>
+        <v>1884.3</v>
       </c>
       <c r="C8" t="n">
-        <v>126.7</v>
+        <v>1884.3</v>
       </c>
       <c r="D8" t="n">
-        <v>122.49</v>
+        <v>1822</v>
       </c>
       <c r="E8" t="n">
-        <v>122.97</v>
+        <v>1843.2</v>
       </c>
       <c r="F8" t="n">
-        <v>10309068</v>
+        <v>86055</v>
       </c>
       <c r="G8" t="n">
-        <v>23410571</v>
+        <v>183615</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5596404718193332</v>
+        <v>-0.531329139776162</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>DALBHARAT</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>TITAGARH</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1132.4</v>
+        <v>669.05</v>
       </c>
       <c r="C9" t="n">
-        <v>1132.5</v>
+        <v>669.05</v>
       </c>
       <c r="D9" t="n">
-        <v>1114</v>
+        <v>642.2</v>
       </c>
       <c r="E9" t="n">
-        <v>1115.1</v>
+        <v>660</v>
       </c>
       <c r="F9" t="n">
-        <v>883212</v>
+        <v>802295</v>
       </c>
       <c r="G9" t="n">
-        <v>1925968</v>
+        <v>1752717</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5414191720734717</v>
+        <v>-0.5422563939301096</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>DMART</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>3825</v>
-      </c>
-      <c r="C10" t="n">
-        <v>3903.9</v>
-      </c>
-      <c r="D10" t="n">
-        <v>3825</v>
-      </c>
-      <c r="E10" t="n">
-        <v>3881.5</v>
-      </c>
-      <c r="F10" t="n">
-        <v>224906</v>
-      </c>
-      <c r="G10" t="n">
-        <v>516200</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-0.564304533126695</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>DMART</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>BSE</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2750</v>
-      </c>
-      <c r="C11" t="n">
-        <v>2789</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2736.4</v>
-      </c>
-      <c r="E11" t="n">
-        <v>2750.9</v>
-      </c>
-      <c r="F11" t="n">
-        <v>3007569</v>
-      </c>
-      <c r="G11" t="n">
-        <v>7464269</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-0.5970711934417154</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>BSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>INDIANB</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>948.05</v>
-      </c>
-      <c r="C12" t="n">
-        <v>954.55</v>
-      </c>
-      <c r="D12" t="n">
-        <v>936.65</v>
-      </c>
-      <c r="E12" t="n">
-        <v>944</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1071588</v>
-      </c>
-      <c r="G12" t="n">
-        <v>2154862</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-0.5027115425488964</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>INDIANB</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>SBICARD</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>728.5</v>
-      </c>
-      <c r="C13" t="n">
-        <v>735.45</v>
-      </c>
-      <c r="D13" t="n">
-        <v>720.6</v>
-      </c>
-      <c r="E13" t="n">
-        <v>722.1</v>
-      </c>
-      <c r="F13" t="n">
-        <v>981079</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2088983</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-0.5303556802520653</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>SBICARD</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>MPHASIS</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2230</v>
-      </c>
-      <c r="C14" t="n">
-        <v>2286.9</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2210</v>
-      </c>
-      <c r="E14" t="n">
-        <v>2224.9</v>
-      </c>
-      <c r="F14" t="n">
-        <v>287592</v>
-      </c>
-      <c r="G14" t="n">
-        <v>684794</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-0.5800313670972584</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>MPHASIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>UNOMINDA</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1117.9</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1134.9</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1112.1</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1127.4</v>
-      </c>
-      <c r="F15" t="n">
-        <v>425766</v>
-      </c>
-      <c r="G15" t="n">
-        <v>938497</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-0.5463320607311478</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>UNOMINDA</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>PHOENIXLTD</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1626</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1626</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1596.5</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1613.1</v>
-      </c>
-      <c r="F16" t="n">
-        <v>289704</v>
-      </c>
-      <c r="G16" t="n">
-        <v>643717</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-0.5499512984743296</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>PHOENIXLTD</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>IGL</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>159</v>
-      </c>
-      <c r="C17" t="n">
-        <v>159.2</v>
-      </c>
-      <c r="D17" t="n">
-        <v>156.08</v>
-      </c>
-      <c r="E17" t="n">
-        <v>157.65</v>
-      </c>
-      <c r="F17" t="n">
-        <v>2074749</v>
-      </c>
-      <c r="G17" t="n">
-        <v>4311565</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-0.5187944516666222</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>IGL</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>SJVN</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>72.06</v>
-      </c>
-      <c r="C18" t="n">
-        <v>73.2</v>
-      </c>
-      <c r="D18" t="n">
-        <v>70.59999999999999</v>
-      </c>
-      <c r="E18" t="n">
-        <v>70.95</v>
-      </c>
-      <c r="F18" t="n">
-        <v>3487613</v>
-      </c>
-      <c r="G18" t="n">
-        <v>8398954</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-0.5847562684591439</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>SJVN</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>ALKEM</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>5580</v>
-      </c>
-      <c r="C19" t="n">
-        <v>5583</v>
-      </c>
-      <c r="D19" t="n">
-        <v>5497</v>
-      </c>
-      <c r="E19" t="n">
-        <v>5525</v>
-      </c>
-      <c r="F19" t="n">
-        <v>41269</v>
-      </c>
-      <c r="G19" t="n">
-        <v>96348</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-0.5716672894092248</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>ALKEM</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>2562</v>
-      </c>
-      <c r="C20" t="n">
-        <v>2590.7</v>
-      </c>
-      <c r="D20" t="n">
-        <v>2522.8</v>
-      </c>
-      <c r="E20" t="n">
-        <v>2541</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1832576</v>
-      </c>
-      <c r="G20" t="n">
-        <v>3764228</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-0.5131602017731126</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>ABFRL</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>64.28</v>
-      </c>
-      <c r="C21" t="n">
-        <v>64.76000000000001</v>
-      </c>
-      <c r="D21" t="n">
-        <v>61.99</v>
-      </c>
-      <c r="E21" t="n">
-        <v>62.49</v>
-      </c>
-      <c r="F21" t="n">
-        <v>2407538</v>
-      </c>
-      <c r="G21" t="n">
-        <v>4821195</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-0.5006345937055025</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>ABFRL</t>
+          <t>TITAGARH</t>
         </is>
       </c>
     </row>
@@ -1147,7 +751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1200,264 +804,693 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1908.9</v>
+        <v>957.5</v>
       </c>
       <c r="C2" t="n">
-        <v>1908.9</v>
+        <v>993</v>
       </c>
       <c r="D2" t="n">
-        <v>1865</v>
+        <v>934.2</v>
       </c>
       <c r="E2" t="n">
-        <v>1870.4</v>
+        <v>989.9</v>
       </c>
       <c r="F2" t="n">
-        <v>2267317</v>
+        <v>11999852</v>
       </c>
       <c r="G2" t="n">
-        <v>1515601</v>
+        <v>8166989</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4959854209650165</v>
+        <v>0.469311639822216</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5900</v>
+        <v>193.45</v>
       </c>
       <c r="C3" t="n">
-        <v>6118</v>
+        <v>193.7</v>
       </c>
       <c r="D3" t="n">
-        <v>5869</v>
+        <v>187.03</v>
       </c>
       <c r="E3" t="n">
-        <v>6058</v>
+        <v>191.13</v>
       </c>
       <c r="F3" t="n">
-        <v>377080</v>
+        <v>43019965</v>
       </c>
       <c r="G3" t="n">
-        <v>268401</v>
+        <v>28551376</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4049127983874874</v>
+        <v>0.5067562768253271</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4353.5</v>
+        <v>439</v>
       </c>
       <c r="C4" t="n">
-        <v>4380.3</v>
+        <v>447.2</v>
       </c>
       <c r="D4" t="n">
-        <v>4287</v>
+        <v>434.8</v>
       </c>
       <c r="E4" t="n">
-        <v>4325.9</v>
+        <v>438.5</v>
       </c>
       <c r="F4" t="n">
-        <v>413700</v>
+        <v>15824576</v>
       </c>
       <c r="G4" t="n">
-        <v>284382</v>
+        <v>10553695</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4547334219465367</v>
+        <v>0.4994346529817282</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>COALINDIA</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>JIOFIN</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>980</v>
+        <v>233.95</v>
       </c>
       <c r="C5" t="n">
-        <v>1007.7</v>
+        <v>233.95</v>
       </c>
       <c r="D5" t="n">
-        <v>979.8</v>
+        <v>226.3</v>
       </c>
       <c r="E5" t="n">
-        <v>997.2</v>
+        <v>232.5</v>
       </c>
       <c r="F5" t="n">
-        <v>1529030</v>
+        <v>19524751</v>
       </c>
       <c r="G5" t="n">
-        <v>1006629</v>
+        <v>12566465</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5189608087984749</v>
+        <v>0.5537186472090599</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>JIOFIN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1352.5</v>
+        <v>7517</v>
       </c>
       <c r="C6" t="n">
-        <v>1365</v>
+        <v>7517</v>
       </c>
       <c r="D6" t="n">
-        <v>1340.3</v>
+        <v>7237</v>
       </c>
       <c r="E6" t="n">
-        <v>1351</v>
+        <v>7275</v>
       </c>
       <c r="F6" t="n">
-        <v>489820</v>
+        <v>554984</v>
       </c>
       <c r="G6" t="n">
-        <v>320753</v>
+        <v>366235</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5270940567975981</v>
+        <v>0.5153767389790708</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>78</v>
+        <v>655</v>
       </c>
       <c r="C7" t="n">
-        <v>81.91</v>
+        <v>659.9</v>
       </c>
       <c r="D7" t="n">
-        <v>77.95</v>
+        <v>642.1</v>
       </c>
       <c r="E7" t="n">
-        <v>79.89</v>
+        <v>653.75</v>
       </c>
       <c r="F7" t="n">
-        <v>32383963</v>
+        <v>4330230</v>
       </c>
       <c r="G7" t="n">
-        <v>20259988</v>
+        <v>2997163</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5984196535555697</v>
+        <v>0.4447762767657281</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1741.6</v>
+        <v>7588</v>
       </c>
       <c r="C8" t="n">
-        <v>1748.5</v>
+        <v>7809</v>
       </c>
       <c r="D8" t="n">
-        <v>1693.3</v>
+        <v>7556</v>
       </c>
       <c r="E8" t="n">
-        <v>1706.9</v>
+        <v>7791</v>
       </c>
       <c r="F8" t="n">
-        <v>1221346</v>
+        <v>358612</v>
       </c>
       <c r="G8" t="n">
-        <v>833743</v>
+        <v>225749</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4648950575896889</v>
+        <v>0.5885430278760925</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IREDA</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>116.5</v>
+        <v>152</v>
       </c>
       <c r="C9" t="n">
-        <v>120.35</v>
+        <v>152</v>
       </c>
       <c r="D9" t="n">
-        <v>115.08</v>
+        <v>146.41</v>
       </c>
       <c r="E9" t="n">
-        <v>117.4</v>
+        <v>149.18</v>
       </c>
       <c r="F9" t="n">
-        <v>12595130</v>
+        <v>20704576</v>
       </c>
       <c r="G9" t="n">
-        <v>8974731</v>
+        <v>14633439</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4033991659471465</v>
+        <v>0.414881081610413</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>IREDA</t>
+          <t>GAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>RECLTD</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>332</v>
+      </c>
+      <c r="C10" t="n">
+        <v>333.2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>321</v>
+      </c>
+      <c r="E10" t="n">
+        <v>325.5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>7988489</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5579379</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.4317881972169304</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>RECLTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>119.01</v>
+      </c>
+      <c r="C11" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>113</v>
+      </c>
+      <c r="E11" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>14850245</v>
+      </c>
+      <c r="G11" t="n">
+        <v>10309068</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.440503157026416</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1400</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1403.4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1366.6</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1383.3</v>
+      </c>
+      <c r="F12" t="n">
+        <v>806385</v>
+      </c>
+      <c r="G12" t="n">
+        <v>563184</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.431832225347311</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>UPL</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>610</v>
+      </c>
+      <c r="C13" t="n">
+        <v>627.4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>606.25</v>
+      </c>
+      <c r="E13" t="n">
+        <v>625</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4705618</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3095128</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.5203306616075328</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>UPL</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>KEI</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>4860</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4875</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4670.5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4800</v>
+      </c>
+      <c r="F14" t="n">
+        <v>475141</v>
+      </c>
+      <c r="G14" t="n">
+        <v>336511</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.4119627590182787</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>KEI</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NHPC</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>73</v>
+      </c>
+      <c r="C15" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="D15" t="n">
+        <v>72.09</v>
+      </c>
+      <c r="E15" t="n">
+        <v>73.05</v>
+      </c>
+      <c r="F15" t="n">
+        <v>22232154</v>
+      </c>
+      <c r="G15" t="n">
+        <v>14268041</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.5581784493049887</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>NHPC</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>VOLTAS</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1462</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1469.7</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1413</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1435.1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1094929</v>
+      </c>
+      <c r="G16" t="n">
+        <v>686869</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.5940870821073596</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>VOLTAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>LTF</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>265.6</v>
+      </c>
+      <c r="C17" t="n">
+        <v>266.9</v>
+      </c>
+      <c r="D17" t="n">
+        <v>259.8</v>
+      </c>
+      <c r="E17" t="n">
+        <v>266.6</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4006690</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2656845</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.508063135034223</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>LTF</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ICICIPRULI</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>610</v>
+      </c>
+      <c r="C18" t="n">
+        <v>610</v>
+      </c>
+      <c r="D18" t="n">
+        <v>552.65</v>
+      </c>
+      <c r="E18" t="n">
+        <v>604</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1356677</v>
+      </c>
+      <c r="G18" t="n">
+        <v>901309</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.5052296160362317</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ICICIPRULI</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>HUDCO</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>173</v>
+      </c>
+      <c r="C19" t="n">
+        <v>174.94</v>
+      </c>
+      <c r="D19" t="n">
+        <v>167.44</v>
+      </c>
+      <c r="E19" t="n">
+        <v>174.5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4568695</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2905206</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.5725890005734533</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>HUDCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>470</v>
+      </c>
+      <c r="C20" t="n">
+        <v>475.7</v>
+      </c>
+      <c r="D20" t="n">
+        <v>461</v>
+      </c>
+      <c r="E20" t="n">
+        <v>475.35</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1490001</v>
+      </c>
+      <c r="G20" t="n">
+        <v>972797</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.5316669356505006</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>IRB</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>40.01</v>
+      </c>
+      <c r="C21" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="D21" t="n">
+        <v>39.75</v>
+      </c>
+      <c r="E21" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>7656329</v>
+      </c>
+      <c r="G21" t="n">
+        <v>5354011</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.4300174205843059</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>IRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>POONAWALLA</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>415</v>
+      </c>
+      <c r="C22" t="n">
+        <v>416.95</v>
+      </c>
+      <c r="D22" t="n">
+        <v>404.15</v>
+      </c>
+      <c r="E22" t="n">
+        <v>410</v>
+      </c>
+      <c r="F22" t="n">
+        <v>580988</v>
+      </c>
+      <c r="G22" t="n">
+        <v>408658</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.4216973606291814</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>POONAWALLA</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,264 +479,198 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>WIPRO</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1839.1</v>
+        <v>200.5</v>
       </c>
       <c r="C2" t="n">
-        <v>1844.6</v>
+        <v>201.31</v>
       </c>
       <c r="D2" t="n">
-        <v>1802</v>
+        <v>197.42</v>
       </c>
       <c r="E2" t="n">
-        <v>1840.9</v>
+        <v>200.99</v>
       </c>
       <c r="F2" t="n">
-        <v>1009617</v>
+        <v>12982340</v>
       </c>
       <c r="G2" t="n">
-        <v>2267317</v>
+        <v>25862728</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5547084946657217</v>
+        <v>-0.4980289782268909</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>WIPRO</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IRFC</t>
+          <t>BPCL</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>97.11</v>
+        <v>336.5</v>
       </c>
       <c r="C3" t="n">
-        <v>97.95</v>
+        <v>342.2</v>
       </c>
       <c r="D3" t="n">
-        <v>95.27</v>
+        <v>324.35</v>
       </c>
       <c r="E3" t="n">
-        <v>97.75</v>
+        <v>327.05</v>
       </c>
       <c r="F3" t="n">
-        <v>16395706</v>
+        <v>15916729</v>
       </c>
       <c r="G3" t="n">
-        <v>35489993</v>
+        <v>34756111</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5380189001446126</v>
+        <v>-0.5420451672513072</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>IRFC</t>
+          <t>BPCL</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BDL</t>
+          <t>HINDPETRO</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1357</v>
+        <v>396</v>
       </c>
       <c r="C4" t="n">
-        <v>1358.8</v>
+        <v>406.65</v>
       </c>
       <c r="D4" t="n">
-        <v>1298</v>
+        <v>381.1</v>
       </c>
       <c r="E4" t="n">
-        <v>1331.1</v>
+        <v>388.7</v>
       </c>
       <c r="F4" t="n">
-        <v>2077090</v>
+        <v>11411957</v>
       </c>
       <c r="G4" t="n">
-        <v>5023734</v>
+        <v>24836194</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5865445901395256</v>
+        <v>-0.5405110380439129</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>BDL</t>
+          <t>HINDPETRO</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4740</v>
+        <v>504.35</v>
       </c>
       <c r="C5" t="n">
-        <v>4750</v>
+        <v>514.95</v>
       </c>
       <c r="D5" t="n">
-        <v>4621.8</v>
+        <v>504.35</v>
       </c>
       <c r="E5" t="n">
-        <v>4681.1</v>
+        <v>514.1</v>
       </c>
       <c r="F5" t="n">
-        <v>360922</v>
+        <v>1179868</v>
       </c>
       <c r="G5" t="n">
-        <v>892005</v>
+        <v>2597772</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5953811918094629</v>
+        <v>-0.5458154141318021</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ASTRAL</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1677</v>
+        <v>1440</v>
       </c>
       <c r="C6" t="n">
-        <v>1677</v>
+        <v>1464.2</v>
       </c>
       <c r="D6" t="n">
-        <v>1595.2</v>
+        <v>1440</v>
       </c>
       <c r="E6" t="n">
-        <v>1602.5</v>
+        <v>1455.1</v>
       </c>
       <c r="F6" t="n">
-        <v>527194</v>
+        <v>250242</v>
       </c>
       <c r="G6" t="n">
-        <v>1096077</v>
+        <v>566845</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.519017368305329</v>
+        <v>-0.5585354020940468</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ASTRAL</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PAGEIND</t>
+          <t>ANGELONE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30940</v>
+        <v>222.99</v>
       </c>
       <c r="C7" t="n">
-        <v>31350</v>
+        <v>226.5</v>
       </c>
       <c r="D7" t="n">
-        <v>30820</v>
+        <v>220.25</v>
       </c>
       <c r="E7" t="n">
-        <v>31085</v>
+        <v>226.5</v>
       </c>
       <c r="F7" t="n">
-        <v>11361</v>
+        <v>4421152</v>
       </c>
       <c r="G7" t="n">
-        <v>24708</v>
+        <v>8704812</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5401894123360855</v>
+        <v>-0.492102529037962</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PAGEIND</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>DALBHARAT</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1884.3</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1884.3</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1822</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1843.2</v>
-      </c>
-      <c r="F8" t="n">
-        <v>86055</v>
-      </c>
-      <c r="G8" t="n">
-        <v>183615</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-0.531329139776162</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>DALBHARAT</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>TITAGARH</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>669.05</v>
-      </c>
-      <c r="C9" t="n">
-        <v>669.05</v>
-      </c>
-      <c r="D9" t="n">
-        <v>642.2</v>
-      </c>
-      <c r="E9" t="n">
-        <v>660</v>
-      </c>
-      <c r="F9" t="n">
-        <v>802295</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1752717</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-0.5422563939301096</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>TITAGARH</t>
+          <t>ANGELONE</t>
         </is>
       </c>
     </row>
@@ -751,7 +685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -804,691 +738,394 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>957.5</v>
+        <v>850.05</v>
       </c>
       <c r="C2" t="n">
-        <v>993</v>
+        <v>856.8</v>
       </c>
       <c r="D2" t="n">
-        <v>934.2</v>
+        <v>840.6</v>
       </c>
       <c r="E2" t="n">
-        <v>989.9</v>
+        <v>849</v>
       </c>
       <c r="F2" t="n">
-        <v>11999852</v>
+        <v>52866024</v>
       </c>
       <c r="G2" t="n">
-        <v>8166989</v>
+        <v>35592613</v>
       </c>
       <c r="H2" t="n">
-        <v>0.469311639822216</v>
+        <v>0.4853088757490213</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>193.45</v>
+        <v>1880.8</v>
       </c>
       <c r="C3" t="n">
-        <v>193.7</v>
+        <v>1881</v>
       </c>
       <c r="D3" t="n">
-        <v>187.03</v>
+        <v>1846.5</v>
       </c>
       <c r="E3" t="n">
-        <v>191.13</v>
+        <v>1855.7</v>
       </c>
       <c r="F3" t="n">
-        <v>43019965</v>
+        <v>11741600</v>
       </c>
       <c r="G3" t="n">
-        <v>28551376</v>
+        <v>8073518</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5067562768253271</v>
+        <v>0.4543350247067016</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>439</v>
+        <v>1288</v>
       </c>
       <c r="C4" t="n">
-        <v>447.2</v>
+        <v>1329.6</v>
       </c>
       <c r="D4" t="n">
-        <v>434.8</v>
+        <v>1288</v>
       </c>
       <c r="E4" t="n">
-        <v>438.5</v>
+        <v>1311.1</v>
       </c>
       <c r="F4" t="n">
-        <v>15824576</v>
+        <v>2329349</v>
       </c>
       <c r="G4" t="n">
-        <v>10553695</v>
+        <v>1597730</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4994346529817282</v>
+        <v>0.457911536993109</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>DRREDDY</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>233.95</v>
+        <v>720</v>
       </c>
       <c r="C5" t="n">
-        <v>233.95</v>
+        <v>723.95</v>
       </c>
       <c r="D5" t="n">
-        <v>226.3</v>
+        <v>703.1</v>
       </c>
       <c r="E5" t="n">
-        <v>232.5</v>
+        <v>722.85</v>
       </c>
       <c r="F5" t="n">
-        <v>19524751</v>
+        <v>14950497</v>
       </c>
       <c r="G5" t="n">
-        <v>12566465</v>
+        <v>10105473</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5537186472090599</v>
+        <v>0.4794455440136251</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>VEDL</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7517</v>
+        <v>375.9</v>
       </c>
       <c r="C6" t="n">
-        <v>7517</v>
+        <v>384.15</v>
       </c>
       <c r="D6" t="n">
-        <v>7237</v>
+        <v>375.9</v>
       </c>
       <c r="E6" t="n">
-        <v>7275</v>
+        <v>380.55</v>
       </c>
       <c r="F6" t="n">
-        <v>554984</v>
+        <v>7675259</v>
       </c>
       <c r="G6" t="n">
-        <v>366235</v>
+        <v>5063475</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5153767389790708</v>
+        <v>0.5158086096998603</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>655</v>
+        <v>706</v>
       </c>
       <c r="C7" t="n">
-        <v>659.9</v>
+        <v>731.95</v>
       </c>
       <c r="D7" t="n">
-        <v>642.1</v>
+        <v>703.3</v>
       </c>
       <c r="E7" t="n">
-        <v>653.75</v>
+        <v>730</v>
       </c>
       <c r="F7" t="n">
-        <v>4330230</v>
+        <v>3876241</v>
       </c>
       <c r="G7" t="n">
-        <v>2997163</v>
+        <v>2675404</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4447762767657281</v>
+        <v>0.4488432401237346</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>CGPOWER</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>GODREJCP</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7588</v>
+        <v>1111.6</v>
       </c>
       <c r="C8" t="n">
-        <v>7809</v>
+        <v>1123.4</v>
       </c>
       <c r="D8" t="n">
-        <v>7556</v>
+        <v>1092.6</v>
       </c>
       <c r="E8" t="n">
-        <v>7791</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="n">
-        <v>358612</v>
+        <v>1489620</v>
       </c>
       <c r="G8" t="n">
-        <v>225749</v>
+        <v>954053</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5885430278760925</v>
+        <v>0.5613597986694659</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>GODREJCP</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>CUMMINSIND</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>152</v>
+        <v>4780</v>
       </c>
       <c r="C9" t="n">
-        <v>152</v>
+        <v>4909.5</v>
       </c>
       <c r="D9" t="n">
-        <v>146.41</v>
+        <v>4655.2</v>
       </c>
       <c r="E9" t="n">
-        <v>149.18</v>
+        <v>4719</v>
       </c>
       <c r="F9" t="n">
-        <v>20704576</v>
+        <v>557032</v>
       </c>
       <c r="G9" t="n">
-        <v>14633439</v>
+        <v>360922</v>
       </c>
       <c r="H9" t="n">
-        <v>0.414881081610413</v>
+        <v>0.5433583987676007</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>CUMMINSIND</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>332</v>
+        <v>1120</v>
       </c>
       <c r="C10" t="n">
-        <v>333.2</v>
+        <v>1125.7</v>
       </c>
       <c r="D10" t="n">
-        <v>321</v>
+        <v>1089.4</v>
       </c>
       <c r="E10" t="n">
-        <v>325.5</v>
+        <v>1114</v>
       </c>
       <c r="F10" t="n">
-        <v>7988489</v>
+        <v>1883751</v>
       </c>
       <c r="G10" t="n">
-        <v>5579379</v>
+        <v>1268685</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4317881972169304</v>
+        <v>0.4848059210915239</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>ASTRAL</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>119.01</v>
+        <v>1625.4</v>
       </c>
       <c r="C11" t="n">
-        <v>119.5</v>
+        <v>1668</v>
       </c>
       <c r="D11" t="n">
-        <v>113</v>
+        <v>1625.4</v>
       </c>
       <c r="E11" t="n">
-        <v>118.5</v>
+        <v>1665</v>
       </c>
       <c r="F11" t="n">
-        <v>14850245</v>
+        <v>818683</v>
       </c>
       <c r="G11" t="n">
-        <v>10309068</v>
+        <v>527194</v>
       </c>
       <c r="H11" t="n">
-        <v>0.440503157026416</v>
+        <v>0.552906520180427</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>ASTRAL</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>SUPREMEIND</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1400</v>
+        <v>3861</v>
       </c>
       <c r="C12" t="n">
-        <v>1403.4</v>
+        <v>3956</v>
       </c>
       <c r="D12" t="n">
-        <v>1366.6</v>
+        <v>3861</v>
       </c>
       <c r="E12" t="n">
-        <v>1383.3</v>
+        <v>3947.9</v>
       </c>
       <c r="F12" t="n">
-        <v>806385</v>
+        <v>329143</v>
       </c>
       <c r="G12" t="n">
-        <v>563184</v>
+        <v>224138</v>
       </c>
       <c r="H12" t="n">
-        <v>0.431832225347311</v>
+        <v>0.4684837020050148</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>SUPREMEIND</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>UPL</t>
+          <t>POONAWALLA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>610</v>
+        <v>416.95</v>
       </c>
       <c r="C13" t="n">
-        <v>627.4</v>
+        <v>426.5</v>
       </c>
       <c r="D13" t="n">
-        <v>606.25</v>
+        <v>412.3</v>
       </c>
       <c r="E13" t="n">
-        <v>625</v>
+        <v>425.15</v>
       </c>
       <c r="F13" t="n">
-        <v>4705618</v>
+        <v>823564</v>
       </c>
       <c r="G13" t="n">
-        <v>3095128</v>
+        <v>580988</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5203306616075328</v>
+        <v>0.4175232534923269</v>
       </c>
       <c r="I13" t="inlineStr">
-        <is>
-          <t>UPL</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>KEI</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>4860</v>
-      </c>
-      <c r="C14" t="n">
-        <v>4875</v>
-      </c>
-      <c r="D14" t="n">
-        <v>4670.5</v>
-      </c>
-      <c r="E14" t="n">
-        <v>4800</v>
-      </c>
-      <c r="F14" t="n">
-        <v>475141</v>
-      </c>
-      <c r="G14" t="n">
-        <v>336511</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.4119627590182787</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>KEI</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>NHPC</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>73</v>
-      </c>
-      <c r="C15" t="n">
-        <v>73.40000000000001</v>
-      </c>
-      <c r="D15" t="n">
-        <v>72.09</v>
-      </c>
-      <c r="E15" t="n">
-        <v>73.05</v>
-      </c>
-      <c r="F15" t="n">
-        <v>22232154</v>
-      </c>
-      <c r="G15" t="n">
-        <v>14268041</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.5581784493049887</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>NHPC</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>VOLTAS</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1462</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1469.7</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1413</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1435.1</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1094929</v>
-      </c>
-      <c r="G16" t="n">
-        <v>686869</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.5940870821073596</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>VOLTAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>LTF</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>265.6</v>
-      </c>
-      <c r="C17" t="n">
-        <v>266.9</v>
-      </c>
-      <c r="D17" t="n">
-        <v>259.8</v>
-      </c>
-      <c r="E17" t="n">
-        <v>266.6</v>
-      </c>
-      <c r="F17" t="n">
-        <v>4006690</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2656845</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.508063135034223</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>LTF</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>ICICIPRULI</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>610</v>
-      </c>
-      <c r="C18" t="n">
-        <v>610</v>
-      </c>
-      <c r="D18" t="n">
-        <v>552.65</v>
-      </c>
-      <c r="E18" t="n">
-        <v>604</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1356677</v>
-      </c>
-      <c r="G18" t="n">
-        <v>901309</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.5052296160362317</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>ICICIPRULI</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>HUDCO</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>173</v>
-      </c>
-      <c r="C19" t="n">
-        <v>174.94</v>
-      </c>
-      <c r="D19" t="n">
-        <v>167.44</v>
-      </c>
-      <c r="E19" t="n">
-        <v>174.5</v>
-      </c>
-      <c r="F19" t="n">
-        <v>4568695</v>
-      </c>
-      <c r="G19" t="n">
-        <v>2905206</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.5725890005734533</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>HUDCO</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>CONCOR</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>470</v>
-      </c>
-      <c r="C20" t="n">
-        <v>475.7</v>
-      </c>
-      <c r="D20" t="n">
-        <v>461</v>
-      </c>
-      <c r="E20" t="n">
-        <v>475.35</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1490001</v>
-      </c>
-      <c r="G20" t="n">
-        <v>972797</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.5316669356505006</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>CONCOR</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>IRB</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>40.01</v>
-      </c>
-      <c r="C21" t="n">
-        <v>40.6</v>
-      </c>
-      <c r="D21" t="n">
-        <v>39.75</v>
-      </c>
-      <c r="E21" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="F21" t="n">
-        <v>7656329</v>
-      </c>
-      <c r="G21" t="n">
-        <v>5354011</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.4300174205843059</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>IRB</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>POONAWALLA</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>415</v>
-      </c>
-      <c r="C22" t="n">
-        <v>416.95</v>
-      </c>
-      <c r="D22" t="n">
-        <v>404.15</v>
-      </c>
-      <c r="E22" t="n">
-        <v>410</v>
-      </c>
-      <c r="F22" t="n">
-        <v>580988</v>
-      </c>
-      <c r="G22" t="n">
-        <v>408658</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.4216973606291814</v>
-      </c>
-      <c r="I22" t="inlineStr">
         <is>
           <t>POONAWALLA</t>
         </is>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,198 +479,231 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>200.5</v>
+        <v>1021.1</v>
       </c>
       <c r="C2" t="n">
-        <v>201.31</v>
+        <v>1046.7</v>
       </c>
       <c r="D2" t="n">
-        <v>197.42</v>
+        <v>1006.1</v>
       </c>
       <c r="E2" t="n">
-        <v>200.99</v>
+        <v>1029.1</v>
       </c>
       <c r="F2" t="n">
-        <v>12982340</v>
+        <v>7054662</v>
       </c>
       <c r="G2" t="n">
-        <v>25862728</v>
+        <v>14297519</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4980289782268909</v>
+        <v>-0.5065813866028085</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>336.5</v>
+        <v>10475</v>
       </c>
       <c r="C3" t="n">
-        <v>342.2</v>
+        <v>10849</v>
       </c>
       <c r="D3" t="n">
-        <v>324.35</v>
+        <v>10254</v>
       </c>
       <c r="E3" t="n">
-        <v>327.05</v>
+        <v>10803</v>
       </c>
       <c r="F3" t="n">
-        <v>15916729</v>
+        <v>968428</v>
       </c>
       <c r="G3" t="n">
-        <v>34756111</v>
+        <v>2031360</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5420451672513072</v>
+        <v>-0.5232612633900441</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>DIXON</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HINDPETRO</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>396</v>
+        <v>7400</v>
       </c>
       <c r="C4" t="n">
-        <v>406.65</v>
+        <v>7538</v>
       </c>
       <c r="D4" t="n">
-        <v>381.1</v>
+        <v>7282</v>
       </c>
       <c r="E4" t="n">
-        <v>388.7</v>
+        <v>7442</v>
       </c>
       <c r="F4" t="n">
-        <v>11411957</v>
+        <v>498945</v>
       </c>
       <c r="G4" t="n">
-        <v>24836194</v>
+        <v>1056999</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5405110380439129</v>
+        <v>-0.5279607643905055</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>HINDPETRO</t>
+          <t>POLYCAB</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>504.35</v>
+        <v>1638.9</v>
       </c>
       <c r="C5" t="n">
-        <v>514.95</v>
+        <v>1649.6</v>
       </c>
       <c r="D5" t="n">
-        <v>504.35</v>
+        <v>1600.6</v>
       </c>
       <c r="E5" t="n">
-        <v>514.1</v>
+        <v>1612.2</v>
       </c>
       <c r="F5" t="n">
-        <v>1179868</v>
+        <v>762875</v>
       </c>
       <c r="G5" t="n">
-        <v>2597772</v>
+        <v>1595426</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5458154141318021</v>
+        <v>-0.5218361741628882</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TORNTPOWER</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1440</v>
+        <v>2179</v>
       </c>
       <c r="C6" t="n">
-        <v>1464.2</v>
+        <v>2213</v>
       </c>
       <c r="D6" t="n">
-        <v>1440</v>
+        <v>2157</v>
       </c>
       <c r="E6" t="n">
-        <v>1455.1</v>
+        <v>2184.4</v>
       </c>
       <c r="F6" t="n">
-        <v>250242</v>
+        <v>423505</v>
       </c>
       <c r="G6" t="n">
-        <v>566845</v>
+        <v>886101</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5585354020940468</v>
+        <v>-0.5220578692496679</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>TORNTPOWER</t>
+          <t>MPHASIS</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ANGELONE</t>
+          <t>PRESTIGE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>222.99</v>
+        <v>1269.9</v>
       </c>
       <c r="C7" t="n">
-        <v>226.5</v>
+        <v>1283.8</v>
       </c>
       <c r="D7" t="n">
-        <v>220.25</v>
+        <v>1237.4</v>
       </c>
       <c r="E7" t="n">
-        <v>226.5</v>
+        <v>1264</v>
       </c>
       <c r="F7" t="n">
-        <v>4421152</v>
+        <v>483947</v>
       </c>
       <c r="G7" t="n">
-        <v>8704812</v>
+        <v>961586</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.492102529037962</v>
+        <v>-0.496720002163093</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ANGELONE</t>
+          <t>PRESTIGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SONACOMS</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>508</v>
+      </c>
+      <c r="C8" t="n">
+        <v>515.05</v>
+      </c>
+      <c r="D8" t="n">
+        <v>502.7</v>
+      </c>
+      <c r="E8" t="n">
+        <v>510.85</v>
+      </c>
+      <c r="F8" t="n">
+        <v>748268</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1840641</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.5934742299014311</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>SONACOMS</t>
         </is>
       </c>
     </row>
@@ -685,7 +718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -738,396 +771,528 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>850.05</v>
+        <v>1243.2</v>
       </c>
       <c r="C2" t="n">
-        <v>856.8</v>
+        <v>1251.1</v>
       </c>
       <c r="D2" t="n">
-        <v>840.6</v>
+        <v>1231.8</v>
       </c>
       <c r="E2" t="n">
-        <v>849</v>
+        <v>1234.9</v>
       </c>
       <c r="F2" t="n">
-        <v>52866024</v>
+        <v>9663320</v>
       </c>
       <c r="G2" t="n">
-        <v>35592613</v>
+        <v>6289277</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4853088757490213</v>
+        <v>0.5364754963090352</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>AXISBANK</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1880.8</v>
+        <v>13430</v>
       </c>
       <c r="C3" t="n">
-        <v>1881</v>
+        <v>13430</v>
       </c>
       <c r="D3" t="n">
-        <v>1846.5</v>
+        <v>12966</v>
       </c>
       <c r="E3" t="n">
-        <v>1855.7</v>
+        <v>12995</v>
       </c>
       <c r="F3" t="n">
-        <v>11741600</v>
+        <v>544683</v>
       </c>
       <c r="G3" t="n">
-        <v>8073518</v>
+        <v>353715</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4543350247067016</v>
+        <v>0.5398922861625886</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>MARUTI</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1288</v>
+        <v>7590</v>
       </c>
       <c r="C4" t="n">
-        <v>1329.6</v>
+        <v>7662.5</v>
       </c>
       <c r="D4" t="n">
-        <v>1288</v>
+        <v>7542.5</v>
       </c>
       <c r="E4" t="n">
-        <v>1311.1</v>
+        <v>7576</v>
       </c>
       <c r="F4" t="n">
-        <v>2329349</v>
+        <v>550020</v>
       </c>
       <c r="G4" t="n">
-        <v>1597730</v>
+        <v>381453</v>
       </c>
       <c r="H4" t="n">
-        <v>0.457911536993109</v>
+        <v>0.4419076531053629</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>WIPRO</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>720</v>
+        <v>201.06</v>
       </c>
       <c r="C5" t="n">
-        <v>723.95</v>
+        <v>203.8</v>
       </c>
       <c r="D5" t="n">
-        <v>703.1</v>
+        <v>199.7</v>
       </c>
       <c r="E5" t="n">
-        <v>722.85</v>
+        <v>201.96</v>
       </c>
       <c r="F5" t="n">
-        <v>14950497</v>
+        <v>19042475</v>
       </c>
       <c r="G5" t="n">
-        <v>10105473</v>
+        <v>12982340</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4794455440136251</v>
+        <v>0.4667983583853142</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>WIPRO</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>375.9</v>
+        <v>1350</v>
       </c>
       <c r="C6" t="n">
-        <v>384.15</v>
+        <v>1363.4</v>
       </c>
       <c r="D6" t="n">
-        <v>375.9</v>
+        <v>1341</v>
       </c>
       <c r="E6" t="n">
-        <v>380.55</v>
+        <v>1357</v>
       </c>
       <c r="F6" t="n">
-        <v>7675259</v>
+        <v>2616965</v>
       </c>
       <c r="G6" t="n">
-        <v>5063475</v>
+        <v>1671877</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5158086096998603</v>
+        <v>0.565285604144324</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>HCLTECH</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>706</v>
+        <v>1925</v>
       </c>
       <c r="C7" t="n">
-        <v>731.95</v>
+        <v>1948.1</v>
       </c>
       <c r="D7" t="n">
-        <v>703.3</v>
+        <v>1907</v>
       </c>
       <c r="E7" t="n">
-        <v>730</v>
+        <v>1940.9</v>
       </c>
       <c r="F7" t="n">
-        <v>3876241</v>
+        <v>868643</v>
       </c>
       <c r="G7" t="n">
-        <v>2675404</v>
+        <v>587710</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4488432401237346</v>
+        <v>0.4780129655782614</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>SBILIFE</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>BOSCHLTD</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1111.6</v>
+        <v>31620</v>
       </c>
       <c r="C8" t="n">
-        <v>1123.4</v>
+        <v>31620</v>
       </c>
       <c r="D8" t="n">
-        <v>1092.6</v>
+        <v>30815</v>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>31300</v>
       </c>
       <c r="F8" t="n">
-        <v>1489620</v>
+        <v>27041</v>
       </c>
       <c r="G8" t="n">
-        <v>954053</v>
+        <v>17509</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5613597986694659</v>
+        <v>0.5444057341938432</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>BOSCHLTD</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4780</v>
+        <v>403.5</v>
       </c>
       <c r="C9" t="n">
-        <v>4909.5</v>
+        <v>410.2</v>
       </c>
       <c r="D9" t="n">
-        <v>4655.2</v>
+        <v>385.95</v>
       </c>
       <c r="E9" t="n">
-        <v>4719</v>
+        <v>408.5</v>
       </c>
       <c r="F9" t="n">
-        <v>557032</v>
+        <v>20128518</v>
       </c>
       <c r="G9" t="n">
-        <v>360922</v>
+        <v>13040542</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5433583987676007</v>
+        <v>0.5435338500500976</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>SUZLON</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1120</v>
+        <v>41.51</v>
       </c>
       <c r="C10" t="n">
-        <v>1125.7</v>
+        <v>43.54</v>
       </c>
       <c r="D10" t="n">
-        <v>1089.4</v>
+        <v>40.93</v>
       </c>
       <c r="E10" t="n">
-        <v>1114</v>
+        <v>42.53</v>
       </c>
       <c r="F10" t="n">
-        <v>1883751</v>
+        <v>108432510</v>
       </c>
       <c r="G10" t="n">
-        <v>1268685</v>
+        <v>70866917</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4848059210915239</v>
+        <v>0.5300864576908292</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>SUZLON</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ASTRAL</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1625.4</v>
+        <v>73</v>
       </c>
       <c r="C11" t="n">
-        <v>1668</v>
+        <v>76.36</v>
       </c>
       <c r="D11" t="n">
-        <v>1625.4</v>
+        <v>72.76000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>1665</v>
+        <v>74.86</v>
       </c>
       <c r="F11" t="n">
-        <v>818683</v>
+        <v>16804967</v>
       </c>
       <c r="G11" t="n">
-        <v>527194</v>
+        <v>11915288</v>
       </c>
       <c r="H11" t="n">
-        <v>0.552906520180427</v>
+        <v>0.410370189960998</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ASTRAL</t>
+          <t>NHPC</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SUPREMEIND</t>
+          <t>KALYANKJIL</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3861</v>
+        <v>388.5</v>
       </c>
       <c r="C12" t="n">
-        <v>3956</v>
+        <v>393.65</v>
       </c>
       <c r="D12" t="n">
-        <v>3861</v>
+        <v>378.6</v>
       </c>
       <c r="E12" t="n">
-        <v>3947.9</v>
+        <v>389.5</v>
       </c>
       <c r="F12" t="n">
-        <v>329143</v>
+        <v>3218077</v>
       </c>
       <c r="G12" t="n">
-        <v>224138</v>
+        <v>2143619</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4684837020050148</v>
+        <v>0.5012355273954934</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>SUPREMEIND</t>
+          <t>KALYANKJIL</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>POONAWALLA</t>
+          <t>BLUESTARCO</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>416.95</v>
+        <v>1941</v>
       </c>
       <c r="C13" t="n">
-        <v>426.5</v>
+        <v>1969.5</v>
       </c>
       <c r="D13" t="n">
-        <v>412.3</v>
+        <v>1892</v>
       </c>
       <c r="E13" t="n">
-        <v>425.15</v>
+        <v>1942</v>
       </c>
       <c r="F13" t="n">
-        <v>823564</v>
+        <v>638482</v>
       </c>
       <c r="G13" t="n">
-        <v>580988</v>
+        <v>440437</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4175232534923269</v>
+        <v>0.4496556828785956</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>POONAWALLA</t>
+          <t>BLUESTARCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>IREDA</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>114</v>
+      </c>
+      <c r="C14" t="n">
+        <v>118.95</v>
+      </c>
+      <c r="D14" t="n">
+        <v>112.59</v>
+      </c>
+      <c r="E14" t="n">
+        <v>117</v>
+      </c>
+      <c r="F14" t="n">
+        <v>9357674</v>
+      </c>
+      <c r="G14" t="n">
+        <v>6188063</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.5122137573583204</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>IREDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SBICARD</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>712</v>
+      </c>
+      <c r="C15" t="n">
+        <v>715</v>
+      </c>
+      <c r="D15" t="n">
+        <v>698</v>
+      </c>
+      <c r="E15" t="n">
+        <v>710.2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>831279</v>
+      </c>
+      <c r="G15" t="n">
+        <v>519996</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.598625758659682</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>SBICARD</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PIIND</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2981.1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2997.2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2940.1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2940.1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>196476</v>
+      </c>
+      <c r="G16" t="n">
+        <v>140106</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.4023382296261402</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>PIIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>KAYNES</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>3694.6</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3786</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3586</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3695</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1473221</v>
+      </c>
+      <c r="G17" t="n">
+        <v>930709</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.5829018522438271</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>KAYNES</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,231 +479,297 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1021.1</v>
+        <v>861</v>
       </c>
       <c r="C2" t="n">
-        <v>1046.7</v>
+        <v>868.35</v>
       </c>
       <c r="D2" t="n">
-        <v>1006.1</v>
+        <v>848.8</v>
       </c>
       <c r="E2" t="n">
-        <v>1029.1</v>
+        <v>856.5</v>
       </c>
       <c r="F2" t="n">
-        <v>7054662</v>
+        <v>6668639</v>
       </c>
       <c r="G2" t="n">
-        <v>14297519</v>
+        <v>15508258</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5065813866028085</v>
+        <v>-0.5699943217349105</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>SRF</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10475</v>
+        <v>2609.9</v>
       </c>
       <c r="C3" t="n">
-        <v>10849</v>
+        <v>2623.5</v>
       </c>
       <c r="D3" t="n">
-        <v>10254</v>
+        <v>2491.3</v>
       </c>
       <c r="E3" t="n">
-        <v>10803</v>
+        <v>2500.4</v>
       </c>
       <c r="F3" t="n">
-        <v>968428</v>
+        <v>649413</v>
       </c>
       <c r="G3" t="n">
-        <v>2031360</v>
+        <v>1288113</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5232612633900441</v>
+        <v>-0.4958415915373884</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>SRF</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7400</v>
+        <v>439.15</v>
       </c>
       <c r="C4" t="n">
-        <v>7538</v>
+        <v>440.8</v>
       </c>
       <c r="D4" t="n">
-        <v>7282</v>
+        <v>422.7</v>
       </c>
       <c r="E4" t="n">
-        <v>7442</v>
+        <v>424.5</v>
       </c>
       <c r="F4" t="n">
-        <v>498945</v>
+        <v>2702224</v>
       </c>
       <c r="G4" t="n">
-        <v>1056999</v>
+        <v>5403935</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5279607643905055</v>
+        <v>-0.4999525345882214</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1638.9</v>
+        <v>2006.8</v>
       </c>
       <c r="C5" t="n">
-        <v>1649.6</v>
+        <v>2013.5</v>
       </c>
       <c r="D5" t="n">
-        <v>1600.6</v>
+        <v>1908.5</v>
       </c>
       <c r="E5" t="n">
-        <v>1612.2</v>
+        <v>1933.3</v>
       </c>
       <c r="F5" t="n">
-        <v>762875</v>
+        <v>560842</v>
       </c>
       <c r="G5" t="n">
-        <v>1595426</v>
+        <v>1360299</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5218361741628882</v>
+        <v>-0.5877068203387638</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>JUBLFOOD</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2179</v>
+        <v>462.4</v>
       </c>
       <c r="C6" t="n">
-        <v>2213</v>
+        <v>467.05</v>
       </c>
       <c r="D6" t="n">
-        <v>2157</v>
+        <v>453</v>
       </c>
       <c r="E6" t="n">
-        <v>2184.4</v>
+        <v>459.6</v>
       </c>
       <c r="F6" t="n">
-        <v>423505</v>
+        <v>1906381</v>
       </c>
       <c r="G6" t="n">
-        <v>886101</v>
+        <v>4042856</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5220578692496679</v>
+        <v>-0.5284568631680179</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>JUBLFOOD</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PRESTIGE</t>
+          <t>FORTIS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1269.9</v>
+        <v>859</v>
       </c>
       <c r="C7" t="n">
-        <v>1283.8</v>
+        <v>863.6</v>
       </c>
       <c r="D7" t="n">
-        <v>1237.4</v>
+        <v>837.95</v>
       </c>
       <c r="E7" t="n">
-        <v>1264</v>
+        <v>840</v>
       </c>
       <c r="F7" t="n">
-        <v>483947</v>
+        <v>1002669</v>
       </c>
       <c r="G7" t="n">
-        <v>961586</v>
+        <v>2366155</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.496720002163093</v>
+        <v>-0.5762454277086666</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PRESTIGE</t>
+          <t>FORTIS</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SONACOMS</t>
+          <t>IGL</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>508</v>
+        <v>161.9</v>
       </c>
       <c r="C8" t="n">
-        <v>515.05</v>
+        <v>165.29</v>
       </c>
       <c r="D8" t="n">
-        <v>502.7</v>
+        <v>156.05</v>
       </c>
       <c r="E8" t="n">
-        <v>510.85</v>
+        <v>156.8</v>
       </c>
       <c r="F8" t="n">
-        <v>748268</v>
+        <v>3077409</v>
       </c>
       <c r="G8" t="n">
-        <v>1840641</v>
+        <v>6354075</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5934742299014311</v>
+        <v>-0.5156794655398307</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>SONACOMS</t>
+          <t>IGL</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>DALBHARAT</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1895</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1908.8</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1829.8</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1890</v>
+      </c>
+      <c r="F9" t="n">
+        <v>159482</v>
+      </c>
+      <c r="G9" t="n">
+        <v>358226</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.5548006007380816</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>DALBHARAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CESC</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>160.12</v>
+      </c>
+      <c r="C10" t="n">
+        <v>165.6</v>
+      </c>
+      <c r="D10" t="n">
+        <v>158.74</v>
+      </c>
+      <c r="E10" t="n">
+        <v>159.75</v>
+      </c>
+      <c r="F10" t="n">
+        <v>7292740</v>
+      </c>
+      <c r="G10" t="n">
+        <v>16610060</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.5609443915313972</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>CESC</t>
         </is>
       </c>
     </row>
@@ -718,7 +784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -771,528 +837,495 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1243.2</v>
+        <v>308.65</v>
       </c>
       <c r="C2" t="n">
-        <v>1251.1</v>
+        <v>309.5</v>
       </c>
       <c r="D2" t="n">
-        <v>1231.8</v>
+        <v>298.7</v>
       </c>
       <c r="E2" t="n">
-        <v>1234.9</v>
+        <v>301</v>
       </c>
       <c r="F2" t="n">
-        <v>9663320</v>
+        <v>23615092</v>
       </c>
       <c r="G2" t="n">
-        <v>6289277</v>
+        <v>15284297</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5364754963090352</v>
+        <v>0.5450558177454939</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>POWERGRID</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13430</v>
+        <v>714.5</v>
       </c>
       <c r="C3" t="n">
-        <v>13430</v>
+        <v>715.5</v>
       </c>
       <c r="D3" t="n">
-        <v>12966</v>
+        <v>684.45</v>
       </c>
       <c r="E3" t="n">
-        <v>12995</v>
+        <v>687.9</v>
       </c>
       <c r="F3" t="n">
-        <v>544683</v>
+        <v>15416801</v>
       </c>
       <c r="G3" t="n">
-        <v>353715</v>
+        <v>10180516</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5398922861625886</v>
+        <v>0.5143437719659789</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>VEDL</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7590</v>
+        <v>740.55</v>
       </c>
       <c r="C4" t="n">
-        <v>7662.5</v>
+        <v>749</v>
       </c>
       <c r="D4" t="n">
-        <v>7542.5</v>
+        <v>706.45</v>
       </c>
       <c r="E4" t="n">
-        <v>7576</v>
+        <v>708.2</v>
       </c>
       <c r="F4" t="n">
-        <v>550020</v>
+        <v>5430860</v>
       </c>
       <c r="G4" t="n">
-        <v>381453</v>
+        <v>3548443</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4419076531053629</v>
+        <v>0.5304909787193989</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>CGPOWER</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>201.06</v>
+        <v>578</v>
       </c>
       <c r="C5" t="n">
-        <v>203.8</v>
+        <v>581.15</v>
       </c>
       <c r="D5" t="n">
-        <v>199.7</v>
+        <v>545.55</v>
       </c>
       <c r="E5" t="n">
-        <v>201.96</v>
+        <v>551.35</v>
       </c>
       <c r="F5" t="n">
-        <v>19042475</v>
+        <v>6884706</v>
       </c>
       <c r="G5" t="n">
-        <v>12982340</v>
+        <v>4378868</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4667983583853142</v>
+        <v>0.5722570308125297</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>HINDZINC</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1350</v>
+        <v>557.25</v>
       </c>
       <c r="C6" t="n">
-        <v>1363.4</v>
+        <v>558.9</v>
       </c>
       <c r="D6" t="n">
-        <v>1341</v>
+        <v>540.45</v>
       </c>
       <c r="E6" t="n">
-        <v>1357</v>
+        <v>541.75</v>
       </c>
       <c r="F6" t="n">
-        <v>2616965</v>
+        <v>5007908</v>
       </c>
       <c r="G6" t="n">
-        <v>1671877</v>
+        <v>3176429</v>
       </c>
       <c r="H6" t="n">
-        <v>0.565285604144324</v>
+        <v>0.5765842712051804</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>DLF</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1925</v>
+        <v>408.65</v>
       </c>
       <c r="C7" t="n">
-        <v>1948.1</v>
+        <v>411.7</v>
       </c>
       <c r="D7" t="n">
-        <v>1907</v>
+        <v>381.25</v>
       </c>
       <c r="E7" t="n">
-        <v>1940.9</v>
+        <v>386.45</v>
       </c>
       <c r="F7" t="n">
-        <v>868643</v>
+        <v>28466667</v>
       </c>
       <c r="G7" t="n">
-        <v>587710</v>
+        <v>20128518</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4780129655782614</v>
+        <v>0.4142455495233181</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BOSCHLTD</t>
+          <t>PAYTM</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31620</v>
+        <v>1005</v>
       </c>
       <c r="C8" t="n">
-        <v>31620</v>
+        <v>1005.5</v>
       </c>
       <c r="D8" t="n">
-        <v>30815</v>
+        <v>966.7</v>
       </c>
       <c r="E8" t="n">
-        <v>31300</v>
+        <v>977</v>
       </c>
       <c r="F8" t="n">
-        <v>27041</v>
+        <v>3060838</v>
       </c>
       <c r="G8" t="n">
-        <v>17509</v>
+        <v>2037889</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5444057341938432</v>
+        <v>0.5019650236102162</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BOSCHLTD</t>
+          <t>PAYTM</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>403.5</v>
+        <v>75.2</v>
       </c>
       <c r="C9" t="n">
-        <v>410.2</v>
+        <v>76.48</v>
       </c>
       <c r="D9" t="n">
-        <v>385.95</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>408.5</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>20128518</v>
+        <v>26761513</v>
       </c>
       <c r="G9" t="n">
-        <v>13040542</v>
+        <v>16804967</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5435338500500976</v>
+        <v>0.592476379156234</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>NHPC</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SUZLON</t>
+          <t>BLUESTARCO</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>41.51</v>
+        <v>1938</v>
       </c>
       <c r="C10" t="n">
-        <v>43.54</v>
+        <v>1939.9</v>
       </c>
       <c r="D10" t="n">
-        <v>40.93</v>
+        <v>1820</v>
       </c>
       <c r="E10" t="n">
-        <v>42.53</v>
+        <v>1833.2</v>
       </c>
       <c r="F10" t="n">
-        <v>108432510</v>
+        <v>979856</v>
       </c>
       <c r="G10" t="n">
-        <v>70866917</v>
+        <v>638482</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5300864576908292</v>
+        <v>0.5346650336266332</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SUZLON</t>
+          <t>BLUESTARCO</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>BANKINDIA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>73</v>
+        <v>154.06</v>
       </c>
       <c r="C11" t="n">
-        <v>76.36</v>
+        <v>154.65</v>
       </c>
       <c r="D11" t="n">
-        <v>72.76000000000001</v>
+        <v>149.7</v>
       </c>
       <c r="E11" t="n">
-        <v>74.86</v>
+        <v>150.3</v>
       </c>
       <c r="F11" t="n">
-        <v>16804967</v>
+        <v>9551217</v>
       </c>
       <c r="G11" t="n">
-        <v>11915288</v>
+        <v>6364616</v>
       </c>
       <c r="H11" t="n">
-        <v>0.410370189960998</v>
+        <v>0.5006745104496485</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>BANKINDIA</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>KALYANKJIL</t>
+          <t>UPL</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>388.5</v>
+        <v>628</v>
       </c>
       <c r="C12" t="n">
-        <v>393.65</v>
+        <v>628.1</v>
       </c>
       <c r="D12" t="n">
-        <v>378.6</v>
+        <v>603</v>
       </c>
       <c r="E12" t="n">
-        <v>389.5</v>
+        <v>609.3</v>
       </c>
       <c r="F12" t="n">
-        <v>3218077</v>
+        <v>1954960</v>
       </c>
       <c r="G12" t="n">
-        <v>2143619</v>
+        <v>1299556</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5012355273954934</v>
+        <v>0.5043291708860564</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>KALYANKJIL</t>
+          <t>UPL</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BLUESTARCO</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1941</v>
+        <v>1460</v>
       </c>
       <c r="C13" t="n">
-        <v>1969.5</v>
+        <v>1470.4</v>
       </c>
       <c r="D13" t="n">
-        <v>1892</v>
+        <v>1440.6</v>
       </c>
       <c r="E13" t="n">
-        <v>1942</v>
+        <v>1457.5</v>
       </c>
       <c r="F13" t="n">
-        <v>638482</v>
+        <v>703160</v>
       </c>
       <c r="G13" t="n">
-        <v>440437</v>
+        <v>480014</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4496556828785956</v>
+        <v>0.4648739411767157</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>BLUESTARCO</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IREDA</t>
+          <t>ICICIPRULI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>114</v>
+        <v>586</v>
       </c>
       <c r="C14" t="n">
-        <v>118.95</v>
+        <v>591.4</v>
       </c>
       <c r="D14" t="n">
-        <v>112.59</v>
+        <v>580.1</v>
       </c>
       <c r="E14" t="n">
-        <v>117</v>
+        <v>584.65</v>
       </c>
       <c r="F14" t="n">
-        <v>9357674</v>
+        <v>1483478</v>
       </c>
       <c r="G14" t="n">
-        <v>6188063</v>
+        <v>949805</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5122137573583204</v>
+        <v>0.5618763851527419</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>IREDA</t>
+          <t>ICICIPRULI</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SBICARD</t>
+          <t>SONACOMS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>712</v>
+        <v>509.35</v>
       </c>
       <c r="C15" t="n">
-        <v>715</v>
+        <v>511.5</v>
       </c>
       <c r="D15" t="n">
-        <v>698</v>
+        <v>484</v>
       </c>
       <c r="E15" t="n">
-        <v>710.2</v>
+        <v>485</v>
       </c>
       <c r="F15" t="n">
-        <v>831279</v>
+        <v>1136203</v>
       </c>
       <c r="G15" t="n">
-        <v>519996</v>
+        <v>748268</v>
       </c>
       <c r="H15" t="n">
-        <v>0.598625758659682</v>
+        <v>0.5184439265076149</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SBICARD</t>
+          <t>SONACOMS</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PIIND</t>
+          <t>NCC</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2981.1</v>
+        <v>148.7</v>
       </c>
       <c r="C16" t="n">
-        <v>2997.2</v>
+        <v>149.19</v>
       </c>
       <c r="D16" t="n">
-        <v>2940.1</v>
+        <v>142.9</v>
       </c>
       <c r="E16" t="n">
-        <v>2940.1</v>
+        <v>144.2</v>
       </c>
       <c r="F16" t="n">
-        <v>196476</v>
+        <v>3769727</v>
       </c>
       <c r="G16" t="n">
-        <v>140106</v>
+        <v>2375070</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4023382296261402</v>
+        <v>0.5872066928553685</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>PIIND</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>KAYNES</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>3694.6</v>
-      </c>
-      <c r="C17" t="n">
-        <v>3786</v>
-      </c>
-      <c r="D17" t="n">
-        <v>3586</v>
-      </c>
-      <c r="E17" t="n">
-        <v>3695</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1473221</v>
-      </c>
-      <c r="G17" t="n">
-        <v>930709</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.5829018522438271</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>KAYNES</t>
+          <t>NCC</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,297 +479,198 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>861</v>
+        <v>5808.5</v>
       </c>
       <c r="C2" t="n">
-        <v>868.35</v>
+        <v>5872.5</v>
       </c>
       <c r="D2" t="n">
-        <v>848.8</v>
+        <v>5764.5</v>
       </c>
       <c r="E2" t="n">
-        <v>856.5</v>
+        <v>5817</v>
       </c>
       <c r="F2" t="n">
-        <v>6668639</v>
+        <v>350827</v>
       </c>
       <c r="G2" t="n">
-        <v>15508258</v>
+        <v>738522</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5699943217349105</v>
+        <v>-0.5249606646789128</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SRF</t>
+          <t>DMART</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2609.9</v>
+        <v>3824.3</v>
       </c>
       <c r="C3" t="n">
-        <v>2623.5</v>
+        <v>3834.8</v>
       </c>
       <c r="D3" t="n">
-        <v>2491.3</v>
+        <v>3736.1</v>
       </c>
       <c r="E3" t="n">
-        <v>2500.4</v>
+        <v>3815</v>
       </c>
       <c r="F3" t="n">
-        <v>649413</v>
+        <v>401345</v>
       </c>
       <c r="G3" t="n">
-        <v>1288113</v>
+        <v>913594</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4958415915373884</v>
+        <v>-0.5606965457303792</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SRF</t>
+          <t>DMART</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>INDUSTOWER</t>
+          <t>NYKAA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>439.15</v>
+        <v>236.65</v>
       </c>
       <c r="C4" t="n">
-        <v>440.8</v>
+        <v>241.9</v>
       </c>
       <c r="D4" t="n">
-        <v>422.7</v>
+        <v>233.2</v>
       </c>
       <c r="E4" t="n">
-        <v>424.5</v>
+        <v>236</v>
       </c>
       <c r="F4" t="n">
-        <v>2702224</v>
+        <v>3626853</v>
       </c>
       <c r="G4" t="n">
-        <v>5403935</v>
+        <v>7248289</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4999525345882214</v>
+        <v>-0.4996263256059464</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>INDUSTOWER</t>
+          <t>NYKAA</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>MANKIND</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2006.8</v>
+        <v>2126.3</v>
       </c>
       <c r="C5" t="n">
-        <v>2013.5</v>
+        <v>2141.6</v>
       </c>
       <c r="D5" t="n">
-        <v>1908.5</v>
+        <v>2081</v>
       </c>
       <c r="E5" t="n">
-        <v>1933.3</v>
+        <v>2083.5</v>
       </c>
       <c r="F5" t="n">
-        <v>560842</v>
+        <v>332072</v>
       </c>
       <c r="G5" t="n">
-        <v>1360299</v>
+        <v>801859</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5877068203387638</v>
+        <v>-0.5858723291750794</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>MANKIND</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>JUBLFOOD</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>462.4</v>
+        <v>504.15</v>
       </c>
       <c r="C6" t="n">
-        <v>467.05</v>
+        <v>510.95</v>
       </c>
       <c r="D6" t="n">
-        <v>453</v>
+        <v>486</v>
       </c>
       <c r="E6" t="n">
-        <v>459.6</v>
+        <v>508</v>
       </c>
       <c r="F6" t="n">
-        <v>1906381</v>
+        <v>4784689</v>
       </c>
       <c r="G6" t="n">
-        <v>4042856</v>
+        <v>10933102</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5284568631680179</v>
+        <v>-0.562366746418354</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>JUBLFOOD</t>
+          <t>PGEL</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FORTIS</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>859</v>
+        <v>763</v>
       </c>
       <c r="C7" t="n">
-        <v>863.6</v>
+        <v>777.55</v>
       </c>
       <c r="D7" t="n">
-        <v>837.95</v>
+        <v>749.5</v>
       </c>
       <c r="E7" t="n">
-        <v>840</v>
+        <v>768.55</v>
       </c>
       <c r="F7" t="n">
-        <v>1002669</v>
+        <v>534970</v>
       </c>
       <c r="G7" t="n">
-        <v>2366155</v>
+        <v>1112562</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5762454277086666</v>
+        <v>-0.51915488754784</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>FORTIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>IGL</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>161.9</v>
-      </c>
-      <c r="C8" t="n">
-        <v>165.29</v>
-      </c>
-      <c r="D8" t="n">
-        <v>156.05</v>
-      </c>
-      <c r="E8" t="n">
-        <v>156.8</v>
-      </c>
-      <c r="F8" t="n">
-        <v>3077409</v>
-      </c>
-      <c r="G8" t="n">
-        <v>6354075</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-0.5156794655398307</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>IGL</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>DALBHARAT</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1895</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1908.8</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1829.8</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1890</v>
-      </c>
-      <c r="F9" t="n">
-        <v>159482</v>
-      </c>
-      <c r="G9" t="n">
-        <v>358226</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-0.5548006007380816</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>DALBHARAT</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CESC</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>160.12</v>
-      </c>
-      <c r="C10" t="n">
-        <v>165.6</v>
-      </c>
-      <c r="D10" t="n">
-        <v>158.74</v>
-      </c>
-      <c r="E10" t="n">
-        <v>159.75</v>
-      </c>
-      <c r="F10" t="n">
-        <v>7292740</v>
-      </c>
-      <c r="G10" t="n">
-        <v>16610060</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-0.5609443915313972</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>CESC</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
     </row>
@@ -784,7 +685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -837,495 +738,726 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>308.65</v>
+        <v>1798</v>
       </c>
       <c r="C2" t="n">
-        <v>309.5</v>
+        <v>1804.9</v>
       </c>
       <c r="D2" t="n">
-        <v>298.7</v>
+        <v>1770.9</v>
       </c>
       <c r="E2" t="n">
-        <v>301</v>
+        <v>1790</v>
       </c>
       <c r="F2" t="n">
-        <v>23615092</v>
+        <v>14261268</v>
       </c>
       <c r="G2" t="n">
-        <v>15284297</v>
+        <v>8970772</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5450558177454939</v>
+        <v>0.5897481287006291</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>714.5</v>
+        <v>12532</v>
       </c>
       <c r="C3" t="n">
-        <v>715.5</v>
+        <v>12874</v>
       </c>
       <c r="D3" t="n">
-        <v>684.45</v>
+        <v>12400</v>
       </c>
       <c r="E3" t="n">
-        <v>687.9</v>
+        <v>12740</v>
       </c>
       <c r="F3" t="n">
-        <v>15416801</v>
+        <v>1416170</v>
       </c>
       <c r="G3" t="n">
-        <v>10180516</v>
+        <v>939594</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5143437719659789</v>
+        <v>0.5072148183151446</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>MARUTI</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>740.55</v>
+        <v>302.55</v>
       </c>
       <c r="C4" t="n">
-        <v>749</v>
+        <v>309.45</v>
       </c>
       <c r="D4" t="n">
-        <v>706.45</v>
+        <v>302</v>
       </c>
       <c r="E4" t="n">
-        <v>708.2</v>
+        <v>307.45</v>
       </c>
       <c r="F4" t="n">
-        <v>5430860</v>
+        <v>37472204</v>
       </c>
       <c r="G4" t="n">
-        <v>3548443</v>
+        <v>25659996</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5304909787193989</v>
+        <v>0.4603355355160617</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>ITC</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>578</v>
+        <v>990</v>
       </c>
       <c r="C5" t="n">
-        <v>581.15</v>
+        <v>1002.9</v>
       </c>
       <c r="D5" t="n">
-        <v>545.55</v>
+        <v>969.3</v>
       </c>
       <c r="E5" t="n">
-        <v>551.35</v>
+        <v>990</v>
       </c>
       <c r="F5" t="n">
-        <v>6884706</v>
+        <v>10476354</v>
       </c>
       <c r="G5" t="n">
-        <v>4378868</v>
+        <v>6562852</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5722570308125297</v>
+        <v>0.5963111769090633</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>557.25</v>
+        <v>2410</v>
       </c>
       <c r="C6" t="n">
-        <v>558.9</v>
+        <v>2425</v>
       </c>
       <c r="D6" t="n">
-        <v>540.45</v>
+        <v>2366.1</v>
       </c>
       <c r="E6" t="n">
-        <v>541.75</v>
+        <v>2401</v>
       </c>
       <c r="F6" t="n">
-        <v>5007908</v>
+        <v>3807907</v>
       </c>
       <c r="G6" t="n">
-        <v>3176429</v>
+        <v>2466488</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5765842712051804</v>
+        <v>0.5438579064645763</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>TCS</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>408.65</v>
+        <v>1738</v>
       </c>
       <c r="C7" t="n">
-        <v>411.7</v>
+        <v>1784</v>
       </c>
       <c r="D7" t="n">
-        <v>381.25</v>
+        <v>1729</v>
       </c>
       <c r="E7" t="n">
-        <v>386.45</v>
+        <v>1762.2</v>
       </c>
       <c r="F7" t="n">
-        <v>28466667</v>
+        <v>2085547</v>
       </c>
       <c r="G7" t="n">
-        <v>20128518</v>
+        <v>1390698</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4142455495233181</v>
+        <v>0.499640468311596</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PAYTM</t>
+          <t>AMBUJACEM</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1005</v>
+        <v>425.55</v>
       </c>
       <c r="C8" t="n">
-        <v>1005.5</v>
+        <v>434.95</v>
       </c>
       <c r="D8" t="n">
-        <v>966.7</v>
+        <v>424.75</v>
       </c>
       <c r="E8" t="n">
-        <v>977</v>
+        <v>428</v>
       </c>
       <c r="F8" t="n">
-        <v>3060838</v>
+        <v>6857558</v>
       </c>
       <c r="G8" t="n">
-        <v>2037889</v>
+        <v>4856344</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5019650236102162</v>
+        <v>0.4120824224972531</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>PAYTM</t>
+          <t>AMBUJACEM</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>BANKBARODA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>75.2</v>
+        <v>280</v>
       </c>
       <c r="C9" t="n">
-        <v>76.48</v>
+        <v>282.5</v>
       </c>
       <c r="D9" t="n">
-        <v>74.34999999999999</v>
+        <v>272.5</v>
       </c>
       <c r="E9" t="n">
-        <v>75.09999999999999</v>
+        <v>279.05</v>
       </c>
       <c r="F9" t="n">
-        <v>26761513</v>
+        <v>9554841</v>
       </c>
       <c r="G9" t="n">
-        <v>16804967</v>
+        <v>6237801</v>
       </c>
       <c r="H9" t="n">
-        <v>0.592476379156234</v>
+        <v>0.5317643188681396</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>BANKBARODA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BLUESTARCO</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1938</v>
+        <v>6010</v>
       </c>
       <c r="C10" t="n">
-        <v>1939.9</v>
+        <v>6130</v>
       </c>
       <c r="D10" t="n">
-        <v>1820</v>
+        <v>5927</v>
       </c>
       <c r="E10" t="n">
-        <v>1833.2</v>
+        <v>6066.5</v>
       </c>
       <c r="F10" t="n">
-        <v>979856</v>
+        <v>282845</v>
       </c>
       <c r="G10" t="n">
-        <v>638482</v>
+        <v>200936</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5346650336266332</v>
+        <v>0.4076372576342716</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>BLUESTARCO</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BANKINDIA</t>
+          <t>IRFC</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>154.06</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="C11" t="n">
-        <v>154.65</v>
+        <v>97.13</v>
       </c>
       <c r="D11" t="n">
-        <v>149.7</v>
+        <v>94.31999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>150.3</v>
+        <v>96.29000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>9551217</v>
+        <v>16521257</v>
       </c>
       <c r="G11" t="n">
-        <v>6364616</v>
+        <v>11414655</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5006745104496485</v>
+        <v>0.447372434821727</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>BANKINDIA</t>
+          <t>IRFC</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UPL</t>
+          <t>SRF</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>628</v>
+        <v>2484.9</v>
       </c>
       <c r="C12" t="n">
-        <v>628.1</v>
+        <v>2523.4</v>
       </c>
       <c r="D12" t="n">
-        <v>603</v>
+        <v>2425.9</v>
       </c>
       <c r="E12" t="n">
-        <v>609.3</v>
+        <v>2445.7</v>
       </c>
       <c r="F12" t="n">
-        <v>1954960</v>
+        <v>973496</v>
       </c>
       <c r="G12" t="n">
-        <v>1299556</v>
+        <v>649413</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5043291708860564</v>
+        <v>0.4990399021885918</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>UPL</t>
+          <t>SRF</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>RVNL</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1460</v>
+        <v>271.25</v>
       </c>
       <c r="C13" t="n">
-        <v>1470.4</v>
+        <v>271.9</v>
       </c>
       <c r="D13" t="n">
-        <v>1440.6</v>
+        <v>260.7</v>
       </c>
       <c r="E13" t="n">
-        <v>1457.5</v>
+        <v>266.8</v>
       </c>
       <c r="F13" t="n">
-        <v>703160</v>
+        <v>6663574</v>
       </c>
       <c r="G13" t="n">
-        <v>480014</v>
+        <v>4564446</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4648739411767157</v>
+        <v>0.4598866981885644</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>RVNL</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ICICIPRULI</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>586</v>
+        <v>1464.1</v>
       </c>
       <c r="C14" t="n">
-        <v>591.4</v>
+        <v>1464.1</v>
       </c>
       <c r="D14" t="n">
-        <v>580.1</v>
+        <v>1395.5</v>
       </c>
       <c r="E14" t="n">
-        <v>584.65</v>
+        <v>1415</v>
       </c>
       <c r="F14" t="n">
-        <v>1483478</v>
+        <v>1082381</v>
       </c>
       <c r="G14" t="n">
-        <v>949805</v>
+        <v>703160</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5618763851527419</v>
+        <v>0.5393096876955458</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ICICIPRULI</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SONACOMS</t>
+          <t>GMRAIRPORT</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>509.35</v>
+        <v>90</v>
       </c>
       <c r="C15" t="n">
-        <v>511.5</v>
+        <v>92.05</v>
       </c>
       <c r="D15" t="n">
-        <v>484</v>
+        <v>88.77</v>
       </c>
       <c r="E15" t="n">
-        <v>485</v>
+        <v>90.18000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>1136203</v>
+        <v>15405960</v>
       </c>
       <c r="G15" t="n">
-        <v>748268</v>
+        <v>10707023</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5184439265076149</v>
+        <v>0.4388649393953856</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SONACOMS</t>
+          <t>GMRAIRPORT</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NCC</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>148.7</v>
+        <v>1565.5</v>
       </c>
       <c r="C16" t="n">
-        <v>149.19</v>
+        <v>1566</v>
       </c>
       <c r="D16" t="n">
-        <v>142.9</v>
+        <v>1507</v>
       </c>
       <c r="E16" t="n">
-        <v>144.2</v>
+        <v>1533.5</v>
       </c>
       <c r="F16" t="n">
-        <v>3769727</v>
+        <v>788989</v>
       </c>
       <c r="G16" t="n">
-        <v>2375070</v>
+        <v>551464</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5872066928553685</v>
+        <v>0.4307171456341665</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>NCC</t>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>DABUR</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>455</v>
+      </c>
+      <c r="C17" t="n">
+        <v>461.45</v>
+      </c>
+      <c r="D17" t="n">
+        <v>449.2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>457</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2534686</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1711951</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.4805832643574495</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>DABUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>453.6</v>
+      </c>
+      <c r="C18" t="n">
+        <v>457.5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>443.5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>452.9</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2268253</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1590961</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.4257125096089722</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>DALBHARAT</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1856</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1868</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1803.6</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1850.7</v>
+      </c>
+      <c r="F19" t="n">
+        <v>237882</v>
+      </c>
+      <c r="G19" t="n">
+        <v>159482</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.4915915275705095</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>DALBHARAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>IRB</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>41.84</v>
+      </c>
+      <c r="C20" t="n">
+        <v>41.87</v>
+      </c>
+      <c r="D20" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="E20" t="n">
+        <v>41.33</v>
+      </c>
+      <c r="F20" t="n">
+        <v>9469080</v>
+      </c>
+      <c r="G20" t="n">
+        <v>6476141</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.462148523325851</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>IRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2474</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2577</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2440.8</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2557.9</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3474374</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2434350</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.4272286236572391</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>MANAPPURAM</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>253.85</v>
+      </c>
+      <c r="C22" t="n">
+        <v>257.05</v>
+      </c>
+      <c r="D22" t="n">
+        <v>246.95</v>
+      </c>
+      <c r="E22" t="n">
+        <v>250.75</v>
+      </c>
+      <c r="F22" t="n">
+        <v>5145342</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3401711</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.5125747013782181</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>MANAPPURAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>GRANULES</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>560.5</v>
+      </c>
+      <c r="C23" t="n">
+        <v>572.7</v>
+      </c>
+      <c r="D23" t="n">
+        <v>555.75</v>
+      </c>
+      <c r="E23" t="n">
+        <v>565</v>
+      </c>
+      <c r="F23" t="n">
+        <v>661428</v>
+      </c>
+      <c r="G23" t="n">
+        <v>432376</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.529751882620682</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>GRANULES</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,198 +479,594 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5808.5</v>
+        <v>1797</v>
       </c>
       <c r="C2" t="n">
-        <v>5872.5</v>
+        <v>1834.5</v>
       </c>
       <c r="D2" t="n">
-        <v>5764.5</v>
+        <v>1791.1</v>
       </c>
       <c r="E2" t="n">
-        <v>5817</v>
+        <v>1823.4</v>
       </c>
       <c r="F2" t="n">
-        <v>350827</v>
+        <v>7181491</v>
       </c>
       <c r="G2" t="n">
-        <v>738522</v>
+        <v>14261268</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5249606646789128</v>
+        <v>-0.4964339075599729</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3824.3</v>
+        <v>928.9</v>
       </c>
       <c r="C3" t="n">
-        <v>3834.8</v>
+        <v>942</v>
       </c>
       <c r="D3" t="n">
-        <v>3736.1</v>
+        <v>916.35</v>
       </c>
       <c r="E3" t="n">
-        <v>3815</v>
+        <v>935</v>
       </c>
       <c r="F3" t="n">
-        <v>401345</v>
+        <v>4862641</v>
       </c>
       <c r="G3" t="n">
-        <v>913594</v>
+        <v>10755610</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5606965457303792</v>
+        <v>-0.5478972368838215</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>HINDALCO</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NYKAA</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>236.65</v>
+        <v>11090</v>
       </c>
       <c r="C4" t="n">
-        <v>241.9</v>
+        <v>11160</v>
       </c>
       <c r="D4" t="n">
-        <v>233.2</v>
+        <v>10991</v>
       </c>
       <c r="E4" t="n">
-        <v>236</v>
+        <v>11119</v>
       </c>
       <c r="F4" t="n">
-        <v>3626853</v>
+        <v>332933</v>
       </c>
       <c r="G4" t="n">
-        <v>7248289</v>
+        <v>728077</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4996263256059464</v>
+        <v>-0.5427228164054076</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>NYKAA</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2126.3</v>
+        <v>302</v>
       </c>
       <c r="C5" t="n">
-        <v>2141.6</v>
+        <v>302</v>
       </c>
       <c r="D5" t="n">
-        <v>2081</v>
+        <v>292.15</v>
       </c>
       <c r="E5" t="n">
-        <v>2083.5</v>
+        <v>297.1</v>
       </c>
       <c r="F5" t="n">
-        <v>332072</v>
+        <v>12300000</v>
       </c>
       <c r="G5" t="n">
-        <v>801859</v>
+        <v>25911819</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5858723291750794</v>
+        <v>-0.5253131399227511</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>POWERGRID</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>504.15</v>
+        <v>9100</v>
       </c>
       <c r="C6" t="n">
-        <v>510.95</v>
+        <v>9250</v>
       </c>
       <c r="D6" t="n">
-        <v>486</v>
+        <v>9006.5</v>
       </c>
       <c r="E6" t="n">
-        <v>508</v>
+        <v>9111</v>
       </c>
       <c r="F6" t="n">
-        <v>4784689</v>
+        <v>245258</v>
       </c>
       <c r="G6" t="n">
-        <v>10933102</v>
+        <v>580318</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.562366746418354</v>
+        <v>-0.5773730954407755</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PNBHOUSING</t>
+          <t>ATGL</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>763</v>
+        <v>525.7</v>
       </c>
       <c r="C7" t="n">
-        <v>777.55</v>
+        <v>533.7</v>
       </c>
       <c r="D7" t="n">
-        <v>749.5</v>
+        <v>490</v>
       </c>
       <c r="E7" t="n">
-        <v>768.55</v>
+        <v>515.05</v>
       </c>
       <c r="F7" t="n">
-        <v>534970</v>
+        <v>8611067</v>
       </c>
       <c r="G7" t="n">
-        <v>1112562</v>
+        <v>18277892</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.51915488754784</v>
+        <v>-0.5288807374504675</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PNBHOUSING</t>
+          <t>ATGL</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MUTHOOTFIN</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3370.2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3428</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3336.4</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3425</v>
+      </c>
+      <c r="F8" t="n">
+        <v>627317</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1333026</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.5294037775707301</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MUTHOOTFIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>63.84</v>
+      </c>
+      <c r="D9" t="n">
+        <v>62.39</v>
+      </c>
+      <c r="E9" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="F9" t="n">
+        <v>21678024</v>
+      </c>
+      <c r="G9" t="n">
+        <v>43729894</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.5042744901233924</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PRESTIGE</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1255</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1275</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1230.4</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1274.7</v>
+      </c>
+      <c r="F10" t="n">
+        <v>903233</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1786830</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.494505353055411</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>PRESTIGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1284.9</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1295</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1275.1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1289.8</v>
+      </c>
+      <c r="F11" t="n">
+        <v>635152</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1436685</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.5579044814973358</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>GMRAIRPORT</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="C12" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="D12" t="n">
+        <v>89.66</v>
+      </c>
+      <c r="E12" t="n">
+        <v>90.29000000000001</v>
+      </c>
+      <c r="F12" t="n">
+        <v>6931780</v>
+      </c>
+      <c r="G12" t="n">
+        <v>15405960</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.5500585487694373</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>GMRAIRPORT</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ICICIPRULI</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>583</v>
+      </c>
+      <c r="C13" t="n">
+        <v>601.1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>581.3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>592.7</v>
+      </c>
+      <c r="F13" t="n">
+        <v>633223</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1391776</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.5450252052054354</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ICICIPRULI</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SYNGENE</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>409.5</v>
+      </c>
+      <c r="C14" t="n">
+        <v>415.3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>407.8</v>
+      </c>
+      <c r="E14" t="n">
+        <v>411</v>
+      </c>
+      <c r="F14" t="n">
+        <v>818059</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1806446</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.5471445036275648</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>SYNGENE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PAGEIND</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>30200</v>
+      </c>
+      <c r="C15" t="n">
+        <v>30675</v>
+      </c>
+      <c r="D15" t="n">
+        <v>30200</v>
+      </c>
+      <c r="E15" t="n">
+        <v>30525</v>
+      </c>
+      <c r="F15" t="n">
+        <v>8132</v>
+      </c>
+      <c r="G15" t="n">
+        <v>17643</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.5390806552173667</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>PAGEIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>DALBHARAT</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1871.3</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1871.3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1844.5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1870</v>
+      </c>
+      <c r="F16" t="n">
+        <v>99261</v>
+      </c>
+      <c r="G16" t="n">
+        <v>237882</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.5827300930713547</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>DALBHARAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="C17" t="n">
+        <v>72.18000000000001</v>
+      </c>
+      <c r="D17" t="n">
+        <v>70.34999999999999</v>
+      </c>
+      <c r="E17" t="n">
+        <v>71.45</v>
+      </c>
+      <c r="F17" t="n">
+        <v>10071338</v>
+      </c>
+      <c r="G17" t="n">
+        <v>20368200</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.5055361789456113</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TITAGARH</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>628</v>
+      </c>
+      <c r="C18" t="n">
+        <v>635.65</v>
+      </c>
+      <c r="D18" t="n">
+        <v>622.2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>630.6</v>
+      </c>
+      <c r="F18" t="n">
+        <v>494782</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1118626</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.5576877347746253</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>TITAGARH</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CESC</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>156.55</v>
+      </c>
+      <c r="C19" t="n">
+        <v>158.25</v>
+      </c>
+      <c r="D19" t="n">
+        <v>155.25</v>
+      </c>
+      <c r="E19" t="n">
+        <v>155.75</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1205564</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2560226</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.5291181325398617</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>CESC</t>
         </is>
       </c>
     </row>
@@ -685,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -738,726 +1134,363 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1798</v>
+        <v>1213.4</v>
       </c>
       <c r="C2" t="n">
-        <v>1804.9</v>
+        <v>1225</v>
       </c>
       <c r="D2" t="n">
-        <v>1770.9</v>
+        <v>1199.1</v>
       </c>
       <c r="E2" t="n">
-        <v>1790</v>
+        <v>1207.1</v>
       </c>
       <c r="F2" t="n">
-        <v>14261268</v>
+        <v>1673011</v>
       </c>
       <c r="G2" t="n">
-        <v>8970772</v>
+        <v>1100151</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5897481287006291</v>
+        <v>0.5207103388534846</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12532</v>
+        <v>3390</v>
       </c>
       <c r="C3" t="n">
-        <v>12874</v>
+        <v>3505</v>
       </c>
       <c r="D3" t="n">
-        <v>12400</v>
+        <v>3352.2</v>
       </c>
       <c r="E3" t="n">
-        <v>12740</v>
+        <v>3484.5</v>
       </c>
       <c r="F3" t="n">
-        <v>1416170</v>
+        <v>1460188</v>
       </c>
       <c r="G3" t="n">
-        <v>939594</v>
+        <v>985489</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5072148183151446</v>
+        <v>0.4816887859732579</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>302.55</v>
+        <v>391</v>
       </c>
       <c r="C4" t="n">
-        <v>309.45</v>
+        <v>402.3</v>
       </c>
       <c r="D4" t="n">
-        <v>302</v>
+        <v>391</v>
       </c>
       <c r="E4" t="n">
-        <v>307.45</v>
+        <v>400.55</v>
       </c>
       <c r="F4" t="n">
-        <v>37472204</v>
+        <v>12085084</v>
       </c>
       <c r="G4" t="n">
-        <v>25659996</v>
+        <v>8028549</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4603355355160617</v>
+        <v>0.5052637780500561</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>UNITDSPR</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>990</v>
+        <v>1325</v>
       </c>
       <c r="C5" t="n">
-        <v>1002.9</v>
+        <v>1332.5</v>
       </c>
       <c r="D5" t="n">
-        <v>969.3</v>
+        <v>1298.7</v>
       </c>
       <c r="E5" t="n">
-        <v>990</v>
+        <v>1305</v>
       </c>
       <c r="F5" t="n">
-        <v>10476354</v>
+        <v>1291896</v>
       </c>
       <c r="G5" t="n">
-        <v>6562852</v>
+        <v>885117</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5963111769090633</v>
+        <v>0.4595765305603666</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>UNITDSPR</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2410</v>
+        <v>2179.9</v>
       </c>
       <c r="C6" t="n">
-        <v>2425</v>
+        <v>2184.7</v>
       </c>
       <c r="D6" t="n">
-        <v>2366.1</v>
+        <v>2136</v>
       </c>
       <c r="E6" t="n">
-        <v>2401</v>
+        <v>2144.1</v>
       </c>
       <c r="F6" t="n">
-        <v>3807907</v>
+        <v>773805</v>
       </c>
       <c r="G6" t="n">
-        <v>2466488</v>
+        <v>528614</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5438579064645763</v>
+        <v>0.4638375071413167</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>GLENMARK</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1738</v>
+        <v>314.6</v>
       </c>
       <c r="C7" t="n">
-        <v>1784</v>
+        <v>324.15</v>
       </c>
       <c r="D7" t="n">
-        <v>1729</v>
+        <v>313.6</v>
       </c>
       <c r="E7" t="n">
-        <v>1762.2</v>
+        <v>319</v>
       </c>
       <c r="F7" t="n">
-        <v>2085547</v>
+        <v>4360168</v>
       </c>
       <c r="G7" t="n">
-        <v>1390698</v>
+        <v>3069058</v>
       </c>
       <c r="H7" t="n">
-        <v>0.499640468311596</v>
+        <v>0.420686086740622</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AMBUJACEM</t>
+          <t>SBICARD</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>425.55</v>
+        <v>702</v>
       </c>
       <c r="C8" t="n">
-        <v>434.95</v>
+        <v>712</v>
       </c>
       <c r="D8" t="n">
-        <v>424.75</v>
+        <v>687.8</v>
       </c>
       <c r="E8" t="n">
-        <v>428</v>
+        <v>700.1</v>
       </c>
       <c r="F8" t="n">
-        <v>6857558</v>
+        <v>1866238</v>
       </c>
       <c r="G8" t="n">
-        <v>4856344</v>
+        <v>1191414</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4120824224972531</v>
+        <v>0.5664059680346211</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AMBUJACEM</t>
+          <t>SBICARD</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>280</v>
+        <v>1018.5</v>
       </c>
       <c r="C9" t="n">
-        <v>282.5</v>
+        <v>1057</v>
       </c>
       <c r="D9" t="n">
-        <v>272.5</v>
+        <v>1007.1</v>
       </c>
       <c r="E9" t="n">
-        <v>279.05</v>
+        <v>1054.5</v>
       </c>
       <c r="F9" t="n">
-        <v>9554841</v>
+        <v>1034552</v>
       </c>
       <c r="G9" t="n">
-        <v>6237801</v>
+        <v>675736</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5317643188681396</v>
+        <v>0.5310002722956895</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>MANAPPURAM</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6010</v>
+        <v>251.45</v>
       </c>
       <c r="C10" t="n">
-        <v>6130</v>
+        <v>260.55</v>
       </c>
       <c r="D10" t="n">
-        <v>5927</v>
+        <v>249.7</v>
       </c>
       <c r="E10" t="n">
-        <v>6066.5</v>
+        <v>257.25</v>
       </c>
       <c r="F10" t="n">
-        <v>282845</v>
+        <v>7837935</v>
       </c>
       <c r="G10" t="n">
-        <v>200936</v>
+        <v>5145342</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4076372576342716</v>
+        <v>0.5233069055468033</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>MANAPPURAM</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IRFC</t>
+          <t>KFINTECH</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>96.90000000000001</v>
+        <v>914.35</v>
       </c>
       <c r="C11" t="n">
-        <v>97.13</v>
+        <v>914.35</v>
       </c>
       <c r="D11" t="n">
-        <v>94.31999999999999</v>
+        <v>892</v>
       </c>
       <c r="E11" t="n">
-        <v>96.29000000000001</v>
+        <v>901.45</v>
       </c>
       <c r="F11" t="n">
-        <v>16521257</v>
+        <v>1035925</v>
       </c>
       <c r="G11" t="n">
-        <v>11414655</v>
+        <v>700236</v>
       </c>
       <c r="H11" t="n">
-        <v>0.447372434821727</v>
+        <v>0.4793940899925168</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>IRFC</t>
+          <t>KFINTECH</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SRF</t>
+          <t>IIFL</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2484.9</v>
+        <v>475</v>
       </c>
       <c r="C12" t="n">
-        <v>2523.4</v>
+        <v>475.9</v>
       </c>
       <c r="D12" t="n">
-        <v>2425.9</v>
+        <v>462.6</v>
       </c>
       <c r="E12" t="n">
-        <v>2445.7</v>
+        <v>474</v>
       </c>
       <c r="F12" t="n">
-        <v>973496</v>
+        <v>1367487</v>
       </c>
       <c r="G12" t="n">
-        <v>649413</v>
+        <v>971832</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4990399021885918</v>
+        <v>0.4071228360457363</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>SRF</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>RVNL</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>271.25</v>
-      </c>
-      <c r="C13" t="n">
-        <v>271.9</v>
-      </c>
-      <c r="D13" t="n">
-        <v>260.7</v>
-      </c>
-      <c r="E13" t="n">
-        <v>266.8</v>
-      </c>
-      <c r="F13" t="n">
-        <v>6663574</v>
-      </c>
-      <c r="G13" t="n">
-        <v>4564446</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.4598866981885644</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>RVNL</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>OBEROIRLTY</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1464.1</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1464.1</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1395.5</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1415</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1082381</v>
-      </c>
-      <c r="G14" t="n">
-        <v>703160</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.5393096876955458</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>OBEROIRLTY</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>GMRAIRPORT</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>90</v>
-      </c>
-      <c r="C15" t="n">
-        <v>92.05</v>
-      </c>
-      <c r="D15" t="n">
-        <v>88.77</v>
-      </c>
-      <c r="E15" t="n">
-        <v>90.18000000000001</v>
-      </c>
-      <c r="F15" t="n">
-        <v>15405960</v>
-      </c>
-      <c r="G15" t="n">
-        <v>10707023</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.4388649393953856</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>GMRAIRPORT</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>PHOENIXLTD</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1565.5</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1566</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1507</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1533.5</v>
-      </c>
-      <c r="F16" t="n">
-        <v>788989</v>
-      </c>
-      <c r="G16" t="n">
-        <v>551464</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.4307171456341665</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>PHOENIXLTD</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>DABUR</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>455</v>
-      </c>
-      <c r="C17" t="n">
-        <v>461.45</v>
-      </c>
-      <c r="D17" t="n">
-        <v>449.2</v>
-      </c>
-      <c r="E17" t="n">
-        <v>457</v>
-      </c>
-      <c r="F17" t="n">
-        <v>2534686</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1711951</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.4805832643574495</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>DABUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>CONCOR</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>453.6</v>
-      </c>
-      <c r="C18" t="n">
-        <v>457.5</v>
-      </c>
-      <c r="D18" t="n">
-        <v>443.5</v>
-      </c>
-      <c r="E18" t="n">
-        <v>452.9</v>
-      </c>
-      <c r="F18" t="n">
-        <v>2268253</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1590961</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.4257125096089722</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>CONCOR</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>DALBHARAT</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1856</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1868</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1803.6</v>
-      </c>
-      <c r="E19" t="n">
-        <v>1850.7</v>
-      </c>
-      <c r="F19" t="n">
-        <v>237882</v>
-      </c>
-      <c r="G19" t="n">
-        <v>159482</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.4915915275705095</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>DALBHARAT</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>IRB</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>41.84</v>
-      </c>
-      <c r="C20" t="n">
-        <v>41.87</v>
-      </c>
-      <c r="D20" t="n">
-        <v>40.4</v>
-      </c>
-      <c r="E20" t="n">
-        <v>41.33</v>
-      </c>
-      <c r="F20" t="n">
-        <v>9469080</v>
-      </c>
-      <c r="G20" t="n">
-        <v>6476141</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.462148523325851</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>IRB</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>2474</v>
-      </c>
-      <c r="C21" t="n">
-        <v>2577</v>
-      </c>
-      <c r="D21" t="n">
-        <v>2440.8</v>
-      </c>
-      <c r="E21" t="n">
-        <v>2557.9</v>
-      </c>
-      <c r="F21" t="n">
-        <v>3474374</v>
-      </c>
-      <c r="G21" t="n">
-        <v>2434350</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.4272286236572391</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>MANAPPURAM</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>253.85</v>
-      </c>
-      <c r="C22" t="n">
-        <v>257.05</v>
-      </c>
-      <c r="D22" t="n">
-        <v>246.95</v>
-      </c>
-      <c r="E22" t="n">
-        <v>250.75</v>
-      </c>
-      <c r="F22" t="n">
-        <v>5145342</v>
-      </c>
-      <c r="G22" t="n">
-        <v>3401711</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.5125747013782181</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>MANAPPURAM</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>GRANULES</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>560.5</v>
-      </c>
-      <c r="C23" t="n">
-        <v>572.7</v>
-      </c>
-      <c r="D23" t="n">
-        <v>555.75</v>
-      </c>
-      <c r="E23" t="n">
-        <v>565</v>
-      </c>
-      <c r="F23" t="n">
-        <v>661428</v>
-      </c>
-      <c r="G23" t="n">
-        <v>432376</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.529751882620682</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>GRANULES</t>
+          <t>IIFL</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,594 +479,66 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1797</v>
+        <v>1397.2</v>
       </c>
       <c r="C2" t="n">
-        <v>1834.5</v>
+        <v>1412.9</v>
       </c>
       <c r="D2" t="n">
-        <v>1791.1</v>
+        <v>1397.2</v>
       </c>
       <c r="E2" t="n">
-        <v>1823.4</v>
+        <v>1407.2</v>
       </c>
       <c r="F2" t="n">
-        <v>7181491</v>
+        <v>9559327</v>
       </c>
       <c r="G2" t="n">
-        <v>14261268</v>
+        <v>19007744</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4964339075599729</v>
+        <v>-0.4970825048990559</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>RELIANCE</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>JUBLFOOD</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>928.9</v>
+        <v>465.95</v>
       </c>
       <c r="C3" t="n">
-        <v>942</v>
+        <v>479.85</v>
       </c>
       <c r="D3" t="n">
-        <v>916.35</v>
+        <v>462.9</v>
       </c>
       <c r="E3" t="n">
-        <v>935</v>
+        <v>475.55</v>
       </c>
       <c r="F3" t="n">
-        <v>4862641</v>
+        <v>823728</v>
       </c>
       <c r="G3" t="n">
-        <v>10755610</v>
+        <v>1940585</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5478972368838215</v>
+        <v>-0.5755259367664906</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ULTRACEMCO</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>11090</v>
-      </c>
-      <c r="C4" t="n">
-        <v>11160</v>
-      </c>
-      <c r="D4" t="n">
-        <v>10991</v>
-      </c>
-      <c r="E4" t="n">
-        <v>11119</v>
-      </c>
-      <c r="F4" t="n">
-        <v>332933</v>
-      </c>
-      <c r="G4" t="n">
-        <v>728077</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-0.5427228164054076</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>ULTRACEMCO</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>POWERGRID</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>302</v>
-      </c>
-      <c r="C5" t="n">
-        <v>302</v>
-      </c>
-      <c r="D5" t="n">
-        <v>292.15</v>
-      </c>
-      <c r="E5" t="n">
-        <v>297.1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>12300000</v>
-      </c>
-      <c r="G5" t="n">
-        <v>25911819</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-0.5253131399227511</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>POWERGRID</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>BAJAJ-AUTO</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>9100</v>
-      </c>
-      <c r="C6" t="n">
-        <v>9250</v>
-      </c>
-      <c r="D6" t="n">
-        <v>9006.5</v>
-      </c>
-      <c r="E6" t="n">
-        <v>9111</v>
-      </c>
-      <c r="F6" t="n">
-        <v>245258</v>
-      </c>
-      <c r="G6" t="n">
-        <v>580318</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-0.5773730954407755</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>BAJAJ-AUTO</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ATGL</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>525.7</v>
-      </c>
-      <c r="C7" t="n">
-        <v>533.7</v>
-      </c>
-      <c r="D7" t="n">
-        <v>490</v>
-      </c>
-      <c r="E7" t="n">
-        <v>515.05</v>
-      </c>
-      <c r="F7" t="n">
-        <v>8611067</v>
-      </c>
-      <c r="G7" t="n">
-        <v>18277892</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-0.5288807374504675</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>ATGL</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>MUTHOOTFIN</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>3370.2</v>
-      </c>
-      <c r="C8" t="n">
-        <v>3428</v>
-      </c>
-      <c r="D8" t="n">
-        <v>3336.4</v>
-      </c>
-      <c r="E8" t="n">
-        <v>3425</v>
-      </c>
-      <c r="F8" t="n">
-        <v>627317</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1333026</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-0.5294037775707301</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>MUTHOOTFIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>IDFCFIRSTB</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>63.1</v>
-      </c>
-      <c r="C9" t="n">
-        <v>63.84</v>
-      </c>
-      <c r="D9" t="n">
-        <v>62.39</v>
-      </c>
-      <c r="E9" t="n">
-        <v>63.7</v>
-      </c>
-      <c r="F9" t="n">
-        <v>21678024</v>
-      </c>
-      <c r="G9" t="n">
-        <v>43729894</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-0.5042744901233924</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>IDFCFIRSTB</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>PRESTIGE</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1255</v>
-      </c>
-      <c r="C10" t="n">
-        <v>1275</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1230.4</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1274.7</v>
-      </c>
-      <c r="F10" t="n">
-        <v>903233</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1786830</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-0.494505353055411</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>PRESTIGE</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>AUROPHARMA</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1284.9</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1295</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1275.1</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1289.8</v>
-      </c>
-      <c r="F11" t="n">
-        <v>635152</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1436685</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-0.5579044814973358</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>AUROPHARMA</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>GMRAIRPORT</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>90.90000000000001</v>
-      </c>
-      <c r="C12" t="n">
-        <v>91.09999999999999</v>
-      </c>
-      <c r="D12" t="n">
-        <v>89.66</v>
-      </c>
-      <c r="E12" t="n">
-        <v>90.29000000000001</v>
-      </c>
-      <c r="F12" t="n">
-        <v>6931780</v>
-      </c>
-      <c r="G12" t="n">
-        <v>15405960</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-0.5500585487694373</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>GMRAIRPORT</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>ICICIPRULI</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>583</v>
-      </c>
-      <c r="C13" t="n">
-        <v>601.1</v>
-      </c>
-      <c r="D13" t="n">
-        <v>581.3</v>
-      </c>
-      <c r="E13" t="n">
-        <v>592.7</v>
-      </c>
-      <c r="F13" t="n">
-        <v>633223</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1391776</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-0.5450252052054354</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>ICICIPRULI</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>SYNGENE</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>409.5</v>
-      </c>
-      <c r="C14" t="n">
-        <v>415.3</v>
-      </c>
-      <c r="D14" t="n">
-        <v>407.8</v>
-      </c>
-      <c r="E14" t="n">
-        <v>411</v>
-      </c>
-      <c r="F14" t="n">
-        <v>818059</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1806446</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-0.5471445036275648</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>SYNGENE</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>PAGEIND</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>30200</v>
-      </c>
-      <c r="C15" t="n">
-        <v>30675</v>
-      </c>
-      <c r="D15" t="n">
-        <v>30200</v>
-      </c>
-      <c r="E15" t="n">
-        <v>30525</v>
-      </c>
-      <c r="F15" t="n">
-        <v>8132</v>
-      </c>
-      <c r="G15" t="n">
-        <v>17643</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-0.5390806552173667</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>PAGEIND</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>DALBHARAT</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1871.3</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1871.3</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1844.5</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1870</v>
-      </c>
-      <c r="F16" t="n">
-        <v>99261</v>
-      </c>
-      <c r="G16" t="n">
-        <v>237882</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-0.5827300930713547</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>DALBHARAT</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>HFCL</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>71.5</v>
-      </c>
-      <c r="C17" t="n">
-        <v>72.18000000000001</v>
-      </c>
-      <c r="D17" t="n">
-        <v>70.34999999999999</v>
-      </c>
-      <c r="E17" t="n">
-        <v>71.45</v>
-      </c>
-      <c r="F17" t="n">
-        <v>10071338</v>
-      </c>
-      <c r="G17" t="n">
-        <v>20368200</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-0.5055361789456113</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>HFCL</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>TITAGARH</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>628</v>
-      </c>
-      <c r="C18" t="n">
-        <v>635.65</v>
-      </c>
-      <c r="D18" t="n">
-        <v>622.2</v>
-      </c>
-      <c r="E18" t="n">
-        <v>630.6</v>
-      </c>
-      <c r="F18" t="n">
-        <v>494782</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1118626</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-0.5576877347746253</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>TITAGARH</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>CESC</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>156.55</v>
-      </c>
-      <c r="C19" t="n">
-        <v>158.25</v>
-      </c>
-      <c r="D19" t="n">
-        <v>155.25</v>
-      </c>
-      <c r="E19" t="n">
-        <v>155.75</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1205564</v>
-      </c>
-      <c r="G19" t="n">
-        <v>2560226</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-0.5291181325398617</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>CESC</t>
+          <t>JUBLFOOD</t>
         </is>
       </c>
     </row>
@@ -1081,7 +553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1134,363 +606,594 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1213.4</v>
+        <v>876.1</v>
       </c>
       <c r="C2" t="n">
-        <v>1225</v>
+        <v>893.95</v>
       </c>
       <c r="D2" t="n">
-        <v>1199.1</v>
+        <v>858.2</v>
       </c>
       <c r="E2" t="n">
-        <v>1207.1</v>
+        <v>882.95</v>
       </c>
       <c r="F2" t="n">
-        <v>1673011</v>
+        <v>12375517</v>
       </c>
       <c r="G2" t="n">
-        <v>1100151</v>
+        <v>7941385</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5207103388534846</v>
+        <v>0.5583575157230131</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3390</v>
+        <v>2165</v>
       </c>
       <c r="C3" t="n">
-        <v>3505</v>
+        <v>2175</v>
       </c>
       <c r="D3" t="n">
-        <v>3352.2</v>
+        <v>2129.7</v>
       </c>
       <c r="E3" t="n">
-        <v>3484.5</v>
+        <v>2134.5</v>
       </c>
       <c r="F3" t="n">
-        <v>1460188</v>
+        <v>2441148</v>
       </c>
       <c r="G3" t="n">
-        <v>985489</v>
+        <v>1705956</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4816887859732579</v>
+        <v>0.430956015278237</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>391</v>
+        <v>7511.5</v>
       </c>
       <c r="C4" t="n">
-        <v>402.3</v>
+        <v>7605</v>
       </c>
       <c r="D4" t="n">
-        <v>391</v>
+        <v>7455.5</v>
       </c>
       <c r="E4" t="n">
-        <v>400.55</v>
+        <v>7460</v>
       </c>
       <c r="F4" t="n">
-        <v>12085084</v>
+        <v>497712</v>
       </c>
       <c r="G4" t="n">
-        <v>8028549</v>
+        <v>343558</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5052637780500561</v>
+        <v>0.4486986185738653</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>GRASIM</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1325</v>
+        <v>2699</v>
       </c>
       <c r="C5" t="n">
-        <v>1332.5</v>
+        <v>2732.9</v>
       </c>
       <c r="D5" t="n">
-        <v>1298.7</v>
+        <v>2686.7</v>
       </c>
       <c r="E5" t="n">
-        <v>1305</v>
+        <v>2716</v>
       </c>
       <c r="F5" t="n">
-        <v>1291896</v>
+        <v>933801</v>
       </c>
       <c r="G5" t="n">
-        <v>885117</v>
+        <v>603520</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4595765305603666</v>
+        <v>0.5472577545068928</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>GRASIM</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2179.9</v>
+        <v>2367.4</v>
       </c>
       <c r="C6" t="n">
-        <v>2184.7</v>
+        <v>2465</v>
       </c>
       <c r="D6" t="n">
-        <v>2136</v>
+        <v>2363</v>
       </c>
       <c r="E6" t="n">
-        <v>2144.1</v>
+        <v>2459.5</v>
       </c>
       <c r="F6" t="n">
-        <v>773805</v>
+        <v>2070389</v>
       </c>
       <c r="G6" t="n">
-        <v>528614</v>
+        <v>1335155</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4638375071413167</v>
+        <v>0.550673142818624</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>VBL</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>314.6</v>
+        <v>410</v>
       </c>
       <c r="C7" t="n">
-        <v>324.15</v>
+        <v>418</v>
       </c>
       <c r="D7" t="n">
-        <v>313.6</v>
+        <v>408.3</v>
       </c>
       <c r="E7" t="n">
-        <v>319</v>
+        <v>415.5</v>
       </c>
       <c r="F7" t="n">
-        <v>4360168</v>
+        <v>6377212</v>
       </c>
       <c r="G7" t="n">
-        <v>3069058</v>
+        <v>4489728</v>
       </c>
       <c r="H7" t="n">
-        <v>0.420686086740622</v>
+        <v>0.420400523149732</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>VBL</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SBICARD</t>
+          <t>ICICIGI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>702</v>
+        <v>1837.5</v>
       </c>
       <c r="C8" t="n">
-        <v>712</v>
+        <v>1847.3</v>
       </c>
       <c r="D8" t="n">
-        <v>687.8</v>
+        <v>1796.3</v>
       </c>
       <c r="E8" t="n">
-        <v>700.1</v>
+        <v>1830</v>
       </c>
       <c r="F8" t="n">
-        <v>1866238</v>
+        <v>954930</v>
       </c>
       <c r="G8" t="n">
-        <v>1191414</v>
+        <v>623480</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5664059680346211</v>
+        <v>0.5316128825303137</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>SBICARD</t>
+          <t>ICICIGI</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>AMBUJACEM</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1018.5</v>
+        <v>438</v>
       </c>
       <c r="C9" t="n">
-        <v>1057</v>
+        <v>444.3</v>
       </c>
       <c r="D9" t="n">
-        <v>1007.1</v>
+        <v>433.45</v>
       </c>
       <c r="E9" t="n">
-        <v>1054.5</v>
+        <v>441</v>
       </c>
       <c r="F9" t="n">
-        <v>1034552</v>
+        <v>3070154</v>
       </c>
       <c r="G9" t="n">
-        <v>675736</v>
+        <v>2154056</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5310002722956895</v>
+        <v>0.4252897789101119</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>AMBUJACEM</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MANAPPURAM</t>
+          <t>DMART</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>251.45</v>
+        <v>3800</v>
       </c>
       <c r="C10" t="n">
-        <v>260.55</v>
+        <v>3905.3</v>
       </c>
       <c r="D10" t="n">
-        <v>249.7</v>
+        <v>3790.3</v>
       </c>
       <c r="E10" t="n">
-        <v>257.25</v>
+        <v>3849</v>
       </c>
       <c r="F10" t="n">
-        <v>7837935</v>
+        <v>340765</v>
       </c>
       <c r="G10" t="n">
-        <v>5145342</v>
+        <v>229556</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5233069055468033</v>
+        <v>0.4844525954451201</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MANAPPURAM</t>
+          <t>DMART</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>KFINTECH</t>
+          <t>KPITTECH</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>914.35</v>
+        <v>658</v>
       </c>
       <c r="C11" t="n">
-        <v>914.35</v>
+        <v>698.85</v>
       </c>
       <c r="D11" t="n">
-        <v>892</v>
+        <v>654.1</v>
       </c>
       <c r="E11" t="n">
-        <v>901.45</v>
+        <v>687.9</v>
       </c>
       <c r="F11" t="n">
-        <v>1035925</v>
+        <v>4250732</v>
       </c>
       <c r="G11" t="n">
-        <v>700236</v>
+        <v>2692241</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4793940899925168</v>
+        <v>0.5788824254589392</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>KFINTECH</t>
+          <t>KPITTECH</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IIFL</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>475</v>
+        <v>1057.7</v>
       </c>
       <c r="C12" t="n">
-        <v>475.9</v>
+        <v>1086</v>
       </c>
       <c r="D12" t="n">
-        <v>462.6</v>
+        <v>1048.6</v>
       </c>
       <c r="E12" t="n">
-        <v>474</v>
+        <v>1073</v>
       </c>
       <c r="F12" t="n">
-        <v>1367487</v>
+        <v>1549593</v>
       </c>
       <c r="G12" t="n">
-        <v>971832</v>
+        <v>1034552</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4071228360457363</v>
+        <v>0.4978396445997881</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>IIFL</t>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MFSL</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1655</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1684.8</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1655</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1672</v>
+      </c>
+      <c r="F13" t="n">
+        <v>722792</v>
+      </c>
+      <c r="G13" t="n">
+        <v>459172</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.5741203731934874</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MFSL</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SUPREMEIND</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>3900</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4029</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3900</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3986</v>
+      </c>
+      <c r="F14" t="n">
+        <v>282357</v>
+      </c>
+      <c r="G14" t="n">
+        <v>182453</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.5475601935841011</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>SUPREMEIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2680</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2702.7</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2575.1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2609.8</v>
+      </c>
+      <c r="F15" t="n">
+        <v>5748986</v>
+      </c>
+      <c r="G15" t="n">
+        <v>4027322</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.4274959886495294</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PNBHOUSING</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>784.05</v>
+      </c>
+      <c r="C16" t="n">
+        <v>813.45</v>
+      </c>
+      <c r="D16" t="n">
+        <v>783.2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>803.5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1029247</v>
+      </c>
+      <c r="G16" t="n">
+        <v>716898</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.4356951756037818</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>PNBHOUSING</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TITAGARH</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>635</v>
+      </c>
+      <c r="C17" t="n">
+        <v>653.95</v>
+      </c>
+      <c r="D17" t="n">
+        <v>632.4</v>
+      </c>
+      <c r="E17" t="n">
+        <v>650</v>
+      </c>
+      <c r="F17" t="n">
+        <v>709654</v>
+      </c>
+      <c r="G17" t="n">
+        <v>494782</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.4342761054363336</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>TITAGARH</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ABFRL</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>58.55</v>
+      </c>
+      <c r="C18" t="n">
+        <v>60.75</v>
+      </c>
+      <c r="D18" t="n">
+        <v>58.55</v>
+      </c>
+      <c r="E18" t="n">
+        <v>59.28</v>
+      </c>
+      <c r="F18" t="n">
+        <v>6279922</v>
+      </c>
+      <c r="G18" t="n">
+        <v>4108524</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.5285104821098769</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ABFRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CESC</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>157</v>
+      </c>
+      <c r="C19" t="n">
+        <v>158.6</v>
+      </c>
+      <c r="D19" t="n">
+        <v>155.6</v>
+      </c>
+      <c r="E19" t="n">
+        <v>156.1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1732665</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1205564</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.4372235733648318</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>CESC</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,66 +479,561 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1397.2</v>
+        <v>1364.1</v>
       </c>
       <c r="C2" t="n">
-        <v>1412.9</v>
+        <v>1379.3</v>
       </c>
       <c r="D2" t="n">
-        <v>1397.2</v>
+        <v>1331.1</v>
       </c>
       <c r="E2" t="n">
-        <v>1407.2</v>
+        <v>1350</v>
       </c>
       <c r="F2" t="n">
-        <v>9559327</v>
+        <v>1219405</v>
       </c>
       <c r="G2" t="n">
-        <v>19007744</v>
+        <v>2969039</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4970825048990559</v>
+        <v>-0.5892930338739235</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>TECHM</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>JUBLFOOD</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>465.95</v>
+        <v>1253.9</v>
       </c>
       <c r="C3" t="n">
-        <v>479.85</v>
+        <v>1263.5</v>
       </c>
       <c r="D3" t="n">
-        <v>462.9</v>
+        <v>1235.4</v>
       </c>
       <c r="E3" t="n">
-        <v>475.55</v>
+        <v>1245</v>
       </c>
       <c r="F3" t="n">
-        <v>823728</v>
+        <v>1080395</v>
       </c>
       <c r="G3" t="n">
-        <v>1940585</v>
+        <v>2226496</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5755259367664906</v>
+        <v>-0.5147554722757194</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>JUBLFOOD</t>
+          <t>CIPLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>423</v>
+      </c>
+      <c r="C4" t="n">
+        <v>426.65</v>
+      </c>
+      <c r="D4" t="n">
+        <v>409.1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>413.9</v>
+      </c>
+      <c r="F4" t="n">
+        <v>6730692</v>
+      </c>
+      <c r="G4" t="n">
+        <v>15012423</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.5516585164167037</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>PFC</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>UNITDSPR</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1311.1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1317.6</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1281.1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1295.9</v>
+      </c>
+      <c r="F5" t="n">
+        <v>806047</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1747262</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.5386799461099709</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>UNITDSPR</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1014.5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1025.9</v>
+      </c>
+      <c r="D6" t="n">
+        <v>999.1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1007</v>
+      </c>
+      <c r="F6" t="n">
+        <v>719181</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1643508</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.5624110135149936</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>HAVELLS</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1323.8</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1335.8</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1290</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1300.9</v>
+      </c>
+      <c r="F7" t="n">
+        <v>506987</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1048399</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.5164178905168738</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>HAVELLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>629.35</v>
+      </c>
+      <c r="C8" t="n">
+        <v>629.35</v>
+      </c>
+      <c r="D8" t="n">
+        <v>611.55</v>
+      </c>
+      <c r="E8" t="n">
+        <v>615.7</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1029632</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.5709866666666666</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1760.2</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1773</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1701</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1715</v>
+      </c>
+      <c r="F9" t="n">
+        <v>874537</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2118929</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.5872740426885469</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1255</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1269</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1240</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1253</v>
+      </c>
+      <c r="F10" t="n">
+        <v>816613</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1700454</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.5197676620479001</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TATATECH</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>542.5</v>
+      </c>
+      <c r="C11" t="n">
+        <v>542.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>521</v>
+      </c>
+      <c r="E11" t="n">
+        <v>524</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1299226</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3031766</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.5714623094262552</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>TATATECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1053</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1057</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1032.5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1043.8</v>
+      </c>
+      <c r="F12" t="n">
+        <v>655607</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1549593</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.5769166484360733</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>454</v>
+      </c>
+      <c r="C13" t="n">
+        <v>454.95</v>
+      </c>
+      <c r="D13" t="n">
+        <v>438.4</v>
+      </c>
+      <c r="E13" t="n">
+        <v>442.5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1517788</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3362845</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.5486595427383659</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>535</v>
+      </c>
+      <c r="C14" t="n">
+        <v>535</v>
+      </c>
+      <c r="D14" t="n">
+        <v>524.2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>527.7</v>
+      </c>
+      <c r="F14" t="n">
+        <v>978842</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2207154</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.5565139541690339</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>239</v>
+      </c>
+      <c r="C15" t="n">
+        <v>240.75</v>
+      </c>
+      <c r="D15" t="n">
+        <v>235.7</v>
+      </c>
+      <c r="E15" t="n">
+        <v>238.75</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2092196</v>
+      </c>
+      <c r="G15" t="n">
+        <v>4888577</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.5720235152274373</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PIIND</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2893.6</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2913.5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2865.3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2899</v>
+      </c>
+      <c r="F16" t="n">
+        <v>95404</v>
+      </c>
+      <c r="G16" t="n">
+        <v>200637</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.5244944850650678</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>PIIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>DELHIVERY</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>418.8</v>
+      </c>
+      <c r="C17" t="n">
+        <v>418.8</v>
+      </c>
+      <c r="D17" t="n">
+        <v>410.65</v>
+      </c>
+      <c r="E17" t="n">
+        <v>414.05</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1890729</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3826912</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.5059387307573312</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>DELHIVERY</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ABFRL</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="C18" t="n">
+        <v>58.79</v>
+      </c>
+      <c r="D18" t="n">
+        <v>56.52</v>
+      </c>
+      <c r="E18" t="n">
+        <v>57</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2707556</v>
+      </c>
+      <c r="G18" t="n">
+        <v>6279922</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.5688551545703912</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ABFRL</t>
         </is>
       </c>
     </row>
@@ -553,7 +1048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -606,594 +1101,231 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>876.1</v>
+        <v>1984</v>
       </c>
       <c r="C2" t="n">
-        <v>893.95</v>
+        <v>1988.6</v>
       </c>
       <c r="D2" t="n">
-        <v>858.2</v>
+        <v>1930</v>
       </c>
       <c r="E2" t="n">
-        <v>882.95</v>
+        <v>1938.4</v>
       </c>
       <c r="F2" t="n">
-        <v>12375517</v>
+        <v>1510588</v>
       </c>
       <c r="G2" t="n">
-        <v>7941385</v>
+        <v>1041095</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5583575157230131</v>
+        <v>0.4509607672690772</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>ADANIENT</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2165</v>
+        <v>919.8</v>
       </c>
       <c r="C3" t="n">
-        <v>2175</v>
+        <v>919.8</v>
       </c>
       <c r="D3" t="n">
-        <v>2129.7</v>
+        <v>896.2</v>
       </c>
       <c r="E3" t="n">
-        <v>2134.5</v>
+        <v>905.55</v>
       </c>
       <c r="F3" t="n">
-        <v>2441148</v>
+        <v>2442610</v>
       </c>
       <c r="G3" t="n">
-        <v>1705956</v>
+        <v>1605839</v>
       </c>
       <c r="H3" t="n">
-        <v>0.430956015278237</v>
+        <v>0.5210802577344305</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>AUBANK</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>NMDC</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7511.5</v>
+        <v>78.2</v>
       </c>
       <c r="C4" t="n">
-        <v>7605</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>7455.5</v>
+        <v>77.5</v>
       </c>
       <c r="E4" t="n">
-        <v>7460</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>497712</v>
+        <v>22414516</v>
       </c>
       <c r="G4" t="n">
-        <v>343558</v>
+        <v>15877573</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4486986185738653</v>
+        <v>0.411709207698179</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>NMDC</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2699</v>
+        <v>1635.1</v>
       </c>
       <c r="C5" t="n">
-        <v>2732.9</v>
+        <v>1650</v>
       </c>
       <c r="D5" t="n">
-        <v>2686.7</v>
+        <v>1623.3</v>
       </c>
       <c r="E5" t="n">
-        <v>2716</v>
+        <v>1628.5</v>
       </c>
       <c r="F5" t="n">
-        <v>933801</v>
+        <v>1070360</v>
       </c>
       <c r="G5" t="n">
-        <v>603520</v>
+        <v>722792</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5472577545068928</v>
+        <v>0.4808686316395311</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>MFSL</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>BDL</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2367.4</v>
+        <v>1300</v>
       </c>
       <c r="C6" t="n">
-        <v>2465</v>
+        <v>1305</v>
       </c>
       <c r="D6" t="n">
-        <v>2363</v>
+        <v>1252</v>
       </c>
       <c r="E6" t="n">
-        <v>2459.5</v>
+        <v>1260.7</v>
       </c>
       <c r="F6" t="n">
-        <v>2070389</v>
+        <v>1287316</v>
       </c>
       <c r="G6" t="n">
-        <v>1335155</v>
+        <v>871241</v>
       </c>
       <c r="H6" t="n">
-        <v>0.550673142818624</v>
+        <v>0.4775659088587429</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>BDL</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VBL</t>
+          <t>BLUESTARCO</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>410</v>
+        <v>1800</v>
       </c>
       <c r="C7" t="n">
-        <v>418</v>
+        <v>1800</v>
       </c>
       <c r="D7" t="n">
-        <v>408.3</v>
+        <v>1727.2</v>
       </c>
       <c r="E7" t="n">
-        <v>415.5</v>
+        <v>1734</v>
       </c>
       <c r="F7" t="n">
-        <v>6377212</v>
+        <v>464044</v>
       </c>
       <c r="G7" t="n">
-        <v>4489728</v>
+        <v>326171</v>
       </c>
       <c r="H7" t="n">
-        <v>0.420400523149732</v>
+        <v>0.4227015890437838</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>VBL</t>
+          <t>BLUESTARCO</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>COLPAL</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1837.5</v>
+        <v>1930.1</v>
       </c>
       <c r="C8" t="n">
-        <v>1847.3</v>
+        <v>1935.2</v>
       </c>
       <c r="D8" t="n">
-        <v>1796.3</v>
+        <v>1882.6</v>
       </c>
       <c r="E8" t="n">
-        <v>1830</v>
+        <v>1892</v>
       </c>
       <c r="F8" t="n">
-        <v>954930</v>
+        <v>340333</v>
       </c>
       <c r="G8" t="n">
-        <v>623480</v>
+        <v>214981</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5316128825303137</v>
+        <v>0.5830840865006675</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>AMBUJACEM</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>438</v>
-      </c>
-      <c r="C9" t="n">
-        <v>444.3</v>
-      </c>
-      <c r="D9" t="n">
-        <v>433.45</v>
-      </c>
-      <c r="E9" t="n">
-        <v>441</v>
-      </c>
-      <c r="F9" t="n">
-        <v>3070154</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2154056</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.4252897789101119</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>AMBUJACEM</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>DMART</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>3800</v>
-      </c>
-      <c r="C10" t="n">
-        <v>3905.3</v>
-      </c>
-      <c r="D10" t="n">
-        <v>3790.3</v>
-      </c>
-      <c r="E10" t="n">
-        <v>3849</v>
-      </c>
-      <c r="F10" t="n">
-        <v>340765</v>
-      </c>
-      <c r="G10" t="n">
-        <v>229556</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.4844525954451201</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>DMART</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>KPITTECH</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>658</v>
-      </c>
-      <c r="C11" t="n">
-        <v>698.85</v>
-      </c>
-      <c r="D11" t="n">
-        <v>654.1</v>
-      </c>
-      <c r="E11" t="n">
-        <v>687.9</v>
-      </c>
-      <c r="F11" t="n">
-        <v>4250732</v>
-      </c>
-      <c r="G11" t="n">
-        <v>2692241</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.5788824254589392</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>KPITTECH</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>UNOMINDA</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1057.7</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1086</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1048.6</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1073</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1549593</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1034552</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.4978396445997881</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>UNOMINDA</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>MFSL</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1655</v>
-      </c>
-      <c r="C13" t="n">
-        <v>1684.8</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1655</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1672</v>
-      </c>
-      <c r="F13" t="n">
-        <v>722792</v>
-      </c>
-      <c r="G13" t="n">
-        <v>459172</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.5741203731934874</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>MFSL</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>SUPREMEIND</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>3900</v>
-      </c>
-      <c r="C14" t="n">
-        <v>4029</v>
-      </c>
-      <c r="D14" t="n">
-        <v>3900</v>
-      </c>
-      <c r="E14" t="n">
-        <v>3986</v>
-      </c>
-      <c r="F14" t="n">
-        <v>282357</v>
-      </c>
-      <c r="G14" t="n">
-        <v>182453</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.5475601935841011</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>SUPREMEIND</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2680</v>
-      </c>
-      <c r="C15" t="n">
-        <v>2702.7</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2575.1</v>
-      </c>
-      <c r="E15" t="n">
-        <v>2609.8</v>
-      </c>
-      <c r="F15" t="n">
-        <v>5748986</v>
-      </c>
-      <c r="G15" t="n">
-        <v>4027322</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.4274959886495294</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>PNBHOUSING</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>784.05</v>
-      </c>
-      <c r="C16" t="n">
-        <v>813.45</v>
-      </c>
-      <c r="D16" t="n">
-        <v>783.2</v>
-      </c>
-      <c r="E16" t="n">
-        <v>803.5</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1029247</v>
-      </c>
-      <c r="G16" t="n">
-        <v>716898</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.4356951756037818</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>PNBHOUSING</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>TITAGARH</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>635</v>
-      </c>
-      <c r="C17" t="n">
-        <v>653.95</v>
-      </c>
-      <c r="D17" t="n">
-        <v>632.4</v>
-      </c>
-      <c r="E17" t="n">
-        <v>650</v>
-      </c>
-      <c r="F17" t="n">
-        <v>709654</v>
-      </c>
-      <c r="G17" t="n">
-        <v>494782</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.4342761054363336</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>TITAGARH</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>ABFRL</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>58.55</v>
-      </c>
-      <c r="C18" t="n">
-        <v>60.75</v>
-      </c>
-      <c r="D18" t="n">
-        <v>58.55</v>
-      </c>
-      <c r="E18" t="n">
-        <v>59.28</v>
-      </c>
-      <c r="F18" t="n">
-        <v>6279922</v>
-      </c>
-      <c r="G18" t="n">
-        <v>4108524</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.5285104821098769</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>ABFRL</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>CESC</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>157</v>
-      </c>
-      <c r="C19" t="n">
-        <v>158.6</v>
-      </c>
-      <c r="D19" t="n">
-        <v>155.6</v>
-      </c>
-      <c r="E19" t="n">
-        <v>156.1</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1732665</v>
-      </c>
-      <c r="G19" t="n">
-        <v>1205564</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.4372235733648318</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>CESC</t>
+          <t>COLPAL</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,561 +479,99 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1364.1</v>
+        <v>488.7</v>
       </c>
       <c r="C2" t="n">
-        <v>1379.3</v>
+        <v>494.65</v>
       </c>
       <c r="D2" t="n">
-        <v>1331.1</v>
+        <v>483.5</v>
       </c>
       <c r="E2" t="n">
-        <v>1350</v>
+        <v>485.5</v>
       </c>
       <c r="F2" t="n">
-        <v>1219405</v>
+        <v>1165789</v>
       </c>
       <c r="G2" t="n">
-        <v>2969039</v>
+        <v>2785790</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5892930338739235</v>
+        <v>-0.5815230150154893</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>DALBHARAT</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1253.9</v>
+        <v>1850</v>
       </c>
       <c r="C3" t="n">
-        <v>1263.5</v>
+        <v>1895</v>
       </c>
       <c r="D3" t="n">
-        <v>1235.4</v>
+        <v>1825.3</v>
       </c>
       <c r="E3" t="n">
-        <v>1245</v>
+        <v>1830</v>
       </c>
       <c r="F3" t="n">
-        <v>1080395</v>
+        <v>124129</v>
       </c>
       <c r="G3" t="n">
-        <v>2226496</v>
+        <v>274365</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5147554722757194</v>
+        <v>-0.5475771326517596</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>DALBHARAT</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>MANAPPURAM</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>423</v>
+        <v>265.35</v>
       </c>
       <c r="C4" t="n">
-        <v>426.65</v>
+        <v>268</v>
       </c>
       <c r="D4" t="n">
-        <v>409.1</v>
+        <v>258.5</v>
       </c>
       <c r="E4" t="n">
-        <v>413.9</v>
+        <v>259.25</v>
       </c>
       <c r="F4" t="n">
-        <v>6730692</v>
+        <v>3301085</v>
       </c>
       <c r="G4" t="n">
-        <v>15012423</v>
+        <v>7163097</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5516585164167037</v>
+        <v>-0.5391539441668876</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>PFC</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>UNITDSPR</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1311.1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1317.6</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1281.1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1295.9</v>
-      </c>
-      <c r="F5" t="n">
-        <v>806047</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1747262</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-0.5386799461099709</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>UNITDSPR</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ADANIENSOL</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1014.5</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1025.9</v>
-      </c>
-      <c r="D6" t="n">
-        <v>999.1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1007</v>
-      </c>
-      <c r="F6" t="n">
-        <v>719181</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1643508</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-0.5624110135149936</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>ADANIENSOL</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>HAVELLS</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1323.8</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1335.8</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1290</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1300.9</v>
-      </c>
-      <c r="F7" t="n">
-        <v>506987</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1048399</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-0.5164178905168738</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>HAVELLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>INDHOTEL</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>629.35</v>
-      </c>
-      <c r="C8" t="n">
-        <v>629.35</v>
-      </c>
-      <c r="D8" t="n">
-        <v>611.55</v>
-      </c>
-      <c r="E8" t="n">
-        <v>615.7</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1029632</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-0.5709866666666666</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>INDHOTEL</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>BHARATFORG</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1760.2</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1773</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1701</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1715</v>
-      </c>
-      <c r="F9" t="n">
-        <v>874537</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2118929</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-0.5872740426885469</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>BHARATFORG</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>AUROPHARMA</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1255</v>
-      </c>
-      <c r="C10" t="n">
-        <v>1269</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1240</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1253</v>
-      </c>
-      <c r="F10" t="n">
-        <v>816613</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1700454</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-0.5197676620479001</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>AUROPHARMA</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>TATATECH</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>542.5</v>
-      </c>
-      <c r="C11" t="n">
-        <v>542.5</v>
-      </c>
-      <c r="D11" t="n">
-        <v>521</v>
-      </c>
-      <c r="E11" t="n">
-        <v>524</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1299226</v>
-      </c>
-      <c r="G11" t="n">
-        <v>3031766</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-0.5714623094262552</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>TATATECH</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>UNOMINDA</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1053</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1057</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1032.5</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1043.8</v>
-      </c>
-      <c r="F12" t="n">
-        <v>655607</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1549593</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-0.5769166484360733</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>UNOMINDA</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>CONCOR</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>454</v>
-      </c>
-      <c r="C13" t="n">
-        <v>454.95</v>
-      </c>
-      <c r="D13" t="n">
-        <v>438.4</v>
-      </c>
-      <c r="E13" t="n">
-        <v>442.5</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1517788</v>
-      </c>
-      <c r="G13" t="n">
-        <v>3362845</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-0.5486595427383659</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>CONCOR</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>IRCTC</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>535</v>
-      </c>
-      <c r="C14" t="n">
-        <v>535</v>
-      </c>
-      <c r="D14" t="n">
-        <v>524.2</v>
-      </c>
-      <c r="E14" t="n">
-        <v>527.7</v>
-      </c>
-      <c r="F14" t="n">
-        <v>978842</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2207154</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-0.5565139541690339</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>IRCTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>NYKAA</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>239</v>
-      </c>
-      <c r="C15" t="n">
-        <v>240.75</v>
-      </c>
-      <c r="D15" t="n">
-        <v>235.7</v>
-      </c>
-      <c r="E15" t="n">
-        <v>238.75</v>
-      </c>
-      <c r="F15" t="n">
-        <v>2092196</v>
-      </c>
-      <c r="G15" t="n">
-        <v>4888577</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-0.5720235152274373</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>NYKAA</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>PIIND</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>2893.6</v>
-      </c>
-      <c r="C16" t="n">
-        <v>2913.5</v>
-      </c>
-      <c r="D16" t="n">
-        <v>2865.3</v>
-      </c>
-      <c r="E16" t="n">
-        <v>2899</v>
-      </c>
-      <c r="F16" t="n">
-        <v>95404</v>
-      </c>
-      <c r="G16" t="n">
-        <v>200637</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-0.5244944850650678</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>PIIND</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>DELHIVERY</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>418.8</v>
-      </c>
-      <c r="C17" t="n">
-        <v>418.8</v>
-      </c>
-      <c r="D17" t="n">
-        <v>410.65</v>
-      </c>
-      <c r="E17" t="n">
-        <v>414.05</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1890729</v>
-      </c>
-      <c r="G17" t="n">
-        <v>3826912</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-0.5059387307573312</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>DELHIVERY</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>ABFRL</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="C18" t="n">
-        <v>58.79</v>
-      </c>
-      <c r="D18" t="n">
-        <v>56.52</v>
-      </c>
-      <c r="E18" t="n">
-        <v>57</v>
-      </c>
-      <c r="F18" t="n">
-        <v>2707556</v>
-      </c>
-      <c r="G18" t="n">
-        <v>6279922</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-0.5688551545703912</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>ABFRL</t>
+          <t>MANAPPURAM</t>
         </is>
       </c>
     </row>
@@ -1048,7 +586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1101,231 +639,693 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1984</v>
+        <v>3059.2</v>
       </c>
       <c r="C2" t="n">
-        <v>1988.6</v>
+        <v>3106.6</v>
       </c>
       <c r="D2" t="n">
-        <v>1930</v>
+        <v>3043.2</v>
       </c>
       <c r="E2" t="n">
-        <v>1938.4</v>
+        <v>3075</v>
       </c>
       <c r="F2" t="n">
-        <v>1510588</v>
+        <v>4471960</v>
       </c>
       <c r="G2" t="n">
-        <v>1041095</v>
+        <v>3059501</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4509607672690772</v>
+        <v>0.4616631927886279</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>M&amp;M</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>919.8</v>
+        <v>2386</v>
       </c>
       <c r="C3" t="n">
-        <v>919.8</v>
+        <v>2407.8</v>
       </c>
       <c r="D3" t="n">
-        <v>896.2</v>
+        <v>2364.2</v>
       </c>
       <c r="E3" t="n">
-        <v>905.55</v>
+        <v>2397.6</v>
       </c>
       <c r="F3" t="n">
-        <v>2442610</v>
+        <v>4206320</v>
       </c>
       <c r="G3" t="n">
-        <v>1605839</v>
+        <v>2757060</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5210802577344305</v>
+        <v>0.5256541388290425</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>TCS</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>78.2</v>
+        <v>432.2</v>
       </c>
       <c r="C4" t="n">
-        <v>78.90000000000001</v>
+        <v>438.95</v>
       </c>
       <c r="D4" t="n">
-        <v>77.5</v>
+        <v>424.7</v>
       </c>
       <c r="E4" t="n">
-        <v>78.09999999999999</v>
+        <v>426.75</v>
       </c>
       <c r="F4" t="n">
-        <v>22414516</v>
+        <v>17599734</v>
       </c>
       <c r="G4" t="n">
-        <v>15877573</v>
+        <v>12237975</v>
       </c>
       <c r="H4" t="n">
-        <v>0.411709207698179</v>
+        <v>0.4381246897464654</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>BEL</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1635.1</v>
+        <v>1755.1</v>
       </c>
       <c r="C5" t="n">
-        <v>1650</v>
+        <v>1781.3</v>
       </c>
       <c r="D5" t="n">
-        <v>1623.3</v>
+        <v>1754.3</v>
       </c>
       <c r="E5" t="n">
-        <v>1628.5</v>
+        <v>1770.6</v>
       </c>
       <c r="F5" t="n">
-        <v>1070360</v>
+        <v>3591446</v>
       </c>
       <c r="G5" t="n">
-        <v>722792</v>
+        <v>2301164</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4808686316395311</v>
+        <v>0.5607084067019995</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BDL</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1300</v>
+        <v>635</v>
       </c>
       <c r="C6" t="n">
-        <v>1305</v>
+        <v>635.5</v>
       </c>
       <c r="D6" t="n">
-        <v>1252</v>
+        <v>622.05</v>
       </c>
       <c r="E6" t="n">
-        <v>1260.7</v>
+        <v>624.6</v>
       </c>
       <c r="F6" t="n">
-        <v>1287316</v>
+        <v>3012022</v>
       </c>
       <c r="G6" t="n">
-        <v>871241</v>
+        <v>1942109</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4775659088587429</v>
+        <v>0.5509026527347333</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>BDL</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BLUESTARCO</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1800</v>
+        <v>335.8</v>
       </c>
       <c r="C7" t="n">
-        <v>1800</v>
+        <v>342</v>
       </c>
       <c r="D7" t="n">
-        <v>1727.2</v>
+        <v>329.25</v>
       </c>
       <c r="E7" t="n">
-        <v>1734</v>
+        <v>330.1</v>
       </c>
       <c r="F7" t="n">
-        <v>464044</v>
+        <v>10305459</v>
       </c>
       <c r="G7" t="n">
-        <v>326171</v>
+        <v>6669467</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4227015890437838</v>
+        <v>0.5451698014249114</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>BLUESTARCO</t>
+          <t>RECLTD</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>COLPAL</t>
+          <t>BANKBARODA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1930.1</v>
+        <v>275.85</v>
       </c>
       <c r="C8" t="n">
-        <v>1935.2</v>
+        <v>283.8</v>
       </c>
       <c r="D8" t="n">
-        <v>1882.6</v>
+        <v>275.25</v>
       </c>
       <c r="E8" t="n">
-        <v>1892</v>
+        <v>279.95</v>
       </c>
       <c r="F8" t="n">
-        <v>340333</v>
+        <v>9423497</v>
       </c>
       <c r="G8" t="n">
-        <v>214981</v>
+        <v>6659439</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5830840865006675</v>
+        <v>0.4150586858742906</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>COLPAL</t>
+          <t>BANKBARODA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>974.5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1003.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>971.1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>988.9</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1956522</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1356584</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.4422416894198958</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HAVELLS</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1301.1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1314.6</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1278</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1282.9</v>
+      </c>
+      <c r="F10" t="n">
+        <v>811006</v>
+      </c>
+      <c r="G10" t="n">
+        <v>506987</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.599658373883354</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>HAVELLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SHREECEM</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>23405</v>
+      </c>
+      <c r="C11" t="n">
+        <v>23710</v>
+      </c>
+      <c r="D11" t="n">
+        <v>23360</v>
+      </c>
+      <c r="E11" t="n">
+        <v>23550</v>
+      </c>
+      <c r="F11" t="n">
+        <v>29852</v>
+      </c>
+      <c r="G11" t="n">
+        <v>20065</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.4877647645153252</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>SHREECEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>BSE</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2920</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2939</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2783.1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2801.7</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5795250</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3871447</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.496920918715922</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>BSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>INDUSINDBK</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>822</v>
+      </c>
+      <c r="C13" t="n">
+        <v>837</v>
+      </c>
+      <c r="D13" t="n">
+        <v>813.1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>819.3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>7872290</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5080824</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.549412063869955</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>INDUSINDBK</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CUMMINSIND</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>4526</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4654.9</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4525</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4629.4</v>
+      </c>
+      <c r="F14" t="n">
+        <v>878443</v>
+      </c>
+      <c r="G14" t="n">
+        <v>580101</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.5142932006667804</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>CUMMINSIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>268.05</v>
+      </c>
+      <c r="C15" t="n">
+        <v>274.3</v>
+      </c>
+      <c r="D15" t="n">
+        <v>266</v>
+      </c>
+      <c r="E15" t="n">
+        <v>267.2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>14660431</v>
+      </c>
+      <c r="G15" t="n">
+        <v>9790533</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.4974088744708792</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>4680.1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>4745.8</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4675</v>
+      </c>
+      <c r="E16" t="n">
+        <v>4739</v>
+      </c>
+      <c r="F16" t="n">
+        <v>654131</v>
+      </c>
+      <c r="G16" t="n">
+        <v>446961</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.4635080018167133</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>MANKIND</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2047.4</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1966.7</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1185624</v>
+      </c>
+      <c r="G17" t="n">
+        <v>836827</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.4168089700738624</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>MANKIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>YESBANK</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>18.53</v>
+      </c>
+      <c r="C18" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="D18" t="n">
+        <v>18.51</v>
+      </c>
+      <c r="E18" t="n">
+        <v>18.56</v>
+      </c>
+      <c r="F18" t="n">
+        <v>102980717</v>
+      </c>
+      <c r="G18" t="n">
+        <v>73345327</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.4040528716982883</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>YESBANK</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SBICARD</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>693.9</v>
+      </c>
+      <c r="C19" t="n">
+        <v>700.6</v>
+      </c>
+      <c r="D19" t="n">
+        <v>683.25</v>
+      </c>
+      <c r="E19" t="n">
+        <v>693</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2019181</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1343483</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.50294495724918</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>SBICARD</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>JSL</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>712.7</v>
+      </c>
+      <c r="C20" t="n">
+        <v>744.95</v>
+      </c>
+      <c r="D20" t="n">
+        <v>712.7</v>
+      </c>
+      <c r="E20" t="n">
+        <v>727</v>
+      </c>
+      <c r="F20" t="n">
+        <v>623699</v>
+      </c>
+      <c r="G20" t="n">
+        <v>423342</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.4732745628829646</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>JSL</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>BANDHANBNK</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>159.31</v>
+      </c>
+      <c r="C21" t="n">
+        <v>161.58</v>
+      </c>
+      <c r="D21" t="n">
+        <v>156.53</v>
+      </c>
+      <c r="E21" t="n">
+        <v>158.5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>14307044</v>
+      </c>
+      <c r="G21" t="n">
+        <v>9761408</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.4656742142117203</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>BANDHANBNK</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PNBHOUSING</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>795</v>
+      </c>
+      <c r="C22" t="n">
+        <v>810.7</v>
+      </c>
+      <c r="D22" t="n">
+        <v>789.05</v>
+      </c>
+      <c r="E22" t="n">
+        <v>790.6</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1237594</v>
+      </c>
+      <c r="G22" t="n">
+        <v>826493</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.4974040917466935</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>PNBHOUSING</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,99 +479,231 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>488.7</v>
+        <v>1238.2</v>
       </c>
       <c r="C2" t="n">
-        <v>494.65</v>
+        <v>1261.1</v>
       </c>
       <c r="D2" t="n">
-        <v>483.5</v>
+        <v>1227.4</v>
       </c>
       <c r="E2" t="n">
-        <v>485.5</v>
+        <v>1253</v>
       </c>
       <c r="F2" t="n">
-        <v>1165789</v>
+        <v>12420293</v>
       </c>
       <c r="G2" t="n">
-        <v>2785790</v>
+        <v>27299975</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5815230150154893</v>
+        <v>-0.5450437958276518</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>INFY</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DALBHARAT</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1850</v>
+        <v>466</v>
       </c>
       <c r="C3" t="n">
-        <v>1895</v>
+        <v>466</v>
       </c>
       <c r="D3" t="n">
-        <v>1825.3</v>
+        <v>450.65</v>
       </c>
       <c r="E3" t="n">
-        <v>1830</v>
+        <v>456.25</v>
       </c>
       <c r="F3" t="n">
-        <v>124129</v>
+        <v>10163783</v>
       </c>
       <c r="G3" t="n">
-        <v>274365</v>
+        <v>23878653</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5475771326517596</v>
+        <v>-0.5743569371354406</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>DALBHARAT</t>
+          <t>COALINDIA</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MANAPPURAM</t>
+          <t>WIPRO</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>265.35</v>
+        <v>189.41</v>
       </c>
       <c r="C4" t="n">
-        <v>268</v>
+        <v>190.62</v>
       </c>
       <c r="D4" t="n">
-        <v>258.5</v>
+        <v>187</v>
       </c>
       <c r="E4" t="n">
-        <v>259.25</v>
+        <v>187.6</v>
       </c>
       <c r="F4" t="n">
-        <v>3301085</v>
+        <v>12014988</v>
       </c>
       <c r="G4" t="n">
-        <v>7163097</v>
+        <v>24395304</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5391539441668876</v>
+        <v>-0.5074876705779112</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MANAPPURAM</t>
+          <t>WIPRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>357.5</v>
+      </c>
+      <c r="C5" t="n">
+        <v>361.2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>347</v>
+      </c>
+      <c r="E5" t="n">
+        <v>349</v>
+      </c>
+      <c r="F5" t="n">
+        <v>14168007</v>
+      </c>
+      <c r="G5" t="n">
+        <v>34262576</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.5864873966277375</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>235</v>
+      </c>
+      <c r="C6" t="n">
+        <v>236.9</v>
+      </c>
+      <c r="D6" t="n">
+        <v>232.9</v>
+      </c>
+      <c r="E6" t="n">
+        <v>233.75</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4174364</v>
+      </c>
+      <c r="G6" t="n">
+        <v>9494678</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.5603469648997048</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>GMRAIRPORT</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>90.15000000000001</v>
+      </c>
+      <c r="C7" t="n">
+        <v>90.15000000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>84.48999999999999</v>
+      </c>
+      <c r="E7" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10647285</v>
+      </c>
+      <c r="G7" t="n">
+        <v>24147369</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.5590705968836605</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>GMRAIRPORT</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1053.1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1053.1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1010</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1031.1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>531522</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1061778</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.49940383017919</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
         </is>
       </c>
     </row>
@@ -586,7 +718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -639,693 +771,627 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3059.2</v>
+        <v>4069.8</v>
       </c>
       <c r="C2" t="n">
-        <v>3106.6</v>
+        <v>4103.9</v>
       </c>
       <c r="D2" t="n">
-        <v>3043.2</v>
+        <v>3895.2</v>
       </c>
       <c r="E2" t="n">
-        <v>3075</v>
+        <v>3950</v>
       </c>
       <c r="F2" t="n">
-        <v>4471960</v>
+        <v>2919605</v>
       </c>
       <c r="G2" t="n">
-        <v>3059501</v>
+        <v>1888215</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4616631927886279</v>
+        <v>0.5462248737564314</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>INDIGO</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2386</v>
+        <v>4056.6</v>
       </c>
       <c r="C3" t="n">
-        <v>2407.8</v>
+        <v>4059</v>
       </c>
       <c r="D3" t="n">
-        <v>2364.2</v>
+        <v>3825</v>
       </c>
       <c r="E3" t="n">
-        <v>2397.6</v>
+        <v>3842.6</v>
       </c>
       <c r="F3" t="n">
-        <v>4206320</v>
+        <v>1533645</v>
       </c>
       <c r="G3" t="n">
-        <v>2757060</v>
+        <v>1019586</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5256541388290425</v>
+        <v>0.5041840511737117</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>TITAN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>JIOFIN</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>432.2</v>
+        <v>236.2</v>
       </c>
       <c r="C4" t="n">
-        <v>438.95</v>
+        <v>236.3</v>
       </c>
       <c r="D4" t="n">
-        <v>424.7</v>
+        <v>225.4</v>
       </c>
       <c r="E4" t="n">
-        <v>426.75</v>
+        <v>225.9</v>
       </c>
       <c r="F4" t="n">
-        <v>17599734</v>
+        <v>21172068</v>
       </c>
       <c r="G4" t="n">
-        <v>12237975</v>
+        <v>15021105</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4381246897464654</v>
+        <v>0.4094880503132093</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>JIOFIN</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1755.1</v>
+        <v>615.1</v>
       </c>
       <c r="C5" t="n">
-        <v>1781.3</v>
+        <v>617</v>
       </c>
       <c r="D5" t="n">
-        <v>1754.3</v>
+        <v>590.1</v>
       </c>
       <c r="E5" t="n">
-        <v>1770.6</v>
+        <v>590.1</v>
       </c>
       <c r="F5" t="n">
-        <v>3591446</v>
+        <v>4223148</v>
       </c>
       <c r="G5" t="n">
-        <v>2301164</v>
+        <v>3012022</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5607084067019995</v>
+        <v>0.4020973286383698</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>635</v>
+        <v>110.6</v>
       </c>
       <c r="C6" t="n">
-        <v>635.5</v>
+        <v>110.7</v>
       </c>
       <c r="D6" t="n">
-        <v>622.05</v>
+        <v>105.2</v>
       </c>
       <c r="E6" t="n">
-        <v>624.6</v>
+        <v>105.35</v>
       </c>
       <c r="F6" t="n">
-        <v>3012022</v>
+        <v>24198613</v>
       </c>
       <c r="G6" t="n">
-        <v>1942109</v>
+        <v>17182097</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5509026527347333</v>
+        <v>0.4083620293844226</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>PNB</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>335.8</v>
+        <v>3110</v>
       </c>
       <c r="C7" t="n">
-        <v>342</v>
+        <v>3110</v>
       </c>
       <c r="D7" t="n">
-        <v>329.25</v>
+        <v>2937</v>
       </c>
       <c r="E7" t="n">
-        <v>330.1</v>
+        <v>3000</v>
       </c>
       <c r="F7" t="n">
-        <v>10305459</v>
+        <v>524215</v>
       </c>
       <c r="G7" t="n">
-        <v>6669467</v>
+        <v>336513</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5451698014249114</v>
+        <v>0.5577852861553639</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>SIEMENS</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>275.85</v>
+        <v>890.45</v>
       </c>
       <c r="C8" t="n">
-        <v>283.8</v>
+        <v>899</v>
       </c>
       <c r="D8" t="n">
-        <v>275.25</v>
+        <v>858</v>
       </c>
       <c r="E8" t="n">
-        <v>279.95</v>
+        <v>860</v>
       </c>
       <c r="F8" t="n">
-        <v>9423497</v>
+        <v>662395</v>
       </c>
       <c r="G8" t="n">
-        <v>6659439</v>
+        <v>424095</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4150586858742906</v>
+        <v>0.5619024039425129</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>MUTHOOTFIN</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>974.5</v>
+        <v>3190</v>
       </c>
       <c r="C9" t="n">
-        <v>1003.5</v>
+        <v>3220.5</v>
       </c>
       <c r="D9" t="n">
-        <v>971.1</v>
+        <v>3042.1</v>
       </c>
       <c r="E9" t="n">
-        <v>988.9</v>
+        <v>3090</v>
       </c>
       <c r="F9" t="n">
-        <v>1956522</v>
+        <v>2186867</v>
       </c>
       <c r="G9" t="n">
-        <v>1356584</v>
+        <v>1556677</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4422416894198958</v>
+        <v>0.4048302891351256</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>MUTHOOTFIN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1301.1</v>
+        <v>7100</v>
       </c>
       <c r="C10" t="n">
-        <v>1314.6</v>
+        <v>7100</v>
       </c>
       <c r="D10" t="n">
-        <v>1278</v>
+        <v>6750</v>
       </c>
       <c r="E10" t="n">
-        <v>1282.9</v>
+        <v>6800</v>
       </c>
       <c r="F10" t="n">
-        <v>811006</v>
+        <v>652615</v>
       </c>
       <c r="G10" t="n">
-        <v>506987</v>
+        <v>450944</v>
       </c>
       <c r="H10" t="n">
-        <v>0.599658373883354</v>
+        <v>0.447219610417258</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>POLYCAB</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23405</v>
+        <v>1700</v>
       </c>
       <c r="C11" t="n">
-        <v>23710</v>
+        <v>1700</v>
       </c>
       <c r="D11" t="n">
-        <v>23360</v>
+        <v>1634</v>
       </c>
       <c r="E11" t="n">
-        <v>23550</v>
+        <v>1659</v>
       </c>
       <c r="F11" t="n">
-        <v>29852</v>
+        <v>1394239</v>
       </c>
       <c r="G11" t="n">
-        <v>20065</v>
+        <v>939720</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4877647645153252</v>
+        <v>0.4836749244455795</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2920</v>
+        <v>307</v>
       </c>
       <c r="C12" t="n">
-        <v>2939</v>
+        <v>307</v>
       </c>
       <c r="D12" t="n">
-        <v>2783.1</v>
+        <v>292.25</v>
       </c>
       <c r="E12" t="n">
-        <v>2801.7</v>
+        <v>294.1</v>
       </c>
       <c r="F12" t="n">
-        <v>5795250</v>
+        <v>6021434</v>
       </c>
       <c r="G12" t="n">
-        <v>3871447</v>
+        <v>3909838</v>
       </c>
       <c r="H12" t="n">
-        <v>0.496920918715922</v>
+        <v>0.5400725042827862</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>RVNL</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>822</v>
+        <v>260.7</v>
       </c>
       <c r="C13" t="n">
-        <v>837</v>
+        <v>260.75</v>
       </c>
       <c r="D13" t="n">
-        <v>813.1</v>
+        <v>249.1</v>
       </c>
       <c r="E13" t="n">
-        <v>819.3</v>
+        <v>249.85</v>
       </c>
       <c r="F13" t="n">
-        <v>7872290</v>
+        <v>6637313</v>
       </c>
       <c r="G13" t="n">
-        <v>5080824</v>
+        <v>4440790</v>
       </c>
       <c r="H13" t="n">
-        <v>0.549412063869955</v>
+        <v>0.4946243798963698</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>RVNL</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>KEI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4526</v>
+        <v>4110</v>
       </c>
       <c r="C14" t="n">
-        <v>4654.9</v>
+        <v>4121.5</v>
       </c>
       <c r="D14" t="n">
-        <v>4525</v>
+        <v>3937</v>
       </c>
       <c r="E14" t="n">
-        <v>4629.4</v>
+        <v>4001</v>
       </c>
       <c r="F14" t="n">
-        <v>878443</v>
+        <v>370258</v>
       </c>
       <c r="G14" t="n">
-        <v>580101</v>
+        <v>241373</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5142932006667804</v>
+        <v>0.5339661022566733</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>KEI</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>268.05</v>
+        <v>520</v>
       </c>
       <c r="C15" t="n">
-        <v>274.3</v>
+        <v>522.8</v>
       </c>
       <c r="D15" t="n">
-        <v>266</v>
+        <v>506.6</v>
       </c>
       <c r="E15" t="n">
-        <v>267.2</v>
+        <v>510</v>
       </c>
       <c r="F15" t="n">
-        <v>14660431</v>
+        <v>2589941</v>
       </c>
       <c r="G15" t="n">
-        <v>9790533</v>
+        <v>1740070</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4974088744708792</v>
+        <v>0.4884119604383731</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>IRCTC</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4680.1</v>
+        <v>442.95</v>
       </c>
       <c r="C16" t="n">
-        <v>4745.8</v>
+        <v>442.95</v>
       </c>
       <c r="D16" t="n">
-        <v>4675</v>
+        <v>421.45</v>
       </c>
       <c r="E16" t="n">
-        <v>4739</v>
+        <v>425.1</v>
       </c>
       <c r="F16" t="n">
-        <v>654131</v>
+        <v>2538797</v>
       </c>
       <c r="G16" t="n">
-        <v>446961</v>
+        <v>1689715</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4635080018167133</v>
+        <v>0.5025001257608531</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>CONCOR</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2030</v>
+        <v>70</v>
       </c>
       <c r="C17" t="n">
-        <v>2047.4</v>
+        <v>70</v>
       </c>
       <c r="D17" t="n">
-        <v>1966.7</v>
+        <v>66.2</v>
       </c>
       <c r="E17" t="n">
-        <v>2000</v>
+        <v>66.2</v>
       </c>
       <c r="F17" t="n">
-        <v>1185624</v>
+        <v>16207486</v>
       </c>
       <c r="G17" t="n">
-        <v>836827</v>
+        <v>11233604</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4168089700738624</v>
+        <v>0.442768144577644</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>HFCL</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>YESBANK</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18.53</v>
+        <v>118.71</v>
       </c>
       <c r="C18" t="n">
-        <v>18.99</v>
+        <v>119.42</v>
       </c>
       <c r="D18" t="n">
-        <v>18.51</v>
+        <v>114.72</v>
       </c>
       <c r="E18" t="n">
-        <v>18.56</v>
+        <v>115.2</v>
       </c>
       <c r="F18" t="n">
-        <v>102980717</v>
+        <v>7773470</v>
       </c>
       <c r="G18" t="n">
-        <v>73345327</v>
+        <v>5086862</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4040528716982883</v>
+        <v>0.5281464289772358</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>YESBANK</t>
+          <t>IEX</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SBICARD</t>
+          <t>TITAGARH</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>693.9</v>
+        <v>624.95</v>
       </c>
       <c r="C19" t="n">
-        <v>700.6</v>
+        <v>624.95</v>
       </c>
       <c r="D19" t="n">
-        <v>683.25</v>
+        <v>590.45</v>
       </c>
       <c r="E19" t="n">
-        <v>693</v>
+        <v>592.25</v>
       </c>
       <c r="F19" t="n">
-        <v>2019181</v>
+        <v>790682</v>
       </c>
       <c r="G19" t="n">
-        <v>1343483</v>
+        <v>527597</v>
       </c>
       <c r="H19" t="n">
-        <v>0.50294495724918</v>
+        <v>0.4986476420449699</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>SBICARD</t>
+          <t>TITAGARH</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>JSL</t>
+          <t>CYIENT</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>712.7</v>
+        <v>820</v>
       </c>
       <c r="C20" t="n">
-        <v>744.95</v>
+        <v>825.35</v>
       </c>
       <c r="D20" t="n">
-        <v>712.7</v>
+        <v>788.25</v>
       </c>
       <c r="E20" t="n">
-        <v>727</v>
+        <v>790.95</v>
       </c>
       <c r="F20" t="n">
-        <v>623699</v>
+        <v>309297</v>
       </c>
       <c r="G20" t="n">
-        <v>423342</v>
+        <v>199549</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4732745628829646</v>
+        <v>0.5499802053630938</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>JSL</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>BANDHANBNK</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>159.31</v>
-      </c>
-      <c r="C21" t="n">
-        <v>161.58</v>
-      </c>
-      <c r="D21" t="n">
-        <v>156.53</v>
-      </c>
-      <c r="E21" t="n">
-        <v>158.5</v>
-      </c>
-      <c r="F21" t="n">
-        <v>14307044</v>
-      </c>
-      <c r="G21" t="n">
-        <v>9761408</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.4656742142117203</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>BANDHANBNK</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>PNBHOUSING</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>795</v>
-      </c>
-      <c r="C22" t="n">
-        <v>810.7</v>
-      </c>
-      <c r="D22" t="n">
-        <v>789.05</v>
-      </c>
-      <c r="E22" t="n">
-        <v>790.6</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1237594</v>
-      </c>
-      <c r="G22" t="n">
-        <v>826493</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.4974040917466935</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>PNBHOUSING</t>
+          <t>CYIENT</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -479,231 +479,231 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1238.2</v>
+        <v>1131.9</v>
       </c>
       <c r="C2" t="n">
-        <v>1261.1</v>
+        <v>1142.7</v>
       </c>
       <c r="D2" t="n">
-        <v>1227.4</v>
+        <v>1112</v>
       </c>
       <c r="E2" t="n">
-        <v>1253</v>
+        <v>1136.5</v>
       </c>
       <c r="F2" t="n">
-        <v>12420293</v>
+        <v>1218013</v>
       </c>
       <c r="G2" t="n">
-        <v>27299975</v>
+        <v>2532216</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5450437958276518</v>
+        <v>-0.518993245441937</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>ICICIGI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>466</v>
+        <v>1750</v>
       </c>
       <c r="C3" t="n">
-        <v>466</v>
+        <v>1758</v>
       </c>
       <c r="D3" t="n">
-        <v>450.65</v>
+        <v>1703.2</v>
       </c>
       <c r="E3" t="n">
-        <v>456.25</v>
+        <v>1730</v>
       </c>
       <c r="F3" t="n">
-        <v>10163783</v>
+        <v>603516</v>
       </c>
       <c r="G3" t="n">
-        <v>23878653</v>
+        <v>1369456</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5743569371354406</v>
+        <v>-0.5593023799231227</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>ICICIGI</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>189.41</v>
+        <v>262.25</v>
       </c>
       <c r="C4" t="n">
-        <v>190.62</v>
+        <v>263.9</v>
       </c>
       <c r="D4" t="n">
-        <v>187</v>
+        <v>257.6</v>
       </c>
       <c r="E4" t="n">
-        <v>187.6</v>
+        <v>263.9</v>
       </c>
       <c r="F4" t="n">
-        <v>12014988</v>
+        <v>6880170</v>
       </c>
       <c r="G4" t="n">
-        <v>24395304</v>
+        <v>13966492</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5074876705779112</v>
+        <v>-0.5073802354950692</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>357.5</v>
+        <v>243.1</v>
       </c>
       <c r="C5" t="n">
-        <v>361.2</v>
+        <v>244.5</v>
       </c>
       <c r="D5" t="n">
-        <v>347</v>
+        <v>236.25</v>
       </c>
       <c r="E5" t="n">
-        <v>349</v>
+        <v>241.6</v>
       </c>
       <c r="F5" t="n">
-        <v>14168007</v>
+        <v>6096343</v>
       </c>
       <c r="G5" t="n">
-        <v>34262576</v>
+        <v>12355833</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5864873966277375</v>
+        <v>-0.5066020235139145</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>PETRONET</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NYKAA</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>235</v>
+        <v>1461</v>
       </c>
       <c r="C6" t="n">
-        <v>236.9</v>
+        <v>1487.5</v>
       </c>
       <c r="D6" t="n">
-        <v>232.9</v>
+        <v>1438.3</v>
       </c>
       <c r="E6" t="n">
-        <v>233.75</v>
+        <v>1465.9</v>
       </c>
       <c r="F6" t="n">
-        <v>4174364</v>
+        <v>927309</v>
       </c>
       <c r="G6" t="n">
-        <v>9494678</v>
+        <v>1887266</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5603469648997048</v>
+        <v>-0.5086495491361578</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>NYKAA</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GMRAIRPORT</t>
+          <t>SONACOMS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>90.15000000000001</v>
+        <v>492.3</v>
       </c>
       <c r="C7" t="n">
-        <v>90.15000000000001</v>
+        <v>498.85</v>
       </c>
       <c r="D7" t="n">
-        <v>84.48999999999999</v>
+        <v>479.65</v>
       </c>
       <c r="E7" t="n">
-        <v>84.59999999999999</v>
+        <v>493.05</v>
       </c>
       <c r="F7" t="n">
-        <v>10647285</v>
+        <v>1604537</v>
       </c>
       <c r="G7" t="n">
-        <v>24147369</v>
+        <v>3152852</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5590705968836605</v>
+        <v>-0.491083945583237</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>GMRAIRPORT</t>
+          <t>SONACOMS</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1053.1</v>
+        <v>151.65</v>
       </c>
       <c r="C8" t="n">
-        <v>1053.1</v>
+        <v>151.89</v>
       </c>
       <c r="D8" t="n">
-        <v>1010</v>
+        <v>145.91</v>
       </c>
       <c r="E8" t="n">
-        <v>1031.1</v>
+        <v>149.64</v>
       </c>
       <c r="F8" t="n">
-        <v>531522</v>
+        <v>8127874</v>
       </c>
       <c r="G8" t="n">
-        <v>1061778</v>
+        <v>16048372</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.49940383017919</v>
+        <v>-0.4935390331181256</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -771,627 +771,528 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4069.8</v>
+        <v>7210</v>
       </c>
       <c r="C2" t="n">
-        <v>4103.9</v>
+        <v>7464</v>
       </c>
       <c r="D2" t="n">
-        <v>3895.2</v>
+        <v>7199</v>
       </c>
       <c r="E2" t="n">
-        <v>3950</v>
+        <v>7433.5</v>
       </c>
       <c r="F2" t="n">
-        <v>2919605</v>
+        <v>653790</v>
       </c>
       <c r="G2" t="n">
-        <v>1888215</v>
+        <v>464969</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5462248737564314</v>
+        <v>0.4060937395826388</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4056.6</v>
+        <v>1267.2</v>
       </c>
       <c r="C3" t="n">
-        <v>4059</v>
+        <v>1279.8</v>
       </c>
       <c r="D3" t="n">
-        <v>3825</v>
+        <v>1248.4</v>
       </c>
       <c r="E3" t="n">
-        <v>3842.6</v>
+        <v>1256.6</v>
       </c>
       <c r="F3" t="n">
-        <v>1533645</v>
+        <v>3166135</v>
       </c>
       <c r="G3" t="n">
-        <v>1019586</v>
+        <v>2112613</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5041840511737117</v>
+        <v>0.498681963994352</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>DRREDDY</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>236.2</v>
+        <v>2184</v>
       </c>
       <c r="C4" t="n">
-        <v>236.3</v>
+        <v>2224.5</v>
       </c>
       <c r="D4" t="n">
-        <v>225.4</v>
+        <v>2153.3</v>
       </c>
       <c r="E4" t="n">
-        <v>225.9</v>
+        <v>2220.5</v>
       </c>
       <c r="F4" t="n">
-        <v>21172068</v>
+        <v>1561016</v>
       </c>
       <c r="G4" t="n">
-        <v>15021105</v>
+        <v>978398</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4094880503132093</v>
+        <v>0.595481593380199</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>615.1</v>
+        <v>141.58</v>
       </c>
       <c r="C5" t="n">
-        <v>617</v>
+        <v>142.5</v>
       </c>
       <c r="D5" t="n">
-        <v>590.1</v>
+        <v>137.02</v>
       </c>
       <c r="E5" t="n">
-        <v>590.1</v>
+        <v>138.8</v>
       </c>
       <c r="F5" t="n">
-        <v>4223148</v>
+        <v>30509694</v>
       </c>
       <c r="G5" t="n">
-        <v>3012022</v>
+        <v>21048472</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4020973286383698</v>
+        <v>0.4494968565889249</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>IOC</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>110.6</v>
+        <v>110.5</v>
       </c>
       <c r="C6" t="n">
-        <v>110.7</v>
+        <v>111.66</v>
       </c>
       <c r="D6" t="n">
-        <v>105.2</v>
+        <v>106.53</v>
       </c>
       <c r="E6" t="n">
-        <v>105.35</v>
+        <v>111.16</v>
       </c>
       <c r="F6" t="n">
-        <v>24198613</v>
+        <v>32098828</v>
       </c>
       <c r="G6" t="n">
-        <v>17182097</v>
+        <v>21402616</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4083620293844226</v>
+        <v>0.4997618982651467</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3110</v>
+        <v>833</v>
       </c>
       <c r="C7" t="n">
-        <v>3110</v>
+        <v>842.15</v>
       </c>
       <c r="D7" t="n">
-        <v>2937</v>
+        <v>801.4</v>
       </c>
       <c r="E7" t="n">
-        <v>3000</v>
+        <v>839</v>
       </c>
       <c r="F7" t="n">
-        <v>524215</v>
+        <v>4139485</v>
       </c>
       <c r="G7" t="n">
-        <v>336513</v>
+        <v>2746629</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5577852861553639</v>
+        <v>0.5071147213547953</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>UNITDSPR</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>890.45</v>
+        <v>1290.9</v>
       </c>
       <c r="C8" t="n">
-        <v>899</v>
+        <v>1334.9</v>
       </c>
       <c r="D8" t="n">
-        <v>858</v>
+        <v>1282.7</v>
       </c>
       <c r="E8" t="n">
-        <v>860</v>
+        <v>1331.5</v>
       </c>
       <c r="F8" t="n">
-        <v>662395</v>
+        <v>1628922</v>
       </c>
       <c r="G8" t="n">
-        <v>424095</v>
+        <v>1141612</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5619024039425129</v>
+        <v>0.4268613154031317</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>UNITDSPR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>DMART</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3190</v>
+        <v>3730</v>
       </c>
       <c r="C9" t="n">
-        <v>3220.5</v>
+        <v>3820.5</v>
       </c>
       <c r="D9" t="n">
-        <v>3042.1</v>
+        <v>3685.1</v>
       </c>
       <c r="E9" t="n">
-        <v>3090</v>
+        <v>3759.8</v>
       </c>
       <c r="F9" t="n">
-        <v>2186867</v>
+        <v>416887</v>
       </c>
       <c r="G9" t="n">
-        <v>1556677</v>
+        <v>296381</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4048302891351256</v>
+        <v>0.4065915156504634</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>DMART</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>UPL</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7100</v>
+        <v>615</v>
       </c>
       <c r="C10" t="n">
-        <v>7100</v>
+        <v>625.6</v>
       </c>
       <c r="D10" t="n">
-        <v>6750</v>
+        <v>608.45</v>
       </c>
       <c r="E10" t="n">
-        <v>6800</v>
+        <v>620.95</v>
       </c>
       <c r="F10" t="n">
-        <v>652615</v>
+        <v>2609729</v>
       </c>
       <c r="G10" t="n">
-        <v>450944</v>
+        <v>1690435</v>
       </c>
       <c r="H10" t="n">
-        <v>0.447219610417258</v>
+        <v>0.5438209691588259</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>UPL</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1700</v>
+        <v>2099.6</v>
       </c>
       <c r="C11" t="n">
-        <v>1700</v>
+        <v>2138.2</v>
       </c>
       <c r="D11" t="n">
-        <v>1634</v>
+        <v>2056.7</v>
       </c>
       <c r="E11" t="n">
-        <v>1659</v>
+        <v>2117</v>
       </c>
       <c r="F11" t="n">
-        <v>1394239</v>
+        <v>747214</v>
       </c>
       <c r="G11" t="n">
-        <v>939720</v>
+        <v>471389</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4836749244455795</v>
+        <v>0.5851324489964763</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>MPHASIS</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>GMRAIRPORT</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>307</v>
+        <v>88</v>
       </c>
       <c r="C12" t="n">
-        <v>307</v>
+        <v>90.34</v>
       </c>
       <c r="D12" t="n">
-        <v>292.25</v>
+        <v>86.95</v>
       </c>
       <c r="E12" t="n">
-        <v>294.1</v>
+        <v>89</v>
       </c>
       <c r="F12" t="n">
-        <v>6021434</v>
+        <v>15094837</v>
       </c>
       <c r="G12" t="n">
-        <v>3909838</v>
+        <v>10647285</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5400725042827862</v>
+        <v>0.4177170048514715</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>GMRAIRPORT</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>RVNL</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>260.7</v>
+        <v>6610</v>
       </c>
       <c r="C13" t="n">
-        <v>260.75</v>
+        <v>6675</v>
       </c>
       <c r="D13" t="n">
-        <v>249.1</v>
+        <v>6468</v>
       </c>
       <c r="E13" t="n">
-        <v>249.85</v>
+        <v>6575</v>
       </c>
       <c r="F13" t="n">
-        <v>6637313</v>
+        <v>167921</v>
       </c>
       <c r="G13" t="n">
-        <v>4440790</v>
+        <v>118364</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4946243798963698</v>
+        <v>0.4186830455205975</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>RVNL</t>
+          <t>OFSS</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>KEI</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4110</v>
+        <v>1044</v>
       </c>
       <c r="C14" t="n">
-        <v>4121.5</v>
+        <v>1078.1</v>
       </c>
       <c r="D14" t="n">
-        <v>3937</v>
+        <v>1039.4</v>
       </c>
       <c r="E14" t="n">
-        <v>4001</v>
+        <v>1071.7</v>
       </c>
       <c r="F14" t="n">
-        <v>370258</v>
+        <v>771989</v>
       </c>
       <c r="G14" t="n">
-        <v>241373</v>
+        <v>531522</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5339661022566733</v>
+        <v>0.4524121296954783</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>KEI</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>520</v>
+        <v>1380.3</v>
       </c>
       <c r="C15" t="n">
-        <v>522.8</v>
+        <v>1415</v>
       </c>
       <c r="D15" t="n">
-        <v>506.6</v>
+        <v>1358.6</v>
       </c>
       <c r="E15" t="n">
-        <v>510</v>
+        <v>1367.6</v>
       </c>
       <c r="F15" t="n">
-        <v>2589941</v>
+        <v>479377</v>
       </c>
       <c r="G15" t="n">
-        <v>1740070</v>
+        <v>336557</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4884119604383731</v>
+        <v>0.4243560526151588</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>AMBER</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>442.95</v>
+        <v>6467</v>
       </c>
       <c r="C16" t="n">
-        <v>442.95</v>
+        <v>6520</v>
       </c>
       <c r="D16" t="n">
-        <v>421.45</v>
+        <v>6136</v>
       </c>
       <c r="E16" t="n">
-        <v>425.1</v>
+        <v>6450</v>
       </c>
       <c r="F16" t="n">
-        <v>2538797</v>
+        <v>469079</v>
       </c>
       <c r="G16" t="n">
-        <v>1689715</v>
+        <v>314526</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5025001257608531</v>
+        <v>0.4913838601578248</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>AMBER</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>70</v>
+        <v>978</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>1001.5</v>
       </c>
       <c r="D17" t="n">
-        <v>66.2</v>
+        <v>966</v>
       </c>
       <c r="E17" t="n">
-        <v>66.2</v>
+        <v>992</v>
       </c>
       <c r="F17" t="n">
-        <v>16207486</v>
+        <v>1521765</v>
       </c>
       <c r="G17" t="n">
-        <v>11233604</v>
+        <v>1068049</v>
       </c>
       <c r="H17" t="n">
-        <v>0.442768144577644</v>
+        <v>0.4248082250907964</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>HFCL</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>IEX</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>118.71</v>
-      </c>
-      <c r="C18" t="n">
-        <v>119.42</v>
-      </c>
-      <c r="D18" t="n">
-        <v>114.72</v>
-      </c>
-      <c r="E18" t="n">
-        <v>115.2</v>
-      </c>
-      <c r="F18" t="n">
-        <v>7773470</v>
-      </c>
-      <c r="G18" t="n">
-        <v>5086862</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.5281464289772358</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>IEX</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>TITAGARH</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>624.95</v>
-      </c>
-      <c r="C19" t="n">
-        <v>624.95</v>
-      </c>
-      <c r="D19" t="n">
-        <v>590.45</v>
-      </c>
-      <c r="E19" t="n">
-        <v>592.25</v>
-      </c>
-      <c r="F19" t="n">
-        <v>790682</v>
-      </c>
-      <c r="G19" t="n">
-        <v>527597</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.4986476420449699</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>TITAGARH</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>CYIENT</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>820</v>
-      </c>
-      <c r="C20" t="n">
-        <v>825.35</v>
-      </c>
-      <c r="D20" t="n">
-        <v>788.25</v>
-      </c>
-      <c r="E20" t="n">
-        <v>790.95</v>
-      </c>
-      <c r="F20" t="n">
-        <v>309297</v>
-      </c>
-      <c r="G20" t="n">
-        <v>199549</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.5499802053630938</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>CYIENT</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,231 +479,198 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1131.9</v>
+        <v>443.55</v>
       </c>
       <c r="C2" t="n">
-        <v>1142.7</v>
+        <v>446.4</v>
       </c>
       <c r="D2" t="n">
-        <v>1112</v>
+        <v>438.8</v>
       </c>
       <c r="E2" t="n">
-        <v>1136.5</v>
+        <v>443.95</v>
       </c>
       <c r="F2" t="n">
-        <v>1218013</v>
+        <v>8630612</v>
       </c>
       <c r="G2" t="n">
-        <v>2532216</v>
+        <v>20320746</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.518993245441937</v>
+        <v>-0.5752807500275826</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>COALINDIA</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1750</v>
+        <v>1268.9</v>
       </c>
       <c r="C3" t="n">
-        <v>1758</v>
+        <v>1309</v>
       </c>
       <c r="D3" t="n">
-        <v>1703.2</v>
+        <v>1260.1</v>
       </c>
       <c r="E3" t="n">
-        <v>1730</v>
+        <v>1307.9</v>
       </c>
       <c r="F3" t="n">
-        <v>603516</v>
+        <v>1577150</v>
       </c>
       <c r="G3" t="n">
-        <v>1369456</v>
+        <v>3166135</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5593023799231227</v>
+        <v>-0.5018689980054546</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>DRREDDY</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>262.25</v>
+        <v>23500</v>
       </c>
       <c r="C4" t="n">
-        <v>263.9</v>
+        <v>24355</v>
       </c>
       <c r="D4" t="n">
-        <v>257.6</v>
+        <v>23445</v>
       </c>
       <c r="E4" t="n">
-        <v>263.9</v>
+        <v>24260</v>
       </c>
       <c r="F4" t="n">
-        <v>6880170</v>
+        <v>19081</v>
       </c>
       <c r="G4" t="n">
-        <v>13966492</v>
+        <v>39516</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5073802354950692</v>
+        <v>-0.517132300840166</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>SHREECEM</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>243.1</v>
+        <v>802.95</v>
       </c>
       <c r="C5" t="n">
-        <v>244.5</v>
+        <v>834.3</v>
       </c>
       <c r="D5" t="n">
-        <v>236.25</v>
+        <v>802.95</v>
       </c>
       <c r="E5" t="n">
-        <v>241.6</v>
+        <v>820.55</v>
       </c>
       <c r="F5" t="n">
-        <v>6096343</v>
+        <v>3095936</v>
       </c>
       <c r="G5" t="n">
-        <v>12355833</v>
+        <v>6347812</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5066020235139145</v>
+        <v>-0.5122829724635827</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1461</v>
+        <v>999.8</v>
       </c>
       <c r="C6" t="n">
-        <v>1487.5</v>
+        <v>1018.8</v>
       </c>
       <c r="D6" t="n">
-        <v>1438.3</v>
+        <v>992.1</v>
       </c>
       <c r="E6" t="n">
-        <v>1465.9</v>
+        <v>1001</v>
       </c>
       <c r="F6" t="n">
-        <v>927309</v>
+        <v>871077</v>
       </c>
       <c r="G6" t="n">
-        <v>1887266</v>
+        <v>2023338</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5086495491361578</v>
+        <v>-0.5694851774641706</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>360ONE</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SONACOMS</t>
+          <t>BIOCON</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>492.3</v>
+        <v>371</v>
       </c>
       <c r="C7" t="n">
-        <v>498.85</v>
+        <v>382</v>
       </c>
       <c r="D7" t="n">
-        <v>479.65</v>
+        <v>371</v>
       </c>
       <c r="E7" t="n">
-        <v>493.05</v>
+        <v>379.2</v>
       </c>
       <c r="F7" t="n">
-        <v>1604537</v>
+        <v>2037267</v>
       </c>
       <c r="G7" t="n">
-        <v>3152852</v>
+        <v>4115023</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.491083945583237</v>
+        <v>-0.5049196565851515</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SONACOMS</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>BANDHANBNK</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>151.65</v>
-      </c>
-      <c r="C8" t="n">
-        <v>151.89</v>
-      </c>
-      <c r="D8" t="n">
-        <v>145.91</v>
-      </c>
-      <c r="E8" t="n">
-        <v>149.64</v>
-      </c>
-      <c r="F8" t="n">
-        <v>8127874</v>
-      </c>
-      <c r="G8" t="n">
-        <v>16048372</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-0.4935390331181256</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>BANDHANBNK</t>
+          <t>BIOCON</t>
         </is>
       </c>
     </row>
@@ -718,7 +685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -771,528 +738,495 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>SOLARINDS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7210</v>
+        <v>12674</v>
       </c>
       <c r="C2" t="n">
-        <v>7464</v>
+        <v>13258</v>
       </c>
       <c r="D2" t="n">
-        <v>7199</v>
+        <v>12674</v>
       </c>
       <c r="E2" t="n">
-        <v>7433.5</v>
+        <v>12890</v>
       </c>
       <c r="F2" t="n">
-        <v>653790</v>
+        <v>199867</v>
       </c>
       <c r="G2" t="n">
-        <v>464969</v>
+        <v>135319</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4060937395826388</v>
+        <v>0.4770061853841663</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>SOLARINDS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1267.2</v>
+        <v>1130</v>
       </c>
       <c r="C3" t="n">
-        <v>1279.8</v>
+        <v>1165.7</v>
       </c>
       <c r="D3" t="n">
-        <v>1248.4</v>
+        <v>1110.2</v>
       </c>
       <c r="E3" t="n">
-        <v>1256.6</v>
+        <v>1162</v>
       </c>
       <c r="F3" t="n">
-        <v>3166135</v>
+        <v>4460380</v>
       </c>
       <c r="G3" t="n">
-        <v>2112613</v>
+        <v>3020611</v>
       </c>
       <c r="H3" t="n">
-        <v>0.498681963994352</v>
+        <v>0.476648267519386</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>COFORGE</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2184</v>
+        <v>431.8</v>
       </c>
       <c r="C4" t="n">
-        <v>2224.5</v>
+        <v>434.8</v>
       </c>
       <c r="D4" t="n">
-        <v>2153.3</v>
+        <v>422</v>
       </c>
       <c r="E4" t="n">
-        <v>2220.5</v>
+        <v>427.4</v>
       </c>
       <c r="F4" t="n">
-        <v>1561016</v>
+        <v>7419269</v>
       </c>
       <c r="G4" t="n">
-        <v>978398</v>
+        <v>4652608</v>
       </c>
       <c r="H4" t="n">
-        <v>0.595481593380199</v>
+        <v>0.594647346176596</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>141.58</v>
+        <v>176.01</v>
       </c>
       <c r="C5" t="n">
-        <v>142.5</v>
+        <v>183.49</v>
       </c>
       <c r="D5" t="n">
-        <v>137.02</v>
+        <v>175.52</v>
       </c>
       <c r="E5" t="n">
-        <v>138.8</v>
+        <v>180.3</v>
       </c>
       <c r="F5" t="n">
-        <v>30509694</v>
+        <v>17554430</v>
       </c>
       <c r="G5" t="n">
-        <v>21048472</v>
+        <v>12443272</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4494968565889249</v>
+        <v>0.4107567527254889</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>110.5</v>
+        <v>1738.5</v>
       </c>
       <c r="C6" t="n">
-        <v>111.66</v>
+        <v>1751.4</v>
       </c>
       <c r="D6" t="n">
-        <v>106.53</v>
+        <v>1720</v>
       </c>
       <c r="E6" t="n">
-        <v>111.16</v>
+        <v>1734.9</v>
       </c>
       <c r="F6" t="n">
-        <v>32098828</v>
+        <v>1733055</v>
       </c>
       <c r="G6" t="n">
-        <v>21402616</v>
+        <v>1227249</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4997618982651467</v>
+        <v>0.4121461903819029</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>833</v>
+        <v>265.5</v>
       </c>
       <c r="C7" t="n">
-        <v>842.15</v>
+        <v>273.9</v>
       </c>
       <c r="D7" t="n">
-        <v>801.4</v>
+        <v>264.8</v>
       </c>
       <c r="E7" t="n">
-        <v>839</v>
+        <v>270.9</v>
       </c>
       <c r="F7" t="n">
-        <v>4139485</v>
+        <v>9709681</v>
       </c>
       <c r="G7" t="n">
-        <v>2746629</v>
+        <v>6880170</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5071147213547953</v>
+        <v>0.411255971872788</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1290.9</v>
+        <v>2139.9</v>
       </c>
       <c r="C8" t="n">
-        <v>1334.9</v>
+        <v>2154.4</v>
       </c>
       <c r="D8" t="n">
-        <v>1282.7</v>
+        <v>2100.9</v>
       </c>
       <c r="E8" t="n">
-        <v>1331.5</v>
+        <v>2140</v>
       </c>
       <c r="F8" t="n">
-        <v>1628922</v>
+        <v>1105605</v>
       </c>
       <c r="G8" t="n">
-        <v>1141612</v>
+        <v>747214</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4268613154031317</v>
+        <v>0.4796363558498636</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>MPHASIS</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3730</v>
+        <v>246.65</v>
       </c>
       <c r="C9" t="n">
-        <v>3820.5</v>
+        <v>251.25</v>
       </c>
       <c r="D9" t="n">
-        <v>3685.1</v>
+        <v>244.55</v>
       </c>
       <c r="E9" t="n">
-        <v>3759.8</v>
+        <v>251</v>
       </c>
       <c r="F9" t="n">
-        <v>416887</v>
+        <v>8711316</v>
       </c>
       <c r="G9" t="n">
-        <v>296381</v>
+        <v>6096343</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4065915156504634</v>
+        <v>0.4289412521572359</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>PETRONET</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UPL</t>
+          <t>JUBLFOOD</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>615</v>
+        <v>450</v>
       </c>
       <c r="C10" t="n">
-        <v>625.6</v>
+        <v>470.05</v>
       </c>
       <c r="D10" t="n">
-        <v>608.45</v>
+        <v>448.6</v>
       </c>
       <c r="E10" t="n">
-        <v>620.95</v>
+        <v>463</v>
       </c>
       <c r="F10" t="n">
-        <v>2609729</v>
+        <v>3256950</v>
       </c>
       <c r="G10" t="n">
-        <v>1690435</v>
+        <v>2152093</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5438209691588259</v>
+        <v>0.5133872002743376</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>UPL</t>
+          <t>JUBLFOOD</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>BANKINDIA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2099.6</v>
+        <v>148</v>
       </c>
       <c r="C11" t="n">
-        <v>2138.2</v>
+        <v>150.8</v>
       </c>
       <c r="D11" t="n">
-        <v>2056.7</v>
+        <v>147.81</v>
       </c>
       <c r="E11" t="n">
-        <v>2117</v>
+        <v>149.95</v>
       </c>
       <c r="F11" t="n">
-        <v>747214</v>
+        <v>8785495</v>
       </c>
       <c r="G11" t="n">
-        <v>471389</v>
+        <v>5828421</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5851324489964763</v>
+        <v>0.5073542216665543</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>BANKINDIA</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GMRAIRPORT</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>88</v>
+        <v>1530</v>
       </c>
       <c r="C12" t="n">
-        <v>90.34</v>
+        <v>1580.5</v>
       </c>
       <c r="D12" t="n">
-        <v>86.95</v>
+        <v>1516.5</v>
       </c>
       <c r="E12" t="n">
-        <v>89</v>
+        <v>1557</v>
       </c>
       <c r="F12" t="n">
-        <v>15094837</v>
+        <v>692165</v>
       </c>
       <c r="G12" t="n">
-        <v>10647285</v>
+        <v>465679</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4177170048514715</v>
+        <v>0.4863564816107233</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>GMRAIRPORT</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>PRESTIGE</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6610</v>
+        <v>1215</v>
       </c>
       <c r="C13" t="n">
-        <v>6675</v>
+        <v>1250.4</v>
       </c>
       <c r="D13" t="n">
-        <v>6468</v>
+        <v>1215</v>
       </c>
       <c r="E13" t="n">
-        <v>6575</v>
+        <v>1234</v>
       </c>
       <c r="F13" t="n">
-        <v>167921</v>
+        <v>734311</v>
       </c>
       <c r="G13" t="n">
-        <v>118364</v>
+        <v>490182</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4186830455205975</v>
+        <v>0.4980374636359556</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>PRESTIGE</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>ANGELONE</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1044</v>
+        <v>233.5</v>
       </c>
       <c r="C14" t="n">
-        <v>1078.1</v>
+        <v>243.8</v>
       </c>
       <c r="D14" t="n">
-        <v>1039.4</v>
+        <v>233.1</v>
       </c>
       <c r="E14" t="n">
-        <v>1071.7</v>
+        <v>241.3</v>
       </c>
       <c r="F14" t="n">
-        <v>771989</v>
+        <v>8880739</v>
       </c>
       <c r="G14" t="n">
-        <v>531522</v>
+        <v>6207473</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4524121296954783</v>
+        <v>0.4306528598674533</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>ANGELONE</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TORNTPOWER</t>
+          <t>NUVAMA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1380.3</v>
+        <v>1156</v>
       </c>
       <c r="C15" t="n">
-        <v>1415</v>
+        <v>1206.8</v>
       </c>
       <c r="D15" t="n">
-        <v>1358.6</v>
+        <v>1149.9</v>
       </c>
       <c r="E15" t="n">
-        <v>1367.6</v>
+        <v>1201</v>
       </c>
       <c r="F15" t="n">
-        <v>479377</v>
+        <v>540971</v>
       </c>
       <c r="G15" t="n">
-        <v>336557</v>
+        <v>385998</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4243560526151588</v>
+        <v>0.4014865361996695</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>TORNTPOWER</t>
+          <t>NUVAMA</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>CYIENT</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6467</v>
+        <v>807</v>
       </c>
       <c r="C16" t="n">
-        <v>6520</v>
+        <v>827.8</v>
       </c>
       <c r="D16" t="n">
-        <v>6136</v>
+        <v>795.45</v>
       </c>
       <c r="E16" t="n">
-        <v>6450</v>
+        <v>814</v>
       </c>
       <c r="F16" t="n">
-        <v>469079</v>
+        <v>586179</v>
       </c>
       <c r="G16" t="n">
-        <v>314526</v>
+        <v>414210</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4913838601578248</v>
+        <v>0.4151734627362932</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>AMBER</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>LAURUSLABS</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>978</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1001.5</v>
-      </c>
-      <c r="D17" t="n">
-        <v>966</v>
-      </c>
-      <c r="E17" t="n">
-        <v>992</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1521765</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1068049</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.4248082250907964</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>LAURUSLABS</t>
+          <t>CYIENT</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,6 +473,138 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>filterdata</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>UNITDSPR</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1314.5</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1314.6</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1250.6</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1251.9</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1426042</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3189905</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-0.5529515769278396</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>UNITDSPR</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GMRAIRPORT</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>90.12</v>
+      </c>
+      <c r="C3" t="n">
+        <v>90.19</v>
+      </c>
+      <c r="D3" t="n">
+        <v>87.59</v>
+      </c>
+      <c r="E3" t="n">
+        <v>89.33</v>
+      </c>
+      <c r="F3" t="n">
+        <v>9727084</v>
+      </c>
+      <c r="G3" t="n">
+        <v>20843793</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-0.5333342640660459</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>GMRAIRPORT</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BLUESTARCO</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1739</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1739</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1668.1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1673</v>
+      </c>
+      <c r="F4" t="n">
+        <v>366704</v>
+      </c>
+      <c r="G4" t="n">
+        <v>902460</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.5936617689426679</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>BLUESTARCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>512.05</v>
+      </c>
+      <c r="C5" t="n">
+        <v>514.95</v>
+      </c>
+      <c r="D5" t="n">
+        <v>485.6</v>
+      </c>
+      <c r="E5" t="n">
+        <v>487</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3276476</v>
+      </c>
+      <c r="G5" t="n">
+        <v>8024061</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.591668607703755</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>PGEL</t>
         </is>
       </c>
     </row>
@@ -487,7 +619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,6 +669,600 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>12626</v>
+      </c>
+      <c r="C2" t="n">
+        <v>12646</v>
+      </c>
+      <c r="D2" t="n">
+        <v>12342</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12411</v>
+      </c>
+      <c r="F2" t="n">
+        <v>775339</v>
+      </c>
+      <c r="G2" t="n">
+        <v>540649</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.4340893999618977</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>411.9</v>
+      </c>
+      <c r="C3" t="n">
+        <v>413.45</v>
+      </c>
+      <c r="D3" t="n">
+        <v>403.25</v>
+      </c>
+      <c r="E3" t="n">
+        <v>405.95</v>
+      </c>
+      <c r="F3" t="n">
+        <v>21818224</v>
+      </c>
+      <c r="G3" t="n">
+        <v>15134997</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.4415743855119363</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2651</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2655</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2604.6</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2642.1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2406056</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1656810</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.4522220411513692</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1785</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1819</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1785</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1794</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2975423</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1900794</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.5653579504144057</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1375</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1375</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1330.1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1339.9</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2667313</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1856531</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.4367188051263351</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1226.5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1249.2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1226.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1242</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2220695</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1466775</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.5139983978456136</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>605</v>
+      </c>
+      <c r="C8" t="n">
+        <v>612.45</v>
+      </c>
+      <c r="D8" t="n">
+        <v>600</v>
+      </c>
+      <c r="E8" t="n">
+        <v>610.9</v>
+      </c>
+      <c r="F8" t="n">
+        <v>4422345</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2915736</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.5167165340071941</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BANKBARODA</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>269.5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>269.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>258.35</v>
+      </c>
+      <c r="E9" t="n">
+        <v>260.7</v>
+      </c>
+      <c r="F9" t="n">
+        <v>19957366</v>
+      </c>
+      <c r="G9" t="n">
+        <v>13583867</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.4691962163646037</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>BANKBARODA</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>390</v>
+      </c>
+      <c r="C10" t="n">
+        <v>391.55</v>
+      </c>
+      <c r="D10" t="n">
+        <v>384.6</v>
+      </c>
+      <c r="E10" t="n">
+        <v>385</v>
+      </c>
+      <c r="F10" t="n">
+        <v>9994317</v>
+      </c>
+      <c r="G10" t="n">
+        <v>6900597</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.4483264274091068</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1135.9</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1154.7</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1122.4</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1129.8</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1840045</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1230757</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.495051419573482</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1351.7</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1359</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1310</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1315.9</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1353886</v>
+      </c>
+      <c r="G12" t="n">
+        <v>886923</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.5264977906763045</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1464.8</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1473.9</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1393.3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1455</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3003383</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2038094</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.4736233951917821</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SYNGENE</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>419</v>
+      </c>
+      <c r="C14" t="n">
+        <v>426.15</v>
+      </c>
+      <c r="D14" t="n">
+        <v>402.75</v>
+      </c>
+      <c r="E14" t="n">
+        <v>410.5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4019947</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2747812</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.4629628955692748</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>SYNGENE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>441</v>
+      </c>
+      <c r="C15" t="n">
+        <v>442.75</v>
+      </c>
+      <c r="D15" t="n">
+        <v>432.85</v>
+      </c>
+      <c r="E15" t="n">
+        <v>440</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2067540</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1469610</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.406863045297732</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>JSL</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>722.8</v>
+      </c>
+      <c r="C16" t="n">
+        <v>727.7</v>
+      </c>
+      <c r="D16" t="n">
+        <v>698.5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>713</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1187748</v>
+      </c>
+      <c r="G16" t="n">
+        <v>841403</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.4116279594914684</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>JSL</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SJVN</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="C17" t="n">
+        <v>67.89</v>
+      </c>
+      <c r="D17" t="n">
+        <v>66.05</v>
+      </c>
+      <c r="E17" t="n">
+        <v>66.09</v>
+      </c>
+      <c r="F17" t="n">
+        <v>7389422</v>
+      </c>
+      <c r="G17" t="n">
+        <v>4989064</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.4811239142251933</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>SJVN</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>IEX</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>121</v>
+      </c>
+      <c r="C18" t="n">
+        <v>122.76</v>
+      </c>
+      <c r="D18" t="n">
+        <v>118.31</v>
+      </c>
+      <c r="E18" t="n">
+        <v>118.82</v>
+      </c>
+      <c r="F18" t="n">
+        <v>11710831</v>
+      </c>
+      <c r="G18" t="n">
+        <v>7993787</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.4649916241200823</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>IEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>KFINTECH</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>929.85</v>
+      </c>
+      <c r="C19" t="n">
+        <v>931.05</v>
+      </c>
+      <c r="D19" t="n">
+        <v>904</v>
+      </c>
+      <c r="E19" t="n">
+        <v>912</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1511906</v>
+      </c>
+      <c r="G19" t="n">
+        <v>965199</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.5664189457303623</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>KFINTECH</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -479,132 +479,132 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>BPCL</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1314.5</v>
+        <v>274.95</v>
       </c>
       <c r="C2" t="n">
-        <v>1314.6</v>
+        <v>285.25</v>
       </c>
       <c r="D2" t="n">
-        <v>1250.6</v>
+        <v>273.1</v>
       </c>
       <c r="E2" t="n">
-        <v>1251.9</v>
+        <v>281.35</v>
       </c>
       <c r="F2" t="n">
-        <v>1426042</v>
+        <v>14757987</v>
       </c>
       <c r="G2" t="n">
-        <v>3189905</v>
+        <v>29524543</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5529515769278396</v>
+        <v>-0.5001451165560802</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>BPCL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GMRAIRPORT</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>90.12</v>
+        <v>2371.2</v>
       </c>
       <c r="C3" t="n">
-        <v>90.19</v>
+        <v>2416</v>
       </c>
       <c r="D3" t="n">
-        <v>87.59</v>
+        <v>2345</v>
       </c>
       <c r="E3" t="n">
-        <v>89.33</v>
+        <v>2390</v>
       </c>
       <c r="F3" t="n">
-        <v>9727084</v>
+        <v>3743842</v>
       </c>
       <c r="G3" t="n">
-        <v>20843793</v>
+        <v>7840574</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5333342640660459</v>
+        <v>-0.5225040921748841</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>GMRAIRPORT</t>
+          <t>MCX</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BLUESTARCO</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1739</v>
+        <v>1135</v>
       </c>
       <c r="C4" t="n">
-        <v>1739</v>
+        <v>1136.4</v>
       </c>
       <c r="D4" t="n">
-        <v>1668.1</v>
+        <v>1111</v>
       </c>
       <c r="E4" t="n">
-        <v>1673</v>
+        <v>1114.7</v>
       </c>
       <c r="F4" t="n">
-        <v>366704</v>
+        <v>1568667</v>
       </c>
       <c r="G4" t="n">
-        <v>902460</v>
+        <v>3106962</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5936617689426679</v>
+        <v>-0.4951122672243819</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>BLUESTARCO</t>
+          <t>COFORGE</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>SONACOMS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>512.05</v>
+        <v>484.05</v>
       </c>
       <c r="C5" t="n">
-        <v>514.95</v>
+        <v>488.9</v>
       </c>
       <c r="D5" t="n">
-        <v>485.6</v>
+        <v>474.5</v>
       </c>
       <c r="E5" t="n">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="F5" t="n">
-        <v>3276476</v>
+        <v>3529118</v>
       </c>
       <c r="G5" t="n">
-        <v>8024061</v>
+        <v>8344260</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.591668607703755</v>
+        <v>-0.5770603984056105</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>SONACOMS</t>
         </is>
       </c>
     </row>
@@ -672,594 +672,594 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12626</v>
+        <v>745.2</v>
       </c>
       <c r="C2" t="n">
-        <v>12646</v>
+        <v>751</v>
       </c>
       <c r="D2" t="n">
-        <v>12342</v>
+        <v>726.65</v>
       </c>
       <c r="E2" t="n">
-        <v>12411</v>
+        <v>735</v>
       </c>
       <c r="F2" t="n">
-        <v>775339</v>
+        <v>103500135</v>
       </c>
       <c r="G2" t="n">
-        <v>540649</v>
+        <v>65485199</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4340893999618977</v>
+        <v>0.5805118802494591</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>411.9</v>
+        <v>4030</v>
       </c>
       <c r="C3" t="n">
-        <v>413.45</v>
+        <v>4092.2</v>
       </c>
       <c r="D3" t="n">
-        <v>403.25</v>
+        <v>3930.6</v>
       </c>
       <c r="E3" t="n">
-        <v>405.95</v>
+        <v>3950</v>
       </c>
       <c r="F3" t="n">
-        <v>21818224</v>
+        <v>2450995</v>
       </c>
       <c r="G3" t="n">
-        <v>15134997</v>
+        <v>1693708</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4415743855119363</v>
+        <v>0.4471178030687698</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>INDIGO</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2651</v>
+        <v>1786.8</v>
       </c>
       <c r="C4" t="n">
-        <v>2655</v>
+        <v>1790</v>
       </c>
       <c r="D4" t="n">
-        <v>2604.6</v>
+        <v>1750.1</v>
       </c>
       <c r="E4" t="n">
-        <v>2642.1</v>
+        <v>1762</v>
       </c>
       <c r="F4" t="n">
-        <v>2406056</v>
+        <v>4182503</v>
       </c>
       <c r="G4" t="n">
-        <v>1656810</v>
+        <v>2975423</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4522220411513692</v>
+        <v>0.4056834944140715</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1785</v>
+        <v>10985</v>
       </c>
       <c r="C5" t="n">
-        <v>1819</v>
+        <v>10990</v>
       </c>
       <c r="D5" t="n">
-        <v>1785</v>
+        <v>10687</v>
       </c>
       <c r="E5" t="n">
-        <v>1794</v>
+        <v>10800</v>
       </c>
       <c r="F5" t="n">
-        <v>2975423</v>
+        <v>632265</v>
       </c>
       <c r="G5" t="n">
-        <v>1900794</v>
+        <v>418469</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5653579504144057</v>
+        <v>0.5109004490177289</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1375</v>
+        <v>3300</v>
       </c>
       <c r="C6" t="n">
-        <v>1375</v>
+        <v>3383.6</v>
       </c>
       <c r="D6" t="n">
-        <v>1330.1</v>
+        <v>3275.5</v>
       </c>
       <c r="E6" t="n">
-        <v>1339.9</v>
+        <v>3298.8</v>
       </c>
       <c r="F6" t="n">
-        <v>2667313</v>
+        <v>1835877</v>
       </c>
       <c r="G6" t="n">
-        <v>1856531</v>
+        <v>1288297</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4367188051263351</v>
+        <v>0.4250417411513028</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>TRENT</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1226.5</v>
+        <v>3942</v>
       </c>
       <c r="C7" t="n">
-        <v>1249.2</v>
+        <v>4007.4</v>
       </c>
       <c r="D7" t="n">
-        <v>1226.5</v>
+        <v>3914.1</v>
       </c>
       <c r="E7" t="n">
-        <v>1242</v>
+        <v>3955.4</v>
       </c>
       <c r="F7" t="n">
-        <v>2220695</v>
+        <v>1488223</v>
       </c>
       <c r="G7" t="n">
-        <v>1466775</v>
+        <v>1040658</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5139983978456136</v>
+        <v>0.4300788539558625</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>TITAN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>605</v>
+        <v>7470</v>
       </c>
       <c r="C8" t="n">
-        <v>612.45</v>
+        <v>7509.5</v>
       </c>
       <c r="D8" t="n">
-        <v>600</v>
+        <v>7360.5</v>
       </c>
       <c r="E8" t="n">
-        <v>610.9</v>
+        <v>7499.5</v>
       </c>
       <c r="F8" t="n">
-        <v>4422345</v>
+        <v>764508</v>
       </c>
       <c r="G8" t="n">
-        <v>2915736</v>
+        <v>533512</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5167165340071941</v>
+        <v>0.4329724542278337</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>269.5</v>
+        <v>608.95</v>
       </c>
       <c r="C9" t="n">
-        <v>269.5</v>
+        <v>610</v>
       </c>
       <c r="D9" t="n">
-        <v>258.35</v>
+        <v>587.85</v>
       </c>
       <c r="E9" t="n">
-        <v>260.7</v>
+        <v>592.95</v>
       </c>
       <c r="F9" t="n">
-        <v>19957366</v>
+        <v>6294260</v>
       </c>
       <c r="G9" t="n">
-        <v>13583867</v>
+        <v>4422345</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4691962163646037</v>
+        <v>0.4232856097839495</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>390</v>
+        <v>652.95</v>
       </c>
       <c r="C10" t="n">
-        <v>391.55</v>
+        <v>678.6</v>
       </c>
       <c r="D10" t="n">
-        <v>384.6</v>
+        <v>650.25</v>
       </c>
       <c r="E10" t="n">
-        <v>385</v>
+        <v>658.55</v>
       </c>
       <c r="F10" t="n">
-        <v>9994317</v>
+        <v>24457507</v>
       </c>
       <c r="G10" t="n">
-        <v>6900597</v>
+        <v>17226044</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4483264274091068</v>
+        <v>0.4197982427073796</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>VEDL</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1135.9</v>
+        <v>23365</v>
       </c>
       <c r="C11" t="n">
-        <v>1154.7</v>
+        <v>23625</v>
       </c>
       <c r="D11" t="n">
-        <v>1122.4</v>
+        <v>22955</v>
       </c>
       <c r="E11" t="n">
-        <v>1129.8</v>
+        <v>23000</v>
       </c>
       <c r="F11" t="n">
-        <v>1840045</v>
+        <v>81205</v>
       </c>
       <c r="G11" t="n">
-        <v>1230757</v>
+        <v>52525</v>
       </c>
       <c r="H11" t="n">
-        <v>0.495051419573482</v>
+        <v>0.5460257020466445</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>SHREECEM</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1351.7</v>
+        <v>4855</v>
       </c>
       <c r="C12" t="n">
-        <v>1359</v>
+        <v>4929.5</v>
       </c>
       <c r="D12" t="n">
-        <v>1310</v>
+        <v>4825</v>
       </c>
       <c r="E12" t="n">
-        <v>1315.9</v>
+        <v>4850</v>
       </c>
       <c r="F12" t="n">
-        <v>1353886</v>
+        <v>1293604</v>
       </c>
       <c r="G12" t="n">
-        <v>886923</v>
+        <v>872749</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5264977906763045</v>
+        <v>0.4822176822889513</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1464.8</v>
+        <v>425.05</v>
       </c>
       <c r="C13" t="n">
-        <v>1473.9</v>
+        <v>429</v>
       </c>
       <c r="D13" t="n">
-        <v>1393.3</v>
+        <v>415.5</v>
       </c>
       <c r="E13" t="n">
-        <v>1455</v>
+        <v>415.5</v>
       </c>
       <c r="F13" t="n">
-        <v>3003383</v>
+        <v>8737012</v>
       </c>
       <c r="G13" t="n">
-        <v>2038094</v>
+        <v>6160559</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4736233951917821</v>
+        <v>0.4182174052711775</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SYNGENE</t>
+          <t>PAYTM</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>419</v>
+        <v>992</v>
       </c>
       <c r="C14" t="n">
-        <v>426.15</v>
+        <v>997.9</v>
       </c>
       <c r="D14" t="n">
-        <v>402.75</v>
+        <v>930.6</v>
       </c>
       <c r="E14" t="n">
-        <v>410.5</v>
+        <v>951</v>
       </c>
       <c r="F14" t="n">
-        <v>4019947</v>
+        <v>3108158</v>
       </c>
       <c r="G14" t="n">
-        <v>2747812</v>
+        <v>2219237</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4629628955692748</v>
+        <v>0.4005525322441902</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>SYNGENE</t>
+          <t>PAYTM</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>441</v>
+        <v>1477</v>
       </c>
       <c r="C15" t="n">
-        <v>442.75</v>
+        <v>1523.6</v>
       </c>
       <c r="D15" t="n">
-        <v>432.85</v>
+        <v>1475</v>
       </c>
       <c r="E15" t="n">
-        <v>440</v>
+        <v>1500</v>
       </c>
       <c r="F15" t="n">
-        <v>2067540</v>
+        <v>1275726</v>
       </c>
       <c r="G15" t="n">
-        <v>1469610</v>
+        <v>884732</v>
       </c>
       <c r="H15" t="n">
-        <v>0.406863045297732</v>
+        <v>0.4419349588349918</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>JSL</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>722.8</v>
+        <v>1534</v>
       </c>
       <c r="C16" t="n">
-        <v>727.7</v>
+        <v>1556.8</v>
       </c>
       <c r="D16" t="n">
-        <v>698.5</v>
+        <v>1473.6</v>
       </c>
       <c r="E16" t="n">
-        <v>713</v>
+        <v>1475.7</v>
       </c>
       <c r="F16" t="n">
-        <v>1187748</v>
+        <v>1255227</v>
       </c>
       <c r="G16" t="n">
-        <v>841403</v>
+        <v>832203</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4116279594914684</v>
+        <v>0.5083182829189513</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>JSL</t>
+          <t>MFSL</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SJVN</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>67.5</v>
+        <v>431.95</v>
       </c>
       <c r="C17" t="n">
-        <v>67.89</v>
+        <v>434.2</v>
       </c>
       <c r="D17" t="n">
-        <v>66.05</v>
+        <v>423.5</v>
       </c>
       <c r="E17" t="n">
-        <v>66.09</v>
+        <v>424</v>
       </c>
       <c r="F17" t="n">
-        <v>7389422</v>
+        <v>3050426</v>
       </c>
       <c r="G17" t="n">
-        <v>4989064</v>
+        <v>2067540</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4811239142251933</v>
+        <v>0.4753891097632936</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>SJVN</t>
+          <t>CONCOR</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>121</v>
+        <v>417.5</v>
       </c>
       <c r="C18" t="n">
-        <v>122.76</v>
+        <v>417.5</v>
       </c>
       <c r="D18" t="n">
-        <v>118.31</v>
+        <v>408</v>
       </c>
       <c r="E18" t="n">
-        <v>118.82</v>
+        <v>410</v>
       </c>
       <c r="F18" t="n">
-        <v>11710831</v>
+        <v>2504445</v>
       </c>
       <c r="G18" t="n">
-        <v>7993787</v>
+        <v>1692776</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4649916241200823</v>
+        <v>0.4794899029759401</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>DABUR</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>KFINTECH</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>929.85</v>
+        <v>785</v>
       </c>
       <c r="C19" t="n">
-        <v>931.05</v>
+        <v>785.9</v>
       </c>
       <c r="D19" t="n">
-        <v>904</v>
+        <v>749</v>
       </c>
       <c r="E19" t="n">
-        <v>912</v>
+        <v>760</v>
       </c>
       <c r="F19" t="n">
-        <v>1511906</v>
+        <v>1471638</v>
       </c>
       <c r="G19" t="n">
-        <v>965199</v>
+        <v>947914</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5664189457303623</v>
+        <v>0.5525015982462544</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>KFINTECH</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,6 +473,732 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>filterdata</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1399.7</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1399.7</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1349</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1356</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2469237</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5541018</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-0.5543712364767629</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MAXHEALTH</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>966.2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>981.5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>952.3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>956</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2467966</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4941358</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-0.5005490393531494</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>MAXHEALTH</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>WIPRO</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>191.51</v>
+      </c>
+      <c r="C4" t="n">
+        <v>194.49</v>
+      </c>
+      <c r="D4" t="n">
+        <v>190.41</v>
+      </c>
+      <c r="E4" t="n">
+        <v>191.1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>11769673</v>
+      </c>
+      <c r="G4" t="n">
+        <v>27946986</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.5788571619136318</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>WIPRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1828.4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1845.6</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1762.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1793</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1132054</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2274502</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.5022848957705907</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CUMMINSIND</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4640</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4670.2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4544.2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4618</v>
+      </c>
+      <c r="F6" t="n">
+        <v>598276</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1251680</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.5220216029656142</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>CUMMINSIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>673</v>
+      </c>
+      <c r="C7" t="n">
+        <v>690.25</v>
+      </c>
+      <c r="D7" t="n">
+        <v>672.4</v>
+      </c>
+      <c r="E7" t="n">
+        <v>679.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2316056</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4829822</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.5204676279995412</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SUZLON</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>41.39</v>
+      </c>
+      <c r="C8" t="n">
+        <v>41.59</v>
+      </c>
+      <c r="D8" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="E8" t="n">
+        <v>41.19</v>
+      </c>
+      <c r="F8" t="n">
+        <v>58512083</v>
+      </c>
+      <c r="G8" t="n">
+        <v>126591848</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.5377894870450109</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>SUZLON</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AUBANK</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>859.65</v>
+      </c>
+      <c r="C9" t="n">
+        <v>884.8</v>
+      </c>
+      <c r="D9" t="n">
+        <v>859.65</v>
+      </c>
+      <c r="E9" t="n">
+        <v>873.85</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2150156</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4276408</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.4972051310352053</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>AUBANK</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ICICIGI</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1735</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1754.9</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1689</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1695.9</v>
+      </c>
+      <c r="F10" t="n">
+        <v>952924</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2042303</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.5334071389015244</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ICICIGI</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>UPL</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>573</v>
+      </c>
+      <c r="C11" t="n">
+        <v>601.85</v>
+      </c>
+      <c r="D11" t="n">
+        <v>573</v>
+      </c>
+      <c r="E11" t="n">
+        <v>598.2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2182769</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5317081</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.589479829252178</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>UPL</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LICI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>745</v>
+      </c>
+      <c r="C12" t="n">
+        <v>758.05</v>
+      </c>
+      <c r="D12" t="n">
+        <v>736.55</v>
+      </c>
+      <c r="E12" t="n">
+        <v>747.6</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1461768</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3174107</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.5394711016358301</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>LICI</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>JSWENERGY</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>477.5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>490</v>
+      </c>
+      <c r="D13" t="n">
+        <v>477.5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>484.35</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2188358</v>
+      </c>
+      <c r="G13" t="n">
+        <v>4311729</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.4924639280437152</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>JSWENERGY</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>COLPAL</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1822</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1845</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1810.3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1831.8</v>
+      </c>
+      <c r="F14" t="n">
+        <v>407513</v>
+      </c>
+      <c r="G14" t="n">
+        <v>907544</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.5509716333312765</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>COLPAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PATANJALI</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>473.8</v>
+      </c>
+      <c r="C15" t="n">
+        <v>478</v>
+      </c>
+      <c r="D15" t="n">
+        <v>465.2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>469.85</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1460492</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3158842</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.5376495563880688</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>PATANJALI</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PAGEIND</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>32305</v>
+      </c>
+      <c r="C16" t="n">
+        <v>32820</v>
+      </c>
+      <c r="D16" t="n">
+        <v>32000</v>
+      </c>
+      <c r="E16" t="n">
+        <v>32795</v>
+      </c>
+      <c r="F16" t="n">
+        <v>18816</v>
+      </c>
+      <c r="G16" t="n">
+        <v>41114</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.5423456730067617</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>PAGEIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>966.05</v>
+      </c>
+      <c r="C17" t="n">
+        <v>982.7</v>
+      </c>
+      <c r="D17" t="n">
+        <v>950</v>
+      </c>
+      <c r="E17" t="n">
+        <v>955</v>
+      </c>
+      <c r="F17" t="n">
+        <v>610228</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1347427</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.5471160960853538</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SONACOMS</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>492</v>
+      </c>
+      <c r="C18" t="n">
+        <v>507.8</v>
+      </c>
+      <c r="D18" t="n">
+        <v>492</v>
+      </c>
+      <c r="E18" t="n">
+        <v>497.4</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1772619</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3529118</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.4977161432403224</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>SONACOMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TATATECH</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>519</v>
+      </c>
+      <c r="C19" t="n">
+        <v>539.2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>519</v>
+      </c>
+      <c r="E19" t="n">
+        <v>531.2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1067785</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2327922</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.5413140990119085</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>TATATECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SYNGENE</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>395.05</v>
+      </c>
+      <c r="C20" t="n">
+        <v>404.5</v>
+      </c>
+      <c r="D20" t="n">
+        <v>390.45</v>
+      </c>
+      <c r="E20" t="n">
+        <v>395</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1377179</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3055190</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-0.5492329445959171</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>SYNGENE</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>KFINTECH</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>914</v>
+      </c>
+      <c r="C21" t="n">
+        <v>920.7</v>
+      </c>
+      <c r="D21" t="n">
+        <v>897</v>
+      </c>
+      <c r="E21" t="n">
+        <v>903</v>
+      </c>
+      <c r="F21" t="n">
+        <v>461461</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1139443</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.5950117732962509</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>KFINTECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>NCC</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>135</v>
+      </c>
+      <c r="C22" t="n">
+        <v>139.8</v>
+      </c>
+      <c r="D22" t="n">
+        <v>134.5</v>
+      </c>
+      <c r="E22" t="n">
+        <v>138.9</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2543175</v>
+      </c>
+      <c r="G22" t="n">
+        <v>5402525</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-0.5292617803712153</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>NCC</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PPLPHARMA</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>140</v>
+      </c>
+      <c r="C23" t="n">
+        <v>144.18</v>
+      </c>
+      <c r="D23" t="n">
+        <v>139.62</v>
+      </c>
+      <c r="E23" t="n">
+        <v>142.5</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2094474</v>
+      </c>
+      <c r="G23" t="n">
+        <v>4589871</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.543674756872252</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>PPLPHARMA</t>
         </is>
       </c>
     </row>
@@ -487,7 +1213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,6 +1263,204 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>600</v>
+      </c>
+      <c r="C2" t="n">
+        <v>606.15</v>
+      </c>
+      <c r="D2" t="n">
+        <v>569</v>
+      </c>
+      <c r="E2" t="n">
+        <v>572.15</v>
+      </c>
+      <c r="F2" t="n">
+        <v>9823726</v>
+      </c>
+      <c r="G2" t="n">
+        <v>6294260</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.5607435981354441</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>DMART</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>4075</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4294.8</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4066.1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4263.3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2710202</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1738503</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.5589285724557277</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>DMART</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1020.1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1044.4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1017.55</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1042</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2351992</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1517014</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.550408895369456</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MANKIND</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2049.8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1973.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2004</v>
+      </c>
+      <c r="F5" t="n">
+        <v>961650</v>
+      </c>
+      <c r="G5" t="n">
+        <v>609779</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.5770467661234644</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>MANKIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KAYNES</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3629.5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3674.8</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3520.8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3538</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2072395</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1304022</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.5892331571093126</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>KAYNES</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CESC</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>153.49</v>
+      </c>
+      <c r="C7" t="n">
+        <v>154.9</v>
+      </c>
+      <c r="D7" t="n">
+        <v>150.92</v>
+      </c>
+      <c r="E7" t="n">
+        <v>153.45</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2218241</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1452067</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.5276436968817555</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>CESC</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,726 +479,198 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1399.7</v>
+        <v>4070</v>
       </c>
       <c r="C2" t="n">
-        <v>1399.7</v>
+        <v>4211.4</v>
       </c>
       <c r="D2" t="n">
-        <v>1349</v>
+        <v>3970</v>
       </c>
       <c r="E2" t="n">
-        <v>1356</v>
+        <v>4170</v>
       </c>
       <c r="F2" t="n">
-        <v>2469237</v>
+        <v>2222700</v>
       </c>
       <c r="G2" t="n">
-        <v>5541018</v>
+        <v>4361610</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5543712364767629</v>
+        <v>-0.4903946019933006</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>INDIGO</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MAXHEALTH</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>966.2</v>
+        <v>448.4</v>
       </c>
       <c r="C3" t="n">
-        <v>981.5</v>
+        <v>453.3</v>
       </c>
       <c r="D3" t="n">
-        <v>952.3</v>
+        <v>440.5</v>
       </c>
       <c r="E3" t="n">
-        <v>956</v>
+        <v>449.3</v>
       </c>
       <c r="F3" t="n">
-        <v>2467966</v>
+        <v>6701003</v>
       </c>
       <c r="G3" t="n">
-        <v>4941358</v>
+        <v>14960312</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5005490393531494</v>
+        <v>-0.5520813335978555</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MAXHEALTH</t>
+          <t>COALINDIA</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>HDFCAMC</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>191.51</v>
+        <v>2298</v>
       </c>
       <c r="C4" t="n">
-        <v>194.49</v>
+        <v>2358.3</v>
       </c>
       <c r="D4" t="n">
-        <v>190.41</v>
+        <v>2241.2</v>
       </c>
       <c r="E4" t="n">
-        <v>191.1</v>
+        <v>2357.5</v>
       </c>
       <c r="F4" t="n">
-        <v>11769673</v>
+        <v>1124725</v>
       </c>
       <c r="G4" t="n">
-        <v>27946986</v>
+        <v>2438152</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5788571619136318</v>
+        <v>-0.5386977514117249</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>HDFCAMC</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>GMRAIRPORT</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1828.4</v>
+        <v>88.36</v>
       </c>
       <c r="C5" t="n">
-        <v>1845.6</v>
+        <v>89.17</v>
       </c>
       <c r="D5" t="n">
-        <v>1762.5</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>1793</v>
+        <v>88.98999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>1132054</v>
+        <v>8419680</v>
       </c>
       <c r="G5" t="n">
-        <v>2274502</v>
+        <v>18020403</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5022848957705907</v>
+        <v>-0.5327696056519935</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>GMRAIRPORT</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4640</v>
+        <v>425</v>
       </c>
       <c r="C6" t="n">
-        <v>4670.2</v>
+        <v>428.65</v>
       </c>
       <c r="D6" t="n">
-        <v>4544.2</v>
+        <v>415.55</v>
       </c>
       <c r="E6" t="n">
-        <v>4618</v>
+        <v>426.1</v>
       </c>
       <c r="F6" t="n">
-        <v>598276</v>
+        <v>1423697</v>
       </c>
       <c r="G6" t="n">
-        <v>1251680</v>
+        <v>2796488</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5220216029656142</v>
+        <v>-0.4908982266328338</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>NUVAMA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>673</v>
+        <v>1124.9</v>
       </c>
       <c r="C7" t="n">
-        <v>690.25</v>
+        <v>1149.4</v>
       </c>
       <c r="D7" t="n">
-        <v>672.4</v>
+        <v>1109.5</v>
       </c>
       <c r="E7" t="n">
-        <v>679.5</v>
+        <v>1140</v>
       </c>
       <c r="F7" t="n">
-        <v>2316056</v>
+        <v>364291</v>
       </c>
       <c r="G7" t="n">
-        <v>4829822</v>
+        <v>820494</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5204676279995412</v>
+        <v>-0.5560101597330389</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>SUZLON</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>41.39</v>
-      </c>
-      <c r="C8" t="n">
-        <v>41.59</v>
-      </c>
-      <c r="D8" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="E8" t="n">
-        <v>41.19</v>
-      </c>
-      <c r="F8" t="n">
-        <v>58512083</v>
-      </c>
-      <c r="G8" t="n">
-        <v>126591848</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-0.5377894870450109</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>SUZLON</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>AUBANK</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>859.65</v>
-      </c>
-      <c r="C9" t="n">
-        <v>884.8</v>
-      </c>
-      <c r="D9" t="n">
-        <v>859.65</v>
-      </c>
-      <c r="E9" t="n">
-        <v>873.85</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2150156</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4276408</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-0.4972051310352053</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>AUBANK</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>ICICIGI</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1735</v>
-      </c>
-      <c r="C10" t="n">
-        <v>1754.9</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1689</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1695.9</v>
-      </c>
-      <c r="F10" t="n">
-        <v>952924</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2042303</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-0.5334071389015244</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>ICICIGI</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>UPL</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>573</v>
-      </c>
-      <c r="C11" t="n">
-        <v>601.85</v>
-      </c>
-      <c r="D11" t="n">
-        <v>573</v>
-      </c>
-      <c r="E11" t="n">
-        <v>598.2</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2182769</v>
-      </c>
-      <c r="G11" t="n">
-        <v>5317081</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-0.589479829252178</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>UPL</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>LICI</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>745</v>
-      </c>
-      <c r="C12" t="n">
-        <v>758.05</v>
-      </c>
-      <c r="D12" t="n">
-        <v>736.55</v>
-      </c>
-      <c r="E12" t="n">
-        <v>747.6</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1461768</v>
-      </c>
-      <c r="G12" t="n">
-        <v>3174107</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-0.5394711016358301</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>LICI</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>JSWENERGY</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>477.5</v>
-      </c>
-      <c r="C13" t="n">
-        <v>490</v>
-      </c>
-      <c r="D13" t="n">
-        <v>477.5</v>
-      </c>
-      <c r="E13" t="n">
-        <v>484.35</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2188358</v>
-      </c>
-      <c r="G13" t="n">
-        <v>4311729</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-0.4924639280437152</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>JSWENERGY</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>COLPAL</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1822</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1845</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1810.3</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1831.8</v>
-      </c>
-      <c r="F14" t="n">
-        <v>407513</v>
-      </c>
-      <c r="G14" t="n">
-        <v>907544</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-0.5509716333312765</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>COLPAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>PATANJALI</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>473.8</v>
-      </c>
-      <c r="C15" t="n">
-        <v>478</v>
-      </c>
-      <c r="D15" t="n">
-        <v>465.2</v>
-      </c>
-      <c r="E15" t="n">
-        <v>469.85</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1460492</v>
-      </c>
-      <c r="G15" t="n">
-        <v>3158842</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-0.5376495563880688</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>PATANJALI</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>PAGEIND</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>32305</v>
-      </c>
-      <c r="C16" t="n">
-        <v>32820</v>
-      </c>
-      <c r="D16" t="n">
-        <v>32000</v>
-      </c>
-      <c r="E16" t="n">
-        <v>32795</v>
-      </c>
-      <c r="F16" t="n">
-        <v>18816</v>
-      </c>
-      <c r="G16" t="n">
-        <v>41114</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-0.5423456730067617</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>PAGEIND</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>360ONE</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>966.05</v>
-      </c>
-      <c r="C17" t="n">
-        <v>982.7</v>
-      </c>
-      <c r="D17" t="n">
-        <v>950</v>
-      </c>
-      <c r="E17" t="n">
-        <v>955</v>
-      </c>
-      <c r="F17" t="n">
-        <v>610228</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1347427</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-0.5471160960853538</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>360ONE</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>SONACOMS</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>492</v>
-      </c>
-      <c r="C18" t="n">
-        <v>507.8</v>
-      </c>
-      <c r="D18" t="n">
-        <v>492</v>
-      </c>
-      <c r="E18" t="n">
-        <v>497.4</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1772619</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3529118</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-0.4977161432403224</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>SONACOMS</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>TATATECH</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>519</v>
-      </c>
-      <c r="C19" t="n">
-        <v>539.2</v>
-      </c>
-      <c r="D19" t="n">
-        <v>519</v>
-      </c>
-      <c r="E19" t="n">
-        <v>531.2</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1067785</v>
-      </c>
-      <c r="G19" t="n">
-        <v>2327922</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-0.5413140990119085</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>TATATECH</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>SYNGENE</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>395.05</v>
-      </c>
-      <c r="C20" t="n">
-        <v>404.5</v>
-      </c>
-      <c r="D20" t="n">
-        <v>390.45</v>
-      </c>
-      <c r="E20" t="n">
-        <v>395</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1377179</v>
-      </c>
-      <c r="G20" t="n">
-        <v>3055190</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-0.5492329445959171</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>SYNGENE</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>KFINTECH</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>914</v>
-      </c>
-      <c r="C21" t="n">
-        <v>920.7</v>
-      </c>
-      <c r="D21" t="n">
-        <v>897</v>
-      </c>
-      <c r="E21" t="n">
-        <v>903</v>
-      </c>
-      <c r="F21" t="n">
-        <v>461461</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1139443</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-0.5950117732962509</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>KFINTECH</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>NCC</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>135</v>
-      </c>
-      <c r="C22" t="n">
-        <v>139.8</v>
-      </c>
-      <c r="D22" t="n">
-        <v>134.5</v>
-      </c>
-      <c r="E22" t="n">
-        <v>138.9</v>
-      </c>
-      <c r="F22" t="n">
-        <v>2543175</v>
-      </c>
-      <c r="G22" t="n">
-        <v>5402525</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-0.5292617803712153</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>NCC</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>PPLPHARMA</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>140</v>
-      </c>
-      <c r="C23" t="n">
-        <v>144.18</v>
-      </c>
-      <c r="D23" t="n">
-        <v>139.62</v>
-      </c>
-      <c r="E23" t="n">
-        <v>142.5</v>
-      </c>
-      <c r="F23" t="n">
-        <v>2094474</v>
-      </c>
-      <c r="G23" t="n">
-        <v>4589871</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-0.543674756872252</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>PPLPHARMA</t>
+          <t>NUVAMA</t>
         </is>
       </c>
     </row>
@@ -1213,7 +685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1266,198 +738,363 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>600</v>
+        <v>1357</v>
       </c>
       <c r="C2" t="n">
-        <v>606.15</v>
+        <v>1358.2</v>
       </c>
       <c r="D2" t="n">
-        <v>569</v>
+        <v>1328</v>
       </c>
       <c r="E2" t="n">
-        <v>572.15</v>
+        <v>1350.9</v>
       </c>
       <c r="F2" t="n">
-        <v>9823726</v>
+        <v>21280051</v>
       </c>
       <c r="G2" t="n">
-        <v>6294260</v>
+        <v>14404619</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5607435981354441</v>
+        <v>0.4773074525608765</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>RELIANCE</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4075</v>
+        <v>1260</v>
       </c>
       <c r="C3" t="n">
-        <v>4294.8</v>
+        <v>1305.4</v>
       </c>
       <c r="D3" t="n">
-        <v>4066.1</v>
+        <v>1259.8</v>
       </c>
       <c r="E3" t="n">
-        <v>4263.3</v>
+        <v>1297.5</v>
       </c>
       <c r="F3" t="n">
-        <v>2710202</v>
+        <v>12873492</v>
       </c>
       <c r="G3" t="n">
-        <v>1738503</v>
+        <v>8137156</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5589285724557277</v>
+        <v>0.5820628239153827</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>INFY</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1020.1</v>
+        <v>1174.6</v>
       </c>
       <c r="C4" t="n">
-        <v>1044.4</v>
+        <v>1202.3</v>
       </c>
       <c r="D4" t="n">
-        <v>1017.55</v>
+        <v>1150.3</v>
       </c>
       <c r="E4" t="n">
-        <v>1042</v>
+        <v>1198.1</v>
       </c>
       <c r="F4" t="n">
-        <v>2351992</v>
+        <v>9501543</v>
       </c>
       <c r="G4" t="n">
-        <v>1517014</v>
+        <v>6595695</v>
       </c>
       <c r="H4" t="n">
-        <v>0.550408895369456</v>
+        <v>0.4405673700800295</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>AXISBANK</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2016</v>
+        <v>1187.5</v>
       </c>
       <c r="C5" t="n">
-        <v>2049.8</v>
+        <v>1222.6</v>
       </c>
       <c r="D5" t="n">
-        <v>1973.5</v>
+        <v>1167.5</v>
       </c>
       <c r="E5" t="n">
-        <v>2004</v>
+        <v>1214</v>
       </c>
       <c r="F5" t="n">
-        <v>961650</v>
+        <v>3560727</v>
       </c>
       <c r="G5" t="n">
-        <v>609779</v>
+        <v>2240507</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5770467661234644</v>
+        <v>0.5892505580210193</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>DRREDDY</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KAYNES</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3629.5</v>
+        <v>2185</v>
       </c>
       <c r="C6" t="n">
-        <v>3674.8</v>
+        <v>2185.1</v>
       </c>
       <c r="D6" t="n">
-        <v>3520.8</v>
+        <v>2142.4</v>
       </c>
       <c r="E6" t="n">
-        <v>3538</v>
+        <v>2170.4</v>
       </c>
       <c r="F6" t="n">
-        <v>2072395</v>
+        <v>1854061</v>
       </c>
       <c r="G6" t="n">
-        <v>1304022</v>
+        <v>1209900</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5892331571093126</v>
+        <v>0.532408463509381</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>KAYNES</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CESC</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>153.49</v>
+        <v>1190</v>
       </c>
       <c r="C7" t="n">
-        <v>154.9</v>
+        <v>1196.6</v>
       </c>
       <c r="D7" t="n">
-        <v>150.92</v>
+        <v>1165.7</v>
       </c>
       <c r="E7" t="n">
-        <v>153.45</v>
+        <v>1195</v>
       </c>
       <c r="F7" t="n">
-        <v>2218241</v>
+        <v>3128666</v>
       </c>
       <c r="G7" t="n">
-        <v>1452067</v>
+        <v>2180444</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5276436968817555</v>
+        <v>0.4348756491797083</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CESC</t>
+          <t>CIPLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1390</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1447</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1383.5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1439</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2501510</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1624500</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.5398645737149892</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>WIPRO</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>190.5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>195.34</v>
+      </c>
+      <c r="D9" t="n">
+        <v>188.58</v>
+      </c>
+      <c r="E9" t="n">
+        <v>194.8</v>
+      </c>
+      <c r="F9" t="n">
+        <v>16623045</v>
+      </c>
+      <c r="G9" t="n">
+        <v>11769673</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.4123625184828839</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>WIPRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>378.85</v>
+      </c>
+      <c r="C10" t="n">
+        <v>386.65</v>
+      </c>
+      <c r="D10" t="n">
+        <v>368</v>
+      </c>
+      <c r="E10" t="n">
+        <v>382.5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>9543544</v>
+      </c>
+      <c r="G10" t="n">
+        <v>6063436</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.5739498198711094</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>4970.1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5267</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4963.9</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5225.9</v>
+      </c>
+      <c r="F11" t="n">
+        <v>964640</v>
+      </c>
+      <c r="G11" t="n">
+        <v>686833</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.404475323695862</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>POONAWALLA</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>379.7</v>
+      </c>
+      <c r="C12" t="n">
+        <v>395.9</v>
+      </c>
+      <c r="D12" t="n">
+        <v>366.7</v>
+      </c>
+      <c r="E12" t="n">
+        <v>391</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1026499</v>
+      </c>
+      <c r="G12" t="n">
+        <v>663831</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.5463257967765892</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>POONAWALLA</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,6 +473,303 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>filterdata</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1213</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1234.4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1200.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1228.6</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10058414</v>
+      </c>
+      <c r="G2" t="n">
+        <v>20851722</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-0.5176219019225367</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>232.8</v>
+      </c>
+      <c r="C3" t="n">
+        <v>234.8</v>
+      </c>
+      <c r="D3" t="n">
+        <v>228.02</v>
+      </c>
+      <c r="E3" t="n">
+        <v>232.09</v>
+      </c>
+      <c r="F3" t="n">
+        <v>31590365</v>
+      </c>
+      <c r="G3" t="n">
+        <v>66556155</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-0.5253577223624171</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2474</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2482</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2448.2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2472</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2572417</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5378361</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.5217098666303731</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1213.4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1227.9</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1217</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2994825</v>
+      </c>
+      <c r="G5" t="n">
+        <v>6403645</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.5323249493062154</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5019.5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>5122.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4985.5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5108</v>
+      </c>
+      <c r="F6" t="n">
+        <v>348536</v>
+      </c>
+      <c r="G6" t="n">
+        <v>753867</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.5376691113949809</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>VOLTAS</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1225</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1256.6</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1204.1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1253.9</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1213038</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2452341</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.50535508724113</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>VOLTAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>KEI</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4058.2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4150.9</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4009.3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4125.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>257078</v>
+      </c>
+      <c r="G8" t="n">
+        <v>559572</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.5405810154904105</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>KEI</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SUPREMEIND</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3649.2</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3723.3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3516</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3695.8</v>
+      </c>
+      <c r="F9" t="n">
+        <v>224359</v>
+      </c>
+      <c r="G9" t="n">
+        <v>494260</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.5460708938615304</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>SUPREMEIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CYIENT</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>804.8</v>
+      </c>
+      <c r="C10" t="n">
+        <v>817.05</v>
+      </c>
+      <c r="D10" t="n">
+        <v>796.2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>812.9</v>
+      </c>
+      <c r="F10" t="n">
+        <v>169371</v>
+      </c>
+      <c r="G10" t="n">
+        <v>396748</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.5731018177785395</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>CYIENT</t>
         </is>
       </c>
     </row>
@@ -487,7 +784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,6 +834,435 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>6699</v>
+      </c>
+      <c r="C2" t="n">
+        <v>6710.5</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6572.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>6592</v>
+      </c>
+      <c r="F2" t="n">
+        <v>971230</v>
+      </c>
+      <c r="G2" t="n">
+        <v>660432</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.4705980328027715</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>WIPRO</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>197</v>
+      </c>
+      <c r="C3" t="n">
+        <v>201.18</v>
+      </c>
+      <c r="D3" t="n">
+        <v>196.11</v>
+      </c>
+      <c r="E3" t="n">
+        <v>197.7</v>
+      </c>
+      <c r="F3" t="n">
+        <v>23282287</v>
+      </c>
+      <c r="G3" t="n">
+        <v>16623045</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.4006030182797436</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>WIPRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>JSWSTEEL</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1132</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1145.7</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1115.1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1132.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3213623</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2208479</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.4551295257958079</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>JSWSTEEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BANKBARODA</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>252.61</v>
+      </c>
+      <c r="C5" t="n">
+        <v>260.69</v>
+      </c>
+      <c r="D5" t="n">
+        <v>251.91</v>
+      </c>
+      <c r="E5" t="n">
+        <v>260.5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>22152306</v>
+      </c>
+      <c r="G5" t="n">
+        <v>14887386</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.4879916460821262</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>BANKBARODA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>LODHA</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>696.05</v>
+      </c>
+      <c r="C6" t="n">
+        <v>715.8</v>
+      </c>
+      <c r="D6" t="n">
+        <v>686.65</v>
+      </c>
+      <c r="E6" t="n">
+        <v>713.65</v>
+      </c>
+      <c r="F6" t="n">
+        <v>7760768</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4877982</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.5909792205055288</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>LODHA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SIEMENS</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3041.4</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3065.9</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2965.1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3060</v>
+      </c>
+      <c r="F7" t="n">
+        <v>372908</v>
+      </c>
+      <c r="G7" t="n">
+        <v>265901</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.4024317321108232</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>SIEMENS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SHREECEM</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>23460</v>
+      </c>
+      <c r="C8" t="n">
+        <v>24015</v>
+      </c>
+      <c r="D8" t="n">
+        <v>22980</v>
+      </c>
+      <c r="E8" t="n">
+        <v>23580</v>
+      </c>
+      <c r="F8" t="n">
+        <v>31374</v>
+      </c>
+      <c r="G8" t="n">
+        <v>20490</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.531185944363104</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>SHREECEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1002</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1032.05</v>
+      </c>
+      <c r="D9" t="n">
+        <v>977</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1027</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3280196</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2181909</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.5033605892821378</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SRF</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2425</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2443.6</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2355</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2434.4</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1106561</v>
+      </c>
+      <c r="G10" t="n">
+        <v>715256</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.5470838413099646</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>SRF</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>60.51</v>
+      </c>
+      <c r="C11" t="n">
+        <v>61.29</v>
+      </c>
+      <c r="D11" t="n">
+        <v>59.17</v>
+      </c>
+      <c r="E11" t="n">
+        <v>61.24</v>
+      </c>
+      <c r="F11" t="n">
+        <v>41063566</v>
+      </c>
+      <c r="G11" t="n">
+        <v>25908484</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.5849466915933792</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>BANKINDIA</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>140.38</v>
+      </c>
+      <c r="C12" t="n">
+        <v>145.49</v>
+      </c>
+      <c r="D12" t="n">
+        <v>137.88</v>
+      </c>
+      <c r="E12" t="n">
+        <v>143.19</v>
+      </c>
+      <c r="F12" t="n">
+        <v>14321009</v>
+      </c>
+      <c r="G12" t="n">
+        <v>9218922</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.5534363996137509</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>BANKINDIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>876.85</v>
+      </c>
+      <c r="C13" t="n">
+        <v>904.65</v>
+      </c>
+      <c r="D13" t="n">
+        <v>864.25</v>
+      </c>
+      <c r="E13" t="n">
+        <v>901</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2261012</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1607041</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.4069410799102201</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NCC</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>141.99</v>
+      </c>
+      <c r="C14" t="n">
+        <v>143.29</v>
+      </c>
+      <c r="D14" t="n">
+        <v>139.23</v>
+      </c>
+      <c r="E14" t="n">
+        <v>142.7</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2823160</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1766761</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.5979297709197792</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>NCC</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,297 +479,330 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1213</v>
+        <v>3818.2</v>
       </c>
       <c r="C2" t="n">
-        <v>1234.4</v>
+        <v>3898.8</v>
       </c>
       <c r="D2" t="n">
-        <v>1200.5</v>
+        <v>3776.3</v>
       </c>
       <c r="E2" t="n">
-        <v>1228.6</v>
+        <v>3815</v>
       </c>
       <c r="F2" t="n">
-        <v>10058414</v>
+        <v>1992402</v>
       </c>
       <c r="G2" t="n">
-        <v>20851722</v>
+        <v>4877807</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5176219019225367</v>
+        <v>-0.5915373445484825</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>TRENT</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>232.8</v>
+        <v>1890</v>
       </c>
       <c r="C3" t="n">
-        <v>234.8</v>
+        <v>1904.6</v>
       </c>
       <c r="D3" t="n">
-        <v>228.02</v>
+        <v>1865</v>
       </c>
       <c r="E3" t="n">
-        <v>232.09</v>
+        <v>1884</v>
       </c>
       <c r="F3" t="n">
-        <v>31590365</v>
+        <v>1566909</v>
       </c>
       <c r="G3" t="n">
-        <v>66556155</v>
+        <v>3153437</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5253577223624171</v>
+        <v>-0.5031107328289736</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>ADANIENT</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>BANKBARODA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2474</v>
+        <v>257.99</v>
       </c>
       <c r="C4" t="n">
-        <v>2482</v>
+        <v>259</v>
       </c>
       <c r="D4" t="n">
-        <v>2448.2</v>
+        <v>254.82</v>
       </c>
       <c r="E4" t="n">
-        <v>2472</v>
+        <v>258</v>
       </c>
       <c r="F4" t="n">
-        <v>2572417</v>
+        <v>9211553</v>
       </c>
       <c r="G4" t="n">
-        <v>5378361</v>
+        <v>22152306</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5217098666303731</v>
+        <v>-0.5841718239175642</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>BANKBARODA</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1213.4</v>
+        <v>3053.4</v>
       </c>
       <c r="C5" t="n">
-        <v>1227.9</v>
+        <v>3084</v>
       </c>
       <c r="D5" t="n">
-        <v>1200</v>
+        <v>2992.8</v>
       </c>
       <c r="E5" t="n">
-        <v>1217</v>
+        <v>3080</v>
       </c>
       <c r="F5" t="n">
-        <v>2994825</v>
+        <v>184684</v>
       </c>
       <c r="G5" t="n">
-        <v>6403645</v>
+        <v>372908</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5323249493062154</v>
+        <v>-0.504746479024317</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>SIEMENS</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>LTF</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5019.5</v>
+        <v>252.5</v>
       </c>
       <c r="C6" t="n">
-        <v>5122.5</v>
+        <v>257.31</v>
       </c>
       <c r="D6" t="n">
-        <v>4985.5</v>
+        <v>250.7</v>
       </c>
       <c r="E6" t="n">
-        <v>5108</v>
+        <v>254.49</v>
       </c>
       <c r="F6" t="n">
-        <v>348536</v>
+        <v>5784978</v>
       </c>
       <c r="G6" t="n">
-        <v>753867</v>
+        <v>11678955</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5376691113949809</v>
+        <v>-0.5046664705874798</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>LTF</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VOLTAS</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1225</v>
+        <v>1564.2</v>
       </c>
       <c r="C7" t="n">
-        <v>1256.6</v>
+        <v>1611.8</v>
       </c>
       <c r="D7" t="n">
-        <v>1204.1</v>
+        <v>1545.9</v>
       </c>
       <c r="E7" t="n">
-        <v>1253.9</v>
+        <v>1601.1</v>
       </c>
       <c r="F7" t="n">
-        <v>1213038</v>
+        <v>893011</v>
       </c>
       <c r="G7" t="n">
-        <v>2452341</v>
+        <v>2223294</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.50535508724113</v>
+        <v>-0.5983387712106452</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>VOLTAS</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KEI</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4058.2</v>
+        <v>778</v>
       </c>
       <c r="C8" t="n">
-        <v>4150.9</v>
+        <v>787.8</v>
       </c>
       <c r="D8" t="n">
-        <v>4009.3</v>
+        <v>770.3</v>
       </c>
       <c r="E8" t="n">
-        <v>4125.5</v>
+        <v>783</v>
       </c>
       <c r="F8" t="n">
-        <v>257078</v>
+        <v>1165539</v>
       </c>
       <c r="G8" t="n">
-        <v>559572</v>
+        <v>2512596</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5405810154904105</v>
+        <v>-0.5361216049058424</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>KEI</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SUPREMEIND</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3649.2</v>
+        <v>1367</v>
       </c>
       <c r="C9" t="n">
-        <v>3723.3</v>
+        <v>1403.3</v>
       </c>
       <c r="D9" t="n">
-        <v>3516</v>
+        <v>1362.3</v>
       </c>
       <c r="E9" t="n">
-        <v>3695.8</v>
+        <v>1400</v>
       </c>
       <c r="F9" t="n">
-        <v>224359</v>
+        <v>258766</v>
       </c>
       <c r="G9" t="n">
-        <v>494260</v>
+        <v>546934</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5460708938615304</v>
+        <v>-0.5268789287190044</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SUPREMEIND</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CYIENT</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>804.8</v>
+        <v>814.05</v>
       </c>
       <c r="C10" t="n">
-        <v>817.05</v>
+        <v>820.15</v>
       </c>
       <c r="D10" t="n">
-        <v>796.2</v>
+        <v>804.7</v>
       </c>
       <c r="E10" t="n">
-        <v>812.9</v>
+        <v>813.6</v>
       </c>
       <c r="F10" t="n">
-        <v>169371</v>
+        <v>421808</v>
       </c>
       <c r="G10" t="n">
-        <v>396748</v>
+        <v>832589</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5731018177785395</v>
+        <v>-0.4933778851269954</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>CYIENT</t>
+          <t>PNBHOUSING</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>IRB</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20.67</v>
+      </c>
+      <c r="C11" t="n">
+        <v>20.94</v>
+      </c>
+      <c r="D11" t="n">
+        <v>20.46</v>
+      </c>
+      <c r="E11" t="n">
+        <v>20.52</v>
+      </c>
+      <c r="F11" t="n">
+        <v>15352433</v>
+      </c>
+      <c r="G11" t="n">
+        <v>34751539</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.5582229322275483</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>IRB</t>
         </is>
       </c>
     </row>
@@ -784,7 +817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -837,429 +870,297 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6699</v>
+        <v>1302</v>
       </c>
       <c r="C2" t="n">
-        <v>6710.5</v>
+        <v>1345.1</v>
       </c>
       <c r="D2" t="n">
-        <v>6572.5</v>
+        <v>1293.5</v>
       </c>
       <c r="E2" t="n">
-        <v>6592</v>
+        <v>1340</v>
       </c>
       <c r="F2" t="n">
-        <v>971230</v>
+        <v>15355792</v>
       </c>
       <c r="G2" t="n">
-        <v>660432</v>
+        <v>10208682</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4705980328027715</v>
+        <v>0.5041894732346448</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>INFY</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>197</v>
+        <v>294.15</v>
       </c>
       <c r="C3" t="n">
-        <v>201.18</v>
+        <v>299</v>
       </c>
       <c r="D3" t="n">
-        <v>196.11</v>
+        <v>292.75</v>
       </c>
       <c r="E3" t="n">
-        <v>197.7</v>
+        <v>298.65</v>
       </c>
       <c r="F3" t="n">
-        <v>23282287</v>
+        <v>26963485</v>
       </c>
       <c r="G3" t="n">
-        <v>16623045</v>
+        <v>18047063</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4006030182797436</v>
+        <v>0.4940649899654032</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>ITC</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>KEI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1132</v>
+        <v>4137</v>
       </c>
       <c r="C4" t="n">
-        <v>1145.7</v>
+        <v>4246</v>
       </c>
       <c r="D4" t="n">
-        <v>1115.1</v>
+        <v>4031</v>
       </c>
       <c r="E4" t="n">
-        <v>1132.5</v>
+        <v>4240</v>
       </c>
       <c r="F4" t="n">
-        <v>3213623</v>
+        <v>400852</v>
       </c>
       <c r="G4" t="n">
-        <v>2208479</v>
+        <v>257078</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4551295257958079</v>
+        <v>0.5592621694582967</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>KEI</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>HAVELLS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>252.61</v>
+        <v>1200</v>
       </c>
       <c r="C5" t="n">
-        <v>260.69</v>
+        <v>1236.7</v>
       </c>
       <c r="D5" t="n">
-        <v>251.91</v>
+        <v>1186.3</v>
       </c>
       <c r="E5" t="n">
-        <v>260.5</v>
+        <v>1230.1</v>
       </c>
       <c r="F5" t="n">
-        <v>22152306</v>
+        <v>1033027</v>
       </c>
       <c r="G5" t="n">
-        <v>14887386</v>
+        <v>693409</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4879916460821262</v>
+        <v>0.4897802018721995</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>HAVELLS</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LODHA</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>696.05</v>
+        <v>6988.5</v>
       </c>
       <c r="C6" t="n">
-        <v>715.8</v>
+        <v>7210</v>
       </c>
       <c r="D6" t="n">
-        <v>686.65</v>
+        <v>6943</v>
       </c>
       <c r="E6" t="n">
-        <v>713.65</v>
+        <v>7196</v>
       </c>
       <c r="F6" t="n">
-        <v>7760768</v>
+        <v>153224</v>
       </c>
       <c r="G6" t="n">
-        <v>4877982</v>
+        <v>97867</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5909792205055288</v>
+        <v>0.5656349944312179</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>LODHA</t>
+          <t>OFSS</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3041.4</v>
+        <v>1912</v>
       </c>
       <c r="C7" t="n">
-        <v>3065.9</v>
+        <v>1912.1</v>
       </c>
       <c r="D7" t="n">
-        <v>2965.1</v>
+        <v>1859.6</v>
       </c>
       <c r="E7" t="n">
-        <v>3060</v>
+        <v>1896.9</v>
       </c>
       <c r="F7" t="n">
-        <v>372908</v>
+        <v>552064</v>
       </c>
       <c r="G7" t="n">
-        <v>265901</v>
+        <v>364128</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4024317321108232</v>
+        <v>0.5161261973811407</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23460</v>
+        <v>1037.4</v>
       </c>
       <c r="C8" t="n">
-        <v>24015</v>
+        <v>1053.7</v>
       </c>
       <c r="D8" t="n">
-        <v>22980</v>
+        <v>1013.9</v>
       </c>
       <c r="E8" t="n">
-        <v>23580</v>
+        <v>1021</v>
       </c>
       <c r="F8" t="n">
-        <v>31374</v>
+        <v>990099</v>
       </c>
       <c r="G8" t="n">
-        <v>20490</v>
+        <v>619772</v>
       </c>
       <c r="H8" t="n">
-        <v>0.531185944363104</v>
+        <v>0.5975213465597026</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PAYTM</t>
+          <t>UPL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1002</v>
+        <v>607.5</v>
       </c>
       <c r="C9" t="n">
-        <v>1032.05</v>
+        <v>610.75</v>
       </c>
       <c r="D9" t="n">
-        <v>977</v>
+        <v>600.1</v>
       </c>
       <c r="E9" t="n">
-        <v>1027</v>
+        <v>608</v>
       </c>
       <c r="F9" t="n">
-        <v>3280196</v>
+        <v>1533818</v>
       </c>
       <c r="G9" t="n">
-        <v>2181909</v>
+        <v>1075781</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5033605892821378</v>
+        <v>0.425771602212718</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>PAYTM</t>
+          <t>UPL</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SRF</t>
+          <t>SONACOMS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2425</v>
+        <v>509.9</v>
       </c>
       <c r="C10" t="n">
-        <v>2443.6</v>
+        <v>517</v>
       </c>
       <c r="D10" t="n">
-        <v>2355</v>
+        <v>498.85</v>
       </c>
       <c r="E10" t="n">
-        <v>2434.4</v>
+        <v>515.8</v>
       </c>
       <c r="F10" t="n">
-        <v>1106561</v>
+        <v>1373705</v>
       </c>
       <c r="G10" t="n">
-        <v>715256</v>
+        <v>967766</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5470838413099646</v>
+        <v>0.4194598694312468</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SRF</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>IDFCFIRSTB</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>60.51</v>
-      </c>
-      <c r="C11" t="n">
-        <v>61.29</v>
-      </c>
-      <c r="D11" t="n">
-        <v>59.17</v>
-      </c>
-      <c r="E11" t="n">
-        <v>61.24</v>
-      </c>
-      <c r="F11" t="n">
-        <v>41063566</v>
-      </c>
-      <c r="G11" t="n">
-        <v>25908484</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.5849466915933792</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>IDFCFIRSTB</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>BANKINDIA</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>140.38</v>
-      </c>
-      <c r="C12" t="n">
-        <v>145.49</v>
-      </c>
-      <c r="D12" t="n">
-        <v>137.88</v>
-      </c>
-      <c r="E12" t="n">
-        <v>143.19</v>
-      </c>
-      <c r="F12" t="n">
-        <v>14321009</v>
-      </c>
-      <c r="G12" t="n">
-        <v>9218922</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.5534363996137509</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>BANKINDIA</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>INDIANB</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>876.85</v>
-      </c>
-      <c r="C13" t="n">
-        <v>904.65</v>
-      </c>
-      <c r="D13" t="n">
-        <v>864.25</v>
-      </c>
-      <c r="E13" t="n">
-        <v>901</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2261012</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1607041</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.4069410799102201</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>INDIANB</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>NCC</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>141.99</v>
-      </c>
-      <c r="C14" t="n">
-        <v>143.29</v>
-      </c>
-      <c r="D14" t="n">
-        <v>139.23</v>
-      </c>
-      <c r="E14" t="n">
-        <v>142.7</v>
-      </c>
-      <c r="F14" t="n">
-        <v>2823160</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1766761</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.5979297709197792</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>NCC</t>
+          <t>SONACOMS</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,330 +479,33 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>JUBLFOOD</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3818.2</v>
+        <v>429.8</v>
       </c>
       <c r="C2" t="n">
-        <v>3898.8</v>
+        <v>443.3</v>
       </c>
       <c r="D2" t="n">
-        <v>3776.3</v>
+        <v>423.6</v>
       </c>
       <c r="E2" t="n">
-        <v>3815</v>
+        <v>435.5</v>
       </c>
       <c r="F2" t="n">
-        <v>1992402</v>
+        <v>12865710</v>
       </c>
       <c r="G2" t="n">
-        <v>4877807</v>
+        <v>26718173</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5915373445484825</v>
+        <v>-0.5184659519945469</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>TRENT</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ADANIENT</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1890</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1904.6</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1865</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1884</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1566909</v>
-      </c>
-      <c r="G3" t="n">
-        <v>3153437</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-0.5031107328289736</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>ADANIENT</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>BANKBARODA</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>257.99</v>
-      </c>
-      <c r="C4" t="n">
-        <v>259</v>
-      </c>
-      <c r="D4" t="n">
-        <v>254.82</v>
-      </c>
-      <c r="E4" t="n">
-        <v>258</v>
-      </c>
-      <c r="F4" t="n">
-        <v>9211553</v>
-      </c>
-      <c r="G4" t="n">
-        <v>22152306</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-0.5841718239175642</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>BANKBARODA</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>SIEMENS</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3053.4</v>
-      </c>
-      <c r="C5" t="n">
-        <v>3084</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2992.8</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3080</v>
-      </c>
-      <c r="F5" t="n">
-        <v>184684</v>
-      </c>
-      <c r="G5" t="n">
-        <v>372908</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-0.504746479024317</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>SIEMENS</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>LTF</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>252.5</v>
-      </c>
-      <c r="C6" t="n">
-        <v>257.31</v>
-      </c>
-      <c r="D6" t="n">
-        <v>250.7</v>
-      </c>
-      <c r="E6" t="n">
-        <v>254.49</v>
-      </c>
-      <c r="F6" t="n">
-        <v>5784978</v>
-      </c>
-      <c r="G6" t="n">
-        <v>11678955</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-0.5046664705874798</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>LTF</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>GODREJPROP</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1564.2</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1611.8</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1545.9</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1601.1</v>
-      </c>
-      <c r="F7" t="n">
-        <v>893011</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2223294</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-0.5983387712106452</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>GODREJPROP</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>INDUSINDBK</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>778</v>
-      </c>
-      <c r="C8" t="n">
-        <v>787.8</v>
-      </c>
-      <c r="D8" t="n">
-        <v>770.3</v>
-      </c>
-      <c r="E8" t="n">
-        <v>783</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1165539</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2512596</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-0.5361216049058424</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>INDUSINDBK</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>TORNTPOWER</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1367</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1403.3</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1362.3</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1400</v>
-      </c>
-      <c r="F9" t="n">
-        <v>258766</v>
-      </c>
-      <c r="G9" t="n">
-        <v>546934</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-0.5268789287190044</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>TORNTPOWER</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>PNBHOUSING</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>814.05</v>
-      </c>
-      <c r="C10" t="n">
-        <v>820.15</v>
-      </c>
-      <c r="D10" t="n">
-        <v>804.7</v>
-      </c>
-      <c r="E10" t="n">
-        <v>813.6</v>
-      </c>
-      <c r="F10" t="n">
-        <v>421808</v>
-      </c>
-      <c r="G10" t="n">
-        <v>832589</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-0.4933778851269954</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>PNBHOUSING</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>IRB</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>20.67</v>
-      </c>
-      <c r="C11" t="n">
-        <v>20.94</v>
-      </c>
-      <c r="D11" t="n">
-        <v>20.46</v>
-      </c>
-      <c r="E11" t="n">
-        <v>20.52</v>
-      </c>
-      <c r="F11" t="n">
-        <v>15352433</v>
-      </c>
-      <c r="G11" t="n">
-        <v>34751539</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-0.5582229322275483</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>IRB</t>
+          <t>JUBLFOOD</t>
         </is>
       </c>
     </row>
@@ -817,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -870,297 +573,924 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1302</v>
+        <v>1300.1</v>
       </c>
       <c r="C2" t="n">
-        <v>1345.1</v>
+        <v>1335.6</v>
       </c>
       <c r="D2" t="n">
-        <v>1293.5</v>
+        <v>1300.1</v>
       </c>
       <c r="E2" t="n">
-        <v>1340</v>
+        <v>1333.4</v>
       </c>
       <c r="F2" t="n">
-        <v>15355792</v>
+        <v>13519723</v>
       </c>
       <c r="G2" t="n">
-        <v>10208682</v>
+        <v>9248545</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5041894732346448</v>
+        <v>0.4618216162650449</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>AXISBANK</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>294.15</v>
+        <v>243.55</v>
       </c>
       <c r="C3" t="n">
-        <v>299</v>
+        <v>246.92</v>
       </c>
       <c r="D3" t="n">
-        <v>292.75</v>
+        <v>241</v>
       </c>
       <c r="E3" t="n">
-        <v>298.65</v>
+        <v>244.4</v>
       </c>
       <c r="F3" t="n">
-        <v>26963485</v>
+        <v>61801744</v>
       </c>
       <c r="G3" t="n">
-        <v>18047063</v>
+        <v>40364387</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4940649899654032</v>
+        <v>0.5310958147339139</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>ETERNAL</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KEI</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4137</v>
+        <v>2130</v>
       </c>
       <c r="C4" t="n">
-        <v>4246</v>
+        <v>2192.8</v>
       </c>
       <c r="D4" t="n">
-        <v>4031</v>
+        <v>2130</v>
       </c>
       <c r="E4" t="n">
-        <v>4240</v>
+        <v>2145</v>
       </c>
       <c r="F4" t="n">
-        <v>400852</v>
+        <v>3794437</v>
       </c>
       <c r="G4" t="n">
-        <v>257078</v>
+        <v>2709707</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5592621694582967</v>
+        <v>0.4003126537297206</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>KEI</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1200</v>
+        <v>373.5</v>
       </c>
       <c r="C5" t="n">
-        <v>1236.7</v>
+        <v>375.55</v>
       </c>
       <c r="D5" t="n">
-        <v>1186.3</v>
+        <v>368.25</v>
       </c>
       <c r="E5" t="n">
-        <v>1230.1</v>
+        <v>373</v>
       </c>
       <c r="F5" t="n">
-        <v>1033027</v>
+        <v>19491331</v>
       </c>
       <c r="G5" t="n">
-        <v>693409</v>
+        <v>12603971</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4897802018721995</v>
+        <v>0.5464436565269787</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>NTPC</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>JIOFIN</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6988.5</v>
+        <v>245.1</v>
       </c>
       <c r="C6" t="n">
-        <v>7210</v>
+        <v>248.1</v>
       </c>
       <c r="D6" t="n">
-        <v>6943</v>
+        <v>242.15</v>
       </c>
       <c r="E6" t="n">
-        <v>7196</v>
+        <v>248</v>
       </c>
       <c r="F6" t="n">
-        <v>153224</v>
+        <v>19911975</v>
       </c>
       <c r="G6" t="n">
-        <v>97867</v>
+        <v>13783445</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5656349944312179</v>
+        <v>0.4446297714395784</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>JIOFIN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1912</v>
+        <v>1076</v>
       </c>
       <c r="C7" t="n">
-        <v>1912.1</v>
+        <v>1091.9</v>
       </c>
       <c r="D7" t="n">
-        <v>1859.6</v>
+        <v>1066</v>
       </c>
       <c r="E7" t="n">
-        <v>1896.9</v>
+        <v>1069</v>
       </c>
       <c r="F7" t="n">
-        <v>552064</v>
+        <v>1950233</v>
       </c>
       <c r="G7" t="n">
-        <v>364128</v>
+        <v>1342335</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5161261973811407</v>
+        <v>0.4528660878245743</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1037.4</v>
+        <v>621.5</v>
       </c>
       <c r="C8" t="n">
-        <v>1053.7</v>
+        <v>643.5</v>
       </c>
       <c r="D8" t="n">
-        <v>1013.9</v>
+        <v>621.5</v>
       </c>
       <c r="E8" t="n">
-        <v>1021</v>
+        <v>638.95</v>
       </c>
       <c r="F8" t="n">
-        <v>990099</v>
+        <v>3317869</v>
       </c>
       <c r="G8" t="n">
-        <v>619772</v>
+        <v>2169845</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5975213465597026</v>
+        <v>0.5290811094801703</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UPL</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>607.5</v>
+        <v>10572.5</v>
       </c>
       <c r="C9" t="n">
-        <v>610.75</v>
+        <v>10710</v>
       </c>
       <c r="D9" t="n">
-        <v>600.1</v>
+        <v>10430</v>
       </c>
       <c r="E9" t="n">
-        <v>608</v>
+        <v>10699</v>
       </c>
       <c r="F9" t="n">
-        <v>1533818</v>
+        <v>979189</v>
       </c>
       <c r="G9" t="n">
-        <v>1075781</v>
+        <v>624630</v>
       </c>
       <c r="H9" t="n">
-        <v>0.425771602212718</v>
+        <v>0.5676304372188336</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>UPL</t>
+          <t>DIXON</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SONACOMS</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>509.9</v>
+        <v>1716.5</v>
       </c>
       <c r="C10" t="n">
-        <v>517</v>
+        <v>1791.4</v>
       </c>
       <c r="D10" t="n">
-        <v>498.85</v>
+        <v>1716.5</v>
       </c>
       <c r="E10" t="n">
-        <v>515.8</v>
+        <v>1782.9</v>
       </c>
       <c r="F10" t="n">
-        <v>1373705</v>
+        <v>1961222</v>
       </c>
       <c r="G10" t="n">
-        <v>967766</v>
+        <v>1247449</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4194598694312468</v>
+        <v>0.5721861174284479</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SONACOMS</t>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>LTF</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>268</v>
+      </c>
+      <c r="C11" t="n">
+        <v>278.89</v>
+      </c>
+      <c r="D11" t="n">
+        <v>268</v>
+      </c>
+      <c r="E11" t="n">
+        <v>276.47</v>
+      </c>
+      <c r="F11" t="n">
+        <v>8622875</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5784978</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.4905631447518037</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>LTF</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>GODREJPROP</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1698</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1723</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1673.5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1705</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1332784</v>
+      </c>
+      <c r="G12" t="n">
+        <v>893011</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.4924608991378606</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>GODREJPROP</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MARICO</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>772</v>
+      </c>
+      <c r="C13" t="n">
+        <v>772</v>
+      </c>
+      <c r="D13" t="n">
+        <v>746.25</v>
+      </c>
+      <c r="E13" t="n">
+        <v>748.9</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2798459</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1819912</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.537689184971581</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MARICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>BDL</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1294.9</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1294.9</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1254</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1292.9</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1591207</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1062581</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.497492426459724</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>BDL</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>VOLTAS</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1250</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1278</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1246.4</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1265</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1548576</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1023903</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.5124245167755148</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>VOLTAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1974.7</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2055.1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1961.1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2050.6</v>
+      </c>
+      <c r="F16" t="n">
+        <v>811179</v>
+      </c>
+      <c r="G16" t="n">
+        <v>552064</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.4693568137027591</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1060</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1100.5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1050</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1090.1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1391634</v>
+      </c>
+      <c r="G17" t="n">
+        <v>990099</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.4055503540555035</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>GLENMARK</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2165</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2187</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2129.6</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2174.6</v>
+      </c>
+      <c r="F18" t="n">
+        <v>544557</v>
+      </c>
+      <c r="G18" t="n">
+        <v>387544</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.4051488347129616</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>GLENMARK</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>HUDCO</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>180</v>
+      </c>
+      <c r="C19" t="n">
+        <v>185.01</v>
+      </c>
+      <c r="D19" t="n">
+        <v>176.9</v>
+      </c>
+      <c r="E19" t="n">
+        <v>183.4</v>
+      </c>
+      <c r="F19" t="n">
+        <v>5212278</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3520596</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.480510118173173</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>HUDCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>COLPAL</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1885</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1915.8</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1869.6</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1907</v>
+      </c>
+      <c r="F20" t="n">
+        <v>453684</v>
+      </c>
+      <c r="G20" t="n">
+        <v>295165</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.5370521572679687</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>COLPAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TORNTPOWER</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1430</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1475</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1424.9</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1452.2</v>
+      </c>
+      <c r="F21" t="n">
+        <v>375842</v>
+      </c>
+      <c r="G21" t="n">
+        <v>258766</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.4524396559053353</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>TORNTPOWER</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ICICIPRULI</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>541</v>
+      </c>
+      <c r="C22" t="n">
+        <v>546.35</v>
+      </c>
+      <c r="D22" t="n">
+        <v>532.5</v>
+      </c>
+      <c r="E22" t="n">
+        <v>542</v>
+      </c>
+      <c r="F22" t="n">
+        <v>827961</v>
+      </c>
+      <c r="G22" t="n">
+        <v>584434</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.4166886252339871</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ICICIPRULI</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SJVN</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>69.94</v>
+      </c>
+      <c r="C23" t="n">
+        <v>70.75</v>
+      </c>
+      <c r="D23" t="n">
+        <v>69.11</v>
+      </c>
+      <c r="E23" t="n">
+        <v>70.70999999999999</v>
+      </c>
+      <c r="F23" t="n">
+        <v>6361101</v>
+      </c>
+      <c r="G23" t="n">
+        <v>4059061</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.5671360937911503</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>SJVN</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>471.1</v>
+      </c>
+      <c r="C24" t="n">
+        <v>493</v>
+      </c>
+      <c r="D24" t="n">
+        <v>462.3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>483.45</v>
+      </c>
+      <c r="F24" t="n">
+        <v>8706149</v>
+      </c>
+      <c r="G24" t="n">
+        <v>5549876</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.5687105441635092</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>DELHIVERY</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>452</v>
+      </c>
+      <c r="C25" t="n">
+        <v>465</v>
+      </c>
+      <c r="D25" t="n">
+        <v>449.15</v>
+      </c>
+      <c r="E25" t="n">
+        <v>457.8</v>
+      </c>
+      <c r="F25" t="n">
+        <v>4701999</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3268452</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.4386012093798532</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>DELHIVERY</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>KFINTECH</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>942</v>
+      </c>
+      <c r="C26" t="n">
+        <v>946.9</v>
+      </c>
+      <c r="D26" t="n">
+        <v>914</v>
+      </c>
+      <c r="E26" t="n">
+        <v>920.7</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2029678</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1420169</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.4291806116032669</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>KFINTECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>NBCC</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="C27" t="n">
+        <v>89.25</v>
+      </c>
+      <c r="D27" t="n">
+        <v>86.91</v>
+      </c>
+      <c r="E27" t="n">
+        <v>89</v>
+      </c>
+      <c r="F27" t="n">
+        <v>12193416</v>
+      </c>
+      <c r="G27" t="n">
+        <v>7862081</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.5509145733807627</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>NBCC</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CROMPTON</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>242</v>
+      </c>
+      <c r="C28" t="n">
+        <v>248.8</v>
+      </c>
+      <c r="D28" t="n">
+        <v>240</v>
+      </c>
+      <c r="E28" t="n">
+        <v>245.5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3871701</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2440115</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.5866879224954562</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>CROMPTON</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>PPLPHARMA</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>145.9</v>
+      </c>
+      <c r="C29" t="n">
+        <v>146.33</v>
+      </c>
+      <c r="D29" t="n">
+        <v>143.22</v>
+      </c>
+      <c r="E29" t="n">
+        <v>144.2</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2989219</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1869299</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.599112287547364</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>PPLPHARMA</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,528 +479,264 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1322.3</v>
+        <v>4068</v>
       </c>
       <c r="C2" t="n">
-        <v>1338.6</v>
+        <v>4138.6</v>
       </c>
       <c r="D2" t="n">
-        <v>1312.8</v>
+        <v>4063</v>
       </c>
       <c r="E2" t="n">
-        <v>1319.5</v>
+        <v>4107.1</v>
       </c>
       <c r="F2" t="n">
-        <v>6542529</v>
+        <v>1281358</v>
       </c>
       <c r="G2" t="n">
-        <v>13519723</v>
+        <v>2791024</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5160752184049925</v>
+        <v>-0.5409004007131433</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>HAL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1010.1</v>
+        <v>279</v>
       </c>
       <c r="C3" t="n">
-        <v>1015</v>
+        <v>286.18</v>
       </c>
       <c r="D3" t="n">
-        <v>990.45</v>
+        <v>278.99</v>
       </c>
       <c r="E3" t="n">
-        <v>995.55</v>
+        <v>283.79</v>
       </c>
       <c r="F3" t="n">
-        <v>7668209</v>
+        <v>15013291</v>
       </c>
       <c r="G3" t="n">
-        <v>18256527</v>
+        <v>31642983</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5799743839559408</v>
+        <v>-0.5255412234680908</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>BHEL</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>HINDPETRO</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>377</v>
+        <v>361</v>
       </c>
       <c r="C4" t="n">
-        <v>378.7</v>
+        <v>366.9</v>
       </c>
       <c r="D4" t="n">
-        <v>369.45</v>
+        <v>357.05</v>
       </c>
       <c r="E4" t="n">
-        <v>371.85</v>
+        <v>361</v>
       </c>
       <c r="F4" t="n">
-        <v>12422256</v>
+        <v>6347879</v>
       </c>
       <c r="G4" t="n">
-        <v>30162218</v>
+        <v>13372048</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5881517731885633</v>
+        <v>-0.5252874503591373</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>HINDPETRO</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>BDL</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1437</v>
+        <v>1338</v>
       </c>
       <c r="C5" t="n">
-        <v>1456.2</v>
+        <v>1362</v>
       </c>
       <c r="D5" t="n">
-        <v>1415.2</v>
+        <v>1332</v>
       </c>
       <c r="E5" t="n">
-        <v>1442.2</v>
+        <v>1345</v>
       </c>
       <c r="F5" t="n">
-        <v>3159307</v>
+        <v>1216787</v>
       </c>
       <c r="G5" t="n">
-        <v>7636467</v>
+        <v>2714078</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5862868260937945</v>
+        <v>-0.5516757440279904</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>BDL</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>FORTIS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>449.25</v>
+        <v>854</v>
       </c>
       <c r="C6" t="n">
-        <v>456.2</v>
+        <v>859.35</v>
       </c>
       <c r="D6" t="n">
-        <v>447.85</v>
+        <v>845.6</v>
       </c>
       <c r="E6" t="n">
-        <v>454.4</v>
+        <v>848</v>
       </c>
       <c r="F6" t="n">
-        <v>9468415</v>
+        <v>725996</v>
       </c>
       <c r="G6" t="n">
-        <v>20653569</v>
+        <v>1471110</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5415603472697624</v>
+        <v>-0.5064978145753887</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>FORTIS</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>142.89</v>
+        <v>1465</v>
       </c>
       <c r="C7" t="n">
-        <v>142.89</v>
+        <v>1482.4</v>
       </c>
       <c r="D7" t="n">
-        <v>140.5</v>
+        <v>1450.1</v>
       </c>
       <c r="E7" t="n">
-        <v>141.54</v>
+        <v>1477.7</v>
       </c>
       <c r="F7" t="n">
-        <v>22052191</v>
+        <v>315205</v>
       </c>
       <c r="G7" t="n">
-        <v>45807508</v>
+        <v>637993</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5185900311363806</v>
+        <v>-0.5059428551723921</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HDFCAMC</t>
+          <t>ANGELONE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2537</v>
+        <v>281.49</v>
       </c>
       <c r="C8" t="n">
-        <v>2548.7</v>
+        <v>287.9</v>
       </c>
       <c r="D8" t="n">
-        <v>2491.9</v>
+        <v>279.54</v>
       </c>
       <c r="E8" t="n">
-        <v>2528</v>
+        <v>281.2</v>
       </c>
       <c r="F8" t="n">
-        <v>996857</v>
+        <v>14403261</v>
       </c>
       <c r="G8" t="n">
-        <v>2035265</v>
+        <v>29671494</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5102077616428328</v>
+        <v>-0.5145758080129029</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>HDFCAMC</t>
+          <t>ANGELONE</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4351</v>
+        <v>473.05</v>
       </c>
       <c r="C9" t="n">
-        <v>4430</v>
+        <v>474.95</v>
       </c>
       <c r="D9" t="n">
-        <v>4322.3</v>
+        <v>467</v>
       </c>
       <c r="E9" t="n">
-        <v>4405</v>
+        <v>469.35</v>
       </c>
       <c r="F9" t="n">
-        <v>549708</v>
+        <v>1862603</v>
       </c>
       <c r="G9" t="n">
-        <v>1093580</v>
+        <v>4080774</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4973316995555881</v>
+        <v>-0.5435662450309672</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>DMART</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>ADANIENSOL</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1073.2</v>
-      </c>
-      <c r="C10" t="n">
-        <v>1085</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1052.8</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1074.8</v>
-      </c>
-      <c r="F10" t="n">
-        <v>2130340</v>
-      </c>
-      <c r="G10" t="n">
-        <v>4475280</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-0.523976153447382</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>ADANIENSOL</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>HINDZINC</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>554.25</v>
-      </c>
-      <c r="C11" t="n">
-        <v>563.9</v>
-      </c>
-      <c r="D11" t="n">
-        <v>546.95</v>
-      </c>
-      <c r="E11" t="n">
-        <v>558</v>
-      </c>
-      <c r="F11" t="n">
-        <v>3021130</v>
-      </c>
-      <c r="G11" t="n">
-        <v>6904276</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-0.5624262413611507</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>HINDZINC</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>GAIL</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>153.3</v>
-      </c>
-      <c r="C12" t="n">
-        <v>154.7</v>
-      </c>
-      <c r="D12" t="n">
-        <v>151.24</v>
-      </c>
-      <c r="E12" t="n">
-        <v>152.2</v>
-      </c>
-      <c r="F12" t="n">
-        <v>10066115</v>
-      </c>
-      <c r="G12" t="n">
-        <v>21095009</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-0.5228200661113726</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>GAIL</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>PIDILITIND</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1355</v>
-      </c>
-      <c r="C13" t="n">
-        <v>1365.1</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1335</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1348</v>
-      </c>
-      <c r="F13" t="n">
-        <v>924142</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1855865</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-0.5020424438199976</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>PIDILITIND</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>LICI</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>796.7</v>
-      </c>
-      <c r="C14" t="n">
-        <v>799</v>
-      </c>
-      <c r="D14" t="n">
-        <v>786.3</v>
-      </c>
-      <c r="E14" t="n">
-        <v>794.05</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1861476</v>
-      </c>
-      <c r="G14" t="n">
-        <v>4526133</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-0.5887270656871992</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>LICI</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>IDFCFIRSTB</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>65.86</v>
-      </c>
-      <c r="C15" t="n">
-        <v>66.25</v>
-      </c>
-      <c r="D15" t="n">
-        <v>64.95</v>
-      </c>
-      <c r="E15" t="n">
-        <v>65.23999999999999</v>
-      </c>
-      <c r="F15" t="n">
-        <v>19666295</v>
-      </c>
-      <c r="G15" t="n">
-        <v>42736119</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-0.5398202864420141</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>IDFCFIRSTB</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>NUVAMA</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1284</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1321.8</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1276</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1299</v>
-      </c>
-      <c r="F16" t="n">
-        <v>329939</v>
-      </c>
-      <c r="G16" t="n">
-        <v>687903</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-0.5203698777298543</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>NUVAMA</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>GRANULES</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>643.3</v>
-      </c>
-      <c r="C17" t="n">
-        <v>648.75</v>
-      </c>
-      <c r="D17" t="n">
-        <v>630.6</v>
-      </c>
-      <c r="E17" t="n">
-        <v>634.2</v>
-      </c>
-      <c r="F17" t="n">
-        <v>442660</v>
-      </c>
-      <c r="G17" t="n">
-        <v>973546</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-0.5453116750518209</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>GRANULES</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
     </row>
@@ -1015,7 +751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1068,132 +804,363 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2381.1</v>
+        <v>2267.7</v>
       </c>
       <c r="C2" t="n">
-        <v>2468.6</v>
+        <v>2376.9</v>
       </c>
       <c r="D2" t="n">
-        <v>2373</v>
+        <v>2267.7</v>
       </c>
       <c r="E2" t="n">
-        <v>2440.8</v>
+        <v>2356</v>
       </c>
       <c r="F2" t="n">
-        <v>2726784</v>
+        <v>3018178</v>
       </c>
       <c r="G2" t="n">
-        <v>1926538</v>
+        <v>1980060</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4153803350881218</v>
+        <v>0.5242861327434523</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>503.4</v>
+        <v>3880</v>
       </c>
       <c r="C3" t="n">
-        <v>507.9</v>
+        <v>3969</v>
       </c>
       <c r="D3" t="n">
-        <v>486.9</v>
+        <v>3871.3</v>
       </c>
       <c r="E3" t="n">
-        <v>488.85</v>
+        <v>3927</v>
       </c>
       <c r="F3" t="n">
-        <v>3223088</v>
+        <v>1186264</v>
       </c>
       <c r="G3" t="n">
-        <v>2194458</v>
+        <v>749640</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4687398893029623</v>
+        <v>0.5824449068886399</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>TRENT</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PIIND</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2885.4</v>
+        <v>569.95</v>
       </c>
       <c r="C4" t="n">
-        <v>2893.4</v>
+        <v>576</v>
       </c>
       <c r="D4" t="n">
-        <v>2808</v>
+        <v>564.2</v>
       </c>
       <c r="E4" t="n">
-        <v>2893.4</v>
+        <v>569.05</v>
       </c>
       <c r="F4" t="n">
-        <v>437619</v>
+        <v>6281265</v>
       </c>
       <c r="G4" t="n">
-        <v>279838</v>
+        <v>4323997</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5638297872340425</v>
+        <v>0.4526524879642608</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>PIIND</t>
+          <t>DLF</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>JSL</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>757</v>
+        <v>153.49</v>
       </c>
       <c r="C5" t="n">
-        <v>764.7</v>
+        <v>154.98</v>
       </c>
       <c r="D5" t="n">
-        <v>748</v>
+        <v>151.91</v>
       </c>
       <c r="E5" t="n">
-        <v>758</v>
+        <v>154.1</v>
       </c>
       <c r="F5" t="n">
-        <v>823506</v>
+        <v>14099404</v>
       </c>
       <c r="G5" t="n">
-        <v>582752</v>
+        <v>10066115</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4131328592608863</v>
+        <v>0.4006798054661605</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>JSL</t>
+          <t>GAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5931</v>
+      </c>
+      <c r="C6" t="n">
+        <v>6130</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5931</v>
+      </c>
+      <c r="E6" t="n">
+        <v>6120</v>
+      </c>
+      <c r="F6" t="n">
+        <v>334871</v>
+      </c>
+      <c r="G6" t="n">
+        <v>237284</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.4112666677904958</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>5470.7</v>
+      </c>
+      <c r="C7" t="n">
+        <v>5470.7</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5302.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5428</v>
+      </c>
+      <c r="F7" t="n">
+        <v>904088</v>
+      </c>
+      <c r="G7" t="n">
+        <v>600754</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.5049221478342216</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2415.1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2415.1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2276.2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2329</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1026126</v>
+      </c>
+      <c r="G8" t="n">
+        <v>695846</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.4746452519666708</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>319</v>
+      </c>
+      <c r="C9" t="n">
+        <v>326.8</v>
+      </c>
+      <c r="D9" t="n">
+        <v>318.7</v>
+      </c>
+      <c r="E9" t="n">
+        <v>321</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5058997</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3517302</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.4383174944886734</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>IGL</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>156</v>
+      </c>
+      <c r="C10" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>155.6</v>
+      </c>
+      <c r="E10" t="n">
+        <v>161.6</v>
+      </c>
+      <c r="F10" t="n">
+        <v>8990056</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5994358</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.4997529343425935</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>IGL</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>GRANULES</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>636.2</v>
+      </c>
+      <c r="C11" t="n">
+        <v>647.3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>628.65</v>
+      </c>
+      <c r="E11" t="n">
+        <v>631.95</v>
+      </c>
+      <c r="F11" t="n">
+        <v>660503</v>
+      </c>
+      <c r="G11" t="n">
+        <v>442660</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.4921226223286495</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>GRANULES</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PPLPHARMA</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>143.65</v>
+      </c>
+      <c r="C12" t="n">
+        <v>147.19</v>
+      </c>
+      <c r="D12" t="n">
+        <v>143.25</v>
+      </c>
+      <c r="E12" t="n">
+        <v>146.1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2366991</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1581920</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.4962773085870335</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>PPLPHARMA</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,264 +479,495 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4068</v>
+        <v>1654.9</v>
       </c>
       <c r="C2" t="n">
-        <v>4138.6</v>
+        <v>1668.7</v>
       </c>
       <c r="D2" t="n">
-        <v>4063</v>
+        <v>1640.1</v>
       </c>
       <c r="E2" t="n">
-        <v>4107.1</v>
+        <v>1653.6</v>
       </c>
       <c r="F2" t="n">
-        <v>1281358</v>
+        <v>3751005</v>
       </c>
       <c r="G2" t="n">
-        <v>2791024</v>
+        <v>8089531</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5409004007131433</v>
+        <v>-0.5363136626832878</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>WIPRO</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>279</v>
+        <v>203.01</v>
       </c>
       <c r="C3" t="n">
-        <v>286.18</v>
+        <v>203.4</v>
       </c>
       <c r="D3" t="n">
-        <v>278.99</v>
+        <v>200.31</v>
       </c>
       <c r="E3" t="n">
-        <v>283.79</v>
+        <v>202.96</v>
       </c>
       <c r="F3" t="n">
-        <v>15013291</v>
+        <v>21930624</v>
       </c>
       <c r="G3" t="n">
-        <v>31642983</v>
+        <v>51219565</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5255412234680908</v>
+        <v>-0.571831115707445</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>WIPRO</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HINDPETRO</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>361</v>
+        <v>9701.5</v>
       </c>
       <c r="C4" t="n">
-        <v>366.9</v>
+        <v>9851</v>
       </c>
       <c r="D4" t="n">
-        <v>357.05</v>
+        <v>9700</v>
       </c>
       <c r="E4" t="n">
-        <v>361</v>
+        <v>9792</v>
       </c>
       <c r="F4" t="n">
-        <v>6347879</v>
+        <v>363886</v>
       </c>
       <c r="G4" t="n">
-        <v>13372048</v>
+        <v>738971</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5252874503591373</v>
+        <v>-0.5075774286135721</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>HINDPETRO</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BDL</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1338</v>
+        <v>3769.8</v>
       </c>
       <c r="C5" t="n">
-        <v>1362</v>
+        <v>3779.4</v>
       </c>
       <c r="D5" t="n">
-        <v>1332</v>
+        <v>3711</v>
       </c>
       <c r="E5" t="n">
-        <v>1345</v>
+        <v>3732.5</v>
       </c>
       <c r="F5" t="n">
-        <v>1216787</v>
+        <v>625221</v>
       </c>
       <c r="G5" t="n">
-        <v>2714078</v>
+        <v>1331891</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5516757440279904</v>
+        <v>-0.5305764510759514</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>BDL</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FORTIS</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>854</v>
+        <v>6725</v>
       </c>
       <c r="C6" t="n">
-        <v>859.35</v>
+        <v>6878.5</v>
       </c>
       <c r="D6" t="n">
-        <v>845.6</v>
+        <v>6688</v>
       </c>
       <c r="E6" t="n">
-        <v>848</v>
+        <v>6835</v>
       </c>
       <c r="F6" t="n">
-        <v>725996</v>
+        <v>320237</v>
       </c>
       <c r="G6" t="n">
-        <v>1471110</v>
+        <v>798909</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5064978145753887</v>
+        <v>-0.5991571004958012</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>FORTIS</t>
+          <t>ABB</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TORNTPOWER</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1465</v>
+        <v>1330</v>
       </c>
       <c r="C7" t="n">
-        <v>1482.4</v>
+        <v>1343.5</v>
       </c>
       <c r="D7" t="n">
-        <v>1450.1</v>
+        <v>1314.3</v>
       </c>
       <c r="E7" t="n">
-        <v>1477.7</v>
+        <v>1328.9</v>
       </c>
       <c r="F7" t="n">
-        <v>315205</v>
+        <v>724962</v>
       </c>
       <c r="G7" t="n">
-        <v>637993</v>
+        <v>1610183</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5059428551723921</v>
+        <v>-0.5497642193464967</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>TORNTPOWER</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ANGELONE</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>281.49</v>
+        <v>5319.5</v>
       </c>
       <c r="C8" t="n">
-        <v>287.9</v>
+        <v>5408.8</v>
       </c>
       <c r="D8" t="n">
-        <v>279.54</v>
+        <v>5317</v>
       </c>
       <c r="E8" t="n">
-        <v>281.2</v>
+        <v>5380</v>
       </c>
       <c r="F8" t="n">
-        <v>14403261</v>
+        <v>460222</v>
       </c>
       <c r="G8" t="n">
-        <v>29671494</v>
+        <v>904088</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5145758080129029</v>
+        <v>-0.4909544203661591</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ANGELONE</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DELHIVERY</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>473.05</v>
+        <v>1212.3</v>
       </c>
       <c r="C9" t="n">
-        <v>474.95</v>
+        <v>1238.7</v>
       </c>
       <c r="D9" t="n">
-        <v>467</v>
+        <v>1200</v>
       </c>
       <c r="E9" t="n">
-        <v>469.35</v>
+        <v>1230</v>
       </c>
       <c r="F9" t="n">
-        <v>1862603</v>
+        <v>2000659</v>
       </c>
       <c r="G9" t="n">
-        <v>4080774</v>
+        <v>4067185</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5435662450309672</v>
+        <v>-0.5080973695565852</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>DELHIVERY</t>
+          <t>COFORGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>GODREJPROP</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1695.9</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1722.9</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1641</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1706</v>
+      </c>
+      <c r="F10" t="n">
+        <v>915224</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2202543</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.5844694064996688</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>GODREJPROP</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PAGEIND</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>35700</v>
+      </c>
+      <c r="C11" t="n">
+        <v>36400</v>
+      </c>
+      <c r="D11" t="n">
+        <v>35505</v>
+      </c>
+      <c r="E11" t="n">
+        <v>35905</v>
+      </c>
+      <c r="F11" t="n">
+        <v>23574</v>
+      </c>
+      <c r="G11" t="n">
+        <v>46384</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.4917644015177647</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>PAGEIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>7200.5</v>
+      </c>
+      <c r="C12" t="n">
+        <v>7211.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>7077</v>
+      </c>
+      <c r="E12" t="n">
+        <v>7160</v>
+      </c>
+      <c r="F12" t="n">
+        <v>68906</v>
+      </c>
+      <c r="G12" t="n">
+        <v>151932</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.5464681568069926</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>476.1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>482.65</v>
+      </c>
+      <c r="D13" t="n">
+        <v>467.5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>482</v>
+      </c>
+      <c r="F13" t="n">
+        <v>743371</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1714106</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.566321452698958</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TIINDIA</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2699.2</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2744</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2648.6</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2702.6</v>
+      </c>
+      <c r="F14" t="n">
+        <v>90668</v>
+      </c>
+      <c r="G14" t="n">
+        <v>223968</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.5951743106158023</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>TIINDIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ANGELONE</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>273</v>
+      </c>
+      <c r="C15" t="n">
+        <v>282.8</v>
+      </c>
+      <c r="D15" t="n">
+        <v>273</v>
+      </c>
+      <c r="E15" t="n">
+        <v>280.85</v>
+      </c>
+      <c r="F15" t="n">
+        <v>6934623</v>
+      </c>
+      <c r="G15" t="n">
+        <v>14403261</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.518537989417813</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ANGELONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>316.2</v>
+      </c>
+      <c r="C16" t="n">
+        <v>318.1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>311.35</v>
+      </c>
+      <c r="E16" t="n">
+        <v>316.05</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2261240</v>
+      </c>
+      <c r="G16" t="n">
+        <v>5058997</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.5530260247238731</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
         </is>
       </c>
     </row>
@@ -751,7 +982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -804,363 +1035,231 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2267.7</v>
+        <v>1321.2</v>
       </c>
       <c r="C2" t="n">
-        <v>2376.9</v>
+        <v>1327.6</v>
       </c>
       <c r="D2" t="n">
-        <v>2267.7</v>
+        <v>1310</v>
       </c>
       <c r="E2" t="n">
-        <v>2356</v>
+        <v>1314</v>
       </c>
       <c r="F2" t="n">
-        <v>3018178</v>
+        <v>28753269</v>
       </c>
       <c r="G2" t="n">
-        <v>1980060</v>
+        <v>19364461</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5242861327434523</v>
+        <v>0.4848473706549333</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>RELIANCE</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3880</v>
+        <v>1525</v>
       </c>
       <c r="C3" t="n">
-        <v>3969</v>
+        <v>1542</v>
       </c>
       <c r="D3" t="n">
-        <v>3871.3</v>
+        <v>1502</v>
       </c>
       <c r="E3" t="n">
-        <v>3927</v>
+        <v>1505.5</v>
       </c>
       <c r="F3" t="n">
-        <v>1186264</v>
+        <v>3388598</v>
       </c>
       <c r="G3" t="n">
-        <v>749640</v>
+        <v>2340856</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5824449068886399</v>
+        <v>0.4475892579466657</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>569.95</v>
+        <v>181.5</v>
       </c>
       <c r="C4" t="n">
-        <v>576</v>
+        <v>185.27</v>
       </c>
       <c r="D4" t="n">
-        <v>564.2</v>
+        <v>178.81</v>
       </c>
       <c r="E4" t="n">
-        <v>569.05</v>
+        <v>185.27</v>
       </c>
       <c r="F4" t="n">
-        <v>6281265</v>
+        <v>18738060</v>
       </c>
       <c r="G4" t="n">
-        <v>4323997</v>
+        <v>12959457</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4526524879642608</v>
+        <v>0.445898543434343</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>153.49</v>
+        <v>2650</v>
       </c>
       <c r="C5" t="n">
-        <v>154.98</v>
+        <v>2776.4</v>
       </c>
       <c r="D5" t="n">
-        <v>151.91</v>
+        <v>2629</v>
       </c>
       <c r="E5" t="n">
-        <v>154.1</v>
+        <v>2774</v>
       </c>
       <c r="F5" t="n">
-        <v>14099404</v>
+        <v>4807666</v>
       </c>
       <c r="G5" t="n">
-        <v>10066115</v>
+        <v>3165287</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4006798054661605</v>
+        <v>0.5188720643657273</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>MCX</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>HINDPETRO</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5931</v>
+        <v>346.1</v>
       </c>
       <c r="C6" t="n">
-        <v>6130</v>
+        <v>351</v>
       </c>
       <c r="D6" t="n">
-        <v>5931</v>
+        <v>340.8</v>
       </c>
       <c r="E6" t="n">
-        <v>6120</v>
+        <v>350.5</v>
       </c>
       <c r="F6" t="n">
-        <v>334871</v>
+        <v>9327976</v>
       </c>
       <c r="G6" t="n">
-        <v>237284</v>
+        <v>6347879</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4112666677904958</v>
+        <v>0.4694634223494178</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>HINDPETRO</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5470.7</v>
+        <v>1340</v>
       </c>
       <c r="C7" t="n">
-        <v>5470.7</v>
+        <v>1353</v>
       </c>
       <c r="D7" t="n">
-        <v>5302.5</v>
+        <v>1333</v>
       </c>
       <c r="E7" t="n">
-        <v>5428</v>
+        <v>1340</v>
       </c>
       <c r="F7" t="n">
-        <v>904088</v>
+        <v>1378435</v>
       </c>
       <c r="G7" t="n">
-        <v>600754</v>
+        <v>907020</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5049221478342216</v>
+        <v>0.5197404687878988</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2415.1</v>
+        <v>127.5</v>
       </c>
       <c r="C8" t="n">
-        <v>2415.1</v>
+        <v>131.22</v>
       </c>
       <c r="D8" t="n">
-        <v>2276.2</v>
+        <v>126.52</v>
       </c>
       <c r="E8" t="n">
-        <v>2329</v>
+        <v>129</v>
       </c>
       <c r="F8" t="n">
-        <v>1026126</v>
+        <v>5914574</v>
       </c>
       <c r="G8" t="n">
-        <v>695846</v>
+        <v>3717367</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4746452519666708</v>
+        <v>0.5910653965562184</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>RBLBANK</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>319</v>
-      </c>
-      <c r="C9" t="n">
-        <v>326.8</v>
-      </c>
-      <c r="D9" t="n">
-        <v>318.7</v>
-      </c>
-      <c r="E9" t="n">
-        <v>321</v>
-      </c>
-      <c r="F9" t="n">
-        <v>5058997</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3517302</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.4383174944886734</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>RBLBANK</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>IGL</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>156</v>
-      </c>
-      <c r="C10" t="n">
-        <v>162.5</v>
-      </c>
-      <c r="D10" t="n">
-        <v>155.6</v>
-      </c>
-      <c r="E10" t="n">
-        <v>161.6</v>
-      </c>
-      <c r="F10" t="n">
-        <v>8990056</v>
-      </c>
-      <c r="G10" t="n">
-        <v>5994358</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.4997529343425935</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>IGL</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>GRANULES</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>636.2</v>
-      </c>
-      <c r="C11" t="n">
-        <v>647.3</v>
-      </c>
-      <c r="D11" t="n">
-        <v>628.65</v>
-      </c>
-      <c r="E11" t="n">
-        <v>631.95</v>
-      </c>
-      <c r="F11" t="n">
-        <v>660503</v>
-      </c>
-      <c r="G11" t="n">
-        <v>442660</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.4921226223286495</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>GRANULES</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>PPLPHARMA</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>143.65</v>
-      </c>
-      <c r="C12" t="n">
-        <v>147.19</v>
-      </c>
-      <c r="D12" t="n">
-        <v>143.25</v>
-      </c>
-      <c r="E12" t="n">
-        <v>146.1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>2366991</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1581920</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.4962773085870335</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>PPLPHARMA</t>
+          <t>IEX</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,6 +473,336 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>filterdata</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2187</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2200</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2136</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2138</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1779015</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3729773</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-0.5230232510128633</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>390.25</v>
+      </c>
+      <c r="C3" t="n">
+        <v>393.95</v>
+      </c>
+      <c r="D3" t="n">
+        <v>387.1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>392</v>
+      </c>
+      <c r="F3" t="n">
+        <v>7722460</v>
+      </c>
+      <c r="G3" t="n">
+        <v>15240045</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-0.4932783991123386</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1107</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1123.75</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1091.3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1094.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2759798</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5816187</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.5254970309585988</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1195</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1205.7</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1165.2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1168.05</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2053037</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4050611</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.4931537489035605</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1537.1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1567.9</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1535.6</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1549.6</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1410204</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3388598</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.5838385078430667</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>VOLTAS</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1390</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1412.8</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1380.8</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1396462</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2793680</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.5001353054036253</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>VOLTAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ATGL</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>585</v>
+      </c>
+      <c r="C8" t="n">
+        <v>590.95</v>
+      </c>
+      <c r="D8" t="n">
+        <v>573.05</v>
+      </c>
+      <c r="E8" t="n">
+        <v>584.9</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2469791</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4867094</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.4925532566250004</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ATGL</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SUPREMEIND</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3866.8</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3879.8</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3806.5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3816</v>
+      </c>
+      <c r="F9" t="n">
+        <v>157385</v>
+      </c>
+      <c r="G9" t="n">
+        <v>329863</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.5228776795214983</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>SUPREMEIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="C10" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>87.51000000000001</v>
+      </c>
+      <c r="E10" t="n">
+        <v>88.15000000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>34514977</v>
+      </c>
+      <c r="G10" t="n">
+        <v>71995655</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.5205963887681833</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>POONAWALLA</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>414.1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>418.8</v>
+      </c>
+      <c r="D11" t="n">
+        <v>408.65</v>
+      </c>
+      <c r="E11" t="n">
+        <v>413.5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2035643</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4188411</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.5139820328043261</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>POONAWALLA</t>
         </is>
       </c>
     </row>
@@ -487,7 +817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,6 +867,534 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2501.9</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2559</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2493.4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2552.8</v>
+      </c>
+      <c r="F2" t="n">
+        <v>5261384</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3739587</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.4069425313543982</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>9901.5</v>
+      </c>
+      <c r="C3" t="n">
+        <v>9976</v>
+      </c>
+      <c r="D3" t="n">
+        <v>9830</v>
+      </c>
+      <c r="E3" t="n">
+        <v>9865</v>
+      </c>
+      <c r="F3" t="n">
+        <v>551624</v>
+      </c>
+      <c r="G3" t="n">
+        <v>363886</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.5159253172696944</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>7516.5</v>
+      </c>
+      <c r="C4" t="n">
+        <v>7686</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7500</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7619.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>464570</v>
+      </c>
+      <c r="G4" t="n">
+        <v>310575</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.4958383643242373</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>438.8</v>
+      </c>
+      <c r="C5" t="n">
+        <v>446.5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>438</v>
+      </c>
+      <c r="E5" t="n">
+        <v>445</v>
+      </c>
+      <c r="F5" t="n">
+        <v>13577979</v>
+      </c>
+      <c r="G5" t="n">
+        <v>8965276</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.5145076403671232</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>PFC</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>578.2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>590.45</v>
+      </c>
+      <c r="D6" t="n">
+        <v>575.7</v>
+      </c>
+      <c r="E6" t="n">
+        <v>587</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6111306</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4218013</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.4488589769637979</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>VBL</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>437</v>
+      </c>
+      <c r="C7" t="n">
+        <v>451.7</v>
+      </c>
+      <c r="D7" t="n">
+        <v>436.1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>445.05</v>
+      </c>
+      <c r="F7" t="n">
+        <v>7797798</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5357143</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.4555889211842954</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>VBL</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>6890</v>
+      </c>
+      <c r="C8" t="n">
+        <v>6993</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6844</v>
+      </c>
+      <c r="E8" t="n">
+        <v>6851.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>499662</v>
+      </c>
+      <c r="G8" t="n">
+        <v>320237</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.5602881615803296</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>5670</v>
+      </c>
+      <c r="C9" t="n">
+        <v>5724</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5600.5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5665</v>
+      </c>
+      <c r="F9" t="n">
+        <v>542939</v>
+      </c>
+      <c r="G9" t="n">
+        <v>350782</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.5477960670729969</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>641.05</v>
+      </c>
+      <c r="C10" t="n">
+        <v>653.4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>638.9</v>
+      </c>
+      <c r="E10" t="n">
+        <v>647</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3031172</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2083643</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.4547463265060281</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1360</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1360.1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1325.1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1330</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1064359</v>
+      </c>
+      <c r="G11" t="n">
+        <v>724962</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.468158331057352</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>10714.5</v>
+      </c>
+      <c r="C12" t="n">
+        <v>11099</v>
+      </c>
+      <c r="D12" t="n">
+        <v>10714.5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>11077</v>
+      </c>
+      <c r="F12" t="n">
+        <v>852184</v>
+      </c>
+      <c r="G12" t="n">
+        <v>570575</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.4935529947859615</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1830</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1849.3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1811.5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1826.5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1709299</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1138866</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.5008780664274813</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>GMRAIRPORT</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="C14" t="n">
+        <v>100</v>
+      </c>
+      <c r="D14" t="n">
+        <v>97.06</v>
+      </c>
+      <c r="E14" t="n">
+        <v>99.01000000000001</v>
+      </c>
+      <c r="F14" t="n">
+        <v>21552860</v>
+      </c>
+      <c r="G14" t="n">
+        <v>15006282</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.436255829391984</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>GMRAIRPORT</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>UPL</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>654</v>
+      </c>
+      <c r="C15" t="n">
+        <v>661.55</v>
+      </c>
+      <c r="D15" t="n">
+        <v>648.55</v>
+      </c>
+      <c r="E15" t="n">
+        <v>660</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2544691</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1737923</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.4642138920999377</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>UPL</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1705.4</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1720</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1689.2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1706.2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>908276</v>
+      </c>
+      <c r="G16" t="n">
+        <v>627290</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.4479363611726634</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>KAYNES</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>3973.5</v>
+      </c>
+      <c r="C17" t="n">
+        <v>4069</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3923</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4018</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1601955</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1003874</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.5957729754929404</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>KAYNES</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,330 +479,297 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2187</v>
+        <v>1222</v>
       </c>
       <c r="C2" t="n">
-        <v>2200</v>
+        <v>1227.6</v>
       </c>
       <c r="D2" t="n">
-        <v>2136</v>
+        <v>1214.1</v>
       </c>
       <c r="E2" t="n">
-        <v>2138</v>
+        <v>1221.5</v>
       </c>
       <c r="F2" t="n">
-        <v>1779015</v>
+        <v>2014236</v>
       </c>
       <c r="G2" t="n">
-        <v>3729773</v>
+        <v>4693413</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5230232510128633</v>
+        <v>-0.5708376825137699</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>DRREDDY</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>390.25</v>
+        <v>1971.1</v>
       </c>
       <c r="C3" t="n">
-        <v>393.95</v>
+        <v>1990.9</v>
       </c>
       <c r="D3" t="n">
-        <v>387.1</v>
+        <v>1962.1</v>
       </c>
       <c r="E3" t="n">
-        <v>392</v>
+        <v>1974</v>
       </c>
       <c r="F3" t="n">
-        <v>7722460</v>
+        <v>642257</v>
       </c>
       <c r="G3" t="n">
-        <v>15240045</v>
+        <v>1341053</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4932783991123386</v>
+        <v>-0.5210800766263526</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>SBILIFE</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1107</v>
+        <v>3600</v>
       </c>
       <c r="C4" t="n">
-        <v>1123.75</v>
+        <v>3619.3</v>
       </c>
       <c r="D4" t="n">
-        <v>1091.3</v>
+        <v>3532.8</v>
       </c>
       <c r="E4" t="n">
-        <v>1094.5</v>
+        <v>3569.9</v>
       </c>
       <c r="F4" t="n">
-        <v>2759798</v>
+        <v>1020682</v>
       </c>
       <c r="G4" t="n">
-        <v>5816187</v>
+        <v>2134727</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5254970309585988</v>
+        <v>-0.5218676673879142</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>SIEMENS</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>DMART</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1195</v>
+        <v>4496.1</v>
       </c>
       <c r="C5" t="n">
-        <v>1205.7</v>
+        <v>4506.9</v>
       </c>
       <c r="D5" t="n">
-        <v>1165.2</v>
+        <v>4386</v>
       </c>
       <c r="E5" t="n">
-        <v>1168.05</v>
+        <v>4436.5</v>
       </c>
       <c r="F5" t="n">
-        <v>2053037</v>
+        <v>342142</v>
       </c>
       <c r="G5" t="n">
-        <v>4050611</v>
+        <v>846585</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4931537489035605</v>
+        <v>-0.5958562932251339</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>DMART</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1537.1</v>
+        <v>25200</v>
       </c>
       <c r="C6" t="n">
-        <v>1567.9</v>
+        <v>25275</v>
       </c>
       <c r="D6" t="n">
-        <v>1535.6</v>
+        <v>24830</v>
       </c>
       <c r="E6" t="n">
-        <v>1549.6</v>
+        <v>25130</v>
       </c>
       <c r="F6" t="n">
-        <v>1410204</v>
+        <v>34710</v>
       </c>
       <c r="G6" t="n">
-        <v>3388598</v>
+        <v>82224</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5838385078430667</v>
+        <v>-0.5778604786923526</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>SHREECEM</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VOLTAS</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1390</v>
+        <v>465.85</v>
       </c>
       <c r="C7" t="n">
-        <v>1412.8</v>
+        <v>466.9</v>
       </c>
       <c r="D7" t="n">
-        <v>1380.8</v>
+        <v>461.15</v>
       </c>
       <c r="E7" t="n">
-        <v>1400</v>
+        <v>462</v>
       </c>
       <c r="F7" t="n">
-        <v>1396462</v>
+        <v>3612628</v>
       </c>
       <c r="G7" t="n">
-        <v>2793680</v>
+        <v>7533552</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5001353054036253</v>
+        <v>-0.5204615299662099</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>VOLTAS</t>
+          <t>OIL</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ATGL</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>585</v>
+        <v>1071</v>
       </c>
       <c r="C8" t="n">
-        <v>590.95</v>
+        <v>1085</v>
       </c>
       <c r="D8" t="n">
-        <v>573.05</v>
+        <v>1056.9</v>
       </c>
       <c r="E8" t="n">
-        <v>584.9</v>
+        <v>1080</v>
       </c>
       <c r="F8" t="n">
-        <v>2469791</v>
+        <v>796315</v>
       </c>
       <c r="G8" t="n">
-        <v>4867094</v>
+        <v>1795093</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4925532566250004</v>
+        <v>-0.5563934570520859</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ATGL</t>
+          <t>360ONE</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SUPREMEIND</t>
+          <t>SRF</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3866.8</v>
+        <v>2512</v>
       </c>
       <c r="C9" t="n">
-        <v>3879.8</v>
+        <v>2521.7</v>
       </c>
       <c r="D9" t="n">
-        <v>3806.5</v>
+        <v>2480</v>
       </c>
       <c r="E9" t="n">
-        <v>3816</v>
+        <v>2506</v>
       </c>
       <c r="F9" t="n">
-        <v>157385</v>
+        <v>238499</v>
       </c>
       <c r="G9" t="n">
-        <v>329863</v>
+        <v>551458</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5228776795214983</v>
+        <v>-0.5675119410725749</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SUPREMEIND</t>
+          <t>SRF</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>DALBHARAT</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>87.90000000000001</v>
+        <v>1994.3</v>
       </c>
       <c r="C10" t="n">
-        <v>91.2</v>
+        <v>1994.7</v>
       </c>
       <c r="D10" t="n">
-        <v>87.51000000000001</v>
+        <v>1955.5</v>
       </c>
       <c r="E10" t="n">
-        <v>88.15000000000001</v>
+        <v>1965</v>
       </c>
       <c r="F10" t="n">
-        <v>34514977</v>
+        <v>151683</v>
       </c>
       <c r="G10" t="n">
-        <v>71995655</v>
+        <v>309119</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5205963887681833</v>
+        <v>-0.5093054778256917</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>HFCL</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>POONAWALLA</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>414.1</v>
-      </c>
-      <c r="C11" t="n">
-        <v>418.8</v>
-      </c>
-      <c r="D11" t="n">
-        <v>408.65</v>
-      </c>
-      <c r="E11" t="n">
-        <v>413.5</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2035643</v>
-      </c>
-      <c r="G11" t="n">
-        <v>4188411</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-0.5139820328043261</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>POONAWALLA</t>
+          <t>DALBHARAT</t>
         </is>
       </c>
     </row>
@@ -817,7 +784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -870,528 +837,462 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2501.9</v>
+        <v>818</v>
       </c>
       <c r="C2" t="n">
-        <v>2559</v>
+        <v>820.05</v>
       </c>
       <c r="D2" t="n">
-        <v>2493.4</v>
+        <v>792.2</v>
       </c>
       <c r="E2" t="n">
-        <v>2552.8</v>
+        <v>794</v>
       </c>
       <c r="F2" t="n">
-        <v>5261384</v>
+        <v>62861293</v>
       </c>
       <c r="G2" t="n">
-        <v>3739587</v>
+        <v>39769515</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4069425313543982</v>
+        <v>0.5806401712467452</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9901.5</v>
+        <v>1863.5</v>
       </c>
       <c r="C3" t="n">
-        <v>9976</v>
+        <v>1864.9</v>
       </c>
       <c r="D3" t="n">
-        <v>9830</v>
+        <v>1823.2</v>
       </c>
       <c r="E3" t="n">
-        <v>9865</v>
+        <v>1835.5</v>
       </c>
       <c r="F3" t="n">
-        <v>551624</v>
+        <v>15871247</v>
       </c>
       <c r="G3" t="n">
-        <v>363886</v>
+        <v>11049107</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5159253172696944</v>
+        <v>0.4364280298851301</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7516.5</v>
+        <v>1322.1</v>
       </c>
       <c r="C4" t="n">
-        <v>7686</v>
+        <v>1331</v>
       </c>
       <c r="D4" t="n">
-        <v>7500</v>
+        <v>1309</v>
       </c>
       <c r="E4" t="n">
-        <v>7619.5</v>
+        <v>1316</v>
       </c>
       <c r="F4" t="n">
-        <v>464570</v>
+        <v>18527029</v>
       </c>
       <c r="G4" t="n">
-        <v>310575</v>
+        <v>12098912</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4958383643242373</v>
+        <v>0.5312971116741737</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>INFY</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>438.8</v>
+        <v>1182.15</v>
       </c>
       <c r="C5" t="n">
-        <v>446.5</v>
+        <v>1229.5</v>
       </c>
       <c r="D5" t="n">
-        <v>438</v>
+        <v>1172.15</v>
       </c>
       <c r="E5" t="n">
-        <v>445</v>
+        <v>1228.05</v>
       </c>
       <c r="F5" t="n">
-        <v>13577979</v>
+        <v>3144521</v>
       </c>
       <c r="G5" t="n">
-        <v>8965276</v>
+        <v>2053037</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5145076403671232</v>
+        <v>0.5316436089559029</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>578.2</v>
+        <v>1339</v>
       </c>
       <c r="C6" t="n">
-        <v>590.45</v>
+        <v>1342.9</v>
       </c>
       <c r="D6" t="n">
-        <v>575.7</v>
+        <v>1317.3</v>
       </c>
       <c r="E6" t="n">
-        <v>587</v>
+        <v>1332</v>
       </c>
       <c r="F6" t="n">
-        <v>6111306</v>
+        <v>1586537</v>
       </c>
       <c r="G6" t="n">
-        <v>4218013</v>
+        <v>1064359</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4488589769637979</v>
+        <v>0.4906032645000418</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VBL</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>437</v>
+        <v>1299</v>
       </c>
       <c r="C7" t="n">
-        <v>451.7</v>
+        <v>1334.9</v>
       </c>
       <c r="D7" t="n">
-        <v>436.1</v>
+        <v>1291</v>
       </c>
       <c r="E7" t="n">
-        <v>445.05</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="n">
-        <v>7797798</v>
+        <v>3695658</v>
       </c>
       <c r="G7" t="n">
-        <v>5357143</v>
+        <v>2626157</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4555889211842954</v>
+        <v>0.4072494523366272</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>VBL</t>
+          <t>COFORGE</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6890</v>
+        <v>5315</v>
       </c>
       <c r="C8" t="n">
-        <v>6993</v>
+        <v>5349</v>
       </c>
       <c r="D8" t="n">
-        <v>6844</v>
+        <v>5129.5</v>
       </c>
       <c r="E8" t="n">
-        <v>6851.5</v>
+        <v>5168</v>
       </c>
       <c r="F8" t="n">
-        <v>499662</v>
+        <v>920301</v>
       </c>
       <c r="G8" t="n">
-        <v>320237</v>
+        <v>651858</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5602881615803296</v>
+        <v>0.4118120817724106</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5670</v>
+        <v>289.5</v>
       </c>
       <c r="C9" t="n">
-        <v>5724</v>
+        <v>289.8</v>
       </c>
       <c r="D9" t="n">
-        <v>5600.5</v>
+        <v>281.6</v>
       </c>
       <c r="E9" t="n">
-        <v>5665</v>
+        <v>283.85</v>
       </c>
       <c r="F9" t="n">
-        <v>542939</v>
+        <v>10948325</v>
       </c>
       <c r="G9" t="n">
-        <v>350782</v>
+        <v>7778158</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5477960670729969</v>
+        <v>0.4075729755039689</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>ATGL</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>641.05</v>
+        <v>589.9</v>
       </c>
       <c r="C10" t="n">
-        <v>653.4</v>
+        <v>603</v>
       </c>
       <c r="D10" t="n">
-        <v>638.9</v>
+        <v>582.5</v>
       </c>
       <c r="E10" t="n">
-        <v>647</v>
+        <v>600.5</v>
       </c>
       <c r="F10" t="n">
-        <v>3031172</v>
+        <v>3797212</v>
       </c>
       <c r="G10" t="n">
-        <v>2083643</v>
+        <v>2469791</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4547463265060281</v>
+        <v>0.5374628865357433</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>ATGL</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>KAYNES</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1360</v>
+        <v>4070</v>
       </c>
       <c r="C11" t="n">
-        <v>1360.1</v>
+        <v>4218</v>
       </c>
       <c r="D11" t="n">
-        <v>1325.1</v>
+        <v>4060</v>
       </c>
       <c r="E11" t="n">
-        <v>1330</v>
+        <v>4204</v>
       </c>
       <c r="F11" t="n">
-        <v>1064359</v>
+        <v>2268105</v>
       </c>
       <c r="G11" t="n">
-        <v>724962</v>
+        <v>1601955</v>
       </c>
       <c r="H11" t="n">
-        <v>0.468158331057352</v>
+        <v>0.4158356508141615</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>KAYNES</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>KFINTECH</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10714.5</v>
+        <v>945</v>
       </c>
       <c r="C12" t="n">
-        <v>11099</v>
+        <v>965.5</v>
       </c>
       <c r="D12" t="n">
-        <v>10714.5</v>
+        <v>941.1</v>
       </c>
       <c r="E12" t="n">
-        <v>11077</v>
+        <v>956</v>
       </c>
       <c r="F12" t="n">
-        <v>852184</v>
+        <v>1670400</v>
       </c>
       <c r="G12" t="n">
-        <v>570575</v>
+        <v>1104720</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4935529947859615</v>
+        <v>0.5120573538996307</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>KFINTECH</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>NCC</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1830</v>
+        <v>158</v>
       </c>
       <c r="C13" t="n">
-        <v>1849.3</v>
+        <v>161.5</v>
       </c>
       <c r="D13" t="n">
-        <v>1811.5</v>
+        <v>156.06</v>
       </c>
       <c r="E13" t="n">
-        <v>1826.5</v>
+        <v>161.25</v>
       </c>
       <c r="F13" t="n">
-        <v>1709299</v>
+        <v>3981046</v>
       </c>
       <c r="G13" t="n">
-        <v>1138866</v>
+        <v>2749247</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5008780664274813</v>
+        <v>0.4480495932158878</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>NCC</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GMRAIRPORT</t>
+          <t>SYNGENE</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>97.59999999999999</v>
+        <v>417.95</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>439.25</v>
       </c>
       <c r="D14" t="n">
-        <v>97.06</v>
+        <v>417.95</v>
       </c>
       <c r="E14" t="n">
-        <v>99.01000000000001</v>
+        <v>434.55</v>
       </c>
       <c r="F14" t="n">
-        <v>21552860</v>
+        <v>1464476</v>
       </c>
       <c r="G14" t="n">
-        <v>15006282</v>
+        <v>935725</v>
       </c>
       <c r="H14" t="n">
-        <v>0.436255829391984</v>
+        <v>0.5650709343022789</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>GMRAIRPORT</t>
+          <t>SYNGENE</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>UPL</t>
+          <t>TATATECH</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>654</v>
+        <v>580.95</v>
       </c>
       <c r="C15" t="n">
-        <v>661.55</v>
+        <v>592.2</v>
       </c>
       <c r="D15" t="n">
-        <v>648.55</v>
+        <v>578.55</v>
       </c>
       <c r="E15" t="n">
-        <v>660</v>
+        <v>587.5</v>
       </c>
       <c r="F15" t="n">
-        <v>2544691</v>
+        <v>874908</v>
       </c>
       <c r="G15" t="n">
-        <v>1737923</v>
+        <v>610713</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4642138920999377</v>
+        <v>0.4326009107387594</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>UPL</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>OBEROIRLTY</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1705.4</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1720</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1689.2</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1706.2</v>
-      </c>
-      <c r="F16" t="n">
-        <v>908276</v>
-      </c>
-      <c r="G16" t="n">
-        <v>627290</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.4479363611726634</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>OBEROIRLTY</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>KAYNES</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>3973.5</v>
-      </c>
-      <c r="C17" t="n">
-        <v>4069</v>
-      </c>
-      <c r="D17" t="n">
-        <v>3923</v>
-      </c>
-      <c r="E17" t="n">
-        <v>4018</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1601955</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1003874</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.5957729754929404</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>KAYNES</t>
+          <t>TATATECH</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,297 +479,528 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1222</v>
+        <v>1340</v>
       </c>
       <c r="C2" t="n">
-        <v>1227.6</v>
+        <v>1368.4</v>
       </c>
       <c r="D2" t="n">
-        <v>1214.1</v>
+        <v>1340</v>
       </c>
       <c r="E2" t="n">
-        <v>1221.5</v>
+        <v>1364.9</v>
       </c>
       <c r="F2" t="n">
-        <v>2014236</v>
+        <v>13869105</v>
       </c>
       <c r="G2" t="n">
-        <v>4693413</v>
+        <v>30211012</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5708376825137699</v>
+        <v>-0.5409255075599586</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>RELIANCE</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1971.1</v>
+        <v>1837.1</v>
       </c>
       <c r="C3" t="n">
-        <v>1990.9</v>
+        <v>1851.4</v>
       </c>
       <c r="D3" t="n">
-        <v>1962.1</v>
+        <v>1829.7</v>
       </c>
       <c r="E3" t="n">
-        <v>1974</v>
+        <v>1847.3</v>
       </c>
       <c r="F3" t="n">
-        <v>642257</v>
+        <v>7344787</v>
       </c>
       <c r="G3" t="n">
-        <v>1341053</v>
+        <v>15871247</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5210800766263526</v>
+        <v>-0.5372268480227168</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3600</v>
+        <v>990.65</v>
       </c>
       <c r="C4" t="n">
-        <v>3619.3</v>
+        <v>1011.4</v>
       </c>
       <c r="D4" t="n">
-        <v>3532.8</v>
+        <v>983</v>
       </c>
       <c r="E4" t="n">
-        <v>3569.9</v>
+        <v>1008</v>
       </c>
       <c r="F4" t="n">
-        <v>1020682</v>
+        <v>1640745</v>
       </c>
       <c r="G4" t="n">
-        <v>2134727</v>
+        <v>3370119</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5218676673879142</v>
+        <v>-0.5131492389437881</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4496.1</v>
+        <v>1828.8</v>
       </c>
       <c r="C5" t="n">
-        <v>4506.9</v>
+        <v>1845.5</v>
       </c>
       <c r="D5" t="n">
-        <v>4386</v>
+        <v>1811.7</v>
       </c>
       <c r="E5" t="n">
-        <v>4436.5</v>
+        <v>1838</v>
       </c>
       <c r="F5" t="n">
-        <v>342142</v>
+        <v>487836</v>
       </c>
       <c r="G5" t="n">
-        <v>846585</v>
+        <v>1035217</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5958562932251339</v>
+        <v>-0.528759670677742</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>PFC</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25200</v>
+        <v>460</v>
       </c>
       <c r="C6" t="n">
-        <v>25275</v>
+        <v>467.2</v>
       </c>
       <c r="D6" t="n">
-        <v>24830</v>
+        <v>455.45</v>
       </c>
       <c r="E6" t="n">
-        <v>25130</v>
+        <v>464.5</v>
       </c>
       <c r="F6" t="n">
-        <v>34710</v>
+        <v>10255394</v>
       </c>
       <c r="G6" t="n">
-        <v>82224</v>
+        <v>23065922</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5778604786923526</v>
+        <v>-0.5553876406934871</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>PFC</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>465.85</v>
+        <v>4380</v>
       </c>
       <c r="C7" t="n">
-        <v>466.9</v>
+        <v>4399.4</v>
       </c>
       <c r="D7" t="n">
-        <v>461.15</v>
+        <v>4346.6</v>
       </c>
       <c r="E7" t="n">
-        <v>462</v>
+        <v>4381</v>
       </c>
       <c r="F7" t="n">
-        <v>3612628</v>
+        <v>1038094</v>
       </c>
       <c r="G7" t="n">
-        <v>7533552</v>
+        <v>2251283</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5204615299662099</v>
+        <v>-0.5388878252978413</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>HAL</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1071</v>
+        <v>1564</v>
       </c>
       <c r="C8" t="n">
-        <v>1085</v>
+        <v>1585</v>
       </c>
       <c r="D8" t="n">
-        <v>1056.9</v>
+        <v>1542.4</v>
       </c>
       <c r="E8" t="n">
-        <v>1080</v>
+        <v>1579.1</v>
       </c>
       <c r="F8" t="n">
-        <v>796315</v>
+        <v>1168171</v>
       </c>
       <c r="G8" t="n">
-        <v>1795093</v>
+        <v>2767683</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5563934570520859</v>
+        <v>-0.5779245672282556</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SRF</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2512</v>
+        <v>6305.5</v>
       </c>
       <c r="C9" t="n">
-        <v>2521.7</v>
+        <v>6325</v>
       </c>
       <c r="D9" t="n">
-        <v>2480</v>
+        <v>6212</v>
       </c>
       <c r="E9" t="n">
-        <v>2506</v>
+        <v>6228</v>
       </c>
       <c r="F9" t="n">
-        <v>238499</v>
+        <v>169295</v>
       </c>
       <c r="G9" t="n">
-        <v>551458</v>
+        <v>350424</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5675119410725749</v>
+        <v>-0.5168852590005251</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SRF</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DALBHARAT</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1994.3</v>
+        <v>25110</v>
       </c>
       <c r="C10" t="n">
-        <v>1994.7</v>
+        <v>25325</v>
       </c>
       <c r="D10" t="n">
-        <v>1955.5</v>
+        <v>25055</v>
       </c>
       <c r="E10" t="n">
-        <v>1965</v>
+        <v>25300</v>
       </c>
       <c r="F10" t="n">
-        <v>151683</v>
+        <v>16254</v>
       </c>
       <c r="G10" t="n">
-        <v>309119</v>
+        <v>34710</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5093054778256917</v>
+        <v>-0.5317199654278306</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>DALBHARAT</t>
+          <t>SHREECEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>INDUSINDBK</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>849</v>
+      </c>
+      <c r="C11" t="n">
+        <v>857.45</v>
+      </c>
+      <c r="D11" t="n">
+        <v>838.55</v>
+      </c>
+      <c r="E11" t="n">
+        <v>853</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1850548</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3785293</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.5111215961353586</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>INDUSINDBK</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AUBANK</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>989</v>
+      </c>
+      <c r="C12" t="n">
+        <v>994.8</v>
+      </c>
+      <c r="D12" t="n">
+        <v>978.05</v>
+      </c>
+      <c r="E12" t="n">
+        <v>990</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1186537</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2610962</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.5455556227934378</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>AUBANK</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="C13" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="D13" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>68.45</v>
+      </c>
+      <c r="F13" t="n">
+        <v>16355291</v>
+      </c>
+      <c r="G13" t="n">
+        <v>35142366</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.534599036388159</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>558.05</v>
+      </c>
+      <c r="C14" t="n">
+        <v>565</v>
+      </c>
+      <c r="D14" t="n">
+        <v>551.35</v>
+      </c>
+      <c r="E14" t="n">
+        <v>561.75</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2859883</v>
+      </c>
+      <c r="G14" t="n">
+        <v>6605253</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.567028999494796</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CROMPTON</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>263</v>
+      </c>
+      <c r="C15" t="n">
+        <v>263.5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>258.51</v>
+      </c>
+      <c r="E15" t="n">
+        <v>262.02</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4340724</v>
+      </c>
+      <c r="G15" t="n">
+        <v>8988325</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.5170708669301566</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>CROMPTON</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>POONAWALLA</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>407.75</v>
+      </c>
+      <c r="C16" t="n">
+        <v>417.4</v>
+      </c>
+      <c r="D16" t="n">
+        <v>401.85</v>
+      </c>
+      <c r="E16" t="n">
+        <v>412.9</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2687668</v>
+      </c>
+      <c r="G16" t="n">
+        <v>5836499</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.5395068173574603</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>POONAWALLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>BANDHANBNK</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>174.7</v>
+      </c>
+      <c r="C17" t="n">
+        <v>176.28</v>
+      </c>
+      <c r="D17" t="n">
+        <v>172.51</v>
+      </c>
+      <c r="E17" t="n">
+        <v>174.4</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4242898</v>
+      </c>
+      <c r="G17" t="n">
+        <v>9311571</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.5443413361719521</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>BANDHANBNK</t>
         </is>
       </c>
     </row>
@@ -784,7 +1015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -837,462 +1068,198 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>818</v>
+        <v>393</v>
       </c>
       <c r="C2" t="n">
-        <v>820.05</v>
+        <v>396.25</v>
       </c>
       <c r="D2" t="n">
-        <v>792.2</v>
+        <v>388.45</v>
       </c>
       <c r="E2" t="n">
-        <v>794</v>
+        <v>393.7</v>
       </c>
       <c r="F2" t="n">
-        <v>62861293</v>
+        <v>15320653</v>
       </c>
       <c r="G2" t="n">
-        <v>39769515</v>
+        <v>9896906</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5806401712467452</v>
+        <v>0.5480245038196786</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>NTPC</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1863.5</v>
+        <v>1234.55</v>
       </c>
       <c r="C3" t="n">
-        <v>1864.9</v>
+        <v>1266.45</v>
       </c>
       <c r="D3" t="n">
-        <v>1823.2</v>
+        <v>1221.6</v>
       </c>
       <c r="E3" t="n">
-        <v>1835.5</v>
+        <v>1249.95</v>
       </c>
       <c r="F3" t="n">
-        <v>15871247</v>
+        <v>4943744</v>
       </c>
       <c r="G3" t="n">
-        <v>11049107</v>
+        <v>3144521</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4364280298851301</v>
+        <v>0.5721771296804823</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>IRFC</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1322.1</v>
+        <v>103.75</v>
       </c>
       <c r="C4" t="n">
-        <v>1331</v>
+        <v>106.78</v>
       </c>
       <c r="D4" t="n">
-        <v>1309</v>
+        <v>103.25</v>
       </c>
       <c r="E4" t="n">
-        <v>1316</v>
+        <v>104.95</v>
       </c>
       <c r="F4" t="n">
-        <v>18527029</v>
+        <v>32766513</v>
       </c>
       <c r="G4" t="n">
-        <v>12098912</v>
+        <v>21466219</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5312971116741737</v>
+        <v>0.5264221892080762</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>IRFC</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1182.15</v>
+        <v>177.47</v>
       </c>
       <c r="C5" t="n">
-        <v>1229.5</v>
+        <v>177.47</v>
       </c>
       <c r="D5" t="n">
-        <v>1172.15</v>
+        <v>173.17</v>
       </c>
       <c r="E5" t="n">
-        <v>1228.05</v>
+        <v>174.7</v>
       </c>
       <c r="F5" t="n">
-        <v>3144521</v>
+        <v>21780071</v>
       </c>
       <c r="G5" t="n">
-        <v>2053037</v>
+        <v>15255848</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5316436089559029</v>
+        <v>0.4276539068821346</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>KEI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1339</v>
+        <v>4689.9</v>
       </c>
       <c r="C6" t="n">
-        <v>1342.9</v>
+        <v>4866.2</v>
       </c>
       <c r="D6" t="n">
-        <v>1317.3</v>
+        <v>4634.5</v>
       </c>
       <c r="E6" t="n">
-        <v>1332</v>
+        <v>4833.8</v>
       </c>
       <c r="F6" t="n">
-        <v>1586537</v>
+        <v>489014</v>
       </c>
       <c r="G6" t="n">
-        <v>1064359</v>
+        <v>340276</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4906032645000418</v>
+        <v>0.437109875512819</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>KEI</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>SJVN</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1299</v>
+        <v>76.89</v>
       </c>
       <c r="C7" t="n">
-        <v>1334.9</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>1291</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>79</v>
       </c>
       <c r="F7" t="n">
-        <v>3695658</v>
+        <v>9792864</v>
       </c>
       <c r="G7" t="n">
-        <v>2626157</v>
+        <v>6658685</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4072494523366272</v>
+        <v>0.4706903840623186</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>COFORGE</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>HEROMOTOCO</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>5315</v>
-      </c>
-      <c r="C8" t="n">
-        <v>5349</v>
-      </c>
-      <c r="D8" t="n">
-        <v>5129.5</v>
-      </c>
-      <c r="E8" t="n">
-        <v>5168</v>
-      </c>
-      <c r="F8" t="n">
-        <v>920301</v>
-      </c>
-      <c r="G8" t="n">
-        <v>651858</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.4118120817724106</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>HEROMOTOCO</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>FEDERALBNK</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>289.5</v>
-      </c>
-      <c r="C9" t="n">
-        <v>289.8</v>
-      </c>
-      <c r="D9" t="n">
-        <v>281.6</v>
-      </c>
-      <c r="E9" t="n">
-        <v>283.85</v>
-      </c>
-      <c r="F9" t="n">
-        <v>10948325</v>
-      </c>
-      <c r="G9" t="n">
-        <v>7778158</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.4075729755039689</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>FEDERALBNK</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>ATGL</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>589.9</v>
-      </c>
-      <c r="C10" t="n">
-        <v>603</v>
-      </c>
-      <c r="D10" t="n">
-        <v>582.5</v>
-      </c>
-      <c r="E10" t="n">
-        <v>600.5</v>
-      </c>
-      <c r="F10" t="n">
-        <v>3797212</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2469791</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.5374628865357433</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>ATGL</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>KAYNES</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>4070</v>
-      </c>
-      <c r="C11" t="n">
-        <v>4218</v>
-      </c>
-      <c r="D11" t="n">
-        <v>4060</v>
-      </c>
-      <c r="E11" t="n">
-        <v>4204</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2268105</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1601955</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.4158356508141615</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>KAYNES</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>KFINTECH</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>945</v>
-      </c>
-      <c r="C12" t="n">
-        <v>965.5</v>
-      </c>
-      <c r="D12" t="n">
-        <v>941.1</v>
-      </c>
-      <c r="E12" t="n">
-        <v>956</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1670400</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1104720</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.5120573538996307</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>KFINTECH</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>NCC</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>158</v>
-      </c>
-      <c r="C13" t="n">
-        <v>161.5</v>
-      </c>
-      <c r="D13" t="n">
-        <v>156.06</v>
-      </c>
-      <c r="E13" t="n">
-        <v>161.25</v>
-      </c>
-      <c r="F13" t="n">
-        <v>3981046</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2749247</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.4480495932158878</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>NCC</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>SYNGENE</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>417.95</v>
-      </c>
-      <c r="C14" t="n">
-        <v>439.25</v>
-      </c>
-      <c r="D14" t="n">
-        <v>417.95</v>
-      </c>
-      <c r="E14" t="n">
-        <v>434.55</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1464476</v>
-      </c>
-      <c r="G14" t="n">
-        <v>935725</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.5650709343022789</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>SYNGENE</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>TATATECH</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>580.95</v>
-      </c>
-      <c r="C15" t="n">
-        <v>592.2</v>
-      </c>
-      <c r="D15" t="n">
-        <v>578.55</v>
-      </c>
-      <c r="E15" t="n">
-        <v>587.5</v>
-      </c>
-      <c r="F15" t="n">
-        <v>874908</v>
-      </c>
-      <c r="G15" t="n">
-        <v>610713</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.4326009107387594</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>TATATECH</t>
+          <t>SJVN</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,528 +479,660 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1340</v>
+        <v>1572.4</v>
       </c>
       <c r="C2" t="n">
-        <v>1368.4</v>
+        <v>1600.5</v>
       </c>
       <c r="D2" t="n">
-        <v>1340</v>
+        <v>1566.1</v>
       </c>
       <c r="E2" t="n">
-        <v>1364.9</v>
+        <v>1572.1</v>
       </c>
       <c r="F2" t="n">
-        <v>13869105</v>
+        <v>2998603</v>
       </c>
       <c r="G2" t="n">
-        <v>30211012</v>
+        <v>6024587</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5409255075599586</v>
+        <v>-0.5022724379281103</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1837.1</v>
+        <v>1245</v>
       </c>
       <c r="C3" t="n">
-        <v>1851.4</v>
+        <v>1246</v>
       </c>
       <c r="D3" t="n">
-        <v>1829.7</v>
+        <v>1226</v>
       </c>
       <c r="E3" t="n">
-        <v>1847.3</v>
+        <v>1228.8</v>
       </c>
       <c r="F3" t="n">
-        <v>7344787</v>
+        <v>1158618</v>
       </c>
       <c r="G3" t="n">
-        <v>15871247</v>
+        <v>2291092</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5372268480227168</v>
+        <v>-0.4942944237944177</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>CIPLA</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MAXHEALTH</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>990.65</v>
+        <v>1253.1</v>
       </c>
       <c r="C4" t="n">
-        <v>1011.4</v>
+        <v>1291.5</v>
       </c>
       <c r="D4" t="n">
-        <v>983</v>
+        <v>1246.35</v>
       </c>
       <c r="E4" t="n">
-        <v>1008</v>
+        <v>1256</v>
       </c>
       <c r="F4" t="n">
-        <v>1640745</v>
+        <v>2335390</v>
       </c>
       <c r="G4" t="n">
-        <v>3370119</v>
+        <v>4943744</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5131492389437881</v>
+        <v>-0.5276070120135671</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MAXHEALTH</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>HDFCAMC</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1828.8</v>
+        <v>2791.8</v>
       </c>
       <c r="C5" t="n">
-        <v>1845.5</v>
+        <v>2809.8</v>
       </c>
       <c r="D5" t="n">
-        <v>1811.7</v>
+        <v>2753.4</v>
       </c>
       <c r="E5" t="n">
-        <v>1838</v>
+        <v>2769</v>
       </c>
       <c r="F5" t="n">
-        <v>487836</v>
+        <v>1049876</v>
       </c>
       <c r="G5" t="n">
-        <v>1035217</v>
+        <v>2259343</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.528759670677742</v>
+        <v>-0.5353180105898042</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>HDFCAMC</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>VBL</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>460</v>
+        <v>476.4</v>
       </c>
       <c r="C6" t="n">
-        <v>467.2</v>
+        <v>476.95</v>
       </c>
       <c r="D6" t="n">
-        <v>455.45</v>
+        <v>464.3</v>
       </c>
       <c r="E6" t="n">
-        <v>464.5</v>
+        <v>466.9</v>
       </c>
       <c r="F6" t="n">
-        <v>10255394</v>
+        <v>6027104</v>
       </c>
       <c r="G6" t="n">
-        <v>23065922</v>
+        <v>11968336</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5553876406934871</v>
+        <v>-0.4964125338727121</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>VBL</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>IRFC</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4380</v>
+        <v>105.14</v>
       </c>
       <c r="C7" t="n">
-        <v>4399.4</v>
+        <v>105.14</v>
       </c>
       <c r="D7" t="n">
-        <v>4346.6</v>
+        <v>102.3</v>
       </c>
       <c r="E7" t="n">
-        <v>4381</v>
+        <v>102.85</v>
       </c>
       <c r="F7" t="n">
-        <v>1038094</v>
+        <v>15091460</v>
       </c>
       <c r="G7" t="n">
-        <v>2251283</v>
+        <v>32766513</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5388878252978413</v>
+        <v>-0.5394242896703717</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>IRFC</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>UNITDSPR</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1564</v>
+        <v>1309</v>
       </c>
       <c r="C8" t="n">
-        <v>1585</v>
+        <v>1318.5</v>
       </c>
       <c r="D8" t="n">
-        <v>1542.4</v>
+        <v>1294</v>
       </c>
       <c r="E8" t="n">
-        <v>1579.1</v>
+        <v>1309</v>
       </c>
       <c r="F8" t="n">
-        <v>1168171</v>
+        <v>1189368</v>
       </c>
       <c r="G8" t="n">
-        <v>2767683</v>
+        <v>2825738</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5779245672282556</v>
+        <v>-0.5790947356053534</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>UNITDSPR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6305.5</v>
+        <v>157.92</v>
       </c>
       <c r="C9" t="n">
-        <v>6325</v>
+        <v>158.9</v>
       </c>
       <c r="D9" t="n">
-        <v>6212</v>
+        <v>156.02</v>
       </c>
       <c r="E9" t="n">
-        <v>6228</v>
+        <v>157.6</v>
       </c>
       <c r="F9" t="n">
-        <v>169295</v>
+        <v>5864225</v>
       </c>
       <c r="G9" t="n">
-        <v>350424</v>
+        <v>13015627</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5168852590005251</v>
+        <v>-0.5494473681521451</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>GAIL</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>SUZLON</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25110</v>
+        <v>53.34</v>
       </c>
       <c r="C10" t="n">
-        <v>25325</v>
+        <v>53.45</v>
       </c>
       <c r="D10" t="n">
-        <v>25055</v>
+        <v>51.87</v>
       </c>
       <c r="E10" t="n">
-        <v>25300</v>
+        <v>52.4</v>
       </c>
       <c r="F10" t="n">
-        <v>16254</v>
+        <v>153681261</v>
       </c>
       <c r="G10" t="n">
-        <v>34710</v>
+        <v>337159969</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5317199654278306</v>
+        <v>-0.5441888861960359</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>SUZLON</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>849</v>
+        <v>1600.6</v>
       </c>
       <c r="C11" t="n">
-        <v>857.45</v>
+        <v>1632</v>
       </c>
       <c r="D11" t="n">
-        <v>838.55</v>
+        <v>1582.1</v>
       </c>
       <c r="E11" t="n">
-        <v>853</v>
+        <v>1603.5</v>
       </c>
       <c r="F11" t="n">
-        <v>1850548</v>
+        <v>1874530</v>
       </c>
       <c r="G11" t="n">
-        <v>3785293</v>
+        <v>3749052</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5111215961353586</v>
+        <v>-0.4999989330636118</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>ATGL</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>989</v>
+        <v>634.35</v>
       </c>
       <c r="C12" t="n">
-        <v>994.8</v>
+        <v>640.5</v>
       </c>
       <c r="D12" t="n">
-        <v>978.05</v>
+        <v>611.05</v>
       </c>
       <c r="E12" t="n">
-        <v>990</v>
+        <v>615</v>
       </c>
       <c r="F12" t="n">
-        <v>1186537</v>
+        <v>3748704</v>
       </c>
       <c r="G12" t="n">
-        <v>2610962</v>
+        <v>8867488</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5455556227934378</v>
+        <v>-0.5772529943090986</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>ATGL</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IDFCFIRSTB</t>
+          <t>ASTRAL</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>67.8</v>
+        <v>1605</v>
       </c>
       <c r="C13" t="n">
-        <v>68.8</v>
+        <v>1618.4</v>
       </c>
       <c r="D13" t="n">
-        <v>67.3</v>
+        <v>1580</v>
       </c>
       <c r="E13" t="n">
-        <v>68.45</v>
+        <v>1591</v>
       </c>
       <c r="F13" t="n">
-        <v>16355291</v>
+        <v>793939</v>
       </c>
       <c r="G13" t="n">
-        <v>35142366</v>
+        <v>1631264</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.534599036388159</v>
+        <v>-0.513298276673794</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>IDFCFIRSTB</t>
+          <t>ASTRAL</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>558.05</v>
+        <v>1392</v>
       </c>
       <c r="C14" t="n">
-        <v>565</v>
+        <v>1392</v>
       </c>
       <c r="D14" t="n">
-        <v>551.35</v>
+        <v>1363.5</v>
       </c>
       <c r="E14" t="n">
-        <v>561.75</v>
+        <v>1365.5</v>
       </c>
       <c r="F14" t="n">
-        <v>2859883</v>
+        <v>707108</v>
       </c>
       <c r="G14" t="n">
-        <v>6605253</v>
+        <v>1612415</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.567028999494796</v>
+        <v>-0.5614602940310032</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CROMPTON</t>
+          <t>ICICIPRULI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>263</v>
+        <v>562</v>
       </c>
       <c r="C15" t="n">
-        <v>263.5</v>
+        <v>562.65</v>
       </c>
       <c r="D15" t="n">
-        <v>258.51</v>
+        <v>549.8</v>
       </c>
       <c r="E15" t="n">
-        <v>262.02</v>
+        <v>557.5</v>
       </c>
       <c r="F15" t="n">
-        <v>4340724</v>
+        <v>1615514</v>
       </c>
       <c r="G15" t="n">
-        <v>8988325</v>
+        <v>3333771</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5170708669301566</v>
+        <v>-0.5154094267422688</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>CROMPTON</t>
+          <t>ICICIPRULI</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>POONAWALLA</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>407.75</v>
+        <v>2472</v>
       </c>
       <c r="C16" t="n">
-        <v>417.4</v>
+        <v>2474.2</v>
       </c>
       <c r="D16" t="n">
-        <v>401.85</v>
+        <v>2405.1</v>
       </c>
       <c r="E16" t="n">
-        <v>412.9</v>
+        <v>2414</v>
       </c>
       <c r="F16" t="n">
-        <v>2687668</v>
+        <v>180997</v>
       </c>
       <c r="G16" t="n">
-        <v>5836499</v>
+        <v>416448</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.5395068173574603</v>
+        <v>-0.5653791109574304</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>POONAWALLA</t>
+          <t>MPHASIS</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>174.7</v>
+        <v>5582</v>
       </c>
       <c r="C17" t="n">
-        <v>176.28</v>
+        <v>5676.5</v>
       </c>
       <c r="D17" t="n">
-        <v>172.51</v>
+        <v>5534</v>
       </c>
       <c r="E17" t="n">
-        <v>174.4</v>
+        <v>5607.5</v>
       </c>
       <c r="F17" t="n">
-        <v>4242898</v>
+        <v>64218</v>
       </c>
       <c r="G17" t="n">
-        <v>9311571</v>
+        <v>126039</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5443413361719521</v>
+        <v>-0.490491038488087</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>ALKEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SONACOMS</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>595</v>
+      </c>
+      <c r="C18" t="n">
+        <v>595.6</v>
+      </c>
+      <c r="D18" t="n">
+        <v>574.3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>576</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1308363</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2982180</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.5612729613906605</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>SONACOMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CAMS</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>751</v>
+      </c>
+      <c r="C19" t="n">
+        <v>752</v>
+      </c>
+      <c r="D19" t="n">
+        <v>735.25</v>
+      </c>
+      <c r="E19" t="n">
+        <v>746.5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1023700</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2273576</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.5497401450402362</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>CAMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>IGL</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>169.9</v>
+      </c>
+      <c r="C20" t="n">
+        <v>170.06</v>
+      </c>
+      <c r="D20" t="n">
+        <v>161.3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>166.75</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3670818</v>
+      </c>
+      <c r="G20" t="n">
+        <v>8478431</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-0.567040411132673</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>IGL</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TITAGARH</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>744</v>
+      </c>
+      <c r="C21" t="n">
+        <v>746.35</v>
+      </c>
+      <c r="D21" t="n">
+        <v>727</v>
+      </c>
+      <c r="E21" t="n">
+        <v>731</v>
+      </c>
+      <c r="F21" t="n">
+        <v>699349</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1421965</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.5081812843494742</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>TITAGARH</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1068,198 +1200,363 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>393</v>
+        <v>3207</v>
       </c>
       <c r="C2" t="n">
-        <v>396.25</v>
+        <v>3235.5</v>
       </c>
       <c r="D2" t="n">
-        <v>388.45</v>
+        <v>3162.6</v>
       </c>
       <c r="E2" t="n">
-        <v>393.7</v>
+        <v>3212.5</v>
       </c>
       <c r="F2" t="n">
-        <v>15320653</v>
+        <v>3201466</v>
       </c>
       <c r="G2" t="n">
-        <v>9896906</v>
+        <v>2180404</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5480245038196786</v>
+        <v>0.4682902801499172</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>M&amp;M</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1234.55</v>
+        <v>1005.15</v>
       </c>
       <c r="C3" t="n">
-        <v>1266.45</v>
+        <v>1022</v>
       </c>
       <c r="D3" t="n">
-        <v>1221.6</v>
+        <v>1002.05</v>
       </c>
       <c r="E3" t="n">
-        <v>1249.95</v>
+        <v>1008.65</v>
       </c>
       <c r="F3" t="n">
-        <v>4943744</v>
+        <v>2301160</v>
       </c>
       <c r="G3" t="n">
-        <v>3144521</v>
+        <v>1640745</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5721771296804823</v>
+        <v>0.4025092259918512</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IRFC</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>103.75</v>
+        <v>142.8</v>
       </c>
       <c r="C4" t="n">
-        <v>106.78</v>
+        <v>144.49</v>
       </c>
       <c r="D4" t="n">
-        <v>103.25</v>
+        <v>141.31</v>
       </c>
       <c r="E4" t="n">
-        <v>104.95</v>
+        <v>142.75</v>
       </c>
       <c r="F4" t="n">
-        <v>32766513</v>
+        <v>21390225</v>
       </c>
       <c r="G4" t="n">
-        <v>21466219</v>
+        <v>13628290</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5264221892080762</v>
+        <v>0.5695457757356205</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>IRFC</t>
+          <t>CANBK</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>177.47</v>
+        <v>540</v>
       </c>
       <c r="C5" t="n">
-        <v>177.47</v>
+        <v>550.6</v>
       </c>
       <c r="D5" t="n">
-        <v>173.17</v>
+        <v>528.5</v>
       </c>
       <c r="E5" t="n">
-        <v>174.7</v>
+        <v>541</v>
       </c>
       <c r="F5" t="n">
-        <v>21780071</v>
+        <v>5760078</v>
       </c>
       <c r="G5" t="n">
-        <v>15255848</v>
+        <v>3657509</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4276539068821346</v>
+        <v>0.5748636572049447</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KEI</t>
+          <t>VOLTAS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4689.9</v>
+        <v>1447</v>
       </c>
       <c r="C6" t="n">
-        <v>4866.2</v>
+        <v>1476.5</v>
       </c>
       <c r="D6" t="n">
-        <v>4634.5</v>
+        <v>1429.9</v>
       </c>
       <c r="E6" t="n">
-        <v>4833.8</v>
+        <v>1434.6</v>
       </c>
       <c r="F6" t="n">
-        <v>489014</v>
+        <v>1789507</v>
       </c>
       <c r="G6" t="n">
-        <v>340276</v>
+        <v>1266294</v>
       </c>
       <c r="H6" t="n">
-        <v>0.437109875512819</v>
+        <v>0.4131844579536821</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>KEI</t>
+          <t>VOLTAS</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SJVN</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>76.89</v>
+        <v>1564</v>
       </c>
       <c r="C7" t="n">
-        <v>79.68000000000001</v>
+        <v>1637.6</v>
       </c>
       <c r="D7" t="n">
-        <v>76.59999999999999</v>
+        <v>1551.8</v>
       </c>
       <c r="E7" t="n">
-        <v>79</v>
+        <v>1604</v>
       </c>
       <c r="F7" t="n">
-        <v>9792864</v>
+        <v>1442253</v>
       </c>
       <c r="G7" t="n">
-        <v>6658685</v>
+        <v>961504</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4706903840623186</v>
+        <v>0.4999968798881752</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SJVN</t>
+          <t>TORNTPOWER</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2120.1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2150.7</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2087.5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2139</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1061518</v>
+      </c>
+      <c r="G8" t="n">
+        <v>725283</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.4635914532672074</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8063.5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>8175</v>
+      </c>
+      <c r="D9" t="n">
+        <v>7917.5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>8080</v>
+      </c>
+      <c r="F9" t="n">
+        <v>271398</v>
+      </c>
+      <c r="G9" t="n">
+        <v>175320</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.5480150581793293</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FORTIS</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>894</v>
+      </c>
+      <c r="C10" t="n">
+        <v>898.8</v>
+      </c>
+      <c r="D10" t="n">
+        <v>882.6</v>
+      </c>
+      <c r="E10" t="n">
+        <v>890.5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1276682</v>
+      </c>
+      <c r="G10" t="n">
+        <v>899582</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.4191946926461401</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>FORTIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>273.8</v>
+      </c>
+      <c r="C11" t="n">
+        <v>274.94</v>
+      </c>
+      <c r="D11" t="n">
+        <v>270.01</v>
+      </c>
+      <c r="E11" t="n">
+        <v>271.6</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2605561</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1802511</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.4455173921268719</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>316.3</v>
+      </c>
+      <c r="C12" t="n">
+        <v>319.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>312.7</v>
+      </c>
+      <c r="E12" t="n">
+        <v>316.75</v>
+      </c>
+      <c r="F12" t="n">
+        <v>4734160</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3190055</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.4840371090780566</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,658 +479,427 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1572.4</v>
+        <v>1284.4</v>
       </c>
       <c r="C2" t="n">
-        <v>1600.5</v>
+        <v>1296.4</v>
       </c>
       <c r="D2" t="n">
-        <v>1566.1</v>
+        <v>1273.7</v>
       </c>
       <c r="E2" t="n">
-        <v>1572.1</v>
+        <v>1283</v>
       </c>
       <c r="F2" t="n">
-        <v>2998603</v>
+        <v>2108883</v>
       </c>
       <c r="G2" t="n">
-        <v>6024587</v>
+        <v>4606071</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5022724379281103</v>
+        <v>-0.5421514344872235</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1245</v>
+        <v>7243</v>
       </c>
       <c r="C3" t="n">
-        <v>1246</v>
+        <v>7296</v>
       </c>
       <c r="D3" t="n">
-        <v>1226</v>
+        <v>7215</v>
       </c>
       <c r="E3" t="n">
-        <v>1228.8</v>
+        <v>7220</v>
       </c>
       <c r="F3" t="n">
-        <v>1158618</v>
+        <v>353002</v>
       </c>
       <c r="G3" t="n">
-        <v>2291092</v>
+        <v>695282</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4942944237944177</v>
+        <v>-0.4922894595286517</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>PFC</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1253.1</v>
+        <v>474</v>
       </c>
       <c r="C4" t="n">
-        <v>1291.5</v>
+        <v>479</v>
       </c>
       <c r="D4" t="n">
-        <v>1246.35</v>
+        <v>469.35</v>
       </c>
       <c r="E4" t="n">
-        <v>1256</v>
+        <v>470.7</v>
       </c>
       <c r="F4" t="n">
-        <v>2335390</v>
+        <v>5478143</v>
       </c>
       <c r="G4" t="n">
-        <v>4943744</v>
+        <v>10992233</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5276070120135671</v>
+        <v>-0.5016351090811121</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>PFC</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HDFCAMC</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2791.8</v>
+        <v>7200</v>
       </c>
       <c r="C5" t="n">
-        <v>2809.8</v>
+        <v>7300</v>
       </c>
       <c r="D5" t="n">
-        <v>2753.4</v>
+        <v>7184</v>
       </c>
       <c r="E5" t="n">
-        <v>2769</v>
+        <v>7268</v>
       </c>
       <c r="F5" t="n">
-        <v>1049876</v>
+        <v>260767</v>
       </c>
       <c r="G5" t="n">
-        <v>2259343</v>
+        <v>559841</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5353180105898042</v>
+        <v>-0.5342123924471412</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>HDFCAMC</t>
+          <t>ABB</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VBL</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>476.4</v>
+        <v>5715</v>
       </c>
       <c r="C6" t="n">
-        <v>476.95</v>
+        <v>5864.5</v>
       </c>
       <c r="D6" t="n">
-        <v>464.3</v>
+        <v>5685</v>
       </c>
       <c r="E6" t="n">
-        <v>466.9</v>
+        <v>5850</v>
       </c>
       <c r="F6" t="n">
-        <v>6027104</v>
+        <v>270416</v>
       </c>
       <c r="G6" t="n">
-        <v>11968336</v>
+        <v>610941</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4964125338727121</v>
+        <v>-0.5573778810065129</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>VBL</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IRFC</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>105.14</v>
+        <v>327.01</v>
       </c>
       <c r="C7" t="n">
-        <v>105.14</v>
+        <v>333.79</v>
       </c>
       <c r="D7" t="n">
-        <v>102.3</v>
+        <v>322.51</v>
       </c>
       <c r="E7" t="n">
-        <v>102.85</v>
+        <v>332</v>
       </c>
       <c r="F7" t="n">
-        <v>15091460</v>
+        <v>20292270</v>
       </c>
       <c r="G7" t="n">
-        <v>32766513</v>
+        <v>49865330</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5394242896703717</v>
+        <v>-0.593058543882092</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>IRFC</t>
+          <t>BHEL</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1309</v>
+        <v>5260</v>
       </c>
       <c r="C8" t="n">
-        <v>1318.5</v>
+        <v>5310</v>
       </c>
       <c r="D8" t="n">
-        <v>1294</v>
+        <v>5252</v>
       </c>
       <c r="E8" t="n">
-        <v>1309</v>
+        <v>5268</v>
       </c>
       <c r="F8" t="n">
-        <v>1189368</v>
+        <v>321063</v>
       </c>
       <c r="G8" t="n">
-        <v>2825738</v>
+        <v>654258</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5790947356053534</v>
+        <v>-0.5092715717652669</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>ATGL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>157.92</v>
+        <v>621</v>
       </c>
       <c r="C9" t="n">
-        <v>158.9</v>
+        <v>631.7</v>
       </c>
       <c r="D9" t="n">
-        <v>156.02</v>
+        <v>612.5</v>
       </c>
       <c r="E9" t="n">
-        <v>157.6</v>
+        <v>614.2</v>
       </c>
       <c r="F9" t="n">
-        <v>5864225</v>
+        <v>1844260</v>
       </c>
       <c r="G9" t="n">
-        <v>13015627</v>
+        <v>3748704</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5494473681521451</v>
+        <v>-0.5080273075708298</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>ATGL</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SUZLON</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>53.34</v>
+        <v>1600</v>
       </c>
       <c r="C10" t="n">
-        <v>53.45</v>
+        <v>1631</v>
       </c>
       <c r="D10" t="n">
-        <v>51.87</v>
+        <v>1593.4</v>
       </c>
       <c r="E10" t="n">
-        <v>52.4</v>
+        <v>1624</v>
       </c>
       <c r="F10" t="n">
-        <v>153681261</v>
+        <v>595204</v>
       </c>
       <c r="G10" t="n">
-        <v>337159969</v>
+        <v>1442253</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5441888861960359</v>
+        <v>-0.5873095774458434</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SUZLON</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>HUDCO</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1600.6</v>
+        <v>199.4</v>
       </c>
       <c r="C11" t="n">
-        <v>1632</v>
+        <v>202.88</v>
       </c>
       <c r="D11" t="n">
-        <v>1582.1</v>
+        <v>198</v>
       </c>
       <c r="E11" t="n">
-        <v>1603.5</v>
+        <v>198</v>
       </c>
       <c r="F11" t="n">
-        <v>1874530</v>
+        <v>3218467</v>
       </c>
       <c r="G11" t="n">
-        <v>3749052</v>
+        <v>7287259</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4999989330636118</v>
+        <v>-0.5583432673382406</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>HUDCO</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ATGL</t>
+          <t>KPITTECH</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>634.35</v>
+        <v>734</v>
       </c>
       <c r="C12" t="n">
-        <v>640.5</v>
+        <v>749.3</v>
       </c>
       <c r="D12" t="n">
-        <v>611.05</v>
+        <v>730.05</v>
       </c>
       <c r="E12" t="n">
-        <v>615</v>
+        <v>745</v>
       </c>
       <c r="F12" t="n">
-        <v>3748704</v>
+        <v>745302</v>
       </c>
       <c r="G12" t="n">
-        <v>8867488</v>
+        <v>1674776</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5772529943090986</v>
+        <v>-0.5549840695113855</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ATGL</t>
+          <t>KPITTECH</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ASTRAL</t>
+          <t>SJVN</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1605</v>
+        <v>77.2</v>
       </c>
       <c r="C13" t="n">
-        <v>1618.4</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>1580</v>
+        <v>76.52</v>
       </c>
       <c r="E13" t="n">
-        <v>1591</v>
+        <v>76.66</v>
       </c>
       <c r="F13" t="n">
-        <v>793939</v>
+        <v>3511490</v>
       </c>
       <c r="G13" t="n">
-        <v>1631264</v>
+        <v>7067252</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.513298276673794</v>
+        <v>-0.5031321933900192</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ASTRAL</t>
+          <t>SJVN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>TITAGARH</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1392</v>
+        <v>730.6</v>
       </c>
       <c r="C14" t="n">
-        <v>1392</v>
+        <v>741</v>
       </c>
       <c r="D14" t="n">
-        <v>1363.5</v>
+        <v>730</v>
       </c>
       <c r="E14" t="n">
-        <v>1365.5</v>
+        <v>737.95</v>
       </c>
       <c r="F14" t="n">
-        <v>707108</v>
+        <v>320230</v>
       </c>
       <c r="G14" t="n">
-        <v>1612415</v>
+        <v>699349</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5614602940310032</v>
+        <v>-0.5421027269646486</v>
       </c>
       <c r="I14" t="inlineStr">
-        <is>
-          <t>AUROPHARMA</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>ICICIPRULI</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>562</v>
-      </c>
-      <c r="C15" t="n">
-        <v>562.65</v>
-      </c>
-      <c r="D15" t="n">
-        <v>549.8</v>
-      </c>
-      <c r="E15" t="n">
-        <v>557.5</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1615514</v>
-      </c>
-      <c r="G15" t="n">
-        <v>3333771</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-0.5154094267422688</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>ICICIPRULI</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>MPHASIS</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>2472</v>
-      </c>
-      <c r="C16" t="n">
-        <v>2474.2</v>
-      </c>
-      <c r="D16" t="n">
-        <v>2405.1</v>
-      </c>
-      <c r="E16" t="n">
-        <v>2414</v>
-      </c>
-      <c r="F16" t="n">
-        <v>180997</v>
-      </c>
-      <c r="G16" t="n">
-        <v>416448</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-0.5653791109574304</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>MPHASIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>ALKEM</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>5582</v>
-      </c>
-      <c r="C17" t="n">
-        <v>5676.5</v>
-      </c>
-      <c r="D17" t="n">
-        <v>5534</v>
-      </c>
-      <c r="E17" t="n">
-        <v>5607.5</v>
-      </c>
-      <c r="F17" t="n">
-        <v>64218</v>
-      </c>
-      <c r="G17" t="n">
-        <v>126039</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-0.490491038488087</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>ALKEM</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>SONACOMS</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>595</v>
-      </c>
-      <c r="C18" t="n">
-        <v>595.6</v>
-      </c>
-      <c r="D18" t="n">
-        <v>574.3</v>
-      </c>
-      <c r="E18" t="n">
-        <v>576</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1308363</v>
-      </c>
-      <c r="G18" t="n">
-        <v>2982180</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-0.5612729613906605</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>SONACOMS</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>CAMS</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>751</v>
-      </c>
-      <c r="C19" t="n">
-        <v>752</v>
-      </c>
-      <c r="D19" t="n">
-        <v>735.25</v>
-      </c>
-      <c r="E19" t="n">
-        <v>746.5</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1023700</v>
-      </c>
-      <c r="G19" t="n">
-        <v>2273576</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-0.5497401450402362</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>CAMS</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>IGL</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>169.9</v>
-      </c>
-      <c r="C20" t="n">
-        <v>170.06</v>
-      </c>
-      <c r="D20" t="n">
-        <v>161.3</v>
-      </c>
-      <c r="E20" t="n">
-        <v>166.75</v>
-      </c>
-      <c r="F20" t="n">
-        <v>3670818</v>
-      </c>
-      <c r="G20" t="n">
-        <v>8478431</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-0.567040411132673</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>IGL</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>TITAGARH</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>744</v>
-      </c>
-      <c r="C21" t="n">
-        <v>746.35</v>
-      </c>
-      <c r="D21" t="n">
-        <v>727</v>
-      </c>
-      <c r="E21" t="n">
-        <v>731</v>
-      </c>
-      <c r="F21" t="n">
-        <v>699349</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1421965</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-0.5081812843494742</v>
-      </c>
-      <c r="I21" t="inlineStr">
         <is>
           <t>TITAGARH</t>
         </is>
@@ -1147,7 +916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1200,363 +969,462 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3207</v>
+        <v>1310</v>
       </c>
       <c r="C2" t="n">
-        <v>3235.5</v>
+        <v>1325</v>
       </c>
       <c r="D2" t="n">
-        <v>3162.6</v>
+        <v>1299.3</v>
       </c>
       <c r="E2" t="n">
-        <v>3212.5</v>
+        <v>1314.5</v>
       </c>
       <c r="F2" t="n">
-        <v>3201466</v>
+        <v>10057440</v>
       </c>
       <c r="G2" t="n">
-        <v>2180404</v>
+        <v>7172300</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4682902801499172</v>
+        <v>0.4022614781869135</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>INFY</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MAXHEALTH</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1005.15</v>
+        <v>1578.5</v>
       </c>
       <c r="C3" t="n">
-        <v>1022</v>
+        <v>1611.9</v>
       </c>
       <c r="D3" t="n">
-        <v>1002.05</v>
+        <v>1578.4</v>
       </c>
       <c r="E3" t="n">
-        <v>1008.65</v>
+        <v>1598</v>
       </c>
       <c r="F3" t="n">
-        <v>2301160</v>
+        <v>4276868</v>
       </c>
       <c r="G3" t="n">
-        <v>1640745</v>
+        <v>2998603</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4025092259918512</v>
+        <v>0.4262868409055817</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MAXHEALTH</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>142.8</v>
+        <v>1501</v>
       </c>
       <c r="C4" t="n">
-        <v>144.49</v>
+        <v>1510.9</v>
       </c>
       <c r="D4" t="n">
-        <v>141.31</v>
+        <v>1489</v>
       </c>
       <c r="E4" t="n">
-        <v>142.75</v>
+        <v>1499</v>
       </c>
       <c r="F4" t="n">
-        <v>21390225</v>
+        <v>2001948</v>
       </c>
       <c r="G4" t="n">
-        <v>13628290</v>
+        <v>1341688</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5695457757356205</v>
+        <v>0.4921114297809923</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>TECHM</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>HDFCAMC</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>540</v>
+        <v>2754</v>
       </c>
       <c r="C5" t="n">
-        <v>550.6</v>
+        <v>2816.8</v>
       </c>
       <c r="D5" t="n">
-        <v>528.5</v>
+        <v>2733.9</v>
       </c>
       <c r="E5" t="n">
-        <v>541</v>
+        <v>2790</v>
       </c>
       <c r="F5" t="n">
-        <v>5760078</v>
+        <v>1593751</v>
       </c>
       <c r="G5" t="n">
-        <v>3657509</v>
+        <v>1049876</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5748636572049447</v>
+        <v>0.518037368222533</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>HDFCAMC</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VOLTAS</t>
+          <t>SOLARINDS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1447</v>
+        <v>14851</v>
       </c>
       <c r="C6" t="n">
-        <v>1476.5</v>
+        <v>15169</v>
       </c>
       <c r="D6" t="n">
-        <v>1429.9</v>
+        <v>14851</v>
       </c>
       <c r="E6" t="n">
-        <v>1434.6</v>
+        <v>14958</v>
       </c>
       <c r="F6" t="n">
-        <v>1789507</v>
+        <v>124161</v>
       </c>
       <c r="G6" t="n">
-        <v>1266294</v>
+        <v>85713</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4131844579536821</v>
+        <v>0.4485667285009275</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>VOLTAS</t>
+          <t>SOLARINDS</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TORNTPOWER</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1564</v>
+        <v>174.4</v>
       </c>
       <c r="C7" t="n">
-        <v>1637.6</v>
+        <v>177.68</v>
       </c>
       <c r="D7" t="n">
-        <v>1551.8</v>
+        <v>174</v>
       </c>
       <c r="E7" t="n">
-        <v>1604</v>
+        <v>174.9</v>
       </c>
       <c r="F7" t="n">
-        <v>1442253</v>
+        <v>27069051</v>
       </c>
       <c r="G7" t="n">
-        <v>961504</v>
+        <v>17825908</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4999968798881752</v>
+        <v>0.5185229835136589</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>TORNTPOWER</t>
+          <t>SAIL</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2120.1</v>
+        <v>1776.4</v>
       </c>
       <c r="C8" t="n">
-        <v>2150.7</v>
+        <v>1834.9</v>
       </c>
       <c r="D8" t="n">
-        <v>2087.5</v>
+        <v>1776</v>
       </c>
       <c r="E8" t="n">
-        <v>2139</v>
+        <v>1807</v>
       </c>
       <c r="F8" t="n">
-        <v>1061518</v>
+        <v>919144</v>
       </c>
       <c r="G8" t="n">
-        <v>725283</v>
+        <v>620529</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4635914532672074</v>
+        <v>0.4812265019040206</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>GMRAIRPORT</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8063.5</v>
+        <v>97.39</v>
       </c>
       <c r="C9" t="n">
-        <v>8175</v>
+        <v>98.95</v>
       </c>
       <c r="D9" t="n">
-        <v>7917.5</v>
+        <v>97.03</v>
       </c>
       <c r="E9" t="n">
-        <v>8080</v>
+        <v>97.3</v>
       </c>
       <c r="F9" t="n">
-        <v>271398</v>
+        <v>15749965</v>
       </c>
       <c r="G9" t="n">
-        <v>175320</v>
+        <v>10712271</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5480150581793293</v>
+        <v>0.4702732035065207</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>GMRAIRPORT</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FORTIS</t>
+          <t>NYKAA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>894</v>
+        <v>265.25</v>
       </c>
       <c r="C10" t="n">
-        <v>898.8</v>
+        <v>267.2</v>
       </c>
       <c r="D10" t="n">
-        <v>882.6</v>
+        <v>263.6</v>
       </c>
       <c r="E10" t="n">
-        <v>890.5</v>
+        <v>265</v>
       </c>
       <c r="F10" t="n">
-        <v>1276682</v>
+        <v>4709445</v>
       </c>
       <c r="G10" t="n">
-        <v>899582</v>
+        <v>2956051</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4191946926461401</v>
+        <v>0.5931541776511975</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>FORTIS</t>
+          <t>NYKAA</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>HAVELLS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>273.8</v>
+        <v>1309</v>
       </c>
       <c r="C11" t="n">
-        <v>274.94</v>
+        <v>1337.4</v>
       </c>
       <c r="D11" t="n">
-        <v>270.01</v>
+        <v>1308.6</v>
       </c>
       <c r="E11" t="n">
-        <v>271.6</v>
+        <v>1332</v>
       </c>
       <c r="F11" t="n">
-        <v>2605561</v>
+        <v>896686</v>
       </c>
       <c r="G11" t="n">
-        <v>1802511</v>
+        <v>639788</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4455173921268719</v>
+        <v>0.401536133844336</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>HAVELLS</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>RBLBANK</t>
+          <t>MANKIND</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>316.3</v>
+        <v>2150</v>
       </c>
       <c r="C12" t="n">
-        <v>319.5</v>
+        <v>2206.2</v>
       </c>
       <c r="D12" t="n">
-        <v>312.7</v>
+        <v>2137</v>
       </c>
       <c r="E12" t="n">
-        <v>316.75</v>
+        <v>2200</v>
       </c>
       <c r="F12" t="n">
-        <v>4734160</v>
+        <v>471362</v>
       </c>
       <c r="G12" t="n">
-        <v>3190055</v>
+        <v>297462</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4840371090780566</v>
+        <v>0.5846124883178355</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>RBLBANK</t>
+          <t>MANKIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2424</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2440</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2388.2</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2416.3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>275259</v>
+      </c>
+      <c r="G13" t="n">
+        <v>180997</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.5207931623176075</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>POONAWALLA</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>420.85</v>
+      </c>
+      <c r="C14" t="n">
+        <v>426.4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>417.25</v>
+      </c>
+      <c r="E14" t="n">
+        <v>422.6</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4575565</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2927314</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.5630591730166289</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>POONAWALLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SONACOMS</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>575.8</v>
+      </c>
+      <c r="C15" t="n">
+        <v>585.65</v>
+      </c>
+      <c r="D15" t="n">
+        <v>575.25</v>
+      </c>
+      <c r="E15" t="n">
+        <v>581.9</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1887348</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1308363</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.4425262713788146</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>SONACOMS</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,429 +479,165 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1284.4</v>
+        <v>810</v>
       </c>
       <c r="C2" t="n">
-        <v>1296.4</v>
+        <v>813.05</v>
       </c>
       <c r="D2" t="n">
-        <v>1273.7</v>
+        <v>798</v>
       </c>
       <c r="E2" t="n">
-        <v>1283</v>
+        <v>799.4</v>
       </c>
       <c r="F2" t="n">
-        <v>2108883</v>
+        <v>23876412</v>
       </c>
       <c r="G2" t="n">
-        <v>4606071</v>
+        <v>49135752</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5421514344872235</v>
+        <v>-0.514072522997104</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7243</v>
+        <v>1588.9</v>
       </c>
       <c r="C3" t="n">
-        <v>7296</v>
+        <v>1603.4</v>
       </c>
       <c r="D3" t="n">
-        <v>7215</v>
+        <v>1582</v>
       </c>
       <c r="E3" t="n">
-        <v>7220</v>
+        <v>1589.7</v>
       </c>
       <c r="F3" t="n">
-        <v>353002</v>
+        <v>1918773</v>
       </c>
       <c r="G3" t="n">
-        <v>695282</v>
+        <v>4276868</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4922894595286517</v>
+        <v>-0.5513602477326867</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>474</v>
+        <v>769.7</v>
       </c>
       <c r="C4" t="n">
-        <v>479</v>
+        <v>773.85</v>
       </c>
       <c r="D4" t="n">
-        <v>469.35</v>
+        <v>755.5</v>
       </c>
       <c r="E4" t="n">
-        <v>470.7</v>
+        <v>758.25</v>
       </c>
       <c r="F4" t="n">
-        <v>5478143</v>
+        <v>14257215</v>
       </c>
       <c r="G4" t="n">
-        <v>10992233</v>
+        <v>30562626</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5016351090811121</v>
+        <v>-0.5335081808742482</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>VEDL</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7200</v>
+        <v>1037</v>
       </c>
       <c r="C5" t="n">
-        <v>7300</v>
+        <v>1054.4</v>
       </c>
       <c r="D5" t="n">
-        <v>7184</v>
+        <v>1032.05</v>
       </c>
       <c r="E5" t="n">
-        <v>7268</v>
+        <v>1044</v>
       </c>
       <c r="F5" t="n">
-        <v>260767</v>
+        <v>2050971</v>
       </c>
       <c r="G5" t="n">
-        <v>559841</v>
+        <v>4152949</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5342123924471412</v>
+        <v>-0.5061410578362509</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>AUBANK</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5715</v>
+        <v>2115.2</v>
       </c>
       <c r="C6" t="n">
-        <v>5864.5</v>
+        <v>2126</v>
       </c>
       <c r="D6" t="n">
-        <v>5685</v>
+        <v>2101.6</v>
       </c>
       <c r="E6" t="n">
-        <v>5850</v>
+        <v>2120.5</v>
       </c>
       <c r="F6" t="n">
-        <v>270416</v>
+        <v>263001</v>
       </c>
       <c r="G6" t="n">
-        <v>610941</v>
+        <v>593683</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5573778810065129</v>
+        <v>-0.55700095842394</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>BHEL</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>327.01</v>
-      </c>
-      <c r="C7" t="n">
-        <v>333.79</v>
-      </c>
-      <c r="D7" t="n">
-        <v>322.51</v>
-      </c>
-      <c r="E7" t="n">
-        <v>332</v>
-      </c>
-      <c r="F7" t="n">
-        <v>20292270</v>
-      </c>
-      <c r="G7" t="n">
-        <v>49865330</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-0.593058543882092</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>BHEL</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>HEROMOTOCO</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>5260</v>
-      </c>
-      <c r="C8" t="n">
-        <v>5310</v>
-      </c>
-      <c r="D8" t="n">
-        <v>5252</v>
-      </c>
-      <c r="E8" t="n">
-        <v>5268</v>
-      </c>
-      <c r="F8" t="n">
-        <v>321063</v>
-      </c>
-      <c r="G8" t="n">
-        <v>654258</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-0.5092715717652669</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>HEROMOTOCO</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>ATGL</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>621</v>
-      </c>
-      <c r="C9" t="n">
-        <v>631.7</v>
-      </c>
-      <c r="D9" t="n">
-        <v>612.5</v>
-      </c>
-      <c r="E9" t="n">
-        <v>614.2</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1844260</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3748704</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-0.5080273075708298</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>ATGL</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>TORNTPOWER</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1600</v>
-      </c>
-      <c r="C10" t="n">
-        <v>1631</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1593.4</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1624</v>
-      </c>
-      <c r="F10" t="n">
-        <v>595204</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1442253</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-0.5873095774458434</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>TORNTPOWER</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>HUDCO</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>199.4</v>
-      </c>
-      <c r="C11" t="n">
-        <v>202.88</v>
-      </c>
-      <c r="D11" t="n">
-        <v>198</v>
-      </c>
-      <c r="E11" t="n">
-        <v>198</v>
-      </c>
-      <c r="F11" t="n">
-        <v>3218467</v>
-      </c>
-      <c r="G11" t="n">
-        <v>7287259</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-0.5583432673382406</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>HUDCO</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>KPITTECH</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>734</v>
-      </c>
-      <c r="C12" t="n">
-        <v>749.3</v>
-      </c>
-      <c r="D12" t="n">
-        <v>730.05</v>
-      </c>
-      <c r="E12" t="n">
-        <v>745</v>
-      </c>
-      <c r="F12" t="n">
-        <v>745302</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1674776</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-0.5549840695113855</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>KPITTECH</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>SJVN</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>77.2</v>
-      </c>
-      <c r="C13" t="n">
-        <v>78.34999999999999</v>
-      </c>
-      <c r="D13" t="n">
-        <v>76.52</v>
-      </c>
-      <c r="E13" t="n">
-        <v>76.66</v>
-      </c>
-      <c r="F13" t="n">
-        <v>3511490</v>
-      </c>
-      <c r="G13" t="n">
-        <v>7067252</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-0.5031321933900192</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>SJVN</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>TITAGARH</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>730.6</v>
-      </c>
-      <c r="C14" t="n">
-        <v>741</v>
-      </c>
-      <c r="D14" t="n">
-        <v>730</v>
-      </c>
-      <c r="E14" t="n">
-        <v>737.95</v>
-      </c>
-      <c r="F14" t="n">
-        <v>320230</v>
-      </c>
-      <c r="G14" t="n">
-        <v>699349</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-0.5421027269646486</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>TITAGARH</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
     </row>
@@ -916,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -969,462 +705,594 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1310</v>
+        <v>257.03</v>
       </c>
       <c r="C2" t="n">
-        <v>1325</v>
+        <v>264.8</v>
       </c>
       <c r="D2" t="n">
-        <v>1299.3</v>
+        <v>256.29</v>
       </c>
       <c r="E2" t="n">
-        <v>1314.5</v>
+        <v>262.25</v>
       </c>
       <c r="F2" t="n">
-        <v>10057440</v>
+        <v>45717764</v>
       </c>
       <c r="G2" t="n">
-        <v>7172300</v>
+        <v>29052896</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4022614781869135</v>
+        <v>0.5736043663254775</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>ETERNAL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1578.5</v>
+        <v>3214.1</v>
       </c>
       <c r="C3" t="n">
-        <v>1611.9</v>
+        <v>3249.9</v>
       </c>
       <c r="D3" t="n">
-        <v>1578.4</v>
+        <v>3143</v>
       </c>
       <c r="E3" t="n">
-        <v>1598</v>
+        <v>3150</v>
       </c>
       <c r="F3" t="n">
-        <v>4276868</v>
+        <v>3096787</v>
       </c>
       <c r="G3" t="n">
-        <v>2998603</v>
+        <v>1972188</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4262868409055817</v>
+        <v>0.5702291059473032</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>M&amp;M</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1501</v>
+        <v>13452</v>
       </c>
       <c r="C4" t="n">
-        <v>1510.9</v>
+        <v>13530</v>
       </c>
       <c r="D4" t="n">
-        <v>1489</v>
+        <v>13300</v>
       </c>
       <c r="E4" t="n">
-        <v>1499</v>
+        <v>13379</v>
       </c>
       <c r="F4" t="n">
-        <v>2001948</v>
+        <v>434640</v>
       </c>
       <c r="G4" t="n">
-        <v>1341688</v>
+        <v>292879</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4921114297809923</v>
+        <v>0.4840258263651542</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>MARUTI</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HDFCAMC</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2754</v>
+        <v>1030</v>
       </c>
       <c r="C5" t="n">
-        <v>2816.8</v>
+        <v>1043.35</v>
       </c>
       <c r="D5" t="n">
-        <v>2733.9</v>
+        <v>1017</v>
       </c>
       <c r="E5" t="n">
-        <v>2790</v>
+        <v>1038.55</v>
       </c>
       <c r="F5" t="n">
-        <v>1593751</v>
+        <v>4474181</v>
       </c>
       <c r="G5" t="n">
-        <v>1049876</v>
+        <v>3002043</v>
       </c>
       <c r="H5" t="n">
-        <v>0.518037368222533</v>
+        <v>0.4903787187591916</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>HDFCAMC</t>
+          <t>HINDALCO</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SOLARINDS</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14851</v>
+        <v>7215</v>
       </c>
       <c r="C6" t="n">
-        <v>15169</v>
+        <v>7267</v>
       </c>
       <c r="D6" t="n">
-        <v>14851</v>
+        <v>7136.5</v>
       </c>
       <c r="E6" t="n">
-        <v>14958</v>
+        <v>7220</v>
       </c>
       <c r="F6" t="n">
-        <v>124161</v>
+        <v>497850</v>
       </c>
       <c r="G6" t="n">
-        <v>85713</v>
+        <v>353002</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4485667285009275</v>
+        <v>0.4103319527934686</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>SOLARINDS</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>VBL</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>174.4</v>
+        <v>486.95</v>
       </c>
       <c r="C7" t="n">
-        <v>177.68</v>
+        <v>498.7</v>
       </c>
       <c r="D7" t="n">
-        <v>174</v>
+        <v>484.35</v>
       </c>
       <c r="E7" t="n">
-        <v>174.9</v>
+        <v>495</v>
       </c>
       <c r="F7" t="n">
-        <v>27069051</v>
+        <v>11943145</v>
       </c>
       <c r="G7" t="n">
-        <v>17825908</v>
+        <v>7932444</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5185229835136589</v>
+        <v>0.5056072252133138</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>VBL</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PHOENIXLTD</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1776.4</v>
+        <v>191.38</v>
       </c>
       <c r="C8" t="n">
-        <v>1834.9</v>
+        <v>197.13</v>
       </c>
       <c r="D8" t="n">
-        <v>1776</v>
+        <v>190.4</v>
       </c>
       <c r="E8" t="n">
-        <v>1807</v>
+        <v>194.3</v>
       </c>
       <c r="F8" t="n">
-        <v>919144</v>
+        <v>21651436</v>
       </c>
       <c r="G8" t="n">
-        <v>620529</v>
+        <v>13904723</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4812265019040206</v>
+        <v>0.55712817867713</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>PHOENIXLTD</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GMRAIRPORT</t>
+          <t>MUTHOOTFIN</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>97.39</v>
+        <v>3610.2</v>
       </c>
       <c r="C9" t="n">
-        <v>98.95</v>
+        <v>3646</v>
       </c>
       <c r="D9" t="n">
-        <v>97.03</v>
+        <v>3571.5</v>
       </c>
       <c r="E9" t="n">
-        <v>97.3</v>
+        <v>3593</v>
       </c>
       <c r="F9" t="n">
-        <v>15749965</v>
+        <v>826036</v>
       </c>
       <c r="G9" t="n">
-        <v>10712271</v>
+        <v>522743</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4702732035065207</v>
+        <v>0.5801952393432337</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>GMRAIRPORT</t>
+          <t>MUTHOOTFIN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NYKAA</t>
+          <t>JUBLFOOD</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>265.25</v>
+        <v>474.6</v>
       </c>
       <c r="C10" t="n">
-        <v>267.2</v>
+        <v>494.65</v>
       </c>
       <c r="D10" t="n">
-        <v>263.6</v>
+        <v>473.3</v>
       </c>
       <c r="E10" t="n">
-        <v>265</v>
+        <v>490.35</v>
       </c>
       <c r="F10" t="n">
-        <v>4709445</v>
+        <v>4625853</v>
       </c>
       <c r="G10" t="n">
-        <v>2956051</v>
+        <v>3095871</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5931541776511975</v>
+        <v>0.4942008242591504</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>NYKAA</t>
+          <t>JUBLFOOD</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1309</v>
+        <v>1621</v>
       </c>
       <c r="C11" t="n">
-        <v>1337.4</v>
+        <v>1663.7</v>
       </c>
       <c r="D11" t="n">
-        <v>1308.6</v>
+        <v>1616</v>
       </c>
       <c r="E11" t="n">
-        <v>1332</v>
+        <v>1654</v>
       </c>
       <c r="F11" t="n">
-        <v>896686</v>
+        <v>840616</v>
       </c>
       <c r="G11" t="n">
-        <v>639788</v>
+        <v>595204</v>
       </c>
       <c r="H11" t="n">
-        <v>0.401536133844336</v>
+        <v>0.4123157774477322</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2150</v>
+        <v>5685</v>
       </c>
       <c r="C12" t="n">
-        <v>2206.2</v>
+        <v>5735</v>
       </c>
       <c r="D12" t="n">
-        <v>2137</v>
+        <v>5539</v>
       </c>
       <c r="E12" t="n">
-        <v>2200</v>
+        <v>5550</v>
       </c>
       <c r="F12" t="n">
-        <v>471362</v>
+        <v>199874</v>
       </c>
       <c r="G12" t="n">
-        <v>297462</v>
+        <v>127553</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5846124883178355</v>
+        <v>0.5669878403487177</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>ALKEM</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>UPL</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2424</v>
+        <v>650.8</v>
       </c>
       <c r="C13" t="n">
-        <v>2440</v>
+        <v>657.4</v>
       </c>
       <c r="D13" t="n">
-        <v>2388.2</v>
+        <v>649</v>
       </c>
       <c r="E13" t="n">
-        <v>2416.3</v>
+        <v>654.3</v>
       </c>
       <c r="F13" t="n">
-        <v>275259</v>
+        <v>1709380</v>
       </c>
       <c r="G13" t="n">
-        <v>180997</v>
+        <v>1144716</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5207931623176075</v>
+        <v>0.4932786822233637</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>UPL</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>POONAWALLA</t>
+          <t>IDFCFIRSTB</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>420.85</v>
+        <v>67.94</v>
       </c>
       <c r="C14" t="n">
-        <v>426.4</v>
+        <v>68.58</v>
       </c>
       <c r="D14" t="n">
-        <v>417.25</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>422.6</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>4575565</v>
+        <v>16016883</v>
       </c>
       <c r="G14" t="n">
-        <v>2927314</v>
+        <v>10588919</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5630591730166289</v>
+        <v>0.512607944210358</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>POONAWALLA</t>
+          <t>IDFCFIRSTB</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SONACOMS</t>
+          <t>SUPREMEIND</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>575.8</v>
+        <v>3651.1</v>
       </c>
       <c r="C15" t="n">
-        <v>585.65</v>
+        <v>3737.9</v>
       </c>
       <c r="D15" t="n">
-        <v>575.25</v>
+        <v>3645</v>
       </c>
       <c r="E15" t="n">
-        <v>581.9</v>
+        <v>3697</v>
       </c>
       <c r="F15" t="n">
-        <v>1887348</v>
+        <v>266549</v>
       </c>
       <c r="G15" t="n">
-        <v>1308363</v>
+        <v>179930</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4425262713788146</v>
+        <v>0.4814038792863892</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SONACOMS</t>
+          <t>SUPREMEIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SBICARD</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>680</v>
+      </c>
+      <c r="C16" t="n">
+        <v>691.35</v>
+      </c>
+      <c r="D16" t="n">
+        <v>675.5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>685.5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1167501</v>
+      </c>
+      <c r="G16" t="n">
+        <v>757476</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.5413042789474518</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>SBICARD</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>559.95</v>
+      </c>
+      <c r="C17" t="n">
+        <v>577.95</v>
+      </c>
+      <c r="D17" t="n">
+        <v>556.2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>570</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2811624</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1801968</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.560307397245678</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>NBCC</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>93.22</v>
+      </c>
+      <c r="C18" t="n">
+        <v>94.73999999999999</v>
+      </c>
+      <c r="D18" t="n">
+        <v>92.81999999999999</v>
+      </c>
+      <c r="E18" t="n">
+        <v>94</v>
+      </c>
+      <c r="F18" t="n">
+        <v>11345558</v>
+      </c>
+      <c r="G18" t="n">
+        <v>7224140</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.5705063855351641</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>NBCC</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>GRANULES</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>667.75</v>
+      </c>
+      <c r="C19" t="n">
+        <v>689.9</v>
+      </c>
+      <c r="D19" t="n">
+        <v>666.9</v>
+      </c>
+      <c r="E19" t="n">
+        <v>674</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1315243</v>
+      </c>
+      <c r="G19" t="n">
+        <v>932037</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.4111489136160904</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>GRANULES</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,165 +479,429 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>810</v>
+        <v>2529</v>
       </c>
       <c r="C2" t="n">
-        <v>813.05</v>
+        <v>2559.5</v>
       </c>
       <c r="D2" t="n">
-        <v>798</v>
+        <v>2516.3</v>
       </c>
       <c r="E2" t="n">
-        <v>799.4</v>
+        <v>2518.2</v>
       </c>
       <c r="F2" t="n">
-        <v>23876412</v>
+        <v>2509050</v>
       </c>
       <c r="G2" t="n">
-        <v>49135752</v>
+        <v>5232045</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.514072522997104</v>
+        <v>-0.5204456383689361</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>TCS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1588.9</v>
+        <v>304</v>
       </c>
       <c r="C3" t="n">
-        <v>1603.4</v>
+        <v>306.35</v>
       </c>
       <c r="D3" t="n">
-        <v>1582</v>
+        <v>303.25</v>
       </c>
       <c r="E3" t="n">
-        <v>1589.7</v>
+        <v>305.35</v>
       </c>
       <c r="F3" t="n">
-        <v>1918773</v>
+        <v>10701849</v>
       </c>
       <c r="G3" t="n">
-        <v>4276868</v>
+        <v>24500511</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5513602477326867</v>
+        <v>-0.5631989471566532</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>ITC</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>769.7</v>
+        <v>7685</v>
       </c>
       <c r="C4" t="n">
-        <v>773.85</v>
+        <v>7815</v>
       </c>
       <c r="D4" t="n">
-        <v>755.5</v>
+        <v>7601</v>
       </c>
       <c r="E4" t="n">
-        <v>758.25</v>
+        <v>7773</v>
       </c>
       <c r="F4" t="n">
-        <v>14257215</v>
+        <v>304110</v>
       </c>
       <c r="G4" t="n">
-        <v>30562626</v>
+        <v>608446</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5335081808742482</v>
+        <v>-0.5001857190284759</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>MUTHOOTFIN</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1037</v>
+        <v>3579</v>
       </c>
       <c r="C5" t="n">
-        <v>1054.4</v>
+        <v>3609</v>
       </c>
       <c r="D5" t="n">
-        <v>1032.05</v>
+        <v>3544</v>
       </c>
       <c r="E5" t="n">
-        <v>1044</v>
+        <v>3570</v>
       </c>
       <c r="F5" t="n">
-        <v>2050971</v>
+        <v>338452</v>
       </c>
       <c r="G5" t="n">
-        <v>4152949</v>
+        <v>826036</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5061410578362509</v>
+        <v>-0.5902696734767008</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>MUTHOOTFIN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2115.2</v>
+        <v>1408</v>
       </c>
       <c r="C6" t="n">
-        <v>2126</v>
+        <v>1412</v>
       </c>
       <c r="D6" t="n">
-        <v>2101.6</v>
+        <v>1396.8</v>
       </c>
       <c r="E6" t="n">
-        <v>2120.5</v>
+        <v>1404.5</v>
       </c>
       <c r="F6" t="n">
-        <v>263001</v>
+        <v>319278</v>
       </c>
       <c r="G6" t="n">
-        <v>593683</v>
+        <v>629961</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.55700095842394</v>
+        <v>-0.4931781491235172</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>EXIDEIND</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>353.8</v>
+      </c>
+      <c r="C7" t="n">
+        <v>359.85</v>
+      </c>
+      <c r="D7" t="n">
+        <v>345.05</v>
+      </c>
+      <c r="E7" t="n">
+        <v>347.45</v>
+      </c>
+      <c r="F7" t="n">
+        <v>6747931</v>
+      </c>
+      <c r="G7" t="n">
+        <v>15696406</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.5700970655320715</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>EXIDEIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FORTIS</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>919.5</v>
+      </c>
+      <c r="C8" t="n">
+        <v>932.3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>913.35</v>
+      </c>
+      <c r="E8" t="n">
+        <v>924.95</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1261689</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2678373</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.5289345434709803</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>FORTIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SJVN</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="C9" t="n">
+        <v>82.09</v>
+      </c>
+      <c r="D9" t="n">
+        <v>78.70999999999999</v>
+      </c>
+      <c r="E9" t="n">
+        <v>79</v>
+      </c>
+      <c r="F9" t="n">
+        <v>8426676</v>
+      </c>
+      <c r="G9" t="n">
+        <v>16968781</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.5034012166224551</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>SJVN</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PATANJALI</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>471.9</v>
+      </c>
+      <c r="C10" t="n">
+        <v>472.4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>466.65</v>
+      </c>
+      <c r="E10" t="n">
+        <v>467</v>
+      </c>
+      <c r="F10" t="n">
+        <v>758763</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1656672</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.5419956394506577</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>PATANJALI</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CDSL</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1317</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1335</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1312.6</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1323.8</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1334615</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3311575</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.5969848184021198</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>CDSL</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PNBHOUSING</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>981.5</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1011.7</v>
+      </c>
+      <c r="D12" t="n">
+        <v>981</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1003.45</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1723043</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3936595</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.5623011765243822</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>PNBHOUSING</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>POONAWALLA</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>420</v>
+      </c>
+      <c r="C13" t="n">
+        <v>428.4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>417.4</v>
+      </c>
+      <c r="E13" t="n">
+        <v>422.1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1311394</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2719870</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.517846808854835</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>POONAWALLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NUVAMA</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1363.3</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1382</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1360</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1377</v>
+      </c>
+      <c r="F14" t="n">
+        <v>241228</v>
+      </c>
+      <c r="G14" t="n">
+        <v>514586</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.531219271414302</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>NUVAMA</t>
         </is>
       </c>
     </row>
@@ -652,7 +916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -705,594 +969,495 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>257.03</v>
+        <v>792</v>
       </c>
       <c r="C2" t="n">
-        <v>264.8</v>
+        <v>796.65</v>
       </c>
       <c r="D2" t="n">
-        <v>256.29</v>
+        <v>782.5</v>
       </c>
       <c r="E2" t="n">
-        <v>262.25</v>
+        <v>783.9</v>
       </c>
       <c r="F2" t="n">
-        <v>45717764</v>
+        <v>37677616</v>
       </c>
       <c r="G2" t="n">
-        <v>29052896</v>
+        <v>23876412</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5736043663254775</v>
+        <v>0.5780267152367785</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3214.1</v>
+        <v>1348.4</v>
       </c>
       <c r="C3" t="n">
-        <v>3249.9</v>
+        <v>1354</v>
       </c>
       <c r="D3" t="n">
-        <v>3143</v>
+        <v>1343.5</v>
       </c>
       <c r="E3" t="n">
-        <v>3150</v>
+        <v>1347</v>
       </c>
       <c r="F3" t="n">
-        <v>3096787</v>
+        <v>20111792</v>
       </c>
       <c r="G3" t="n">
-        <v>1972188</v>
+        <v>13613487</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5702291059473032</v>
+        <v>0.4773431671106749</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13452</v>
+        <v>3105</v>
       </c>
       <c r="C4" t="n">
-        <v>13530</v>
+        <v>3114.7</v>
       </c>
       <c r="D4" t="n">
-        <v>13300</v>
+        <v>3032.2</v>
       </c>
       <c r="E4" t="n">
-        <v>13379</v>
+        <v>3060</v>
       </c>
       <c r="F4" t="n">
-        <v>434640</v>
+        <v>4540875</v>
       </c>
       <c r="G4" t="n">
-        <v>292879</v>
+        <v>3096787</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4840258263651542</v>
+        <v>0.4663181549134635</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>M&amp;M</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1030</v>
+        <v>926.1</v>
       </c>
       <c r="C5" t="n">
-        <v>1043.35</v>
+        <v>929.85</v>
       </c>
       <c r="D5" t="n">
-        <v>1017</v>
+        <v>909.35</v>
       </c>
       <c r="E5" t="n">
-        <v>1038.55</v>
+        <v>916.5</v>
       </c>
       <c r="F5" t="n">
-        <v>4474181</v>
+        <v>9143598</v>
       </c>
       <c r="G5" t="n">
-        <v>3002043</v>
+        <v>5759028</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4903787187591916</v>
+        <v>0.5876981323931747</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7215</v>
+        <v>1369</v>
       </c>
       <c r="C6" t="n">
-        <v>7267</v>
+        <v>1384.2</v>
       </c>
       <c r="D6" t="n">
-        <v>7136.5</v>
+        <v>1365.4</v>
       </c>
       <c r="E6" t="n">
-        <v>7220</v>
+        <v>1369.2</v>
       </c>
       <c r="F6" t="n">
-        <v>497850</v>
+        <v>5671255</v>
       </c>
       <c r="G6" t="n">
-        <v>353002</v>
+        <v>3997911</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4103319527934686</v>
+        <v>0.4185545901346979</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>AXISBANK</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VBL</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>486.95</v>
+        <v>1669</v>
       </c>
       <c r="C7" t="n">
-        <v>498.7</v>
+        <v>1713</v>
       </c>
       <c r="D7" t="n">
-        <v>484.35</v>
+        <v>1661.2</v>
       </c>
       <c r="E7" t="n">
-        <v>495</v>
+        <v>1678</v>
       </c>
       <c r="F7" t="n">
-        <v>11943145</v>
+        <v>3245164</v>
       </c>
       <c r="G7" t="n">
-        <v>7932444</v>
+        <v>2169514</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5056072252133138</v>
+        <v>0.4958022856731968</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>VBL</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>191.38</v>
+        <v>9575</v>
       </c>
       <c r="C8" t="n">
-        <v>197.13</v>
+        <v>9591</v>
       </c>
       <c r="D8" t="n">
-        <v>190.4</v>
+        <v>9477</v>
       </c>
       <c r="E8" t="n">
-        <v>194.3</v>
+        <v>9557.5</v>
       </c>
       <c r="F8" t="n">
-        <v>21651436</v>
+        <v>444028</v>
       </c>
       <c r="G8" t="n">
-        <v>13904723</v>
+        <v>301870</v>
       </c>
       <c r="H8" t="n">
-        <v>0.55712817867713</v>
+        <v>0.4709245701792162</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3610.2</v>
+        <v>146.4</v>
       </c>
       <c r="C9" t="n">
-        <v>3646</v>
+        <v>147.35</v>
       </c>
       <c r="D9" t="n">
-        <v>3571.5</v>
+        <v>145.1</v>
       </c>
       <c r="E9" t="n">
-        <v>3593</v>
+        <v>145.58</v>
       </c>
       <c r="F9" t="n">
-        <v>826036</v>
+        <v>11146793</v>
       </c>
       <c r="G9" t="n">
-        <v>522743</v>
+        <v>7680576</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5801952393432337</v>
+        <v>0.4512964913048188</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>IOC</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>JUBLFOOD</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>474.6</v>
+        <v>11249</v>
       </c>
       <c r="C10" t="n">
-        <v>494.65</v>
+        <v>11249</v>
       </c>
       <c r="D10" t="n">
-        <v>473.3</v>
+        <v>10820</v>
       </c>
       <c r="E10" t="n">
-        <v>490.35</v>
+        <v>10829</v>
       </c>
       <c r="F10" t="n">
-        <v>4625853</v>
+        <v>733524</v>
       </c>
       <c r="G10" t="n">
-        <v>3095871</v>
+        <v>474026</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4942008242591504</v>
+        <v>0.5474341069899119</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>JUBLFOOD</t>
+          <t>DIXON</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TORNTPOWER</t>
+          <t>HINDPETRO</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1621</v>
+        <v>377.35</v>
       </c>
       <c r="C11" t="n">
-        <v>1663.7</v>
+        <v>378.9</v>
       </c>
       <c r="D11" t="n">
-        <v>1616</v>
+        <v>371.1</v>
       </c>
       <c r="E11" t="n">
-        <v>1654</v>
+        <v>377.4</v>
       </c>
       <c r="F11" t="n">
-        <v>840616</v>
+        <v>6774817</v>
       </c>
       <c r="G11" t="n">
-        <v>595204</v>
+        <v>4754747</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4123157774477322</v>
+        <v>0.4248533097554928</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>TORNTPOWER</t>
+          <t>HINDPETRO</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5685</v>
+        <v>1648.1</v>
       </c>
       <c r="C12" t="n">
-        <v>5735</v>
+        <v>1741</v>
       </c>
       <c r="D12" t="n">
-        <v>5539</v>
+        <v>1645.1</v>
       </c>
       <c r="E12" t="n">
-        <v>5550</v>
+        <v>1735</v>
       </c>
       <c r="F12" t="n">
-        <v>199874</v>
+        <v>1220697</v>
       </c>
       <c r="G12" t="n">
-        <v>127553</v>
+        <v>840616</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5669878403487177</v>
+        <v>0.4521458073603167</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>UPL</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>650.8</v>
+        <v>774.95</v>
       </c>
       <c r="C13" t="n">
-        <v>657.4</v>
+        <v>780.1</v>
       </c>
       <c r="D13" t="n">
-        <v>649</v>
+        <v>765.65</v>
       </c>
       <c r="E13" t="n">
-        <v>654.3</v>
+        <v>778</v>
       </c>
       <c r="F13" t="n">
-        <v>1709380</v>
+        <v>2177488</v>
       </c>
       <c r="G13" t="n">
-        <v>1144716</v>
+        <v>1529460</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4932786822233637</v>
+        <v>0.4236972526251095</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>UPL</t>
+          <t>MARICO</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IDFCFIRSTB</t>
+          <t>UPL</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>67.94</v>
+        <v>653.5</v>
       </c>
       <c r="C14" t="n">
-        <v>68.58</v>
+        <v>656.55</v>
       </c>
       <c r="D14" t="n">
-        <v>67.59999999999999</v>
+        <v>638.45</v>
       </c>
       <c r="E14" t="n">
-        <v>68.40000000000001</v>
+        <v>642</v>
       </c>
       <c r="F14" t="n">
-        <v>16016883</v>
+        <v>2471569</v>
       </c>
       <c r="G14" t="n">
-        <v>10588919</v>
+        <v>1709380</v>
       </c>
       <c r="H14" t="n">
-        <v>0.512607944210358</v>
+        <v>0.4458862277550925</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>IDFCFIRSTB</t>
+          <t>UPL</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SUPREMEIND</t>
+          <t>BLUESTARCO</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3651.1</v>
+        <v>1898</v>
       </c>
       <c r="C15" t="n">
-        <v>3737.9</v>
+        <v>1898</v>
       </c>
       <c r="D15" t="n">
-        <v>3645</v>
+        <v>1820.3</v>
       </c>
       <c r="E15" t="n">
-        <v>3697</v>
+        <v>1836</v>
       </c>
       <c r="F15" t="n">
-        <v>266549</v>
+        <v>777802</v>
       </c>
       <c r="G15" t="n">
-        <v>179930</v>
+        <v>504021</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4814038792863892</v>
+        <v>0.543193636773071</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SUPREMEIND</t>
+          <t>BLUESTARCO</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SBICARD</t>
+          <t>COLPAL</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>680</v>
+        <v>2110.3</v>
       </c>
       <c r="C16" t="n">
-        <v>691.35</v>
+        <v>2155</v>
       </c>
       <c r="D16" t="n">
-        <v>675.5</v>
+        <v>2057.6</v>
       </c>
       <c r="E16" t="n">
-        <v>685.5</v>
+        <v>2145</v>
       </c>
       <c r="F16" t="n">
-        <v>1167501</v>
+        <v>649058</v>
       </c>
       <c r="G16" t="n">
-        <v>757476</v>
+        <v>450554</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5413042789474518</v>
+        <v>0.4405776000213071</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>SBICARD</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>PGEL</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>559.95</v>
-      </c>
-      <c r="C17" t="n">
-        <v>577.95</v>
-      </c>
-      <c r="D17" t="n">
-        <v>556.2</v>
-      </c>
-      <c r="E17" t="n">
-        <v>570</v>
-      </c>
-      <c r="F17" t="n">
-        <v>2811624</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1801968</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.560307397245678</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>PGEL</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>NBCC</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>93.22</v>
-      </c>
-      <c r="C18" t="n">
-        <v>94.73999999999999</v>
-      </c>
-      <c r="D18" t="n">
-        <v>92.81999999999999</v>
-      </c>
-      <c r="E18" t="n">
-        <v>94</v>
-      </c>
-      <c r="F18" t="n">
-        <v>11345558</v>
-      </c>
-      <c r="G18" t="n">
-        <v>7224140</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.5705063855351641</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>NBCC</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>GRANULES</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>667.75</v>
-      </c>
-      <c r="C19" t="n">
-        <v>689.9</v>
-      </c>
-      <c r="D19" t="n">
-        <v>666.9</v>
-      </c>
-      <c r="E19" t="n">
-        <v>674</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1315243</v>
-      </c>
-      <c r="G19" t="n">
-        <v>932037</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.4111489136160904</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>GRANULES</t>
+          <t>COLPAL</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,429 +479,561 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>JIOFIN</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2529</v>
+        <v>252</v>
       </c>
       <c r="C2" t="n">
-        <v>2559.5</v>
+        <v>253.2</v>
       </c>
       <c r="D2" t="n">
-        <v>2516.3</v>
+        <v>244.1</v>
       </c>
       <c r="E2" t="n">
-        <v>2518.2</v>
+        <v>245.8</v>
       </c>
       <c r="F2" t="n">
-        <v>2509050</v>
+        <v>32701729</v>
       </c>
       <c r="G2" t="n">
-        <v>5232045</v>
+        <v>74432271</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5204456383689361</v>
+        <v>-0.5606511992627499</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>JIOFIN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>304</v>
+        <v>3047.7</v>
       </c>
       <c r="C3" t="n">
-        <v>306.35</v>
+        <v>3089</v>
       </c>
       <c r="D3" t="n">
-        <v>303.25</v>
+        <v>3035</v>
       </c>
       <c r="E3" t="n">
-        <v>305.35</v>
+        <v>3040</v>
       </c>
       <c r="F3" t="n">
-        <v>10701849</v>
+        <v>2300917</v>
       </c>
       <c r="G3" t="n">
-        <v>24500511</v>
+        <v>4540875</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5631989471566532</v>
+        <v>-0.4932877474055111</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>M&amp;M</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7685</v>
+        <v>920</v>
       </c>
       <c r="C4" t="n">
-        <v>7815</v>
+        <v>924.7</v>
       </c>
       <c r="D4" t="n">
-        <v>7601</v>
+        <v>909.8</v>
       </c>
       <c r="E4" t="n">
-        <v>7773</v>
+        <v>922.1</v>
       </c>
       <c r="F4" t="n">
-        <v>304110</v>
+        <v>3982355</v>
       </c>
       <c r="G4" t="n">
-        <v>608446</v>
+        <v>9143598</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5001857190284759</v>
+        <v>-0.564465213803144</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3579</v>
+        <v>9600</v>
       </c>
       <c r="C5" t="n">
-        <v>3609</v>
+        <v>9663</v>
       </c>
       <c r="D5" t="n">
-        <v>3544</v>
+        <v>9528</v>
       </c>
       <c r="E5" t="n">
-        <v>3570</v>
+        <v>9581</v>
       </c>
       <c r="F5" t="n">
-        <v>338452</v>
+        <v>190469</v>
       </c>
       <c r="G5" t="n">
-        <v>826036</v>
+        <v>444028</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5902696734767008</v>
+        <v>-0.5710428171196411</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1408</v>
+        <v>179.3</v>
       </c>
       <c r="C6" t="n">
-        <v>1412</v>
+        <v>180.75</v>
       </c>
       <c r="D6" t="n">
-        <v>1396.8</v>
+        <v>174.4</v>
       </c>
       <c r="E6" t="n">
-        <v>1404.5</v>
+        <v>176.6</v>
       </c>
       <c r="F6" t="n">
-        <v>319278</v>
+        <v>27300659</v>
       </c>
       <c r="G6" t="n">
-        <v>629961</v>
+        <v>65651090</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4931781491235172</v>
+        <v>-0.5841552821133663</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EXIDEIND</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>353.8</v>
+        <v>636.85</v>
       </c>
       <c r="C7" t="n">
-        <v>359.85</v>
+        <v>641.55</v>
       </c>
       <c r="D7" t="n">
-        <v>345.05</v>
+        <v>630.4</v>
       </c>
       <c r="E7" t="n">
-        <v>347.45</v>
+        <v>637.05</v>
       </c>
       <c r="F7" t="n">
-        <v>6747931</v>
+        <v>2239399</v>
       </c>
       <c r="G7" t="n">
-        <v>15696406</v>
+        <v>4493765</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5700970655320715</v>
+        <v>-0.5016653073758863</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>EXIDEIND</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FORTIS</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>919.5</v>
+        <v>128.07</v>
       </c>
       <c r="C8" t="n">
-        <v>932.3</v>
+        <v>129.1</v>
       </c>
       <c r="D8" t="n">
-        <v>913.35</v>
+        <v>125.33</v>
       </c>
       <c r="E8" t="n">
-        <v>924.95</v>
+        <v>125.9</v>
       </c>
       <c r="F8" t="n">
-        <v>1261689</v>
+        <v>11238446</v>
       </c>
       <c r="G8" t="n">
-        <v>2678373</v>
+        <v>23191134</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5289345434709803</v>
+        <v>-0.5153990313712128</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>FORTIS</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SJVN</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>80.59999999999999</v>
+        <v>3882</v>
       </c>
       <c r="C9" t="n">
-        <v>82.09</v>
+        <v>3893.6</v>
       </c>
       <c r="D9" t="n">
-        <v>78.70999999999999</v>
+        <v>3767.9</v>
       </c>
       <c r="E9" t="n">
-        <v>79</v>
+        <v>3817</v>
       </c>
       <c r="F9" t="n">
-        <v>8426676</v>
+        <v>315661</v>
       </c>
       <c r="G9" t="n">
-        <v>16968781</v>
+        <v>663008</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5034012166224551</v>
+        <v>-0.5238956392683044</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SJVN</t>
+          <t>SIEMENS</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PATANJALI</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>471.9</v>
+        <v>948</v>
       </c>
       <c r="C10" t="n">
-        <v>472.4</v>
+        <v>951.75</v>
       </c>
       <c r="D10" t="n">
-        <v>466.65</v>
+        <v>922.55</v>
       </c>
       <c r="E10" t="n">
-        <v>467</v>
+        <v>926.95</v>
       </c>
       <c r="F10" t="n">
-        <v>758763</v>
+        <v>701337</v>
       </c>
       <c r="G10" t="n">
-        <v>1656672</v>
+        <v>1693451</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5419956394506577</v>
+        <v>-0.5858533845974876</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>PATANJALI</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1317</v>
+        <v>2351</v>
       </c>
       <c r="C11" t="n">
-        <v>1335</v>
+        <v>2372.8</v>
       </c>
       <c r="D11" t="n">
-        <v>1312.6</v>
+        <v>2283.2</v>
       </c>
       <c r="E11" t="n">
-        <v>1323.8</v>
+        <v>2287</v>
       </c>
       <c r="F11" t="n">
-        <v>1334615</v>
+        <v>838461</v>
       </c>
       <c r="G11" t="n">
-        <v>3311575</v>
+        <v>1703667</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5969848184021198</v>
+        <v>-0.5078492451869996</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>GLENMARK</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PNBHOUSING</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>981.5</v>
+        <v>1685</v>
       </c>
       <c r="C12" t="n">
-        <v>1011.7</v>
+        <v>1701.1</v>
       </c>
       <c r="D12" t="n">
-        <v>981</v>
+        <v>1667</v>
       </c>
       <c r="E12" t="n">
-        <v>1003.45</v>
+        <v>1695</v>
       </c>
       <c r="F12" t="n">
-        <v>1723043</v>
+        <v>1113981</v>
       </c>
       <c r="G12" t="n">
-        <v>3936595</v>
+        <v>2260644</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5623011765243822</v>
+        <v>-0.5072284711790092</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>PNBHOUSING</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>POONAWALLA</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>420</v>
+        <v>1436.9</v>
       </c>
       <c r="C13" t="n">
-        <v>428.4</v>
+        <v>1446</v>
       </c>
       <c r="D13" t="n">
-        <v>417.4</v>
+        <v>1411.7</v>
       </c>
       <c r="E13" t="n">
-        <v>422.1</v>
+        <v>1414</v>
       </c>
       <c r="F13" t="n">
-        <v>1311394</v>
+        <v>967660</v>
       </c>
       <c r="G13" t="n">
-        <v>2719870</v>
+        <v>2238307</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.517846808854835</v>
+        <v>-0.5676821812200025</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>POONAWALLA</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NUVAMA</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1363.3</v>
+        <v>1884</v>
       </c>
       <c r="C14" t="n">
-        <v>1382</v>
+        <v>1892.1</v>
       </c>
       <c r="D14" t="n">
-        <v>1360</v>
+        <v>1836</v>
       </c>
       <c r="E14" t="n">
-        <v>1377</v>
+        <v>1863</v>
       </c>
       <c r="F14" t="n">
-        <v>241228</v>
+        <v>680205</v>
       </c>
       <c r="G14" t="n">
-        <v>514586</v>
+        <v>1398269</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.531219271414302</v>
+        <v>-0.513537809963605</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>NUVAMA</t>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SRF</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2559</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2563.7</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2472.2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2494.5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>411464</v>
+      </c>
+      <c r="G15" t="n">
+        <v>950680</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.5671898009845584</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>SRF</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SJVN</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>79</v>
+      </c>
+      <c r="C16" t="n">
+        <v>79.68000000000001</v>
+      </c>
+      <c r="D16" t="n">
+        <v>76.83</v>
+      </c>
+      <c r="E16" t="n">
+        <v>78.04000000000001</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3627404</v>
+      </c>
+      <c r="G16" t="n">
+        <v>8426676</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.5695332299473719</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>SJVN</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CAMS</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>773</v>
+      </c>
+      <c r="C17" t="n">
+        <v>775.85</v>
+      </c>
+      <c r="D17" t="n">
+        <v>755</v>
+      </c>
+      <c r="E17" t="n">
+        <v>760</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1458679</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2996865</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.5132650286215762</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>CAMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CROMPTON</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>254.63</v>
+      </c>
+      <c r="C18" t="n">
+        <v>257</v>
+      </c>
+      <c r="D18" t="n">
+        <v>248.31</v>
+      </c>
+      <c r="E18" t="n">
+        <v>250</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2472229</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5335493</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.5366446924398551</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>CROMPTON</t>
         </is>
       </c>
     </row>
@@ -916,7 +1048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -969,495 +1101,363 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>792</v>
+        <v>306.65</v>
       </c>
       <c r="C2" t="n">
-        <v>796.65</v>
+        <v>306.65</v>
       </c>
       <c r="D2" t="n">
-        <v>782.5</v>
+        <v>301.1</v>
       </c>
       <c r="E2" t="n">
-        <v>783.9</v>
+        <v>301.45</v>
       </c>
       <c r="F2" t="n">
-        <v>37677616</v>
+        <v>17011704</v>
       </c>
       <c r="G2" t="n">
-        <v>23876412</v>
+        <v>10701849</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5780267152367785</v>
+        <v>0.5896041889583753</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>ITC</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1348.4</v>
+        <v>4475.5</v>
       </c>
       <c r="C3" t="n">
-        <v>1354</v>
+        <v>4486.6</v>
       </c>
       <c r="D3" t="n">
-        <v>1343.5</v>
+        <v>4361.4</v>
       </c>
       <c r="E3" t="n">
-        <v>1347</v>
+        <v>4416</v>
       </c>
       <c r="F3" t="n">
-        <v>20111792</v>
+        <v>958536</v>
       </c>
       <c r="G3" t="n">
-        <v>13613487</v>
+        <v>680187</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4773431671106749</v>
+        <v>0.4092242280431705</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>TITAN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3105</v>
+        <v>12203</v>
       </c>
       <c r="C4" t="n">
-        <v>3114.7</v>
+        <v>12246</v>
       </c>
       <c r="D4" t="n">
-        <v>3032.2</v>
+        <v>11954</v>
       </c>
       <c r="E4" t="n">
-        <v>3060</v>
+        <v>12021</v>
       </c>
       <c r="F4" t="n">
-        <v>4540875</v>
+        <v>349586</v>
       </c>
       <c r="G4" t="n">
-        <v>3096787</v>
+        <v>227223</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4663181549134635</v>
+        <v>0.5385150270879269</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>AMBUJACEM</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>926.1</v>
+        <v>451</v>
       </c>
       <c r="C5" t="n">
-        <v>929.85</v>
+        <v>457.7</v>
       </c>
       <c r="D5" t="n">
-        <v>909.35</v>
+        <v>440.4</v>
       </c>
       <c r="E5" t="n">
-        <v>916.5</v>
+        <v>450.3</v>
       </c>
       <c r="F5" t="n">
-        <v>9143598</v>
+        <v>3729295</v>
       </c>
       <c r="G5" t="n">
-        <v>5759028</v>
+        <v>2393788</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5876981323931747</v>
+        <v>0.5579052948715593</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>AMBUJACEM</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>BOSCHLTD</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1369</v>
+        <v>37495</v>
       </c>
       <c r="C6" t="n">
-        <v>1384.2</v>
+        <v>37690</v>
       </c>
       <c r="D6" t="n">
-        <v>1365.4</v>
+        <v>36295</v>
       </c>
       <c r="E6" t="n">
-        <v>1369.2</v>
+        <v>36800</v>
       </c>
       <c r="F6" t="n">
-        <v>5671255</v>
+        <v>30157</v>
       </c>
       <c r="G6" t="n">
-        <v>3997911</v>
+        <v>20767</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4185545901346979</v>
+        <v>0.4521596764096885</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>BOSCHLTD</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1669</v>
+        <v>1406</v>
       </c>
       <c r="C7" t="n">
-        <v>1713</v>
+        <v>1408.9</v>
       </c>
       <c r="D7" t="n">
-        <v>1661.2</v>
+        <v>1389.4</v>
       </c>
       <c r="E7" t="n">
-        <v>1678</v>
+        <v>1392</v>
       </c>
       <c r="F7" t="n">
-        <v>3245164</v>
+        <v>506429</v>
       </c>
       <c r="G7" t="n">
-        <v>2169514</v>
+        <v>319278</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4958022856731968</v>
+        <v>0.5861694197533184</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9575</v>
+        <v>81.48</v>
       </c>
       <c r="C8" t="n">
-        <v>9591</v>
+        <v>82.28</v>
       </c>
       <c r="D8" t="n">
-        <v>9477</v>
+        <v>79.98</v>
       </c>
       <c r="E8" t="n">
-        <v>9557.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>444028</v>
+        <v>14088780</v>
       </c>
       <c r="G8" t="n">
-        <v>301870</v>
+        <v>9025789</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4709245701792162</v>
+        <v>0.5609471925390678</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>NHPC</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>ANGELONE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>146.4</v>
+        <v>322.81</v>
       </c>
       <c r="C9" t="n">
-        <v>147.35</v>
+        <v>323</v>
       </c>
       <c r="D9" t="n">
-        <v>145.1</v>
+        <v>309.51</v>
       </c>
       <c r="E9" t="n">
-        <v>145.58</v>
+        <v>314.29</v>
       </c>
       <c r="F9" t="n">
-        <v>11146793</v>
+        <v>9294838</v>
       </c>
       <c r="G9" t="n">
-        <v>7680576</v>
+        <v>6611292</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4512964913048188</v>
+        <v>0.405903414945218</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>ANGELONE</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11249</v>
+        <v>128.4</v>
       </c>
       <c r="C10" t="n">
-        <v>11249</v>
+        <v>129.7</v>
       </c>
       <c r="D10" t="n">
-        <v>10820</v>
+        <v>122.34</v>
       </c>
       <c r="E10" t="n">
-        <v>10829</v>
+        <v>123.19</v>
       </c>
       <c r="F10" t="n">
-        <v>733524</v>
+        <v>18209699</v>
       </c>
       <c r="G10" t="n">
-        <v>474026</v>
+        <v>12806668</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5474341069899119</v>
+        <v>0.4218920175021325</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>IEX</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HINDPETRO</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>377.35</v>
+        <v>445</v>
       </c>
       <c r="C11" t="n">
-        <v>378.9</v>
+        <v>451.85</v>
       </c>
       <c r="D11" t="n">
-        <v>371.1</v>
+        <v>441.65</v>
       </c>
       <c r="E11" t="n">
-        <v>377.4</v>
+        <v>447.95</v>
       </c>
       <c r="F11" t="n">
-        <v>6774817</v>
+        <v>4832080</v>
       </c>
       <c r="G11" t="n">
-        <v>4754747</v>
+        <v>3195024</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4248533097554928</v>
+        <v>0.5123767458397809</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>HINDPETRO</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TORNTPOWER</t>
+          <t>TITAGARH</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1648.1</v>
+        <v>743.55</v>
       </c>
       <c r="C12" t="n">
-        <v>1741</v>
+        <v>761.95</v>
       </c>
       <c r="D12" t="n">
-        <v>1645.1</v>
+        <v>722</v>
       </c>
       <c r="E12" t="n">
-        <v>1735</v>
+        <v>760</v>
       </c>
       <c r="F12" t="n">
-        <v>1220697</v>
+        <v>1031823</v>
       </c>
       <c r="G12" t="n">
-        <v>840616</v>
+        <v>680079</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4521458073603167</v>
+        <v>0.5172105005447897</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>TORNTPOWER</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>MARICO</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>774.95</v>
-      </c>
-      <c r="C13" t="n">
-        <v>780.1</v>
-      </c>
-      <c r="D13" t="n">
-        <v>765.65</v>
-      </c>
-      <c r="E13" t="n">
-        <v>778</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2177488</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1529460</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.4236972526251095</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>MARICO</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>UPL</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>653.5</v>
-      </c>
-      <c r="C14" t="n">
-        <v>656.55</v>
-      </c>
-      <c r="D14" t="n">
-        <v>638.45</v>
-      </c>
-      <c r="E14" t="n">
-        <v>642</v>
-      </c>
-      <c r="F14" t="n">
-        <v>2471569</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1709380</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.4458862277550925</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>UPL</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>BLUESTARCO</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1898</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1898</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1820.3</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1836</v>
-      </c>
-      <c r="F15" t="n">
-        <v>777802</v>
-      </c>
-      <c r="G15" t="n">
-        <v>504021</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.543193636773071</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>BLUESTARCO</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>COLPAL</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>2110.3</v>
-      </c>
-      <c r="C16" t="n">
-        <v>2155</v>
-      </c>
-      <c r="D16" t="n">
-        <v>2057.6</v>
-      </c>
-      <c r="E16" t="n">
-        <v>2145</v>
-      </c>
-      <c r="F16" t="n">
-        <v>649058</v>
-      </c>
-      <c r="G16" t="n">
-        <v>450554</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.4405776000213071</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>COLPAL</t>
+          <t>TITAGARH</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,561 +479,495 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>252</v>
+        <v>1154.6</v>
       </c>
       <c r="C2" t="n">
-        <v>253.2</v>
+        <v>1179.9</v>
       </c>
       <c r="D2" t="n">
-        <v>244.1</v>
+        <v>1154.5</v>
       </c>
       <c r="E2" t="n">
-        <v>245.8</v>
+        <v>1172.9</v>
       </c>
       <c r="F2" t="n">
-        <v>32701729</v>
+        <v>19579883</v>
       </c>
       <c r="G2" t="n">
-        <v>74432271</v>
+        <v>42078914</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5606511992627499</v>
+        <v>-0.5346865891073139</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>INFY</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3047.7</v>
+        <v>458.5</v>
       </c>
       <c r="C3" t="n">
-        <v>3089</v>
+        <v>460.65</v>
       </c>
       <c r="D3" t="n">
-        <v>3035</v>
+        <v>450.65</v>
       </c>
       <c r="E3" t="n">
-        <v>3040</v>
+        <v>454.5</v>
       </c>
       <c r="F3" t="n">
-        <v>2300917</v>
+        <v>6922067</v>
       </c>
       <c r="G3" t="n">
-        <v>4540875</v>
+        <v>16441909</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4932877474055111</v>
+        <v>-0.5789985822205925</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>COALINDIA</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>920</v>
+        <v>1362.9</v>
       </c>
       <c r="C4" t="n">
-        <v>924.7</v>
+        <v>1400.5</v>
       </c>
       <c r="D4" t="n">
-        <v>909.8</v>
+        <v>1360.2</v>
       </c>
       <c r="E4" t="n">
-        <v>922.1</v>
+        <v>1398</v>
       </c>
       <c r="F4" t="n">
-        <v>3982355</v>
+        <v>1834277</v>
       </c>
       <c r="G4" t="n">
-        <v>9143598</v>
+        <v>3693260</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.564465213803144</v>
+        <v>-0.5033447415020876</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>TECHM</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9600</v>
+        <v>1429</v>
       </c>
       <c r="C5" t="n">
-        <v>9663</v>
+        <v>1437.9</v>
       </c>
       <c r="D5" t="n">
-        <v>9528</v>
+        <v>1410</v>
       </c>
       <c r="E5" t="n">
-        <v>9581</v>
+        <v>1411.7</v>
       </c>
       <c r="F5" t="n">
-        <v>190469</v>
+        <v>1719329</v>
       </c>
       <c r="G5" t="n">
-        <v>444028</v>
+        <v>3419416</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5710428171196411</v>
+        <v>-0.49718636164772</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>179.3</v>
+        <v>1000</v>
       </c>
       <c r="C6" t="n">
-        <v>180.75</v>
+        <v>1015.4</v>
       </c>
       <c r="D6" t="n">
-        <v>174.4</v>
+        <v>1000</v>
       </c>
       <c r="E6" t="n">
-        <v>176.6</v>
+        <v>1008</v>
       </c>
       <c r="F6" t="n">
-        <v>27300659</v>
+        <v>1065883</v>
       </c>
       <c r="G6" t="n">
-        <v>65651090</v>
+        <v>2553726</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5841552821133663</v>
+        <v>-0.5826165375611949</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>BPCL</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>636.85</v>
+        <v>308.3</v>
       </c>
       <c r="C7" t="n">
-        <v>641.55</v>
+        <v>315.1</v>
       </c>
       <c r="D7" t="n">
-        <v>630.4</v>
+        <v>306.7</v>
       </c>
       <c r="E7" t="n">
-        <v>637.05</v>
+        <v>313.7</v>
       </c>
       <c r="F7" t="n">
-        <v>2239399</v>
+        <v>5296412</v>
       </c>
       <c r="G7" t="n">
-        <v>4493765</v>
+        <v>10531252</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5016653073758863</v>
+        <v>-0.4970767008519025</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>BPCL</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>HDFCAMC</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>128.07</v>
+        <v>2749.9</v>
       </c>
       <c r="C8" t="n">
-        <v>129.1</v>
+        <v>2776.5</v>
       </c>
       <c r="D8" t="n">
-        <v>125.33</v>
+        <v>2719.6</v>
       </c>
       <c r="E8" t="n">
-        <v>125.9</v>
+        <v>2767</v>
       </c>
       <c r="F8" t="n">
-        <v>11238446</v>
+        <v>483814</v>
       </c>
       <c r="G8" t="n">
-        <v>23191134</v>
+        <v>1081669</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5153990313712128</v>
+        <v>-0.5527152946049115</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>HDFCAMC</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3882</v>
+        <v>8087.5</v>
       </c>
       <c r="C9" t="n">
-        <v>3893.6</v>
+        <v>8147</v>
       </c>
       <c r="D9" t="n">
-        <v>3767.9</v>
+        <v>8020</v>
       </c>
       <c r="E9" t="n">
-        <v>3817</v>
+        <v>8062.5</v>
       </c>
       <c r="F9" t="n">
-        <v>315661</v>
+        <v>291146</v>
       </c>
       <c r="G9" t="n">
-        <v>663008</v>
+        <v>616686</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5238956392683044</v>
+        <v>-0.5278861527584541</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>POLYCAB</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>948</v>
+        <v>442.95</v>
       </c>
       <c r="C10" t="n">
-        <v>951.75</v>
+        <v>445.15</v>
       </c>
       <c r="D10" t="n">
-        <v>922.55</v>
+        <v>439.4</v>
       </c>
       <c r="E10" t="n">
-        <v>926.95</v>
+        <v>441.6</v>
       </c>
       <c r="F10" t="n">
-        <v>701337</v>
+        <v>5256456</v>
       </c>
       <c r="G10" t="n">
-        <v>1693451</v>
+        <v>11786646</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5858533845974876</v>
+        <v>-0.5540329284514017</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2351</v>
+        <v>1057</v>
       </c>
       <c r="C11" t="n">
-        <v>2372.8</v>
+        <v>1059.9</v>
       </c>
       <c r="D11" t="n">
-        <v>2283.2</v>
+        <v>1028</v>
       </c>
       <c r="E11" t="n">
-        <v>2287</v>
+        <v>1040.5</v>
       </c>
       <c r="F11" t="n">
-        <v>838461</v>
+        <v>1933016</v>
       </c>
       <c r="G11" t="n">
-        <v>1703667</v>
+        <v>4259236</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5078492451869996</v>
+        <v>-0.5461589825029654</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>AUBANK</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1685</v>
+        <v>783.3</v>
       </c>
       <c r="C12" t="n">
-        <v>1701.1</v>
+        <v>794</v>
       </c>
       <c r="D12" t="n">
-        <v>1667</v>
+        <v>781.3</v>
       </c>
       <c r="E12" t="n">
-        <v>1695</v>
+        <v>786</v>
       </c>
       <c r="F12" t="n">
-        <v>1113981</v>
+        <v>1072431</v>
       </c>
       <c r="G12" t="n">
-        <v>2260644</v>
+        <v>2522454</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5072284711790092</v>
+        <v>-0.57484616171395</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>MARICO</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>COLPAL</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1436.9</v>
+        <v>2180</v>
       </c>
       <c r="C13" t="n">
-        <v>1446</v>
+        <v>2190.1</v>
       </c>
       <c r="D13" t="n">
-        <v>1411.7</v>
+        <v>2135.4</v>
       </c>
       <c r="E13" t="n">
-        <v>1414</v>
+        <v>2140</v>
       </c>
       <c r="F13" t="n">
-        <v>967660</v>
+        <v>371678</v>
       </c>
       <c r="G13" t="n">
-        <v>2238307</v>
+        <v>738058</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.5676821812200025</v>
+        <v>-0.4964108511797176</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>COLPAL</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1884</v>
+        <v>2970</v>
       </c>
       <c r="C14" t="n">
-        <v>1892.1</v>
+        <v>3013.9</v>
       </c>
       <c r="D14" t="n">
-        <v>1836</v>
+        <v>2950</v>
       </c>
       <c r="E14" t="n">
-        <v>1863</v>
+        <v>2994.9</v>
       </c>
       <c r="F14" t="n">
-        <v>680205</v>
+        <v>243557</v>
       </c>
       <c r="G14" t="n">
-        <v>1398269</v>
+        <v>577229</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.513537809963605</v>
+        <v>-0.578058274965395</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>TIINDIA</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SRF</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2559</v>
+        <v>452.45</v>
       </c>
       <c r="C15" t="n">
-        <v>2563.7</v>
+        <v>457.4</v>
       </c>
       <c r="D15" t="n">
-        <v>2472.2</v>
+        <v>451</v>
       </c>
       <c r="E15" t="n">
-        <v>2494.5</v>
+        <v>452.4</v>
       </c>
       <c r="F15" t="n">
-        <v>411464</v>
+        <v>677273</v>
       </c>
       <c r="G15" t="n">
-        <v>950680</v>
+        <v>1509926</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5671898009845584</v>
+        <v>-0.5514528526563554</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SRF</t>
+          <t>DABUR</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SJVN</t>
+          <t>CYIENT</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>79</v>
+        <v>880</v>
       </c>
       <c r="C16" t="n">
-        <v>79.68000000000001</v>
+        <v>893.9</v>
       </c>
       <c r="D16" t="n">
-        <v>76.83</v>
+        <v>874.6</v>
       </c>
       <c r="E16" t="n">
-        <v>78.04000000000001</v>
+        <v>890.4</v>
       </c>
       <c r="F16" t="n">
-        <v>3627404</v>
+        <v>945939</v>
       </c>
       <c r="G16" t="n">
-        <v>8426676</v>
+        <v>2049322</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.5695332299473719</v>
+        <v>-0.5384136802318035</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>SJVN</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>CAMS</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>773</v>
-      </c>
-      <c r="C17" t="n">
-        <v>775.85</v>
-      </c>
-      <c r="D17" t="n">
-        <v>755</v>
-      </c>
-      <c r="E17" t="n">
-        <v>760</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1458679</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2996865</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-0.5132650286215762</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>CAMS</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>CROMPTON</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>254.63</v>
-      </c>
-      <c r="C18" t="n">
-        <v>257</v>
-      </c>
-      <c r="D18" t="n">
-        <v>248.31</v>
-      </c>
-      <c r="E18" t="n">
-        <v>250</v>
-      </c>
-      <c r="F18" t="n">
-        <v>2472229</v>
-      </c>
-      <c r="G18" t="n">
-        <v>5335493</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-0.5366446924398551</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>CROMPTON</t>
+          <t>CYIENT</t>
         </is>
       </c>
     </row>
@@ -1101,363 +1035,363 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>306.65</v>
+        <v>445</v>
       </c>
       <c r="C2" t="n">
-        <v>306.65</v>
+        <v>448.3</v>
       </c>
       <c r="D2" t="n">
-        <v>301.1</v>
+        <v>432.95</v>
       </c>
       <c r="E2" t="n">
-        <v>301.45</v>
+        <v>436</v>
       </c>
       <c r="F2" t="n">
-        <v>17011704</v>
+        <v>18502535</v>
       </c>
       <c r="G2" t="n">
-        <v>10701849</v>
+        <v>11651499</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5896041889583753</v>
+        <v>0.5879961024757415</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>BEL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4475.5</v>
+        <v>211</v>
       </c>
       <c r="C3" t="n">
-        <v>4486.6</v>
+        <v>215</v>
       </c>
       <c r="D3" t="n">
-        <v>4361.4</v>
+        <v>210.93</v>
       </c>
       <c r="E3" t="n">
-        <v>4416</v>
+        <v>213.28</v>
       </c>
       <c r="F3" t="n">
-        <v>958536</v>
+        <v>33068230</v>
       </c>
       <c r="G3" t="n">
-        <v>680187</v>
+        <v>22379072</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4092242280431705</v>
+        <v>0.4776408065535515</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12203</v>
+        <v>606.2</v>
       </c>
       <c r="C4" t="n">
-        <v>12246</v>
+        <v>633.3</v>
       </c>
       <c r="D4" t="n">
-        <v>11954</v>
+        <v>594.35</v>
       </c>
       <c r="E4" t="n">
-        <v>12021</v>
+        <v>629</v>
       </c>
       <c r="F4" t="n">
-        <v>349586</v>
+        <v>20875698</v>
       </c>
       <c r="G4" t="n">
-        <v>227223</v>
+        <v>13298013</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5385150270879269</v>
+        <v>0.5698358845039481</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>HINDZINC</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AMBUJACEM</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>451</v>
+        <v>9050</v>
       </c>
       <c r="C5" t="n">
-        <v>457.7</v>
+        <v>9490</v>
       </c>
       <c r="D5" t="n">
-        <v>440.4</v>
+        <v>9010</v>
       </c>
       <c r="E5" t="n">
-        <v>450.3</v>
+        <v>9345</v>
       </c>
       <c r="F5" t="n">
-        <v>3729295</v>
+        <v>843945</v>
       </c>
       <c r="G5" t="n">
-        <v>2393788</v>
+        <v>590278</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5579052948715593</v>
+        <v>0.4297415793914054</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AMBUJACEM</t>
+          <t>OFSS</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BOSCHLTD</t>
+          <t>HAVELLS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>37495</v>
+        <v>1248</v>
       </c>
       <c r="C6" t="n">
-        <v>37690</v>
+        <v>1281.5</v>
       </c>
       <c r="D6" t="n">
-        <v>36295</v>
+        <v>1243.1</v>
       </c>
       <c r="E6" t="n">
-        <v>36800</v>
+        <v>1273.1</v>
       </c>
       <c r="F6" t="n">
-        <v>30157</v>
+        <v>2461604</v>
       </c>
       <c r="G6" t="n">
-        <v>20767</v>
+        <v>1752335</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4521596764096885</v>
+        <v>0.4047565105987154</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>BOSCHLTD</t>
+          <t>HAVELLS</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>TATAELXSI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1406</v>
+        <v>4204.9</v>
       </c>
       <c r="C7" t="n">
-        <v>1408.9</v>
+        <v>4283.4</v>
       </c>
       <c r="D7" t="n">
-        <v>1389.4</v>
+        <v>4180</v>
       </c>
       <c r="E7" t="n">
-        <v>1392</v>
+        <v>4196</v>
       </c>
       <c r="F7" t="n">
-        <v>506429</v>
+        <v>632056</v>
       </c>
       <c r="G7" t="n">
-        <v>319278</v>
+        <v>412945</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5861694197533184</v>
+        <v>0.5306057707442879</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>TATAELXSI</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>81.48</v>
+        <v>1697</v>
       </c>
       <c r="C8" t="n">
-        <v>82.28</v>
+        <v>1735</v>
       </c>
       <c r="D8" t="n">
-        <v>79.98</v>
+        <v>1690</v>
       </c>
       <c r="E8" t="n">
-        <v>80.59999999999999</v>
+        <v>1721.7</v>
       </c>
       <c r="F8" t="n">
-        <v>14088780</v>
+        <v>758413</v>
       </c>
       <c r="G8" t="n">
-        <v>9025789</v>
+        <v>517538</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5609471925390678</v>
+        <v>0.4654247610803458</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ANGELONE</t>
+          <t>MANKIND</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>322.81</v>
+        <v>2271.8</v>
       </c>
       <c r="C9" t="n">
-        <v>323</v>
+        <v>2309.8</v>
       </c>
       <c r="D9" t="n">
-        <v>309.51</v>
+        <v>2251.2</v>
       </c>
       <c r="E9" t="n">
-        <v>314.29</v>
+        <v>2270.8</v>
       </c>
       <c r="F9" t="n">
-        <v>9294838</v>
+        <v>412688</v>
       </c>
       <c r="G9" t="n">
-        <v>6611292</v>
+        <v>293014</v>
       </c>
       <c r="H9" t="n">
-        <v>0.405903414945218</v>
+        <v>0.4084241708587303</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ANGELONE</t>
+          <t>MANKIND</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>128.4</v>
+        <v>544</v>
       </c>
       <c r="C10" t="n">
-        <v>129.7</v>
+        <v>545.4</v>
       </c>
       <c r="D10" t="n">
-        <v>122.34</v>
+        <v>534.4</v>
       </c>
       <c r="E10" t="n">
-        <v>123.19</v>
+        <v>543.5</v>
       </c>
       <c r="F10" t="n">
-        <v>18209699</v>
+        <v>1595904</v>
       </c>
       <c r="G10" t="n">
-        <v>12806668</v>
+        <v>1046981</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4218920175021325</v>
+        <v>0.5242912717613787</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DELHIVERY</t>
+          <t>NBCC</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>445</v>
+        <v>94.62</v>
       </c>
       <c r="C11" t="n">
-        <v>451.85</v>
+        <v>96.5</v>
       </c>
       <c r="D11" t="n">
-        <v>441.65</v>
+        <v>94.13</v>
       </c>
       <c r="E11" t="n">
-        <v>447.95</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>4832080</v>
+        <v>13917958</v>
       </c>
       <c r="G11" t="n">
-        <v>3195024</v>
+        <v>9129145</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5123767458397809</v>
+        <v>0.5245631436459822</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>DELHIVERY</t>
+          <t>NBCC</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TITAGARH</t>
+          <t>ABFRL</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>743.55</v>
+        <v>62.54</v>
       </c>
       <c r="C12" t="n">
-        <v>761.95</v>
+        <v>64.66</v>
       </c>
       <c r="D12" t="n">
-        <v>722</v>
+        <v>62.33</v>
       </c>
       <c r="E12" t="n">
-        <v>760</v>
+        <v>64</v>
       </c>
       <c r="F12" t="n">
-        <v>1031823</v>
+        <v>3578792</v>
       </c>
       <c r="G12" t="n">
-        <v>680079</v>
+        <v>2380448</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5172105005447897</v>
+        <v>0.5034111226122142</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>TITAGARH</t>
+          <t>ABFRL</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,495 +479,363 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1154.6</v>
+        <v>974.5</v>
       </c>
       <c r="C2" t="n">
-        <v>1179.9</v>
+        <v>979.75</v>
       </c>
       <c r="D2" t="n">
-        <v>1154.5</v>
+        <v>949.3</v>
       </c>
       <c r="E2" t="n">
-        <v>1172.9</v>
+        <v>952.5</v>
       </c>
       <c r="F2" t="n">
-        <v>19579883</v>
+        <v>6752420</v>
       </c>
       <c r="G2" t="n">
-        <v>42078914</v>
+        <v>15096574</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5346865891073139</v>
+        <v>-0.5527183849792675</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>458.5</v>
+        <v>3557.9</v>
       </c>
       <c r="C3" t="n">
-        <v>460.65</v>
+        <v>3565</v>
       </c>
       <c r="D3" t="n">
-        <v>450.65</v>
+        <v>3482.8</v>
       </c>
       <c r="E3" t="n">
-        <v>454.5</v>
+        <v>3497.6</v>
       </c>
       <c r="F3" t="n">
-        <v>6922067</v>
+        <v>446619</v>
       </c>
       <c r="G3" t="n">
-        <v>16441909</v>
+        <v>1025395</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5789985822205925</v>
+        <v>-0.5644419955236762</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>SUPREMEIND</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1362.9</v>
+        <v>3700.4</v>
       </c>
       <c r="C4" t="n">
-        <v>1400.5</v>
+        <v>3771.7</v>
       </c>
       <c r="D4" t="n">
-        <v>1360.2</v>
+        <v>3617.1</v>
       </c>
       <c r="E4" t="n">
-        <v>1398</v>
+        <v>3639</v>
       </c>
       <c r="F4" t="n">
-        <v>1834277</v>
+        <v>560369</v>
       </c>
       <c r="G4" t="n">
-        <v>3693260</v>
+        <v>1110497</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5033447415020876</v>
+        <v>-0.4953890015011297</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>SUPREMEIND</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1429</v>
+        <v>1774</v>
       </c>
       <c r="C5" t="n">
-        <v>1437.9</v>
+        <v>1816.6</v>
       </c>
       <c r="D5" t="n">
-        <v>1410</v>
+        <v>1740.3</v>
       </c>
       <c r="E5" t="n">
-        <v>1411.7</v>
+        <v>1755.2</v>
       </c>
       <c r="F5" t="n">
-        <v>1719329</v>
+        <v>988176</v>
       </c>
       <c r="G5" t="n">
-        <v>3419416</v>
+        <v>1964732</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.49718636164772</v>
+        <v>-0.4970428536818253</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MAXHEALTH</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1000</v>
+        <v>1829.3</v>
       </c>
       <c r="C6" t="n">
-        <v>1015.4</v>
+        <v>1845.2</v>
       </c>
       <c r="D6" t="n">
-        <v>1000</v>
+        <v>1820</v>
       </c>
       <c r="E6" t="n">
-        <v>1008</v>
+        <v>1827</v>
       </c>
       <c r="F6" t="n">
-        <v>1065883</v>
+        <v>558117</v>
       </c>
       <c r="G6" t="n">
-        <v>2553726</v>
+        <v>1096981</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5826165375611949</v>
+        <v>-0.4912245517470221</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MAXHEALTH</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>BDL</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>308.3</v>
+        <v>1389.9</v>
       </c>
       <c r="C7" t="n">
-        <v>315.1</v>
+        <v>1406.2</v>
       </c>
       <c r="D7" t="n">
-        <v>306.7</v>
+        <v>1384.2</v>
       </c>
       <c r="E7" t="n">
-        <v>313.7</v>
+        <v>1403</v>
       </c>
       <c r="F7" t="n">
-        <v>5296412</v>
+        <v>723230</v>
       </c>
       <c r="G7" t="n">
-        <v>10531252</v>
+        <v>1457456</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4970767008519025</v>
+        <v>-0.5037723265745244</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>BDL</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HDFCAMC</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2749.9</v>
+        <v>517</v>
       </c>
       <c r="C8" t="n">
-        <v>2776.5</v>
+        <v>519.15</v>
       </c>
       <c r="D8" t="n">
-        <v>2719.6</v>
+        <v>508.8</v>
       </c>
       <c r="E8" t="n">
-        <v>2767</v>
+        <v>510</v>
       </c>
       <c r="F8" t="n">
-        <v>483814</v>
+        <v>1034888</v>
       </c>
       <c r="G8" t="n">
-        <v>1081669</v>
+        <v>2167552</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5527152946049115</v>
+        <v>-0.5225544762017243</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>HDFCAMC</t>
+          <t>CONCOR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8087.5</v>
+        <v>5344</v>
       </c>
       <c r="C9" t="n">
-        <v>8147</v>
+        <v>5454</v>
       </c>
       <c r="D9" t="n">
-        <v>8020</v>
+        <v>5315</v>
       </c>
       <c r="E9" t="n">
-        <v>8062.5</v>
+        <v>5410</v>
       </c>
       <c r="F9" t="n">
-        <v>291146</v>
+        <v>96733</v>
       </c>
       <c r="G9" t="n">
-        <v>616686</v>
+        <v>212162</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5278861527584541</v>
+        <v>-0.5440606706196208</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>ALKEM</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>IIFL</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>442.95</v>
+        <v>437.5</v>
       </c>
       <c r="C10" t="n">
-        <v>445.15</v>
+        <v>446.9</v>
       </c>
       <c r="D10" t="n">
-        <v>439.4</v>
+        <v>432.45</v>
       </c>
       <c r="E10" t="n">
-        <v>441.6</v>
+        <v>440.95</v>
       </c>
       <c r="F10" t="n">
-        <v>5256456</v>
+        <v>3917728</v>
       </c>
       <c r="G10" t="n">
-        <v>11786646</v>
+        <v>8953270</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5540329284514017</v>
+        <v>-0.5624249017398113</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>IIFL</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>INOXWIND</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1057</v>
+        <v>104</v>
       </c>
       <c r="C11" t="n">
-        <v>1059.9</v>
+        <v>105.14</v>
       </c>
       <c r="D11" t="n">
-        <v>1028</v>
+        <v>102.17</v>
       </c>
       <c r="E11" t="n">
-        <v>1040.5</v>
+        <v>103.65</v>
       </c>
       <c r="F11" t="n">
-        <v>1933016</v>
+        <v>9031940</v>
       </c>
       <c r="G11" t="n">
-        <v>4259236</v>
+        <v>19824025</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5461589825029654</v>
+        <v>-0.5443942388087182</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>INOXWIND</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>GRANULES</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>783.3</v>
+        <v>696</v>
       </c>
       <c r="C12" t="n">
-        <v>794</v>
+        <v>710</v>
       </c>
       <c r="D12" t="n">
-        <v>781.3</v>
+        <v>695</v>
       </c>
       <c r="E12" t="n">
-        <v>786</v>
+        <v>703</v>
       </c>
       <c r="F12" t="n">
-        <v>1072431</v>
+        <v>960558</v>
       </c>
       <c r="G12" t="n">
-        <v>2522454</v>
+        <v>2252676</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.57484616171395</v>
+        <v>-0.5735924740175684</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MARICO</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>COLPAL</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2180</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2190.1</v>
-      </c>
-      <c r="D13" t="n">
-        <v>2135.4</v>
-      </c>
-      <c r="E13" t="n">
-        <v>2140</v>
-      </c>
-      <c r="F13" t="n">
-        <v>371678</v>
-      </c>
-      <c r="G13" t="n">
-        <v>738058</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-0.4964108511797176</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>COLPAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>TIINDIA</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2970</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3013.9</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2950</v>
-      </c>
-      <c r="E14" t="n">
-        <v>2994.9</v>
-      </c>
-      <c r="F14" t="n">
-        <v>243557</v>
-      </c>
-      <c r="G14" t="n">
-        <v>577229</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-0.578058274965395</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>TIINDIA</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>DABUR</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>452.45</v>
-      </c>
-      <c r="C15" t="n">
-        <v>457.4</v>
-      </c>
-      <c r="D15" t="n">
-        <v>451</v>
-      </c>
-      <c r="E15" t="n">
-        <v>452.4</v>
-      </c>
-      <c r="F15" t="n">
-        <v>677273</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1509926</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-0.5514528526563554</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>DABUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>CYIENT</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>880</v>
-      </c>
-      <c r="C16" t="n">
-        <v>893.9</v>
-      </c>
-      <c r="D16" t="n">
-        <v>874.6</v>
-      </c>
-      <c r="E16" t="n">
-        <v>890.4</v>
-      </c>
-      <c r="F16" t="n">
-        <v>945939</v>
-      </c>
-      <c r="G16" t="n">
-        <v>2049322</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-0.5384136802318035</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>CYIENT</t>
+          <t>GRANULES</t>
         </is>
       </c>
     </row>
@@ -1035,363 +903,363 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>445</v>
+        <v>3115.9</v>
       </c>
       <c r="C2" t="n">
-        <v>448.3</v>
+        <v>3144</v>
       </c>
       <c r="D2" t="n">
-        <v>432.95</v>
+        <v>3075</v>
       </c>
       <c r="E2" t="n">
-        <v>436</v>
+        <v>3084.8</v>
       </c>
       <c r="F2" t="n">
-        <v>18502535</v>
+        <v>2645344</v>
       </c>
       <c r="G2" t="n">
-        <v>11651499</v>
+        <v>1816150</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5879961024757415</v>
+        <v>0.4565669135258651</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>M&amp;M</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>211</v>
+        <v>4514.8</v>
       </c>
       <c r="C3" t="n">
-        <v>215</v>
+        <v>4547.9</v>
       </c>
       <c r="D3" t="n">
-        <v>210.93</v>
+        <v>4421</v>
       </c>
       <c r="E3" t="n">
-        <v>213.28</v>
+        <v>4465</v>
       </c>
       <c r="F3" t="n">
-        <v>33068230</v>
+        <v>1261879</v>
       </c>
       <c r="G3" t="n">
-        <v>22379072</v>
+        <v>833925</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4776408065535515</v>
+        <v>0.5131804418862608</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>INDIGO</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>GRASIM</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>606.2</v>
+        <v>2780</v>
       </c>
       <c r="C4" t="n">
-        <v>633.3</v>
+        <v>2848.2</v>
       </c>
       <c r="D4" t="n">
-        <v>594.35</v>
+        <v>2772</v>
       </c>
       <c r="E4" t="n">
-        <v>629</v>
+        <v>2775.9</v>
       </c>
       <c r="F4" t="n">
-        <v>20875698</v>
+        <v>1561588</v>
       </c>
       <c r="G4" t="n">
-        <v>13298013</v>
+        <v>986204</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5698358845039481</v>
+        <v>0.5834330422508933</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>GRASIM</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9050</v>
+        <v>2321</v>
       </c>
       <c r="C5" t="n">
-        <v>9490</v>
+        <v>2334.4</v>
       </c>
       <c r="D5" t="n">
-        <v>9010</v>
+        <v>2281.1</v>
       </c>
       <c r="E5" t="n">
-        <v>9345</v>
+        <v>2290</v>
       </c>
       <c r="F5" t="n">
-        <v>843945</v>
+        <v>1629120</v>
       </c>
       <c r="G5" t="n">
-        <v>590278</v>
+        <v>1099681</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4297415793914054</v>
+        <v>0.4814478016806692</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>GODREJCP</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1248</v>
+        <v>1088.2</v>
       </c>
       <c r="C6" t="n">
-        <v>1281.5</v>
+        <v>1105.2</v>
       </c>
       <c r="D6" t="n">
-        <v>1243.1</v>
+        <v>1081.5</v>
       </c>
       <c r="E6" t="n">
-        <v>1273.1</v>
+        <v>1094.9</v>
       </c>
       <c r="F6" t="n">
-        <v>2461604</v>
+        <v>807880</v>
       </c>
       <c r="G6" t="n">
-        <v>1752335</v>
+        <v>556276</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4047565105987154</v>
+        <v>0.4523006565086396</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>GODREJCP</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TATAELXSI</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4204.9</v>
+        <v>3552</v>
       </c>
       <c r="C7" t="n">
-        <v>4283.4</v>
+        <v>3639.6</v>
       </c>
       <c r="D7" t="n">
-        <v>4180</v>
+        <v>3543.6</v>
       </c>
       <c r="E7" t="n">
-        <v>4196</v>
+        <v>3630</v>
       </c>
       <c r="F7" t="n">
-        <v>632056</v>
+        <v>3792795</v>
       </c>
       <c r="G7" t="n">
-        <v>412945</v>
+        <v>2386493</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5306057707442879</v>
+        <v>0.5892755604143821</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>TATAELXSI</t>
+          <t>BSE</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1697</v>
+        <v>5042.5</v>
       </c>
       <c r="C8" t="n">
-        <v>1735</v>
+        <v>5105.5</v>
       </c>
       <c r="D8" t="n">
-        <v>1690</v>
+        <v>5019</v>
       </c>
       <c r="E8" t="n">
-        <v>1721.7</v>
+        <v>5083</v>
       </c>
       <c r="F8" t="n">
-        <v>758413</v>
+        <v>667998</v>
       </c>
       <c r="G8" t="n">
-        <v>517538</v>
+        <v>448144</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4654247610803458</v>
+        <v>0.4905878467635403</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2271.8</v>
+        <v>2299.1</v>
       </c>
       <c r="C9" t="n">
-        <v>2309.8</v>
+        <v>2319.4</v>
       </c>
       <c r="D9" t="n">
-        <v>2251.2</v>
+        <v>2260.3</v>
       </c>
       <c r="E9" t="n">
-        <v>2270.8</v>
+        <v>2303</v>
       </c>
       <c r="F9" t="n">
-        <v>412688</v>
+        <v>1261666</v>
       </c>
       <c r="G9" t="n">
-        <v>293014</v>
+        <v>898638</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4084241708587303</v>
+        <v>0.403975794480091</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>LUPIN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>544</v>
+        <v>1132</v>
       </c>
       <c r="C10" t="n">
-        <v>545.4</v>
+        <v>1133</v>
       </c>
       <c r="D10" t="n">
-        <v>534.4</v>
+        <v>1085</v>
       </c>
       <c r="E10" t="n">
-        <v>543.5</v>
+        <v>1094.7</v>
       </c>
       <c r="F10" t="n">
-        <v>1595904</v>
+        <v>2044775</v>
       </c>
       <c r="G10" t="n">
-        <v>1046981</v>
+        <v>1363246</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5242912717613787</v>
+        <v>0.4999310469277005</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NBCC</t>
+          <t>GMRAIRPORT</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>94.62</v>
+        <v>95.62</v>
       </c>
       <c r="C11" t="n">
-        <v>96.5</v>
+        <v>98.26000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>94.13</v>
+        <v>95.5</v>
       </c>
       <c r="E11" t="n">
-        <v>95.51000000000001</v>
+        <v>98.05</v>
       </c>
       <c r="F11" t="n">
-        <v>13917958</v>
+        <v>16047591</v>
       </c>
       <c r="G11" t="n">
-        <v>9129145</v>
+        <v>10479798</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5245631436459822</v>
+        <v>0.5312881984939023</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>NBCC</t>
+          <t>GMRAIRPORT</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ABFRL</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>62.54</v>
+        <v>817.95</v>
       </c>
       <c r="C12" t="n">
-        <v>64.66</v>
+        <v>822.9</v>
       </c>
       <c r="D12" t="n">
-        <v>62.33</v>
+        <v>815</v>
       </c>
       <c r="E12" t="n">
-        <v>64</v>
+        <v>817.3</v>
       </c>
       <c r="F12" t="n">
-        <v>3578792</v>
+        <v>1629817</v>
       </c>
       <c r="G12" t="n">
-        <v>2380448</v>
+        <v>1084031</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5034111226122142</v>
+        <v>0.5034782215637744</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ABFRL</t>
+          <t>LICI</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,363 +479,297 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>974.5</v>
+        <v>1078</v>
       </c>
       <c r="C2" t="n">
-        <v>979.75</v>
+        <v>1080</v>
       </c>
       <c r="D2" t="n">
-        <v>949.3</v>
+        <v>1053</v>
       </c>
       <c r="E2" t="n">
-        <v>952.5</v>
+        <v>1069.75</v>
       </c>
       <c r="F2" t="n">
-        <v>6752420</v>
+        <v>3710080</v>
       </c>
       <c r="G2" t="n">
-        <v>15096574</v>
+        <v>7798496</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5527183849792675</v>
+        <v>-0.5242569849365827</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>HINDALCO</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3557.9</v>
+        <v>1778</v>
       </c>
       <c r="C3" t="n">
-        <v>3565</v>
+        <v>1793.9</v>
       </c>
       <c r="D3" t="n">
-        <v>3482.8</v>
+        <v>1760.8</v>
       </c>
       <c r="E3" t="n">
-        <v>3497.6</v>
+        <v>1760.8</v>
       </c>
       <c r="F3" t="n">
-        <v>446619</v>
+        <v>699788</v>
       </c>
       <c r="G3" t="n">
-        <v>1025395</v>
+        <v>1414112</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5644419955236762</v>
+        <v>-0.505139621189835</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SUPREMEIND</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3700.4</v>
+        <v>464.3</v>
       </c>
       <c r="C4" t="n">
-        <v>3771.7</v>
+        <v>464.4</v>
       </c>
       <c r="D4" t="n">
-        <v>3617.1</v>
+        <v>449.4</v>
       </c>
       <c r="E4" t="n">
-        <v>3639</v>
+        <v>450.2</v>
       </c>
       <c r="F4" t="n">
-        <v>560369</v>
+        <v>7412182</v>
       </c>
       <c r="G4" t="n">
-        <v>1110497</v>
+        <v>16158141</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4953890015011297</v>
+        <v>-0.5412726006042403</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SUPREMEIND</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TORNTPOWER</t>
+          <t>BANKBARODA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1774</v>
+        <v>269.2</v>
       </c>
       <c r="C5" t="n">
-        <v>1816.6</v>
+        <v>271.81</v>
       </c>
       <c r="D5" t="n">
-        <v>1740.3</v>
+        <v>267.4</v>
       </c>
       <c r="E5" t="n">
-        <v>1755.2</v>
+        <v>268.3</v>
       </c>
       <c r="F5" t="n">
-        <v>988176</v>
+        <v>5919525</v>
       </c>
       <c r="G5" t="n">
-        <v>1964732</v>
+        <v>12427177</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4970428536818253</v>
+        <v>-0.5236629364818736</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>TORNTPOWER</t>
+          <t>BANKBARODA</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1829.3</v>
+        <v>25100</v>
       </c>
       <c r="C6" t="n">
-        <v>1845.2</v>
+        <v>25355</v>
       </c>
       <c r="D6" t="n">
-        <v>1820</v>
+        <v>24500</v>
       </c>
       <c r="E6" t="n">
-        <v>1827</v>
+        <v>24615</v>
       </c>
       <c r="F6" t="n">
-        <v>558117</v>
+        <v>11849</v>
       </c>
       <c r="G6" t="n">
-        <v>1096981</v>
+        <v>29353</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4912245517470221</v>
+        <v>-0.5963274622696146</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>SHREECEM</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BDL</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1389.9</v>
+        <v>2418.7</v>
       </c>
       <c r="C7" t="n">
-        <v>1406.2</v>
+        <v>2474</v>
       </c>
       <c r="D7" t="n">
-        <v>1384.2</v>
+        <v>2403.7</v>
       </c>
       <c r="E7" t="n">
-        <v>1403</v>
+        <v>2415</v>
       </c>
       <c r="F7" t="n">
-        <v>723230</v>
+        <v>616900</v>
       </c>
       <c r="G7" t="n">
-        <v>1457456</v>
+        <v>1537658</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5037723265745244</v>
+        <v>-0.5988054560897157</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>BDL</t>
+          <t>GLENMARK</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>HUDCO</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>517</v>
+        <v>215</v>
       </c>
       <c r="C8" t="n">
-        <v>519.15</v>
+        <v>220.3</v>
       </c>
       <c r="D8" t="n">
-        <v>508.8</v>
+        <v>212.8</v>
       </c>
       <c r="E8" t="n">
-        <v>510</v>
+        <v>216.8</v>
       </c>
       <c r="F8" t="n">
-        <v>1034888</v>
+        <v>4480936</v>
       </c>
       <c r="G8" t="n">
-        <v>2167552</v>
+        <v>8860387</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5225544762017243</v>
+        <v>-0.4942731056781154</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>HUDCO</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>DALBHARAT</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5344</v>
+        <v>1920.9</v>
       </c>
       <c r="C9" t="n">
-        <v>5454</v>
+        <v>1980</v>
       </c>
       <c r="D9" t="n">
-        <v>5315</v>
+        <v>1918</v>
       </c>
       <c r="E9" t="n">
-        <v>5410</v>
+        <v>1964.8</v>
       </c>
       <c r="F9" t="n">
-        <v>96733</v>
+        <v>419247</v>
       </c>
       <c r="G9" t="n">
-        <v>212162</v>
+        <v>923966</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5440606706196208</v>
+        <v>-0.5462527841933578</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>DALBHARAT</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IIFL</t>
+          <t>ICICIPRULI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>437.5</v>
+        <v>522</v>
       </c>
       <c r="C10" t="n">
-        <v>446.9</v>
+        <v>530.4</v>
       </c>
       <c r="D10" t="n">
-        <v>432.45</v>
+        <v>522</v>
       </c>
       <c r="E10" t="n">
-        <v>440.95</v>
+        <v>524.2</v>
       </c>
       <c r="F10" t="n">
-        <v>3917728</v>
+        <v>567464</v>
       </c>
       <c r="G10" t="n">
-        <v>8953270</v>
+        <v>1284261</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5624249017398113</v>
+        <v>-0.5581396616419871</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>IIFL</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>INOXWIND</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>104</v>
-      </c>
-      <c r="C11" t="n">
-        <v>105.14</v>
-      </c>
-      <c r="D11" t="n">
-        <v>102.17</v>
-      </c>
-      <c r="E11" t="n">
-        <v>103.65</v>
-      </c>
-      <c r="F11" t="n">
-        <v>9031940</v>
-      </c>
-      <c r="G11" t="n">
-        <v>19824025</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-0.5443942388087182</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>INOXWIND</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>GRANULES</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>696</v>
-      </c>
-      <c r="C12" t="n">
-        <v>710</v>
-      </c>
-      <c r="D12" t="n">
-        <v>695</v>
-      </c>
-      <c r="E12" t="n">
-        <v>703</v>
-      </c>
-      <c r="F12" t="n">
-        <v>960558</v>
-      </c>
-      <c r="G12" t="n">
-        <v>2252676</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-0.5735924740175684</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>GRANULES</t>
+          <t>ICICIPRULI</t>
         </is>
       </c>
     </row>
@@ -850,7 +784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -903,363 +837,528 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3115.9</v>
+        <v>263.3</v>
       </c>
       <c r="C2" t="n">
-        <v>3144</v>
+        <v>265.4</v>
       </c>
       <c r="D2" t="n">
-        <v>3075</v>
+        <v>253</v>
       </c>
       <c r="E2" t="n">
-        <v>3084.8</v>
+        <v>253.47</v>
       </c>
       <c r="F2" t="n">
-        <v>2645344</v>
+        <v>152137971</v>
       </c>
       <c r="G2" t="n">
-        <v>1816150</v>
+        <v>104988011</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4565669135258651</v>
+        <v>0.4490985165915754</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>ETERNAL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4514.8</v>
+        <v>3100</v>
       </c>
       <c r="C3" t="n">
-        <v>4547.9</v>
+        <v>3192</v>
       </c>
       <c r="D3" t="n">
-        <v>4421</v>
+        <v>3092</v>
       </c>
       <c r="E3" t="n">
-        <v>4465</v>
+        <v>3149</v>
       </c>
       <c r="F3" t="n">
-        <v>1261879</v>
+        <v>3917359</v>
       </c>
       <c r="G3" t="n">
-        <v>833925</v>
+        <v>2645344</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5131804418862608</v>
+        <v>0.4808505056431224</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>M&amp;M</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2780</v>
+        <v>409.5</v>
       </c>
       <c r="C4" t="n">
-        <v>2848.2</v>
+        <v>410</v>
       </c>
       <c r="D4" t="n">
-        <v>2772</v>
+        <v>399.65</v>
       </c>
       <c r="E4" t="n">
-        <v>2775.9</v>
+        <v>400.1</v>
       </c>
       <c r="F4" t="n">
-        <v>1561588</v>
+        <v>11920835</v>
       </c>
       <c r="G4" t="n">
-        <v>986204</v>
+        <v>7726655</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5834330422508933</v>
+        <v>0.5428196289338659</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>NTPC</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2321</v>
+        <v>745</v>
       </c>
       <c r="C5" t="n">
-        <v>2334.4</v>
+        <v>780</v>
       </c>
       <c r="D5" t="n">
-        <v>2281.1</v>
+        <v>732.2</v>
       </c>
       <c r="E5" t="n">
-        <v>2290</v>
+        <v>775</v>
       </c>
       <c r="F5" t="n">
-        <v>1629120</v>
+        <v>54738724</v>
       </c>
       <c r="G5" t="n">
-        <v>1099681</v>
+        <v>37978285</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4814478016806692</v>
+        <v>0.4413163732906844</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>VEDL</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1088.2</v>
+        <v>368.05</v>
       </c>
       <c r="C6" t="n">
-        <v>1105.2</v>
+        <v>372.45</v>
       </c>
       <c r="D6" t="n">
-        <v>1081.5</v>
+        <v>358.1</v>
       </c>
       <c r="E6" t="n">
-        <v>1094.9</v>
+        <v>362.3</v>
       </c>
       <c r="F6" t="n">
-        <v>807880</v>
+        <v>16891422</v>
       </c>
       <c r="G6" t="n">
-        <v>556276</v>
+        <v>10991705</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4523006565086396</v>
+        <v>0.5367426618527334</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>RECLTD</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3552</v>
+        <v>5674</v>
       </c>
       <c r="C7" t="n">
-        <v>3639.6</v>
+        <v>5734.5</v>
       </c>
       <c r="D7" t="n">
-        <v>3543.6</v>
+        <v>5665</v>
       </c>
       <c r="E7" t="n">
-        <v>3630</v>
+        <v>5719</v>
       </c>
       <c r="F7" t="n">
-        <v>3792795</v>
+        <v>363567</v>
       </c>
       <c r="G7" t="n">
-        <v>2386493</v>
+        <v>249233</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5892755604143821</v>
+        <v>0.4587434248273703</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>BOSCHLTD</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5042.5</v>
+        <v>37165</v>
       </c>
       <c r="C8" t="n">
-        <v>5105.5</v>
+        <v>37470</v>
       </c>
       <c r="D8" t="n">
-        <v>5019</v>
+        <v>36190</v>
       </c>
       <c r="E8" t="n">
-        <v>5083</v>
+        <v>36350</v>
       </c>
       <c r="F8" t="n">
-        <v>667998</v>
+        <v>34734</v>
       </c>
       <c r="G8" t="n">
-        <v>448144</v>
+        <v>21761</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4905878467635403</v>
+        <v>0.5961582647856256</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>BOSCHLTD</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2299.1</v>
+        <v>2911.9</v>
       </c>
       <c r="C9" t="n">
-        <v>2319.4</v>
+        <v>2980.9</v>
       </c>
       <c r="D9" t="n">
-        <v>2260.3</v>
+        <v>2862</v>
       </c>
       <c r="E9" t="n">
-        <v>2303</v>
+        <v>2975</v>
       </c>
       <c r="F9" t="n">
-        <v>1261666</v>
+        <v>2698924</v>
       </c>
       <c r="G9" t="n">
-        <v>898638</v>
+        <v>1771034</v>
       </c>
       <c r="H9" t="n">
-        <v>0.403975794480091</v>
+        <v>0.5239255711635123</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>MCX</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDFCFIRSTB</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1132</v>
+        <v>69.02</v>
       </c>
       <c r="C10" t="n">
-        <v>1133</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>1085</v>
+        <v>68.55</v>
       </c>
       <c r="E10" t="n">
-        <v>1094.7</v>
+        <v>70</v>
       </c>
       <c r="F10" t="n">
-        <v>2044775</v>
+        <v>35995299</v>
       </c>
       <c r="G10" t="n">
-        <v>1363246</v>
+        <v>25640804</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4999310469277005</v>
+        <v>0.40382879569611</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IDFCFIRSTB</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GMRAIRPORT</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>95.62</v>
+        <v>339.95</v>
       </c>
       <c r="C11" t="n">
-        <v>98.26000000000001</v>
+        <v>354.65</v>
       </c>
       <c r="D11" t="n">
-        <v>95.5</v>
+        <v>337.55</v>
       </c>
       <c r="E11" t="n">
-        <v>98.05</v>
+        <v>347.65</v>
       </c>
       <c r="F11" t="n">
-        <v>16047591</v>
+        <v>6756111</v>
       </c>
       <c r="G11" t="n">
-        <v>10479798</v>
+        <v>4701866</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5312881984939023</v>
+        <v>0.4368999456811402</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>GMRAIRPORT</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>KEI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>817.95</v>
+        <v>4997</v>
       </c>
       <c r="C12" t="n">
-        <v>822.9</v>
+        <v>5050</v>
       </c>
       <c r="D12" t="n">
-        <v>815</v>
+        <v>4917.1</v>
       </c>
       <c r="E12" t="n">
-        <v>817.3</v>
+        <v>4959</v>
       </c>
       <c r="F12" t="n">
-        <v>1629817</v>
+        <v>354086</v>
       </c>
       <c r="G12" t="n">
-        <v>1084031</v>
+        <v>236667</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5034782215637744</v>
+        <v>0.4961359209353226</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>KEI</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>GODREJPROP</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1831</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1883.8</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1831</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1858</v>
+      </c>
+      <c r="F13" t="n">
+        <v>860344</v>
+      </c>
+      <c r="G13" t="n">
+        <v>558117</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.5415119052098395</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>GODREJPROP</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>413.55</v>
+      </c>
+      <c r="C14" t="n">
+        <v>420.6</v>
+      </c>
+      <c r="D14" t="n">
+        <v>409.45</v>
+      </c>
+      <c r="E14" t="n">
+        <v>412.8</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3443668</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2219506</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.5515470559665079</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PATANJALI</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>465</v>
+      </c>
+      <c r="C15" t="n">
+        <v>469.4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>462.1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>465</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1582925</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1079986</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.4656902959853183</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>PATANJALI</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CROMPTON</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>270.9</v>
+      </c>
+      <c r="C16" t="n">
+        <v>280.89</v>
+      </c>
+      <c r="D16" t="n">
+        <v>269.63</v>
+      </c>
+      <c r="E16" t="n">
+        <v>275.61</v>
+      </c>
+      <c r="F16" t="n">
+        <v>17813850</v>
+      </c>
+      <c r="G16" t="n">
+        <v>11443201</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.5567191382900641</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>CROMPTON</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CDSL</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1331</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1345.5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1300.2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1304.8</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1876708</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1238028</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.5158849395974889</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>CDSL</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -479,297 +479,297 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1078</v>
+        <v>249</v>
       </c>
       <c r="C2" t="n">
-        <v>1080</v>
+        <v>251.69</v>
       </c>
       <c r="D2" t="n">
-        <v>1053</v>
+        <v>242.65</v>
       </c>
       <c r="E2" t="n">
-        <v>1069.75</v>
+        <v>246.6</v>
       </c>
       <c r="F2" t="n">
-        <v>3710080</v>
+        <v>72700438</v>
       </c>
       <c r="G2" t="n">
-        <v>7798496</v>
+        <v>152137971</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5242569849365827</v>
+        <v>-0.5221413988753669</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>ETERNAL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1778</v>
+        <v>1771</v>
       </c>
       <c r="C3" t="n">
-        <v>1793.9</v>
+        <v>1815</v>
       </c>
       <c r="D3" t="n">
-        <v>1760.8</v>
+        <v>1761.4</v>
       </c>
       <c r="E3" t="n">
-        <v>1760.8</v>
+        <v>1810</v>
       </c>
       <c r="F3" t="n">
-        <v>699788</v>
+        <v>4749798</v>
       </c>
       <c r="G3" t="n">
-        <v>1414112</v>
+        <v>9809449</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.505139621189835</v>
+        <v>-0.5157935986006962</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>464.3</v>
+        <v>413</v>
       </c>
       <c r="C4" t="n">
-        <v>464.4</v>
+        <v>413.9</v>
       </c>
       <c r="D4" t="n">
-        <v>449.4</v>
+        <v>407</v>
       </c>
       <c r="E4" t="n">
-        <v>450.2</v>
+        <v>410.4</v>
       </c>
       <c r="F4" t="n">
-        <v>7412182</v>
+        <v>4414903</v>
       </c>
       <c r="G4" t="n">
-        <v>16158141</v>
+        <v>10438131</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5412726006042403</v>
+        <v>-0.5770408514704405</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>269.2</v>
+        <v>556</v>
       </c>
       <c r="C5" t="n">
-        <v>271.81</v>
+        <v>564.85</v>
       </c>
       <c r="D5" t="n">
-        <v>267.4</v>
+        <v>549.3</v>
       </c>
       <c r="E5" t="n">
-        <v>268.3</v>
+        <v>560.5</v>
       </c>
       <c r="F5" t="n">
-        <v>5919525</v>
+        <v>1886082</v>
       </c>
       <c r="G5" t="n">
-        <v>12427177</v>
+        <v>4306287</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5236629364818736</v>
+        <v>-0.5620166514679583</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>EXIDEIND</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25100</v>
+        <v>362</v>
       </c>
       <c r="C6" t="n">
-        <v>25355</v>
+        <v>363.2</v>
       </c>
       <c r="D6" t="n">
-        <v>24500</v>
+        <v>356</v>
       </c>
       <c r="E6" t="n">
-        <v>24615</v>
+        <v>359.5</v>
       </c>
       <c r="F6" t="n">
-        <v>11849</v>
+        <v>2235828</v>
       </c>
       <c r="G6" t="n">
-        <v>29353</v>
+        <v>4899239</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5963274622696146</v>
+        <v>-0.5436376955686383</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>EXIDEIND</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>JUBLFOOD</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2418.7</v>
+        <v>483.75</v>
       </c>
       <c r="C7" t="n">
-        <v>2474</v>
+        <v>483.75</v>
       </c>
       <c r="D7" t="n">
-        <v>2403.7</v>
+        <v>469.6</v>
       </c>
       <c r="E7" t="n">
-        <v>2415</v>
+        <v>479</v>
       </c>
       <c r="F7" t="n">
-        <v>616900</v>
+        <v>1109585</v>
       </c>
       <c r="G7" t="n">
-        <v>1537658</v>
+        <v>2549457</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5988054560897157</v>
+        <v>-0.5647759503298153</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>JUBLFOOD</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HUDCO</t>
+          <t>ASTRAL</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>215</v>
+        <v>1546</v>
       </c>
       <c r="C8" t="n">
-        <v>220.3</v>
+        <v>1548.9</v>
       </c>
       <c r="D8" t="n">
-        <v>212.8</v>
+        <v>1520.6</v>
       </c>
       <c r="E8" t="n">
-        <v>216.8</v>
+        <v>1534.4</v>
       </c>
       <c r="F8" t="n">
-        <v>4480936</v>
+        <v>333474</v>
       </c>
       <c r="G8" t="n">
-        <v>8860387</v>
+        <v>803166</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4942731056781154</v>
+        <v>-0.5848006514219974</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>HUDCO</t>
+          <t>ASTRAL</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DALBHARAT</t>
+          <t>NCC</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1920.9</v>
+        <v>164</v>
       </c>
       <c r="C9" t="n">
-        <v>1980</v>
+        <v>164.94</v>
       </c>
       <c r="D9" t="n">
-        <v>1918</v>
+        <v>161.5</v>
       </c>
       <c r="E9" t="n">
-        <v>1964.8</v>
+        <v>164</v>
       </c>
       <c r="F9" t="n">
-        <v>419247</v>
+        <v>2111875</v>
       </c>
       <c r="G9" t="n">
-        <v>923966</v>
+        <v>4245653</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5462527841933578</v>
+        <v>-0.5025794618636992</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>DALBHARAT</t>
+          <t>NCC</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ICICIPRULI</t>
+          <t>ABFRL</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>522</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>530.4</v>
+        <v>66.31</v>
       </c>
       <c r="D10" t="n">
-        <v>522</v>
+        <v>63.87</v>
       </c>
       <c r="E10" t="n">
-        <v>524.2</v>
+        <v>63.9</v>
       </c>
       <c r="F10" t="n">
-        <v>567464</v>
+        <v>4094830</v>
       </c>
       <c r="G10" t="n">
-        <v>1284261</v>
+        <v>8814902</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5581396616419871</v>
+        <v>-0.5354650567867912</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ICICIPRULI</t>
+          <t>ABFRL</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -837,528 +837,363 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>263.3</v>
+        <v>1261</v>
       </c>
       <c r="C2" t="n">
-        <v>265.4</v>
+        <v>1272.2</v>
       </c>
       <c r="D2" t="n">
-        <v>253</v>
+        <v>1259</v>
       </c>
       <c r="E2" t="n">
-        <v>253.47</v>
+        <v>1265.7</v>
       </c>
       <c r="F2" t="n">
-        <v>152137971</v>
+        <v>17740110</v>
       </c>
       <c r="G2" t="n">
-        <v>104988011</v>
+        <v>11716030</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4490985165915754</v>
+        <v>0.5141741699193327</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3100</v>
+        <v>1167.5</v>
       </c>
       <c r="C3" t="n">
-        <v>3192</v>
+        <v>1189.8</v>
       </c>
       <c r="D3" t="n">
-        <v>3092</v>
+        <v>1159.6</v>
       </c>
       <c r="E3" t="n">
-        <v>3149</v>
+        <v>1182.6</v>
       </c>
       <c r="F3" t="n">
-        <v>3917359</v>
+        <v>12205669</v>
       </c>
       <c r="G3" t="n">
-        <v>2645344</v>
+        <v>8303109</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4808505056431224</v>
+        <v>0.4700118955441871</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>INFY</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>409.5</v>
+        <v>2479</v>
       </c>
       <c r="C4" t="n">
-        <v>410</v>
+        <v>2491</v>
       </c>
       <c r="D4" t="n">
-        <v>399.65</v>
+        <v>2438</v>
       </c>
       <c r="E4" t="n">
-        <v>400.1</v>
+        <v>2474.8</v>
       </c>
       <c r="F4" t="n">
-        <v>11920835</v>
+        <v>3970446</v>
       </c>
       <c r="G4" t="n">
-        <v>7726655</v>
+        <v>2835961</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5428196289338659</v>
+        <v>0.40003547298429</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>TCS</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>HDFCAMC</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>745</v>
+        <v>2770.1</v>
       </c>
       <c r="C5" t="n">
-        <v>780</v>
+        <v>2774.9</v>
       </c>
       <c r="D5" t="n">
-        <v>732.2</v>
+        <v>2703.7</v>
       </c>
       <c r="E5" t="n">
-        <v>775</v>
+        <v>2719.6</v>
       </c>
       <c r="F5" t="n">
-        <v>54738724</v>
+        <v>1255481</v>
       </c>
       <c r="G5" t="n">
-        <v>37978285</v>
+        <v>832683</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4413163732906844</v>
+        <v>0.5077538511054026</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>HDFCAMC</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>UNITDSPR</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>368.05</v>
+        <v>1350</v>
       </c>
       <c r="C6" t="n">
-        <v>372.45</v>
+        <v>1350</v>
       </c>
       <c r="D6" t="n">
-        <v>358.1</v>
+        <v>1322</v>
       </c>
       <c r="E6" t="n">
-        <v>362.3</v>
+        <v>1328</v>
       </c>
       <c r="F6" t="n">
-        <v>16891422</v>
+        <v>1077576</v>
       </c>
       <c r="G6" t="n">
-        <v>10991705</v>
+        <v>769004</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5367426618527334</v>
+        <v>0.4012618920057633</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>UNITDSPR</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5674</v>
+        <v>8132.5</v>
       </c>
       <c r="C7" t="n">
-        <v>5734.5</v>
+        <v>8163.5</v>
       </c>
       <c r="D7" t="n">
-        <v>5665</v>
+        <v>7970.5</v>
       </c>
       <c r="E7" t="n">
-        <v>5719</v>
+        <v>8088.5</v>
       </c>
       <c r="F7" t="n">
-        <v>363567</v>
+        <v>415486</v>
       </c>
       <c r="G7" t="n">
-        <v>249233</v>
+        <v>263510</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4587434248273703</v>
+        <v>0.576737125725779</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>POLYCAB</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BOSCHLTD</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>37165</v>
+        <v>2297</v>
       </c>
       <c r="C8" t="n">
-        <v>37470</v>
+        <v>2317.4</v>
       </c>
       <c r="D8" t="n">
-        <v>36190</v>
+        <v>2277.7</v>
       </c>
       <c r="E8" t="n">
-        <v>36350</v>
+        <v>2312.3</v>
       </c>
       <c r="F8" t="n">
-        <v>34734</v>
+        <v>1095515</v>
       </c>
       <c r="G8" t="n">
-        <v>21761</v>
+        <v>706510</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5961582647856256</v>
+        <v>0.550600840752431</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BOSCHLTD</t>
+          <t>LUPIN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>VOLTAS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2911.9</v>
+        <v>1470</v>
       </c>
       <c r="C9" t="n">
-        <v>2980.9</v>
+        <v>1470</v>
       </c>
       <c r="D9" t="n">
-        <v>2862</v>
+        <v>1418.2</v>
       </c>
       <c r="E9" t="n">
-        <v>2975</v>
+        <v>1438</v>
       </c>
       <c r="F9" t="n">
-        <v>2698924</v>
+        <v>1259835</v>
       </c>
       <c r="G9" t="n">
-        <v>1771034</v>
+        <v>793781</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5239255711635123</v>
+        <v>0.5871317151708091</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>VOLTAS</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IDFCFIRSTB</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>69.02</v>
+        <v>1678.5</v>
       </c>
       <c r="C10" t="n">
-        <v>71.15000000000001</v>
+        <v>1769.9</v>
       </c>
       <c r="D10" t="n">
-        <v>68.55</v>
+        <v>1666.1</v>
       </c>
       <c r="E10" t="n">
-        <v>70</v>
+        <v>1750</v>
       </c>
       <c r="F10" t="n">
-        <v>35995299</v>
+        <v>779793</v>
       </c>
       <c r="G10" t="n">
-        <v>25640804</v>
+        <v>549933</v>
       </c>
       <c r="H10" t="n">
-        <v>0.40382879569611</v>
+        <v>0.4179781900704267</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>IDFCFIRSTB</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>339.95</v>
+        <v>1038.2</v>
       </c>
       <c r="C11" t="n">
-        <v>354.65</v>
+        <v>1041.35</v>
       </c>
       <c r="D11" t="n">
-        <v>337.55</v>
+        <v>1009</v>
       </c>
       <c r="E11" t="n">
-        <v>347.65</v>
+        <v>1040</v>
       </c>
       <c r="F11" t="n">
-        <v>6756111</v>
+        <v>1026753</v>
       </c>
       <c r="G11" t="n">
-        <v>4701866</v>
+        <v>687054</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4368999456811402</v>
+        <v>0.4944283855417478</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>360ONE</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>KEI</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4997</v>
+        <v>5354.5</v>
       </c>
       <c r="C12" t="n">
-        <v>5050</v>
+        <v>5435</v>
       </c>
       <c r="D12" t="n">
-        <v>4917.1</v>
+        <v>5291</v>
       </c>
       <c r="E12" t="n">
-        <v>4959</v>
+        <v>5429.5</v>
       </c>
       <c r="F12" t="n">
-        <v>354086</v>
+        <v>151866</v>
       </c>
       <c r="G12" t="n">
-        <v>236667</v>
+        <v>96480</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4961359209353226</v>
+        <v>0.5740671641791045</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>KEI</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>GODREJPROP</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1831</v>
-      </c>
-      <c r="C13" t="n">
-        <v>1883.8</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1831</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1858</v>
-      </c>
-      <c r="F13" t="n">
-        <v>860344</v>
-      </c>
-      <c r="G13" t="n">
-        <v>558117</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.5415119052098395</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>GODREJPROP</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>KALYANKJIL</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>413.55</v>
-      </c>
-      <c r="C14" t="n">
-        <v>420.6</v>
-      </c>
-      <c r="D14" t="n">
-        <v>409.45</v>
-      </c>
-      <c r="E14" t="n">
-        <v>412.8</v>
-      </c>
-      <c r="F14" t="n">
-        <v>3443668</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2219506</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.5515470559665079</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>KALYANKJIL</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>PATANJALI</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>465</v>
-      </c>
-      <c r="C15" t="n">
-        <v>469.4</v>
-      </c>
-      <c r="D15" t="n">
-        <v>462.1</v>
-      </c>
-      <c r="E15" t="n">
-        <v>465</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1582925</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1079986</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.4656902959853183</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>PATANJALI</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>CROMPTON</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>270.9</v>
-      </c>
-      <c r="C16" t="n">
-        <v>280.89</v>
-      </c>
-      <c r="D16" t="n">
-        <v>269.63</v>
-      </c>
-      <c r="E16" t="n">
-        <v>275.61</v>
-      </c>
-      <c r="F16" t="n">
-        <v>17813850</v>
-      </c>
-      <c r="G16" t="n">
-        <v>11443201</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.5567191382900641</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>CROMPTON</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>CDSL</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1331</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1345.5</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1300.2</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1304.8</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1876708</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1238028</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.5158849395974889</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>CDSL</t>
+          <t>ALKEM</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,6 +473,402 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>filterdata</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>481.6</v>
+      </c>
+      <c r="C2" t="n">
+        <v>487</v>
+      </c>
+      <c r="D2" t="n">
+        <v>475.6</v>
+      </c>
+      <c r="E2" t="n">
+        <v>480</v>
+      </c>
+      <c r="F2" t="n">
+        <v>7757497</v>
+      </c>
+      <c r="G2" t="n">
+        <v>16935052</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-0.5419265910727643</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>591.95</v>
+      </c>
+      <c r="C3" t="n">
+        <v>596.2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>583</v>
+      </c>
+      <c r="E3" t="n">
+        <v>587.5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2591864</v>
+      </c>
+      <c r="G3" t="n">
+        <v>6234625</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-0.5842790865529202</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BANKBARODA</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>264.95</v>
+      </c>
+      <c r="C4" t="n">
+        <v>271.6</v>
+      </c>
+      <c r="D4" t="n">
+        <v>264.2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>265.9</v>
+      </c>
+      <c r="F4" t="n">
+        <v>6230309</v>
+      </c>
+      <c r="G4" t="n">
+        <v>12323040</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.4944178546852075</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>BANKBARODA</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1378.2</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1389</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1361.1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1364.9</v>
+      </c>
+      <c r="F5" t="n">
+        <v>649397</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1333712</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.5130905322888299</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1912.3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1916.1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1837.5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1847</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1030440</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2076179</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.5036844125675098</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>HAVELLS</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1241.1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1264</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1238.1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1255</v>
+      </c>
+      <c r="F7" t="n">
+        <v>769063</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1559906</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.5069811898922114</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>HAVELLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>VOLTAS</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1445.2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1463.7</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1413.3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1454</v>
+      </c>
+      <c r="F8" t="n">
+        <v>506557</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1259835</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.597917981322951</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>VOLTAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MARICO</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>781</v>
+      </c>
+      <c r="C9" t="n">
+        <v>786.75</v>
+      </c>
+      <c r="D9" t="n">
+        <v>774.9</v>
+      </c>
+      <c r="E9" t="n">
+        <v>786</v>
+      </c>
+      <c r="F9" t="n">
+        <v>869429</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1716176</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.4933917034150344</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MARICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SUPREMEIND</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3669</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3691.2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3581.2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3625</v>
+      </c>
+      <c r="F10" t="n">
+        <v>146015</v>
+      </c>
+      <c r="G10" t="n">
+        <v>302540</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.5173696040193032</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>SUPREMEIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1669</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1708.9</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1665.4</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1687.6</v>
+      </c>
+      <c r="F11" t="n">
+        <v>227992</v>
+      </c>
+      <c r="G11" t="n">
+        <v>482607</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.5275824842988187</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CAMS</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>750</v>
+      </c>
+      <c r="C12" t="n">
+        <v>750.6</v>
+      </c>
+      <c r="D12" t="n">
+        <v>715.5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>733</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1152415</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2717763</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.57596928061792</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>CAMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PPLPHARMA</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>163.34</v>
+      </c>
+      <c r="C13" t="n">
+        <v>163.96</v>
+      </c>
+      <c r="D13" t="n">
+        <v>159.45</v>
+      </c>
+      <c r="E13" t="n">
+        <v>160.49</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1744074</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3440783</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.4931171189813481</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>PPLPHARMA</t>
         </is>
       </c>
     </row>
@@ -487,7 +883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,6 +933,237 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BSE</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3681</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3755</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3673</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3764178</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2381291</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.580729948586712</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>BSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>487</v>
+      </c>
+      <c r="C3" t="n">
+        <v>490.8</v>
+      </c>
+      <c r="D3" t="n">
+        <v>472.6</v>
+      </c>
+      <c r="E3" t="n">
+        <v>477</v>
+      </c>
+      <c r="F3" t="n">
+        <v>6718867</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4736274</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.4185976149183936</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1209.8</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1211.2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1147.1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1153.9</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2133159</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1424354</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.497632610994177</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ICICIPRULI</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>519.35</v>
+      </c>
+      <c r="C5" t="n">
+        <v>538.35</v>
+      </c>
+      <c r="D5" t="n">
+        <v>516.25</v>
+      </c>
+      <c r="E5" t="n">
+        <v>537</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1731763</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1123792</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.5409995799934507</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ICICIPRULI</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DALBHARAT</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1928.7</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2007.6</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1920.6</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1988</v>
+      </c>
+      <c r="F6" t="n">
+        <v>409383</v>
+      </c>
+      <c r="G6" t="n">
+        <v>275052</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.4883840146590463</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>DALBHARAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PRESTIGE</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1416.5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1473.2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1416.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1451.3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>432497</v>
+      </c>
+      <c r="G7" t="n">
+        <v>301820</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.4329633556424359</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>PRESTIGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BANDHANBNK</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>202.7</v>
+      </c>
+      <c r="C8" t="n">
+        <v>212.66</v>
+      </c>
+      <c r="D8" t="n">
+        <v>201.3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>206.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>40101677</v>
+      </c>
+      <c r="G8" t="n">
+        <v>27193264</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.4746915633224463</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>BANDHANBNK</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,396 +479,231 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>481.6</v>
+        <v>1287.6</v>
       </c>
       <c r="C2" t="n">
-        <v>487</v>
+        <v>1292.4</v>
       </c>
       <c r="D2" t="n">
-        <v>475.6</v>
+        <v>1268.5</v>
       </c>
       <c r="E2" t="n">
-        <v>480</v>
+        <v>1272.1</v>
       </c>
       <c r="F2" t="n">
-        <v>7757497</v>
+        <v>986348</v>
       </c>
       <c r="G2" t="n">
-        <v>16935052</v>
+        <v>2285506</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5419265910727643</v>
+        <v>-0.568433423495716</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>DRREDDY</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>591.95</v>
+        <v>1465</v>
       </c>
       <c r="C3" t="n">
-        <v>596.2</v>
+        <v>1483.8</v>
       </c>
       <c r="D3" t="n">
-        <v>583</v>
+        <v>1447.1</v>
       </c>
       <c r="E3" t="n">
-        <v>587.5</v>
+        <v>1451.2</v>
       </c>
       <c r="F3" t="n">
-        <v>2591864</v>
+        <v>711081</v>
       </c>
       <c r="G3" t="n">
-        <v>6234625</v>
+        <v>1483759</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5842790865529202</v>
+        <v>-0.5207570771264066</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>TECHM</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>264.95</v>
+        <v>1644</v>
       </c>
       <c r="C4" t="n">
-        <v>271.6</v>
+        <v>1666.9</v>
       </c>
       <c r="D4" t="n">
-        <v>264.2</v>
+        <v>1623</v>
       </c>
       <c r="E4" t="n">
-        <v>265.9</v>
+        <v>1656</v>
       </c>
       <c r="F4" t="n">
-        <v>6230309</v>
+        <v>2688312</v>
       </c>
       <c r="G4" t="n">
-        <v>12323040</v>
+        <v>5637755</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4944178546852075</v>
+        <v>-0.5231591298309345</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1378.2</v>
+        <v>1882.6</v>
       </c>
       <c r="C5" t="n">
-        <v>1389</v>
+        <v>1882.6</v>
       </c>
       <c r="D5" t="n">
-        <v>1361.1</v>
+        <v>1848.1</v>
       </c>
       <c r="E5" t="n">
-        <v>1364.9</v>
+        <v>1880</v>
       </c>
       <c r="F5" t="n">
-        <v>649397</v>
+        <v>1091446</v>
       </c>
       <c r="G5" t="n">
-        <v>1333712</v>
+        <v>2345967</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5130905322888299</v>
+        <v>-0.5347564565059952</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>ICICIPRULI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1912.3</v>
+        <v>535.9</v>
       </c>
       <c r="C6" t="n">
-        <v>1916.1</v>
+        <v>540.7</v>
       </c>
       <c r="D6" t="n">
-        <v>1837.5</v>
+        <v>528.8</v>
       </c>
       <c r="E6" t="n">
-        <v>1847</v>
+        <v>538</v>
       </c>
       <c r="F6" t="n">
-        <v>1030440</v>
+        <v>824889</v>
       </c>
       <c r="G6" t="n">
-        <v>2076179</v>
+        <v>1731763</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5036844125675098</v>
+        <v>-0.5236709642139253</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>ICICIPRULI</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>SONACOMS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1241.1</v>
+        <v>575.45</v>
       </c>
       <c r="C7" t="n">
-        <v>1264</v>
+        <v>581</v>
       </c>
       <c r="D7" t="n">
-        <v>1238.1</v>
+        <v>569.35</v>
       </c>
       <c r="E7" t="n">
-        <v>1255</v>
+        <v>577</v>
       </c>
       <c r="F7" t="n">
-        <v>769063</v>
+        <v>3817731</v>
       </c>
       <c r="G7" t="n">
-        <v>1559906</v>
+        <v>9158079</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5069811898922114</v>
+        <v>-0.5831297153038317</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>SONACOMS</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VOLTAS</t>
+          <t>ABFRL</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1445.2</v>
+        <v>65.05</v>
       </c>
       <c r="C8" t="n">
-        <v>1463.7</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>1413.3</v>
+        <v>63.51</v>
       </c>
       <c r="E8" t="n">
-        <v>1454</v>
+        <v>63.96</v>
       </c>
       <c r="F8" t="n">
-        <v>506557</v>
+        <v>5748983</v>
       </c>
       <c r="G8" t="n">
-        <v>1259835</v>
+        <v>13102078</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.597917981322951</v>
+        <v>-0.5612159384183181</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>VOLTAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>MARICO</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>781</v>
-      </c>
-      <c r="C9" t="n">
-        <v>786.75</v>
-      </c>
-      <c r="D9" t="n">
-        <v>774.9</v>
-      </c>
-      <c r="E9" t="n">
-        <v>786</v>
-      </c>
-      <c r="F9" t="n">
-        <v>869429</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1716176</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-0.4933917034150344</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>MARICO</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>SUPREMEIND</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>3669</v>
-      </c>
-      <c r="C10" t="n">
-        <v>3691.2</v>
-      </c>
-      <c r="D10" t="n">
-        <v>3581.2</v>
-      </c>
-      <c r="E10" t="n">
-        <v>3625</v>
-      </c>
-      <c r="F10" t="n">
-        <v>146015</v>
-      </c>
-      <c r="G10" t="n">
-        <v>302540</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-0.5173696040193032</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>SUPREMEIND</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>OBEROIRLTY</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1669</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1708.9</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1665.4</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1687.6</v>
-      </c>
-      <c r="F11" t="n">
-        <v>227992</v>
-      </c>
-      <c r="G11" t="n">
-        <v>482607</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-0.5275824842988187</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>OBEROIRLTY</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CAMS</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>750</v>
-      </c>
-      <c r="C12" t="n">
-        <v>750.6</v>
-      </c>
-      <c r="D12" t="n">
-        <v>715.5</v>
-      </c>
-      <c r="E12" t="n">
-        <v>733</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1152415</v>
-      </c>
-      <c r="G12" t="n">
-        <v>2717763</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-0.57596928061792</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>CAMS</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>PPLPHARMA</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>163.34</v>
-      </c>
-      <c r="C13" t="n">
-        <v>163.96</v>
-      </c>
-      <c r="D13" t="n">
-        <v>159.45</v>
-      </c>
-      <c r="E13" t="n">
-        <v>160.49</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1744074</v>
-      </c>
-      <c r="G13" t="n">
-        <v>3440783</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-0.4931171189813481</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>PPLPHARMA</t>
+          <t>ABFRL</t>
         </is>
       </c>
     </row>
@@ -936,231 +771,231 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3681</v>
+        <v>1456</v>
       </c>
       <c r="C2" t="n">
-        <v>3755</v>
+        <v>1480.4</v>
       </c>
       <c r="D2" t="n">
-        <v>3673</v>
+        <v>1447.6</v>
       </c>
       <c r="E2" t="n">
-        <v>3712</v>
+        <v>1473</v>
       </c>
       <c r="F2" t="n">
-        <v>3764178</v>
+        <v>2490700</v>
       </c>
       <c r="G2" t="n">
-        <v>2381291</v>
+        <v>1744112</v>
       </c>
       <c r="H2" t="n">
-        <v>0.580729948586712</v>
+        <v>0.4280619593237132</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>487</v>
+        <v>587.05</v>
       </c>
       <c r="C3" t="n">
-        <v>490.8</v>
+        <v>601.95</v>
       </c>
       <c r="D3" t="n">
-        <v>472.6</v>
+        <v>586</v>
       </c>
       <c r="E3" t="n">
-        <v>477</v>
+        <v>595</v>
       </c>
       <c r="F3" t="n">
-        <v>6718867</v>
+        <v>4081766</v>
       </c>
       <c r="G3" t="n">
-        <v>4736274</v>
+        <v>2591864</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4185976149183936</v>
+        <v>0.5748380316251162</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1209.8</v>
+        <v>1394.6</v>
       </c>
       <c r="C4" t="n">
-        <v>1211.2</v>
+        <v>1438</v>
       </c>
       <c r="D4" t="n">
-        <v>1147.1</v>
+        <v>1377</v>
       </c>
       <c r="E4" t="n">
-        <v>1153.9</v>
+        <v>1408.5</v>
       </c>
       <c r="F4" t="n">
-        <v>2133159</v>
+        <v>5440472</v>
       </c>
       <c r="G4" t="n">
-        <v>1424354</v>
+        <v>3745191</v>
       </c>
       <c r="H4" t="n">
-        <v>0.497632610994177</v>
+        <v>0.4526554186422001</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ICICIPRULI</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>519.35</v>
+        <v>11400</v>
       </c>
       <c r="C5" t="n">
-        <v>538.35</v>
+        <v>11674</v>
       </c>
       <c r="D5" t="n">
-        <v>516.25</v>
+        <v>11200</v>
       </c>
       <c r="E5" t="n">
-        <v>537</v>
+        <v>11287</v>
       </c>
       <c r="F5" t="n">
-        <v>1731763</v>
+        <v>552400</v>
       </c>
       <c r="G5" t="n">
-        <v>1123792</v>
+        <v>380919</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5409995799934507</v>
+        <v>0.4501770717659135</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ICICIPRULI</t>
+          <t>DIXON</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DALBHARAT</t>
+          <t>BLUESTARCO</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1928.7</v>
+        <v>1802.2</v>
       </c>
       <c r="C6" t="n">
-        <v>2007.6</v>
+        <v>1824.9</v>
       </c>
       <c r="D6" t="n">
-        <v>1920.6</v>
+        <v>1781</v>
       </c>
       <c r="E6" t="n">
-        <v>1988</v>
+        <v>1800</v>
       </c>
       <c r="F6" t="n">
-        <v>409383</v>
+        <v>465048</v>
       </c>
       <c r="G6" t="n">
-        <v>275052</v>
+        <v>305152</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4883840146590463</v>
+        <v>0.5239880453020134</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>DALBHARAT</t>
+          <t>BLUESTARCO</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PRESTIGE</t>
+          <t>MANAPPURAM</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1416.5</v>
+        <v>307.4</v>
       </c>
       <c r="C7" t="n">
-        <v>1473.2</v>
+        <v>309.5</v>
       </c>
       <c r="D7" t="n">
-        <v>1416.5</v>
+        <v>296.4</v>
       </c>
       <c r="E7" t="n">
-        <v>1451.3</v>
+        <v>308.75</v>
       </c>
       <c r="F7" t="n">
-        <v>432497</v>
+        <v>11108758</v>
       </c>
       <c r="G7" t="n">
-        <v>301820</v>
+        <v>7852190</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4329633556424359</v>
+        <v>0.4147337239674537</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PRESTIGE</t>
+          <t>MANAPPURAM</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>AMBER</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>202.7</v>
+        <v>8030</v>
       </c>
       <c r="C8" t="n">
-        <v>212.66</v>
+        <v>8271</v>
       </c>
       <c r="D8" t="n">
-        <v>201.3</v>
+        <v>7961</v>
       </c>
       <c r="E8" t="n">
-        <v>206.5</v>
+        <v>8200</v>
       </c>
       <c r="F8" t="n">
-        <v>40101677</v>
+        <v>297825</v>
       </c>
       <c r="G8" t="n">
-        <v>27193264</v>
+        <v>206473</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4746915633224463</v>
+        <v>0.4424404159381614</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>AMBER</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,231 +479,99 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1287.6</v>
+        <v>1817</v>
       </c>
       <c r="C2" t="n">
-        <v>1292.4</v>
+        <v>1841.5</v>
       </c>
       <c r="D2" t="n">
-        <v>1268.5</v>
+        <v>1813.8</v>
       </c>
       <c r="E2" t="n">
-        <v>1272.1</v>
+        <v>1833.8</v>
       </c>
       <c r="F2" t="n">
-        <v>986348</v>
+        <v>5507749</v>
       </c>
       <c r="G2" t="n">
-        <v>2285506</v>
+        <v>11407461</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.568433423495716</v>
+        <v>-0.5171801157154953</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>TATACHEM</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1465</v>
+        <v>804</v>
       </c>
       <c r="C3" t="n">
-        <v>1483.8</v>
+        <v>830.5</v>
       </c>
       <c r="D3" t="n">
-        <v>1447.1</v>
+        <v>802.2</v>
       </c>
       <c r="E3" t="n">
-        <v>1451.2</v>
+        <v>816</v>
       </c>
       <c r="F3" t="n">
-        <v>711081</v>
+        <v>2550372</v>
       </c>
       <c r="G3" t="n">
-        <v>1483759</v>
+        <v>5080048</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5207570771264066</v>
+        <v>-0.4979630113731209</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>TATACHEM</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>MANAPPURAM</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1644</v>
+        <v>309.4</v>
       </c>
       <c r="C4" t="n">
-        <v>1666.9</v>
+        <v>313.45</v>
       </c>
       <c r="D4" t="n">
-        <v>1623</v>
+        <v>306.1</v>
       </c>
       <c r="E4" t="n">
-        <v>1656</v>
+        <v>310.85</v>
       </c>
       <c r="F4" t="n">
-        <v>2688312</v>
+        <v>4898526</v>
       </c>
       <c r="G4" t="n">
-        <v>5637755</v>
+        <v>11108758</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5231591298309345</v>
+        <v>-0.5590392733373074</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>APLAPOLLO</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1882.6</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1882.6</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1848.1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1880</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1091446</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2345967</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-0.5347564565059952</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>APLAPOLLO</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ICICIPRULI</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>535.9</v>
-      </c>
-      <c r="C6" t="n">
-        <v>540.7</v>
-      </c>
-      <c r="D6" t="n">
-        <v>528.8</v>
-      </c>
-      <c r="E6" t="n">
-        <v>538</v>
-      </c>
-      <c r="F6" t="n">
-        <v>824889</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1731763</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-0.5236709642139253</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>ICICIPRULI</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>SONACOMS</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>575.45</v>
-      </c>
-      <c r="C7" t="n">
-        <v>581</v>
-      </c>
-      <c r="D7" t="n">
-        <v>569.35</v>
-      </c>
-      <c r="E7" t="n">
-        <v>577</v>
-      </c>
-      <c r="F7" t="n">
-        <v>3817731</v>
-      </c>
-      <c r="G7" t="n">
-        <v>9158079</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-0.5831297153038317</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>SONACOMS</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>ABFRL</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>65.05</v>
-      </c>
-      <c r="C8" t="n">
-        <v>65.34999999999999</v>
-      </c>
-      <c r="D8" t="n">
-        <v>63.51</v>
-      </c>
-      <c r="E8" t="n">
-        <v>63.96</v>
-      </c>
-      <c r="F8" t="n">
-        <v>5748983</v>
-      </c>
-      <c r="G8" t="n">
-        <v>13102078</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-0.5612159384183181</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>ABFRL</t>
+          <t>MANAPPURAM</t>
         </is>
       </c>
     </row>
@@ -718,7 +586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -771,231 +639,363 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1456</v>
+        <v>980</v>
       </c>
       <c r="C2" t="n">
-        <v>1480.4</v>
+        <v>1007.45</v>
       </c>
       <c r="D2" t="n">
-        <v>1447.6</v>
+        <v>976.05</v>
       </c>
       <c r="E2" t="n">
-        <v>1473</v>
+        <v>1007</v>
       </c>
       <c r="F2" t="n">
-        <v>2490700</v>
+        <v>5858946</v>
       </c>
       <c r="G2" t="n">
-        <v>1744112</v>
+        <v>4029508</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4280619593237132</v>
+        <v>0.4540102662657575</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>587.05</v>
+        <v>1208</v>
       </c>
       <c r="C3" t="n">
-        <v>601.95</v>
+        <v>1212</v>
       </c>
       <c r="D3" t="n">
-        <v>586</v>
+        <v>1186.4</v>
       </c>
       <c r="E3" t="n">
-        <v>595</v>
+        <v>1190.9</v>
       </c>
       <c r="F3" t="n">
-        <v>4081766</v>
+        <v>3541520</v>
       </c>
       <c r="G3" t="n">
-        <v>2591864</v>
+        <v>2459953</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5748380316251162</v>
+        <v>0.439669782308849</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>HCLTECH</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>WIPRO</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1394.6</v>
+        <v>200.51</v>
       </c>
       <c r="C4" t="n">
-        <v>1438</v>
+        <v>201.13</v>
       </c>
       <c r="D4" t="n">
-        <v>1377</v>
+        <v>198.25</v>
       </c>
       <c r="E4" t="n">
-        <v>1408.5</v>
+        <v>199.25</v>
       </c>
       <c r="F4" t="n">
-        <v>5440472</v>
+        <v>13166683</v>
       </c>
       <c r="G4" t="n">
-        <v>3745191</v>
+        <v>8899200</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4526554186422001</v>
+        <v>0.4795355762315714</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>WIPRO</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11400</v>
+        <v>1160</v>
       </c>
       <c r="C5" t="n">
-        <v>11674</v>
+        <v>1166.9</v>
       </c>
       <c r="D5" t="n">
-        <v>11200</v>
+        <v>1138.9</v>
       </c>
       <c r="E5" t="n">
-        <v>11287</v>
+        <v>1149.5</v>
       </c>
       <c r="F5" t="n">
-        <v>552400</v>
+        <v>1566762</v>
       </c>
       <c r="G5" t="n">
-        <v>380919</v>
+        <v>1065572</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4501770717659135</v>
+        <v>0.4703483199633624</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BLUESTARCO</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1802.2</v>
+        <v>358.9</v>
       </c>
       <c r="C6" t="n">
-        <v>1824.9</v>
+        <v>361.1</v>
       </c>
       <c r="D6" t="n">
-        <v>1781</v>
+        <v>351.85</v>
       </c>
       <c r="E6" t="n">
-        <v>1800</v>
+        <v>359</v>
       </c>
       <c r="F6" t="n">
-        <v>465048</v>
+        <v>9798302</v>
       </c>
       <c r="G6" t="n">
-        <v>305152</v>
+        <v>6734583</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5239880453020134</v>
+        <v>0.4549233412076145</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>BLUESTARCO</t>
+          <t>RECLTD</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MANAPPURAM</t>
+          <t>PAYTM</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>307.4</v>
+        <v>1105</v>
       </c>
       <c r="C7" t="n">
-        <v>309.5</v>
+        <v>1121.1</v>
       </c>
       <c r="D7" t="n">
-        <v>296.4</v>
+        <v>1089.1</v>
       </c>
       <c r="E7" t="n">
-        <v>308.75</v>
+        <v>1110</v>
       </c>
       <c r="F7" t="n">
-        <v>11108758</v>
+        <v>2556125</v>
       </c>
       <c r="G7" t="n">
-        <v>7852190</v>
+        <v>1742149</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4147337239674537</v>
+        <v>0.4672252488162608</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MANAPPURAM</t>
+          <t>PAYTM</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8030</v>
+        <v>920.4</v>
       </c>
       <c r="C8" t="n">
-        <v>8271</v>
+        <v>949.75</v>
       </c>
       <c r="D8" t="n">
-        <v>7961</v>
+        <v>917.95</v>
       </c>
       <c r="E8" t="n">
-        <v>8200</v>
+        <v>948</v>
       </c>
       <c r="F8" t="n">
-        <v>297825</v>
+        <v>2901974</v>
       </c>
       <c r="G8" t="n">
-        <v>206473</v>
+        <v>2006111</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4424404159381614</v>
+        <v>0.4465670144872342</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>INDUSINDBK</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AUBANK</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1015</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1028.4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1002</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1027</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2454365</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1582710</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.5507357633426212</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>AUBANK</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1094.8</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1133.3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1086.5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1133</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1268118</v>
+      </c>
+      <c r="G10" t="n">
+        <v>865301</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.4655224020312007</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MFSL</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1604.9</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1657</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1604.9</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1653.7</v>
+      </c>
+      <c r="F11" t="n">
+        <v>612555</v>
+      </c>
+      <c r="G11" t="n">
+        <v>417763</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.4662739400090482</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MFSL</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TORNTPOWER</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1757</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1757</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1713.5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1726</v>
+      </c>
+      <c r="F12" t="n">
+        <v>529878</v>
+      </c>
+      <c r="G12" t="n">
+        <v>338438</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.5656575207275779</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>TORNTPOWER</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,99 +479,297 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1817</v>
+        <v>4340.8</v>
       </c>
       <c r="C2" t="n">
-        <v>1841.5</v>
+        <v>4355</v>
       </c>
       <c r="D2" t="n">
-        <v>1813.8</v>
+        <v>4287.7</v>
       </c>
       <c r="E2" t="n">
-        <v>1833.8</v>
+        <v>4296</v>
       </c>
       <c r="F2" t="n">
-        <v>5507749</v>
+        <v>599368</v>
       </c>
       <c r="G2" t="n">
-        <v>11407461</v>
+        <v>1384413</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5171801157154953</v>
+        <v>-0.5670598296895507</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>TRENT</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TATACHEM</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>804</v>
+        <v>1273</v>
       </c>
       <c r="C3" t="n">
-        <v>830.5</v>
+        <v>1284.4</v>
       </c>
       <c r="D3" t="n">
-        <v>802.2</v>
+        <v>1254.2</v>
       </c>
       <c r="E3" t="n">
-        <v>816</v>
+        <v>1254.2</v>
       </c>
       <c r="F3" t="n">
-        <v>2550372</v>
+        <v>992992</v>
       </c>
       <c r="G3" t="n">
-        <v>5080048</v>
+        <v>1985427</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4979630113731209</v>
+        <v>-0.4998597279073972</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>TATACHEM</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MANAPPURAM</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>309.4</v>
+        <v>11.39</v>
       </c>
       <c r="C4" t="n">
-        <v>313.45</v>
+        <v>11.39</v>
       </c>
       <c r="D4" t="n">
-        <v>306.1</v>
+        <v>11.11</v>
       </c>
       <c r="E4" t="n">
-        <v>310.85</v>
+        <v>11.23</v>
       </c>
       <c r="F4" t="n">
-        <v>4898526</v>
+        <v>422871156</v>
       </c>
       <c r="G4" t="n">
-        <v>11108758</v>
+        <v>879179908</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5590392733373074</v>
+        <v>-0.5190163558651297</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MANAPPURAM</t>
+          <t>IDEA</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>LUPIN</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2454.9</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2494</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2430.4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2462</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1409904</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2886186</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.5114992588835231</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>LUPIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1475.1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1498.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1469.3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1479.7</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1228324</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2420846</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.4926054775892394</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BANKINDIA</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>143.25</v>
+      </c>
+      <c r="C7" t="n">
+        <v>143.59</v>
+      </c>
+      <c r="D7" t="n">
+        <v>139.7</v>
+      </c>
+      <c r="E7" t="n">
+        <v>140.36</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10811865</v>
+      </c>
+      <c r="G7" t="n">
+        <v>21321991</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.4929242301997032</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>BANKINDIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>LTF</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>301.8</v>
+      </c>
+      <c r="C8" t="n">
+        <v>305.2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>297.85</v>
+      </c>
+      <c r="E8" t="n">
+        <v>303.95</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3760248</v>
+      </c>
+      <c r="G8" t="n">
+        <v>8849214</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.5750754812800323</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>LTF</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SBICARD</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>653.95</v>
+      </c>
+      <c r="C9" t="n">
+        <v>655.75</v>
+      </c>
+      <c r="D9" t="n">
+        <v>644.05</v>
+      </c>
+      <c r="E9" t="n">
+        <v>648</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1402065</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3405721</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.5883206522201907</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>SBICARD</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>IGL</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>170.8</v>
+      </c>
+      <c r="C10" t="n">
+        <v>171.84</v>
+      </c>
+      <c r="D10" t="n">
+        <v>168.95</v>
+      </c>
+      <c r="E10" t="n">
+        <v>170</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3341947</v>
+      </c>
+      <c r="G10" t="n">
+        <v>6848692</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.5120313484677074</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>IGL</t>
         </is>
       </c>
     </row>
@@ -586,7 +784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -639,363 +837,429 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>980</v>
+        <v>1835</v>
       </c>
       <c r="C2" t="n">
-        <v>1007.45</v>
+        <v>1843.9</v>
       </c>
       <c r="D2" t="n">
-        <v>976.05</v>
+        <v>1821.2</v>
       </c>
       <c r="E2" t="n">
-        <v>1007</v>
+        <v>1829.6</v>
       </c>
       <c r="F2" t="n">
-        <v>5858946</v>
+        <v>7914845</v>
       </c>
       <c r="G2" t="n">
-        <v>4029508</v>
+        <v>5507749</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4540102662657575</v>
+        <v>0.4370380712701323</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1208</v>
+        <v>7360.5</v>
       </c>
       <c r="C3" t="n">
-        <v>1212</v>
+        <v>7471.5</v>
       </c>
       <c r="D3" t="n">
-        <v>1186.4</v>
+        <v>7310.5</v>
       </c>
       <c r="E3" t="n">
-        <v>1190.9</v>
+        <v>7342</v>
       </c>
       <c r="F3" t="n">
-        <v>3541520</v>
+        <v>606372</v>
       </c>
       <c r="G3" t="n">
-        <v>2459953</v>
+        <v>403588</v>
       </c>
       <c r="H3" t="n">
-        <v>0.439669782308849</v>
+        <v>0.5024529966203157</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>200.51</v>
+        <v>2310</v>
       </c>
       <c r="C4" t="n">
-        <v>201.13</v>
+        <v>2327.9</v>
       </c>
       <c r="D4" t="n">
-        <v>198.25</v>
+        <v>2268.1</v>
       </c>
       <c r="E4" t="n">
-        <v>199.25</v>
+        <v>2273</v>
       </c>
       <c r="F4" t="n">
-        <v>13166683</v>
+        <v>1859012</v>
       </c>
       <c r="G4" t="n">
-        <v>8899200</v>
+        <v>1196175</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4795355762315714</v>
+        <v>0.5541304574999477</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>WIPRO</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1160</v>
+        <v>199.5</v>
       </c>
       <c r="C5" t="n">
-        <v>1166.9</v>
+        <v>200.28</v>
       </c>
       <c r="D5" t="n">
-        <v>1138.9</v>
+        <v>197.19</v>
       </c>
       <c r="E5" t="n">
-        <v>1149.5</v>
+        <v>197.39</v>
       </c>
       <c r="F5" t="n">
-        <v>1566762</v>
+        <v>19303572</v>
       </c>
       <c r="G5" t="n">
-        <v>1065572</v>
+        <v>13166683</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4703483199633624</v>
+        <v>0.4660922572526429</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>WIPRO</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>358.9</v>
+        <v>1024</v>
       </c>
       <c r="C6" t="n">
-        <v>361.1</v>
+        <v>1025.9</v>
       </c>
       <c r="D6" t="n">
-        <v>351.85</v>
+        <v>1008.9</v>
       </c>
       <c r="E6" t="n">
-        <v>359</v>
+        <v>1013.6</v>
       </c>
       <c r="F6" t="n">
-        <v>9798302</v>
+        <v>1886787</v>
       </c>
       <c r="G6" t="n">
-        <v>6734583</v>
+        <v>1327465</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4549233412076145</v>
+        <v>0.4213459488574087</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PAYTM</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1105</v>
+        <v>841.5</v>
       </c>
       <c r="C7" t="n">
-        <v>1121.1</v>
+        <v>872.35</v>
       </c>
       <c r="D7" t="n">
-        <v>1089.1</v>
+        <v>830.05</v>
       </c>
       <c r="E7" t="n">
-        <v>1110</v>
+        <v>860.35</v>
       </c>
       <c r="F7" t="n">
-        <v>2556125</v>
+        <v>13476263</v>
       </c>
       <c r="G7" t="n">
-        <v>1742149</v>
+        <v>8627698</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4672252488162608</v>
+        <v>0.5619766709497713</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PAYTM</t>
+          <t>CGPOWER</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>920.4</v>
+        <v>2651</v>
       </c>
       <c r="C8" t="n">
-        <v>949.75</v>
+        <v>2693.4</v>
       </c>
       <c r="D8" t="n">
-        <v>917.95</v>
+        <v>2636</v>
       </c>
       <c r="E8" t="n">
-        <v>948</v>
+        <v>2688</v>
       </c>
       <c r="F8" t="n">
-        <v>2901974</v>
+        <v>1507905</v>
       </c>
       <c r="G8" t="n">
-        <v>2006111</v>
+        <v>1033434</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4465670144872342</v>
+        <v>0.4591207566230645</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>CUMMINSIND</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1015</v>
+        <v>5352.5</v>
       </c>
       <c r="C9" t="n">
-        <v>1028.4</v>
+        <v>5424</v>
       </c>
       <c r="D9" t="n">
-        <v>1002</v>
+        <v>5317.5</v>
       </c>
       <c r="E9" t="n">
-        <v>1027</v>
+        <v>5415</v>
       </c>
       <c r="F9" t="n">
-        <v>2454365</v>
+        <v>496602</v>
       </c>
       <c r="G9" t="n">
-        <v>1582710</v>
+        <v>343679</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5507357633426212</v>
+        <v>0.4449588133112585</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>CUMMINSIND</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>GMRAIRPORT</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1094.8</v>
+        <v>99.11</v>
       </c>
       <c r="C10" t="n">
-        <v>1133.3</v>
+        <v>101.18</v>
       </c>
       <c r="D10" t="n">
-        <v>1086.5</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>1133</v>
+        <v>100.7</v>
       </c>
       <c r="F10" t="n">
-        <v>1268118</v>
+        <v>22959362</v>
       </c>
       <c r="G10" t="n">
-        <v>865301</v>
+        <v>15376427</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4655224020312007</v>
+        <v>0.493153253353331</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>GMRAIRPORT</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1604.9</v>
+        <v>283.35</v>
       </c>
       <c r="C11" t="n">
-        <v>1657</v>
+        <v>284.05</v>
       </c>
       <c r="D11" t="n">
-        <v>1604.9</v>
+        <v>278.1</v>
       </c>
       <c r="E11" t="n">
-        <v>1653.7</v>
+        <v>281.6</v>
       </c>
       <c r="F11" t="n">
-        <v>612555</v>
+        <v>6361421</v>
       </c>
       <c r="G11" t="n">
-        <v>417763</v>
+        <v>4247311</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4662739400090482</v>
+        <v>0.4977525780429076</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>PETRONET</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TORNTPOWER</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1757</v>
+        <v>2228</v>
       </c>
       <c r="C12" t="n">
-        <v>1757</v>
+        <v>2237.3</v>
       </c>
       <c r="D12" t="n">
-        <v>1713.5</v>
+        <v>2177.1</v>
       </c>
       <c r="E12" t="n">
-        <v>1726</v>
+        <v>2217</v>
       </c>
       <c r="F12" t="n">
-        <v>529878</v>
+        <v>592910</v>
       </c>
       <c r="G12" t="n">
-        <v>338438</v>
+        <v>416557</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5656575207275779</v>
+        <v>0.4233586279908872</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>TORNTPOWER</t>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NUVAMA</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1420</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1478.6</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1402</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1475</v>
+      </c>
+      <c r="F13" t="n">
+        <v>980887</v>
+      </c>
+      <c r="G13" t="n">
+        <v>683716</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.4346409912887807</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>NUVAMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>KFINTECH</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>920</v>
+      </c>
+      <c r="C14" t="n">
+        <v>938.1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>915</v>
+      </c>
+      <c r="E14" t="n">
+        <v>922.1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1292194</v>
+      </c>
+      <c r="G14" t="n">
+        <v>911245</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.4180533226519761</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>KFINTECH</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,297 +479,693 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4340.8</v>
+        <v>1279.6</v>
       </c>
       <c r="C2" t="n">
-        <v>4355</v>
+        <v>1279.6</v>
       </c>
       <c r="D2" t="n">
-        <v>4287.7</v>
+        <v>1261.2</v>
       </c>
       <c r="E2" t="n">
-        <v>4296</v>
+        <v>1267.8</v>
       </c>
       <c r="F2" t="n">
-        <v>599368</v>
+        <v>11137424</v>
       </c>
       <c r="G2" t="n">
-        <v>1384413</v>
+        <v>25028552</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5670598296895507</v>
+        <v>-0.5550112527484611</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1273</v>
+        <v>1426</v>
       </c>
       <c r="C3" t="n">
-        <v>1284.4</v>
+        <v>1442.8</v>
       </c>
       <c r="D3" t="n">
-        <v>1254.2</v>
+        <v>1417.5</v>
       </c>
       <c r="E3" t="n">
-        <v>1254.2</v>
+        <v>1436</v>
       </c>
       <c r="F3" t="n">
-        <v>992992</v>
+        <v>8663105</v>
       </c>
       <c r="G3" t="n">
-        <v>1985427</v>
+        <v>19816903</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4998597279073972</v>
+        <v>-0.5628426399422756</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>RELIANCE</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11.39</v>
+        <v>3357.8</v>
       </c>
       <c r="C4" t="n">
-        <v>11.39</v>
+        <v>3363</v>
       </c>
       <c r="D4" t="n">
-        <v>11.11</v>
+        <v>3317.6</v>
       </c>
       <c r="E4" t="n">
-        <v>11.23</v>
+        <v>3331.5</v>
       </c>
       <c r="F4" t="n">
-        <v>422871156</v>
+        <v>2071348</v>
       </c>
       <c r="G4" t="n">
-        <v>879179908</v>
+        <v>4916193</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5190163558651297</v>
+        <v>-0.57866829068753</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>M&amp;M</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2454.9</v>
+        <v>4010</v>
       </c>
       <c r="C5" t="n">
-        <v>2494</v>
+        <v>4014</v>
       </c>
       <c r="D5" t="n">
-        <v>2430.4</v>
+        <v>3960</v>
       </c>
       <c r="E5" t="n">
-        <v>2462</v>
+        <v>3978</v>
       </c>
       <c r="F5" t="n">
-        <v>1409904</v>
+        <v>1620273</v>
       </c>
       <c r="G5" t="n">
-        <v>2886186</v>
+        <v>3477185</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5114992588835231</v>
+        <v>-0.5340273813443921</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>LT</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1475.1</v>
+        <v>4488</v>
       </c>
       <c r="C6" t="n">
-        <v>1498.5</v>
+        <v>4545.8</v>
       </c>
       <c r="D6" t="n">
-        <v>1469.3</v>
+        <v>4465.7</v>
       </c>
       <c r="E6" t="n">
-        <v>1479.7</v>
+        <v>4522</v>
       </c>
       <c r="F6" t="n">
-        <v>1228324</v>
+        <v>827316</v>
       </c>
       <c r="G6" t="n">
-        <v>2420846</v>
+        <v>1723948</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4926054775892394</v>
+        <v>-0.5201038546406273</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>INDIGO</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BANKINDIA</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>143.25</v>
+        <v>398</v>
       </c>
       <c r="C7" t="n">
-        <v>143.59</v>
+        <v>405.1</v>
       </c>
       <c r="D7" t="n">
-        <v>139.7</v>
+        <v>397.15</v>
       </c>
       <c r="E7" t="n">
-        <v>140.36</v>
+        <v>402.25</v>
       </c>
       <c r="F7" t="n">
-        <v>10811865</v>
+        <v>4740939</v>
       </c>
       <c r="G7" t="n">
-        <v>21321991</v>
+        <v>9700378</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4929242301997032</v>
+        <v>-0.5112624477108005</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>BANKINDIA</t>
+          <t>NTPC</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LTF</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>301.8</v>
+        <v>7299.5</v>
       </c>
       <c r="C8" t="n">
-        <v>305.2</v>
+        <v>7370</v>
       </c>
       <c r="D8" t="n">
-        <v>297.85</v>
+        <v>7228</v>
       </c>
       <c r="E8" t="n">
-        <v>303.95</v>
+        <v>7315</v>
       </c>
       <c r="F8" t="n">
-        <v>3760248</v>
+        <v>259522</v>
       </c>
       <c r="G8" t="n">
-        <v>8849214</v>
+        <v>606372</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5750754812800323</v>
+        <v>-0.5720086019803026</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>LTF</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SBICARD</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>653.95</v>
+        <v>1283.4</v>
       </c>
       <c r="C9" t="n">
-        <v>655.75</v>
+        <v>1284.9</v>
       </c>
       <c r="D9" t="n">
-        <v>644.05</v>
+        <v>1266.8</v>
       </c>
       <c r="E9" t="n">
-        <v>648</v>
+        <v>1277</v>
       </c>
       <c r="F9" t="n">
-        <v>1402065</v>
+        <v>811858</v>
       </c>
       <c r="G9" t="n">
-        <v>3405721</v>
+        <v>1773360</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5883206522201907</v>
+        <v>-0.5421922226733432</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SBICARD</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IGL</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>170.8</v>
+        <v>305.65</v>
       </c>
       <c r="C10" t="n">
-        <v>171.84</v>
+        <v>306.4</v>
       </c>
       <c r="D10" t="n">
-        <v>168.95</v>
+        <v>295.9</v>
       </c>
       <c r="E10" t="n">
-        <v>170</v>
+        <v>297</v>
       </c>
       <c r="F10" t="n">
-        <v>3341947</v>
+        <v>32681575</v>
       </c>
       <c r="G10" t="n">
-        <v>6848692</v>
+        <v>64690914</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5120313484677074</v>
+        <v>-0.4948042471621285</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>IGL</t>
+          <t>VEDL</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>130.99</v>
+      </c>
+      <c r="C11" t="n">
+        <v>132.76</v>
+      </c>
+      <c r="D11" t="n">
+        <v>130.52</v>
+      </c>
+      <c r="E11" t="n">
+        <v>131.57</v>
+      </c>
+      <c r="F11" t="n">
+        <v>17361170</v>
+      </c>
+      <c r="G11" t="n">
+        <v>38333083</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.5470969553896826</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>634.75</v>
+      </c>
+      <c r="C12" t="n">
+        <v>642.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>629.15</v>
+      </c>
+      <c r="E12" t="n">
+        <v>635</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3564594</v>
+      </c>
+      <c r="G12" t="n">
+        <v>7886637</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.5480210386252087</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>6700</v>
+      </c>
+      <c r="C13" t="n">
+        <v>6759</v>
+      </c>
+      <c r="D13" t="n">
+        <v>6675</v>
+      </c>
+      <c r="E13" t="n">
+        <v>6705</v>
+      </c>
+      <c r="F13" t="n">
+        <v>155071</v>
+      </c>
+      <c r="G13" t="n">
+        <v>330052</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.530161913880237</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>406.1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>408.9</v>
+      </c>
+      <c r="D14" t="n">
+        <v>400.1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>403.5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>17888566</v>
+      </c>
+      <c r="G14" t="n">
+        <v>37208886</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.5192394096399446</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2009.4</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2044</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1975.1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1984</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3399059</v>
+      </c>
+      <c r="G15" t="n">
+        <v>7055670</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.51825142048877</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1986.8</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2011.7</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1943.4</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1951</v>
+      </c>
+      <c r="F16" t="n">
+        <v>639610</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1360049</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.5297154734866171</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ABCAPITAL</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>369</v>
+      </c>
+      <c r="C17" t="n">
+        <v>369.85</v>
+      </c>
+      <c r="D17" t="n">
+        <v>361.35</v>
+      </c>
+      <c r="E17" t="n">
+        <v>362.3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2976183</v>
+      </c>
+      <c r="G17" t="n">
+        <v>6091049</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.511384163877191</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ABCAPITAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ASTRAL</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1565.2</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1594.6</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1565.2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1573</v>
+      </c>
+      <c r="F18" t="n">
+        <v>488596</v>
+      </c>
+      <c r="G18" t="n">
+        <v>984891</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.5039085543476385</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2199</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2228</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2182.9</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2211.5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>271921</v>
+      </c>
+      <c r="G19" t="n">
+        <v>592910</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.5413789613938035</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>566.05</v>
+      </c>
+      <c r="C20" t="n">
+        <v>570.85</v>
+      </c>
+      <c r="D20" t="n">
+        <v>564</v>
+      </c>
+      <c r="E20" t="n">
+        <v>565.45</v>
+      </c>
+      <c r="F20" t="n">
+        <v>675440</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1391332</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-0.5145371485741721</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1840</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1845</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1810.2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1845</v>
+      </c>
+      <c r="F21" t="n">
+        <v>144521</v>
+      </c>
+      <c r="G21" t="n">
+        <v>323880</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.5537822650364332</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CESC</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>186.46</v>
+      </c>
+      <c r="C22" t="n">
+        <v>187.45</v>
+      </c>
+      <c r="D22" t="n">
+        <v>183.92</v>
+      </c>
+      <c r="E22" t="n">
+        <v>185</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2029703</v>
+      </c>
+      <c r="G22" t="n">
+        <v>4218285</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-0.5188321794283696</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>CESC</t>
         </is>
       </c>
     </row>
@@ -784,7 +1180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -837,429 +1233,198 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1835</v>
+        <v>1740.4</v>
       </c>
       <c r="C2" t="n">
-        <v>1843.9</v>
+        <v>1792</v>
       </c>
       <c r="D2" t="n">
-        <v>1821.2</v>
+        <v>1727.7</v>
       </c>
       <c r="E2" t="n">
-        <v>1829.6</v>
+        <v>1760</v>
       </c>
       <c r="F2" t="n">
-        <v>7914845</v>
+        <v>4984856</v>
       </c>
       <c r="G2" t="n">
-        <v>5507749</v>
+        <v>3280485</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4370380712701323</v>
+        <v>0.5195484813983299</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7360.5</v>
+        <v>3069</v>
       </c>
       <c r="C3" t="n">
-        <v>7471.5</v>
+        <v>3136</v>
       </c>
       <c r="D3" t="n">
-        <v>7310.5</v>
+        <v>3022.4</v>
       </c>
       <c r="E3" t="n">
-        <v>7342</v>
+        <v>3098</v>
       </c>
       <c r="F3" t="n">
-        <v>606372</v>
+        <v>3775007</v>
       </c>
       <c r="G3" t="n">
-        <v>403588</v>
+        <v>2366069</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5024529966203157</v>
+        <v>0.5954762942247246</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>MCX</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2310</v>
+        <v>1032.4</v>
       </c>
       <c r="C4" t="n">
-        <v>2327.9</v>
+        <v>1052.3</v>
       </c>
       <c r="D4" t="n">
-        <v>2268.1</v>
+        <v>1026.3</v>
       </c>
       <c r="E4" t="n">
-        <v>2273</v>
+        <v>1051</v>
       </c>
       <c r="F4" t="n">
-        <v>1859012</v>
+        <v>2406953</v>
       </c>
       <c r="G4" t="n">
-        <v>1196175</v>
+        <v>1658965</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5541304574999477</v>
+        <v>0.4508762993794324</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>AUBANK</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>199.5</v>
+        <v>981.85</v>
       </c>
       <c r="C5" t="n">
-        <v>200.28</v>
+        <v>988.8</v>
       </c>
       <c r="D5" t="n">
-        <v>197.19</v>
+        <v>973.3</v>
       </c>
       <c r="E5" t="n">
-        <v>197.39</v>
+        <v>978</v>
       </c>
       <c r="F5" t="n">
-        <v>19303572</v>
+        <v>1597738</v>
       </c>
       <c r="G5" t="n">
-        <v>13166683</v>
+        <v>1114882</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4660922572526429</v>
+        <v>0.4331005433758909</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>NAUKRI</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MAXHEALTH</t>
+          <t>PRESTIGE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1024</v>
+        <v>1480</v>
       </c>
       <c r="C6" t="n">
-        <v>1025.9</v>
+        <v>1514.7</v>
       </c>
       <c r="D6" t="n">
-        <v>1008.9</v>
+        <v>1477.8</v>
       </c>
       <c r="E6" t="n">
-        <v>1013.6</v>
+        <v>1495.5</v>
       </c>
       <c r="F6" t="n">
-        <v>1886787</v>
+        <v>918187</v>
       </c>
       <c r="G6" t="n">
-        <v>1327465</v>
+        <v>616457</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4213459488574087</v>
+        <v>0.4894583077165155</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MAXHEALTH</t>
+          <t>PRESTIGE</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>841.5</v>
+        <v>1270</v>
       </c>
       <c r="C7" t="n">
-        <v>872.35</v>
+        <v>1274.4</v>
       </c>
       <c r="D7" t="n">
-        <v>830.05</v>
+        <v>1250.2</v>
       </c>
       <c r="E7" t="n">
-        <v>860.35</v>
+        <v>1261</v>
       </c>
       <c r="F7" t="n">
-        <v>13476263</v>
+        <v>2883848</v>
       </c>
       <c r="G7" t="n">
-        <v>8627698</v>
+        <v>1958453</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5619766709497713</v>
+        <v>0.4725132540837079</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>MAZDOCK</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2651</v>
-      </c>
-      <c r="C8" t="n">
-        <v>2693.4</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2636</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2688</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1507905</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1033434</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.4591207566230645</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>MAZDOCK</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CUMMINSIND</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>5352.5</v>
-      </c>
-      <c r="C9" t="n">
-        <v>5424</v>
-      </c>
-      <c r="D9" t="n">
-        <v>5317.5</v>
-      </c>
-      <c r="E9" t="n">
-        <v>5415</v>
-      </c>
-      <c r="F9" t="n">
-        <v>496602</v>
-      </c>
-      <c r="G9" t="n">
-        <v>343679</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.4449588133112585</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>CUMMINSIND</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>GMRAIRPORT</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>99.11</v>
-      </c>
-      <c r="C10" t="n">
-        <v>101.18</v>
-      </c>
-      <c r="D10" t="n">
-        <v>99.09999999999999</v>
-      </c>
-      <c r="E10" t="n">
-        <v>100.7</v>
-      </c>
-      <c r="F10" t="n">
-        <v>22959362</v>
-      </c>
-      <c r="G10" t="n">
-        <v>15376427</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.493153253353331</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>GMRAIRPORT</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>PETRONET</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>283.35</v>
-      </c>
-      <c r="C11" t="n">
-        <v>284.05</v>
-      </c>
-      <c r="D11" t="n">
-        <v>278.1</v>
-      </c>
-      <c r="E11" t="n">
-        <v>281.6</v>
-      </c>
-      <c r="F11" t="n">
-        <v>6361421</v>
-      </c>
-      <c r="G11" t="n">
-        <v>4247311</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.4977525780429076</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>PETRONET</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>MPHASIS</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2228</v>
-      </c>
-      <c r="C12" t="n">
-        <v>2237.3</v>
-      </c>
-      <c r="D12" t="n">
-        <v>2177.1</v>
-      </c>
-      <c r="E12" t="n">
-        <v>2217</v>
-      </c>
-      <c r="F12" t="n">
-        <v>592910</v>
-      </c>
-      <c r="G12" t="n">
-        <v>416557</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.4233586279908872</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>MPHASIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>NUVAMA</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1420</v>
-      </c>
-      <c r="C13" t="n">
-        <v>1478.6</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1402</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1475</v>
-      </c>
-      <c r="F13" t="n">
-        <v>980887</v>
-      </c>
-      <c r="G13" t="n">
-        <v>683716</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.4346409912887807</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>NUVAMA</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>KFINTECH</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>920</v>
-      </c>
-      <c r="C14" t="n">
-        <v>938.1</v>
-      </c>
-      <c r="D14" t="n">
-        <v>915</v>
-      </c>
-      <c r="E14" t="n">
-        <v>922.1</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1292194</v>
-      </c>
-      <c r="G14" t="n">
-        <v>911245</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.4180533226519761</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>KFINTECH</t>
+          <t>CDSL</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,693 +479,363 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1279.6</v>
+        <v>13442</v>
       </c>
       <c r="C2" t="n">
-        <v>1279.6</v>
+        <v>13455</v>
       </c>
       <c r="D2" t="n">
-        <v>1261.2</v>
+        <v>13150</v>
       </c>
       <c r="E2" t="n">
-        <v>1267.8</v>
+        <v>13188</v>
       </c>
       <c r="F2" t="n">
-        <v>11137424</v>
+        <v>302512</v>
       </c>
       <c r="G2" t="n">
-        <v>25028552</v>
+        <v>634354</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5550112527484611</v>
+        <v>-0.5231180066650483</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>MARUTI</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1426</v>
+        <v>4297.1</v>
       </c>
       <c r="C3" t="n">
-        <v>1442.8</v>
+        <v>4309.1</v>
       </c>
       <c r="D3" t="n">
-        <v>1417.5</v>
+        <v>4187.7</v>
       </c>
       <c r="E3" t="n">
-        <v>1436</v>
+        <v>4228.2</v>
       </c>
       <c r="F3" t="n">
-        <v>8663105</v>
+        <v>758162</v>
       </c>
       <c r="G3" t="n">
-        <v>19816903</v>
+        <v>1791551</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5628426399422756</v>
+        <v>-0.5768124937554108</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>INDIGO</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3357.8</v>
+        <v>2546.2</v>
       </c>
       <c r="C4" t="n">
-        <v>3363</v>
+        <v>2555.7</v>
       </c>
       <c r="D4" t="n">
-        <v>3317.6</v>
+        <v>2500</v>
       </c>
       <c r="E4" t="n">
-        <v>3331.5</v>
+        <v>2508</v>
       </c>
       <c r="F4" t="n">
-        <v>2071348</v>
+        <v>628802</v>
       </c>
       <c r="G4" t="n">
-        <v>4916193</v>
+        <v>1271257</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.57866829068753</v>
+        <v>-0.5053698819357534</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4010</v>
+        <v>6360</v>
       </c>
       <c r="C5" t="n">
-        <v>4014</v>
+        <v>6403</v>
       </c>
       <c r="D5" t="n">
-        <v>3960</v>
+        <v>6171.5</v>
       </c>
       <c r="E5" t="n">
-        <v>3978</v>
+        <v>6369</v>
       </c>
       <c r="F5" t="n">
-        <v>1620273</v>
+        <v>976463</v>
       </c>
       <c r="G5" t="n">
-        <v>3477185</v>
+        <v>2419336</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5340273813443921</v>
+        <v>-0.5963921505735458</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>ABB</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4488</v>
+        <v>127.66</v>
       </c>
       <c r="C6" t="n">
-        <v>4545.8</v>
+        <v>132.35</v>
       </c>
       <c r="D6" t="n">
-        <v>4465.7</v>
+        <v>127.43</v>
       </c>
       <c r="E6" t="n">
-        <v>4522</v>
+        <v>130.25</v>
       </c>
       <c r="F6" t="n">
-        <v>827316</v>
+        <v>29525188</v>
       </c>
       <c r="G6" t="n">
-        <v>1723948</v>
+        <v>71593041</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5201038546406273</v>
+        <v>-0.5875969565254254</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>CANBK</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>398</v>
+        <v>4509.5</v>
       </c>
       <c r="C7" t="n">
-        <v>405.1</v>
+        <v>4509.5</v>
       </c>
       <c r="D7" t="n">
-        <v>397.15</v>
+        <v>4373</v>
       </c>
       <c r="E7" t="n">
-        <v>402.25</v>
+        <v>4382.1</v>
       </c>
       <c r="F7" t="n">
-        <v>4740939</v>
+        <v>273700</v>
       </c>
       <c r="G7" t="n">
-        <v>9700378</v>
+        <v>567958</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5112624477108005</v>
+        <v>-0.5180981692308234</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7299.5</v>
+        <v>12.04</v>
       </c>
       <c r="C8" t="n">
-        <v>7370</v>
+        <v>12.11</v>
       </c>
       <c r="D8" t="n">
-        <v>7228</v>
+        <v>11.63</v>
       </c>
       <c r="E8" t="n">
-        <v>7315</v>
+        <v>11.99</v>
       </c>
       <c r="F8" t="n">
-        <v>259522</v>
+        <v>919513608</v>
       </c>
       <c r="G8" t="n">
-        <v>606372</v>
+        <v>1860835451</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5720086019803026</v>
+        <v>-0.5058597967349237</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>IDEA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1283.4</v>
+        <v>2256</v>
       </c>
       <c r="C9" t="n">
-        <v>1284.9</v>
+        <v>2289.8</v>
       </c>
       <c r="D9" t="n">
-        <v>1266.8</v>
+        <v>2233</v>
       </c>
       <c r="E9" t="n">
-        <v>1277</v>
+        <v>2251</v>
       </c>
       <c r="F9" t="n">
-        <v>811858</v>
+        <v>1412650</v>
       </c>
       <c r="G9" t="n">
-        <v>1773360</v>
+        <v>3278889</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5421922226733432</v>
+        <v>-0.5691680932169403</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>LUPIN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>COLPAL</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>305.65</v>
+        <v>2139.9</v>
       </c>
       <c r="C10" t="n">
-        <v>306.4</v>
+        <v>2157.2</v>
       </c>
       <c r="D10" t="n">
-        <v>295.9</v>
+        <v>2118</v>
       </c>
       <c r="E10" t="n">
-        <v>297</v>
+        <v>2145</v>
       </c>
       <c r="F10" t="n">
-        <v>32681575</v>
+        <v>299031</v>
       </c>
       <c r="G10" t="n">
-        <v>64690914</v>
+        <v>588255</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4948042471621285</v>
+        <v>-0.4916643292449703</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>COLPAL</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>PPLPHARMA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>130.99</v>
+        <v>184.15</v>
       </c>
       <c r="C11" t="n">
-        <v>132.76</v>
+        <v>184.7</v>
       </c>
       <c r="D11" t="n">
-        <v>130.52</v>
+        <v>175.1</v>
       </c>
       <c r="E11" t="n">
-        <v>131.57</v>
+        <v>178</v>
       </c>
       <c r="F11" t="n">
-        <v>17361170</v>
+        <v>5993063</v>
       </c>
       <c r="G11" t="n">
-        <v>38333083</v>
+        <v>13884083</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5470969553896826</v>
+        <v>-0.568350102775963</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>PPLPHARMA</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>SYNGENE</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>634.75</v>
+        <v>486.25</v>
       </c>
       <c r="C12" t="n">
-        <v>642.5</v>
+        <v>486.25</v>
       </c>
       <c r="D12" t="n">
-        <v>629.15</v>
+        <v>470</v>
       </c>
       <c r="E12" t="n">
-        <v>635</v>
+        <v>477.5</v>
       </c>
       <c r="F12" t="n">
-        <v>3564594</v>
+        <v>2171349</v>
       </c>
       <c r="G12" t="n">
-        <v>7886637</v>
+        <v>5131483</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5480210386252087</v>
+        <v>-0.5768574113954972</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>DIVISLAB</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>6700</v>
-      </c>
-      <c r="C13" t="n">
-        <v>6759</v>
-      </c>
-      <c r="D13" t="n">
-        <v>6675</v>
-      </c>
-      <c r="E13" t="n">
-        <v>6705</v>
-      </c>
-      <c r="F13" t="n">
-        <v>155071</v>
-      </c>
-      <c r="G13" t="n">
-        <v>330052</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-0.530161913880237</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>DIVISLAB</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>BHEL</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>406.1</v>
-      </c>
-      <c r="C14" t="n">
-        <v>408.9</v>
-      </c>
-      <c r="D14" t="n">
-        <v>400.1</v>
-      </c>
-      <c r="E14" t="n">
-        <v>403.5</v>
-      </c>
-      <c r="F14" t="n">
-        <v>17888566</v>
-      </c>
-      <c r="G14" t="n">
-        <v>37208886</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-0.5192394096399446</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>BHEL</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>BHARATFORG</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2009.4</v>
-      </c>
-      <c r="C15" t="n">
-        <v>2044</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1975.1</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1984</v>
-      </c>
-      <c r="F15" t="n">
-        <v>3399059</v>
-      </c>
-      <c r="G15" t="n">
-        <v>7055670</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-0.51825142048877</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>BHARATFORG</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>APLAPOLLO</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1986.8</v>
-      </c>
-      <c r="C16" t="n">
-        <v>2011.7</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1943.4</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1951</v>
-      </c>
-      <c r="F16" t="n">
-        <v>639610</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1360049</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-0.5297154734866171</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>APLAPOLLO</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>ABCAPITAL</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>369</v>
-      </c>
-      <c r="C17" t="n">
-        <v>369.85</v>
-      </c>
-      <c r="D17" t="n">
-        <v>361.35</v>
-      </c>
-      <c r="E17" t="n">
-        <v>362.3</v>
-      </c>
-      <c r="F17" t="n">
-        <v>2976183</v>
-      </c>
-      <c r="G17" t="n">
-        <v>6091049</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-0.511384163877191</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>ABCAPITAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>ASTRAL</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1565.2</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1594.6</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1565.2</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1573</v>
-      </c>
-      <c r="F18" t="n">
-        <v>488596</v>
-      </c>
-      <c r="G18" t="n">
-        <v>984891</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-0.5039085543476385</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>ASTRAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>MPHASIS</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>2199</v>
-      </c>
-      <c r="C19" t="n">
-        <v>2228</v>
-      </c>
-      <c r="D19" t="n">
-        <v>2182.9</v>
-      </c>
-      <c r="E19" t="n">
-        <v>2211.5</v>
-      </c>
-      <c r="F19" t="n">
-        <v>271921</v>
-      </c>
-      <c r="G19" t="n">
-        <v>592910</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-0.5413789613938035</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>MPHASIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>IRCTC</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>566.05</v>
-      </c>
-      <c r="C20" t="n">
-        <v>570.85</v>
-      </c>
-      <c r="D20" t="n">
-        <v>564</v>
-      </c>
-      <c r="E20" t="n">
-        <v>565.45</v>
-      </c>
-      <c r="F20" t="n">
-        <v>675440</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1391332</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-0.5145371485741721</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>IRCTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>PHOENIXLTD</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1840</v>
-      </c>
-      <c r="C21" t="n">
-        <v>1845</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1810.2</v>
-      </c>
-      <c r="E21" t="n">
-        <v>1845</v>
-      </c>
-      <c r="F21" t="n">
-        <v>144521</v>
-      </c>
-      <c r="G21" t="n">
-        <v>323880</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-0.5537822650364332</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>PHOENIXLTD</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>CESC</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>186.46</v>
-      </c>
-      <c r="C22" t="n">
-        <v>187.45</v>
-      </c>
-      <c r="D22" t="n">
-        <v>183.92</v>
-      </c>
-      <c r="E22" t="n">
-        <v>185</v>
-      </c>
-      <c r="F22" t="n">
-        <v>2029703</v>
-      </c>
-      <c r="G22" t="n">
-        <v>4218285</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-0.5188321794283696</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>CESC</t>
+          <t>SYNGENE</t>
         </is>
       </c>
     </row>
@@ -1180,7 +850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1233,198 +903,528 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1740.4</v>
+        <v>1392</v>
       </c>
       <c r="C2" t="n">
-        <v>1792</v>
+        <v>1393.5</v>
       </c>
       <c r="D2" t="n">
-        <v>1727.7</v>
+        <v>1360.3</v>
       </c>
       <c r="E2" t="n">
-        <v>1760</v>
+        <v>1366.5</v>
       </c>
       <c r="F2" t="n">
-        <v>4984856</v>
+        <v>24357500</v>
       </c>
       <c r="G2" t="n">
-        <v>3280485</v>
+        <v>15261787</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5195484813983299</v>
+        <v>0.5959795533773339</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>RELIANCE</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3069</v>
+        <v>971</v>
       </c>
       <c r="C3" t="n">
-        <v>3136</v>
+        <v>979.95</v>
       </c>
       <c r="D3" t="n">
-        <v>3022.4</v>
+        <v>925.95</v>
       </c>
       <c r="E3" t="n">
-        <v>3098</v>
+        <v>933.9</v>
       </c>
       <c r="F3" t="n">
-        <v>3775007</v>
+        <v>8674062</v>
       </c>
       <c r="G3" t="n">
-        <v>2366069</v>
+        <v>5927270</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5954762942247246</v>
+        <v>0.4634160414490988</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1032.4</v>
+        <v>1183</v>
       </c>
       <c r="C4" t="n">
-        <v>1052.3</v>
+        <v>1184</v>
       </c>
       <c r="D4" t="n">
-        <v>1026.3</v>
+        <v>1142.6</v>
       </c>
       <c r="E4" t="n">
-        <v>1051</v>
+        <v>1147</v>
       </c>
       <c r="F4" t="n">
-        <v>2406953</v>
+        <v>3959561</v>
       </c>
       <c r="G4" t="n">
-        <v>1658965</v>
+        <v>2505962</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4508762993794324</v>
+        <v>0.580056281779213</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>HCLTECH</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>981.85</v>
+        <v>10550</v>
       </c>
       <c r="C5" t="n">
-        <v>988.8</v>
+        <v>10684.5</v>
       </c>
       <c r="D5" t="n">
-        <v>973.3</v>
+        <v>10366</v>
       </c>
       <c r="E5" t="n">
-        <v>978</v>
+        <v>10405</v>
       </c>
       <c r="F5" t="n">
-        <v>1597738</v>
+        <v>409439</v>
       </c>
       <c r="G5" t="n">
-        <v>1114882</v>
+        <v>256703</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4331005433758909</v>
+        <v>0.5949910986626569</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PRESTIGE</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1480</v>
+        <v>1262</v>
       </c>
       <c r="C6" t="n">
-        <v>1514.7</v>
+        <v>1272.6</v>
       </c>
       <c r="D6" t="n">
-        <v>1477.8</v>
+        <v>1246.2</v>
       </c>
       <c r="E6" t="n">
-        <v>1495.5</v>
+        <v>1252.2</v>
       </c>
       <c r="F6" t="n">
-        <v>918187</v>
+        <v>1475577</v>
       </c>
       <c r="G6" t="n">
-        <v>616457</v>
+        <v>1023862</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4894583077165155</v>
+        <v>0.4411873865813948</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>PRESTIGE</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>VBL</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1270</v>
+        <v>499</v>
       </c>
       <c r="C7" t="n">
-        <v>1274.4</v>
+        <v>505.65</v>
       </c>
       <c r="D7" t="n">
-        <v>1250.2</v>
+        <v>486.6</v>
       </c>
       <c r="E7" t="n">
-        <v>1261</v>
+        <v>489.7</v>
       </c>
       <c r="F7" t="n">
-        <v>2883848</v>
+        <v>3884745</v>
       </c>
       <c r="G7" t="n">
-        <v>1958453</v>
+        <v>2707721</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4725132540837079</v>
+        <v>0.4346917573856391</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>VBL</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DMART</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4389</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4419.2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4325</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4330</v>
+      </c>
+      <c r="F8" t="n">
+        <v>245222</v>
+      </c>
+      <c r="G8" t="n">
+        <v>165017</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.4860408321566869</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>DMART</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SUZLON</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>53</v>
+      </c>
+      <c r="C9" t="n">
+        <v>53.96</v>
+      </c>
+      <c r="D9" t="n">
+        <v>51.31</v>
+      </c>
+      <c r="E9" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="F9" t="n">
+        <v>99265010</v>
+      </c>
+      <c r="G9" t="n">
+        <v>70005148</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.4179672900627251</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>SUZLON</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1640</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1649.2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1593.9</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1596</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1482394</v>
+      </c>
+      <c r="G10" t="n">
+        <v>968844</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.5300646956579181</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>KPITTECH</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>733</v>
+      </c>
+      <c r="C11" t="n">
+        <v>733</v>
+      </c>
+      <c r="D11" t="n">
+        <v>703.25</v>
+      </c>
+      <c r="E11" t="n">
+        <v>709.6</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2937642</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1990591</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.4757637304699961</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>KPITTECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1486.6</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1504</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1478.6</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1490</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1343339</v>
+      </c>
+      <c r="G12" t="n">
+        <v>925400</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.4516306462070456</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BLUESTARCO</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1651.4</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1699</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1626.2</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1633.9</v>
+      </c>
+      <c r="F13" t="n">
+        <v>949693</v>
+      </c>
+      <c r="G13" t="n">
+        <v>668476</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.4206837642637881</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>BLUESTARCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>HAVELLS</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1225.5</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1231.6</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1187.4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1193.4</v>
+      </c>
+      <c r="F14" t="n">
+        <v>969615</v>
+      </c>
+      <c r="G14" t="n">
+        <v>617476</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.5702877520745746</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>HAVELLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PIIND</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>3088.8</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3088.8</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2991</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2995.3</v>
+      </c>
+      <c r="F15" t="n">
+        <v>166680</v>
+      </c>
+      <c r="G15" t="n">
+        <v>111486</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.4950756148754104</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>PIIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>KAYNES</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>4342.2</v>
+      </c>
+      <c r="C16" t="n">
+        <v>4376</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4020.1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>4068</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1865243</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1189671</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.567864560874393</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>KAYNES</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CROMPTON</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>290</v>
+      </c>
+      <c r="C17" t="n">
+        <v>290.2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>280.3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>285.2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>5419634</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3478542</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.5580188481266002</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>CROMPTON</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,363 +479,330 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13442</v>
+        <v>2306</v>
       </c>
       <c r="C2" t="n">
-        <v>13455</v>
+        <v>2309.2</v>
       </c>
       <c r="D2" t="n">
-        <v>13150</v>
+        <v>2269</v>
       </c>
       <c r="E2" t="n">
-        <v>13188</v>
+        <v>2274</v>
       </c>
       <c r="F2" t="n">
-        <v>302512</v>
+        <v>3171843</v>
       </c>
       <c r="G2" t="n">
-        <v>634354</v>
+        <v>6347884</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5231180066650483</v>
+        <v>-0.5003306613668429</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>TCS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4297.1</v>
+        <v>297</v>
       </c>
       <c r="C3" t="n">
-        <v>4309.1</v>
+        <v>300.2</v>
       </c>
       <c r="D3" t="n">
-        <v>4187.7</v>
+        <v>294.1</v>
       </c>
       <c r="E3" t="n">
-        <v>4228.2</v>
+        <v>297.35</v>
       </c>
       <c r="F3" t="n">
-        <v>758162</v>
+        <v>24381295</v>
       </c>
       <c r="G3" t="n">
-        <v>1791551</v>
+        <v>52080828</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5768124937554108</v>
+        <v>-0.5318566171797422</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>ONGC</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2546.2</v>
+        <v>1321</v>
       </c>
       <c r="C4" t="n">
-        <v>2555.7</v>
+        <v>1328</v>
       </c>
       <c r="D4" t="n">
-        <v>2500</v>
+        <v>1291.4</v>
       </c>
       <c r="E4" t="n">
-        <v>2508</v>
+        <v>1295.5</v>
       </c>
       <c r="F4" t="n">
-        <v>628802</v>
+        <v>2151407</v>
       </c>
       <c r="G4" t="n">
-        <v>1271257</v>
+        <v>4590660</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5053698819357534</v>
+        <v>-0.5313512653953898</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>COFORGE</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>UPL</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6360</v>
+        <v>627</v>
       </c>
       <c r="C5" t="n">
-        <v>6403</v>
+        <v>636.5</v>
       </c>
       <c r="D5" t="n">
-        <v>6171.5</v>
+        <v>624.3</v>
       </c>
       <c r="E5" t="n">
-        <v>6369</v>
+        <v>632.8</v>
       </c>
       <c r="F5" t="n">
-        <v>976463</v>
+        <v>2501012</v>
       </c>
       <c r="G5" t="n">
-        <v>2419336</v>
+        <v>5371994</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5963921505735458</v>
+        <v>-0.5344350719676902</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>UPL</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>127.66</v>
+        <v>4855</v>
       </c>
       <c r="C6" t="n">
-        <v>132.35</v>
+        <v>4914</v>
       </c>
       <c r="D6" t="n">
-        <v>127.43</v>
+        <v>4815.8</v>
       </c>
       <c r="E6" t="n">
-        <v>130.25</v>
+        <v>4848.2</v>
       </c>
       <c r="F6" t="n">
-        <v>29525188</v>
+        <v>310545</v>
       </c>
       <c r="G6" t="n">
-        <v>71593041</v>
+        <v>697635</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5875969565254254</v>
+        <v>-0.5548603496097529</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>KPITTECH</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4509.5</v>
+        <v>711</v>
       </c>
       <c r="C7" t="n">
-        <v>4509.5</v>
+        <v>718.05</v>
       </c>
       <c r="D7" t="n">
-        <v>4373</v>
+        <v>705</v>
       </c>
       <c r="E7" t="n">
-        <v>4382.1</v>
+        <v>710.7</v>
       </c>
       <c r="F7" t="n">
-        <v>273700</v>
+        <v>1300856</v>
       </c>
       <c r="G7" t="n">
-        <v>567958</v>
+        <v>2937642</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5180981692308234</v>
+        <v>-0.5571768105167342</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>KPITTECH</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>BLUESTARCO</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12.04</v>
+        <v>1630.6</v>
       </c>
       <c r="C8" t="n">
-        <v>12.11</v>
+        <v>1662.9</v>
       </c>
       <c r="D8" t="n">
-        <v>11.63</v>
+        <v>1623</v>
       </c>
       <c r="E8" t="n">
-        <v>11.99</v>
+        <v>1635</v>
       </c>
       <c r="F8" t="n">
-        <v>919513608</v>
+        <v>415498</v>
       </c>
       <c r="G8" t="n">
-        <v>1860835451</v>
+        <v>949693</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5058597967349237</v>
+        <v>-0.5624923001433094</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>BLUESTARCO</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2256</v>
+        <v>1869.1</v>
       </c>
       <c r="C9" t="n">
-        <v>2289.8</v>
+        <v>1906.3</v>
       </c>
       <c r="D9" t="n">
-        <v>2233</v>
+        <v>1865.2</v>
       </c>
       <c r="E9" t="n">
-        <v>2251</v>
+        <v>1900.1</v>
       </c>
       <c r="F9" t="n">
-        <v>1412650</v>
+        <v>242539</v>
       </c>
       <c r="G9" t="n">
-        <v>3278889</v>
+        <v>482177</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5691680932169403</v>
+        <v>-0.4969917685829063</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COLPAL</t>
+          <t>ANGELONE</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2139.9</v>
+        <v>300.1</v>
       </c>
       <c r="C10" t="n">
-        <v>2157.2</v>
+        <v>303.4</v>
       </c>
       <c r="D10" t="n">
-        <v>2118</v>
+        <v>297.05</v>
       </c>
       <c r="E10" t="n">
-        <v>2145</v>
+        <v>298</v>
       </c>
       <c r="F10" t="n">
-        <v>299031</v>
+        <v>4043706</v>
       </c>
       <c r="G10" t="n">
-        <v>588255</v>
+        <v>8637203</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4916643292449703</v>
+        <v>-0.5318269120223295</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>COLPAL</t>
+          <t>ANGELONE</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PPLPHARMA</t>
+          <t>NUVAMA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>184.15</v>
+        <v>1541.1</v>
       </c>
       <c r="C11" t="n">
-        <v>184.7</v>
+        <v>1563.6</v>
       </c>
       <c r="D11" t="n">
-        <v>175.1</v>
+        <v>1515.4</v>
       </c>
       <c r="E11" t="n">
-        <v>178</v>
+        <v>1525</v>
       </c>
       <c r="F11" t="n">
-        <v>5993063</v>
+        <v>329597</v>
       </c>
       <c r="G11" t="n">
-        <v>13884083</v>
+        <v>747332</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.568350102775963</v>
+        <v>-0.5589684370534114</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>PPLPHARMA</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>SYNGENE</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>486.25</v>
-      </c>
-      <c r="C12" t="n">
-        <v>486.25</v>
-      </c>
-      <c r="D12" t="n">
-        <v>470</v>
-      </c>
-      <c r="E12" t="n">
-        <v>477.5</v>
-      </c>
-      <c r="F12" t="n">
-        <v>2171349</v>
-      </c>
-      <c r="G12" t="n">
-        <v>5131483</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-0.5768574113954972</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>SYNGENE</t>
+          <t>NUVAMA</t>
         </is>
       </c>
     </row>
@@ -850,7 +817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -903,528 +870,264 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1392</v>
+        <v>4030</v>
       </c>
       <c r="C2" t="n">
-        <v>1393.5</v>
+        <v>4110</v>
       </c>
       <c r="D2" t="n">
-        <v>1360.3</v>
+        <v>3985.1</v>
       </c>
       <c r="E2" t="n">
-        <v>1366.5</v>
+        <v>4079</v>
       </c>
       <c r="F2" t="n">
-        <v>24357500</v>
+        <v>2841521</v>
       </c>
       <c r="G2" t="n">
-        <v>15261787</v>
+        <v>1978748</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5959795533773339</v>
+        <v>0.436019644745061</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>TITAN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>971</v>
+        <v>1392.9</v>
       </c>
       <c r="C3" t="n">
-        <v>979.95</v>
+        <v>1399.9</v>
       </c>
       <c r="D3" t="n">
-        <v>925.95</v>
+        <v>1371.6</v>
       </c>
       <c r="E3" t="n">
-        <v>933.9</v>
+        <v>1375</v>
       </c>
       <c r="F3" t="n">
-        <v>8674062</v>
+        <v>2142904</v>
       </c>
       <c r="G3" t="n">
-        <v>5927270</v>
+        <v>1474910</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4634160414490988</v>
+        <v>0.4529049230122516</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>TECHM</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1183</v>
+        <v>311.95</v>
       </c>
       <c r="C4" t="n">
-        <v>1184</v>
+        <v>325.5</v>
       </c>
       <c r="D4" t="n">
-        <v>1142.6</v>
+        <v>308.8</v>
       </c>
       <c r="E4" t="n">
-        <v>1147</v>
+        <v>323.95</v>
       </c>
       <c r="F4" t="n">
-        <v>3959561</v>
+        <v>72680545</v>
       </c>
       <c r="G4" t="n">
-        <v>2505962</v>
+        <v>47596105</v>
       </c>
       <c r="H4" t="n">
-        <v>0.580056281779213</v>
+        <v>0.5270271590500946</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>VEDL</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>BANKBARODA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10550</v>
+        <v>260.7</v>
       </c>
       <c r="C5" t="n">
-        <v>10684.5</v>
+        <v>264.3</v>
       </c>
       <c r="D5" t="n">
-        <v>10366</v>
+        <v>258.1</v>
       </c>
       <c r="E5" t="n">
-        <v>10405</v>
+        <v>262.3</v>
       </c>
       <c r="F5" t="n">
-        <v>409439</v>
+        <v>14028629</v>
       </c>
       <c r="G5" t="n">
-        <v>256703</v>
+        <v>9935242</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5949910986626569</v>
+        <v>0.4120067734635955</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>BANKBARODA</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>CUMMINSIND</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1262</v>
+        <v>5170</v>
       </c>
       <c r="C6" t="n">
-        <v>1272.6</v>
+        <v>5270</v>
       </c>
       <c r="D6" t="n">
-        <v>1246.2</v>
+        <v>5147.5</v>
       </c>
       <c r="E6" t="n">
-        <v>1252.2</v>
+        <v>5248</v>
       </c>
       <c r="F6" t="n">
-        <v>1475577</v>
+        <v>590903</v>
       </c>
       <c r="G6" t="n">
-        <v>1023862</v>
+        <v>403954</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4411873865813948</v>
+        <v>0.4627977442976181</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>CUMMINSIND</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VBL</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>499</v>
+        <v>102.99</v>
       </c>
       <c r="C7" t="n">
-        <v>505.65</v>
+        <v>103.89</v>
       </c>
       <c r="D7" t="n">
-        <v>486.6</v>
+        <v>101.35</v>
       </c>
       <c r="E7" t="n">
-        <v>489.7</v>
+        <v>102.9</v>
       </c>
       <c r="F7" t="n">
-        <v>3884745</v>
+        <v>23167254</v>
       </c>
       <c r="G7" t="n">
-        <v>2707721</v>
+        <v>14949440</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4346917573856391</v>
+        <v>0.5497071462208618</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>VBL</t>
+          <t>PNB</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>RVNL</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4389</v>
+        <v>283.7</v>
       </c>
       <c r="C8" t="n">
-        <v>4419.2</v>
+        <v>291.35</v>
       </c>
       <c r="D8" t="n">
-        <v>4325</v>
+        <v>283.7</v>
       </c>
       <c r="E8" t="n">
-        <v>4330</v>
+        <v>286.8</v>
       </c>
       <c r="F8" t="n">
-        <v>245222</v>
+        <v>6906724</v>
       </c>
       <c r="G8" t="n">
-        <v>165017</v>
+        <v>4640229</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4860408321566869</v>
+        <v>0.4884446435725478</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>RVNL</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SUZLON</t>
+          <t>IGL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>156.21</v>
       </c>
       <c r="C9" t="n">
-        <v>53.96</v>
+        <v>160.1</v>
       </c>
       <c r="D9" t="n">
-        <v>51.31</v>
+        <v>154.74</v>
       </c>
       <c r="E9" t="n">
-        <v>51.7</v>
+        <v>159.57</v>
       </c>
       <c r="F9" t="n">
-        <v>99265010</v>
+        <v>1499363</v>
       </c>
       <c r="G9" t="n">
-        <v>70005148</v>
+        <v>1033120</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4179672900627251</v>
+        <v>0.4512960740281864</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>SUZLON</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>POLICYBZR</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1640</v>
-      </c>
-      <c r="C10" t="n">
-        <v>1649.2</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1593.9</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1596</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1482394</v>
-      </c>
-      <c r="G10" t="n">
-        <v>968844</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.5300646956579181</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>POLICYBZR</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>KPITTECH</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>733</v>
-      </c>
-      <c r="C11" t="n">
-        <v>733</v>
-      </c>
-      <c r="D11" t="n">
-        <v>703.25</v>
-      </c>
-      <c r="E11" t="n">
-        <v>709.6</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2937642</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1990591</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.4757637304699961</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>KPITTECH</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>AUROPHARMA</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1486.6</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1504</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1478.6</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1490</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1343339</v>
-      </c>
-      <c r="G12" t="n">
-        <v>925400</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.4516306462070456</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>AUROPHARMA</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>BLUESTARCO</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1651.4</v>
-      </c>
-      <c r="C13" t="n">
-        <v>1699</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1626.2</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1633.9</v>
-      </c>
-      <c r="F13" t="n">
-        <v>949693</v>
-      </c>
-      <c r="G13" t="n">
-        <v>668476</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.4206837642637881</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>BLUESTARCO</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>HAVELLS</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1225.5</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1231.6</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1187.4</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1193.4</v>
-      </c>
-      <c r="F14" t="n">
-        <v>969615</v>
-      </c>
-      <c r="G14" t="n">
-        <v>617476</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.5702877520745746</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>HAVELLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>PIIND</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>3088.8</v>
-      </c>
-      <c r="C15" t="n">
-        <v>3088.8</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2991</v>
-      </c>
-      <c r="E15" t="n">
-        <v>2995.3</v>
-      </c>
-      <c r="F15" t="n">
-        <v>166680</v>
-      </c>
-      <c r="G15" t="n">
-        <v>111486</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.4950756148754104</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>PIIND</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>KAYNES</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>4342.2</v>
-      </c>
-      <c r="C16" t="n">
-        <v>4376</v>
-      </c>
-      <c r="D16" t="n">
-        <v>4020.1</v>
-      </c>
-      <c r="E16" t="n">
-        <v>4068</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1865243</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1189671</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.567864560874393</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>KAYNES</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>CROMPTON</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>290</v>
-      </c>
-      <c r="C17" t="n">
-        <v>290.2</v>
-      </c>
-      <c r="D17" t="n">
-        <v>280.3</v>
-      </c>
-      <c r="E17" t="n">
-        <v>285.2</v>
-      </c>
-      <c r="F17" t="n">
-        <v>5419634</v>
-      </c>
-      <c r="G17" t="n">
-        <v>3478542</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.5580188481266002</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>CROMPTON</t>
+          <t>IGL</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,330 +479,297 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2306</v>
+        <v>11600</v>
       </c>
       <c r="C2" t="n">
-        <v>2309.2</v>
+        <v>11769</v>
       </c>
       <c r="D2" t="n">
-        <v>2269</v>
+        <v>11550</v>
       </c>
       <c r="E2" t="n">
-        <v>2274</v>
+        <v>11725</v>
       </c>
       <c r="F2" t="n">
-        <v>3171843</v>
+        <v>220410</v>
       </c>
       <c r="G2" t="n">
-        <v>6347884</v>
+        <v>453482</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5003306613668429</v>
+        <v>-0.513960862834688</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>297</v>
+        <v>674</v>
       </c>
       <c r="C3" t="n">
-        <v>300.2</v>
+        <v>678.25</v>
       </c>
       <c r="D3" t="n">
-        <v>294.1</v>
+        <v>664</v>
       </c>
       <c r="E3" t="n">
-        <v>297.35</v>
+        <v>669</v>
       </c>
       <c r="F3" t="n">
-        <v>24381295</v>
+        <v>6362142</v>
       </c>
       <c r="G3" t="n">
-        <v>52080828</v>
+        <v>12976174</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5318566171797422</v>
+        <v>-0.509705865534787</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>HINDZINC</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>PFC</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1321</v>
+        <v>449.75</v>
       </c>
       <c r="C4" t="n">
-        <v>1328</v>
+        <v>452.95</v>
       </c>
       <c r="D4" t="n">
-        <v>1291.4</v>
+        <v>439.1</v>
       </c>
       <c r="E4" t="n">
-        <v>1295.5</v>
+        <v>451.95</v>
       </c>
       <c r="F4" t="n">
-        <v>2151407</v>
+        <v>6275043</v>
       </c>
       <c r="G4" t="n">
-        <v>4590660</v>
+        <v>12771382</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5313512653953898</v>
+        <v>-0.5086637452391605</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>PFC</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>UPL</t>
+          <t>MUTHOOTFIN</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>627</v>
+        <v>3534</v>
       </c>
       <c r="C5" t="n">
-        <v>636.5</v>
+        <v>3587</v>
       </c>
       <c r="D5" t="n">
-        <v>624.3</v>
+        <v>3497.1</v>
       </c>
       <c r="E5" t="n">
-        <v>632.8</v>
+        <v>3523.5</v>
       </c>
       <c r="F5" t="n">
-        <v>2501012</v>
+        <v>603907</v>
       </c>
       <c r="G5" t="n">
-        <v>5371994</v>
+        <v>1385569</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5344350719676902</v>
+        <v>-0.5641451273808811</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>UPL</t>
+          <t>MUTHOOTFIN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4855</v>
+        <v>926.05</v>
       </c>
       <c r="C6" t="n">
-        <v>4914</v>
+        <v>951.8</v>
       </c>
       <c r="D6" t="n">
-        <v>4815.8</v>
+        <v>921.5</v>
       </c>
       <c r="E6" t="n">
-        <v>4848.2</v>
+        <v>938.75</v>
       </c>
       <c r="F6" t="n">
-        <v>310545</v>
+        <v>1119252</v>
       </c>
       <c r="G6" t="n">
-        <v>697635</v>
+        <v>2370054</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5548603496097529</v>
+        <v>-0.5277525322207849</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>NAUKRI</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KPITTECH</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>711</v>
+        <v>514.4</v>
       </c>
       <c r="C7" t="n">
-        <v>718.05</v>
+        <v>517.75</v>
       </c>
       <c r="D7" t="n">
-        <v>705</v>
+        <v>505.2</v>
       </c>
       <c r="E7" t="n">
-        <v>710.7</v>
+        <v>512.75</v>
       </c>
       <c r="F7" t="n">
-        <v>1300856</v>
+        <v>1810666</v>
       </c>
       <c r="G7" t="n">
-        <v>2937642</v>
+        <v>4110399</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5571768105167342</v>
+        <v>-0.5594914265014175</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>KPITTECH</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BLUESTARCO</t>
+          <t>SRF</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1630.6</v>
+        <v>2714</v>
       </c>
       <c r="C8" t="n">
-        <v>1662.9</v>
+        <v>2739.9</v>
       </c>
       <c r="D8" t="n">
-        <v>1623</v>
+        <v>2664.9</v>
       </c>
       <c r="E8" t="n">
-        <v>1635</v>
+        <v>2729.8</v>
       </c>
       <c r="F8" t="n">
-        <v>415498</v>
+        <v>270823</v>
       </c>
       <c r="G8" t="n">
-        <v>949693</v>
+        <v>642859</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5624923001433094</v>
+        <v>-0.578720994806015</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BLUESTARCO</t>
+          <t>SRF</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>COLPAL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1869.1</v>
+        <v>2134.6</v>
       </c>
       <c r="C9" t="n">
-        <v>1906.3</v>
+        <v>2163.5</v>
       </c>
       <c r="D9" t="n">
-        <v>1865.2</v>
+        <v>2124.7</v>
       </c>
       <c r="E9" t="n">
-        <v>1900.1</v>
+        <v>2141</v>
       </c>
       <c r="F9" t="n">
-        <v>242539</v>
+        <v>144948</v>
       </c>
       <c r="G9" t="n">
-        <v>482177</v>
+        <v>310715</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4969917685829063</v>
+        <v>-0.5335017620649148</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>COLPAL</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ANGELONE</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>300.1</v>
+        <v>128.01</v>
       </c>
       <c r="C10" t="n">
-        <v>303.4</v>
+        <v>129.55</v>
       </c>
       <c r="D10" t="n">
-        <v>297.05</v>
+        <v>126</v>
       </c>
       <c r="E10" t="n">
-        <v>298</v>
+        <v>128.5</v>
       </c>
       <c r="F10" t="n">
-        <v>4043706</v>
+        <v>4182230</v>
       </c>
       <c r="G10" t="n">
-        <v>8637203</v>
+        <v>9296236</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5318269120223295</v>
+        <v>-0.5501157672847377</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ANGELONE</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>NUVAMA</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1541.1</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1563.6</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1515.4</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1525</v>
-      </c>
-      <c r="F11" t="n">
-        <v>329597</v>
-      </c>
-      <c r="G11" t="n">
-        <v>747332</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-0.5589684370534114</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>NUVAMA</t>
+          <t>IEX</t>
         </is>
       </c>
     </row>
@@ -817,7 +784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -870,264 +837,396 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4030</v>
+        <v>1362.2</v>
       </c>
       <c r="C2" t="n">
-        <v>4110</v>
+        <v>1442</v>
       </c>
       <c r="D2" t="n">
-        <v>3985.1</v>
+        <v>1362.2</v>
       </c>
       <c r="E2" t="n">
-        <v>4079</v>
+        <v>1435</v>
       </c>
       <c r="F2" t="n">
-        <v>2841521</v>
+        <v>9166941</v>
       </c>
       <c r="G2" t="n">
-        <v>1978748</v>
+        <v>6015153</v>
       </c>
       <c r="H2" t="n">
-        <v>0.436019644745061</v>
+        <v>0.5239747018903759</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>CIPLA</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1392.9</v>
+        <v>4099.2</v>
       </c>
       <c r="C3" t="n">
-        <v>1399.9</v>
+        <v>4166.5</v>
       </c>
       <c r="D3" t="n">
-        <v>1371.6</v>
+        <v>4099.2</v>
       </c>
       <c r="E3" t="n">
-        <v>1375</v>
+        <v>4131</v>
       </c>
       <c r="F3" t="n">
-        <v>2142904</v>
+        <v>670805</v>
       </c>
       <c r="G3" t="n">
-        <v>1474910</v>
+        <v>454880</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4529049230122516</v>
+        <v>0.4746856313753078</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>TRENT</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>311.95</v>
+        <v>525.4</v>
       </c>
       <c r="C4" t="n">
-        <v>325.5</v>
+        <v>531</v>
       </c>
       <c r="D4" t="n">
-        <v>308.8</v>
+        <v>514.6</v>
       </c>
       <c r="E4" t="n">
-        <v>323.95</v>
+        <v>518</v>
       </c>
       <c r="F4" t="n">
-        <v>72680545</v>
+        <v>15476909</v>
       </c>
       <c r="G4" t="n">
-        <v>47596105</v>
+        <v>10297489</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5270271590500946</v>
+        <v>0.5029789301061647</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>OIL</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>260.7</v>
+        <v>415.95</v>
       </c>
       <c r="C5" t="n">
-        <v>264.3</v>
+        <v>425.1</v>
       </c>
       <c r="D5" t="n">
-        <v>258.1</v>
+        <v>415</v>
       </c>
       <c r="E5" t="n">
-        <v>262.3</v>
+        <v>423.15</v>
       </c>
       <c r="F5" t="n">
-        <v>14028629</v>
+        <v>9290441</v>
       </c>
       <c r="G5" t="n">
-        <v>9935242</v>
+        <v>6032427</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4120067734635955</v>
+        <v>0.5400834523152953</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5170</v>
+        <v>570.25</v>
       </c>
       <c r="C6" t="n">
-        <v>5270</v>
+        <v>580.95</v>
       </c>
       <c r="D6" t="n">
-        <v>5147.5</v>
+        <v>546.8</v>
       </c>
       <c r="E6" t="n">
-        <v>5248</v>
+        <v>562</v>
       </c>
       <c r="F6" t="n">
-        <v>590903</v>
+        <v>5113856</v>
       </c>
       <c r="G6" t="n">
-        <v>403954</v>
+        <v>3207656</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4627977442976181</v>
+        <v>0.5942657192666545</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>102.99</v>
+        <v>2949</v>
       </c>
       <c r="C7" t="n">
-        <v>103.89</v>
+        <v>2976.4</v>
       </c>
       <c r="D7" t="n">
-        <v>101.35</v>
+        <v>2761.9</v>
       </c>
       <c r="E7" t="n">
-        <v>102.9</v>
+        <v>2800</v>
       </c>
       <c r="F7" t="n">
-        <v>23167254</v>
+        <v>878389</v>
       </c>
       <c r="G7" t="n">
-        <v>14949440</v>
+        <v>614500</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5497071462208618</v>
+        <v>0.4294369406021156</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>TIINDIA</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RVNL</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>283.7</v>
+        <v>8930</v>
       </c>
       <c r="C8" t="n">
-        <v>291.35</v>
+        <v>8960</v>
       </c>
       <c r="D8" t="n">
-        <v>283.7</v>
+        <v>8646.5</v>
       </c>
       <c r="E8" t="n">
-        <v>286.8</v>
+        <v>8916</v>
       </c>
       <c r="F8" t="n">
-        <v>6906724</v>
+        <v>169127</v>
       </c>
       <c r="G8" t="n">
-        <v>4640229</v>
+        <v>115580</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4884446435725478</v>
+        <v>0.4632894964526735</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>RVNL</t>
+          <t>OFSS</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IGL</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>156.21</v>
+        <v>346.35</v>
       </c>
       <c r="C9" t="n">
-        <v>160.1</v>
+        <v>353.85</v>
       </c>
       <c r="D9" t="n">
-        <v>154.74</v>
+        <v>345.1</v>
       </c>
       <c r="E9" t="n">
-        <v>159.57</v>
+        <v>352.5</v>
       </c>
       <c r="F9" t="n">
-        <v>1499363</v>
+        <v>4170944</v>
       </c>
       <c r="G9" t="n">
-        <v>1033120</v>
+        <v>2904276</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4512960740281864</v>
+        <v>0.4361389895450708</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>IGL</t>
+          <t>ABCAPITAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>KPITTECH</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>711</v>
+      </c>
+      <c r="C10" t="n">
+        <v>716.7</v>
+      </c>
+      <c r="D10" t="n">
+        <v>693</v>
+      </c>
+      <c r="E10" t="n">
+        <v>705.95</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1986342</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1300856</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.5269499468042581</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>KPITTECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>265</v>
+      </c>
+      <c r="C11" t="n">
+        <v>274</v>
+      </c>
+      <c r="D11" t="n">
+        <v>264.55</v>
+      </c>
+      <c r="E11" t="n">
+        <v>273.55</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4700847</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2963479</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.5862595955631877</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1910</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1912.7</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1840.3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1896</v>
+      </c>
+      <c r="F12" t="n">
+        <v>368390</v>
+      </c>
+      <c r="G12" t="n">
+        <v>242539</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.5188897455666923</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ICICIPRULI</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>542.65</v>
+      </c>
+      <c r="C13" t="n">
+        <v>550.75</v>
+      </c>
+      <c r="D13" t="n">
+        <v>539</v>
+      </c>
+      <c r="E13" t="n">
+        <v>543</v>
+      </c>
+      <c r="F13" t="n">
+        <v>719261</v>
+      </c>
+      <c r="G13" t="n">
+        <v>478716</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.5024795494614761</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ICICIPRULI</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,297 +479,528 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11600</v>
+        <v>773</v>
       </c>
       <c r="C2" t="n">
-        <v>11769</v>
+        <v>781.9</v>
       </c>
       <c r="D2" t="n">
-        <v>11550</v>
+        <v>765.4</v>
       </c>
       <c r="E2" t="n">
-        <v>11725</v>
+        <v>770</v>
       </c>
       <c r="F2" t="n">
-        <v>220410</v>
+        <v>24347873</v>
       </c>
       <c r="G2" t="n">
-        <v>453482</v>
+        <v>50992358</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.513960862834688</v>
+        <v>-0.5225191782658883</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>674</v>
+        <v>3949.4</v>
       </c>
       <c r="C3" t="n">
-        <v>678.25</v>
+        <v>3949.4</v>
       </c>
       <c r="D3" t="n">
-        <v>664</v>
+        <v>3893</v>
       </c>
       <c r="E3" t="n">
-        <v>669</v>
+        <v>3905.1</v>
       </c>
       <c r="F3" t="n">
-        <v>6362142</v>
+        <v>1339185</v>
       </c>
       <c r="G3" t="n">
-        <v>12976174</v>
+        <v>2982228</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.509705865534787</v>
+        <v>-0.5509447969772935</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>LT</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>449.75</v>
+        <v>999.05</v>
       </c>
       <c r="C4" t="n">
-        <v>452.95</v>
+        <v>1018.8</v>
       </c>
       <c r="D4" t="n">
-        <v>439.1</v>
+        <v>993</v>
       </c>
       <c r="E4" t="n">
-        <v>451.95</v>
+        <v>1007.95</v>
       </c>
       <c r="F4" t="n">
-        <v>6275043</v>
+        <v>1996110</v>
       </c>
       <c r="G4" t="n">
-        <v>12771382</v>
+        <v>4595018</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5086637452391605</v>
+        <v>-0.5655925613349067</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3534</v>
+        <v>5372.5</v>
       </c>
       <c r="C5" t="n">
-        <v>3587</v>
+        <v>5420</v>
       </c>
       <c r="D5" t="n">
-        <v>3497.1</v>
+        <v>5365</v>
       </c>
       <c r="E5" t="n">
-        <v>3523.5</v>
+        <v>5409</v>
       </c>
       <c r="F5" t="n">
-        <v>603907</v>
+        <v>151714</v>
       </c>
       <c r="G5" t="n">
-        <v>1385569</v>
+        <v>340218</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5641451273808811</v>
+        <v>-0.5540682738714588</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>DMART</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>926.05</v>
+        <v>4341.4</v>
       </c>
       <c r="C6" t="n">
-        <v>951.8</v>
+        <v>4387</v>
       </c>
       <c r="D6" t="n">
-        <v>921.5</v>
+        <v>4330.3</v>
       </c>
       <c r="E6" t="n">
-        <v>938.75</v>
+        <v>4355</v>
       </c>
       <c r="F6" t="n">
-        <v>1119252</v>
+        <v>145953</v>
       </c>
       <c r="G6" t="n">
-        <v>2370054</v>
+        <v>309428</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5277525322207849</v>
+        <v>-0.5283135333583256</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>DMART</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>514.4</v>
+        <v>25030</v>
       </c>
       <c r="C7" t="n">
-        <v>517.75</v>
+        <v>25385</v>
       </c>
       <c r="D7" t="n">
-        <v>505.2</v>
+        <v>24905</v>
       </c>
       <c r="E7" t="n">
-        <v>512.75</v>
+        <v>24920</v>
       </c>
       <c r="F7" t="n">
-        <v>1810666</v>
+        <v>6055</v>
       </c>
       <c r="G7" t="n">
-        <v>4110399</v>
+        <v>14353</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5594914265014175</v>
+        <v>-0.5781369748484637</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>SHREECEM</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SRF</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2714</v>
+        <v>199.99</v>
       </c>
       <c r="C8" t="n">
-        <v>2739.9</v>
+        <v>200.24</v>
       </c>
       <c r="D8" t="n">
-        <v>2664.9</v>
+        <v>191.55</v>
       </c>
       <c r="E8" t="n">
-        <v>2729.8</v>
+        <v>192.3</v>
       </c>
       <c r="F8" t="n">
-        <v>270823</v>
+        <v>24155534</v>
       </c>
       <c r="G8" t="n">
-        <v>642859</v>
+        <v>50058182</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.578720994806015</v>
+        <v>-0.517450833512092</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>SRF</t>
+          <t>SAIL</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COLPAL</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2134.6</v>
+        <v>2134</v>
       </c>
       <c r="C9" t="n">
-        <v>2163.5</v>
+        <v>2172</v>
       </c>
       <c r="D9" t="n">
-        <v>2124.7</v>
+        <v>2075</v>
       </c>
       <c r="E9" t="n">
-        <v>2141</v>
+        <v>2086</v>
       </c>
       <c r="F9" t="n">
-        <v>144948</v>
+        <v>432690</v>
       </c>
       <c r="G9" t="n">
-        <v>310715</v>
+        <v>852974</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5335017620649148</v>
+        <v>-0.4927277970958083</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>COLPAL</t>
+          <t>MPHASIS</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>FORTIS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>128.01</v>
+        <v>975.5</v>
       </c>
       <c r="C10" t="n">
-        <v>129.55</v>
+        <v>977.45</v>
       </c>
       <c r="D10" t="n">
-        <v>126</v>
+        <v>962</v>
       </c>
       <c r="E10" t="n">
-        <v>128.5</v>
+        <v>962.05</v>
       </c>
       <c r="F10" t="n">
-        <v>4182230</v>
+        <v>736724</v>
       </c>
       <c r="G10" t="n">
-        <v>9296236</v>
+        <v>1823259</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5501157672847377</v>
+        <v>-0.5959301448669663</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>FORTIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BLUESTARCO</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1673.1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1688</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1650</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1654.1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>411996</v>
+      </c>
+      <c r="G11" t="n">
+        <v>817538</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.4960527828675854</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>BLUESTARCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PIIND</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3130</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3148</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3087.1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3119.9</v>
+      </c>
+      <c r="F12" t="n">
+        <v>218651</v>
+      </c>
+      <c r="G12" t="n">
+        <v>489760</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.5535548023521725</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>PIIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DABUR</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>465.3</v>
+      </c>
+      <c r="C13" t="n">
+        <v>471.5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>460.5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>466.05</v>
+      </c>
+      <c r="F13" t="n">
+        <v>932763</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1901251</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.509395129838196</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>DABUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1755</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1764.5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1726.5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1732.6</v>
+      </c>
+      <c r="F14" t="n">
+        <v>173908</v>
+      </c>
+      <c r="G14" t="n">
+        <v>387202</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.5508597579557957</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>JSL</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>749.55</v>
+      </c>
+      <c r="C15" t="n">
+        <v>759.25</v>
+      </c>
+      <c r="D15" t="n">
+        <v>742.9</v>
+      </c>
+      <c r="E15" t="n">
+        <v>750.4</v>
+      </c>
+      <c r="F15" t="n">
+        <v>336372</v>
+      </c>
+      <c r="G15" t="n">
+        <v>820264</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.5899222689280524</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>JSL</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>490.6</v>
+      </c>
+      <c r="C16" t="n">
+        <v>492.5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>482.25</v>
+      </c>
+      <c r="E16" t="n">
+        <v>486</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1195634</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2900617</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.5878001128725371</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CYIENT</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>876.25</v>
+      </c>
+      <c r="C17" t="n">
+        <v>884.75</v>
+      </c>
+      <c r="D17" t="n">
+        <v>869</v>
+      </c>
+      <c r="E17" t="n">
+        <v>870</v>
+      </c>
+      <c r="F17" t="n">
+        <v>122437</v>
+      </c>
+      <c r="G17" t="n">
+        <v>267979</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.5431097212841305</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>CYIENT</t>
         </is>
       </c>
     </row>
@@ -784,7 +1015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -837,396 +1068,165 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1362.2</v>
+        <v>2268</v>
       </c>
       <c r="C2" t="n">
-        <v>1442</v>
+        <v>2299</v>
       </c>
       <c r="D2" t="n">
-        <v>1362.2</v>
+        <v>2254.1</v>
       </c>
       <c r="E2" t="n">
-        <v>1435</v>
+        <v>2283.9</v>
       </c>
       <c r="F2" t="n">
-        <v>9166941</v>
+        <v>2059751</v>
       </c>
       <c r="G2" t="n">
-        <v>6015153</v>
+        <v>1452555</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5239747018903759</v>
+        <v>0.4180192832629401</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>LUPIN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4099.2</v>
+        <v>938</v>
       </c>
       <c r="C3" t="n">
-        <v>4166.5</v>
+        <v>954.9</v>
       </c>
       <c r="D3" t="n">
-        <v>4099.2</v>
+        <v>925.55</v>
       </c>
       <c r="E3" t="n">
-        <v>4131</v>
+        <v>927</v>
       </c>
       <c r="F3" t="n">
-        <v>670805</v>
+        <v>1577568</v>
       </c>
       <c r="G3" t="n">
-        <v>454880</v>
+        <v>1119252</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4746856313753078</v>
+        <v>0.4094841912277128</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>NAUKRI</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>CROMPTON</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>525.4</v>
+        <v>289</v>
       </c>
       <c r="C4" t="n">
-        <v>531</v>
+        <v>310.5</v>
       </c>
       <c r="D4" t="n">
-        <v>514.6</v>
+        <v>284</v>
       </c>
       <c r="E4" t="n">
-        <v>518</v>
+        <v>301.8</v>
       </c>
       <c r="F4" t="n">
-        <v>15476909</v>
+        <v>18051421</v>
       </c>
       <c r="G4" t="n">
-        <v>10297489</v>
+        <v>12392861</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5029789301061647</v>
+        <v>0.4565983593296173</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>CROMPTON</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>INDUSTOWER</t>
+          <t>KFINTECH</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>415.95</v>
+        <v>824</v>
       </c>
       <c r="C5" t="n">
-        <v>425.1</v>
+        <v>828.95</v>
       </c>
       <c r="D5" t="n">
-        <v>415</v>
+        <v>805</v>
       </c>
       <c r="E5" t="n">
-        <v>423.15</v>
+        <v>809.55</v>
       </c>
       <c r="F5" t="n">
-        <v>9290441</v>
+        <v>2022597</v>
       </c>
       <c r="G5" t="n">
-        <v>6032427</v>
+        <v>1404199</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5400834523152953</v>
+        <v>0.4403919957214041</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>INDUSTOWER</t>
+          <t>KFINTECH</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>MANAPPURAM</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>570.25</v>
+        <v>312.05</v>
       </c>
       <c r="C6" t="n">
-        <v>580.95</v>
+        <v>313.65</v>
       </c>
       <c r="D6" t="n">
-        <v>546.8</v>
+        <v>303.5</v>
       </c>
       <c r="E6" t="n">
-        <v>562</v>
+        <v>307.8</v>
       </c>
       <c r="F6" t="n">
-        <v>5113856</v>
+        <v>3966063</v>
       </c>
       <c r="G6" t="n">
-        <v>3207656</v>
+        <v>2552084</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5942657192666545</v>
+        <v>0.5540487695546071</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>TIINDIA</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2949</v>
-      </c>
-      <c r="C7" t="n">
-        <v>2976.4</v>
-      </c>
-      <c r="D7" t="n">
-        <v>2761.9</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2800</v>
-      </c>
-      <c r="F7" t="n">
-        <v>878389</v>
-      </c>
-      <c r="G7" t="n">
-        <v>614500</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.4294369406021156</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>TIINDIA</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>OFSS</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>8930</v>
-      </c>
-      <c r="C8" t="n">
-        <v>8960</v>
-      </c>
-      <c r="D8" t="n">
-        <v>8646.5</v>
-      </c>
-      <c r="E8" t="n">
-        <v>8916</v>
-      </c>
-      <c r="F8" t="n">
-        <v>169127</v>
-      </c>
-      <c r="G8" t="n">
-        <v>115580</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.4632894964526735</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>OFSS</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>ABCAPITAL</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>346.35</v>
-      </c>
-      <c r="C9" t="n">
-        <v>353.85</v>
-      </c>
-      <c r="D9" t="n">
-        <v>345.1</v>
-      </c>
-      <c r="E9" t="n">
-        <v>352.5</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4170944</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2904276</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.4361389895450708</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>ABCAPITAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>KPITTECH</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>711</v>
-      </c>
-      <c r="C10" t="n">
-        <v>716.7</v>
-      </c>
-      <c r="D10" t="n">
-        <v>693</v>
-      </c>
-      <c r="E10" t="n">
-        <v>705.95</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1986342</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1300856</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.5269499468042581</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>KPITTECH</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>NYKAA</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>265</v>
-      </c>
-      <c r="C11" t="n">
-        <v>274</v>
-      </c>
-      <c r="D11" t="n">
-        <v>264.55</v>
-      </c>
-      <c r="E11" t="n">
-        <v>273.55</v>
-      </c>
-      <c r="F11" t="n">
-        <v>4700847</v>
-      </c>
-      <c r="G11" t="n">
-        <v>2963479</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.5862595955631877</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>NYKAA</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>APLAPOLLO</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1910</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1912.7</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1840.3</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1896</v>
-      </c>
-      <c r="F12" t="n">
-        <v>368390</v>
-      </c>
-      <c r="G12" t="n">
-        <v>242539</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.5188897455666923</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>APLAPOLLO</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>ICICIPRULI</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>542.65</v>
-      </c>
-      <c r="C13" t="n">
-        <v>550.75</v>
-      </c>
-      <c r="D13" t="n">
-        <v>539</v>
-      </c>
-      <c r="E13" t="n">
-        <v>543</v>
-      </c>
-      <c r="F13" t="n">
-        <v>719261</v>
-      </c>
-      <c r="G13" t="n">
-        <v>478716</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.5024795494614761</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>ICICIPRULI</t>
+          <t>MANAPPURAM</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,528 +479,264 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>773</v>
+        <v>1785.5</v>
       </c>
       <c r="C2" t="n">
-        <v>781.9</v>
+        <v>1793</v>
       </c>
       <c r="D2" t="n">
-        <v>765.4</v>
+        <v>1745</v>
       </c>
       <c r="E2" t="n">
-        <v>770</v>
+        <v>1784</v>
       </c>
       <c r="F2" t="n">
-        <v>24347873</v>
+        <v>2562978</v>
       </c>
       <c r="G2" t="n">
-        <v>50992358</v>
+        <v>5622212</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5225191782658883</v>
+        <v>-0.5441335189779396</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3949.4</v>
+        <v>1336.5</v>
       </c>
       <c r="C3" t="n">
-        <v>3949.4</v>
+        <v>1341.9</v>
       </c>
       <c r="D3" t="n">
-        <v>3893</v>
+        <v>1322</v>
       </c>
       <c r="E3" t="n">
-        <v>3905.1</v>
+        <v>1330.5</v>
       </c>
       <c r="F3" t="n">
-        <v>1339185</v>
+        <v>1926791</v>
       </c>
       <c r="G3" t="n">
-        <v>2982228</v>
+        <v>3982549</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5509447969772935</v>
+        <v>-0.5161915145300158</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>DRREDDY</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>GRASIM</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>999.05</v>
+        <v>2906</v>
       </c>
       <c r="C4" t="n">
-        <v>1018.8</v>
+        <v>2955.5</v>
       </c>
       <c r="D4" t="n">
-        <v>993</v>
+        <v>2885.2</v>
       </c>
       <c r="E4" t="n">
-        <v>1007.95</v>
+        <v>2955</v>
       </c>
       <c r="F4" t="n">
-        <v>1996110</v>
+        <v>800447</v>
       </c>
       <c r="G4" t="n">
-        <v>4595018</v>
+        <v>1586864</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5655925613349067</v>
+        <v>-0.4955793313100555</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>GRASIM</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5372.5</v>
+        <v>1374.9</v>
       </c>
       <c r="C5" t="n">
-        <v>5420</v>
+        <v>1374.9</v>
       </c>
       <c r="D5" t="n">
-        <v>5365</v>
+        <v>1312.4</v>
       </c>
       <c r="E5" t="n">
-        <v>5409</v>
+        <v>1364</v>
       </c>
       <c r="F5" t="n">
-        <v>151714</v>
+        <v>3820968</v>
       </c>
       <c r="G5" t="n">
-        <v>340218</v>
+        <v>9479876</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5540682738714588</v>
+        <v>-0.5969390316919757</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4341.4</v>
+        <v>2240</v>
       </c>
       <c r="C6" t="n">
-        <v>4387</v>
+        <v>2274.9</v>
       </c>
       <c r="D6" t="n">
-        <v>4330.3</v>
+        <v>2214.1</v>
       </c>
       <c r="E6" t="n">
-        <v>4355</v>
+        <v>2254</v>
       </c>
       <c r="F6" t="n">
-        <v>145953</v>
+        <v>907343</v>
       </c>
       <c r="G6" t="n">
-        <v>309428</v>
+        <v>2059751</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5283135333583256</v>
+        <v>-0.559488986775586</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>LUPIN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>BIOCON</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25030</v>
+        <v>428.45</v>
       </c>
       <c r="C7" t="n">
-        <v>25385</v>
+        <v>431.85</v>
       </c>
       <c r="D7" t="n">
-        <v>24905</v>
+        <v>422.35</v>
       </c>
       <c r="E7" t="n">
-        <v>24920</v>
+        <v>427</v>
       </c>
       <c r="F7" t="n">
-        <v>6055</v>
+        <v>3394086</v>
       </c>
       <c r="G7" t="n">
-        <v>14353</v>
+        <v>8177038</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5781369748484637</v>
+        <v>-0.584924761264409</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>BIOCON</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>PATANJALI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>199.99</v>
+        <v>462.1</v>
       </c>
       <c r="C8" t="n">
-        <v>200.24</v>
+        <v>462.5</v>
       </c>
       <c r="D8" t="n">
-        <v>191.55</v>
+        <v>450.1</v>
       </c>
       <c r="E8" t="n">
-        <v>192.3</v>
+        <v>457.95</v>
       </c>
       <c r="F8" t="n">
-        <v>24155534</v>
+        <v>3139729</v>
       </c>
       <c r="G8" t="n">
-        <v>50058182</v>
+        <v>7192210</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.517450833512092</v>
+        <v>-0.5634542094849845</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>PATANJALI</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>IGL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2134</v>
+        <v>151.95</v>
       </c>
       <c r="C9" t="n">
-        <v>2172</v>
+        <v>152.4</v>
       </c>
       <c r="D9" t="n">
-        <v>2075</v>
+        <v>149.61</v>
       </c>
       <c r="E9" t="n">
-        <v>2086</v>
+        <v>152</v>
       </c>
       <c r="F9" t="n">
-        <v>432690</v>
+        <v>2125723</v>
       </c>
       <c r="G9" t="n">
-        <v>852974</v>
+        <v>5194963</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4927277970958083</v>
+        <v>-0.5908107526463615</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>FORTIS</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>975.5</v>
-      </c>
-      <c r="C10" t="n">
-        <v>977.45</v>
-      </c>
-      <c r="D10" t="n">
-        <v>962</v>
-      </c>
-      <c r="E10" t="n">
-        <v>962.05</v>
-      </c>
-      <c r="F10" t="n">
-        <v>736724</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1823259</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-0.5959301448669663</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>FORTIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>BLUESTARCO</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1673.1</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1688</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1650</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1654.1</v>
-      </c>
-      <c r="F11" t="n">
-        <v>411996</v>
-      </c>
-      <c r="G11" t="n">
-        <v>817538</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-0.4960527828675854</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>BLUESTARCO</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>PIIND</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>3130</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3148</v>
-      </c>
-      <c r="D12" t="n">
-        <v>3087.1</v>
-      </c>
-      <c r="E12" t="n">
-        <v>3119.9</v>
-      </c>
-      <c r="F12" t="n">
-        <v>218651</v>
-      </c>
-      <c r="G12" t="n">
-        <v>489760</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-0.5535548023521725</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>PIIND</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>DABUR</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>465.3</v>
-      </c>
-      <c r="C13" t="n">
-        <v>471.5</v>
-      </c>
-      <c r="D13" t="n">
-        <v>460.5</v>
-      </c>
-      <c r="E13" t="n">
-        <v>466.05</v>
-      </c>
-      <c r="F13" t="n">
-        <v>932763</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1901251</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-0.509395129838196</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>DABUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>PHOENIXLTD</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1755</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1764.5</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1726.5</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1732.6</v>
-      </c>
-      <c r="F14" t="n">
-        <v>173908</v>
-      </c>
-      <c r="G14" t="n">
-        <v>387202</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-0.5508597579557957</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>PHOENIXLTD</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>JSL</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>749.55</v>
-      </c>
-      <c r="C15" t="n">
-        <v>759.25</v>
-      </c>
-      <c r="D15" t="n">
-        <v>742.9</v>
-      </c>
-      <c r="E15" t="n">
-        <v>750.4</v>
-      </c>
-      <c r="F15" t="n">
-        <v>336372</v>
-      </c>
-      <c r="G15" t="n">
-        <v>820264</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-0.5899222689280524</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>JSL</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>PGEL</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>490.6</v>
-      </c>
-      <c r="C16" t="n">
-        <v>492.5</v>
-      </c>
-      <c r="D16" t="n">
-        <v>482.25</v>
-      </c>
-      <c r="E16" t="n">
-        <v>486</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1195634</v>
-      </c>
-      <c r="G16" t="n">
-        <v>2900617</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-0.5878001128725371</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>PGEL</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>CYIENT</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>876.25</v>
-      </c>
-      <c r="C17" t="n">
-        <v>884.75</v>
-      </c>
-      <c r="D17" t="n">
-        <v>869</v>
-      </c>
-      <c r="E17" t="n">
-        <v>870</v>
-      </c>
-      <c r="F17" t="n">
-        <v>122437</v>
-      </c>
-      <c r="G17" t="n">
-        <v>267979</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-0.5431097212841305</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>CYIENT</t>
+          <t>IGL</t>
         </is>
       </c>
     </row>
@@ -1015,7 +751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1068,165 +804,594 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2268</v>
+        <v>238.18</v>
       </c>
       <c r="C2" t="n">
-        <v>2299</v>
+        <v>242.35</v>
       </c>
       <c r="D2" t="n">
-        <v>2254.1</v>
+        <v>233.61</v>
       </c>
       <c r="E2" t="n">
-        <v>2283.9</v>
+        <v>240.81</v>
       </c>
       <c r="F2" t="n">
-        <v>2059751</v>
+        <v>26827499</v>
       </c>
       <c r="G2" t="n">
-        <v>1452555</v>
+        <v>18279677</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4180192832629401</v>
+        <v>0.4676134047663971</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>ETERNAL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>938</v>
+        <v>296.3</v>
       </c>
       <c r="C3" t="n">
-        <v>954.9</v>
+        <v>298.45</v>
       </c>
       <c r="D3" t="n">
-        <v>925.55</v>
+        <v>290.2</v>
       </c>
       <c r="E3" t="n">
-        <v>927</v>
+        <v>296.9</v>
       </c>
       <c r="F3" t="n">
-        <v>1577568</v>
+        <v>16036198</v>
       </c>
       <c r="G3" t="n">
-        <v>1119252</v>
+        <v>10092811</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4094841912277128</v>
+        <v>0.5888733079416626</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>POWERGRID</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CROMPTON</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>289</v>
+        <v>4051</v>
       </c>
       <c r="C4" t="n">
-        <v>310.5</v>
+        <v>4068.7</v>
       </c>
       <c r="D4" t="n">
-        <v>284</v>
+        <v>3980.6</v>
       </c>
       <c r="E4" t="n">
-        <v>301.8</v>
+        <v>4034.7</v>
       </c>
       <c r="F4" t="n">
-        <v>18051421</v>
+        <v>1080689</v>
       </c>
       <c r="G4" t="n">
-        <v>12392861</v>
+        <v>683781</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4565983593296173</v>
+        <v>0.5804607030613603</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CROMPTON</t>
+          <t>TRENT</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KFINTECH</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>824</v>
+        <v>2451</v>
       </c>
       <c r="C5" t="n">
-        <v>828.95</v>
+        <v>2459.3</v>
       </c>
       <c r="D5" t="n">
-        <v>805</v>
+        <v>2385</v>
       </c>
       <c r="E5" t="n">
-        <v>809.55</v>
+        <v>2451.9</v>
       </c>
       <c r="F5" t="n">
-        <v>2022597</v>
+        <v>1052491</v>
       </c>
       <c r="G5" t="n">
-        <v>1404199</v>
+        <v>676811</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4403919957214041</v>
+        <v>0.5550737207285342</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>KFINTECH</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MANAPPURAM</t>
+          <t>GODREJCP</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>312.05</v>
+        <v>1035.5</v>
       </c>
       <c r="C6" t="n">
-        <v>313.65</v>
+        <v>1035.5</v>
       </c>
       <c r="D6" t="n">
-        <v>303.5</v>
+        <v>1001.5</v>
       </c>
       <c r="E6" t="n">
-        <v>307.8</v>
+        <v>1018</v>
       </c>
       <c r="F6" t="n">
-        <v>3966063</v>
+        <v>2367584</v>
       </c>
       <c r="G6" t="n">
-        <v>2552084</v>
+        <v>1585449</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5540487695546071</v>
+        <v>0.4933208195280958</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MANAPPURAM</t>
+          <t>GODREJCP</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6310</v>
+      </c>
+      <c r="C7" t="n">
+        <v>6445</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6225</v>
+      </c>
+      <c r="E7" t="n">
+        <v>6445</v>
+      </c>
+      <c r="F7" t="n">
+        <v>370285</v>
+      </c>
+      <c r="G7" t="n">
+        <v>249403</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.4846854288039839</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>651</v>
+      </c>
+      <c r="C8" t="n">
+        <v>651</v>
+      </c>
+      <c r="D8" t="n">
+        <v>633.4</v>
+      </c>
+      <c r="E8" t="n">
+        <v>647</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3030365</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2003906</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.5122291165354064</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>INDUSTOWER</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>425</v>
+      </c>
+      <c r="C9" t="n">
+        <v>434.55</v>
+      </c>
+      <c r="D9" t="n">
+        <v>421.9</v>
+      </c>
+      <c r="E9" t="n">
+        <v>431.95</v>
+      </c>
+      <c r="F9" t="n">
+        <v>12099517</v>
+      </c>
+      <c r="G9" t="n">
+        <v>7749990</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.5612300144903413</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>INDUSTOWER</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>POLYCAB</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>9170</v>
+      </c>
+      <c r="D10" t="n">
+        <v>8943.5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>9169</v>
+      </c>
+      <c r="F10" t="n">
+        <v>295160</v>
+      </c>
+      <c r="G10" t="n">
+        <v>202982</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.454119084450838</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>POLYCAB</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BANKINDIA</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>141</v>
+      </c>
+      <c r="C11" t="n">
+        <v>141</v>
+      </c>
+      <c r="D11" t="n">
+        <v>137.49</v>
+      </c>
+      <c r="E11" t="n">
+        <v>138.45</v>
+      </c>
+      <c r="F11" t="n">
+        <v>12262451</v>
+      </c>
+      <c r="G11" t="n">
+        <v>8539888</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.4359030235525337</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>BANKINDIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>RVNL</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>280</v>
+      </c>
+      <c r="C12" t="n">
+        <v>280.45</v>
+      </c>
+      <c r="D12" t="n">
+        <v>271.1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>277</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5295517</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3490324</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.517199262876455</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>RVNL</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>272.9</v>
+      </c>
+      <c r="C13" t="n">
+        <v>274.45</v>
+      </c>
+      <c r="D13" t="n">
+        <v>265.85</v>
+      </c>
+      <c r="E13" t="n">
+        <v>273.15</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4619071</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3254422</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.4193214647639427</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>HAVELLS</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1206</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1206</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1176.3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1199.9</v>
+      </c>
+      <c r="F14" t="n">
+        <v>943013</v>
+      </c>
+      <c r="G14" t="n">
+        <v>599340</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.5734190943371041</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>HAVELLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>535</v>
+      </c>
+      <c r="C15" t="n">
+        <v>535.05</v>
+      </c>
+      <c r="D15" t="n">
+        <v>523</v>
+      </c>
+      <c r="E15" t="n">
+        <v>532.25</v>
+      </c>
+      <c r="F15" t="n">
+        <v>753397</v>
+      </c>
+      <c r="G15" t="n">
+        <v>531456</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.4176093599470135</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SUPREMEIND</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3498.4</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3509</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3427.7</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3500</v>
+      </c>
+      <c r="F16" t="n">
+        <v>104903</v>
+      </c>
+      <c r="G16" t="n">
+        <v>68250</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.537040293040293</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>SUPREMEIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>BANDHANBNK</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>192</v>
+      </c>
+      <c r="C17" t="n">
+        <v>192.49</v>
+      </c>
+      <c r="D17" t="n">
+        <v>186.55</v>
+      </c>
+      <c r="E17" t="n">
+        <v>190.42</v>
+      </c>
+      <c r="F17" t="n">
+        <v>7391229</v>
+      </c>
+      <c r="G17" t="n">
+        <v>4906699</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.506354679592125</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>BANDHANBNK</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ABFRL</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>61.95</v>
+      </c>
+      <c r="C18" t="n">
+        <v>62.63</v>
+      </c>
+      <c r="D18" t="n">
+        <v>60.52</v>
+      </c>
+      <c r="E18" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2931446</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1886513</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.553896527614705</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ABFRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CYIENT</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>870.7</v>
+      </c>
+      <c r="C19" t="n">
+        <v>879.4</v>
+      </c>
+      <c r="D19" t="n">
+        <v>856.3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>875.85</v>
+      </c>
+      <c r="F19" t="n">
+        <v>182249</v>
+      </c>
+      <c r="G19" t="n">
+        <v>122437</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.4885124594689514</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>CYIENT</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,264 +479,561 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1785.5</v>
+        <v>210.59</v>
       </c>
       <c r="C2" t="n">
-        <v>1793</v>
+        <v>212.33</v>
       </c>
       <c r="D2" t="n">
-        <v>1745</v>
+        <v>208.9</v>
       </c>
       <c r="E2" t="n">
-        <v>1784</v>
+        <v>209</v>
       </c>
       <c r="F2" t="n">
-        <v>2562978</v>
+        <v>32573663</v>
       </c>
       <c r="G2" t="n">
-        <v>5622212</v>
+        <v>73796001</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5441335189779396</v>
+        <v>-0.5585985343568955</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1336.5</v>
+        <v>4041</v>
       </c>
       <c r="C3" t="n">
-        <v>1341.9</v>
+        <v>4109.7</v>
       </c>
       <c r="D3" t="n">
-        <v>1322</v>
+        <v>4026.1</v>
       </c>
       <c r="E3" t="n">
-        <v>1330.5</v>
+        <v>4073.9</v>
       </c>
       <c r="F3" t="n">
-        <v>1926791</v>
+        <v>518757</v>
       </c>
       <c r="G3" t="n">
-        <v>3982549</v>
+        <v>1080689</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5161915145300158</v>
+        <v>-0.5199756821805348</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>TRENT</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2906</v>
+        <v>603.1</v>
       </c>
       <c r="C4" t="n">
-        <v>2955.5</v>
+        <v>617.5</v>
       </c>
       <c r="D4" t="n">
-        <v>2885.2</v>
+        <v>603.1</v>
       </c>
       <c r="E4" t="n">
-        <v>2955</v>
+        <v>611.25</v>
       </c>
       <c r="F4" t="n">
-        <v>800447</v>
+        <v>1778845</v>
       </c>
       <c r="G4" t="n">
-        <v>1586864</v>
+        <v>3980665</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4955793313100555</v>
+        <v>-0.5531286857849128</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>SOLARINDS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1374.9</v>
+        <v>18100</v>
       </c>
       <c r="C5" t="n">
-        <v>1374.9</v>
+        <v>18498</v>
       </c>
       <c r="D5" t="n">
-        <v>1312.4</v>
+        <v>17918</v>
       </c>
       <c r="E5" t="n">
-        <v>1364</v>
+        <v>18100</v>
       </c>
       <c r="F5" t="n">
-        <v>3820968</v>
+        <v>303361</v>
       </c>
       <c r="G5" t="n">
-        <v>9479876</v>
+        <v>688909</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5969390316919757</v>
+        <v>-0.5596501134402366</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>SOLARINDS</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2240</v>
+        <v>333.7</v>
       </c>
       <c r="C6" t="n">
-        <v>2274.9</v>
+        <v>337.15</v>
       </c>
       <c r="D6" t="n">
-        <v>2214.1</v>
+        <v>332.8</v>
       </c>
       <c r="E6" t="n">
-        <v>2254</v>
+        <v>334.25</v>
       </c>
       <c r="F6" t="n">
-        <v>907343</v>
+        <v>2521354</v>
       </c>
       <c r="G6" t="n">
-        <v>2059751</v>
+        <v>6159707</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.559488986775586</v>
+        <v>-0.5906698159506613</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>RECLTD</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BIOCON</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>428.45</v>
+        <v>432</v>
       </c>
       <c r="C7" t="n">
-        <v>431.85</v>
+        <v>439.4</v>
       </c>
       <c r="D7" t="n">
-        <v>422.35</v>
+        <v>427.25</v>
       </c>
       <c r="E7" t="n">
-        <v>427</v>
+        <v>428.2</v>
       </c>
       <c r="F7" t="n">
-        <v>3394086</v>
+        <v>5642333</v>
       </c>
       <c r="G7" t="n">
-        <v>8177038</v>
+        <v>12099517</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.584924761264409</v>
+        <v>-0.5336728730576601</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>BIOCON</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PATANJALI</t>
+          <t>ICICIPRULI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>462.1</v>
+        <v>515.4</v>
       </c>
       <c r="C8" t="n">
-        <v>462.5</v>
+        <v>526.45</v>
       </c>
       <c r="D8" t="n">
-        <v>450.1</v>
+        <v>515.4</v>
       </c>
       <c r="E8" t="n">
-        <v>457.95</v>
+        <v>523</v>
       </c>
       <c r="F8" t="n">
-        <v>3139729</v>
+        <v>3447305</v>
       </c>
       <c r="G8" t="n">
-        <v>7192210</v>
+        <v>6777357</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5634542094849845</v>
+        <v>-0.4913496514939378</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>PATANJALI</t>
+          <t>ICICIPRULI</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IGL</t>
+          <t>KALYANKJIL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>151.95</v>
+        <v>347.6</v>
       </c>
       <c r="C9" t="n">
-        <v>152.4</v>
+        <v>349.6</v>
       </c>
       <c r="D9" t="n">
-        <v>149.61</v>
+        <v>342.1</v>
       </c>
       <c r="E9" t="n">
-        <v>152</v>
+        <v>344</v>
       </c>
       <c r="F9" t="n">
-        <v>2125723</v>
+        <v>3805361</v>
       </c>
       <c r="G9" t="n">
-        <v>5194963</v>
+        <v>7652972</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5908107526463615</v>
+        <v>-0.5027603655155147</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>IGL</t>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>504</v>
+      </c>
+      <c r="C10" t="n">
+        <v>507.95</v>
+      </c>
+      <c r="D10" t="n">
+        <v>500.8</v>
+      </c>
+      <c r="E10" t="n">
+        <v>502.35</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1657578</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3375155</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.5088883325358391</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EXIDEIND</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>343</v>
+      </c>
+      <c r="C11" t="n">
+        <v>347.9</v>
+      </c>
+      <c r="D11" t="n">
+        <v>342.45</v>
+      </c>
+      <c r="E11" t="n">
+        <v>344</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1238881</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2692440</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.5398668122595118</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>EXIDEIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>549</v>
+      </c>
+      <c r="C12" t="n">
+        <v>550</v>
+      </c>
+      <c r="D12" t="n">
+        <v>541.05</v>
+      </c>
+      <c r="E12" t="n">
+        <v>541.5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>763100</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1750842</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.5641525620244431</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>266</v>
+      </c>
+      <c r="C13" t="n">
+        <v>270</v>
+      </c>
+      <c r="D13" t="n">
+        <v>264.3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>264.5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1410279</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2954216</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.5226215686327608</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>501.95</v>
+      </c>
+      <c r="C14" t="n">
+        <v>510.7</v>
+      </c>
+      <c r="D14" t="n">
+        <v>501</v>
+      </c>
+      <c r="E14" t="n">
+        <v>505.2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>519504</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1078736</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.5184141439610803</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AMBER</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>7158</v>
+      </c>
+      <c r="C15" t="n">
+        <v>7208</v>
+      </c>
+      <c r="D15" t="n">
+        <v>6955</v>
+      </c>
+      <c r="E15" t="n">
+        <v>7115</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1102307</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2162867</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.4903491523057127</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>AMBER</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>DELHIVERY</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>460</v>
+      </c>
+      <c r="C16" t="n">
+        <v>464.55</v>
+      </c>
+      <c r="D16" t="n">
+        <v>449.05</v>
+      </c>
+      <c r="E16" t="n">
+        <v>459.5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3324538</v>
+      </c>
+      <c r="G16" t="n">
+        <v>7347316</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.5475166713940165</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>DELHIVERY</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TITAGARH</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>753.15</v>
+      </c>
+      <c r="C17" t="n">
+        <v>753.15</v>
+      </c>
+      <c r="D17" t="n">
+        <v>735.05</v>
+      </c>
+      <c r="E17" t="n">
+        <v>737.8</v>
+      </c>
+      <c r="F17" t="n">
+        <v>413515</v>
+      </c>
+      <c r="G17" t="n">
+        <v>834082</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.5042274021019516</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>TITAGARH</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ABFRL</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>62.35</v>
+      </c>
+      <c r="C18" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>62.11</v>
+      </c>
+      <c r="E18" t="n">
+        <v>62.47</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1234228</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2931446</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.5789695597326371</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ABFRL</t>
         </is>
       </c>
     </row>
@@ -751,7 +1048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -804,594 +1101,330 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>238.18</v>
+        <v>1238.5</v>
       </c>
       <c r="C2" t="n">
-        <v>242.35</v>
+        <v>1249.8</v>
       </c>
       <c r="D2" t="n">
-        <v>233.61</v>
+        <v>1231.3</v>
       </c>
       <c r="E2" t="n">
-        <v>240.81</v>
+        <v>1237.9</v>
       </c>
       <c r="F2" t="n">
-        <v>26827499</v>
+        <v>9200314</v>
       </c>
       <c r="G2" t="n">
-        <v>18279677</v>
+        <v>6052023</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4676134047663971</v>
+        <v>0.5202047315418332</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>AXISBANK</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>296.3</v>
+        <v>388.5</v>
       </c>
       <c r="C3" t="n">
-        <v>298.45</v>
+        <v>391.8</v>
       </c>
       <c r="D3" t="n">
-        <v>290.2</v>
+        <v>380.25</v>
       </c>
       <c r="E3" t="n">
-        <v>296.9</v>
+        <v>382.4</v>
       </c>
       <c r="F3" t="n">
-        <v>16036198</v>
+        <v>22567886</v>
       </c>
       <c r="G3" t="n">
-        <v>10092811</v>
+        <v>14575831</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5888733079416626</v>
+        <v>0.5483087036341187</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4051</v>
+        <v>11540</v>
       </c>
       <c r="C4" t="n">
-        <v>4068.7</v>
+        <v>11556</v>
       </c>
       <c r="D4" t="n">
-        <v>3980.6</v>
+        <v>11347</v>
       </c>
       <c r="E4" t="n">
-        <v>4034.7</v>
+        <v>11355</v>
       </c>
       <c r="F4" t="n">
-        <v>1080689</v>
+        <v>347784</v>
       </c>
       <c r="G4" t="n">
-        <v>683781</v>
+        <v>233668</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5804607030613603</v>
+        <v>0.4883681120221853</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2451</v>
+        <v>1231</v>
       </c>
       <c r="C5" t="n">
-        <v>2459.3</v>
+        <v>1236.6</v>
       </c>
       <c r="D5" t="n">
-        <v>2385</v>
+        <v>1206.4</v>
       </c>
       <c r="E5" t="n">
-        <v>2451.9</v>
+        <v>1211</v>
       </c>
       <c r="F5" t="n">
-        <v>1052491</v>
+        <v>2163846</v>
       </c>
       <c r="G5" t="n">
-        <v>676811</v>
+        <v>1494098</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5550737207285342</v>
+        <v>0.4482624299075429</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>LODHA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1035.5</v>
+        <v>845.7</v>
       </c>
       <c r="C6" t="n">
-        <v>1035.5</v>
+        <v>904</v>
       </c>
       <c r="D6" t="n">
-        <v>1001.5</v>
+        <v>845.7</v>
       </c>
       <c r="E6" t="n">
-        <v>1018</v>
+        <v>895</v>
       </c>
       <c r="F6" t="n">
-        <v>2367584</v>
+        <v>3657358</v>
       </c>
       <c r="G6" t="n">
-        <v>1585449</v>
+        <v>2353716</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4933208195280958</v>
+        <v>0.5538654621033293</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>LODHA</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6310</v>
+        <v>134.1</v>
       </c>
       <c r="C7" t="n">
-        <v>6445</v>
+        <v>136.19</v>
       </c>
       <c r="D7" t="n">
-        <v>6225</v>
+        <v>133.34</v>
       </c>
       <c r="E7" t="n">
-        <v>6445</v>
+        <v>135.08</v>
       </c>
       <c r="F7" t="n">
-        <v>370285</v>
+        <v>22333093</v>
       </c>
       <c r="G7" t="n">
-        <v>249403</v>
+        <v>15772188</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4846854288039839</v>
+        <v>0.4159793809203897</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>IOC</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>651</v>
+        <v>4155.4</v>
       </c>
       <c r="C8" t="n">
-        <v>651</v>
+        <v>4298.9</v>
       </c>
       <c r="D8" t="n">
-        <v>633.4</v>
+        <v>4119</v>
       </c>
       <c r="E8" t="n">
-        <v>647</v>
+        <v>4198.9</v>
       </c>
       <c r="F8" t="n">
-        <v>3030365</v>
+        <v>7088657</v>
       </c>
       <c r="G8" t="n">
-        <v>2003906</v>
+        <v>5053942</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5122291165354064</v>
+        <v>0.4025995945343259</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>BSE</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>INDUSTOWER</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>425</v>
+        <v>4961.5</v>
       </c>
       <c r="C9" t="n">
-        <v>434.55</v>
+        <v>5187.7</v>
       </c>
       <c r="D9" t="n">
-        <v>421.9</v>
+        <v>4961.5</v>
       </c>
       <c r="E9" t="n">
-        <v>431.95</v>
+        <v>5068</v>
       </c>
       <c r="F9" t="n">
-        <v>12099517</v>
+        <v>912186</v>
       </c>
       <c r="G9" t="n">
-        <v>7749990</v>
+        <v>572955</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5612300144903413</v>
+        <v>0.5920726758645967</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>INDUSTOWER</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9100</v>
+        <v>532.25</v>
       </c>
       <c r="C10" t="n">
-        <v>9170</v>
+        <v>537.6</v>
       </c>
       <c r="D10" t="n">
-        <v>8943.5</v>
+        <v>524.7</v>
       </c>
       <c r="E10" t="n">
-        <v>9169</v>
+        <v>529.4</v>
       </c>
       <c r="F10" t="n">
-        <v>295160</v>
+        <v>1146967</v>
       </c>
       <c r="G10" t="n">
-        <v>202982</v>
+        <v>753397</v>
       </c>
       <c r="H10" t="n">
-        <v>0.454119084450838</v>
+        <v>0.5223939038780351</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>IRCTC</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BANKINDIA</t>
+          <t>JSL</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>141</v>
+        <v>748.5</v>
       </c>
       <c r="C11" t="n">
-        <v>141</v>
+        <v>748.5</v>
       </c>
       <c r="D11" t="n">
-        <v>137.49</v>
+        <v>736.1</v>
       </c>
       <c r="E11" t="n">
-        <v>138.45</v>
+        <v>738.3</v>
       </c>
       <c r="F11" t="n">
-        <v>12262451</v>
+        <v>500400</v>
       </c>
       <c r="G11" t="n">
-        <v>8539888</v>
+        <v>322526</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4359030235525337</v>
+        <v>0.5515028245784835</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>BANKINDIA</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>RVNL</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>280</v>
-      </c>
-      <c r="C12" t="n">
-        <v>280.45</v>
-      </c>
-      <c r="D12" t="n">
-        <v>271.1</v>
-      </c>
-      <c r="E12" t="n">
-        <v>277</v>
-      </c>
-      <c r="F12" t="n">
-        <v>5295517</v>
-      </c>
-      <c r="G12" t="n">
-        <v>3490324</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.517199262876455</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>RVNL</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>NYKAA</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>272.9</v>
-      </c>
-      <c r="C13" t="n">
-        <v>274.45</v>
-      </c>
-      <c r="D13" t="n">
-        <v>265.85</v>
-      </c>
-      <c r="E13" t="n">
-        <v>273.15</v>
-      </c>
-      <c r="F13" t="n">
-        <v>4619071</v>
-      </c>
-      <c r="G13" t="n">
-        <v>3254422</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.4193214647639427</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>NYKAA</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>HAVELLS</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1206</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1206</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1176.3</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1199.9</v>
-      </c>
-      <c r="F14" t="n">
-        <v>943013</v>
-      </c>
-      <c r="G14" t="n">
-        <v>599340</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.5734190943371041</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>HAVELLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>IRCTC</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>535</v>
-      </c>
-      <c r="C15" t="n">
-        <v>535.05</v>
-      </c>
-      <c r="D15" t="n">
-        <v>523</v>
-      </c>
-      <c r="E15" t="n">
-        <v>532.25</v>
-      </c>
-      <c r="F15" t="n">
-        <v>753397</v>
-      </c>
-      <c r="G15" t="n">
-        <v>531456</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.4176093599470135</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>IRCTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>SUPREMEIND</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>3498.4</v>
-      </c>
-      <c r="C16" t="n">
-        <v>3509</v>
-      </c>
-      <c r="D16" t="n">
-        <v>3427.7</v>
-      </c>
-      <c r="E16" t="n">
-        <v>3500</v>
-      </c>
-      <c r="F16" t="n">
-        <v>104903</v>
-      </c>
-      <c r="G16" t="n">
-        <v>68250</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.537040293040293</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>SUPREMEIND</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>BANDHANBNK</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>192</v>
-      </c>
-      <c r="C17" t="n">
-        <v>192.49</v>
-      </c>
-      <c r="D17" t="n">
-        <v>186.55</v>
-      </c>
-      <c r="E17" t="n">
-        <v>190.42</v>
-      </c>
-      <c r="F17" t="n">
-        <v>7391229</v>
-      </c>
-      <c r="G17" t="n">
-        <v>4906699</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.506354679592125</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>BANDHANBNK</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>ABFRL</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>61.95</v>
-      </c>
-      <c r="C18" t="n">
-        <v>62.63</v>
-      </c>
-      <c r="D18" t="n">
-        <v>60.52</v>
-      </c>
-      <c r="E18" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="F18" t="n">
-        <v>2931446</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1886513</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.553896527614705</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>ABFRL</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>CYIENT</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>870.7</v>
-      </c>
-      <c r="C19" t="n">
-        <v>879.4</v>
-      </c>
-      <c r="D19" t="n">
-        <v>856.3</v>
-      </c>
-      <c r="E19" t="n">
-        <v>875.85</v>
-      </c>
-      <c r="F19" t="n">
-        <v>182249</v>
-      </c>
-      <c r="G19" t="n">
-        <v>122437</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.4885124594689514</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>CYIENT</t>
+          <t>JSL</t>
         </is>
       </c>
     </row>

--- a/data/filtered_output.xlsx
+++ b/data/filtered_output.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,462 +479,462 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>210.59</v>
+        <v>1187</v>
       </c>
       <c r="C2" t="n">
-        <v>212.33</v>
+        <v>1206.9</v>
       </c>
       <c r="D2" t="n">
-        <v>208.9</v>
+        <v>1184.9</v>
       </c>
       <c r="E2" t="n">
-        <v>209</v>
+        <v>1190</v>
       </c>
       <c r="F2" t="n">
-        <v>32573663</v>
+        <v>15121010</v>
       </c>
       <c r="G2" t="n">
-        <v>73796001</v>
+        <v>32175705</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5585985343568955</v>
+        <v>-0.5300488365367596</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>INFY</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4041</v>
+        <v>11300</v>
       </c>
       <c r="C3" t="n">
-        <v>4109.7</v>
+        <v>11430</v>
       </c>
       <c r="D3" t="n">
-        <v>4026.1</v>
+        <v>11211</v>
       </c>
       <c r="E3" t="n">
-        <v>4073.9</v>
+        <v>11429</v>
       </c>
       <c r="F3" t="n">
-        <v>518757</v>
+        <v>168245</v>
       </c>
       <c r="G3" t="n">
-        <v>1080689</v>
+        <v>347784</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5199756821805348</v>
+        <v>-0.5162370896878522</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>603.1</v>
+        <v>297.5</v>
       </c>
       <c r="C4" t="n">
-        <v>617.5</v>
+        <v>300.8</v>
       </c>
       <c r="D4" t="n">
-        <v>603.1</v>
+        <v>294.55</v>
       </c>
       <c r="E4" t="n">
-        <v>611.25</v>
+        <v>300.7</v>
       </c>
       <c r="F4" t="n">
-        <v>1778845</v>
+        <v>5672695</v>
       </c>
       <c r="G4" t="n">
-        <v>3980665</v>
+        <v>12580156</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5531286857849128</v>
+        <v>-0.5490759415066077</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>POWERGRID</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SOLARINDS</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18100</v>
+        <v>1860</v>
       </c>
       <c r="C5" t="n">
-        <v>18498</v>
+        <v>1882.4</v>
       </c>
       <c r="D5" t="n">
-        <v>17918</v>
+        <v>1856.1</v>
       </c>
       <c r="E5" t="n">
-        <v>18100</v>
+        <v>1861.1</v>
       </c>
       <c r="F5" t="n">
-        <v>303361</v>
+        <v>563774</v>
       </c>
       <c r="G5" t="n">
-        <v>688909</v>
+        <v>1351813</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5596501134402366</v>
+        <v>-0.5829497127191409</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SOLARINDS</t>
+          <t>SBILIFE</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>333.7</v>
+        <v>3285.4</v>
       </c>
       <c r="C6" t="n">
-        <v>337.15</v>
+        <v>3380.9</v>
       </c>
       <c r="D6" t="n">
-        <v>332.8</v>
+        <v>3232.2</v>
       </c>
       <c r="E6" t="n">
-        <v>334.25</v>
+        <v>3365</v>
       </c>
       <c r="F6" t="n">
-        <v>2521354</v>
+        <v>1265474</v>
       </c>
       <c r="G6" t="n">
-        <v>6159707</v>
+        <v>2484911</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5906698159506613</v>
+        <v>-0.4907366903683875</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>INDUSTOWER</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>432</v>
+        <v>197</v>
       </c>
       <c r="C7" t="n">
-        <v>439.4</v>
+        <v>199.8</v>
       </c>
       <c r="D7" t="n">
-        <v>427.25</v>
+        <v>194.3</v>
       </c>
       <c r="E7" t="n">
-        <v>428.2</v>
+        <v>199.2</v>
       </c>
       <c r="F7" t="n">
-        <v>5642333</v>
+        <v>21709606</v>
       </c>
       <c r="G7" t="n">
-        <v>12099517</v>
+        <v>43235882</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5336728730576601</v>
+        <v>-0.4978798859706389</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>INDUSTOWER</t>
+          <t>SAIL</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ICICIPRULI</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>515.4</v>
+        <v>2200</v>
       </c>
       <c r="C8" t="n">
-        <v>526.45</v>
+        <v>2242</v>
       </c>
       <c r="D8" t="n">
-        <v>515.4</v>
+        <v>2175.2</v>
       </c>
       <c r="E8" t="n">
-        <v>523</v>
+        <v>2240</v>
       </c>
       <c r="F8" t="n">
-        <v>3447305</v>
+        <v>471319</v>
       </c>
       <c r="G8" t="n">
-        <v>6777357</v>
+        <v>1176450</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4913496514939378</v>
+        <v>-0.5993718390071826</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ICICIPRULI</t>
+          <t>MPHASIS</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KALYANKJIL</t>
+          <t>PAGEIND</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>347.6</v>
+        <v>38620</v>
       </c>
       <c r="C9" t="n">
-        <v>349.6</v>
+        <v>38700</v>
       </c>
       <c r="D9" t="n">
-        <v>342.1</v>
+        <v>38020</v>
       </c>
       <c r="E9" t="n">
-        <v>344</v>
+        <v>38350</v>
       </c>
       <c r="F9" t="n">
-        <v>3805361</v>
+        <v>19379</v>
       </c>
       <c r="G9" t="n">
-        <v>7652972</v>
+        <v>47817</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5027603655155147</v>
+        <v>-0.5947257251605078</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>KALYANKJIL</t>
+          <t>PAGEIND</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>DALBHARAT</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>504</v>
+        <v>1713.8</v>
       </c>
       <c r="C10" t="n">
-        <v>507.95</v>
+        <v>1716.7</v>
       </c>
       <c r="D10" t="n">
-        <v>500.8</v>
+        <v>1694.1</v>
       </c>
       <c r="E10" t="n">
-        <v>502.35</v>
+        <v>1709.9</v>
       </c>
       <c r="F10" t="n">
-        <v>1657578</v>
+        <v>165926</v>
       </c>
       <c r="G10" t="n">
-        <v>3375155</v>
+        <v>326085</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5088883325358391</v>
+        <v>-0.4911572136099484</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>DALBHARAT</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EXIDEIND</t>
+          <t>SUPREMEIND</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>343</v>
+        <v>3430</v>
       </c>
       <c r="C11" t="n">
-        <v>347.9</v>
+        <v>3480</v>
       </c>
       <c r="D11" t="n">
-        <v>342.45</v>
+        <v>3400</v>
       </c>
       <c r="E11" t="n">
-        <v>344</v>
+        <v>3468</v>
       </c>
       <c r="F11" t="n">
-        <v>1238881</v>
+        <v>81862</v>
       </c>
       <c r="G11" t="n">
-        <v>2692440</v>
+        <v>168782</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5398668122595118</v>
+        <v>-0.5149838252894265</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>EXIDEIND</t>
+          <t>SUPREMEIND</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>549</v>
+        <v>5437.5</v>
       </c>
       <c r="C12" t="n">
-        <v>550</v>
+        <v>5507.5</v>
       </c>
       <c r="D12" t="n">
-        <v>541.05</v>
+        <v>5416.5</v>
       </c>
       <c r="E12" t="n">
-        <v>541.5</v>
+        <v>5440</v>
       </c>
       <c r="F12" t="n">
-        <v>763100</v>
+        <v>50467</v>
       </c>
       <c r="G12" t="n">
-        <v>1750842</v>
+        <v>105741</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5641525620244431</v>
+        <v>-0.5227300668614823</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>ALKEM</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>266</v>
+        <v>526.05</v>
       </c>
       <c r="C13" t="n">
-        <v>270</v>
+        <v>530.7</v>
       </c>
       <c r="D13" t="n">
-        <v>264.3</v>
+        <v>525.2</v>
       </c>
       <c r="E13" t="n">
-        <v>264.5</v>
+        <v>528.8</v>
       </c>
       <c r="F13" t="n">
-        <v>1410279</v>
+        <v>487397</v>
       </c>
       <c r="G13" t="n">
-        <v>2954216</v>
+        <v>1146967</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.5226215686327608</v>
+        <v>-0.5750557775419868</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>IRCTC</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>AMBER</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>501.95</v>
+        <v>7089</v>
       </c>
       <c r="C14" t="n">
-        <v>510.7</v>
+        <v>7117.5</v>
       </c>
       <c r="D14" t="n">
-        <v>501</v>
+        <v>6938</v>
       </c>
       <c r="E14" t="n">
-        <v>505.2</v>
+        <v>7066</v>
       </c>
       <c r="F14" t="n">
-        <v>519504</v>
+        <v>560508</v>
       </c>
       <c r="G14" t="n">
-        <v>1078736</v>
+        <v>1102307</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5184141439610803</v>
+        <v>-0.4915137071614351</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>AMBER</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>TATATECH</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7158</v>
+        <v>666.85</v>
       </c>
       <c r="C15" t="n">
-        <v>7208</v>
+        <v>679.8</v>
       </c>
       <c r="D15" t="n">
-        <v>6955</v>
+        <v>659.25</v>
       </c>
       <c r="E15" t="n">
-        <v>7115</v>
+        <v>674.95</v>
       </c>
       <c r="F15" t="n">
-        <v>1102307</v>
+        <v>2103852</v>
       </c>
       <c r="G15" t="n">
-        <v>2162867</v>
+        <v>4473149</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.4903491523057127</v>
+        <v>-0.5296709320436229</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>TATATECH</t>
         </is>
       </c>
     </row>
@@ -945,25 +945,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>460</v>
+        <v>456.05</v>
       </c>
       <c r="C16" t="n">
-        <v>464.55</v>
+        <v>459</v>
       </c>
       <c r="D16" t="n">
-        <v>449.05</v>
+        <v>452.1</v>
       </c>
       <c r="E16" t="n">
-        <v>459.5</v>
+        <v>457</v>
       </c>
       <c r="F16" t="n">
+        <v>1487135</v>
+      </c>
+      <c r="G16" t="n">
         <v>3324538</v>
       </c>
-      <c r="G16" t="n">
-        <v>7347316</v>
-      </c>
       <c r="H16" t="n">
-        <v>-0.5475166713940165</v>
+        <v>-0.5526791993353662</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -974,66 +974,99 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TITAGARH</t>
+          <t>SYNGENE</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>753.15</v>
+        <v>471.1</v>
       </c>
       <c r="C17" t="n">
-        <v>753.15</v>
+        <v>475.2</v>
       </c>
       <c r="D17" t="n">
-        <v>735.05</v>
+        <v>461.75</v>
       </c>
       <c r="E17" t="n">
-        <v>737.8</v>
+        <v>467.5</v>
       </c>
       <c r="F17" t="n">
-        <v>413515</v>
+        <v>615295</v>
       </c>
       <c r="G17" t="n">
-        <v>834082</v>
+        <v>1286161</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5042274021019516</v>
+        <v>-0.5216034384497742</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>TITAGARH</t>
+          <t>SYNGENE</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ABFRL</t>
+          <t>NCC</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>62.35</v>
+        <v>148.51</v>
       </c>
       <c r="C18" t="n">
-        <v>63.3</v>
+        <v>148.72</v>
       </c>
       <c r="D18" t="n">
-        <v>62.11</v>
+        <v>145.56</v>
       </c>
       <c r="E18" t="n">
-        <v>62.47</v>
+        <v>146.25</v>
       </c>
       <c r="F18" t="n">
-        <v>1234228</v>
+        <v>1170595</v>
       </c>
       <c r="G18" t="n">
-        <v>2931446</v>
+        <v>2384587</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5789695597326371</v>
+        <v>-0.5090994792808985</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ABFRL</t>
+          <t>NCC</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TATACHEM</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>730</v>
+      </c>
+      <c r="C19" t="n">
+        <v>734.45</v>
+      </c>
+      <c r="D19" t="n">
+        <v>726</v>
+      </c>
+      <c r="E19" t="n">
+        <v>730</v>
+      </c>
+      <c r="F19" t="n">
+        <v>207269</v>
+      </c>
+      <c r="G19" t="n">
+        <v>488761</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.5759297488956771</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>TATACHEM</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1101,330 +1134,396 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1238.5</v>
+        <v>6260</v>
       </c>
       <c r="C2" t="n">
-        <v>1249.8</v>
+        <v>6624</v>
       </c>
       <c r="D2" t="n">
-        <v>1231.3</v>
+        <v>6259.5</v>
       </c>
       <c r="E2" t="n">
-        <v>1237.9</v>
+        <v>6600</v>
       </c>
       <c r="F2" t="n">
-        <v>9200314</v>
+        <v>546490</v>
       </c>
       <c r="G2" t="n">
-        <v>6052023</v>
+        <v>344676</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5202047315418332</v>
+        <v>0.5855179937100349</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>ABB</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>BPCL</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>388.5</v>
+        <v>281.85</v>
       </c>
       <c r="C3" t="n">
-        <v>391.8</v>
+        <v>294.75</v>
       </c>
       <c r="D3" t="n">
-        <v>380.25</v>
+        <v>280.05</v>
       </c>
       <c r="E3" t="n">
-        <v>382.4</v>
+        <v>293.25</v>
       </c>
       <c r="F3" t="n">
-        <v>22567886</v>
+        <v>10290169</v>
       </c>
       <c r="G3" t="n">
-        <v>14575831</v>
+        <v>6955573</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5483087036341187</v>
+        <v>0.4794135580203098</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>BPCL</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>GODREJCP</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11540</v>
+        <v>1016.6</v>
       </c>
       <c r="C4" t="n">
-        <v>11556</v>
+        <v>1025.2</v>
       </c>
       <c r="D4" t="n">
-        <v>11347</v>
+        <v>1006</v>
       </c>
       <c r="E4" t="n">
-        <v>11355</v>
+        <v>1025</v>
       </c>
       <c r="F4" t="n">
-        <v>347784</v>
+        <v>2356818</v>
       </c>
       <c r="G4" t="n">
-        <v>233668</v>
+        <v>1636935</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4883681120221853</v>
+        <v>0.4397749452482841</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>GODREJCP</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1231</v>
+        <v>333.4</v>
       </c>
       <c r="C5" t="n">
-        <v>1236.6</v>
+        <v>335</v>
       </c>
       <c r="D5" t="n">
-        <v>1206.4</v>
+        <v>328.15</v>
       </c>
       <c r="E5" t="n">
-        <v>1211</v>
+        <v>334.25</v>
       </c>
       <c r="F5" t="n">
-        <v>2163846</v>
+        <v>3723835</v>
       </c>
       <c r="G5" t="n">
-        <v>1494098</v>
+        <v>2521354</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4482624299075429</v>
+        <v>0.4769187507981822</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>RECLTD</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LODHA</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>845.7</v>
+        <v>966.9</v>
       </c>
       <c r="C6" t="n">
-        <v>904</v>
+        <v>978.9</v>
       </c>
       <c r="D6" t="n">
-        <v>845.7</v>
+        <v>948</v>
       </c>
       <c r="E6" t="n">
-        <v>895</v>
+        <v>972.3</v>
       </c>
       <c r="F6" t="n">
-        <v>3657358</v>
+        <v>1712145</v>
       </c>
       <c r="G6" t="n">
-        <v>2353716</v>
+        <v>1093206</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5538654621033293</v>
+        <v>0.566168681840385</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>LODHA</t>
+          <t>AUBANK</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>134.1</v>
+        <v>502.6</v>
       </c>
       <c r="C7" t="n">
-        <v>136.19</v>
+        <v>511.95</v>
       </c>
       <c r="D7" t="n">
-        <v>133.34</v>
+        <v>498.75</v>
       </c>
       <c r="E7" t="n">
-        <v>135.08</v>
+        <v>506</v>
       </c>
       <c r="F7" t="n">
-        <v>22333093</v>
+        <v>2349833</v>
       </c>
       <c r="G7" t="n">
-        <v>15772188</v>
+        <v>1657578</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4159793809203897</v>
+        <v>0.4176304222184416</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>OIL</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>SRF</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4155.4</v>
+        <v>2617.2</v>
       </c>
       <c r="C8" t="n">
-        <v>4298.9</v>
+        <v>2622.1</v>
       </c>
       <c r="D8" t="n">
-        <v>4119</v>
+        <v>2590.5</v>
       </c>
       <c r="E8" t="n">
-        <v>4198.9</v>
+        <v>2610.2</v>
       </c>
       <c r="F8" t="n">
-        <v>7088657</v>
+        <v>342170</v>
       </c>
       <c r="G8" t="n">
-        <v>5053942</v>
+        <v>226571</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4025995945343259</v>
+        <v>0.5102109272590049</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>SRF</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>HUDCO</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4961.5</v>
+        <v>199.6</v>
       </c>
       <c r="C9" t="n">
-        <v>5187.7</v>
+        <v>210.7</v>
       </c>
       <c r="D9" t="n">
-        <v>4961.5</v>
+        <v>198.02</v>
       </c>
       <c r="E9" t="n">
-        <v>5068</v>
+        <v>204.9</v>
       </c>
       <c r="F9" t="n">
-        <v>912186</v>
+        <v>3242204</v>
       </c>
       <c r="G9" t="n">
-        <v>572955</v>
+        <v>2281328</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5920726758645967</v>
+        <v>0.4211915165202023</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>HUDCO</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>532.25</v>
+        <v>265.15</v>
       </c>
       <c r="C10" t="n">
-        <v>537.6</v>
+        <v>267.5</v>
       </c>
       <c r="D10" t="n">
-        <v>524.7</v>
+        <v>261.35</v>
       </c>
       <c r="E10" t="n">
-        <v>529.4</v>
+        <v>265.05</v>
       </c>
       <c r="F10" t="n">
-        <v>1146967</v>
+        <v>2022657</v>
       </c>
       <c r="G10" t="n">
-        <v>753397</v>
+        <v>1410279</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5223939038780351</v>
+        <v>0.4342247172368021</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>PETRONET</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>JSL</t>
+          <t>MANAPPURAM</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>748.5</v>
+        <v>313</v>
       </c>
       <c r="C11" t="n">
-        <v>748.5</v>
+        <v>323.8</v>
       </c>
       <c r="D11" t="n">
-        <v>736.1</v>
+        <v>311.4</v>
       </c>
       <c r="E11" t="n">
-        <v>738.3</v>
+        <v>319.45</v>
       </c>
       <c r="F11" t="n">
-        <v>500400</v>
+        <v>4971139</v>
       </c>
       <c r="G11" t="n">
-        <v>322526</v>
+        <v>3193575</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5515028245784835</v>
+        <v>0.5566063111090236</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>JSL</t>
+          <t>MANAPPURAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PNBHOUSING</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1061</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1070</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1054.2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1059.5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1175898</v>
+      </c>
+      <c r="G12" t="n">
+        <v>735303</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.5992019616403034</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>PNBHOUSING</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ABFRL</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>63.21</v>
+      </c>
+      <c r="D13" t="n">
+        <v>61.67</v>
+      </c>
+      <c r="E13" t="n">
+        <v>62.55</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1882031</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1234228</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.5248649358141283</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ABFRL</t>
         </is>
       </c>
     </row>
